--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="729">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,31 +47,31 @@
     <t xml:space="preserve">8.98565769195557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08549976348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24887275695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09457492828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12180423736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03104019165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95388984680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8994312286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89489459991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84951114654541</t>
+    <t xml:space="preserve">9.08549785614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24887371063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09457588195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12180519104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03103923797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95389080047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89943218231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89489364624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84951210021973</t>
   </si>
   <si>
     <t xml:space="preserve">8.85858726501465</t>
@@ -80,16 +80,16 @@
     <t xml:space="preserve">8.87674045562744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.767822265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86766529083252</t>
+    <t xml:space="preserve">8.76782321929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8676643371582</t>
   </si>
   <si>
     <t xml:space="preserve">9.04919242858887</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23072147369385</t>
+    <t xml:space="preserve">9.23072052001953</t>
   </si>
   <si>
     <t xml:space="preserve">9.11272716522217</t>
@@ -101,10 +101,10 @@
     <t xml:space="preserve">8.91304683685303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92212295532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00380992889404</t>
+    <t xml:space="preserve">8.92212200164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00381088256836</t>
   </si>
   <si>
     <t xml:space="preserve">9.15810871124268</t>
@@ -116,37 +116,37 @@
     <t xml:space="preserve">9.43947792053223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54839515686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62100791931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8025369644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71177196502686</t>
+    <t xml:space="preserve">9.54839611053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62100696563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80253601074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71177005767822</t>
   </si>
   <si>
     <t xml:space="preserve">9.56654930114746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58470249176025</t>
+    <t xml:space="preserve">9.58470153808594</t>
   </si>
   <si>
     <t xml:space="preserve">9.57562446594238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53024387359619</t>
+    <t xml:space="preserve">9.53024291992188</t>
   </si>
   <si>
     <t xml:space="preserve">9.50301361083984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60285377502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63915920257568</t>
+    <t xml:space="preserve">9.60285568237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63916015625</t>
   </si>
   <si>
     <t xml:space="preserve">9.79345893859863</t>
@@ -155,94 +155,94 @@
     <t xml:space="preserve">9.95683479309082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93868064880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98406505584717</t>
+    <t xml:space="preserve">9.93868160247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98406410217285</t>
   </si>
   <si>
     <t xml:space="preserve">9.73900032043457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7662296295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74807643890381</t>
+    <t xml:space="preserve">9.76623058319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74807548522949</t>
   </si>
   <si>
     <t xml:space="preserve">9.75715446472168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64823722839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82068824768066</t>
+    <t xml:space="preserve">9.64823627471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82068729400635</t>
   </si>
   <si>
     <t xml:space="preserve">9.70269393920898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72084712982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67546463012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66638851165771</t>
+    <t xml:space="preserve">9.72084617614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67546558380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66638946533203</t>
   </si>
   <si>
     <t xml:space="preserve">9.63008308410645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65731334686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68454265594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81161308288574</t>
+    <t xml:space="preserve">9.65731239318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68454170227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81161403656006</t>
   </si>
   <si>
     <t xml:space="preserve">9.8297643661499</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8479175567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83884143829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72992324829102</t>
+    <t xml:space="preserve">9.84791946411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83884239196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72992420196533</t>
   </si>
   <si>
     <t xml:space="preserve">9.78438282012939</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55747127532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34871387481689</t>
+    <t xml:space="preserve">9.55747222900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34871578216553</t>
   </si>
   <si>
     <t xml:space="preserve">9.33963775634766</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27610301971436</t>
+    <t xml:space="preserve">9.27610397338867</t>
   </si>
   <si>
     <t xml:space="preserve">9.25795078277588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19441604614258</t>
+    <t xml:space="preserve">9.19441509246826</t>
   </si>
   <si>
     <t xml:space="preserve">9.18533897399902</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41225051879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22164440155029</t>
+    <t xml:space="preserve">9.41224956512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22164344787598</t>
   </si>
   <si>
     <t xml:space="preserve">9.31240940093994</t>
@@ -257,16 +257,16 @@
     <t xml:space="preserve">9.28517913818359</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37594413757324</t>
+    <t xml:space="preserve">9.37594509124756</t>
   </si>
   <si>
     <t xml:space="preserve">9.36686611175537</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38502025604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45763111114502</t>
+    <t xml:space="preserve">9.3850212097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45763301849365</t>
   </si>
   <si>
     <t xml:space="preserve">9.39409732818604</t>
@@ -275,13 +275,13 @@
     <t xml:space="preserve">9.48486137390137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49393653869629</t>
+    <t xml:space="preserve">9.49393749237061</t>
   </si>
   <si>
     <t xml:space="preserve">9.44855403900146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47578430175781</t>
+    <t xml:space="preserve">9.4757833480835</t>
   </si>
   <si>
     <t xml:space="preserve">9.23979759216309</t>
@@ -290,55 +290,55 @@
     <t xml:space="preserve">9.14903354644775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21256923675537</t>
+    <t xml:space="preserve">9.21256828308105</t>
   </si>
   <si>
     <t xml:space="preserve">9.20349311828613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13088035583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1399564743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94027423858643</t>
+    <t xml:space="preserve">9.13088130950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13995552062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94027614593506</t>
   </si>
   <si>
     <t xml:space="preserve">8.8041296005249</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75874614715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66798305511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62260055541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53183746337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35030841827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16878032684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98725128173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03263378143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12339782714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25954341888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9418683052063</t>
+    <t xml:space="preserve">8.75874805450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66798210144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62260150909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53183555603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35030746459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16877937316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98725032806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03263282775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12339687347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25954437255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94186878204346</t>
   </si>
   <si>
     <t xml:space="preserve">8.3049259185791</t>
@@ -347,10 +347,10 @@
     <t xml:space="preserve">8.21416091918945</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39568996429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5772180557251</t>
+    <t xml:space="preserve">8.39568901062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57721900939941</t>
   </si>
   <si>
     <t xml:space="preserve">8.71336555480957</t>
@@ -359,31 +359,31 @@
     <t xml:space="preserve">9.53202247619629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25706005096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44036960601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16540813446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07375335693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11957836151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98209857940674</t>
+    <t xml:space="preserve">9.25706100463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44036865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16540622711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07375144958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11957931518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98209953308105</t>
   </si>
   <si>
     <t xml:space="preserve">9.02792549133301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62367725372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80698585510254</t>
+    <t xml:space="preserve">9.62367630004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80698394775391</t>
   </si>
   <si>
     <t xml:space="preserve">9.89863967895508</t>
@@ -392,13 +392,13 @@
     <t xml:space="preserve">9.9902925491333</t>
   </si>
   <si>
-    <t xml:space="preserve">10.173602104187</t>
+    <t xml:space="preserve">10.1736011505127</t>
   </si>
   <si>
     <t xml:space="preserve">10.2652549743652</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3569097518921</t>
+    <t xml:space="preserve">10.3569107055664</t>
   </si>
   <si>
     <t xml:space="preserve">10.5402183532715</t>
@@ -407,13 +407,13 @@
     <t xml:space="preserve">10.631872177124</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8151807785034</t>
+    <t xml:space="preserve">10.8151788711548</t>
   </si>
   <si>
     <t xml:space="preserve">10.7235260009766</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9068326950073</t>
+    <t xml:space="preserve">10.906834602356</t>
   </si>
   <si>
     <t xml:space="preserve">10.9984884262085</t>
@@ -422,31 +422,31 @@
     <t xml:space="preserve">11.090142250061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1817970275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2734508514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4567575454712</t>
+    <t xml:space="preserve">11.1817951202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2734498977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4567584991455</t>
   </si>
   <si>
     <t xml:space="preserve">11.3651037216187</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4485645294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71533203125</t>
+    <t xml:space="preserve">10.4485635757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71533012390137</t>
   </si>
   <si>
     <t xml:space="preserve">8.79879093170166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24886703491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21123313903809</t>
+    <t xml:space="preserve">8.24886608123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2112340927124</t>
   </si>
   <si>
     <t xml:space="preserve">9.30288791656494</t>
@@ -467,55 +467,55 @@
     <t xml:space="preserve">9.57784938812256</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0361194610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94446754455566</t>
+    <t xml:space="preserve">10.0361204147339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94446659088135</t>
   </si>
   <si>
     <t xml:space="preserve">9.82552433013916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73283100128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59379005432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96456432342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9182186126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54744434356689</t>
+    <t xml:space="preserve">9.73283004760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59379196166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96456527709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91821575164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54744338989258</t>
   </si>
   <si>
     <t xml:space="preserve">10.010910987854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1036052703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1499509811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1962985992432</t>
+    <t xml:space="preserve">10.1036043167114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1499519348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1962976455688</t>
   </si>
   <si>
     <t xml:space="preserve">9.77917766571045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87187004089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.057258605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2889928817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4743804931641</t>
+    <t xml:space="preserve">9.87187099456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0572595596313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2889919281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4743785858154</t>
   </si>
   <si>
     <t xml:space="preserve">10.2426452636719</t>
@@ -524,22 +524,22 @@
     <t xml:space="preserve">10.381685256958</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68648242950439</t>
+    <t xml:space="preserve">9.68648338317871</t>
   </si>
   <si>
     <t xml:space="preserve">9.64013576507568</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50109577178955</t>
+    <t xml:space="preserve">9.50109672546387</t>
   </si>
   <si>
     <t xml:space="preserve">9.31570911407471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23228359222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19520664215088</t>
+    <t xml:space="preserve">9.23228549957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1952075958252</t>
   </si>
   <si>
     <t xml:space="preserve">9.25082302093506</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">9.269362449646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21374607086182</t>
+    <t xml:space="preserve">9.2137451171875</t>
   </si>
   <si>
     <t xml:space="preserve">9.04689693450928</t>
@@ -557,13 +557,13 @@
     <t xml:space="preserve">9.12105274200439</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0654354095459</t>
+    <t xml:space="preserve">9.06543636322021</t>
   </si>
   <si>
     <t xml:space="preserve">8.97274303436279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17666912078857</t>
+    <t xml:space="preserve">9.17666816711426</t>
   </si>
   <si>
     <t xml:space="preserve">9.02835941314697</t>
@@ -572,19 +572,19 @@
     <t xml:space="preserve">8.95420360565186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71319961547852</t>
+    <t xml:space="preserve">8.71320056915283</t>
   </si>
   <si>
     <t xml:space="preserve">8.99128150939941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76881694793701</t>
+    <t xml:space="preserve">8.7688159942627</t>
   </si>
   <si>
     <t xml:space="preserve">8.89858818054199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93566608428955</t>
+    <t xml:space="preserve">8.93566513061523</t>
   </si>
   <si>
     <t xml:space="preserve">10.3353385925293</t>
@@ -593,55 +593,55 @@
     <t xml:space="preserve">10.9841947555542</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0305404663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2159280776978</t>
+    <t xml:space="preserve">11.0305414199829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2159290313721</t>
   </si>
   <si>
     <t xml:space="preserve">11.4940099716187</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5403547286987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5867023468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6330499649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7257413864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9111299514771</t>
+    <t xml:space="preserve">11.540355682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5867033004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6330490112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7257423400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9111309051514</t>
   </si>
   <si>
     <t xml:space="preserve">11.9574766159058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1892108917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2819042205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3745985031128</t>
+    <t xml:space="preserve">12.1892118453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2819051742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3745994567871</t>
   </si>
   <si>
     <t xml:space="preserve">12.5136384963989</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3282527923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1428661346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0965166091919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.555121421814</t>
+    <t xml:space="preserve">12.3282518386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1428642272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0965194702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5551204681396</t>
   </si>
   <si>
     <t xml:space="preserve">12.5082750320435</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">12.6488170623779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4614276885986</t>
+    <t xml:space="preserve">12.4614267349243</t>
   </si>
   <si>
     <t xml:space="preserve">12.4145793914795</t>
@@ -659,49 +659,49 @@
     <t xml:space="preserve">12.7425127029419</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6956644058228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2271890640259</t>
+    <t xml:space="preserve">12.6956653594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2271909713745</t>
   </si>
   <si>
     <t xml:space="preserve">12.1803426742554</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3208837509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2740383148193</t>
+    <t xml:space="preserve">12.3208847045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.274037361145</t>
   </si>
   <si>
     <t xml:space="preserve">12.8362064361572</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7893581390381</t>
+    <t xml:space="preserve">12.7893600463867</t>
   </si>
   <si>
     <t xml:space="preserve">12.6019687652588</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9299020767212</t>
+    <t xml:space="preserve">12.9299011230469</t>
   </si>
   <si>
     <t xml:space="preserve">12.8830537796021</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0704431533813</t>
+    <t xml:space="preserve">13.0704441070557</t>
   </si>
   <si>
     <t xml:space="preserve">13.679461479187</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8668508529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0542402267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3353252410889</t>
+    <t xml:space="preserve">13.8668518066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0542411804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3353261947632</t>
   </si>
   <si>
     <t xml:space="preserve">14.5695629119873</t>
@@ -710,7 +710,7 @@
     <t xml:space="preserve">15.2254276275635</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1317329406738</t>
+    <t xml:space="preserve">15.1317319869995</t>
   </si>
   <si>
     <t xml:space="preserve">14.7569532394409</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">15.0380373001099</t>
   </si>
   <si>
-    <t xml:space="preserve">15.178581237793</t>
+    <t xml:space="preserve">15.1785802841187</t>
   </si>
   <si>
     <t xml:space="preserve">15.3191232681274</t>
@@ -728,16 +728,16 @@
     <t xml:space="preserve">14.8974952697754</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4596652984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4128179550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5533599853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0686817169189</t>
+    <t xml:space="preserve">15.4596643447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4128189086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5533609390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0686798095703</t>
   </si>
   <si>
     <t xml:space="preserve">16.8650894165039</t>
@@ -749,7 +749,7 @@
     <t xml:space="preserve">16.7713928222656</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1930236816406</t>
+    <t xml:space="preserve">17.193021774292</t>
   </si>
   <si>
     <t xml:space="preserve">17.0524806976318</t>
@@ -764,7 +764,7 @@
     <t xml:space="preserve">16.6308517456055</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5371551513672</t>
+    <t xml:space="preserve">16.5371570587158</t>
   </si>
   <si>
     <t xml:space="preserve">16.584005355835</t>
@@ -773,10 +773,10 @@
     <t xml:space="preserve">16.2092227935791</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2560729980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1461715698242</t>
+    <t xml:space="preserve">16.2560710906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1461734771729</t>
   </si>
   <si>
     <t xml:space="preserve">16.396614074707</t>
@@ -788,46 +788,46 @@
     <t xml:space="preserve">15.8344440460205</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1155319213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0218353271484</t>
+    <t xml:space="preserve">16.1155300140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0218372344971</t>
   </si>
   <si>
     <t xml:space="preserve">16.1623764038086</t>
   </si>
   <si>
-    <t xml:space="preserve">15.974986076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7407484054565</t>
+    <t xml:space="preserve">15.9749870300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7407493591309</t>
   </si>
   <si>
     <t xml:space="preserve">16.4434604644775</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9119338989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0993251800537</t>
+    <t xml:space="preserve">16.9119358062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0993270874023</t>
   </si>
   <si>
     <t xml:space="preserve">16.677698135376</t>
   </si>
   <si>
-    <t xml:space="preserve">16.818244934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.272274017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.084885597229</t>
+    <t xml:space="preserve">16.8182430267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2722749710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0848846435547</t>
   </si>
   <si>
     <t xml:space="preserve">14.9911909103394</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8037996292114</t>
+    <t xml:space="preserve">14.8038005828857</t>
   </si>
   <si>
     <t xml:space="preserve">14.4758682250977</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">14.288477897644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5227146148682</t>
+    <t xml:space="preserve">14.5227155685425</t>
   </si>
   <si>
     <t xml:space="preserve">13.960545539856</t>
@@ -854,7 +854,7 @@
     <t xml:space="preserve">14.1947832107544</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0073938369751</t>
+    <t xml:space="preserve">14.0073928833008</t>
   </si>
   <si>
     <t xml:space="preserve">13.7263078689575</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">14.1479358673096</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4290199279785</t>
+    <t xml:space="preserve">14.4290208816528</t>
   </si>
   <si>
     <t xml:space="preserve">14.6164102554321</t>
@@ -872,19 +872,19 @@
     <t xml:space="preserve">13.7731561660767</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3515281677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3046817779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3983764648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0235967636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1172914505005</t>
+    <t xml:space="preserve">13.3515291213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3046808242798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3983755111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0235958099365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1172904968262</t>
   </si>
   <si>
     <t xml:space="preserve">12.976749420166</t>
@@ -893,19 +893,19 @@
     <t xml:space="preserve">12.3677320480347</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0866470336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9929533004761</t>
+    <t xml:space="preserve">12.0866460800171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9929513931274</t>
   </si>
   <si>
     <t xml:space="preserve">11.8992576599121</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0397987365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1334934234619</t>
+    <t xml:space="preserve">12.0397996902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1334943771362</t>
   </si>
   <si>
     <t xml:space="preserve">11.4776296615601</t>
@@ -914,19 +914,19 @@
     <t xml:space="preserve">11.2433929443359</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3839340209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6650190353394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4307832717896</t>
+    <t xml:space="preserve">11.3839349746704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6650199890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4307823181152</t>
   </si>
   <si>
     <t xml:space="preserve">10.9623079299927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7280712127686</t>
+    <t xml:space="preserve">10.7280702590942</t>
   </si>
   <si>
     <t xml:space="preserve">11.1965446472168</t>
@@ -935,13 +935,13 @@
     <t xml:space="preserve">11.5713243484497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3370876312256</t>
+    <t xml:space="preserve">11.3370885848999</t>
   </si>
   <si>
     <t xml:space="preserve">11.2902402877808</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7118682861328</t>
+    <t xml:space="preserve">11.7118673324585</t>
   </si>
   <si>
     <t xml:space="preserve">11.7587146759033</t>
@@ -953,19 +953,19 @@
     <t xml:space="preserve">11.0091552734375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46318912506104</t>
+    <t xml:space="preserve">9.46318817138672</t>
   </si>
   <si>
     <t xml:space="preserve">8.33884906768799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57308578491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31074142456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45128345489502</t>
+    <t xml:space="preserve">8.57308673858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31074047088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45128440856934</t>
   </si>
   <si>
     <t xml:space="preserve">8.61993408203125</t>
@@ -983,19 +983,19 @@
     <t xml:space="preserve">8.43254470825195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47002220153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32011127471924</t>
+    <t xml:space="preserve">8.47002124786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32011032104492</t>
   </si>
   <si>
     <t xml:space="preserve">8.20767688751221</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08587265014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78605031967163</t>
+    <t xml:space="preserve">8.0858736038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78604936599731</t>
   </si>
   <si>
     <t xml:space="preserve">7.49559545516968</t>
@@ -1010,37 +1010,37 @@
     <t xml:space="preserve">7.83289623260498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90785312652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50496530532837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37379169464111</t>
+    <t xml:space="preserve">7.9078516960144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50496482849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37379217147827</t>
   </si>
   <si>
     <t xml:space="preserve">7.12081527709961</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28009700775146</t>
+    <t xml:space="preserve">7.28009653091431</t>
   </si>
   <si>
     <t xml:space="preserve">6.98027276992798</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93342542648315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06459856033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0271201133728</t>
+    <t xml:space="preserve">6.93342590332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06459808349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02712059020996</t>
   </si>
   <si>
     <t xml:space="preserve">7.34568309783936</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5424427986145</t>
+    <t xml:space="preserve">7.54244232177734</t>
   </si>
   <si>
     <t xml:space="preserve">8.19830703735352</t>
@@ -1049,28 +1049,28 @@
     <t xml:space="preserve">8.2170467376709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65194320678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46116256713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53747463226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68056106567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77595233917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8427267074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825527191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66148281097412</t>
+    <t xml:space="preserve">8.65194225311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46116161346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53747367858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68056201934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77595138549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84272575378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825622558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6614818572998</t>
   </si>
   <si>
     <t xml:space="preserve">8.49931812286377</t>
@@ -1082,16 +1082,16 @@
     <t xml:space="preserve">8.39438915252686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.604248046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48977947235107</t>
+    <t xml:space="preserve">8.60424900054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48977851867676</t>
   </si>
   <si>
     <t xml:space="preserve">8.29899787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12729454040527</t>
+    <t xml:space="preserve">8.12729358673096</t>
   </si>
   <si>
     <t xml:space="preserve">7.89835643768311</t>
@@ -1112,19 +1112,19 @@
     <t xml:space="preserve">8.06052017211914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07959938049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07005882263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92697429656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98420858383179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30853652954102</t>
+    <t xml:space="preserve">8.07959842681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07005977630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92697334289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98420810699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30853748321533</t>
   </si>
   <si>
     <t xml:space="preserve">8.26084136962891</t>
@@ -1133,13 +1133,13 @@
     <t xml:space="preserve">8.27038097381592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18452835083008</t>
+    <t xml:space="preserve">8.18452930450439</t>
   </si>
   <si>
     <t xml:space="preserve">8.03190326690674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96513080596924</t>
+    <t xml:space="preserve">7.96512985229492</t>
   </si>
   <si>
     <t xml:space="preserve">7.86019992828369</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">7.91743516921997</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76481008529663</t>
+    <t xml:space="preserve">7.76480960845947</t>
   </si>
   <si>
     <t xml:space="preserve">7.72665309906006</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">7.63126230239868</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65987968444824</t>
+    <t xml:space="preserve">7.65987873077393</t>
   </si>
   <si>
     <t xml:space="preserve">8.16545104980469</t>
@@ -1175,22 +1175,22 @@
     <t xml:space="preserve">8.32761383056641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11775588989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93651247024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19406795501709</t>
+    <t xml:space="preserve">8.11775493621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9365119934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19406890869141</t>
   </si>
   <si>
     <t xml:space="preserve">8.2322244644165</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31807518005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15591144561768</t>
+    <t xml:space="preserve">8.31807708740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15591239929199</t>
   </si>
   <si>
     <t xml:space="preserve">8.22268486022949</t>
@@ -1199,16 +1199,16 @@
     <t xml:space="preserve">8.25130176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35623168945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24176406860352</t>
+    <t xml:space="preserve">8.35623264312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2417631149292</t>
   </si>
   <si>
     <t xml:space="preserve">8.34669303894043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95559167861938</t>
+    <t xml:space="preserve">7.95559072494507</t>
   </si>
   <si>
     <t xml:space="preserve">7.77434825897217</t>
@@ -1220,10 +1220,10 @@
     <t xml:space="preserve">7.97466850280762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01282596588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05098152160645</t>
+    <t xml:space="preserve">8.01282501220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05098056793213</t>
   </si>
   <si>
     <t xml:space="preserve">7.67895746231079</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">7.73619174957275</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69803524017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51679372787476</t>
+    <t xml:space="preserve">7.6980357170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5167932510376</t>
   </si>
   <si>
     <t xml:space="preserve">7.59310626983643</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">7.62172269821167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52633190155029</t>
+    <t xml:space="preserve">7.52633237838745</t>
   </si>
   <si>
     <t xml:space="preserve">7.34508991241455</t>
@@ -1262,25 +1262,25 @@
     <t xml:space="preserve">7.18292570114136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14476871490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12569046020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23062133789062</t>
+    <t xml:space="preserve">7.14476919174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12569093704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23062086105347</t>
   </si>
   <si>
     <t xml:space="preserve">7.1543083190918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24969863891602</t>
+    <t xml:space="preserve">7.24969911575317</t>
   </si>
   <si>
     <t xml:space="preserve">7.24016046524048</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46909809112549</t>
+    <t xml:space="preserve">7.46909761428833</t>
   </si>
   <si>
     <t xml:space="preserve">7.41186332702637</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">7.45001983642578</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28785514831543</t>
+    <t xml:space="preserve">7.28785562515259</t>
   </si>
   <si>
     <t xml:space="preserve">7.39278507232666</t>
@@ -1304,25 +1304,25 @@
     <t xml:space="preserve">7.90789556503296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94605159759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45955896377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70757484436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8792781829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99374771118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75527000427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81250381469727</t>
+    <t xml:space="preserve">7.94605112075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45955848693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70757436752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87927865982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99374723434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75527048110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81250476837158</t>
   </si>
   <si>
     <t xml:space="preserve">7.79342699050903</t>
@@ -1331,16 +1331,16 @@
     <t xml:space="preserve">7.80296611785889</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85065984725952</t>
+    <t xml:space="preserve">7.85066032409668</t>
   </si>
   <si>
     <t xml:space="preserve">7.74573087692261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83158302307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66941785812378</t>
+    <t xml:space="preserve">7.83158254623413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66941833496094</t>
   </si>
   <si>
     <t xml:space="preserve">7.60264492034912</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">7.58356666564941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88881826400757</t>
+    <t xml:space="preserve">7.88881778717041</t>
   </si>
   <si>
     <t xml:space="preserve">8.00328636169434</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">7.27831649780273</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08753490447998</t>
+    <t xml:space="preserve">7.08753442764282</t>
   </si>
   <si>
     <t xml:space="preserve">7.05891799926758</t>
@@ -1376,10 +1376,10 @@
     <t xml:space="preserve">7.50372648239136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98721408843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02589225769043</t>
+    <t xml:space="preserve">7.98721361160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02589321136475</t>
   </si>
   <si>
     <t xml:space="preserve">8.04523086547852</t>
@@ -1391,25 +1391,25 @@
     <t xml:space="preserve">8.07424163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12258911132812</t>
+    <t xml:space="preserve">8.12259006500244</t>
   </si>
   <si>
     <t xml:space="preserve">8.05490112304688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94853496551514</t>
+    <t xml:space="preserve">7.94853448867798</t>
   </si>
   <si>
     <t xml:space="preserve">8.06457138061523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08390998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97754430770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93886518478394</t>
+    <t xml:space="preserve">8.08391094207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97754383087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93886423110962</t>
   </si>
   <si>
     <t xml:space="preserve">7.79381895065308</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">7.68745088577271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63910293579102</t>
+    <t xml:space="preserve">7.63910245895386</t>
   </si>
   <si>
     <t xml:space="preserve">7.73579978942871</t>
@@ -1436,10 +1436,10 @@
     <t xml:space="preserve">7.90985584259033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85183668136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83249759674072</t>
+    <t xml:space="preserve">7.85183715820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83249807357788</t>
   </si>
   <si>
     <t xml:space="preserve">7.81315755844116</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">7.80348825454712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78414916992188</t>
+    <t xml:space="preserve">7.78414869308472</t>
   </si>
   <si>
     <t xml:space="preserve">7.6681113243103</t>
@@ -1460,13 +1460,13 @@
     <t xml:space="preserve">7.71646022796631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75513982772827</t>
+    <t xml:space="preserve">7.75514030456543</t>
   </si>
   <si>
     <t xml:space="preserve">7.74547004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86150693893433</t>
+    <t xml:space="preserve">7.86150646209717</t>
   </si>
   <si>
     <t xml:space="preserve">7.89051580429077</t>
@@ -1484,10 +1484,10 @@
     <t xml:space="preserve">8.09358024597168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13225936889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1515998840332</t>
+    <t xml:space="preserve">8.1322603225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15159893035889</t>
   </si>
   <si>
     <t xml:space="preserve">8.1129207611084</t>
@@ -1496,10 +1496,10 @@
     <t xml:space="preserve">8.03556251525879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92919492721558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69712066650391</t>
+    <t xml:space="preserve">7.92919540405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69712114334106</t>
   </si>
   <si>
     <t xml:space="preserve">7.60042381286621</t>
@@ -1508,10 +1508,10 @@
     <t xml:space="preserve">7.88084602355957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55207443237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40702819824219</t>
+    <t xml:space="preserve">7.55207490921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40702867507935</t>
   </si>
   <si>
     <t xml:space="preserve">7.34900999069214</t>
@@ -1520,16 +1520,16 @@
     <t xml:space="preserve">7.37801933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43603754043579</t>
+    <t xml:space="preserve">7.43603801727295</t>
   </si>
   <si>
     <t xml:space="preserve">7.41669797897339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52306604385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36834955215454</t>
+    <t xml:space="preserve">7.5230655670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36834907531738</t>
   </si>
   <si>
     <t xml:space="preserve">7.542405128479</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">7.4843864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70679044723511</t>
+    <t xml:space="preserve">7.70679092407227</t>
   </si>
   <si>
     <t xml:space="preserve">7.64877223968506</t>
@@ -1556,10 +1556,10 @@
     <t xml:space="preserve">7.59075355529785</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95820426940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96787405014038</t>
+    <t xml:space="preserve">7.95820331573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96787357330322</t>
   </si>
   <si>
     <t xml:space="preserve">7.90018606185913</t>
@@ -1577,10 +1577,10 @@
     <t xml:space="preserve">8.19027900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29664611816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45136165618896</t>
+    <t xml:space="preserve">8.29664516448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45136070251465</t>
   </si>
   <si>
     <t xml:space="preserve">8.48037147521973</t>
@@ -1607,19 +1607,19 @@
     <t xml:space="preserve">8.50938034057617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4223518371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54805946350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55772972106934</t>
+    <t xml:space="preserve">8.42235279083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54805850982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55772876739502</t>
   </si>
   <si>
     <t xml:space="preserve">8.52871990203857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68343448638916</t>
+    <t xml:space="preserve">8.68343544006348</t>
   </si>
   <si>
     <t xml:space="preserve">8.76079368591309</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">8.65442562103271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75112438201904</t>
+    <t xml:space="preserve">8.75112342834473</t>
   </si>
   <si>
     <t xml:space="preserve">8.70277500152588</t>
@@ -1652,10 +1652,10 @@
     <t xml:space="preserve">8.63508701324463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32565402984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31598472595215</t>
+    <t xml:space="preserve">8.32565498352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31598567962646</t>
   </si>
   <si>
     <t xml:space="preserve">8.30631542205811</t>
@@ -2196,6 +2196,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.19999980926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15999984741211</t>
   </si>
 </sst>
 </file>
@@ -61892,7 +61895,7 @@
     </row>
     <row r="2284">
       <c r="A2284" s="1" t="n">
-        <v>45943.6455787037</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2284" t="n">
         <v>16564</v>
@@ -61913,6 +61916,32 @@
         <v>727</v>
       </c>
       <c r="H2284" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2285">
+      <c r="A2285" s="1" t="n">
+        <v>45944.6437731481</v>
+      </c>
+      <c r="B2285" t="n">
+        <v>24887</v>
+      </c>
+      <c r="C2285" t="n">
+        <v>9.18000030517578</v>
+      </c>
+      <c r="D2285" t="n">
+        <v>8.96000003814697</v>
+      </c>
+      <c r="E2285" t="n">
+        <v>9.07999992370605</v>
+      </c>
+      <c r="F2285" t="n">
+        <v>9.15999984741211</v>
+      </c>
+      <c r="G2285" t="s">
+        <v>728</v>
+      </c>
+      <c r="H2285" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="732">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,58 +38,58 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07642364501953</t>
+    <t xml:space="preserve">9.0764217376709</t>
   </si>
   <si>
     <t xml:space="preserve">FF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98565769195557</t>
+    <t xml:space="preserve">8.98565673828125</t>
   </si>
   <si>
     <t xml:space="preserve">9.08549880981445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24887371063232</t>
+    <t xml:space="preserve">9.24887275695801</t>
   </si>
   <si>
     <t xml:space="preserve">9.09457492828369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12180328369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03104019165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95388889312744</t>
+    <t xml:space="preserve">9.12180519104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03103923797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95389080047607</t>
   </si>
   <si>
     <t xml:space="preserve">8.89943218231201</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89489364624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84951114654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85858726501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87673950195312</t>
+    <t xml:space="preserve">8.89489269256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84951019287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85858821868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87674140930176</t>
   </si>
   <si>
     <t xml:space="preserve">8.76782321929932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86766529083252</t>
+    <t xml:space="preserve">8.86766338348389</t>
   </si>
   <si>
     <t xml:space="preserve">9.04919242858887</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23072147369385</t>
+    <t xml:space="preserve">9.23072052001953</t>
   </si>
   <si>
     <t xml:space="preserve">9.11272716522217</t>
@@ -101,64 +101,64 @@
     <t xml:space="preserve">8.91304588317871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92212200164795</t>
+    <t xml:space="preserve">8.92212295532227</t>
   </si>
   <si>
     <t xml:space="preserve">9.00380992889404</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15810966491699</t>
+    <t xml:space="preserve">9.15810871124268</t>
   </si>
   <si>
     <t xml:space="preserve">9.16718673706055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43947792053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54839611053467</t>
+    <t xml:space="preserve">9.43947887420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54839515686035</t>
   </si>
   <si>
     <t xml:space="preserve">9.62100791931152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80253505706787</t>
+    <t xml:space="preserve">9.80253601074219</t>
   </si>
   <si>
     <t xml:space="preserve">9.71177196502686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56654834747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58470249176025</t>
+    <t xml:space="preserve">9.56654930114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58470153808594</t>
   </si>
   <si>
     <t xml:space="preserve">9.5756254196167</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53024196624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50301361083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60285377502441</t>
+    <t xml:space="preserve">9.53024291992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50301456451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60285472869873</t>
   </si>
   <si>
     <t xml:space="preserve">9.63916015625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79345798492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95683479309082</t>
+    <t xml:space="preserve">9.79345893859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95683574676514</t>
   </si>
   <si>
     <t xml:space="preserve">9.93868160247803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98406410217285</t>
+    <t xml:space="preserve">9.98406505584717</t>
   </si>
   <si>
     <t xml:space="preserve">9.73900032043457</t>
@@ -167,34 +167,34 @@
     <t xml:space="preserve">9.7662296295166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74807739257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75715351104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64823627471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82068824768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70269584655762</t>
+    <t xml:space="preserve">9.74807643890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75715446472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64823532104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82068729400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7026948928833</t>
   </si>
   <si>
     <t xml:space="preserve">9.72084712982178</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67546463012695</t>
+    <t xml:space="preserve">9.67546558380127</t>
   </si>
   <si>
     <t xml:space="preserve">9.66638946533203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63008403778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65731239318848</t>
+    <t xml:space="preserve">9.63008308410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65731334686279</t>
   </si>
   <si>
     <t xml:space="preserve">9.68454170227051</t>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">9.81161212921143</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82976531982422</t>
+    <t xml:space="preserve">9.8297643661499</t>
   </si>
   <si>
     <t xml:space="preserve">9.84791946411133</t>
@@ -212,55 +212,55 @@
     <t xml:space="preserve">9.83884143829346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72992515563965</t>
+    <t xml:space="preserve">9.7299222946167</t>
   </si>
   <si>
     <t xml:space="preserve">9.78438282012939</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55747222900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34871578216553</t>
+    <t xml:space="preserve">9.55747127532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34871482849121</t>
   </si>
   <si>
     <t xml:space="preserve">9.33963775634766</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27610301971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25794982910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19441604614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18533897399902</t>
+    <t xml:space="preserve">9.27610397338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25795078277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19441413879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18533802032471</t>
   </si>
   <si>
     <t xml:space="preserve">9.41224956512451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22164440155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31240844726562</t>
+    <t xml:space="preserve">9.22164535522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31240940093994</t>
   </si>
   <si>
     <t xml:space="preserve">9.26702690124512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29425525665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28518009185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37594413757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.366868019104</t>
+    <t xml:space="preserve">9.29425621032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28517818450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37594223022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36686706542969</t>
   </si>
   <si>
     <t xml:space="preserve">9.38501930236816</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">9.39409732818604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48486042022705</t>
+    <t xml:space="preserve">9.48486137390137</t>
   </si>
   <si>
     <t xml:space="preserve">9.49393749237061</t>
@@ -281,22 +281,22 @@
     <t xml:space="preserve">9.44855499267578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47578430175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23979663848877</t>
+    <t xml:space="preserve">9.4757833480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23979759216309</t>
   </si>
   <si>
     <t xml:space="preserve">9.14903354644775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21256732940674</t>
+    <t xml:space="preserve">9.21256828308105</t>
   </si>
   <si>
     <t xml:space="preserve">9.20349216461182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13088035583496</t>
+    <t xml:space="preserve">9.13088130950928</t>
   </si>
   <si>
     <t xml:space="preserve">9.1399564743042</t>
@@ -305,7 +305,7 @@
     <t xml:space="preserve">8.94027519226074</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8041296005249</t>
+    <t xml:space="preserve">8.80412864685059</t>
   </si>
   <si>
     <t xml:space="preserve">8.75874614715576</t>
@@ -314,22 +314,22 @@
     <t xml:space="preserve">8.66798305511475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62260055541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53183650970459</t>
+    <t xml:space="preserve">8.62259960174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53183555603027</t>
   </si>
   <si>
     <t xml:space="preserve">8.35030746459961</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16878032684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98725175857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03263378143311</t>
+    <t xml:space="preserve">8.16877937316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98725128173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03263473510742</t>
   </si>
   <si>
     <t xml:space="preserve">8.12339782714844</t>
@@ -338,25 +338,25 @@
     <t xml:space="preserve">8.25954437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94186782836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3049259185791</t>
+    <t xml:space="preserve">7.94186973571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30492687225342</t>
   </si>
   <si>
     <t xml:space="preserve">8.21416187286377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39568996429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57721900939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71336555480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53202247619629</t>
+    <t xml:space="preserve">8.39569187164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5772180557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71336460113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53202342987061</t>
   </si>
   <si>
     <t xml:space="preserve">9.34871387481689</t>
@@ -365,61 +365,61 @@
     <t xml:space="preserve">9.25706100463867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44037055969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16540813446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07375240325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11958026885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98209857940674</t>
+    <t xml:space="preserve">9.44036960601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16540718078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07375144958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11957836151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98209762573242</t>
   </si>
   <si>
     <t xml:space="preserve">9.02792549133301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62367630004883</t>
+    <t xml:space="preserve">9.62367725372314</t>
   </si>
   <si>
     <t xml:space="preserve">9.80698585510254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89863872528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99029350280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1736011505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2652549743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3569107055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5402173995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6318731307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8151807785034</t>
+    <t xml:space="preserve">9.89863967895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9902925491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.173602104187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2652559280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3569097518921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5402183532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.631872177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8151798248291</t>
   </si>
   <si>
     <t xml:space="preserve">10.7235260009766</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9068326950073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9984884262085</t>
+    <t xml:space="preserve">10.9068336486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9984874725342</t>
   </si>
   <si>
     <t xml:space="preserve">11.090142250061</t>
@@ -428,16 +428,16 @@
     <t xml:space="preserve">11.1817960739136</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734498977661</t>
+    <t xml:space="preserve">11.2734508514404</t>
   </si>
   <si>
     <t xml:space="preserve">11.4567575454712</t>
   </si>
   <si>
-    <t xml:space="preserve">11.365104675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4485635757446</t>
+    <t xml:space="preserve">11.3651027679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4485626220703</t>
   </si>
   <si>
     <t xml:space="preserve">9.71533203125</t>
@@ -446,34 +446,34 @@
     <t xml:space="preserve">8.79879093170166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24886703491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21123313903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30288696289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03709125518799</t>
+    <t xml:space="preserve">8.24886512756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2112340927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30288791656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03709030151367</t>
   </si>
   <si>
     <t xml:space="preserve">9.39454174041748</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76115798950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66950416564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57784938812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0361194610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94446754455566</t>
+    <t xml:space="preserve">9.76115894317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66950511932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57785034179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0361204147339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94446659088135</t>
   </si>
   <si>
     <t xml:space="preserve">9.82552528381348</t>
@@ -485,82 +485,82 @@
     <t xml:space="preserve">9.59379005432129</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96456432342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9182186126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54744434356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.010910987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1036043167114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1499509811401</t>
+    <t xml:space="preserve">9.96456527709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91821765899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54744338989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0109119415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1036052703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1499519348145</t>
   </si>
   <si>
     <t xml:space="preserve">10.1962985992432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77917766571045</t>
+    <t xml:space="preserve">9.77917861938477</t>
   </si>
   <si>
     <t xml:space="preserve">9.87187099456787</t>
   </si>
   <si>
-    <t xml:space="preserve">10.057258605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2889919281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4743804931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2426452636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.381685256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68648242950439</t>
+    <t xml:space="preserve">10.0572595596313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2889928817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4743795394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2426462173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3816862106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68648338317871</t>
   </si>
   <si>
     <t xml:space="preserve">9.64013576507568</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50109577178955</t>
+    <t xml:space="preserve">9.50109672546387</t>
   </si>
   <si>
     <t xml:space="preserve">9.31570911407471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23228359222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19520664215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25082302093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26936340332031</t>
+    <t xml:space="preserve">9.23228549957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1952075958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25082206726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.269362449646</t>
   </si>
   <si>
     <t xml:space="preserve">9.2137451171875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04689693450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12105274200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06543636322021</t>
+    <t xml:space="preserve">9.04689788818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12105178833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0654354095459</t>
   </si>
   <si>
     <t xml:space="preserve">8.97274303436279</t>
@@ -572,28 +572,28 @@
     <t xml:space="preserve">9.02835845947266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95420360565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71320056915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99128150939941</t>
+    <t xml:space="preserve">8.95420455932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71319961547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9912805557251</t>
   </si>
   <si>
     <t xml:space="preserve">8.76881694793701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89858913421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93566608428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3353385925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9841947555542</t>
+    <t xml:space="preserve">8.89858722686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93566513061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3353395462036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9841938018799</t>
   </si>
   <si>
     <t xml:space="preserve">11.0305404663086</t>
@@ -602,16 +602,16 @@
     <t xml:space="preserve">11.2159280776978</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4940099716187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.540355682373</t>
+    <t xml:space="preserve">11.49400806427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5403547286987</t>
   </si>
   <si>
     <t xml:space="preserve">11.5867023468018</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6330499649048</t>
+    <t xml:space="preserve">11.6330490112305</t>
   </si>
   <si>
     <t xml:space="preserve">11.7257423400879</t>
@@ -620,31 +620,31 @@
     <t xml:space="preserve">11.9111299514771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9574756622314</t>
+    <t xml:space="preserve">11.9574775695801</t>
   </si>
   <si>
     <t xml:space="preserve">12.1892108917236</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2819042205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3745985031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5136384963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3282527923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1428661346436</t>
+    <t xml:space="preserve">12.2819051742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3745994567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5136394500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3282518386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1428651809692</t>
   </si>
   <si>
     <t xml:space="preserve">12.0965175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5551223754883</t>
+    <t xml:space="preserve">12.555121421814</t>
   </si>
   <si>
     <t xml:space="preserve">12.5082750320435</t>
@@ -668,10 +668,10 @@
     <t xml:space="preserve">12.2271890640259</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1803426742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3208847045898</t>
+    <t xml:space="preserve">12.1803417205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3208837509155</t>
   </si>
   <si>
     <t xml:space="preserve">12.274037361145</t>
@@ -680,13 +680,13 @@
     <t xml:space="preserve">12.8362064361572</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7893581390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6019687652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9299011230469</t>
+    <t xml:space="preserve">12.7893590927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6019697189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9299020767212</t>
   </si>
   <si>
     <t xml:space="preserve">12.8830547332764</t>
@@ -701,49 +701,49 @@
     <t xml:space="preserve">13.8668508529663</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0542411804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3353261947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5695629119873</t>
+    <t xml:space="preserve">14.0542402267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3353252410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5695638656616</t>
   </si>
   <si>
     <t xml:space="preserve">15.2254276275635</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1317329406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7569522857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0380382537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.178581237793</t>
+    <t xml:space="preserve">15.1317319869995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7569532394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0380373001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1785802841187</t>
   </si>
   <si>
     <t xml:space="preserve">15.3191232681274</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8974952697754</t>
+    <t xml:space="preserve">14.8974943161011</t>
   </si>
   <si>
     <t xml:space="preserve">15.4596652984619</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4128170013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5533609390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0686817169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8650913238525</t>
+    <t xml:space="preserve">15.4128189086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5533599853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0686836242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8650875091553</t>
   </si>
   <si>
     <t xml:space="preserve">17.0056324005127</t>
@@ -752,31 +752,31 @@
     <t xml:space="preserve">16.7713928222656</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1930236816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0524806976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9587821960449</t>
+    <t xml:space="preserve">17.193021774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0524787902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9587841033936</t>
   </si>
   <si>
     <t xml:space="preserve">16.7245464324951</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6308498382568</t>
+    <t xml:space="preserve">16.6308517456055</t>
   </si>
   <si>
     <t xml:space="preserve">16.5371570587158</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5840034484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2092247009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2560710906982</t>
+    <t xml:space="preserve">16.584005355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2092227935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2560729980469</t>
   </si>
   <si>
     <t xml:space="preserve">17.1461734771729</t>
@@ -785,40 +785,40 @@
     <t xml:space="preserve">16.396614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3029193878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8344449996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1155319213867</t>
+    <t xml:space="preserve">16.3029174804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8344440460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1155300140381</t>
   </si>
   <si>
     <t xml:space="preserve">16.0218353271484</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1623783111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.974986076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7407493591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4434604644775</t>
+    <t xml:space="preserve">16.1623764038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9749879837036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7407484054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4434623718262</t>
   </si>
   <si>
     <t xml:space="preserve">16.9119358062744</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0993251800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6777000427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.818244934082</t>
+    <t xml:space="preserve">17.0993270874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6776962280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8182430267334</t>
   </si>
   <si>
     <t xml:space="preserve">15.272274017334</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">15.084885597229</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9911909103394</t>
+    <t xml:space="preserve">14.991189956665</t>
   </si>
   <si>
     <t xml:space="preserve">14.8038005828857</t>
@@ -842,28 +842,28 @@
     <t xml:space="preserve">14.1010885238647</t>
   </si>
   <si>
-    <t xml:space="preserve">14.288477897644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5227146148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9605464935303</t>
+    <t xml:space="preserve">14.2884788513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5227155685425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.960545539856</t>
   </si>
   <si>
     <t xml:space="preserve">14.2416305541992</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1947822570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0073928833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7263078689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1479368209839</t>
+    <t xml:space="preserve">14.1947832107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0073938369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7263088226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1479358673096</t>
   </si>
   <si>
     <t xml:space="preserve">14.4290199279785</t>
@@ -872,22 +872,22 @@
     <t xml:space="preserve">14.6164102554321</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7731561660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3515281677246</t>
+    <t xml:space="preserve">13.7731552124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3515291213989</t>
   </si>
   <si>
     <t xml:space="preserve">13.3046817779541</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3983774185181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0235958099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1172904968262</t>
+    <t xml:space="preserve">13.3983764648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0235967636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1172924041748</t>
   </si>
   <si>
     <t xml:space="preserve">12.976749420166</t>
@@ -899,19 +899,19 @@
     <t xml:space="preserve">12.0866470336914</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9929533004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8992576599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0397987365723</t>
+    <t xml:space="preserve">11.9929523468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8992567062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0397996902466</t>
   </si>
   <si>
     <t xml:space="preserve">12.1334934234619</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4776306152344</t>
+    <t xml:space="preserve">11.4776296615601</t>
   </si>
   <si>
     <t xml:space="preserve">11.2433929443359</t>
@@ -920,13 +920,13 @@
     <t xml:space="preserve">11.3839340209961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6650199890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4307832717896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9623069763184</t>
+    <t xml:space="preserve">11.6650190353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4307823181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9623079299927</t>
   </si>
   <si>
     <t xml:space="preserve">10.7280712127686</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">11.7587146759033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8055639266968</t>
+    <t xml:space="preserve">11.8055629730225</t>
   </si>
   <si>
     <t xml:space="preserve">11.0091552734375</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">9.46318912506104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3388500213623</t>
+    <t xml:space="preserve">8.33884811401367</t>
   </si>
   <si>
     <t xml:space="preserve">8.57308673858643</t>
@@ -968,55 +968,55 @@
     <t xml:space="preserve">8.31074142456055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45128345489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61993503570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44191455841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32948017120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25452518463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43254566192627</t>
+    <t xml:space="preserve">8.45128440856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61993312835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44191360473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32948112487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25452423095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43254375457764</t>
   </si>
   <si>
     <t xml:space="preserve">8.47002220153809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32011127471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20767593383789</t>
+    <t xml:space="preserve">8.32011032104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20767784118652</t>
   </si>
   <si>
     <t xml:space="preserve">8.08587265014648</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78605031967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49559545516968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33631372451782</t>
+    <t xml:space="preserve">7.78604936599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49559497833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33631420135498</t>
   </si>
   <si>
     <t xml:space="preserve">7.23324918746948</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83289623260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90785264968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50496530532837</t>
+    <t xml:space="preserve">7.83289670944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90785217285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50496482849121</t>
   </si>
   <si>
     <t xml:space="preserve">7.37379169464111</t>
@@ -1028,16 +1028,16 @@
     <t xml:space="preserve">7.28009700775146</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98027324676514</t>
+    <t xml:space="preserve">6.98027276992798</t>
   </si>
   <si>
     <t xml:space="preserve">6.93342542648315</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06459808349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02712059020996</t>
+    <t xml:space="preserve">7.06459856033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0271201133728</t>
   </si>
   <si>
     <t xml:space="preserve">7.34568309783936</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">8.53747367858887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68056201934814</t>
+    <t xml:space="preserve">8.68056106567383</t>
   </si>
   <si>
     <t xml:space="preserve">8.77595138549805</t>
@@ -1070,16 +1070,16 @@
     <t xml:space="preserve">8.84272575378418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72825622558594</t>
+    <t xml:space="preserve">8.72825527191162</t>
   </si>
   <si>
     <t xml:space="preserve">8.66148281097412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49931812286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42300510406494</t>
+    <t xml:space="preserve">8.49931716918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42300605773926</t>
   </si>
   <si>
     <t xml:space="preserve">8.39438915252686</t>
@@ -1094,22 +1094,22 @@
     <t xml:space="preserve">8.29899787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12729454040527</t>
+    <t xml:space="preserve">8.12729549407959</t>
   </si>
   <si>
     <t xml:space="preserve">7.89835643768311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10821723937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84112215042114</t>
+    <t xml:space="preserve">8.10821628570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8411226272583</t>
   </si>
   <si>
     <t xml:space="preserve">8.33715343475342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2036075592041</t>
+    <t xml:space="preserve">8.20360660552979</t>
   </si>
   <si>
     <t xml:space="preserve">8.06052017211914</t>
@@ -1121,22 +1121,22 @@
     <t xml:space="preserve">8.07005977630615</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92697429656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98420810699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30853748321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26084041595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27038097381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18452930450439</t>
+    <t xml:space="preserve">7.92697334289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98420763015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30853652954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26084136962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2703800201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18452835083008</t>
   </si>
   <si>
     <t xml:space="preserve">8.03190422058105</t>
@@ -1145,7 +1145,7 @@
     <t xml:space="preserve">7.96512985229492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86020040512085</t>
+    <t xml:space="preserve">7.86019992828369</t>
   </si>
   <si>
     <t xml:space="preserve">7.86973905563354</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">7.71711397171021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91743516921997</t>
+    <t xml:space="preserve">7.91743421554565</t>
   </si>
   <si>
     <t xml:space="preserve">7.76480960845947</t>
@@ -1169,19 +1169,19 @@
     <t xml:space="preserve">7.63126230239868</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65987920761108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16545009613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32761383056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11775493621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9365119934082</t>
+    <t xml:space="preserve">7.65987968444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.165452003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32761478424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11775588989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93651247024536</t>
   </si>
   <si>
     <t xml:space="preserve">8.19406795501709</t>
@@ -1193,13 +1193,13 @@
     <t xml:space="preserve">8.31807613372803</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15591239929199</t>
+    <t xml:space="preserve">8.15591144561768</t>
   </si>
   <si>
     <t xml:space="preserve">8.22268486022949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25130176544189</t>
+    <t xml:space="preserve">8.25130081176758</t>
   </si>
   <si>
     <t xml:space="preserve">8.35623264312744</t>
@@ -1211,7 +1211,7 @@
     <t xml:space="preserve">8.34669303894043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95559167861938</t>
+    <t xml:space="preserve">7.95559072494507</t>
   </si>
   <si>
     <t xml:space="preserve">7.77434825897217</t>
@@ -1229,31 +1229,31 @@
     <t xml:space="preserve">8.05098152160645</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67895746231079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73619222640991</t>
+    <t xml:space="preserve">7.67895793914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7361912727356</t>
   </si>
   <si>
     <t xml:space="preserve">7.6980357170105</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5167932510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59310626983643</t>
+    <t xml:space="preserve">7.51679372787476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59310579299927</t>
   </si>
   <si>
     <t xml:space="preserve">7.44048070907593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5358715057373</t>
+    <t xml:space="preserve">7.53587198257446</t>
   </si>
   <si>
     <t xml:space="preserve">7.62172269821167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52633190155029</t>
+    <t xml:space="preserve">7.52633237838745</t>
   </si>
   <si>
     <t xml:space="preserve">7.34508991241455</t>
@@ -1262,7 +1262,7 @@
     <t xml:space="preserve">7.20200395584106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18292617797852</t>
+    <t xml:space="preserve">7.1829252243042</t>
   </si>
   <si>
     <t xml:space="preserve">7.14476919174194</t>
@@ -1277,37 +1277,37 @@
     <t xml:space="preserve">7.1543083190918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24969863891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24015998840332</t>
+    <t xml:space="preserve">7.24969911575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24016046524048</t>
   </si>
   <si>
     <t xml:space="preserve">7.46909809112549</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41186332702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45001983642578</t>
+    <t xml:space="preserve">7.41186380386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45001935958862</t>
   </si>
   <si>
     <t xml:space="preserve">7.28785514831543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39278507232666</t>
+    <t xml:space="preserve">7.39278554916382</t>
   </si>
   <si>
     <t xml:space="preserve">7.3355507850647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61218452453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90789556503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94605112075806</t>
+    <t xml:space="preserve">7.61218404769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90789604187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94605159759521</t>
   </si>
   <si>
     <t xml:space="preserve">7.45955896377563</t>
@@ -1316,25 +1316,25 @@
     <t xml:space="preserve">7.70757484436035</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8792781829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99374723434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75527000427246</t>
+    <t xml:space="preserve">7.87927913665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99374675750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75527048110962</t>
   </si>
   <si>
     <t xml:space="preserve">7.81250429153442</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79342699050903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80296564102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85066032409668</t>
+    <t xml:space="preserve">7.79342651367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80296611785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85066080093384</t>
   </si>
   <si>
     <t xml:space="preserve">7.74573087692261</t>
@@ -1346,25 +1346,25 @@
     <t xml:space="preserve">7.66941833496094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60264444351196</t>
+    <t xml:space="preserve">7.60264492034912</t>
   </si>
   <si>
     <t xml:space="preserve">7.58356666564941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88881778717041</t>
+    <t xml:space="preserve">7.88881826400757</t>
   </si>
   <si>
     <t xml:space="preserve">8.00328636169434</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78388690948486</t>
+    <t xml:space="preserve">7.78388738632202</t>
   </si>
   <si>
     <t xml:space="preserve">7.3641676902771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10661268234253</t>
+    <t xml:space="preserve">7.10661315917969</t>
   </si>
   <si>
     <t xml:space="preserve">7.27831649780273</t>
@@ -1379,10 +1379,10 @@
     <t xml:space="preserve">7.50372648239136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98721361160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02589321136475</t>
+    <t xml:space="preserve">7.98721408843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02589225769043</t>
   </si>
   <si>
     <t xml:space="preserve">8.04523086547852</t>
@@ -1394,25 +1394,25 @@
     <t xml:space="preserve">8.07424163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12259006500244</t>
+    <t xml:space="preserve">8.12258911132812</t>
   </si>
   <si>
     <t xml:space="preserve">8.05490112304688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94853448867798</t>
+    <t xml:space="preserve">7.94853496551514</t>
   </si>
   <si>
     <t xml:space="preserve">8.06457138061523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08391094207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97754383087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93886423110962</t>
+    <t xml:space="preserve">8.08390998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97754430770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93886518478394</t>
   </si>
   <si>
     <t xml:space="preserve">7.79381895065308</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">7.68745088577271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63910245895386</t>
+    <t xml:space="preserve">7.63910293579102</t>
   </si>
   <si>
     <t xml:space="preserve">7.73579978942871</t>
@@ -1439,10 +1439,10 @@
     <t xml:space="preserve">7.90985584259033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85183715820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83249807357788</t>
+    <t xml:space="preserve">7.85183668136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83249759674072</t>
   </si>
   <si>
     <t xml:space="preserve">7.81315755844116</t>
@@ -1451,7 +1451,7 @@
     <t xml:space="preserve">7.80348825454712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78414869308472</t>
+    <t xml:space="preserve">7.78414916992188</t>
   </si>
   <si>
     <t xml:space="preserve">7.6681113243103</t>
@@ -1463,13 +1463,13 @@
     <t xml:space="preserve">7.71646022796631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75514030456543</t>
+    <t xml:space="preserve">7.75513982772827</t>
   </si>
   <si>
     <t xml:space="preserve">7.74547004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86150646209717</t>
+    <t xml:space="preserve">7.86150693893433</t>
   </si>
   <si>
     <t xml:space="preserve">7.89051580429077</t>
@@ -1487,10 +1487,10 @@
     <t xml:space="preserve">8.09358024597168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1322603225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15159893035889</t>
+    <t xml:space="preserve">8.13225936889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1515998840332</t>
   </si>
   <si>
     <t xml:space="preserve">8.1129207611084</t>
@@ -1499,10 +1499,10 @@
     <t xml:space="preserve">8.03556251525879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92919540405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69712114334106</t>
+    <t xml:space="preserve">7.92919492721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69712066650391</t>
   </si>
   <si>
     <t xml:space="preserve">7.60042381286621</t>
@@ -1511,10 +1511,10 @@
     <t xml:space="preserve">7.88084602355957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55207490921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40702867507935</t>
+    <t xml:space="preserve">7.55207443237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40702819824219</t>
   </si>
   <si>
     <t xml:space="preserve">7.34900999069214</t>
@@ -1523,16 +1523,16 @@
     <t xml:space="preserve">7.37801933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43603801727295</t>
+    <t xml:space="preserve">7.43603754043579</t>
   </si>
   <si>
     <t xml:space="preserve">7.41669797897339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5230655670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36834907531738</t>
+    <t xml:space="preserve">7.52306604385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36834955215454</t>
   </si>
   <si>
     <t xml:space="preserve">7.542405128479</t>
@@ -1541,7 +1541,7 @@
     <t xml:space="preserve">7.4843864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70679092407227</t>
+    <t xml:space="preserve">7.70679044723511</t>
   </si>
   <si>
     <t xml:space="preserve">7.64877223968506</t>
@@ -1559,10 +1559,10 @@
     <t xml:space="preserve">7.59075355529785</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95820331573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96787357330322</t>
+    <t xml:space="preserve">7.95820426940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96787405014038</t>
   </si>
   <si>
     <t xml:space="preserve">7.90018606185913</t>
@@ -1580,10 +1580,10 @@
     <t xml:space="preserve">8.19027900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29664516448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45136070251465</t>
+    <t xml:space="preserve">8.29664611816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45136165618896</t>
   </si>
   <si>
     <t xml:space="preserve">8.48037147521973</t>
@@ -1610,19 +1610,19 @@
     <t xml:space="preserve">8.50938034057617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42235279083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54805850982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55772876739502</t>
+    <t xml:space="preserve">8.4223518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54805946350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55772972106934</t>
   </si>
   <si>
     <t xml:space="preserve">8.52871990203857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68343544006348</t>
+    <t xml:space="preserve">8.68343448638916</t>
   </si>
   <si>
     <t xml:space="preserve">8.76079368591309</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">8.65442562103271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75112342834473</t>
+    <t xml:space="preserve">8.75112438201904</t>
   </si>
   <si>
     <t xml:space="preserve">8.70277500152588</t>
@@ -1655,10 +1655,10 @@
     <t xml:space="preserve">8.63508701324463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32565498352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31598567962646</t>
+    <t xml:space="preserve">8.32565402984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31598472595215</t>
   </si>
   <si>
     <t xml:space="preserve">8.30631542205811</t>
@@ -2205,6 +2205,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.11999988555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02000045776367</t>
   </si>
 </sst>
 </file>
@@ -61953,7 +61956,7 @@
     </row>
     <row r="2286">
       <c r="A2286" s="1" t="n">
-        <v>45945.6436342593</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2286" t="n">
         <v>7088</v>
@@ -61974,6 +61977,32 @@
         <v>730</v>
       </c>
       <c r="H2286" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2287">
+      <c r="A2287" s="1" t="n">
+        <v>45946.6450810185</v>
+      </c>
+      <c r="B2287" t="n">
+        <v>16819</v>
+      </c>
+      <c r="C2287" t="n">
+        <v>9.14000034332275</v>
+      </c>
+      <c r="D2287" t="n">
+        <v>8.84000015258789</v>
+      </c>
+      <c r="E2287" t="n">
+        <v>9.11999988555908</v>
+      </c>
+      <c r="F2287" t="n">
+        <v>9.02000045776367</v>
+      </c>
+      <c r="G2287" t="s">
+        <v>731</v>
+      </c>
+      <c r="H2287" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="732">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07642269134521</t>
+    <t xml:space="preserve">9.0764217376709</t>
   </si>
   <si>
     <t xml:space="preserve">FF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98565578460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08549976348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24887371063232</t>
+    <t xml:space="preserve">8.98565769195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08549880981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24887275695801</t>
   </si>
   <si>
     <t xml:space="preserve">9.09457492828369</t>
@@ -59,37 +59,37 @@
     <t xml:space="preserve">9.12180328369141</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03104019165039</t>
+    <t xml:space="preserve">9.03103828430176</t>
   </si>
   <si>
     <t xml:space="preserve">8.95389080047607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89943218231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89489459991455</t>
+    <t xml:space="preserve">8.8994312286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89489364624023</t>
   </si>
   <si>
     <t xml:space="preserve">8.84951210021973</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85858821868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87674045562744</t>
+    <t xml:space="preserve">8.85858726501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87673950195312</t>
   </si>
   <si>
     <t xml:space="preserve">8.76782321929932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8676643371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04919338226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23072242736816</t>
+    <t xml:space="preserve">8.86766529083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04919242858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23072052001953</t>
   </si>
   <si>
     <t xml:space="preserve">9.11272811889648</t>
@@ -98,22 +98,22 @@
     <t xml:space="preserve">8.96750450134277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91304588317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92212200164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00380992889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15810966491699</t>
+    <t xml:space="preserve">8.91304683685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92212295532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00381088256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15811061859131</t>
   </si>
   <si>
     <t xml:space="preserve">9.16718673706055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43947982788086</t>
+    <t xml:space="preserve">9.43947792053223</t>
   </si>
   <si>
     <t xml:space="preserve">9.54839611053467</t>
@@ -122,22 +122,22 @@
     <t xml:space="preserve">9.62100696563721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80253601074219</t>
+    <t xml:space="preserve">9.8025369644165</t>
   </si>
   <si>
     <t xml:space="preserve">9.71177196502686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56654930114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58470153808594</t>
+    <t xml:space="preserve">9.56654739379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58470249176025</t>
   </si>
   <si>
     <t xml:space="preserve">9.57562446594238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53024387359619</t>
+    <t xml:space="preserve">9.53024291992188</t>
   </si>
   <si>
     <t xml:space="preserve">9.50301361083984</t>
@@ -146,28 +146,28 @@
     <t xml:space="preserve">9.6028528213501</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63915920257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79345989227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95683479309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93868255615234</t>
+    <t xml:space="preserve">9.63916015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79345893859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95683574676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93868160247803</t>
   </si>
   <si>
     <t xml:space="preserve">9.98406410217285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73900127410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76622867584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74807643890381</t>
+    <t xml:space="preserve">9.73900032043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76623058319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74807834625244</t>
   </si>
   <si>
     <t xml:space="preserve">9.75715351104736</t>
@@ -176,10 +176,10 @@
     <t xml:space="preserve">9.64823627471924</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82068920135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70269393920898</t>
+    <t xml:space="preserve">9.82068729400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7026948928833</t>
   </si>
   <si>
     <t xml:space="preserve">9.72084712982178</t>
@@ -188,22 +188,22 @@
     <t xml:space="preserve">9.67546558380127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6663875579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63008308410645</t>
+    <t xml:space="preserve">9.66638851165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63008213043213</t>
   </si>
   <si>
     <t xml:space="preserve">9.65731334686279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68454170227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81161212921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8297643661499</t>
+    <t xml:space="preserve">9.68454265594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81161403656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82976531982422</t>
   </si>
   <si>
     <t xml:space="preserve">9.84791851043701</t>
@@ -212,43 +212,43 @@
     <t xml:space="preserve">9.83884143829346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72992420196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78438282012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55747318267822</t>
+    <t xml:space="preserve">9.72992515563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78438186645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55747222900391</t>
   </si>
   <si>
     <t xml:space="preserve">9.34871482849121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33963775634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27610397338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25795078277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19441604614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18533897399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41224956512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22164344787598</t>
+    <t xml:space="preserve">9.33963680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27610301971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25794982910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19441509246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18533802032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4122486114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22164440155029</t>
   </si>
   <si>
     <t xml:space="preserve">9.31240844726562</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2670259475708</t>
+    <t xml:space="preserve">9.26702690124512</t>
   </si>
   <si>
     <t xml:space="preserve">9.29425525665283</t>
@@ -257,16 +257,16 @@
     <t xml:space="preserve">9.28517913818359</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37594413757324</t>
+    <t xml:space="preserve">9.37594318389893</t>
   </si>
   <si>
     <t xml:space="preserve">9.36686706542969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38501930236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45763206481934</t>
+    <t xml:space="preserve">9.38502025604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45763111114502</t>
   </si>
   <si>
     <t xml:space="preserve">9.39409732818604</t>
@@ -278,22 +278,22 @@
     <t xml:space="preserve">9.49393653869629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44855499267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47578430175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23979759216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14903259277344</t>
+    <t xml:space="preserve">9.44855403900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4757833480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2397985458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14903163909912</t>
   </si>
   <si>
     <t xml:space="preserve">9.21256828308105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20349311828613</t>
+    <t xml:space="preserve">9.2034912109375</t>
   </si>
   <si>
     <t xml:space="preserve">9.13088035583496</t>
@@ -305,7 +305,7 @@
     <t xml:space="preserve">8.94027519226074</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8041296005249</t>
+    <t xml:space="preserve">8.80412864685059</t>
   </si>
   <si>
     <t xml:space="preserve">8.75874710083008</t>
@@ -314,28 +314,28 @@
     <t xml:space="preserve">8.66798305511475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62259960174561</t>
+    <t xml:space="preserve">8.62260055541992</t>
   </si>
   <si>
     <t xml:space="preserve">8.53183650970459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35030937194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16878032684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98725175857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03263378143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12339687347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25954437255859</t>
+    <t xml:space="preserve">8.35030841827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16877937316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98725032806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03263282775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12339782714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25954341888428</t>
   </si>
   <si>
     <t xml:space="preserve">7.9418683052063</t>
@@ -344,10 +344,10 @@
     <t xml:space="preserve">8.30492496490479</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21416187286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39569091796875</t>
+    <t xml:space="preserve">8.21416282653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39568996429443</t>
   </si>
   <si>
     <t xml:space="preserve">8.57721900939941</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">8.71336650848389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53202152252197</t>
+    <t xml:space="preserve">9.53202342987061</t>
   </si>
   <si>
     <t xml:space="preserve">9.25706100463867</t>
@@ -371,7 +371,7 @@
     <t xml:space="preserve">9.07375240325928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11958026885986</t>
+    <t xml:space="preserve">9.11957931518555</t>
   </si>
   <si>
     <t xml:space="preserve">8.98209857940674</t>
@@ -380,7 +380,7 @@
     <t xml:space="preserve">9.02792549133301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62367725372314</t>
+    <t xml:space="preserve">9.62367630004883</t>
   </si>
   <si>
     <t xml:space="preserve">9.80698490142822</t>
@@ -392,7 +392,7 @@
     <t xml:space="preserve">9.99029350280762</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1736030578613</t>
+    <t xml:space="preserve">10.173602104187</t>
   </si>
   <si>
     <t xml:space="preserve">10.2652559280396</t>
@@ -401,52 +401,52 @@
     <t xml:space="preserve">10.3569097518921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5402183532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.631872177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8151798248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7235260009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.906834602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9984893798828</t>
+    <t xml:space="preserve">10.5402173995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6318712234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8151807785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7235250473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9068326950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9984884262085</t>
   </si>
   <si>
     <t xml:space="preserve">11.090142250061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1817951202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2734489440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4567575454712</t>
+    <t xml:space="preserve">11.1817960739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2734498977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4567594528198</t>
   </si>
   <si>
     <t xml:space="preserve">11.3651037216187</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4485645294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71533203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79879188537598</t>
+    <t xml:space="preserve">10.4485626220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71533012390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79879093170166</t>
   </si>
   <si>
     <t xml:space="preserve">8.24886703491211</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2112340927124</t>
+    <t xml:space="preserve">9.21123313903809</t>
   </si>
   <si>
     <t xml:space="preserve">9.30288791656494</t>
@@ -455,16 +455,16 @@
     <t xml:space="preserve">9.03709030151367</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39454078674316</t>
+    <t xml:space="preserve">9.39454174041748</t>
   </si>
   <si>
     <t xml:space="preserve">9.76115703582764</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66950416564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57784938812256</t>
+    <t xml:space="preserve">9.6695032119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57785034179688</t>
   </si>
   <si>
     <t xml:space="preserve">10.0361204147339</t>
@@ -473,16 +473,16 @@
     <t xml:space="preserve">9.94446659088135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82552528381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73283100128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59378910064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96456527709961</t>
+    <t xml:space="preserve">9.82552433013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73283004760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59379005432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96456432342529</t>
   </si>
   <si>
     <t xml:space="preserve">9.91821765899658</t>
@@ -491,10 +491,10 @@
     <t xml:space="preserve">9.54744338989258</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0109119415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1036052703857</t>
+    <t xml:space="preserve">10.010910987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1036043167114</t>
   </si>
   <si>
     <t xml:space="preserve">10.1499519348145</t>
@@ -503,16 +503,16 @@
     <t xml:space="preserve">10.1962985992432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77917766571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87187004089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.057258605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2889938354492</t>
+    <t xml:space="preserve">9.77917671203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87187099456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0572576522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2889919281006</t>
   </si>
   <si>
     <t xml:space="preserve">10.4743795394897</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">9.68648338317871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64013576507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50109577178955</t>
+    <t xml:space="preserve">9.64013671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50109672546387</t>
   </si>
   <si>
     <t xml:space="preserve">9.31570911407471</t>
@@ -542,43 +542,43 @@
     <t xml:space="preserve">9.1952075958252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25082206726074</t>
+    <t xml:space="preserve">9.25082302093506</t>
   </si>
   <si>
     <t xml:space="preserve">9.269362449646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2137451171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04689788818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12105274200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0654354095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97274303436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17666816711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02835941314697</t>
+    <t xml:space="preserve">9.21374607086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04689693450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12105369567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06543636322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97274208068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17666721343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02835845947266</t>
   </si>
   <si>
     <t xml:space="preserve">8.95420360565186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71319961547852</t>
+    <t xml:space="preserve">8.71320056915283</t>
   </si>
   <si>
     <t xml:space="preserve">8.99128150939941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7688159942627</t>
+    <t xml:space="preserve">8.76881694793701</t>
   </si>
   <si>
     <t xml:space="preserve">8.89858913421631</t>
@@ -590,46 +590,46 @@
     <t xml:space="preserve">10.3353385925293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9841938018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0305414199829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2159290313721</t>
+    <t xml:space="preserve">10.9841947555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0305404663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2159280776978</t>
   </si>
   <si>
     <t xml:space="preserve">11.4940090179443</t>
   </si>
   <si>
-    <t xml:space="preserve">11.540355682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5867023468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6330490112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7257423400879</t>
+    <t xml:space="preserve">11.5403566360474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5867033004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6330499649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7257432937622</t>
   </si>
   <si>
     <t xml:space="preserve">11.9111299514771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9574775695801</t>
+    <t xml:space="preserve">11.9574756622314</t>
   </si>
   <si>
     <t xml:space="preserve">12.1892108917236</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2819051742554</t>
+    <t xml:space="preserve">12.2819042205811</t>
   </si>
   <si>
     <t xml:space="preserve">12.3745994567871</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5136394500732</t>
+    <t xml:space="preserve">12.5136384963989</t>
   </si>
   <si>
     <t xml:space="preserve">12.3282518386841</t>
@@ -656,7 +656,7 @@
     <t xml:space="preserve">12.4145793914795</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7425127029419</t>
+    <t xml:space="preserve">12.7425117492676</t>
   </si>
   <si>
     <t xml:space="preserve">12.6956644058228</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">12.1803426742554</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3208837509155</t>
+    <t xml:space="preserve">12.3208847045898</t>
   </si>
   <si>
     <t xml:space="preserve">12.274037361145</t>
@@ -680,16 +680,16 @@
     <t xml:space="preserve">12.7893581390381</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6019687652588</t>
+    <t xml:space="preserve">12.6019697189331</t>
   </si>
   <si>
     <t xml:space="preserve">12.9299011230469</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8830537796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0704441070557</t>
+    <t xml:space="preserve">12.8830547332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.07044506073</t>
   </si>
   <si>
     <t xml:space="preserve">13.679461479187</t>
@@ -704,31 +704,31 @@
     <t xml:space="preserve">14.3353261947632</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5695629119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2254276275635</t>
+    <t xml:space="preserve">14.5695638656616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2254285812378</t>
   </si>
   <si>
     <t xml:space="preserve">15.1317329406738</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7569532394409</t>
+    <t xml:space="preserve">14.7569522857666</t>
   </si>
   <si>
     <t xml:space="preserve">15.0380382537842</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1785802841187</t>
+    <t xml:space="preserve">15.178581237793</t>
   </si>
   <si>
     <t xml:space="preserve">15.3191232681274</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8974952697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4596652984619</t>
+    <t xml:space="preserve">14.8974943161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4596662521362</t>
   </si>
   <si>
     <t xml:space="preserve">15.4128179550171</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">15.5533609390259</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0686836242676</t>
+    <t xml:space="preserve">16.0686817169189</t>
   </si>
   <si>
     <t xml:space="preserve">16.8650913238525</t>
@@ -746,25 +746,25 @@
     <t xml:space="preserve">17.0056324005127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7713928222656</t>
+    <t xml:space="preserve">16.7713947296143</t>
   </si>
   <si>
     <t xml:space="preserve">17.193021774292</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0524806976318</t>
+    <t xml:space="preserve">17.0524787902832</t>
   </si>
   <si>
     <t xml:space="preserve">16.9587841033936</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7245464324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6308498382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5371551513672</t>
+    <t xml:space="preserve">16.7245483398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6308517456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5371570587158</t>
   </si>
   <si>
     <t xml:space="preserve">16.5840034484863</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">16.2092247009277</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2560729980469</t>
+    <t xml:space="preserve">16.2560710906982</t>
   </si>
   <si>
     <t xml:space="preserve">17.1461734771729</t>
@@ -782,13 +782,13 @@
     <t xml:space="preserve">16.396614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3029193878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8344430923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1155319213867</t>
+    <t xml:space="preserve">16.3029174804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8344449996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1155300140381</t>
   </si>
   <si>
     <t xml:space="preserve">16.0218353271484</t>
@@ -806,7 +806,7 @@
     <t xml:space="preserve">16.4434604644775</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9119358062744</t>
+    <t xml:space="preserve">16.911937713623</t>
   </si>
   <si>
     <t xml:space="preserve">17.0993251800537</t>
@@ -824,10 +824,10 @@
     <t xml:space="preserve">15.084885597229</t>
   </si>
   <si>
-    <t xml:space="preserve">14.991189956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8038015365601</t>
+    <t xml:space="preserve">14.9911909103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8038005828857</t>
   </si>
   <si>
     <t xml:space="preserve">14.4758682250977</t>
@@ -836,7 +836,7 @@
     <t xml:space="preserve">14.382173538208</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1010875701904</t>
+    <t xml:space="preserve">14.1010885238647</t>
   </si>
   <si>
     <t xml:space="preserve">14.288477897644</t>
@@ -857,31 +857,31 @@
     <t xml:space="preserve">14.0073928833008</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7263078689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1479358673096</t>
+    <t xml:space="preserve">13.7263088226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1479368209839</t>
   </si>
   <si>
     <t xml:space="preserve">14.4290199279785</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6164102554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7731552124023</t>
+    <t xml:space="preserve">14.6164112091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7731561660767</t>
   </si>
   <si>
     <t xml:space="preserve">13.3515281677246</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3046817779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3983774185181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0235967636108</t>
+    <t xml:space="preserve">13.3046808242798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3983764648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0235958099365</t>
   </si>
   <si>
     <t xml:space="preserve">13.1172914505005</t>
@@ -890,10 +890,10 @@
     <t xml:space="preserve">12.976749420166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3677310943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0866470336914</t>
+    <t xml:space="preserve">12.3677320480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0866460800171</t>
   </si>
   <si>
     <t xml:space="preserve">11.9929523468018</t>
@@ -902,13 +902,13 @@
     <t xml:space="preserve">11.8992576599121</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0397996902466</t>
+    <t xml:space="preserve">12.0397987365723</t>
   </si>
   <si>
     <t xml:space="preserve">12.1334943771362</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4776296615601</t>
+    <t xml:space="preserve">11.4776306152344</t>
   </si>
   <si>
     <t xml:space="preserve">11.2433938980103</t>
@@ -917,25 +917,25 @@
     <t xml:space="preserve">11.3839340209961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6650199890137</t>
+    <t xml:space="preserve">11.665020942688</t>
   </si>
   <si>
     <t xml:space="preserve">11.4307823181152</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9623079299927</t>
+    <t xml:space="preserve">10.9623069763184</t>
   </si>
   <si>
     <t xml:space="preserve">10.7280712127686</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1965446472168</t>
+    <t xml:space="preserve">11.1965456008911</t>
   </si>
   <si>
     <t xml:space="preserve">11.571325302124</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3370885848999</t>
+    <t xml:space="preserve">11.3370876312256</t>
   </si>
   <si>
     <t xml:space="preserve">11.2902402877808</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">11.7118673324585</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7587146759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8055629730225</t>
+    <t xml:space="preserve">11.7587156295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8055639266968</t>
   </si>
   <si>
     <t xml:space="preserve">11.0091552734375</t>
@@ -962,13 +962,13 @@
     <t xml:space="preserve">8.57308673858643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31074237823486</t>
+    <t xml:space="preserve">8.31074142456055</t>
   </si>
   <si>
     <t xml:space="preserve">8.45128345489502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61993503570557</t>
+    <t xml:space="preserve">8.61993408203125</t>
   </si>
   <si>
     <t xml:space="preserve">8.44191455841064</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">8.32948017120361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25452518463135</t>
+    <t xml:space="preserve">8.25452423095703</t>
   </si>
   <si>
     <t xml:space="preserve">8.43254566192627</t>
@@ -986,34 +986,34 @@
     <t xml:space="preserve">8.47002220153809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32011032104492</t>
+    <t xml:space="preserve">8.32011127471924</t>
   </si>
   <si>
     <t xml:space="preserve">8.20767688751221</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0858736038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78605031967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49559497833252</t>
+    <t xml:space="preserve">8.08587265014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78604936599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49559545516968</t>
   </si>
   <si>
     <t xml:space="preserve">7.33631372451782</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23324871063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83289670944214</t>
+    <t xml:space="preserve">7.23324918746948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83289623260498</t>
   </si>
   <si>
     <t xml:space="preserve">7.90785264968872</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50496530532837</t>
+    <t xml:space="preserve">7.50496482849121</t>
   </si>
   <si>
     <t xml:space="preserve">7.37379169464111</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">7.12081527709961</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28009653091431</t>
+    <t xml:space="preserve">7.28009700775146</t>
   </si>
   <si>
     <t xml:space="preserve">6.98027324676514</t>
@@ -2205,6 +2205,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.02000045776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10000038146973</t>
   </si>
 </sst>
 </file>
@@ -62005,7 +62008,7 @@
     </row>
     <row r="2288">
       <c r="A2288" s="1" t="n">
-        <v>45947.6494791667</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2288" t="n">
         <v>9715</v>
@@ -62026,6 +62029,32 @@
         <v>715</v>
       </c>
       <c r="H2288" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2289">
+      <c r="A2289" s="1" t="n">
+        <v>45950.6452893519</v>
+      </c>
+      <c r="B2289" t="n">
+        <v>26232</v>
+      </c>
+      <c r="C2289" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="D2289" t="n">
+        <v>8.60000038146973</v>
+      </c>
+      <c r="E2289" t="n">
+        <v>9.02000045776367</v>
+      </c>
+      <c r="F2289" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="G2289" t="s">
+        <v>731</v>
+      </c>
+      <c r="H2289" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -44,34 +44,34 @@
     <t xml:space="preserve">FF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98565578460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08549880981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24887275695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09457588195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12180328369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03104019165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95388984680176</t>
+    <t xml:space="preserve">8.98565769195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08549785614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24887371063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09457492828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12180519104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03103923797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95389080047607</t>
   </si>
   <si>
     <t xml:space="preserve">8.89943218231201</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89489364624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84951114654541</t>
+    <t xml:space="preserve">8.89489269256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84951210021973</t>
   </si>
   <si>
     <t xml:space="preserve">8.85858821868896</t>
@@ -80,31 +80,31 @@
     <t xml:space="preserve">8.87673950195312</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76782321929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86766338348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04919147491455</t>
+    <t xml:space="preserve">8.76782417297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86766529083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04919242858887</t>
   </si>
   <si>
     <t xml:space="preserve">9.23072052001953</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11272811889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96750450134277</t>
+    <t xml:space="preserve">9.11272716522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96750545501709</t>
   </si>
   <si>
     <t xml:space="preserve">8.91304492950439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92212390899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00381088256836</t>
+    <t xml:space="preserve">8.92212295532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00381183624268</t>
   </si>
   <si>
     <t xml:space="preserve">9.15810966491699</t>
@@ -113,19 +113,19 @@
     <t xml:space="preserve">9.16718578338623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43947887420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54839515686035</t>
+    <t xml:space="preserve">9.43947696685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54839611053467</t>
   </si>
   <si>
     <t xml:space="preserve">9.62100791931152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80253505706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71177101135254</t>
+    <t xml:space="preserve">9.8025369644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71177005767822</t>
   </si>
   <si>
     <t xml:space="preserve">9.56654930114746</t>
@@ -134,49 +134,49 @@
     <t xml:space="preserve">9.58470153808594</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5756254196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53024291992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50301456451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60285568237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63916110992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79345798492432</t>
+    <t xml:space="preserve">9.57562446594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53024387359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50301265716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60285472869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63915920257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79345893859863</t>
   </si>
   <si>
     <t xml:space="preserve">9.95683479309082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93868160247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98406505584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73900127410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76623058319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74807643890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75715255737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64823627471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82068729400635</t>
+    <t xml:space="preserve">9.93868255615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98406410217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73900032043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76623153686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74807548522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75715351104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64823722839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82068824768066</t>
   </si>
   <si>
     <t xml:space="preserve">9.7026948928833</t>
@@ -185,28 +185,28 @@
     <t xml:space="preserve">9.72084808349609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67546558380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66638851165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63008308410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65731239318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68454265594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81161403656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8297643661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84791851043701</t>
+    <t xml:space="preserve">9.67546463012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66639041900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63008403778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65731334686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68454170227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81161212921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82976531982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8479175567627</t>
   </si>
   <si>
     <t xml:space="preserve">9.83884143829346</t>
@@ -218,7 +218,7 @@
     <t xml:space="preserve">9.78438282012939</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55747318267822</t>
+    <t xml:space="preserve">9.55747222900391</t>
   </si>
   <si>
     <t xml:space="preserve">9.34871482849121</t>
@@ -230,31 +230,31 @@
     <t xml:space="preserve">9.27610397338867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25794982910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19441604614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18533897399902</t>
+    <t xml:space="preserve">9.25795078277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19441509246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18533992767334</t>
   </si>
   <si>
     <t xml:space="preserve">9.41224956512451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22164344787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31240940093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26702690124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29425621032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28517913818359</t>
+    <t xml:space="preserve">9.22164440155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31240844726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2670259475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29425525665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28518009185791</t>
   </si>
   <si>
     <t xml:space="preserve">9.37594413757324</t>
@@ -269,13 +269,13 @@
     <t xml:space="preserve">9.45763206481934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39409732818604</t>
+    <t xml:space="preserve">9.39409828186035</t>
   </si>
   <si>
     <t xml:space="preserve">9.48486042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49393653869629</t>
+    <t xml:space="preserve">9.49393844604492</t>
   </si>
   <si>
     <t xml:space="preserve">9.44855499267578</t>
@@ -284,43 +284,43 @@
     <t xml:space="preserve">9.4757833480835</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23979663848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14903259277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21256828308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20349311828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13088130950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1399564743042</t>
+    <t xml:space="preserve">9.2397985458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14903354644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21256732940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2034912109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13087940216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13995742797852</t>
   </si>
   <si>
     <t xml:space="preserve">8.94027614593506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80412769317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75874805450439</t>
+    <t xml:space="preserve">8.80412864685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75874614715576</t>
   </si>
   <si>
     <t xml:space="preserve">8.66798305511475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62260150909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53183555603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35030746459961</t>
+    <t xml:space="preserve">8.62260055541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53183650970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35030841827393</t>
   </si>
   <si>
     <t xml:space="preserve">8.16878128051758</t>
@@ -329,10 +329,10 @@
     <t xml:space="preserve">7.98725175857544</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03263378143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12339687347412</t>
+    <t xml:space="preserve">8.03263473510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12339782714844</t>
   </si>
   <si>
     <t xml:space="preserve">8.25954437255859</t>
@@ -341,22 +341,22 @@
     <t xml:space="preserve">7.94186878204346</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3049259185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21416187286377</t>
+    <t xml:space="preserve">8.30492687225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21416282653809</t>
   </si>
   <si>
     <t xml:space="preserve">8.39568996429443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57721900939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71336555480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53202247619629</t>
+    <t xml:space="preserve">8.5772180557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71336460113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53202342987061</t>
   </si>
   <si>
     <t xml:space="preserve">9.25706005096436</t>
@@ -365,19 +365,19 @@
     <t xml:space="preserve">9.44036865234375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16540718078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07375144958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11958122253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98209953308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02792644500732</t>
+    <t xml:space="preserve">9.16540622711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07375240325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11957931518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98209857940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02792549133301</t>
   </si>
   <si>
     <t xml:space="preserve">9.62367630004883</t>
@@ -386,7 +386,7 @@
     <t xml:space="preserve">9.80698394775391</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89863872528076</t>
+    <t xml:space="preserve">9.89863967895508</t>
   </si>
   <si>
     <t xml:space="preserve">9.9902925491333</t>
@@ -395,7 +395,7 @@
     <t xml:space="preserve">10.1736011505127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2652549743652</t>
+    <t xml:space="preserve">10.2652559280396</t>
   </si>
   <si>
     <t xml:space="preserve">10.3569097518921</t>
@@ -419,19 +419,19 @@
     <t xml:space="preserve">10.9984884262085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.090142250061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1817960739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2734508514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4567594528198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3651037216187</t>
+    <t xml:space="preserve">11.0901432037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1817951202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2734498977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4567584991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3651027679443</t>
   </si>
   <si>
     <t xml:space="preserve">10.4485635757446</t>
@@ -443,16 +443,16 @@
     <t xml:space="preserve">8.79879093170166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24886608123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21123504638672</t>
+    <t xml:space="preserve">8.24886512756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2112340927124</t>
   </si>
   <si>
     <t xml:space="preserve">9.30288791656494</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03708934783936</t>
+    <t xml:space="preserve">9.03709125518799</t>
   </si>
   <si>
     <t xml:space="preserve">9.39454174041748</t>
@@ -461,16 +461,16 @@
     <t xml:space="preserve">9.76115798950195</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66950511932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57784938812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0361194610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94446563720703</t>
+    <t xml:space="preserve">9.66950416564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57785034179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0361204147339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94446659088135</t>
   </si>
   <si>
     <t xml:space="preserve">9.82552433013916</t>
@@ -479,10 +479,10 @@
     <t xml:space="preserve">9.73283100128174</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59379100799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96456527709961</t>
+    <t xml:space="preserve">9.59379005432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96456432342529</t>
   </si>
   <si>
     <t xml:space="preserve">9.91821670532227</t>
@@ -506,13 +506,13 @@
     <t xml:space="preserve">9.77917766571045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87187004089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.057258605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2889919281006</t>
+    <t xml:space="preserve">9.87187099456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0572595596313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2889938354492</t>
   </si>
   <si>
     <t xml:space="preserve">10.4743795394897</t>
@@ -524,16 +524,16 @@
     <t xml:space="preserve">10.381685256958</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68648338317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64013576507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50109767913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31571006774902</t>
+    <t xml:space="preserve">9.68648242950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64013671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50109577178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31570816040039</t>
   </si>
   <si>
     <t xml:space="preserve">9.23228549957275</t>
@@ -545,10 +545,10 @@
     <t xml:space="preserve">9.25082302093506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26936340332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21374607086182</t>
+    <t xml:space="preserve">9.269362449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2137451171875</t>
   </si>
   <si>
     <t xml:space="preserve">9.04689693450928</t>
@@ -557,25 +557,25 @@
     <t xml:space="preserve">9.12105274200439</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06543636322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97274208068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17666816711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02835941314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95420265197754</t>
+    <t xml:space="preserve">9.0654354095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97274303436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17666721343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02835845947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95420360565186</t>
   </si>
   <si>
     <t xml:space="preserve">8.71319961547852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9912805557251</t>
+    <t xml:space="preserve">8.99128150939941</t>
   </si>
   <si>
     <t xml:space="preserve">8.76881694793701</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">8.89858818054199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93566703796387</t>
+    <t xml:space="preserve">8.93566608428955</t>
   </si>
   <si>
     <t xml:space="preserve">10.3353385925293</t>
@@ -596,25 +596,25 @@
     <t xml:space="preserve">11.0305414199829</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2159290313721</t>
+    <t xml:space="preserve">11.2159280776978</t>
   </si>
   <si>
     <t xml:space="preserve">11.4940090179443</t>
   </si>
   <si>
-    <t xml:space="preserve">11.540355682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5867033004761</t>
+    <t xml:space="preserve">11.5403566360474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5867023468018</t>
   </si>
   <si>
     <t xml:space="preserve">11.6330499649048</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7257423400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9111309051514</t>
+    <t xml:space="preserve">11.7257432937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9111299514771</t>
   </si>
   <si>
     <t xml:space="preserve">11.9574775695801</t>
@@ -623,7 +623,7 @@
     <t xml:space="preserve">12.1892118453979</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2819042205811</t>
+    <t xml:space="preserve">12.2819051742554</t>
   </si>
   <si>
     <t xml:space="preserve">12.3745985031128</t>
@@ -632,31 +632,31 @@
     <t xml:space="preserve">12.5136375427246</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3282518386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1428642272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0965185165405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.555121421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5082750320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6488161087036</t>
+    <t xml:space="preserve">12.3282527923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1428651809692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0965175628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5551223754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5082740783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6488170623779</t>
   </si>
   <si>
     <t xml:space="preserve">12.4614267349243</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4145793914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7425117492676</t>
+    <t xml:space="preserve">12.4145784378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7425127029419</t>
   </si>
   <si>
     <t xml:space="preserve">12.6956644058228</t>
@@ -665,16 +665,16 @@
     <t xml:space="preserve">12.2271900177002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1803417205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3208847045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.274037361145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8362064361572</t>
+    <t xml:space="preserve">12.1803426742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3208837509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2740383148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8362073898315</t>
   </si>
   <si>
     <t xml:space="preserve">12.7893590927124</t>
@@ -686,13 +686,13 @@
     <t xml:space="preserve">12.9299011230469</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8830537796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0704431533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6794624328613</t>
+    <t xml:space="preserve">12.8830528259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0704441070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.679461479187</t>
   </si>
   <si>
     <t xml:space="preserve">13.8668518066406</t>
@@ -707,22 +707,22 @@
     <t xml:space="preserve">14.5695629119873</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2254285812378</t>
+    <t xml:space="preserve">15.2254276275635</t>
   </si>
   <si>
     <t xml:space="preserve">15.1317319869995</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7569522857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0380363464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.178581237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3191232681274</t>
+    <t xml:space="preserve">14.7569532394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0380373001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1785802841187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3191242218018</t>
   </si>
   <si>
     <t xml:space="preserve">14.8974952697754</t>
@@ -731,7 +731,7 @@
     <t xml:space="preserve">15.4596643447876</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4128189086914</t>
+    <t xml:space="preserve">15.4128179550171</t>
   </si>
   <si>
     <t xml:space="preserve">15.5533609390259</t>
@@ -743,13 +743,13 @@
     <t xml:space="preserve">16.8650894165039</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0056324005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7713928222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.193021774292</t>
+    <t xml:space="preserve">17.0056304931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7713947296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1930236816406</t>
   </si>
   <si>
     <t xml:space="preserve">17.0524787902832</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">16.2092227935791</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2560710906982</t>
+    <t xml:space="preserve">16.2560729980469</t>
   </si>
   <si>
     <t xml:space="preserve">17.1461715698242</t>
@@ -797,22 +797,22 @@
     <t xml:space="preserve">16.1623764038086</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9749870300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7407493591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4434604644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9119358062744</t>
+    <t xml:space="preserve">15.9749851226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7407512664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4434623718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9119338989258</t>
   </si>
   <si>
     <t xml:space="preserve">17.0993251800537</t>
   </si>
   <si>
-    <t xml:space="preserve">16.677698135376</t>
+    <t xml:space="preserve">16.6777000427246</t>
   </si>
   <si>
     <t xml:space="preserve">16.8182430267334</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">15.0848846435547</t>
   </si>
   <si>
-    <t xml:space="preserve">14.991189956665</t>
+    <t xml:space="preserve">14.9911909103394</t>
   </si>
   <si>
     <t xml:space="preserve">14.8038005828857</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4758672714233</t>
+    <t xml:space="preserve">14.4758682250977</t>
   </si>
   <si>
     <t xml:space="preserve">14.382173538208</t>
@@ -839,16 +839,16 @@
     <t xml:space="preserve">14.1010885238647</t>
   </si>
   <si>
-    <t xml:space="preserve">14.288477897644</t>
+    <t xml:space="preserve">14.2884769439697</t>
   </si>
   <si>
     <t xml:space="preserve">14.5227155685425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9605464935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2416305541992</t>
+    <t xml:space="preserve">13.960545539856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2416296005249</t>
   </si>
   <si>
     <t xml:space="preserve">14.1947822570801</t>
@@ -857,7 +857,7 @@
     <t xml:space="preserve">14.0073928833008</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7263078689575</t>
+    <t xml:space="preserve">13.7263069152832</t>
   </si>
   <si>
     <t xml:space="preserve">14.1479358673096</t>
@@ -869,10 +869,10 @@
     <t xml:space="preserve">14.6164102554321</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7731561660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3515291213989</t>
+    <t xml:space="preserve">13.7731552124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3515281677246</t>
   </si>
   <si>
     <t xml:space="preserve">13.3046808242798</t>
@@ -881,10 +881,10 @@
     <t xml:space="preserve">13.3983764648438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0235958099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1172914505005</t>
+    <t xml:space="preserve">13.0235967636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1172924041748</t>
   </si>
   <si>
     <t xml:space="preserve">12.976749420166</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">12.3677320480347</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0866470336914</t>
+    <t xml:space="preserve">12.0866460800171</t>
   </si>
   <si>
     <t xml:space="preserve">11.9929523468018</t>
@@ -902,13 +902,13 @@
     <t xml:space="preserve">11.8992576599121</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0398006439209</t>
+    <t xml:space="preserve">12.0397987365723</t>
   </si>
   <si>
     <t xml:space="preserve">12.1334943771362</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4776306152344</t>
+    <t xml:space="preserve">11.4776296615601</t>
   </si>
   <si>
     <t xml:space="preserve">11.2433929443359</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">11.3839349746704</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6650190353394</t>
+    <t xml:space="preserve">11.6650199890137</t>
   </si>
   <si>
     <t xml:space="preserve">11.4307832717896</t>
@@ -929,10 +929,10 @@
     <t xml:space="preserve">10.7280693054199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1965446472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.571325302124</t>
+    <t xml:space="preserve">11.1965436935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5713243484497</t>
   </si>
   <si>
     <t xml:space="preserve">11.3370885848999</t>
@@ -941,7 +941,7 @@
     <t xml:space="preserve">11.2902402877808</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7118673324585</t>
+    <t xml:space="preserve">11.7118682861328</t>
   </si>
   <si>
     <t xml:space="preserve">11.7587146759033</t>
@@ -956,49 +956,49 @@
     <t xml:space="preserve">9.46318912506104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33884906768799</t>
+    <t xml:space="preserve">8.3388500213623</t>
   </si>
   <si>
     <t xml:space="preserve">8.57308578491211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31074047088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45128440856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61993408203125</t>
+    <t xml:space="preserve">8.31074142456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45128345489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61993503570557</t>
   </si>
   <si>
     <t xml:space="preserve">8.44191455841064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32948017120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25452518463135</t>
+    <t xml:space="preserve">8.32948112487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25452423095703</t>
   </si>
   <si>
     <t xml:space="preserve">8.43254470825195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47002124786377</t>
+    <t xml:space="preserve">8.47002220153809</t>
   </si>
   <si>
     <t xml:space="preserve">8.32011032104492</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20767688751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08587265014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78604984283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49559497833252</t>
+    <t xml:space="preserve">8.20767593383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0858736038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78605031967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49559545516968</t>
   </si>
   <si>
     <t xml:space="preserve">7.33631372451782</t>
@@ -1007,25 +1007,25 @@
     <t xml:space="preserve">7.23324918746948</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83289670944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9078516960144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50496482849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37379217147827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12081527709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28009605407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98027324676514</t>
+    <t xml:space="preserve">7.83289623260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90785264968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50496530532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37379169464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12081480026245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28009653091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98027276992798</t>
   </si>
   <si>
     <t xml:space="preserve">6.93342590332031</t>
@@ -1046,25 +1046,25 @@
     <t xml:space="preserve">8.19830703735352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21704769134521</t>
+    <t xml:space="preserve">8.2170467376709</t>
   </si>
   <si>
     <t xml:space="preserve">8.65194320678711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46116161346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53747367858887</t>
+    <t xml:space="preserve">8.46116256713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53747463226318</t>
   </si>
   <si>
     <t xml:space="preserve">8.68056106567383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77595138549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84272575378418</t>
+    <t xml:space="preserve">8.77595233917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8427267074585</t>
   </si>
   <si>
     <t xml:space="preserve">8.72825527191162</t>
@@ -1076,16 +1076,16 @@
     <t xml:space="preserve">8.49931812286377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42300605773926</t>
+    <t xml:space="preserve">8.42300510406494</t>
   </si>
   <si>
     <t xml:space="preserve">8.39438915252686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60424900054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48977851867676</t>
+    <t xml:space="preserve">8.604248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48977947235107</t>
   </si>
   <si>
     <t xml:space="preserve">8.29899787902832</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">8.12729454040527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89835596084595</t>
+    <t xml:space="preserve">7.89835643768311</t>
   </si>
   <si>
     <t xml:space="preserve">8.10821628570557</t>
@@ -1115,16 +1115,16 @@
     <t xml:space="preserve">8.07959938049316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07005977630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92697381973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98420763015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30853748321533</t>
+    <t xml:space="preserve">8.07005882263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92697429656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98420858383179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30853652954102</t>
   </si>
   <si>
     <t xml:space="preserve">8.26084136962891</t>
@@ -1139,10 +1139,10 @@
     <t xml:space="preserve">8.03190326690674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96513032913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86019945144653</t>
+    <t xml:space="preserve">7.96513080596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86019992828369</t>
   </si>
   <si>
     <t xml:space="preserve">7.86973905563354</t>
@@ -1154,19 +1154,19 @@
     <t xml:space="preserve">7.91743516921997</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76480960845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72665357589722</t>
+    <t xml:space="preserve">7.76481008529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72665309906006</t>
   </si>
   <si>
     <t xml:space="preserve">7.65034103393555</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63126182556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65987873077393</t>
+    <t xml:space="preserve">7.63126230239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65987968444824</t>
   </si>
   <si>
     <t xml:space="preserve">8.16545104980469</t>
@@ -1178,16 +1178,16 @@
     <t xml:space="preserve">8.11775588989258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93651151657104</t>
+    <t xml:space="preserve">7.93651247024536</t>
   </si>
   <si>
     <t xml:space="preserve">8.19406795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23222351074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31807708740234</t>
+    <t xml:space="preserve">8.2322244644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31807518005371</t>
   </si>
   <si>
     <t xml:space="preserve">8.15591144561768</t>
@@ -1199,31 +1199,31 @@
     <t xml:space="preserve">8.25130176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35623264312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2417631149292</t>
+    <t xml:space="preserve">8.35623168945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24176406860352</t>
   </si>
   <si>
     <t xml:space="preserve">8.34669303894043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95559072494507</t>
+    <t xml:space="preserve">7.95559167861938</t>
   </si>
   <si>
     <t xml:space="preserve">7.77434825897217</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82204437255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97466897964478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01282501220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05098056793213</t>
+    <t xml:space="preserve">7.82204389572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97466850280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01282596588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05098152160645</t>
   </si>
   <si>
     <t xml:space="preserve">7.67895746231079</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">7.73619174957275</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6980357170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5167932510376</t>
+    <t xml:space="preserve">7.69803524017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51679372787476</t>
   </si>
   <si>
     <t xml:space="preserve">7.59310626983643</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">7.62172269821167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52633237838745</t>
+    <t xml:space="preserve">7.52633190155029</t>
   </si>
   <si>
     <t xml:space="preserve">7.34508991241455</t>
@@ -1265,25 +1265,25 @@
     <t xml:space="preserve">7.14476871490479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12569093704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23062086105347</t>
+    <t xml:space="preserve">7.12569046020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23062133789062</t>
   </si>
   <si>
     <t xml:space="preserve">7.1543083190918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24969911575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24015998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46909761428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41186285018921</t>
+    <t xml:space="preserve">7.24969863891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24016046524048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46909809112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41186332702637</t>
   </si>
   <si>
     <t xml:space="preserve">7.45001983642578</t>
@@ -1295,34 +1295,34 @@
     <t xml:space="preserve">7.39278507232666</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33555126190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61218357086182</t>
+    <t xml:space="preserve">7.3355507850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61218404769897</t>
   </si>
   <si>
     <t xml:space="preserve">7.90789556503296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94605112075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45955848693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70757436752319</t>
+    <t xml:space="preserve">7.94605159759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45955896377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70757484436035</t>
   </si>
   <si>
     <t xml:space="preserve">7.8792781829834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99374723434448</t>
+    <t xml:space="preserve">7.99374771118164</t>
   </si>
   <si>
     <t xml:space="preserve">7.75527000427246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81250476837158</t>
+    <t xml:space="preserve">7.81250381469727</t>
   </si>
   <si>
     <t xml:space="preserve">7.79342699050903</t>
@@ -1331,25 +1331,25 @@
     <t xml:space="preserve">7.80296611785889</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85066032409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74573135375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83158254623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66941833496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60264539718628</t>
+    <t xml:space="preserve">7.85065984725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74573087692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83158302307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66941785812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60264492034912</t>
   </si>
   <si>
     <t xml:space="preserve">7.58356666564941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88881778717041</t>
+    <t xml:space="preserve">7.88881826400757</t>
   </si>
   <si>
     <t xml:space="preserve">8.00328636169434</t>
@@ -1361,7 +1361,7 @@
     <t xml:space="preserve">7.3641676902771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10661315917969</t>
+    <t xml:space="preserve">7.10661268234253</t>
   </si>
   <si>
     <t xml:space="preserve">7.27831649780273</t>
@@ -1376,10 +1376,10 @@
     <t xml:space="preserve">7.50372648239136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98721361160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02589321136475</t>
+    <t xml:space="preserve">7.98721408843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02589225769043</t>
   </si>
   <si>
     <t xml:space="preserve">8.04523086547852</t>
@@ -1391,25 +1391,25 @@
     <t xml:space="preserve">8.07424163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12259006500244</t>
+    <t xml:space="preserve">8.12258911132812</t>
   </si>
   <si>
     <t xml:space="preserve">8.05490112304688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94853448867798</t>
+    <t xml:space="preserve">7.94853496551514</t>
   </si>
   <si>
     <t xml:space="preserve">8.06457138061523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08391094207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97754383087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93886423110962</t>
+    <t xml:space="preserve">8.08390998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97754430770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93886518478394</t>
   </si>
   <si>
     <t xml:space="preserve">7.79381895065308</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">7.68745088577271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63910245895386</t>
+    <t xml:space="preserve">7.63910293579102</t>
   </si>
   <si>
     <t xml:space="preserve">7.73579978942871</t>
@@ -1436,10 +1436,10 @@
     <t xml:space="preserve">7.90985584259033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85183715820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83249807357788</t>
+    <t xml:space="preserve">7.85183668136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83249759674072</t>
   </si>
   <si>
     <t xml:space="preserve">7.81315755844116</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">7.80348825454712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78414869308472</t>
+    <t xml:space="preserve">7.78414916992188</t>
   </si>
   <si>
     <t xml:space="preserve">7.6681113243103</t>
@@ -1460,13 +1460,13 @@
     <t xml:space="preserve">7.71646022796631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75514030456543</t>
+    <t xml:space="preserve">7.75513982772827</t>
   </si>
   <si>
     <t xml:space="preserve">7.74547004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86150646209717</t>
+    <t xml:space="preserve">7.86150693893433</t>
   </si>
   <si>
     <t xml:space="preserve">7.89051580429077</t>
@@ -1484,10 +1484,10 @@
     <t xml:space="preserve">8.09358024597168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1322603225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15159893035889</t>
+    <t xml:space="preserve">8.13225936889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1515998840332</t>
   </si>
   <si>
     <t xml:space="preserve">8.1129207611084</t>
@@ -1496,10 +1496,10 @@
     <t xml:space="preserve">8.03556251525879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92919540405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69712114334106</t>
+    <t xml:space="preserve">7.92919492721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69712066650391</t>
   </si>
   <si>
     <t xml:space="preserve">7.60042381286621</t>
@@ -1508,10 +1508,10 @@
     <t xml:space="preserve">7.88084602355957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55207490921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40702867507935</t>
+    <t xml:space="preserve">7.55207443237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40702819824219</t>
   </si>
   <si>
     <t xml:space="preserve">7.34900999069214</t>
@@ -1520,16 +1520,16 @@
     <t xml:space="preserve">7.37801933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43603801727295</t>
+    <t xml:space="preserve">7.43603754043579</t>
   </si>
   <si>
     <t xml:space="preserve">7.41669797897339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5230655670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36834907531738</t>
+    <t xml:space="preserve">7.52306604385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36834955215454</t>
   </si>
   <si>
     <t xml:space="preserve">7.542405128479</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">7.4843864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70679092407227</t>
+    <t xml:space="preserve">7.70679044723511</t>
   </si>
   <si>
     <t xml:space="preserve">7.64877223968506</t>
@@ -1556,10 +1556,10 @@
     <t xml:space="preserve">7.59075355529785</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95820331573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96787357330322</t>
+    <t xml:space="preserve">7.95820426940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96787405014038</t>
   </si>
   <si>
     <t xml:space="preserve">7.90018606185913</t>
@@ -1577,10 +1577,10 @@
     <t xml:space="preserve">8.19027900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29664516448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45136070251465</t>
+    <t xml:space="preserve">8.29664611816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45136165618896</t>
   </si>
   <si>
     <t xml:space="preserve">8.48037147521973</t>
@@ -1607,19 +1607,19 @@
     <t xml:space="preserve">8.50938034057617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42235279083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54805850982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55772876739502</t>
+    <t xml:space="preserve">8.4223518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54805946350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55772972106934</t>
   </si>
   <si>
     <t xml:space="preserve">8.52871990203857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68343544006348</t>
+    <t xml:space="preserve">8.68343448638916</t>
   </si>
   <si>
     <t xml:space="preserve">8.76079368591309</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">8.65442562103271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75112342834473</t>
+    <t xml:space="preserve">8.75112438201904</t>
   </si>
   <si>
     <t xml:space="preserve">8.70277500152588</t>
@@ -1652,10 +1652,10 @@
     <t xml:space="preserve">8.63508701324463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32565498352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31598567962646</t>
+    <t xml:space="preserve">8.32565402984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31598472595215</t>
   </si>
   <si>
     <t xml:space="preserve">8.30631542205811</t>
@@ -62144,7 +62144,7 @@
     </row>
     <row r="2293">
       <c r="A2293" s="1" t="n">
-        <v>45954.6496064815</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2293" t="n">
         <v>34145</v>
@@ -62165,6 +62165,32 @@
         <v>733</v>
       </c>
       <c r="H2293" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2294">
+      <c r="A2294" s="1" t="n">
+        <v>45957.6912384259</v>
+      </c>
+      <c r="B2294" t="n">
+        <v>55487</v>
+      </c>
+      <c r="C2294" t="n">
+        <v>9.4399995803833</v>
+      </c>
+      <c r="D2294" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="E2294" t="n">
+        <v>9.38000011444092</v>
+      </c>
+      <c r="F2294" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="G2294" t="s">
+        <v>727</v>
+      </c>
+      <c r="H2294" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -44,16 +44,16 @@
     <t xml:space="preserve">FF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98565864562988</t>
+    <t xml:space="preserve">8.98565673828125</t>
   </si>
   <si>
     <t xml:space="preserve">9.08549785614014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24887466430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09457588195801</t>
+    <t xml:space="preserve">9.24887371063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09457492828369</t>
   </si>
   <si>
     <t xml:space="preserve">9.12180423736572</t>
@@ -74,13 +74,13 @@
     <t xml:space="preserve">8.84951019287109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85858726501465</t>
+    <t xml:space="preserve">8.85858821868896</t>
   </si>
   <si>
     <t xml:space="preserve">8.87674045562744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76782321929932</t>
+    <t xml:space="preserve">8.76782512664795</t>
   </si>
   <si>
     <t xml:space="preserve">8.8676643371582</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">8.96750545501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91304492950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92212200164795</t>
+    <t xml:space="preserve">8.91304588317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92212295532227</t>
   </si>
   <si>
     <t xml:space="preserve">9.00381088256836</t>
@@ -110,34 +110,34 @@
     <t xml:space="preserve">9.15810871124268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16718673706055</t>
+    <t xml:space="preserve">9.16718578338623</t>
   </si>
   <si>
     <t xml:space="preserve">9.43947792053223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54839611053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62100696563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80253505706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71177196502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56654930114746</t>
+    <t xml:space="preserve">9.54839515686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62100791931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80253601074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71177101135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56654834747314</t>
   </si>
   <si>
     <t xml:space="preserve">9.58470249176025</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57562446594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53024196624756</t>
+    <t xml:space="preserve">9.57562637329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53024387359619</t>
   </si>
   <si>
     <t xml:space="preserve">9.50301361083984</t>
@@ -149,13 +149,13 @@
     <t xml:space="preserve">9.63916015625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79345989227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95683479309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93868064880371</t>
+    <t xml:space="preserve">9.79345798492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95683574676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93868160247803</t>
   </si>
   <si>
     <t xml:space="preserve">9.98406410217285</t>
@@ -167,28 +167,28 @@
     <t xml:space="preserve">9.7662296295166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74807643890381</t>
+    <t xml:space="preserve">9.74807548522949</t>
   </si>
   <si>
     <t xml:space="preserve">9.75715351104736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64823627471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82068729400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7026948928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72084808349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67546558380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66638946533203</t>
+    <t xml:space="preserve">9.64823532104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82068920135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70269393920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72084712982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67546463012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66638851165771</t>
   </si>
   <si>
     <t xml:space="preserve">9.63008403778076</t>
@@ -197,7 +197,7 @@
     <t xml:space="preserve">9.65731239318848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68454074859619</t>
+    <t xml:space="preserve">9.68454265594482</t>
   </si>
   <si>
     <t xml:space="preserve">9.81161308288574</t>
@@ -212,67 +212,67 @@
     <t xml:space="preserve">9.83884143829346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72992324829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78438282012939</t>
+    <t xml:space="preserve">9.72992515563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78438377380371</t>
   </si>
   <si>
     <t xml:space="preserve">9.55747222900391</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34871387481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33963871002197</t>
+    <t xml:space="preserve">9.34871578216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33963775634766</t>
   </si>
   <si>
     <t xml:space="preserve">9.27610397338867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25795078277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19441509246826</t>
+    <t xml:space="preserve">9.25794982910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19441604614258</t>
   </si>
   <si>
     <t xml:space="preserve">9.18533802032471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41224956512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22164344787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31240844726562</t>
+    <t xml:space="preserve">9.4122486114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22164535522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31240940093994</t>
   </si>
   <si>
     <t xml:space="preserve">9.26702690124512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29425621032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28517913818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37594318389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.366868019104</t>
+    <t xml:space="preserve">9.29425525665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28518009185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37594413757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36686706542969</t>
   </si>
   <si>
     <t xml:space="preserve">9.38502025604248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45763206481934</t>
+    <t xml:space="preserve">9.45763111114502</t>
   </si>
   <si>
     <t xml:space="preserve">9.39409637451172</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48486042022705</t>
+    <t xml:space="preserve">9.48486137390137</t>
   </si>
   <si>
     <t xml:space="preserve">9.49393749237061</t>
@@ -287,37 +287,37 @@
     <t xml:space="preserve">9.23979759216309</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14903259277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21256923675537</t>
+    <t xml:space="preserve">9.14903354644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21256732940674</t>
   </si>
   <si>
     <t xml:space="preserve">9.20349216461182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13088035583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1399564743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94027614593506</t>
+    <t xml:space="preserve">9.13088130950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13995456695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94027519226074</t>
   </si>
   <si>
     <t xml:space="preserve">8.80412864685059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75874710083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66798305511475</t>
+    <t xml:space="preserve">8.75874614715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66798400878906</t>
   </si>
   <si>
     <t xml:space="preserve">8.62260150909424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53183650970459</t>
+    <t xml:space="preserve">8.53183555603027</t>
   </si>
   <si>
     <t xml:space="preserve">8.35030746459961</t>
@@ -326,10 +326,10 @@
     <t xml:space="preserve">8.16877937316895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98725032806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03263378143311</t>
+    <t xml:space="preserve">7.98725128173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03263282775879</t>
   </si>
   <si>
     <t xml:space="preserve">8.12339687347412</t>
@@ -338,13 +338,13 @@
     <t xml:space="preserve">8.25954532623291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94186925888062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30492687225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21416091918945</t>
+    <t xml:space="preserve">7.9418683052063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30492496490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21416187286377</t>
   </si>
   <si>
     <t xml:space="preserve">8.39568996429443</t>
@@ -356,22 +356,22 @@
     <t xml:space="preserve">8.71336650848389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53202247619629</t>
+    <t xml:space="preserve">9.53202342987061</t>
   </si>
   <si>
     <t xml:space="preserve">9.25706100463867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44036865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16540718078613</t>
+    <t xml:space="preserve">9.44036960601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16540622711182</t>
   </si>
   <si>
     <t xml:space="preserve">9.07375144958496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11958026885986</t>
+    <t xml:space="preserve">9.11957931518555</t>
   </si>
   <si>
     <t xml:space="preserve">8.98209857940674</t>
@@ -380,7 +380,7 @@
     <t xml:space="preserve">9.02792549133301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62367630004883</t>
+    <t xml:space="preserve">9.62367725372314</t>
   </si>
   <si>
     <t xml:space="preserve">9.80698490142822</t>
@@ -389,19 +389,19 @@
     <t xml:space="preserve">9.89863872528076</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99029350280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1736030578613</t>
+    <t xml:space="preserve">9.9902925491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1736011505127</t>
   </si>
   <si>
     <t xml:space="preserve">10.2652549743652</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3569097518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5402173995972</t>
+    <t xml:space="preserve">10.3569107055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5402183532715</t>
   </si>
   <si>
     <t xml:space="preserve">10.631872177124</t>
@@ -413,25 +413,25 @@
     <t xml:space="preserve">10.7235260009766</t>
   </si>
   <si>
-    <t xml:space="preserve">10.906834602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9984884262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.090142250061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1817951202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2734518051147</t>
+    <t xml:space="preserve">10.9068336486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9984874725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0901432037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1817960739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2734498977661</t>
   </si>
   <si>
     <t xml:space="preserve">11.4567584991455</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3651037216187</t>
+    <t xml:space="preserve">11.3651027679443</t>
   </si>
   <si>
     <t xml:space="preserve">10.4485635757446</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">9.71533203125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79878997802734</t>
+    <t xml:space="preserve">8.79879093170166</t>
   </si>
   <si>
     <t xml:space="preserve">8.24886608123779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21123218536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30288791656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03709125518799</t>
+    <t xml:space="preserve">9.21123313903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30288696289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03709030151367</t>
   </si>
   <si>
     <t xml:space="preserve">9.39454174041748</t>
@@ -479,10 +479,10 @@
     <t xml:space="preserve">9.73283004760742</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59378910064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96456432342529</t>
+    <t xml:space="preserve">9.59379005432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96456527709961</t>
   </si>
   <si>
     <t xml:space="preserve">9.91821670532227</t>
@@ -491,10 +491,10 @@
     <t xml:space="preserve">9.54744338989258</t>
   </si>
   <si>
-    <t xml:space="preserve">10.010910987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1036043167114</t>
+    <t xml:space="preserve">10.0109119415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1036033630371</t>
   </si>
   <si>
     <t xml:space="preserve">10.1499519348145</t>
@@ -512,10 +512,10 @@
     <t xml:space="preserve">10.057258605957</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2889928817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4743795394897</t>
+    <t xml:space="preserve">10.2889919281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4743804931641</t>
   </si>
   <si>
     <t xml:space="preserve">10.2426443099976</t>
@@ -533,13 +533,13 @@
     <t xml:space="preserve">9.50109672546387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31570816040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23228454589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19520854949951</t>
+    <t xml:space="preserve">9.31570911407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23228359222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1952075958252</t>
   </si>
   <si>
     <t xml:space="preserve">9.25082397460938</t>
@@ -548,31 +548,31 @@
     <t xml:space="preserve">9.269362449646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21374607086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04689693450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12105178833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0654354095459</t>
+    <t xml:space="preserve">9.2137451171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04689788818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12105274200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06543636322021</t>
   </si>
   <si>
     <t xml:space="preserve">8.97274303436279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17666816711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02835941314697</t>
+    <t xml:space="preserve">9.17666721343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02835750579834</t>
   </si>
   <si>
     <t xml:space="preserve">8.95420360565186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71320056915283</t>
+    <t xml:space="preserve">8.71319961547852</t>
   </si>
   <si>
     <t xml:space="preserve">8.99128150939941</t>
@@ -581,10 +581,10 @@
     <t xml:space="preserve">8.7688159942627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89858722686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93566608428955</t>
+    <t xml:space="preserve">8.89858818054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93566513061523</t>
   </si>
   <si>
     <t xml:space="preserve">10.3353395462036</t>
@@ -596,19 +596,19 @@
     <t xml:space="preserve">11.0305414199829</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2159280776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4940099716187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.540355682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5867023468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6330499649048</t>
+    <t xml:space="preserve">11.2159290313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4940090179443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5403566360474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5867033004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6330490112305</t>
   </si>
   <si>
     <t xml:space="preserve">11.7257432937622</t>
@@ -617,13 +617,13 @@
     <t xml:space="preserve">11.9111309051514</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9574775695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1892118453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2819042205811</t>
+    <t xml:space="preserve">11.9574766159058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1892099380493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2819051742554</t>
   </si>
   <si>
     <t xml:space="preserve">12.3745985031128</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">12.1428642272949</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0965175628662</t>
+    <t xml:space="preserve">12.0965185165405</t>
   </si>
   <si>
     <t xml:space="preserve">12.555121421814</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">12.7425117492676</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6956644058228</t>
+    <t xml:space="preserve">12.6956634521484</t>
   </si>
   <si>
     <t xml:space="preserve">12.2271890640259</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">12.1803417205811</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3208837509155</t>
+    <t xml:space="preserve">12.3208847045898</t>
   </si>
   <si>
     <t xml:space="preserve">12.274037361145</t>
@@ -686,34 +686,34 @@
     <t xml:space="preserve">12.9299020767212</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8830537796021</t>
+    <t xml:space="preserve">12.8830547332764</t>
   </si>
   <si>
     <t xml:space="preserve">13.0704441070557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6794624328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8668508529663</t>
+    <t xml:space="preserve">13.679461479187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8668518066406</t>
   </si>
   <si>
     <t xml:space="preserve">14.0542402267456</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3353252410889</t>
+    <t xml:space="preserve">14.3353261947632</t>
   </si>
   <si>
     <t xml:space="preserve">14.5695638656616</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2254276275635</t>
+    <t xml:space="preserve">15.2254266738892</t>
   </si>
   <si>
     <t xml:space="preserve">15.1317319869995</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7569532394409</t>
+    <t xml:space="preserve">14.7569522857666</t>
   </si>
   <si>
     <t xml:space="preserve">15.0380373001099</t>
@@ -731,7 +731,7 @@
     <t xml:space="preserve">15.4596662521362</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4128189086914</t>
+    <t xml:space="preserve">15.4128198623657</t>
   </si>
   <si>
     <t xml:space="preserve">15.5533599853516</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">16.8650894165039</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0056304931641</t>
+    <t xml:space="preserve">17.0056324005127</t>
   </si>
   <si>
     <t xml:space="preserve">16.7713928222656</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">17.0524806976318</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9587860107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7245464324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6308517456055</t>
+    <t xml:space="preserve">16.9587841033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7245483398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6308498382568</t>
   </si>
   <si>
     <t xml:space="preserve">16.5371570587158</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">16.584005355835</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2092227935791</t>
+    <t xml:space="preserve">16.2092247009277</t>
   </si>
   <si>
     <t xml:space="preserve">16.2560729980469</t>
@@ -788,10 +788,10 @@
     <t xml:space="preserve">15.8344430923462</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1155300140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0218372344971</t>
+    <t xml:space="preserve">16.1155281066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0218353271484</t>
   </si>
   <si>
     <t xml:space="preserve">16.1623764038086</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">17.0993270874023</t>
   </si>
   <si>
-    <t xml:space="preserve">16.677698135376</t>
+    <t xml:space="preserve">16.6776962280273</t>
   </si>
   <si>
     <t xml:space="preserve">16.8182430267334</t>
@@ -821,13 +821,13 @@
     <t xml:space="preserve">15.272274017334</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0848865509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.991189956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8038015365601</t>
+    <t xml:space="preserve">15.084885597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9911909103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8038005828857</t>
   </si>
   <si>
     <t xml:space="preserve">14.4758682250977</t>
@@ -836,7 +836,7 @@
     <t xml:space="preserve">14.382173538208</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1010885238647</t>
+    <t xml:space="preserve">14.1010875701904</t>
   </si>
   <si>
     <t xml:space="preserve">14.2884788513184</t>
@@ -848,13 +848,13 @@
     <t xml:space="preserve">13.960545539856</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2416315078735</t>
+    <t xml:space="preserve">14.2416305541992</t>
   </si>
   <si>
     <t xml:space="preserve">14.1947822570801</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0073928833008</t>
+    <t xml:space="preserve">14.0073938369751</t>
   </si>
   <si>
     <t xml:space="preserve">13.7263088226318</t>
@@ -869,13 +869,13 @@
     <t xml:space="preserve">14.6164102554321</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7731561660767</t>
+    <t xml:space="preserve">13.7731552124023</t>
   </si>
   <si>
     <t xml:space="preserve">13.3515291213989</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3046808242798</t>
+    <t xml:space="preserve">13.3046817779541</t>
   </si>
   <si>
     <t xml:space="preserve">13.3983764648438</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">13.0235958099365</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1172924041748</t>
+    <t xml:space="preserve">13.1172914505005</t>
   </si>
   <si>
     <t xml:space="preserve">12.9767484664917</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">12.0398006439209</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1334943771362</t>
+    <t xml:space="preserve">12.1334934234619</t>
   </si>
   <si>
     <t xml:space="preserve">11.4776306152344</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">11.1965446472168</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5713262557983</t>
+    <t xml:space="preserve">11.571325302124</t>
   </si>
   <si>
     <t xml:space="preserve">11.3370885848999</t>
@@ -941,22 +941,22 @@
     <t xml:space="preserve">11.2902402877808</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7118673324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7587146759033</t>
+    <t xml:space="preserve">11.7118663787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7587156295776</t>
   </si>
   <si>
     <t xml:space="preserve">11.8055629730225</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0091562271118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46318912506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33884906768799</t>
+    <t xml:space="preserve">11.0091552734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46318817138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33884811401367</t>
   </si>
   <si>
     <t xml:space="preserve">8.57308673858643</t>
@@ -965,13 +965,13 @@
     <t xml:space="preserve">8.31074142456055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45128345489502</t>
+    <t xml:space="preserve">8.45128440856934</t>
   </si>
   <si>
     <t xml:space="preserve">8.61993408203125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44191455841064</t>
+    <t xml:space="preserve">8.44191360473633</t>
   </si>
   <si>
     <t xml:space="preserve">8.32948017120361</t>
@@ -986,19 +986,19 @@
     <t xml:space="preserve">8.47002220153809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32011032104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20767688751221</t>
+    <t xml:space="preserve">8.32011127471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20767784118652</t>
   </si>
   <si>
     <t xml:space="preserve">8.08587265014648</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78604984283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49559497833252</t>
+    <t xml:space="preserve">7.78604936599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49559545516968</t>
   </si>
   <si>
     <t xml:space="preserve">7.33631372451782</t>
@@ -1013,13 +1013,13 @@
     <t xml:space="preserve">7.90785217285156</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50496530532837</t>
+    <t xml:space="preserve">7.50496482849121</t>
   </si>
   <si>
     <t xml:space="preserve">7.37379169464111</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12081575393677</t>
+    <t xml:space="preserve">7.12081527709961</t>
   </si>
   <si>
     <t xml:space="preserve">7.28009700775146</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">6.98027276992798</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93342542648315</t>
+    <t xml:space="preserve">6.93342590332031</t>
   </si>
   <si>
     <t xml:space="preserve">7.06459856033325</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">7.34568357467651</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54244327545166</t>
+    <t xml:space="preserve">7.5424427986145</t>
   </si>
   <si>
     <t xml:space="preserve">8.19830703735352</t>
@@ -62225,7 +62225,7 @@
     </row>
     <row r="2296">
       <c r="A2296" s="1" t="n">
-        <v>45959.6868055556</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B2296" t="n">
         <v>12031</v>
@@ -62246,6 +62246,32 @@
         <v>734</v>
       </c>
       <c r="H2296" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2297">
+      <c r="A2297" s="1" t="n">
+        <v>45960.6910532407</v>
+      </c>
+      <c r="B2297" t="n">
+        <v>22843</v>
+      </c>
+      <c r="C2297" t="n">
+        <v>9.35999965667725</v>
+      </c>
+      <c r="D2297" t="n">
+        <v>9.15999984741211</v>
+      </c>
+      <c r="E2297" t="n">
+        <v>9.35999965667725</v>
+      </c>
+      <c r="F2297" t="n">
+        <v>9.22000026702881</v>
+      </c>
+      <c r="G2297" t="s">
+        <v>725</v>
+      </c>
+      <c r="H2297" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="735" uniqueCount="735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="736">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07642269134521</t>
+    <t xml:space="preserve">9.0764217376709</t>
   </si>
   <si>
     <t xml:space="preserve">FF.MI</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">8.98565673828125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08549785614014</t>
+    <t xml:space="preserve">9.08549880981445</t>
   </si>
   <si>
     <t xml:space="preserve">9.24887371063232</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">9.09457492828369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12180423736572</t>
+    <t xml:space="preserve">9.12180328369141</t>
   </si>
   <si>
     <t xml:space="preserve">9.03104019165039</t>
@@ -68,85 +68,85 @@
     <t xml:space="preserve">8.8994312286377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89489269256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84951019287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85858821868896</t>
+    <t xml:space="preserve">8.89489364624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84951114654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85858726501465</t>
   </si>
   <si>
     <t xml:space="preserve">8.87674045562744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76782512664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8676643371582</t>
+    <t xml:space="preserve">8.767822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86766529083252</t>
   </si>
   <si>
     <t xml:space="preserve">9.04919338226318</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23072052001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11272621154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96750545501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91304588317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92212295532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00381088256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15810871124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16718578338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43947792053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54839515686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62100791931152</t>
+    <t xml:space="preserve">9.23072242736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11272811889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96750450134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91304683685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92212390899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00380992889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15811061859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16718673706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43947887420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54839611053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62100696563721</t>
   </si>
   <si>
     <t xml:space="preserve">9.80253601074219</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71177101135254</t>
+    <t xml:space="preserve">9.71177196502686</t>
   </si>
   <si>
     <t xml:space="preserve">9.56654834747314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58470249176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57562637329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53024387359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50301361083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60285472869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63916015625</t>
+    <t xml:space="preserve">9.58470153808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57562446594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53024196624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50301265716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60285377502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63915920257568</t>
   </si>
   <si>
     <t xml:space="preserve">9.79345798492432</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">9.95683574676514</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93868160247803</t>
+    <t xml:space="preserve">9.93868255615234</t>
   </si>
   <si>
     <t xml:space="preserve">9.98406410217285</t>
@@ -167,31 +167,31 @@
     <t xml:space="preserve">9.7662296295166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74807548522949</t>
+    <t xml:space="preserve">9.74807739257812</t>
   </si>
   <si>
     <t xml:space="preserve">9.75715351104736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64823532104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82068920135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70269393920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72084712982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67546463012695</t>
+    <t xml:space="preserve">9.64823627471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82068824768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7026948928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72084808349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67546558380127</t>
   </si>
   <si>
     <t xml:space="preserve">9.66638851165771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63008403778076</t>
+    <t xml:space="preserve">9.63008308410645</t>
   </si>
   <si>
     <t xml:space="preserve">9.65731239318848</t>
@@ -200,58 +200,58 @@
     <t xml:space="preserve">9.68454265594482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81161308288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82976627349854</t>
+    <t xml:space="preserve">9.81161212921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8297643661499</t>
   </si>
   <si>
     <t xml:space="preserve">9.8479175567627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83884143829346</t>
+    <t xml:space="preserve">9.83884048461914</t>
   </si>
   <si>
     <t xml:space="preserve">9.72992515563965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78438377380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55747222900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34871578216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33963775634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27610397338867</t>
+    <t xml:space="preserve">9.78438186645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55747318267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34871482849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33963680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27610301971436</t>
   </si>
   <si>
     <t xml:space="preserve">9.25794982910156</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19441604614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18533802032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4122486114502</t>
+    <t xml:space="preserve">9.19441699981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18533992767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41224956512451</t>
   </si>
   <si>
     <t xml:space="preserve">9.22164535522461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31240940093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26702690124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29425525665283</t>
+    <t xml:space="preserve">9.31240844726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2670259475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29425621032715</t>
   </si>
   <si>
     <t xml:space="preserve">9.28518009185791</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">9.36686706542969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38502025604248</t>
+    <t xml:space="preserve">9.38501930236816</t>
   </si>
   <si>
     <t xml:space="preserve">9.45763111114502</t>
@@ -272,37 +272,37 @@
     <t xml:space="preserve">9.39409637451172</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48486137390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49393749237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4485559463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47578430175781</t>
+    <t xml:space="preserve">9.48486042022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49393653869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44855499267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4757833480835</t>
   </si>
   <si>
     <t xml:space="preserve">9.23979759216309</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14903354644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21256732940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20349216461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13088130950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13995456695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94027519226074</t>
+    <t xml:space="preserve">9.14903259277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21256828308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20349407196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13088035583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1399564743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94027614593506</t>
   </si>
   <si>
     <t xml:space="preserve">8.80412864685059</t>
@@ -314,61 +314,61 @@
     <t xml:space="preserve">8.66798400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62260150909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53183555603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35030746459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16877937316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98725128173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03263282775879</t>
+    <t xml:space="preserve">8.62260055541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53183746337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35030937194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16878032684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98725175857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03263473510742</t>
   </si>
   <si>
     <t xml:space="preserve">8.12339687347412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25954532623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9418683052063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30492496490479</t>
+    <t xml:space="preserve">8.25954437255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94186925888062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3049259185791</t>
   </si>
   <si>
     <t xml:space="preserve">8.21416187286377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39568996429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5772180557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71336650848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53202342987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25706100463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44036960601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16540622711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07375144958496</t>
+    <t xml:space="preserve">8.39569091796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57721900939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71336555480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53202247619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25706195831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44036865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16540718078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07375335693359</t>
   </si>
   <si>
     <t xml:space="preserve">9.11957931518555</t>
@@ -377,19 +377,19 @@
     <t xml:space="preserve">8.98209857940674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02792549133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62367725372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80698490142822</t>
+    <t xml:space="preserve">9.02792644500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62367630004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80698585510254</t>
   </si>
   <si>
     <t xml:space="preserve">9.89863872528076</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9902925491333</t>
+    <t xml:space="preserve">9.99029350280762</t>
   </si>
   <si>
     <t xml:space="preserve">10.1736011505127</t>
@@ -416,13 +416,13 @@
     <t xml:space="preserve">10.9068336486816</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9984874725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0901432037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1817960739136</t>
+    <t xml:space="preserve">10.9984884262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.090142250061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1817970275879</t>
   </si>
   <si>
     <t xml:space="preserve">11.2734498977661</t>
@@ -431,34 +431,34 @@
     <t xml:space="preserve">11.4567584991455</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3651027679443</t>
+    <t xml:space="preserve">11.3651037216187</t>
   </si>
   <si>
     <t xml:space="preserve">10.4485635757446</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71533203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79879093170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24886608123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21123313903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30288696289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03709030151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39454174041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76115703582764</t>
+    <t xml:space="preserve">9.71533107757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79878997802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24886512756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2112340927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30288887023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03709125518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39454078674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76115798950195</t>
   </si>
   <si>
     <t xml:space="preserve">9.66950416564941</t>
@@ -470,10 +470,10 @@
     <t xml:space="preserve">10.0361204147339</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94446659088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82552528381348</t>
+    <t xml:space="preserve">9.94446563720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82552433013916</t>
   </si>
   <si>
     <t xml:space="preserve">9.73283004760742</t>
@@ -485,16 +485,16 @@
     <t xml:space="preserve">9.96456527709961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91821670532227</t>
+    <t xml:space="preserve">9.9182186126709</t>
   </si>
   <si>
     <t xml:space="preserve">9.54744338989258</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0109119415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1036033630371</t>
+    <t xml:space="preserve">10.010910987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1036052703857</t>
   </si>
   <si>
     <t xml:space="preserve">10.1499519348145</t>
@@ -503,13 +503,13 @@
     <t xml:space="preserve">10.1962985992432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77917671203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87187004089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.057258605957</t>
+    <t xml:space="preserve">9.77917766571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87187099456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0572576522827</t>
   </si>
   <si>
     <t xml:space="preserve">10.2889919281006</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">10.4743804931641</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2426443099976</t>
+    <t xml:space="preserve">10.2426452636719</t>
   </si>
   <si>
     <t xml:space="preserve">10.381685256958</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">9.64013671875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50109672546387</t>
+    <t xml:space="preserve">9.50109577178955</t>
   </si>
   <si>
     <t xml:space="preserve">9.31570911407471</t>
@@ -542,58 +542,58 @@
     <t xml:space="preserve">9.1952075958252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25082397460938</t>
+    <t xml:space="preserve">9.25082302093506</t>
   </si>
   <si>
     <t xml:space="preserve">9.269362449646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2137451171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04689788818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12105274200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06543636322021</t>
+    <t xml:space="preserve">9.21374607086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04689693450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12105369567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0654354095459</t>
   </si>
   <si>
     <t xml:space="preserve">8.97274303436279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17666721343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02835750579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95420360565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71319961547852</t>
+    <t xml:space="preserve">9.17666912078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02835845947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95420265197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71320056915283</t>
   </si>
   <si>
     <t xml:space="preserve">8.99128150939941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7688159942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89858818054199</t>
+    <t xml:space="preserve">8.76881694793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89858722686768</t>
   </si>
   <si>
     <t xml:space="preserve">8.93566513061523</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3353395462036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9841947555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0305414199829</t>
+    <t xml:space="preserve">10.3353385925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9841938018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0305404663086</t>
   </si>
   <si>
     <t xml:space="preserve">11.2159290313721</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">11.4940090179443</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5403566360474</t>
+    <t xml:space="preserve">11.540355682373</t>
   </si>
   <si>
     <t xml:space="preserve">11.5867033004761</t>
@@ -611,10 +611,10 @@
     <t xml:space="preserve">11.6330490112305</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7257432937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9111309051514</t>
+    <t xml:space="preserve">11.7257413864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9111299514771</t>
   </si>
   <si>
     <t xml:space="preserve">11.9574766159058</t>
@@ -623,7 +623,7 @@
     <t xml:space="preserve">12.1892099380493</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2819051742554</t>
+    <t xml:space="preserve">12.2819042205811</t>
   </si>
   <si>
     <t xml:space="preserve">12.3745985031128</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">12.3282518386841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1428642272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0965185165405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.555121421814</t>
+    <t xml:space="preserve">12.1428651809692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0965175628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5551223754883</t>
   </si>
   <si>
     <t xml:space="preserve">12.5082750320435</t>
@@ -650,121 +650,121 @@
     <t xml:space="preserve">12.6488170623779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4614267349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4145784378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7425117492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6956634521484</t>
+    <t xml:space="preserve">12.4614276885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4145793914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7425127029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6956644058228</t>
   </si>
   <si>
     <t xml:space="preserve">12.2271890640259</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1803417205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3208847045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.274037361145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8362064361572</t>
+    <t xml:space="preserve">12.1803426742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3208837509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2740383148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8362073898315</t>
   </si>
   <si>
     <t xml:space="preserve">12.7893590927124</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6019697189331</t>
+    <t xml:space="preserve">12.6019687652588</t>
   </si>
   <si>
     <t xml:space="preserve">12.9299020767212</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8830547332764</t>
+    <t xml:space="preserve">12.8830537796021</t>
   </si>
   <si>
     <t xml:space="preserve">13.0704441070557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.679461479187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8668518066406</t>
+    <t xml:space="preserve">13.6794605255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8668508529663</t>
   </si>
   <si>
     <t xml:space="preserve">14.0542402267456</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3353261947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5695638656616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2254266738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1317319869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7569522857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0380373001099</t>
+    <t xml:space="preserve">14.3353252410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5695629119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2254276275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1317329406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7569532394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0380382537842</t>
   </si>
   <si>
     <t xml:space="preserve">15.1785802841187</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3191223144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8974952697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4596662521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4128198623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5533599853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0686817169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8650894165039</t>
+    <t xml:space="preserve">15.3191242218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8974943161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4596652984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4128179550171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5533609390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0686836242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8650875091553</t>
   </si>
   <si>
     <t xml:space="preserve">17.0056324005127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7713928222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1930198669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0524806976318</t>
+    <t xml:space="preserve">16.7713947296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1930236816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0524787902832</t>
   </si>
   <si>
     <t xml:space="preserve">16.9587841033936</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7245483398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6308498382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5371570587158</t>
+    <t xml:space="preserve">16.7245464324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6308536529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5371551513672</t>
   </si>
   <si>
     <t xml:space="preserve">16.584005355835</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">16.2092247009277</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2560729980469</t>
+    <t xml:space="preserve">16.2560749053955</t>
   </si>
   <si>
     <t xml:space="preserve">17.1461734771729</t>
@@ -782,13 +782,13 @@
     <t xml:space="preserve">16.396614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3029193878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8344430923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1155281066895</t>
+    <t xml:space="preserve">16.3029174804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8344440460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1155300140381</t>
   </si>
   <si>
     <t xml:space="preserve">16.0218353271484</t>
@@ -797,37 +797,37 @@
     <t xml:space="preserve">16.1623764038086</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9749879837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7407484054565</t>
+    <t xml:space="preserve">15.974986076355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7407503128052</t>
   </si>
   <si>
     <t xml:space="preserve">16.4434623718262</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9119358062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0993270874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6776962280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8182430267334</t>
+    <t xml:space="preserve">16.9119338989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0993251800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.677698135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.818244934082</t>
   </si>
   <si>
     <t xml:space="preserve">15.272274017334</t>
   </si>
   <si>
-    <t xml:space="preserve">15.084885597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9911909103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8038005828857</t>
+    <t xml:space="preserve">15.0848846435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.991189956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8037996292114</t>
   </si>
   <si>
     <t xml:space="preserve">14.4758682250977</t>
@@ -836,34 +836,34 @@
     <t xml:space="preserve">14.382173538208</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1010875701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2884788513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5227155685425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.960545539856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2416305541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1947822570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0073938369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7263088226318</t>
+    <t xml:space="preserve">14.1010885238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.288477897644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5227146148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9605445861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2416296005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1947832107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0073928833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7263078689575</t>
   </si>
   <si>
     <t xml:space="preserve">14.1479358673096</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4290208816528</t>
+    <t xml:space="preserve">14.4290199279785</t>
   </si>
   <si>
     <t xml:space="preserve">14.6164102554321</t>
@@ -881,13 +881,13 @@
     <t xml:space="preserve">13.3983764648438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0235958099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1172914505005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9767484664917</t>
+    <t xml:space="preserve">13.0235967636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1172924041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.976749420166</t>
   </si>
   <si>
     <t xml:space="preserve">12.3677320480347</t>
@@ -896,31 +896,31 @@
     <t xml:space="preserve">12.0866470336914</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9929523468018</t>
+    <t xml:space="preserve">11.9929533004761</t>
   </si>
   <si>
     <t xml:space="preserve">11.8992576599121</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0398006439209</t>
+    <t xml:space="preserve">12.0397987365723</t>
   </si>
   <si>
     <t xml:space="preserve">12.1334934234619</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4776306152344</t>
+    <t xml:space="preserve">11.4776287078857</t>
   </si>
   <si>
     <t xml:space="preserve">11.2433929443359</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3839349746704</t>
+    <t xml:space="preserve">11.3839340209961</t>
   </si>
   <si>
     <t xml:space="preserve">11.6650190353394</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4307823181152</t>
+    <t xml:space="preserve">11.4307832717896</t>
   </si>
   <si>
     <t xml:space="preserve">10.9623079299927</t>
@@ -929,34 +929,34 @@
     <t xml:space="preserve">10.7280702590942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1965446472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.571325302124</t>
+    <t xml:space="preserve">11.1965436935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5713243484497</t>
   </si>
   <si>
     <t xml:space="preserve">11.3370885848999</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2902402877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7118663787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7587156295776</t>
+    <t xml:space="preserve">11.2902393341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7118682861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.758713722229</t>
   </si>
   <si>
     <t xml:space="preserve">11.8055629730225</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0091552734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46318817138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33884811401367</t>
+    <t xml:space="preserve">11.0091543197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46319007873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33884906768799</t>
   </si>
   <si>
     <t xml:space="preserve">8.57308673858643</t>
@@ -965,7 +965,7 @@
     <t xml:space="preserve">8.31074142456055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45128440856934</t>
+    <t xml:space="preserve">8.45128345489502</t>
   </si>
   <si>
     <t xml:space="preserve">8.61993408203125</t>
@@ -974,13 +974,13 @@
     <t xml:space="preserve">8.44191360473633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32948017120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25452518463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43254470825195</t>
+    <t xml:space="preserve">8.32948112487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25452423095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43254375457764</t>
   </si>
   <si>
     <t xml:space="preserve">8.47002220153809</t>
@@ -989,46 +989,46 @@
     <t xml:space="preserve">8.32011127471924</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20767784118652</t>
+    <t xml:space="preserve">8.20767688751221</t>
   </si>
   <si>
     <t xml:space="preserve">8.08587265014648</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78604936599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49559545516968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33631372451782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23324966430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83289623260498</t>
+    <t xml:space="preserve">7.78605031967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49559497833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33631420135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23324918746948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83289670944214</t>
   </si>
   <si>
     <t xml:space="preserve">7.90785217285156</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50496482849121</t>
+    <t xml:space="preserve">7.50496530532837</t>
   </si>
   <si>
     <t xml:space="preserve">7.37379169464111</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12081527709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28009700775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98027276992798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93342590332031</t>
+    <t xml:space="preserve">7.12081480026245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28009653091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98027229309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93342542648315</t>
   </si>
   <si>
     <t xml:space="preserve">7.06459856033325</t>
@@ -1037,10 +1037,10 @@
     <t xml:space="preserve">7.0271201133728</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34568357467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5424427986145</t>
+    <t xml:space="preserve">7.34568309783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54244232177734</t>
   </si>
   <si>
     <t xml:space="preserve">8.19830703735352</t>
@@ -1052,31 +1052,31 @@
     <t xml:space="preserve">8.65194320678711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46116161346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53747367858887</t>
+    <t xml:space="preserve">8.46116256713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53747463226318</t>
   </si>
   <si>
     <t xml:space="preserve">8.68056106567383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77595138549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84272575378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825622558594</t>
+    <t xml:space="preserve">8.77595233917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8427267074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825527191162</t>
   </si>
   <si>
     <t xml:space="preserve">8.66148281097412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49931716918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42300605773926</t>
+    <t xml:space="preserve">8.49931812286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42300510406494</t>
   </si>
   <si>
     <t xml:space="preserve">8.39438915252686</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">8.604248046875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48977851867676</t>
+    <t xml:space="preserve">8.48977947235107</t>
   </si>
   <si>
     <t xml:space="preserve">8.29899787902832</t>
@@ -1094,19 +1094,19 @@
     <t xml:space="preserve">8.12729454040527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89835596084595</t>
+    <t xml:space="preserve">7.89835643768311</t>
   </si>
   <si>
     <t xml:space="preserve">8.10821628570557</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8411226272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33715438842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20360660552979</t>
+    <t xml:space="preserve">7.84112215042114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33715343475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2036075592041</t>
   </si>
   <si>
     <t xml:space="preserve">8.06052017211914</t>
@@ -1115,13 +1115,13 @@
     <t xml:space="preserve">8.07959938049316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07005977630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92697381973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98420763015747</t>
+    <t xml:space="preserve">8.07005882263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92697429656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98420858383179</t>
   </si>
   <si>
     <t xml:space="preserve">8.30853652954102</t>
@@ -1130,67 +1130,67 @@
     <t xml:space="preserve">8.26084136962891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2703800201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18452930450439</t>
+    <t xml:space="preserve">8.27038097381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18452835083008</t>
   </si>
   <si>
     <t xml:space="preserve">8.03190326690674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96513032913208</t>
+    <t xml:space="preserve">7.96513080596924</t>
   </si>
   <si>
     <t xml:space="preserve">7.86019992828369</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8697395324707</t>
+    <t xml:space="preserve">7.86973905563354</t>
   </si>
   <si>
     <t xml:space="preserve">7.71711397171021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91743421554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76480960845947</t>
+    <t xml:space="preserve">7.91743516921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76481008529663</t>
   </si>
   <si>
     <t xml:space="preserve">7.72665309906006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65034055709839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63126182556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65987920761108</t>
+    <t xml:space="preserve">7.65034103393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63126230239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65987968444824</t>
   </si>
   <si>
     <t xml:space="preserve">8.16545104980469</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32761478424072</t>
+    <t xml:space="preserve">8.32761383056641</t>
   </si>
   <si>
     <t xml:space="preserve">8.11775588989258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93651151657104</t>
+    <t xml:space="preserve">7.93651247024536</t>
   </si>
   <si>
     <t xml:space="preserve">8.19406795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23222351074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31807613372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15591239929199</t>
+    <t xml:space="preserve">8.2322244644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31807518005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15591144561768</t>
   </si>
   <si>
     <t xml:space="preserve">8.22268486022949</t>
@@ -1199,16 +1199,16 @@
     <t xml:space="preserve">8.25130176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35623264312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2417631149292</t>
+    <t xml:space="preserve">8.35623168945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24176406860352</t>
   </si>
   <si>
     <t xml:space="preserve">8.34669303894043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95559072494507</t>
+    <t xml:space="preserve">7.95559167861938</t>
   </si>
   <si>
     <t xml:space="preserve">7.77434825897217</t>
@@ -1217,40 +1217,40 @@
     <t xml:space="preserve">7.82204389572144</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97466802597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01282405853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05098056793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67895793914795</t>
+    <t xml:space="preserve">7.97466850280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01282596588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05098152160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67895746231079</t>
   </si>
   <si>
     <t xml:space="preserve">7.73619174957275</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6980357170105</t>
+    <t xml:space="preserve">7.69803524017334</t>
   </si>
   <si>
     <t xml:space="preserve">7.51679372787476</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59310579299927</t>
+    <t xml:space="preserve">7.59310626983643</t>
   </si>
   <si>
     <t xml:space="preserve">7.44048070907593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53587198257446</t>
+    <t xml:space="preserve">7.5358715057373</t>
   </si>
   <si>
     <t xml:space="preserve">7.62172269821167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52633237838745</t>
+    <t xml:space="preserve">7.52633190155029</t>
   </si>
   <si>
     <t xml:space="preserve">7.34508991241455</t>
@@ -1262,31 +1262,31 @@
     <t xml:space="preserve">7.18292570114136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14476919174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12569093704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23062086105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15430784225464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24969911575317</t>
+    <t xml:space="preserve">7.14476871490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12569046020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23062133789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1543083190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24969863891602</t>
   </si>
   <si>
     <t xml:space="preserve">7.24016046524048</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46909761428833</t>
+    <t xml:space="preserve">7.46909809112549</t>
   </si>
   <si>
     <t xml:space="preserve">7.41186332702637</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45001935958862</t>
+    <t xml:space="preserve">7.45001983642578</t>
   </si>
   <si>
     <t xml:space="preserve">7.28785514831543</t>
@@ -1298,31 +1298,31 @@
     <t xml:space="preserve">7.3355507850647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61218357086182</t>
+    <t xml:space="preserve">7.61218404769897</t>
   </si>
   <si>
     <t xml:space="preserve">7.90789556503296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94605112075806</t>
+    <t xml:space="preserve">7.94605159759521</t>
   </si>
   <si>
     <t xml:space="preserve">7.45955896377563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70757436752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87927865982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99374723434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75527048110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81250476837158</t>
+    <t xml:space="preserve">7.70757484436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8792781829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99374771118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75527000427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81250381469727</t>
   </si>
   <si>
     <t xml:space="preserve">7.79342699050903</t>
@@ -1331,16 +1331,16 @@
     <t xml:space="preserve">7.80296611785889</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85066080093384</t>
+    <t xml:space="preserve">7.85065984725952</t>
   </si>
   <si>
     <t xml:space="preserve">7.74573087692261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83158349990845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66941833496094</t>
+    <t xml:space="preserve">7.83158302307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66941785812378</t>
   </si>
   <si>
     <t xml:space="preserve">7.60264492034912</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">7.58356666564941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88881778717041</t>
+    <t xml:space="preserve">7.88881826400757</t>
   </si>
   <si>
     <t xml:space="preserve">8.00328636169434</t>
@@ -1358,10 +1358,10 @@
     <t xml:space="preserve">7.78388738632202</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36416816711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10661315917969</t>
+    <t xml:space="preserve">7.3641676902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10661268234253</t>
   </si>
   <si>
     <t xml:space="preserve">7.27831649780273</t>
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">7.08753490447998</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05891752243042</t>
+    <t xml:space="preserve">7.05891799926758</t>
   </si>
   <si>
     <t xml:space="preserve">7.50372648239136</t>
@@ -2217,6 +2217,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.38000011444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30000019073486</t>
   </si>
 </sst>
 </file>
@@ -62251,7 +62254,7 @@
     </row>
     <row r="2297">
       <c r="A2297" s="1" t="n">
-        <v>45960.6910532407</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2297" t="n">
         <v>22843</v>
@@ -62272,6 +62275,32 @@
         <v>725</v>
       </c>
       <c r="H2297" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2298">
+      <c r="A2298" s="1" t="n">
+        <v>45961.6910648148</v>
+      </c>
+      <c r="B2298" t="n">
+        <v>16867</v>
+      </c>
+      <c r="C2298" t="n">
+        <v>9.34000015258789</v>
+      </c>
+      <c r="D2298" t="n">
+        <v>9.22000026702881</v>
+      </c>
+      <c r="E2298" t="n">
+        <v>9.31999969482422</v>
+      </c>
+      <c r="F2298" t="n">
+        <v>9.30000019073486</v>
+      </c>
+      <c r="G2298" t="s">
+        <v>735</v>
+      </c>
+      <c r="H2298" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -53,10 +53,10 @@
     <t xml:space="preserve">9.24887371063232</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09457492828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12180328369141</t>
+    <t xml:space="preserve">9.09457397460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12180519104004</t>
   </si>
   <si>
     <t xml:space="preserve">9.03104019165039</t>
@@ -65,43 +65,43 @@
     <t xml:space="preserve">8.95388984680176</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8994312286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89489364624023</t>
+    <t xml:space="preserve">8.89943218231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89489269256592</t>
   </si>
   <si>
     <t xml:space="preserve">8.84951114654541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85858726501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87674045562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.767822265625</t>
+    <t xml:space="preserve">8.85858821868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87673950195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76782321929932</t>
   </si>
   <si>
     <t xml:space="preserve">8.86766529083252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04919338226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23072242736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11272811889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96750450134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91304683685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92212390899658</t>
+    <t xml:space="preserve">9.04919242858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23072147369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11272716522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96750354766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91304588317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92212200164795</t>
   </si>
   <si>
     <t xml:space="preserve">9.00380992889404</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">9.15811061859131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16718673706055</t>
+    <t xml:space="preserve">9.16718578338623</t>
   </si>
   <si>
     <t xml:space="preserve">9.43947887420654</t>
@@ -119,52 +119,52 @@
     <t xml:space="preserve">9.54839611053467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62100696563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80253601074219</t>
+    <t xml:space="preserve">9.62100601196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8025369644165</t>
   </si>
   <si>
     <t xml:space="preserve">9.71177196502686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56654834747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58470153808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57562446594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53024196624756</t>
+    <t xml:space="preserve">9.56654930114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58470249176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57562351226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53024387359619</t>
   </si>
   <si>
     <t xml:space="preserve">9.50301265716553</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60285377502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63915920257568</t>
+    <t xml:space="preserve">9.60285472869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63916110992432</t>
   </si>
   <si>
     <t xml:space="preserve">9.79345798492432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95683574676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93868255615234</t>
+    <t xml:space="preserve">9.95683479309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93868160247803</t>
   </si>
   <si>
     <t xml:space="preserve">9.98406410217285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73900127410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7662296295166</t>
+    <t xml:space="preserve">9.73900032043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76623058319092</t>
   </si>
   <si>
     <t xml:space="preserve">9.74807739257812</t>
@@ -176,13 +176,13 @@
     <t xml:space="preserve">9.64823627471924</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82068824768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7026948928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72084808349609</t>
+    <t xml:space="preserve">9.82068920135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70269393920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72084712982178</t>
   </si>
   <si>
     <t xml:space="preserve">9.67546558380127</t>
@@ -191,16 +191,16 @@
     <t xml:space="preserve">9.66638851165771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63008308410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65731239318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68454265594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81161212921143</t>
+    <t xml:space="preserve">9.63008213043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65731430053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68454170227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81161308288574</t>
   </si>
   <si>
     <t xml:space="preserve">9.8297643661499</t>
@@ -212,22 +212,22 @@
     <t xml:space="preserve">9.83884048461914</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72992515563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78438186645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55747318267822</t>
+    <t xml:space="preserve">9.72992420196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78438377380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55747127532959</t>
   </si>
   <si>
     <t xml:space="preserve">9.34871482849121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33963680267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27610301971436</t>
+    <t xml:space="preserve">9.33963775634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27610397338867</t>
   </si>
   <si>
     <t xml:space="preserve">9.25794982910156</t>
@@ -236,64 +236,64 @@
     <t xml:space="preserve">9.19441699981689</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18533992767334</t>
+    <t xml:space="preserve">9.18533802032471</t>
   </si>
   <si>
     <t xml:space="preserve">9.41224956512451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22164535522461</t>
+    <t xml:space="preserve">9.22164440155029</t>
   </si>
   <si>
     <t xml:space="preserve">9.31240844726562</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2670259475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29425621032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28518009185791</t>
+    <t xml:space="preserve">9.26702690124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29425525665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28517913818359</t>
   </si>
   <si>
     <t xml:space="preserve">9.37594413757324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36686706542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38501930236816</t>
+    <t xml:space="preserve">9.366868019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38502025604248</t>
   </si>
   <si>
     <t xml:space="preserve">9.45763111114502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39409637451172</t>
+    <t xml:space="preserve">9.39409732818604</t>
   </si>
   <si>
     <t xml:space="preserve">9.48486042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49393653869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44855499267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4757833480835</t>
+    <t xml:space="preserve">9.49393844604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4485559463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47578430175781</t>
   </si>
   <si>
     <t xml:space="preserve">9.23979759216309</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14903259277344</t>
+    <t xml:space="preserve">9.14903354644775</t>
   </si>
   <si>
     <t xml:space="preserve">9.21256828308105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20349407196045</t>
+    <t xml:space="preserve">9.20349216461182</t>
   </si>
   <si>
     <t xml:space="preserve">9.13088035583496</t>
@@ -302,25 +302,25 @@
     <t xml:space="preserve">9.1399564743042</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94027614593506</t>
+    <t xml:space="preserve">8.94027519226074</t>
   </si>
   <si>
     <t xml:space="preserve">8.80412864685059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75874614715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66798400878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62260055541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53183746337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35030937194824</t>
+    <t xml:space="preserve">8.75874710083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66798305511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62260150909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53183650970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35030746459961</t>
   </si>
   <si>
     <t xml:space="preserve">8.16878032684326</t>
@@ -329,64 +329,64 @@
     <t xml:space="preserve">7.98725175857544</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03263473510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12339687347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25954437255859</t>
+    <t xml:space="preserve">8.03263378143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12339782714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25954341888428</t>
   </si>
   <si>
     <t xml:space="preserve">7.94186925888062</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3049259185791</t>
+    <t xml:space="preserve">8.30492496490479</t>
   </si>
   <si>
     <t xml:space="preserve">8.21416187286377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39569091796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57721900939941</t>
+    <t xml:space="preserve">8.39568901062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5772180557251</t>
   </si>
   <si>
     <t xml:space="preserve">8.71336555480957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53202247619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25706195831299</t>
+    <t xml:space="preserve">9.53202342987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25706005096436</t>
   </si>
   <si>
     <t xml:space="preserve">9.44036865234375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16540718078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07375335693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11957931518555</t>
+    <t xml:space="preserve">9.16540622711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07375144958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11958026885986</t>
   </si>
   <si>
     <t xml:space="preserve">8.98209857940674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02792644500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62367630004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80698585510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89863872528076</t>
+    <t xml:space="preserve">9.02792549133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62367820739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80698490142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89863967895508</t>
   </si>
   <si>
     <t xml:space="preserve">9.99029350280762</t>
@@ -395,13 +395,13 @@
     <t xml:space="preserve">10.1736011505127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2652549743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3569107055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5402183532715</t>
+    <t xml:space="preserve">10.2652540206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3569087982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5402173995972</t>
   </si>
   <si>
     <t xml:space="preserve">10.631872177124</t>
@@ -410,22 +410,22 @@
     <t xml:space="preserve">10.8151798248291</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7235260009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9068336486816</t>
+    <t xml:space="preserve">10.7235250473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.906834602356</t>
   </si>
   <si>
     <t xml:space="preserve">10.9984884262085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.090142250061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1817970275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2734498977661</t>
+    <t xml:space="preserve">11.0901432037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1817960739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2734508514404</t>
   </si>
   <si>
     <t xml:space="preserve">11.4567584991455</t>
@@ -434,34 +434,34 @@
     <t xml:space="preserve">11.3651037216187</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4485635757446</t>
+    <t xml:space="preserve">10.4485626220703</t>
   </si>
   <si>
     <t xml:space="preserve">9.71533107757568</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79878997802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24886512756348</t>
+    <t xml:space="preserve">8.79879093170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24886703491211</t>
   </si>
   <si>
     <t xml:space="preserve">9.2112340927124</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30288887023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03709125518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39454078674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76115798950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66950416564941</t>
+    <t xml:space="preserve">9.30288791656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03709030151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39454174041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76115608215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6695032119751</t>
   </si>
   <si>
     <t xml:space="preserve">9.57784938812256</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">9.82552433013916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73283004760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59379005432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96456527709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9182186126709</t>
+    <t xml:space="preserve">9.73283100128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59379100799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96456432342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91821670532227</t>
   </si>
   <si>
     <t xml:space="preserve">9.54744338989258</t>
@@ -494,19 +494,19 @@
     <t xml:space="preserve">10.010910987854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1036052703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1499519348145</t>
+    <t xml:space="preserve">10.1036043167114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1499509811401</t>
   </si>
   <si>
     <t xml:space="preserve">10.1962985992432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77917766571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87187099456787</t>
+    <t xml:space="preserve">9.77917671203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87186908721924</t>
   </si>
   <si>
     <t xml:space="preserve">10.0572576522827</t>
@@ -515,28 +515,28 @@
     <t xml:space="preserve">10.2889919281006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4743804931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2426452636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.381685256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68648338317871</t>
+    <t xml:space="preserve">10.4743795394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2426462173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3816862106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68648433685303</t>
   </si>
   <si>
     <t xml:space="preserve">9.64013671875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50109577178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31570911407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23228359222412</t>
+    <t xml:space="preserve">9.50109672546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31571006774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23228454589844</t>
   </si>
   <si>
     <t xml:space="preserve">9.1952075958252</t>
@@ -545,25 +545,25 @@
     <t xml:space="preserve">9.25082302093506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.269362449646</t>
+    <t xml:space="preserve">9.26936149597168</t>
   </si>
   <si>
     <t xml:space="preserve">9.21374607086182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04689693450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12105369567871</t>
+    <t xml:space="preserve">9.04689788818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12105274200439</t>
   </si>
   <si>
     <t xml:space="preserve">9.0654354095459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97274303436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17666912078857</t>
+    <t xml:space="preserve">8.97274208068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17666816711426</t>
   </si>
   <si>
     <t xml:space="preserve">9.02835845947266</t>
@@ -572,7 +572,7 @@
     <t xml:space="preserve">8.95420265197754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71320056915283</t>
+    <t xml:space="preserve">8.71319961547852</t>
   </si>
   <si>
     <t xml:space="preserve">8.99128150939941</t>
@@ -581,25 +581,25 @@
     <t xml:space="preserve">8.76881694793701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89858722686768</t>
+    <t xml:space="preserve">8.89858913421631</t>
   </si>
   <si>
     <t xml:space="preserve">8.93566513061523</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3353385925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9841938018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0305404663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2159290313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4940090179443</t>
+    <t xml:space="preserve">10.3353395462036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9841947555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0305414199829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2159280776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.49400806427</t>
   </si>
   <si>
     <t xml:space="preserve">11.540355682373</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">11.6330490112305</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7257413864136</t>
+    <t xml:space="preserve">11.7257432937622</t>
   </si>
   <si>
     <t xml:space="preserve">11.9111299514771</t>
@@ -620,25 +620,25 @@
     <t xml:space="preserve">11.9574766159058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1892099380493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2819042205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3745985031128</t>
+    <t xml:space="preserve">12.1892118453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2819061279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3745994567871</t>
   </si>
   <si>
     <t xml:space="preserve">12.5136394500732</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3282518386841</t>
+    <t xml:space="preserve">12.3282508850098</t>
   </si>
   <si>
     <t xml:space="preserve">12.1428651809692</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0965175628662</t>
+    <t xml:space="preserve">12.0965185165405</t>
   </si>
   <si>
     <t xml:space="preserve">12.5551223754883</t>
@@ -650,19 +650,19 @@
     <t xml:space="preserve">12.6488170623779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4614276885986</t>
+    <t xml:space="preserve">12.4614267349243</t>
   </si>
   <si>
     <t xml:space="preserve">12.4145793914795</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7425127029419</t>
+    <t xml:space="preserve">12.7425117492676</t>
   </si>
   <si>
     <t xml:space="preserve">12.6956644058228</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2271890640259</t>
+    <t xml:space="preserve">12.2271900177002</t>
   </si>
   <si>
     <t xml:space="preserve">12.1803426742554</t>
@@ -671,100 +671,100 @@
     <t xml:space="preserve">12.3208837509155</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2740383148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8362073898315</t>
+    <t xml:space="preserve">12.274037361145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8362064361572</t>
   </si>
   <si>
     <t xml:space="preserve">12.7893590927124</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6019687652588</t>
+    <t xml:space="preserve">12.6019697189331</t>
   </si>
   <si>
     <t xml:space="preserve">12.9299020767212</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8830537796021</t>
+    <t xml:space="preserve">12.8830547332764</t>
   </si>
   <si>
     <t xml:space="preserve">13.0704441070557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6794605255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8668508529663</t>
+    <t xml:space="preserve">13.679461479187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8668518066406</t>
   </si>
   <si>
     <t xml:space="preserve">14.0542402267456</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3353252410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5695629119873</t>
+    <t xml:space="preserve">14.3353261947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5695638656616</t>
   </si>
   <si>
     <t xml:space="preserve">15.2254276275635</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1317329406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7569532394409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0380382537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1785802841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3191242218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8974943161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4596652984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4128179550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5533609390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0686836242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8650875091553</t>
+    <t xml:space="preserve">15.1317319869995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7569522857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0380373001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.178581237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3191232681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8974952697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4596662521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4128198623657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5533618927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0686798095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8650894165039</t>
   </si>
   <si>
     <t xml:space="preserve">17.0056324005127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7713947296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1930236816406</t>
+    <t xml:space="preserve">16.7713928222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.193021774292</t>
   </si>
   <si>
     <t xml:space="preserve">17.0524787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9587841033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7245464324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6308536529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5371551513672</t>
+    <t xml:space="preserve">16.9587860107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7245483398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6308517456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5371570587158</t>
   </si>
   <si>
     <t xml:space="preserve">16.584005355835</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">16.2092247009277</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2560749053955</t>
+    <t xml:space="preserve">16.2560729980469</t>
   </si>
   <si>
     <t xml:space="preserve">17.1461734771729</t>
@@ -782,10 +782,10 @@
     <t xml:space="preserve">16.396614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3029174804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8344440460205</t>
+    <t xml:space="preserve">16.3029193878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8344430923462</t>
   </si>
   <si>
     <t xml:space="preserve">16.1155300140381</t>
@@ -794,19 +794,19 @@
     <t xml:space="preserve">16.0218353271484</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1623764038086</t>
+    <t xml:space="preserve">16.16237449646</t>
   </si>
   <si>
     <t xml:space="preserve">15.974986076355</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7407503128052</t>
+    <t xml:space="preserve">15.7407484054565</t>
   </si>
   <si>
     <t xml:space="preserve">16.4434623718262</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9119338989258</t>
+    <t xml:space="preserve">16.911937713623</t>
   </si>
   <si>
     <t xml:space="preserve">17.0993251800537</t>
@@ -815,19 +815,19 @@
     <t xml:space="preserve">16.677698135376</t>
   </si>
   <si>
-    <t xml:space="preserve">16.818244934082</t>
+    <t xml:space="preserve">16.8182430267334</t>
   </si>
   <si>
     <t xml:space="preserve">15.272274017334</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0848846435547</t>
+    <t xml:space="preserve">15.084885597229</t>
   </si>
   <si>
     <t xml:space="preserve">14.991189956665</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8037996292114</t>
+    <t xml:space="preserve">14.8038015365601</t>
   </si>
   <si>
     <t xml:space="preserve">14.4758682250977</t>
@@ -842,22 +842,22 @@
     <t xml:space="preserve">14.288477897644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5227146148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9605445861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2416296005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1947832107544</t>
+    <t xml:space="preserve">14.5227155685425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.960545539856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2416315078735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1947822570801</t>
   </si>
   <si>
     <t xml:space="preserve">14.0073928833008</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7263078689575</t>
+    <t xml:space="preserve">13.7263088226318</t>
   </si>
   <si>
     <t xml:space="preserve">14.1479358673096</t>
@@ -866,61 +866,61 @@
     <t xml:space="preserve">14.4290199279785</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6164102554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7731552124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3515291213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3046817779541</t>
+    <t xml:space="preserve">14.6164112091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7731561660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3515281677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3046808242798</t>
   </si>
   <si>
     <t xml:space="preserve">13.3983764648438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0235967636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1172924041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.976749420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3677320480347</t>
+    <t xml:space="preserve">13.0235958099365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1172914505005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9767484664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3677310943604</t>
   </si>
   <si>
     <t xml:space="preserve">12.0866470336914</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9929533004761</t>
+    <t xml:space="preserve">11.9929523468018</t>
   </si>
   <si>
     <t xml:space="preserve">11.8992576599121</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0397987365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1334934234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4776287078857</t>
+    <t xml:space="preserve">12.0397996902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1334943771362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4776306152344</t>
   </si>
   <si>
     <t xml:space="preserve">11.2433929443359</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3839340209961</t>
+    <t xml:space="preserve">11.3839349746704</t>
   </si>
   <si>
     <t xml:space="preserve">11.6650190353394</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4307832717896</t>
+    <t xml:space="preserve">11.4307823181152</t>
   </si>
   <si>
     <t xml:space="preserve">10.9623079299927</t>
@@ -929,10 +929,10 @@
     <t xml:space="preserve">10.7280702590942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1965436935425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5713243484497</t>
+    <t xml:space="preserve">11.1965446472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5713262557983</t>
   </si>
   <si>
     <t xml:space="preserve">11.3370885848999</t>
@@ -941,19 +941,19 @@
     <t xml:space="preserve">11.2902393341064</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7118682861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.758713722229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8055629730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0091543197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46319007873535</t>
+    <t xml:space="preserve">11.7118673324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7587146759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8055620193481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0091552734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46318912506104</t>
   </si>
   <si>
     <t xml:space="preserve">8.33884906768799</t>
@@ -962,7 +962,7 @@
     <t xml:space="preserve">8.57308673858643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31074142456055</t>
+    <t xml:space="preserve">8.31074047088623</t>
   </si>
   <si>
     <t xml:space="preserve">8.45128345489502</t>
@@ -971,37 +971,37 @@
     <t xml:space="preserve">8.61993408203125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44191360473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32948112487793</t>
+    <t xml:space="preserve">8.44191455841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32948017120361</t>
   </si>
   <si>
     <t xml:space="preserve">8.25452423095703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43254375457764</t>
+    <t xml:space="preserve">8.43254470825195</t>
   </si>
   <si>
     <t xml:space="preserve">8.47002220153809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32011127471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20767688751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08587265014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78605031967163</t>
+    <t xml:space="preserve">8.32011222839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20767784118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0858736038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78604936599731</t>
   </si>
   <si>
     <t xml:space="preserve">7.49559497833252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33631420135498</t>
+    <t xml:space="preserve">7.33631372451782</t>
   </si>
   <si>
     <t xml:space="preserve">7.23324918746948</t>
@@ -1010,25 +1010,25 @@
     <t xml:space="preserve">7.83289670944214</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90785217285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50496530532837</t>
+    <t xml:space="preserve">7.90785312652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50496482849121</t>
   </si>
   <si>
     <t xml:space="preserve">7.37379169464111</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12081480026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28009653091431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98027229309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93342542648315</t>
+    <t xml:space="preserve">7.12081575393677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28009700775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98027276992798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93342590332031</t>
   </si>
   <si>
     <t xml:space="preserve">7.06459856033325</t>
@@ -1037,34 +1037,34 @@
     <t xml:space="preserve">7.0271201133728</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34568309783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54244232177734</t>
+    <t xml:space="preserve">7.34568357467651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5424427986145</t>
   </si>
   <si>
     <t xml:space="preserve">8.19830703735352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2170467376709</t>
+    <t xml:space="preserve">8.21704578399658</t>
   </si>
   <si>
     <t xml:space="preserve">8.65194320678711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46116256713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53747463226318</t>
+    <t xml:space="preserve">8.46116161346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53747367858887</t>
   </si>
   <si>
     <t xml:space="preserve">8.68056106567383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77595233917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8427267074585</t>
+    <t xml:space="preserve">8.77595138549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84272575378418</t>
   </si>
   <si>
     <t xml:space="preserve">8.72825527191162</t>
@@ -1076,16 +1076,16 @@
     <t xml:space="preserve">8.49931812286377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42300510406494</t>
+    <t xml:space="preserve">8.42300605773926</t>
   </si>
   <si>
     <t xml:space="preserve">8.39438915252686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.604248046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48977947235107</t>
+    <t xml:space="preserve">8.60424900054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48977851867676</t>
   </si>
   <si>
     <t xml:space="preserve">8.29899787902832</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">8.12729454040527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89835643768311</t>
+    <t xml:space="preserve">7.89835596084595</t>
   </si>
   <si>
     <t xml:space="preserve">8.10821628570557</t>
@@ -1115,16 +1115,16 @@
     <t xml:space="preserve">8.07959938049316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07005882263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92697429656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98420858383179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30853652954102</t>
+    <t xml:space="preserve">8.07005977630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92697381973267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98420763015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30853748321533</t>
   </si>
   <si>
     <t xml:space="preserve">8.26084136962891</t>
@@ -1139,10 +1139,10 @@
     <t xml:space="preserve">8.03190326690674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96513080596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86019992828369</t>
+    <t xml:space="preserve">7.96513032913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86019945144653</t>
   </si>
   <si>
     <t xml:space="preserve">7.86973905563354</t>
@@ -1154,19 +1154,19 @@
     <t xml:space="preserve">7.91743516921997</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76481008529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72665309906006</t>
+    <t xml:space="preserve">7.76480960845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72665357589722</t>
   </si>
   <si>
     <t xml:space="preserve">7.65034103393555</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63126230239868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65987968444824</t>
+    <t xml:space="preserve">7.63126182556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65987873077393</t>
   </si>
   <si>
     <t xml:space="preserve">8.16545104980469</t>
@@ -1178,16 +1178,16 @@
     <t xml:space="preserve">8.11775588989258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93651247024536</t>
+    <t xml:space="preserve">7.93651151657104</t>
   </si>
   <si>
     <t xml:space="preserve">8.19406795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2322244644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31807518005371</t>
+    <t xml:space="preserve">8.23222351074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31807708740234</t>
   </si>
   <si>
     <t xml:space="preserve">8.15591144561768</t>
@@ -1199,31 +1199,31 @@
     <t xml:space="preserve">8.25130176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35623168945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24176406860352</t>
+    <t xml:space="preserve">8.35623264312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2417631149292</t>
   </si>
   <si>
     <t xml:space="preserve">8.34669303894043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95559167861938</t>
+    <t xml:space="preserve">7.95559072494507</t>
   </si>
   <si>
     <t xml:space="preserve">7.77434825897217</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82204389572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97466850280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01282596588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05098152160645</t>
+    <t xml:space="preserve">7.82204437255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97466897964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01282501220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05098056793213</t>
   </si>
   <si>
     <t xml:space="preserve">7.67895746231079</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">7.73619174957275</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69803524017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51679372787476</t>
+    <t xml:space="preserve">7.6980357170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5167932510376</t>
   </si>
   <si>
     <t xml:space="preserve">7.59310626983643</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">7.62172269821167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52633190155029</t>
+    <t xml:space="preserve">7.52633237838745</t>
   </si>
   <si>
     <t xml:space="preserve">7.34508991241455</t>
@@ -1265,25 +1265,25 @@
     <t xml:space="preserve">7.14476871490479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12569046020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23062133789062</t>
+    <t xml:space="preserve">7.12569093704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23062086105347</t>
   </si>
   <si>
     <t xml:space="preserve">7.1543083190918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24969863891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24016046524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46909809112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41186332702637</t>
+    <t xml:space="preserve">7.24969911575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24015998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46909761428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41186285018921</t>
   </si>
   <si>
     <t xml:space="preserve">7.45001983642578</t>
@@ -1295,34 +1295,34 @@
     <t xml:space="preserve">7.39278507232666</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3355507850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61218404769897</t>
+    <t xml:space="preserve">7.33555126190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61218357086182</t>
   </si>
   <si>
     <t xml:space="preserve">7.90789556503296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94605159759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45955896377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70757484436035</t>
+    <t xml:space="preserve">7.94605112075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45955848693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70757436752319</t>
   </si>
   <si>
     <t xml:space="preserve">7.8792781829834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99374771118164</t>
+    <t xml:space="preserve">7.99374723434448</t>
   </si>
   <si>
     <t xml:space="preserve">7.75527000427246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81250381469727</t>
+    <t xml:space="preserve">7.81250476837158</t>
   </si>
   <si>
     <t xml:space="preserve">7.79342699050903</t>
@@ -1331,25 +1331,25 @@
     <t xml:space="preserve">7.80296611785889</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85065984725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74573087692261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83158302307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66941785812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60264492034912</t>
+    <t xml:space="preserve">7.85066032409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74573135375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83158254623413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66941833496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60264539718628</t>
   </si>
   <si>
     <t xml:space="preserve">7.58356666564941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88881826400757</t>
+    <t xml:space="preserve">7.88881778717041</t>
   </si>
   <si>
     <t xml:space="preserve">8.00328636169434</t>
@@ -1361,7 +1361,7 @@
     <t xml:space="preserve">7.3641676902771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10661268234253</t>
+    <t xml:space="preserve">7.10661315917969</t>
   </si>
   <si>
     <t xml:space="preserve">7.27831649780273</t>
@@ -1376,10 +1376,10 @@
     <t xml:space="preserve">7.50372648239136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98721408843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02589225769043</t>
+    <t xml:space="preserve">7.98721361160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02589321136475</t>
   </si>
   <si>
     <t xml:space="preserve">8.04523086547852</t>
@@ -1391,25 +1391,25 @@
     <t xml:space="preserve">8.07424163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12258911132812</t>
+    <t xml:space="preserve">8.12259006500244</t>
   </si>
   <si>
     <t xml:space="preserve">8.05490112304688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94853496551514</t>
+    <t xml:space="preserve">7.94853448867798</t>
   </si>
   <si>
     <t xml:space="preserve">8.06457138061523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08390998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97754430770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93886518478394</t>
+    <t xml:space="preserve">8.08391094207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97754383087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93886423110962</t>
   </si>
   <si>
     <t xml:space="preserve">7.79381895065308</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">7.68745088577271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63910293579102</t>
+    <t xml:space="preserve">7.63910245895386</t>
   </si>
   <si>
     <t xml:space="preserve">7.73579978942871</t>
@@ -1436,10 +1436,10 @@
     <t xml:space="preserve">7.90985584259033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85183668136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83249759674072</t>
+    <t xml:space="preserve">7.85183715820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83249807357788</t>
   </si>
   <si>
     <t xml:space="preserve">7.81315755844116</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">7.80348825454712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78414916992188</t>
+    <t xml:space="preserve">7.78414869308472</t>
   </si>
   <si>
     <t xml:space="preserve">7.6681113243103</t>
@@ -1460,13 +1460,13 @@
     <t xml:space="preserve">7.71646022796631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75513982772827</t>
+    <t xml:space="preserve">7.75514030456543</t>
   </si>
   <si>
     <t xml:space="preserve">7.74547004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86150693893433</t>
+    <t xml:space="preserve">7.86150646209717</t>
   </si>
   <si>
     <t xml:space="preserve">7.89051580429077</t>
@@ -1484,10 +1484,10 @@
     <t xml:space="preserve">8.09358024597168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13225936889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1515998840332</t>
+    <t xml:space="preserve">8.1322603225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15159893035889</t>
   </si>
   <si>
     <t xml:space="preserve">8.1129207611084</t>
@@ -1496,10 +1496,10 @@
     <t xml:space="preserve">8.03556251525879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92919492721558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69712066650391</t>
+    <t xml:space="preserve">7.92919540405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69712114334106</t>
   </si>
   <si>
     <t xml:space="preserve">7.60042381286621</t>
@@ -1508,10 +1508,10 @@
     <t xml:space="preserve">7.88084602355957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55207443237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40702819824219</t>
+    <t xml:space="preserve">7.55207490921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40702867507935</t>
   </si>
   <si>
     <t xml:space="preserve">7.34900999069214</t>
@@ -1520,16 +1520,16 @@
     <t xml:space="preserve">7.37801933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43603754043579</t>
+    <t xml:space="preserve">7.43603801727295</t>
   </si>
   <si>
     <t xml:space="preserve">7.41669797897339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52306604385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36834955215454</t>
+    <t xml:space="preserve">7.5230655670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36834907531738</t>
   </si>
   <si>
     <t xml:space="preserve">7.542405128479</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">7.4843864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70679044723511</t>
+    <t xml:space="preserve">7.70679092407227</t>
   </si>
   <si>
     <t xml:space="preserve">7.64877223968506</t>
@@ -1556,10 +1556,10 @@
     <t xml:space="preserve">7.59075355529785</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95820426940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96787405014038</t>
+    <t xml:space="preserve">7.95820331573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96787357330322</t>
   </si>
   <si>
     <t xml:space="preserve">7.90018606185913</t>
@@ -1577,10 +1577,10 @@
     <t xml:space="preserve">8.19027900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29664611816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45136165618896</t>
+    <t xml:space="preserve">8.29664516448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45136070251465</t>
   </si>
   <si>
     <t xml:space="preserve">8.48037147521973</t>
@@ -1607,19 +1607,19 @@
     <t xml:space="preserve">8.50938034057617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4223518371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54805946350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55772972106934</t>
+    <t xml:space="preserve">8.42235279083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54805850982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55772876739502</t>
   </si>
   <si>
     <t xml:space="preserve">8.52871990203857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68343448638916</t>
+    <t xml:space="preserve">8.68343544006348</t>
   </si>
   <si>
     <t xml:space="preserve">8.76079368591309</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">8.65442562103271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75112438201904</t>
+    <t xml:space="preserve">8.75112342834473</t>
   </si>
   <si>
     <t xml:space="preserve">8.70277500152588</t>
@@ -1652,10 +1652,10 @@
     <t xml:space="preserve">8.63508701324463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32565402984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31598472595215</t>
+    <t xml:space="preserve">8.32565498352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31598567962646</t>
   </si>
   <si>
     <t xml:space="preserve">8.30631542205811</t>
@@ -62280,7 +62280,7 @@
     </row>
     <row r="2298">
       <c r="A2298" s="1" t="n">
-        <v>45961.6910648148</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2298" t="n">
         <v>16867</v>
@@ -62301,6 +62301,32 @@
         <v>735</v>
       </c>
       <c r="H2298" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2299">
+      <c r="A2299" s="1" t="n">
+        <v>45964.6911921296</v>
+      </c>
+      <c r="B2299" t="n">
+        <v>16158</v>
+      </c>
+      <c r="C2299" t="n">
+        <v>9.39999961853027</v>
+      </c>
+      <c r="D2299" t="n">
+        <v>9.23999977111816</v>
+      </c>
+      <c r="E2299" t="n">
+        <v>9.38000011444092</v>
+      </c>
+      <c r="F2299" t="n">
+        <v>9.26000022888184</v>
+      </c>
+      <c r="G2299" t="s">
+        <v>724</v>
+      </c>
+      <c r="H2299" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -50,31 +50,31 @@
     <t xml:space="preserve">9.08549880981445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24887371063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09457397460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12180519104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03104019165039</t>
+    <t xml:space="preserve">9.24887275695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09457588195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12180328369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03103923797607</t>
   </si>
   <si>
     <t xml:space="preserve">8.95388984680176</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89943218231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89489269256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84951114654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85858821868896</t>
+    <t xml:space="preserve">8.8994312286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89489364624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84951210021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85858726501465</t>
   </si>
   <si>
     <t xml:space="preserve">8.87673950195312</t>
@@ -86,46 +86,46 @@
     <t xml:space="preserve">8.86766529083252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04919242858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23072147369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11272716522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96750354766846</t>
+    <t xml:space="preserve">9.0491943359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23072052001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11272621154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96750450134277</t>
   </si>
   <si>
     <t xml:space="preserve">8.91304588317871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92212200164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00380992889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15811061859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16718578338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43947887420654</t>
+    <t xml:space="preserve">8.92212295532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00381088256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15810966491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16718673706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43947792053223</t>
   </si>
   <si>
     <t xml:space="preserve">9.54839611053467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62100601196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8025369644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71177196502686</t>
+    <t xml:space="preserve">9.62100791931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80253505706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71177101135254</t>
   </si>
   <si>
     <t xml:space="preserve">9.56654930114746</t>
@@ -134,22 +134,22 @@
     <t xml:space="preserve">9.58470249176025</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57562351226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53024387359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50301265716553</t>
+    <t xml:space="preserve">9.5756254196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53024291992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50301361083984</t>
   </si>
   <si>
     <t xml:space="preserve">9.60285472869873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63916110992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79345798492432</t>
+    <t xml:space="preserve">9.63915920257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79345989227295</t>
   </si>
   <si>
     <t xml:space="preserve">9.95683479309082</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">9.93868160247803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98406410217285</t>
+    <t xml:space="preserve">9.98406314849854</t>
   </si>
   <si>
     <t xml:space="preserve">9.73900032043457</t>
@@ -167,64 +167,64 @@
     <t xml:space="preserve">9.76623058319092</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74807739257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75715351104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64823627471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82068920135498</t>
+    <t xml:space="preserve">9.74807643890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75715446472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64823532104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82068729400635</t>
   </si>
   <si>
     <t xml:space="preserve">9.70269393920898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72084712982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67546558380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66638851165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63008213043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65731430053711</t>
+    <t xml:space="preserve">9.72084617614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67546463012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66638946533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63008308410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65731239318848</t>
   </si>
   <si>
     <t xml:space="preserve">9.68454170227051</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81161308288574</t>
+    <t xml:space="preserve">9.81161117553711</t>
   </si>
   <si>
     <t xml:space="preserve">9.8297643661499</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8479175567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83884048461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72992420196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78438377380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55747127532959</t>
+    <t xml:space="preserve">9.84791851043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83884143829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72992515563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78438282012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55747222900391</t>
   </si>
   <si>
     <t xml:space="preserve">9.34871482849121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33963775634766</t>
+    <t xml:space="preserve">9.33963871002197</t>
   </si>
   <si>
     <t xml:space="preserve">9.27610397338867</t>
@@ -233,19 +233,19 @@
     <t xml:space="preserve">9.25794982910156</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19441699981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18533802032471</t>
+    <t xml:space="preserve">9.19441604614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18533897399902</t>
   </si>
   <si>
     <t xml:space="preserve">9.41224956512451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22164440155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31240844726562</t>
+    <t xml:space="preserve">9.22164535522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31240940093994</t>
   </si>
   <si>
     <t xml:space="preserve">9.26702690124512</t>
@@ -257,7 +257,7 @@
     <t xml:space="preserve">9.28517913818359</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37594413757324</t>
+    <t xml:space="preserve">9.37594223022461</t>
   </si>
   <si>
     <t xml:space="preserve">9.366868019104</t>
@@ -269,40 +269,40 @@
     <t xml:space="preserve">9.45763111114502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39409732818604</t>
+    <t xml:space="preserve">9.39409828186035</t>
   </si>
   <si>
     <t xml:space="preserve">9.48486042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49393844604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4485559463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47578430175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23979759216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14903354644775</t>
+    <t xml:space="preserve">9.49393749237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44855403900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47578239440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2397985458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14903259277344</t>
   </si>
   <si>
     <t xml:space="preserve">9.21256828308105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20349216461182</t>
+    <t xml:space="preserve">9.2034912109375</t>
   </si>
   <si>
     <t xml:space="preserve">9.13088035583496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1399564743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94027519226074</t>
+    <t xml:space="preserve">9.13995552062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94027614593506</t>
   </si>
   <si>
     <t xml:space="preserve">8.80412864685059</t>
@@ -314,28 +314,28 @@
     <t xml:space="preserve">8.66798305511475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62260150909424</t>
+    <t xml:space="preserve">8.62260055541992</t>
   </si>
   <si>
     <t xml:space="preserve">8.53183650970459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35030746459961</t>
+    <t xml:space="preserve">8.35030937194824</t>
   </si>
   <si>
     <t xml:space="preserve">8.16878032684326</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98725175857544</t>
+    <t xml:space="preserve">7.98725080490112</t>
   </si>
   <si>
     <t xml:space="preserve">8.03263378143311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12339782714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25954341888428</t>
+    <t xml:space="preserve">8.12339687347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25954437255859</t>
   </si>
   <si>
     <t xml:space="preserve">7.94186925888062</t>
@@ -344,58 +344,58 @@
     <t xml:space="preserve">8.30492496490479</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21416187286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39568901062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5772180557251</t>
+    <t xml:space="preserve">8.21416091918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39569091796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57721996307373</t>
   </si>
   <si>
     <t xml:space="preserve">8.71336555480957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53202342987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25706005096436</t>
+    <t xml:space="preserve">9.53202152252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25706195831299</t>
   </si>
   <si>
     <t xml:space="preserve">9.44036865234375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16540622711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07375144958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11958026885986</t>
+    <t xml:space="preserve">9.16540718078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07375240325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11957931518555</t>
   </si>
   <si>
     <t xml:space="preserve">8.98209857940674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02792549133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62367820739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80698490142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89863967895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99029350280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1736011505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2652540206909</t>
+    <t xml:space="preserve">9.02792644500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62367630004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80698394775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89863872528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9902925491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.173602104187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2652549743652</t>
   </si>
   <si>
     <t xml:space="preserve">10.3569087982178</t>
@@ -410,43 +410,43 @@
     <t xml:space="preserve">10.8151798248291</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7235250473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.906834602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9984884262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0901432037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1817960739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2734508514404</t>
+    <t xml:space="preserve">10.7235260009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9068336486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9984893798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0901412963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1817951202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2734498977661</t>
   </si>
   <si>
     <t xml:space="preserve">11.4567584991455</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3651037216187</t>
+    <t xml:space="preserve">11.3651027679443</t>
   </si>
   <si>
     <t xml:space="preserve">10.4485626220703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71533107757568</t>
+    <t xml:space="preserve">9.71533203125</t>
   </si>
   <si>
     <t xml:space="preserve">8.79879093170166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24886703491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2112340927124</t>
+    <t xml:space="preserve">8.24886608123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21123313903809</t>
   </si>
   <si>
     <t xml:space="preserve">9.30288791656494</t>
@@ -458,31 +458,31 @@
     <t xml:space="preserve">9.39454174041748</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76115608215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6695032119751</t>
+    <t xml:space="preserve">9.76115798950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66950416564941</t>
   </si>
   <si>
     <t xml:space="preserve">9.57784938812256</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0361204147339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94446563720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82552433013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73283100128174</t>
+    <t xml:space="preserve">10.0361194610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94446754455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82552528381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73283004760742</t>
   </si>
   <si>
     <t xml:space="preserve">9.59379100799561</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96456432342529</t>
+    <t xml:space="preserve">9.96456527709961</t>
   </si>
   <si>
     <t xml:space="preserve">9.91821670532227</t>
@@ -500,43 +500,43 @@
     <t xml:space="preserve">10.1499509811401</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1962985992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77917671203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87186908721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0572576522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2889919281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4743795394897</t>
+    <t xml:space="preserve">10.1962976455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77917766571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87187099456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0572595596313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2889928817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4743785858154</t>
   </si>
   <si>
     <t xml:space="preserve">10.2426462173462</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3816862106323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68648433685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64013671875</t>
+    <t xml:space="preserve">10.381685256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68648338317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64013576507568</t>
   </si>
   <si>
     <t xml:space="preserve">9.50109672546387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31571006774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23228454589844</t>
+    <t xml:space="preserve">9.31570816040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23228549957275</t>
   </si>
   <si>
     <t xml:space="preserve">9.1952075958252</t>
@@ -545,13 +545,13 @@
     <t xml:space="preserve">9.25082302093506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26936149597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21374607086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04689788818359</t>
+    <t xml:space="preserve">9.269362449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2137451171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04689693450928</t>
   </si>
   <si>
     <t xml:space="preserve">9.12105274200439</t>
@@ -560,7 +560,7 @@
     <t xml:space="preserve">9.0654354095459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97274208068848</t>
+    <t xml:space="preserve">8.97274303436279</t>
   </si>
   <si>
     <t xml:space="preserve">9.17666816711426</t>
@@ -569,10 +569,10 @@
     <t xml:space="preserve">9.02835845947266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95420265197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71319961547852</t>
+    <t xml:space="preserve">8.95420360565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71320056915283</t>
   </si>
   <si>
     <t xml:space="preserve">8.99128150939941</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">8.76881694793701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89858913421631</t>
+    <t xml:space="preserve">8.89858818054199</t>
   </si>
   <si>
     <t xml:space="preserve">8.93566513061523</t>
@@ -590,10 +590,10 @@
     <t xml:space="preserve">10.3353395462036</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9841947555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0305414199829</t>
+    <t xml:space="preserve">10.9841938018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0305404663086</t>
   </si>
   <si>
     <t xml:space="preserve">11.2159280776978</t>
@@ -608,13 +608,13 @@
     <t xml:space="preserve">11.5867033004761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6330490112305</t>
+    <t xml:space="preserve">11.6330499649048</t>
   </si>
   <si>
     <t xml:space="preserve">11.7257432937622</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9111299514771</t>
+    <t xml:space="preserve">11.9111309051514</t>
   </si>
   <si>
     <t xml:space="preserve">11.9574766159058</t>
@@ -623,37 +623,37 @@
     <t xml:space="preserve">12.1892118453979</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2819061279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3745994567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5136394500732</t>
+    <t xml:space="preserve">12.2819042205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3745985031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5136384963989</t>
   </si>
   <si>
     <t xml:space="preserve">12.3282508850098</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1428651809692</t>
+    <t xml:space="preserve">12.1428642272949</t>
   </si>
   <si>
     <t xml:space="preserve">12.0965185165405</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5551223754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5082750320435</t>
+    <t xml:space="preserve">12.555121421814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5082740783691</t>
   </si>
   <si>
     <t xml:space="preserve">12.6488170623779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4614267349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4145793914795</t>
+    <t xml:space="preserve">12.46142578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4145784378052</t>
   </si>
   <si>
     <t xml:space="preserve">12.7425117492676</t>
@@ -665,10 +665,10 @@
     <t xml:space="preserve">12.2271900177002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1803426742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3208837509155</t>
+    <t xml:space="preserve">12.1803417205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3208847045898</t>
   </si>
   <si>
     <t xml:space="preserve">12.274037361145</t>
@@ -683,22 +683,22 @@
     <t xml:space="preserve">12.6019697189331</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9299020767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8830547332764</t>
+    <t xml:space="preserve">12.9299011230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8830537796021</t>
   </si>
   <si>
     <t xml:space="preserve">13.0704441070557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.679461479187</t>
+    <t xml:space="preserve">13.6794624328613</t>
   </si>
   <si>
     <t xml:space="preserve">13.8668518066406</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0542402267456</t>
+    <t xml:space="preserve">14.0542411804199</t>
   </si>
   <si>
     <t xml:space="preserve">14.3353261947632</t>
@@ -710,16 +710,16 @@
     <t xml:space="preserve">15.2254276275635</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1317319869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7569522857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0380373001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.178581237793</t>
+    <t xml:space="preserve">15.1317310333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7569532394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0380363464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1785802841187</t>
   </si>
   <si>
     <t xml:space="preserve">15.3191232681274</t>
@@ -728,22 +728,22 @@
     <t xml:space="preserve">14.8974952697754</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4596662521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4128198623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5533618927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0686798095703</t>
+    <t xml:space="preserve">15.4596643447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4128189086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5533590316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0686817169189</t>
   </si>
   <si>
     <t xml:space="preserve">16.8650894165039</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0056324005127</t>
+    <t xml:space="preserve">17.0056304931641</t>
   </si>
   <si>
     <t xml:space="preserve">16.7713928222656</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">17.0524787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9587860107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7245483398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6308517456055</t>
+    <t xml:space="preserve">16.9587841033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7245464324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6308498382568</t>
   </si>
   <si>
     <t xml:space="preserve">16.5371570587158</t>
@@ -770,13 +770,13 @@
     <t xml:space="preserve">16.584005355835</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2092247009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2560729980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1461734771729</t>
+    <t xml:space="preserve">16.2092208862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2560710906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1461715698242</t>
   </si>
   <si>
     <t xml:space="preserve">16.396614074707</t>
@@ -785,46 +785,46 @@
     <t xml:space="preserve">16.3029193878174</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8344430923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1155300140381</t>
+    <t xml:space="preserve">15.8344440460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1155281066895</t>
   </si>
   <si>
     <t xml:space="preserve">16.0218353271484</t>
   </si>
   <si>
-    <t xml:space="preserve">16.16237449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.974986076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7407484054565</t>
+    <t xml:space="preserve">16.1623764038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9749870300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7407493591309</t>
   </si>
   <si>
     <t xml:space="preserve">16.4434623718262</t>
   </si>
   <si>
-    <t xml:space="preserve">16.911937713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0993251800537</t>
+    <t xml:space="preserve">16.9119358062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0993270874023</t>
   </si>
   <si>
     <t xml:space="preserve">16.677698135376</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8182430267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.272274017334</t>
+    <t xml:space="preserve">16.8182411193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2722749710083</t>
   </si>
   <si>
     <t xml:space="preserve">15.084885597229</t>
   </si>
   <si>
-    <t xml:space="preserve">14.991189956665</t>
+    <t xml:space="preserve">14.9911909103394</t>
   </si>
   <si>
     <t xml:space="preserve">14.8038015365601</t>
@@ -842,34 +842,34 @@
     <t xml:space="preserve">14.288477897644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5227155685425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.960545539856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2416315078735</t>
+    <t xml:space="preserve">14.5227165222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9605464935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2416305541992</t>
   </si>
   <si>
     <t xml:space="preserve">14.1947822570801</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0073928833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7263088226318</t>
+    <t xml:space="preserve">14.0073938369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7263078689575</t>
   </si>
   <si>
     <t xml:space="preserve">14.1479358673096</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4290199279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6164112091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7731561660767</t>
+    <t xml:space="preserve">14.4290208816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6164102554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7731552124023</t>
   </si>
   <si>
     <t xml:space="preserve">13.3515281677246</t>
@@ -881,25 +881,25 @@
     <t xml:space="preserve">13.3983764648438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0235958099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1172914505005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9767484664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3677310943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0866470336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9929523468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8992576599121</t>
+    <t xml:space="preserve">13.0235967636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1172924041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.976749420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3677320480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0866460800171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9929513931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8992567062378</t>
   </si>
   <si>
     <t xml:space="preserve">12.0397996902466</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">11.3839349746704</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6650190353394</t>
+    <t xml:space="preserve">11.6650199890137</t>
   </si>
   <si>
     <t xml:space="preserve">11.4307823181152</t>
@@ -932,25 +932,25 @@
     <t xml:space="preserve">11.1965446472168</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5713262557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3370885848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2902393341064</t>
+    <t xml:space="preserve">11.571325302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3370876312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2902412414551</t>
   </si>
   <si>
     <t xml:space="preserve">11.7118673324585</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7587146759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8055620193481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0091552734375</t>
+    <t xml:space="preserve">11.7587156295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8055629730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0091562271118</t>
   </si>
   <si>
     <t xml:space="preserve">9.46318912506104</t>
@@ -959,13 +959,13 @@
     <t xml:space="preserve">8.33884906768799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57308673858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31074047088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45128345489502</t>
+    <t xml:space="preserve">8.57308578491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31074142456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45128440856934</t>
   </si>
   <si>
     <t xml:space="preserve">8.61993408203125</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">8.44191455841064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32948017120361</t>
+    <t xml:space="preserve">8.32948112487793</t>
   </si>
   <si>
     <t xml:space="preserve">8.25452423095703</t>
@@ -986,10 +986,10 @@
     <t xml:space="preserve">8.47002220153809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32011222839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20767784118652</t>
+    <t xml:space="preserve">8.32010936737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20767688751221</t>
   </si>
   <si>
     <t xml:space="preserve">8.0858736038208</t>
@@ -998,7 +998,7 @@
     <t xml:space="preserve">7.78604936599731</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49559497833252</t>
+    <t xml:space="preserve">7.49559545516968</t>
   </si>
   <si>
     <t xml:space="preserve">7.33631372451782</t>
@@ -1007,10 +1007,10 @@
     <t xml:space="preserve">7.23324918746948</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83289670944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90785312652588</t>
+    <t xml:space="preserve">7.83289623260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90785264968872</t>
   </si>
   <si>
     <t xml:space="preserve">7.50496482849121</t>
@@ -1019,22 +1019,22 @@
     <t xml:space="preserve">7.37379169464111</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12081575393677</t>
+    <t xml:space="preserve">7.12081527709961</t>
   </si>
   <si>
     <t xml:space="preserve">7.28009700775146</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98027276992798</t>
+    <t xml:space="preserve">6.98027324676514</t>
   </si>
   <si>
     <t xml:space="preserve">6.93342590332031</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06459856033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0271201133728</t>
+    <t xml:space="preserve">7.06459808349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02712059020996</t>
   </si>
   <si>
     <t xml:space="preserve">7.34568357467651</t>
@@ -1046,13 +1046,13 @@
     <t xml:space="preserve">8.19830703735352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21704578399658</t>
+    <t xml:space="preserve">8.2170467376709</t>
   </si>
   <si>
     <t xml:space="preserve">8.65194320678711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46116161346436</t>
+    <t xml:space="preserve">8.46116256713867</t>
   </si>
   <si>
     <t xml:space="preserve">8.53747367858887</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">8.66148281097412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49931812286377</t>
+    <t xml:space="preserve">8.49931716918945</t>
   </si>
   <si>
     <t xml:space="preserve">8.42300605773926</t>
@@ -1091,22 +1091,22 @@
     <t xml:space="preserve">8.29899787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12729454040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89835596084595</t>
+    <t xml:space="preserve">8.12729549407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89835643768311</t>
   </si>
   <si>
     <t xml:space="preserve">8.10821628570557</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84112215042114</t>
+    <t xml:space="preserve">7.8411226272583</t>
   </si>
   <si>
     <t xml:space="preserve">8.33715343475342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2036075592041</t>
+    <t xml:space="preserve">8.20360660552979</t>
   </si>
   <si>
     <t xml:space="preserve">8.06052017211914</t>
@@ -1118,31 +1118,31 @@
     <t xml:space="preserve">8.07005977630615</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92697381973267</t>
+    <t xml:space="preserve">7.92697334289551</t>
   </si>
   <si>
     <t xml:space="preserve">7.98420763015747</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30853748321533</t>
+    <t xml:space="preserve">8.30853652954102</t>
   </si>
   <si>
     <t xml:space="preserve">8.26084136962891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27038097381592</t>
+    <t xml:space="preserve">8.2703800201416</t>
   </si>
   <si>
     <t xml:space="preserve">8.18452835083008</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03190326690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96513032913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86019945144653</t>
+    <t xml:space="preserve">8.03190422058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96512985229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86019992828369</t>
   </si>
   <si>
     <t xml:space="preserve">7.86973905563354</t>
@@ -1151,43 +1151,43 @@
     <t xml:space="preserve">7.71711397171021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91743516921997</t>
+    <t xml:space="preserve">7.91743421554565</t>
   </si>
   <si>
     <t xml:space="preserve">7.76480960845947</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72665357589722</t>
+    <t xml:space="preserve">7.72665309906006</t>
   </si>
   <si>
     <t xml:space="preserve">7.65034103393555</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63126182556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65987873077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16545104980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32761383056641</t>
+    <t xml:space="preserve">7.63126230239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65987968444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.165452003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32761478424072</t>
   </si>
   <si>
     <t xml:space="preserve">8.11775588989258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93651151657104</t>
+    <t xml:space="preserve">7.93651247024536</t>
   </si>
   <si>
     <t xml:space="preserve">8.19406795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23222351074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31807708740234</t>
+    <t xml:space="preserve">8.2322244644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31807613372803</t>
   </si>
   <si>
     <t xml:space="preserve">8.15591144561768</t>
@@ -1196,7 +1196,7 @@
     <t xml:space="preserve">8.22268486022949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25130176544189</t>
+    <t xml:space="preserve">8.25130081176758</t>
   </si>
   <si>
     <t xml:space="preserve">8.35623264312744</t>
@@ -1214,37 +1214,37 @@
     <t xml:space="preserve">7.77434825897217</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82204437255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97466897964478</t>
+    <t xml:space="preserve">7.82204389572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97466850280762</t>
   </si>
   <si>
     <t xml:space="preserve">8.01282501220703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05098056793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67895746231079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73619174957275</t>
+    <t xml:space="preserve">8.05098152160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67895793914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7361912727356</t>
   </si>
   <si>
     <t xml:space="preserve">7.6980357170105</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5167932510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59310626983643</t>
+    <t xml:space="preserve">7.51679372787476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59310579299927</t>
   </si>
   <si>
     <t xml:space="preserve">7.44048070907593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5358715057373</t>
+    <t xml:space="preserve">7.53587198257446</t>
   </si>
   <si>
     <t xml:space="preserve">7.62172269821167</t>
@@ -1259,10 +1259,10 @@
     <t xml:space="preserve">7.20200395584106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18292570114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14476871490479</t>
+    <t xml:space="preserve">7.1829252243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14476919174194</t>
   </si>
   <si>
     <t xml:space="preserve">7.12569093704224</t>
@@ -1277,79 +1277,79 @@
     <t xml:space="preserve">7.24969911575317</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24015998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46909761428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41186285018921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45001983642578</t>
+    <t xml:space="preserve">7.24016046524048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46909809112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41186380386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45001935958862</t>
   </si>
   <si>
     <t xml:space="preserve">7.28785514831543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39278507232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33555126190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61218357086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90789556503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94605112075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45955848693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70757436752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8792781829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99374723434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75527000427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81250476837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79342699050903</t>
+    <t xml:space="preserve">7.39278554916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3355507850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61218404769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90789604187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94605159759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45955896377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70757484436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87927913665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99374675750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75527048110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81250429153442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79342651367188</t>
   </si>
   <si>
     <t xml:space="preserve">7.80296611785889</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85066032409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74573135375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83158254623413</t>
+    <t xml:space="preserve">7.85066080093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74573087692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83158302307129</t>
   </si>
   <si>
     <t xml:space="preserve">7.66941833496094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60264539718628</t>
+    <t xml:space="preserve">7.60264492034912</t>
   </si>
   <si>
     <t xml:space="preserve">7.58356666564941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88881778717041</t>
+    <t xml:space="preserve">7.88881826400757</t>
   </si>
   <si>
     <t xml:space="preserve">8.00328636169434</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">7.27831649780273</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08753490447998</t>
+    <t xml:space="preserve">7.08753442764282</t>
   </si>
   <si>
     <t xml:space="preserve">7.05891799926758</t>
@@ -1376,10 +1376,10 @@
     <t xml:space="preserve">7.50372648239136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98721361160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02589321136475</t>
+    <t xml:space="preserve">7.98721408843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02589225769043</t>
   </si>
   <si>
     <t xml:space="preserve">8.04523086547852</t>
@@ -1391,25 +1391,25 @@
     <t xml:space="preserve">8.07424163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12259006500244</t>
+    <t xml:space="preserve">8.12258911132812</t>
   </si>
   <si>
     <t xml:space="preserve">8.05490112304688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94853448867798</t>
+    <t xml:space="preserve">7.94853496551514</t>
   </si>
   <si>
     <t xml:space="preserve">8.06457138061523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08391094207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97754383087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93886423110962</t>
+    <t xml:space="preserve">8.08390998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97754430770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93886518478394</t>
   </si>
   <si>
     <t xml:space="preserve">7.79381895065308</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">7.68745088577271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63910245895386</t>
+    <t xml:space="preserve">7.63910293579102</t>
   </si>
   <si>
     <t xml:space="preserve">7.73579978942871</t>
@@ -1436,10 +1436,10 @@
     <t xml:space="preserve">7.90985584259033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85183715820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83249807357788</t>
+    <t xml:space="preserve">7.85183668136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83249759674072</t>
   </si>
   <si>
     <t xml:space="preserve">7.81315755844116</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">7.80348825454712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78414869308472</t>
+    <t xml:space="preserve">7.78414916992188</t>
   </si>
   <si>
     <t xml:space="preserve">7.6681113243103</t>
@@ -1460,13 +1460,13 @@
     <t xml:space="preserve">7.71646022796631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75514030456543</t>
+    <t xml:space="preserve">7.75513982772827</t>
   </si>
   <si>
     <t xml:space="preserve">7.74547004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86150646209717</t>
+    <t xml:space="preserve">7.86150693893433</t>
   </si>
   <si>
     <t xml:space="preserve">7.89051580429077</t>
@@ -1484,10 +1484,10 @@
     <t xml:space="preserve">8.09358024597168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1322603225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15159893035889</t>
+    <t xml:space="preserve">8.13225936889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1515998840332</t>
   </si>
   <si>
     <t xml:space="preserve">8.1129207611084</t>
@@ -1496,10 +1496,10 @@
     <t xml:space="preserve">8.03556251525879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92919540405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69712114334106</t>
+    <t xml:space="preserve">7.92919492721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69712066650391</t>
   </si>
   <si>
     <t xml:space="preserve">7.60042381286621</t>
@@ -1508,10 +1508,10 @@
     <t xml:space="preserve">7.88084602355957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55207490921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40702867507935</t>
+    <t xml:space="preserve">7.55207443237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40702819824219</t>
   </si>
   <si>
     <t xml:space="preserve">7.34900999069214</t>
@@ -1520,16 +1520,16 @@
     <t xml:space="preserve">7.37801933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43603801727295</t>
+    <t xml:space="preserve">7.43603754043579</t>
   </si>
   <si>
     <t xml:space="preserve">7.41669797897339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5230655670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36834907531738</t>
+    <t xml:space="preserve">7.52306604385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36834955215454</t>
   </si>
   <si>
     <t xml:space="preserve">7.542405128479</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">7.4843864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70679092407227</t>
+    <t xml:space="preserve">7.70679044723511</t>
   </si>
   <si>
     <t xml:space="preserve">7.64877223968506</t>
@@ -1556,10 +1556,10 @@
     <t xml:space="preserve">7.59075355529785</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95820331573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96787357330322</t>
+    <t xml:space="preserve">7.95820426940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96787405014038</t>
   </si>
   <si>
     <t xml:space="preserve">7.90018606185913</t>
@@ -1577,10 +1577,10 @@
     <t xml:space="preserve">8.19027900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29664516448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45136070251465</t>
+    <t xml:space="preserve">8.29664611816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45136165618896</t>
   </si>
   <si>
     <t xml:space="preserve">8.48037147521973</t>
@@ -1607,19 +1607,19 @@
     <t xml:space="preserve">8.50938034057617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42235279083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54805850982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55772876739502</t>
+    <t xml:space="preserve">8.4223518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54805946350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55772972106934</t>
   </si>
   <si>
     <t xml:space="preserve">8.52871990203857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68343544006348</t>
+    <t xml:space="preserve">8.68343448638916</t>
   </si>
   <si>
     <t xml:space="preserve">8.76079368591309</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">8.65442562103271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75112342834473</t>
+    <t xml:space="preserve">8.75112438201904</t>
   </si>
   <si>
     <t xml:space="preserve">8.70277500152588</t>
@@ -1652,10 +1652,10 @@
     <t xml:space="preserve">8.63508701324463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32565498352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31598567962646</t>
+    <t xml:space="preserve">8.32565402984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31598472595215</t>
   </si>
   <si>
     <t xml:space="preserve">8.30631542205811</t>
@@ -62306,7 +62306,7 @@
     </row>
     <row r="2299">
       <c r="A2299" s="1" t="n">
-        <v>45964.6911921296</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2299" t="n">
         <v>16158</v>
@@ -62327,6 +62327,32 @@
         <v>724</v>
       </c>
       <c r="H2299" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2300">
+      <c r="A2300" s="1" t="n">
+        <v>45965.6910069444</v>
+      </c>
+      <c r="B2300" t="n">
+        <v>17274</v>
+      </c>
+      <c r="C2300" t="n">
+        <v>9.4399995803833</v>
+      </c>
+      <c r="D2300" t="n">
+        <v>9.18000030517578</v>
+      </c>
+      <c r="E2300" t="n">
+        <v>9.18000030517578</v>
+      </c>
+      <c r="F2300" t="n">
+        <v>9.35999965667725</v>
+      </c>
+      <c r="G2300" t="s">
+        <v>733</v>
+      </c>
+      <c r="H2300" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="737">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,22 +44,22 @@
     <t xml:space="preserve">FF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98565673828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08549880981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24887275695801</t>
+    <t xml:space="preserve">8.98565578460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08549976348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24887371063232</t>
   </si>
   <si>
     <t xml:space="preserve">9.09457588195801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12180328369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03103923797607</t>
+    <t xml:space="preserve">9.12180423736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03104019165039</t>
   </si>
   <si>
     <t xml:space="preserve">8.95388984680176</t>
@@ -68,10 +68,10 @@
     <t xml:space="preserve">8.8994312286377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89489364624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84951210021973</t>
+    <t xml:space="preserve">8.89489459991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84951114654541</t>
   </si>
   <si>
     <t xml:space="preserve">8.85858726501465</t>
@@ -86,22 +86,22 @@
     <t xml:space="preserve">8.86766529083252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0491943359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23072052001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11272621154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96750450134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91304588317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92212295532227</t>
+    <t xml:space="preserve">9.04919242858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23072147369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11272811889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96750354766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91304683685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92212200164795</t>
   </si>
   <si>
     <t xml:space="preserve">9.00381088256836</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">9.15810966491699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16718673706055</t>
+    <t xml:space="preserve">9.16718578338623</t>
   </si>
   <si>
     <t xml:space="preserve">9.43947792053223</t>
@@ -122,10 +122,10 @@
     <t xml:space="preserve">9.62100791931152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80253505706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71177101135254</t>
+    <t xml:space="preserve">9.8025369644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71177005767822</t>
   </si>
   <si>
     <t xml:space="preserve">9.56654930114746</t>
@@ -137,31 +137,31 @@
     <t xml:space="preserve">9.5756254196167</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53024291992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50301361083984</t>
+    <t xml:space="preserve">9.53024196624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50301456451416</t>
   </si>
   <si>
     <t xml:space="preserve">9.60285472869873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63915920257568</t>
+    <t xml:space="preserve">9.63916015625</t>
   </si>
   <si>
     <t xml:space="preserve">9.79345989227295</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95683479309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93868160247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98406314849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73900032043457</t>
+    <t xml:space="preserve">9.95683574676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93868255615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98406600952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73899936676025</t>
   </si>
   <si>
     <t xml:space="preserve">9.76623058319092</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">9.74807643890381</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75715446472168</t>
+    <t xml:space="preserve">9.75715351104736</t>
   </si>
   <si>
     <t xml:space="preserve">9.64823532104492</t>
@@ -179,31 +179,31 @@
     <t xml:space="preserve">9.82068729400635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70269393920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72084617614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67546463012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66638946533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63008308410645</t>
+    <t xml:space="preserve">9.7026948928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72084712982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67546653747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66638851165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63008403778076</t>
   </si>
   <si>
     <t xml:space="preserve">9.65731239318848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68454170227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81161117553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8297643661499</t>
+    <t xml:space="preserve">9.68454265594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81161308288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82976531982422</t>
   </si>
   <si>
     <t xml:space="preserve">9.84791851043701</t>
@@ -212,34 +212,34 @@
     <t xml:space="preserve">9.83884143829346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72992515563965</t>
+    <t xml:space="preserve">9.72992420196533</t>
   </si>
   <si>
     <t xml:space="preserve">9.78438282012939</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55747222900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34871482849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33963871002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27610397338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25794982910156</t>
+    <t xml:space="preserve">9.55747127532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34871387481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33963680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27610206604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25795078277588</t>
   </si>
   <si>
     <t xml:space="preserve">9.19441604614258</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18533897399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41224956512451</t>
+    <t xml:space="preserve">9.18533802032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41225051879883</t>
   </si>
   <si>
     <t xml:space="preserve">9.22164535522461</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">9.31240940093994</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26702690124512</t>
+    <t xml:space="preserve">9.2670259475708</t>
   </si>
   <si>
     <t xml:space="preserve">9.29425525665283</t>
@@ -257,34 +257,34 @@
     <t xml:space="preserve">9.28517913818359</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37594223022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.366868019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38502025604248</t>
+    <t xml:space="preserve">9.37594413757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36686706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3850212097168</t>
   </si>
   <si>
     <t xml:space="preserve">9.45763111114502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39409828186035</t>
+    <t xml:space="preserve">9.39409732818604</t>
   </si>
   <si>
     <t xml:space="preserve">9.48486042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49393749237061</t>
+    <t xml:space="preserve">9.49393653869629</t>
   </si>
   <si>
     <t xml:space="preserve">9.44855403900146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47578239440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2397985458374</t>
+    <t xml:space="preserve">9.47578430175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23979759216309</t>
   </si>
   <si>
     <t xml:space="preserve">9.14903259277344</t>
@@ -293,40 +293,40 @@
     <t xml:space="preserve">9.21256828308105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2034912109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13088035583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13995552062988</t>
+    <t xml:space="preserve">9.20349311828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13088130950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13995456695557</t>
   </si>
   <si>
     <t xml:space="preserve">8.94027614593506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80412864685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75874710083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66798305511475</t>
+    <t xml:space="preserve">8.8041296005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75874614715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66798210144043</t>
   </si>
   <si>
     <t xml:space="preserve">8.62260055541992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53183650970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35030937194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16878032684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98725080490112</t>
+    <t xml:space="preserve">8.53183555603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35030841827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16877937316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98725032806396</t>
   </si>
   <si>
     <t xml:space="preserve">8.03263378143311</t>
@@ -341,25 +341,25 @@
     <t xml:space="preserve">7.94186925888062</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30492496490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21416091918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39569091796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57721996307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71336555480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53202152252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25706195831299</t>
+    <t xml:space="preserve">8.3049259185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21416282653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39568996429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5772180557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71336460113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53202247619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25706005096436</t>
   </si>
   <si>
     <t xml:space="preserve">9.44036865234375</t>
@@ -377,10 +377,10 @@
     <t xml:space="preserve">8.98209857940674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02792644500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62367630004883</t>
+    <t xml:space="preserve">9.02792549133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62367725372314</t>
   </si>
   <si>
     <t xml:space="preserve">9.80698394775391</t>
@@ -398,73 +398,73 @@
     <t xml:space="preserve">10.2652549743652</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3569087982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5402173995972</t>
+    <t xml:space="preserve">10.3569097518921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5402183532715</t>
   </si>
   <si>
     <t xml:space="preserve">10.631872177124</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8151798248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7235260009766</t>
+    <t xml:space="preserve">10.8151807785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7235250473022</t>
   </si>
   <si>
     <t xml:space="preserve">10.9068336486816</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9984893798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0901412963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1817951202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2734498977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4567584991455</t>
+    <t xml:space="preserve">10.9984874725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0901432037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1817960739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2734508514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4567565917969</t>
   </si>
   <si>
     <t xml:space="preserve">11.3651027679443</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4485626220703</t>
+    <t xml:space="preserve">10.4485635757446</t>
   </si>
   <si>
     <t xml:space="preserve">9.71533203125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79879093170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24886608123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21123313903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30288791656494</t>
+    <t xml:space="preserve">8.79878997802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24886512756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2112340927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30288696289062</t>
   </si>
   <si>
     <t xml:space="preserve">9.03709030151367</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39454174041748</t>
+    <t xml:space="preserve">9.3945426940918</t>
   </si>
   <si>
     <t xml:space="preserve">9.76115798950195</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66950416564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57784938812256</t>
+    <t xml:space="preserve">9.6695032119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57785034179688</t>
   </si>
   <si>
     <t xml:space="preserve">10.0361194610596</t>
@@ -473,58 +473,58 @@
     <t xml:space="preserve">9.94446754455566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82552528381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73283004760742</t>
+    <t xml:space="preserve">9.82552433013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73283100128174</t>
   </si>
   <si>
     <t xml:space="preserve">9.59379100799561</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96456527709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91821670532227</t>
+    <t xml:space="preserve">9.96456432342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91821765899658</t>
   </si>
   <si>
     <t xml:space="preserve">9.54744338989258</t>
   </si>
   <si>
-    <t xml:space="preserve">10.010910987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1036043167114</t>
+    <t xml:space="preserve">10.0109119415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1036052703857</t>
   </si>
   <si>
     <t xml:space="preserve">10.1499509811401</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1962976455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77917766571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87187099456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0572595596313</t>
+    <t xml:space="preserve">10.1962985992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77917671203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87187004089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.057258605957</t>
   </si>
   <si>
     <t xml:space="preserve">10.2889928817749</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4743785858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2426462173462</t>
+    <t xml:space="preserve">10.4743804931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2426443099976</t>
   </si>
   <si>
     <t xml:space="preserve">10.381685256958</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68648338317871</t>
+    <t xml:space="preserve">9.68648242950439</t>
   </si>
   <si>
     <t xml:space="preserve">9.64013576507568</t>
@@ -533,10 +533,10 @@
     <t xml:space="preserve">9.50109672546387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31570816040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23228549957275</t>
+    <t xml:space="preserve">9.31570911407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23228454589844</t>
   </si>
   <si>
     <t xml:space="preserve">9.1952075958252</t>
@@ -545,13 +545,13 @@
     <t xml:space="preserve">9.25082302093506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.269362449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2137451171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04689693450928</t>
+    <t xml:space="preserve">9.26936149597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21374607086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04689788818359</t>
   </si>
   <si>
     <t xml:space="preserve">9.12105274200439</t>
@@ -569,10 +569,10 @@
     <t xml:space="preserve">9.02835845947266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95420360565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71320056915283</t>
+    <t xml:space="preserve">8.95420455932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71319961547852</t>
   </si>
   <si>
     <t xml:space="preserve">8.99128150939941</t>
@@ -581,13 +581,13 @@
     <t xml:space="preserve">8.76881694793701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89858818054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93566513061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3353395462036</t>
+    <t xml:space="preserve">8.89858722686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93566608428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3353385925293</t>
   </si>
   <si>
     <t xml:space="preserve">10.9841938018799</t>
@@ -596,31 +596,31 @@
     <t xml:space="preserve">11.0305404663086</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2159280776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.49400806427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.540355682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5867033004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6330499649048</t>
+    <t xml:space="preserve">11.2159290313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4940090179443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5403547286987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5867023468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6330490112305</t>
   </si>
   <si>
     <t xml:space="preserve">11.7257432937622</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9111309051514</t>
+    <t xml:space="preserve">11.9111299514771</t>
   </si>
   <si>
     <t xml:space="preserve">11.9574766159058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1892118453979</t>
+    <t xml:space="preserve">12.1892108917236</t>
   </si>
   <si>
     <t xml:space="preserve">12.2819042205811</t>
@@ -632,31 +632,31 @@
     <t xml:space="preserve">12.5136384963989</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3282508850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1428642272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0965185165405</t>
+    <t xml:space="preserve">12.3282527923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1428651809692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0965175628662</t>
   </si>
   <si>
     <t xml:space="preserve">12.555121421814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5082740783691</t>
+    <t xml:space="preserve">12.5082750320435</t>
   </si>
   <si>
     <t xml:space="preserve">12.6488170623779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.46142578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4145784378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7425117492676</t>
+    <t xml:space="preserve">12.4614276885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4145793914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7425127029419</t>
   </si>
   <si>
     <t xml:space="preserve">12.6956644058228</t>
@@ -665,25 +665,25 @@
     <t xml:space="preserve">12.2271900177002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1803417205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3208847045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.274037361145</t>
+    <t xml:space="preserve">12.1803426742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3208837509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2740383148193</t>
   </si>
   <si>
     <t xml:space="preserve">12.8362064361572</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7893590927124</t>
+    <t xml:space="preserve">12.7893581390381</t>
   </si>
   <si>
     <t xml:space="preserve">12.6019697189331</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9299011230469</t>
+    <t xml:space="preserve">12.9299020767212</t>
   </si>
   <si>
     <t xml:space="preserve">12.8830537796021</t>
@@ -692,49 +692,49 @@
     <t xml:space="preserve">13.0704441070557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6794624328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8668518066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0542411804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3353261947632</t>
+    <t xml:space="preserve">13.679461479187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8668508529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0542402267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3353252410889</t>
   </si>
   <si>
     <t xml:space="preserve">14.5695638656616</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2254276275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1317310333252</t>
+    <t xml:space="preserve">15.2254285812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1317329406738</t>
   </si>
   <si>
     <t xml:space="preserve">14.7569532394409</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0380363464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1785802841187</t>
+    <t xml:space="preserve">15.0380373001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.178581237793</t>
   </si>
   <si>
     <t xml:space="preserve">15.3191232681274</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8974952697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4596643447876</t>
+    <t xml:space="preserve">14.8974943161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4596662521362</t>
   </si>
   <si>
     <t xml:space="preserve">15.4128189086914</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5533590316772</t>
+    <t xml:space="preserve">15.5533599853516</t>
   </si>
   <si>
     <t xml:space="preserve">16.0686817169189</t>
@@ -743,10 +743,10 @@
     <t xml:space="preserve">16.8650894165039</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0056304931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7713928222656</t>
+    <t xml:space="preserve">17.0056324005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7713947296143</t>
   </si>
   <si>
     <t xml:space="preserve">17.193021774292</t>
@@ -755,25 +755,25 @@
     <t xml:space="preserve">17.0524787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9587841033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7245464324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6308498382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5371570587158</t>
+    <t xml:space="preserve">16.9587860107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7245483398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6308536529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5371551513672</t>
   </si>
   <si>
     <t xml:space="preserve">16.584005355835</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2092208862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2560710906982</t>
+    <t xml:space="preserve">16.2092227935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2560729980469</t>
   </si>
   <si>
     <t xml:space="preserve">17.1461715698242</t>
@@ -782,13 +782,13 @@
     <t xml:space="preserve">16.396614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3029193878174</t>
+    <t xml:space="preserve">16.3029174804688</t>
   </si>
   <si>
     <t xml:space="preserve">15.8344440460205</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1155281066895</t>
+    <t xml:space="preserve">16.1155300140381</t>
   </si>
   <si>
     <t xml:space="preserve">16.0218353271484</t>
@@ -797,28 +797,28 @@
     <t xml:space="preserve">16.1623764038086</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9749870300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7407493591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4434623718262</t>
+    <t xml:space="preserve">15.974986076355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7407484054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4434604644775</t>
   </si>
   <si>
     <t xml:space="preserve">16.9119358062744</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0993270874023</t>
+    <t xml:space="preserve">17.0993251800537</t>
   </si>
   <si>
     <t xml:space="preserve">16.677698135376</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8182411193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2722749710083</t>
+    <t xml:space="preserve">16.818244934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.272274017334</t>
   </si>
   <si>
     <t xml:space="preserve">15.084885597229</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">14.9911909103394</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8038015365601</t>
+    <t xml:space="preserve">14.8037996292114</t>
   </si>
   <si>
     <t xml:space="preserve">14.4758682250977</t>
@@ -842,34 +842,34 @@
     <t xml:space="preserve">14.288477897644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5227165222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9605464935303</t>
+    <t xml:space="preserve">14.5227155685425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.960545539856</t>
   </si>
   <si>
     <t xml:space="preserve">14.2416305541992</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1947822570801</t>
+    <t xml:space="preserve">14.1947832107544</t>
   </si>
   <si>
     <t xml:space="preserve">14.0073938369751</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7263078689575</t>
+    <t xml:space="preserve">13.7263088226318</t>
   </si>
   <si>
     <t xml:space="preserve">14.1479358673096</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4290208816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6164102554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7731552124023</t>
+    <t xml:space="preserve">14.4290199279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6164112091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7731561660767</t>
   </si>
   <si>
     <t xml:space="preserve">13.3515281677246</t>
@@ -896,25 +896,25 @@
     <t xml:space="preserve">12.0866460800171</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9929513931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8992567062378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0397996902466</t>
+    <t xml:space="preserve">11.9929523468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8992576599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0397987365723</t>
   </si>
   <si>
     <t xml:space="preserve">12.1334943771362</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4776306152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2433929443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3839349746704</t>
+    <t xml:space="preserve">11.4776296615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2433938980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3839340209961</t>
   </si>
   <si>
     <t xml:space="preserve">11.6650199890137</t>
@@ -926,22 +926,22 @@
     <t xml:space="preserve">10.9623079299927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7280702590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1965446472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.571325302124</t>
+    <t xml:space="preserve">10.7280712127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1965456008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5713243484497</t>
   </si>
   <si>
     <t xml:space="preserve">11.3370876312256</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2902412414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7118673324585</t>
+    <t xml:space="preserve">11.2902402877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7118682861328</t>
   </si>
   <si>
     <t xml:space="preserve">11.7587156295776</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">11.8055629730225</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0091562271118</t>
+    <t xml:space="preserve">11.0091552734375</t>
   </si>
   <si>
     <t xml:space="preserve">9.46318912506104</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">8.31074142456055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45128440856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61993408203125</t>
+    <t xml:space="preserve">8.45128345489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61993312835693</t>
   </si>
   <si>
     <t xml:space="preserve">8.44191455841064</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">8.32948112487793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25452423095703</t>
+    <t xml:space="preserve">8.25452327728271</t>
   </si>
   <si>
     <t xml:space="preserve">8.43254470825195</t>
@@ -986,13 +986,13 @@
     <t xml:space="preserve">8.47002220153809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32010936737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20767688751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0858736038208</t>
+    <t xml:space="preserve">8.32011127471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20767784118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08587265014648</t>
   </si>
   <si>
     <t xml:space="preserve">7.78604936599731</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">7.83289623260498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90785264968872</t>
+    <t xml:space="preserve">7.90785312652588</t>
   </si>
   <si>
     <t xml:space="preserve">7.50496482849121</t>
@@ -1025,19 +1025,19 @@
     <t xml:space="preserve">7.28009700775146</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98027324676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93342590332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06459808349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02712059020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34568357467651</t>
+    <t xml:space="preserve">6.98027276992798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93342542648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06459856033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0271201133728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34568309783936</t>
   </si>
   <si>
     <t xml:space="preserve">7.5424427986145</t>
@@ -1055,16 +1055,16 @@
     <t xml:space="preserve">8.46116256713867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53747367858887</t>
+    <t xml:space="preserve">8.53747463226318</t>
   </si>
   <si>
     <t xml:space="preserve">8.68056106567383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77595138549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84272575378418</t>
+    <t xml:space="preserve">8.77595233917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8427267074585</t>
   </si>
   <si>
     <t xml:space="preserve">8.72825527191162</t>
@@ -1073,25 +1073,25 @@
     <t xml:space="preserve">8.66148281097412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49931716918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42300605773926</t>
+    <t xml:space="preserve">8.49931812286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42300510406494</t>
   </si>
   <si>
     <t xml:space="preserve">8.39438915252686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60424900054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48977851867676</t>
+    <t xml:space="preserve">8.604248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48977947235107</t>
   </si>
   <si>
     <t xml:space="preserve">8.29899787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12729549407959</t>
+    <t xml:space="preserve">8.12729454040527</t>
   </si>
   <si>
     <t xml:space="preserve">7.89835643768311</t>
@@ -1100,13 +1100,13 @@
     <t xml:space="preserve">8.10821628570557</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8411226272583</t>
+    <t xml:space="preserve">7.84112215042114</t>
   </si>
   <si>
     <t xml:space="preserve">8.33715343475342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20360660552979</t>
+    <t xml:space="preserve">8.2036075592041</t>
   </si>
   <si>
     <t xml:space="preserve">8.06052017211914</t>
@@ -1115,13 +1115,13 @@
     <t xml:space="preserve">8.07959938049316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07005977630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92697334289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98420763015747</t>
+    <t xml:space="preserve">8.07005882263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92697429656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98420858383179</t>
   </si>
   <si>
     <t xml:space="preserve">8.30853652954102</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">8.26084136962891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2703800201416</t>
+    <t xml:space="preserve">8.27038097381592</t>
   </si>
   <si>
     <t xml:space="preserve">8.18452835083008</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03190422058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96512985229492</t>
+    <t xml:space="preserve">8.03190326690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96513080596924</t>
   </si>
   <si>
     <t xml:space="preserve">7.86019992828369</t>
@@ -1151,10 +1151,10 @@
     <t xml:space="preserve">7.71711397171021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91743421554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76480960845947</t>
+    <t xml:space="preserve">7.91743516921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76481008529663</t>
   </si>
   <si>
     <t xml:space="preserve">7.72665309906006</t>
@@ -1169,10 +1169,10 @@
     <t xml:space="preserve">7.65987968444824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.165452003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32761478424072</t>
+    <t xml:space="preserve">8.16545104980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32761383056641</t>
   </si>
   <si>
     <t xml:space="preserve">8.11775588989258</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">8.2322244644165</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31807613372803</t>
+    <t xml:space="preserve">8.31807518005371</t>
   </si>
   <si>
     <t xml:space="preserve">8.15591144561768</t>
@@ -1196,19 +1196,19 @@
     <t xml:space="preserve">8.22268486022949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25130081176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35623264312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2417631149292</t>
+    <t xml:space="preserve">8.25130176544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35623168945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24176406860352</t>
   </si>
   <si>
     <t xml:space="preserve">8.34669303894043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95559072494507</t>
+    <t xml:space="preserve">7.95559167861938</t>
   </si>
   <si>
     <t xml:space="preserve">7.77434825897217</t>
@@ -1220,37 +1220,37 @@
     <t xml:space="preserve">7.97466850280762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01282501220703</t>
+    <t xml:space="preserve">8.01282596588135</t>
   </si>
   <si>
     <t xml:space="preserve">8.05098152160645</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67895793914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7361912727356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6980357170105</t>
+    <t xml:space="preserve">7.67895746231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73619174957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69803524017334</t>
   </si>
   <si>
     <t xml:space="preserve">7.51679372787476</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59310579299927</t>
+    <t xml:space="preserve">7.59310626983643</t>
   </si>
   <si>
     <t xml:space="preserve">7.44048070907593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53587198257446</t>
+    <t xml:space="preserve">7.5358715057373</t>
   </si>
   <si>
     <t xml:space="preserve">7.62172269821167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52633237838745</t>
+    <t xml:space="preserve">7.52633190155029</t>
   </si>
   <si>
     <t xml:space="preserve">7.34508991241455</t>
@@ -1259,22 +1259,22 @@
     <t xml:space="preserve">7.20200395584106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1829252243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14476919174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12569093704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23062086105347</t>
+    <t xml:space="preserve">7.18292570114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14476871490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12569046020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23062133789062</t>
   </si>
   <si>
     <t xml:space="preserve">7.1543083190918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24969911575317</t>
+    <t xml:space="preserve">7.24969863891602</t>
   </si>
   <si>
     <t xml:space="preserve">7.24016046524048</t>
@@ -1283,16 +1283,16 @@
     <t xml:space="preserve">7.46909809112549</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41186380386353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45001935958862</t>
+    <t xml:space="preserve">7.41186332702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45001983642578</t>
   </si>
   <si>
     <t xml:space="preserve">7.28785514831543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39278554916382</t>
+    <t xml:space="preserve">7.39278507232666</t>
   </si>
   <si>
     <t xml:space="preserve">7.3355507850647</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">7.61218404769897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90789604187012</t>
+    <t xml:space="preserve">7.90789556503296</t>
   </si>
   <si>
     <t xml:space="preserve">7.94605159759521</t>
@@ -1313,25 +1313,25 @@
     <t xml:space="preserve">7.70757484436035</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87927913665771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99374675750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75527048110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81250429153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79342651367188</t>
+    <t xml:space="preserve">7.8792781829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99374771118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75527000427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81250381469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79342699050903</t>
   </si>
   <si>
     <t xml:space="preserve">7.80296611785889</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85066080093384</t>
+    <t xml:space="preserve">7.85065984725952</t>
   </si>
   <si>
     <t xml:space="preserve">7.74573087692261</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">7.83158302307129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66941833496094</t>
+    <t xml:space="preserve">7.66941785812378</t>
   </si>
   <si>
     <t xml:space="preserve">7.60264492034912</t>
@@ -1361,13 +1361,13 @@
     <t xml:space="preserve">7.3641676902771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10661315917969</t>
+    <t xml:space="preserve">7.10661268234253</t>
   </si>
   <si>
     <t xml:space="preserve">7.27831649780273</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08753442764282</t>
+    <t xml:space="preserve">7.08753490447998</t>
   </si>
   <si>
     <t xml:space="preserve">7.05891799926758</t>
@@ -2220,6 +2220,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.30000019073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34000015258789</t>
   </si>
 </sst>
 </file>
@@ -62332,7 +62335,7 @@
     </row>
     <row r="2300">
       <c r="A2300" s="1" t="n">
-        <v>45965.6910069444</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2300" t="n">
         <v>17274</v>
@@ -62353,6 +62356,32 @@
         <v>733</v>
       </c>
       <c r="H2300" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2301">
+      <c r="A2301" s="1" t="n">
+        <v>45966.691087963</v>
+      </c>
+      <c r="B2301" t="n">
+        <v>12138</v>
+      </c>
+      <c r="C2301" t="n">
+        <v>9.38000011444092</v>
+      </c>
+      <c r="D2301" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="E2301" t="n">
+        <v>9.34000015258789</v>
+      </c>
+      <c r="F2301" t="n">
+        <v>9.34000015258789</v>
+      </c>
+      <c r="G2301" t="s">
+        <v>736</v>
+      </c>
+      <c r="H2301" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="738">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,37 +38,37 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07642269134521</t>
+    <t xml:space="preserve">9.0764217376709</t>
   </si>
   <si>
     <t xml:space="preserve">FF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98565673828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08549785614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24887275695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09457588195801</t>
+    <t xml:space="preserve">8.98565769195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08549880981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24887371063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09457492828369</t>
   </si>
   <si>
     <t xml:space="preserve">9.12180423736572</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03104114532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95388984680176</t>
+    <t xml:space="preserve">9.03103923797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95389080047607</t>
   </si>
   <si>
     <t xml:space="preserve">8.89943218231201</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89489364624023</t>
+    <t xml:space="preserve">8.89489269256592</t>
   </si>
   <si>
     <t xml:space="preserve">8.84951114654541</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">8.85858821868896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87673950195312</t>
+    <t xml:space="preserve">8.87674140930176</t>
   </si>
   <si>
     <t xml:space="preserve">8.76782321929932</t>
@@ -86,13 +86,13 @@
     <t xml:space="preserve">8.8676643371582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04919052124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23072052001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11272811889648</t>
+    <t xml:space="preserve">9.04919338226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23072147369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11272716522217</t>
   </si>
   <si>
     <t xml:space="preserve">8.96750450134277</t>
@@ -104,94 +104,94 @@
     <t xml:space="preserve">8.92212295532227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00380992889404</t>
+    <t xml:space="preserve">9.00381088256836</t>
   </si>
   <si>
     <t xml:space="preserve">9.15810966491699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16718578338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43947887420654</t>
+    <t xml:space="preserve">9.16718673706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43947792053223</t>
   </si>
   <si>
     <t xml:space="preserve">9.54839611053467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62100696563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80253601074219</t>
+    <t xml:space="preserve">9.62100791931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80253505706787</t>
   </si>
   <si>
     <t xml:space="preserve">9.71177101135254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56655025482178</t>
+    <t xml:space="preserve">9.56654739379883</t>
   </si>
   <si>
     <t xml:space="preserve">9.58470153808594</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57562446594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53024291992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50301456451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60285568237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63916110992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79345798492432</t>
+    <t xml:space="preserve">9.5756254196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53024196624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50301361083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60285377502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63915920257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79345893859863</t>
   </si>
   <si>
     <t xml:space="preserve">9.95683479309082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93868064880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98406505584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73900032043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76623058319092</t>
+    <t xml:space="preserve">9.93868160247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98406410217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73900127410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7662296295166</t>
   </si>
   <si>
     <t xml:space="preserve">9.74807643890381</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75715351104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64823627471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82068729400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7026948928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72084808349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67546558380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66638851165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63008308410645</t>
+    <t xml:space="preserve">9.75715255737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64823722839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82068824768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70269393920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72084712982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67546463012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66638946533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63008213043213</t>
   </si>
   <si>
     <t xml:space="preserve">9.65731239318848</t>
@@ -200,16 +200,16 @@
     <t xml:space="preserve">9.68454265594482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81161403656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82976341247559</t>
+    <t xml:space="preserve">9.81161212921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8297643661499</t>
   </si>
   <si>
     <t xml:space="preserve">9.84791851043701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83884143829346</t>
+    <t xml:space="preserve">9.83884239196777</t>
   </si>
   <si>
     <t xml:space="preserve">9.72992420196533</t>
@@ -218,31 +218,31 @@
     <t xml:space="preserve">9.78438186645508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55747318267822</t>
+    <t xml:space="preserve">9.55747222900391</t>
   </si>
   <si>
     <t xml:space="preserve">9.34871482849121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33963775634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27610397338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25794887542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19441699981689</t>
+    <t xml:space="preserve">9.33963680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27610301971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25794982910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19441509246826</t>
   </si>
   <si>
     <t xml:space="preserve">9.18533897399902</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4122486114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22164344787598</t>
+    <t xml:space="preserve">9.41224956512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22164440155029</t>
   </si>
   <si>
     <t xml:space="preserve">9.31240940093994</t>
@@ -251,49 +251,49 @@
     <t xml:space="preserve">9.26702690124512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29425621032715</t>
+    <t xml:space="preserve">9.29425525665283</t>
   </si>
   <si>
     <t xml:space="preserve">9.28518009185791</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37594413757324</t>
+    <t xml:space="preserve">9.37594318389893</t>
   </si>
   <si>
     <t xml:space="preserve">9.36686706542969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3850212097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45763206481934</t>
+    <t xml:space="preserve">9.38502025604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45763111114502</t>
   </si>
   <si>
     <t xml:space="preserve">9.39409732818604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48486042022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49393653869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4485559463501</t>
+    <t xml:space="preserve">9.48486137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49393749237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44855499267578</t>
   </si>
   <si>
     <t xml:space="preserve">9.4757833480835</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23979759216309</t>
+    <t xml:space="preserve">9.2397985458374</t>
   </si>
   <si>
     <t xml:space="preserve">9.14903259277344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21256828308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20349311828613</t>
+    <t xml:space="preserve">9.21256732940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20349216461182</t>
   </si>
   <si>
     <t xml:space="preserve">9.13088130950928</t>
@@ -305,7 +305,7 @@
     <t xml:space="preserve">8.94027614593506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80412769317627</t>
+    <t xml:space="preserve">8.80412864685059</t>
   </si>
   <si>
     <t xml:space="preserve">8.75874710083008</t>
@@ -314,37 +314,37 @@
     <t xml:space="preserve">8.66798305511475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62260150909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53183555603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35030746459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16878128051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98725175857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03263378143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12339687347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25954437255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94186878204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30492687225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21416187286377</t>
+    <t xml:space="preserve">8.62260055541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53183650970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35030841827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16877841949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98725032806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03263282775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12339782714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25954341888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94186925888062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3049259185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21416091918945</t>
   </si>
   <si>
     <t xml:space="preserve">8.39568996429443</t>
@@ -356,10 +356,10 @@
     <t xml:space="preserve">8.71336555480957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53202152252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25705909729004</t>
+    <t xml:space="preserve">9.53202247619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25706100463867</t>
   </si>
   <si>
     <t xml:space="preserve">9.44036865234375</t>
@@ -368,49 +368,49 @@
     <t xml:space="preserve">9.16540718078613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07375144958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11958122253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98209953308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02792549133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62367725372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80698394775391</t>
+    <t xml:space="preserve">9.07375240325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11958026885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98209857940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02792644500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62367630004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80698490142822</t>
   </si>
   <si>
     <t xml:space="preserve">9.89863872528076</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9902925491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1736011505127</t>
+    <t xml:space="preserve">9.99029350280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.173602104187</t>
   </si>
   <si>
     <t xml:space="preserve">10.2652559280396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3569097518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5402183532715</t>
+    <t xml:space="preserve">10.3569107055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5402173995972</t>
   </si>
   <si>
     <t xml:space="preserve">10.631872177124</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8151798248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7235269546509</t>
+    <t xml:space="preserve">10.8151807785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7235260009766</t>
   </si>
   <si>
     <t xml:space="preserve">10.9068336486816</t>
@@ -419,28 +419,28 @@
     <t xml:space="preserve">10.9984884262085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.090142250061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1817960739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2734508514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4567584991455</t>
+    <t xml:space="preserve">11.0901432037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1817970275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2734489440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4567575454712</t>
   </si>
   <si>
     <t xml:space="preserve">11.3651037216187</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4485645294189</t>
+    <t xml:space="preserve">10.4485635757446</t>
   </si>
   <si>
     <t xml:space="preserve">9.71533107757568</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79879093170166</t>
+    <t xml:space="preserve">8.79878997802734</t>
   </si>
   <si>
     <t xml:space="preserve">8.24886608123779</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">9.2112340927124</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30288791656494</t>
+    <t xml:space="preserve">9.30288696289062</t>
   </si>
   <si>
     <t xml:space="preserve">9.03709030151367</t>
@@ -461,37 +461,37 @@
     <t xml:space="preserve">9.76115798950195</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66950511932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57784843444824</t>
+    <t xml:space="preserve">9.6695032119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57785034179688</t>
   </si>
   <si>
     <t xml:space="preserve">10.0361194610596</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94446659088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82552433013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73283100128174</t>
+    <t xml:space="preserve">9.94446754455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82552528381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73283004760742</t>
   </si>
   <si>
     <t xml:space="preserve">9.59379100799561</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96456527709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91821670532227</t>
+    <t xml:space="preserve">9.96456432342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91821765899658</t>
   </si>
   <si>
     <t xml:space="preserve">9.54744338989258</t>
   </si>
   <si>
-    <t xml:space="preserve">10.010910987854</t>
+    <t xml:space="preserve">10.0109119415283</t>
   </si>
   <si>
     <t xml:space="preserve">10.1036043167114</t>
@@ -503,10 +503,10 @@
     <t xml:space="preserve">10.1962985992432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77917766571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87187004089355</t>
+    <t xml:space="preserve">9.77917671203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87187099456787</t>
   </si>
   <si>
     <t xml:space="preserve">10.057258605957</t>
@@ -515,43 +515,43 @@
     <t xml:space="preserve">10.2889919281006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4743795394897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2426452636719</t>
+    <t xml:space="preserve">10.4743804931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2426443099976</t>
   </si>
   <si>
     <t xml:space="preserve">10.381685256958</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68648338317871</t>
+    <t xml:space="preserve">9.68648242950439</t>
   </si>
   <si>
     <t xml:space="preserve">9.64013576507568</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50109767913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31571006774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23228549957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19520664215088</t>
+    <t xml:space="preserve">9.50109672546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31570911407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23228454589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1952075958252</t>
   </si>
   <si>
     <t xml:space="preserve">9.25082302093506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26936340332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21374607086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04689693450928</t>
+    <t xml:space="preserve">9.269362449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2137451171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04689788818359</t>
   </si>
   <si>
     <t xml:space="preserve">9.12105274200439</t>
@@ -560,22 +560,22 @@
     <t xml:space="preserve">9.06543636322021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97274208068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17666816711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02835941314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95420265197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71319961547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9912805557251</t>
+    <t xml:space="preserve">8.97274303436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17666721343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02835750579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95420455932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71320056915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99128150939941</t>
   </si>
   <si>
     <t xml:space="preserve">8.76881694793701</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">8.89858818054199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93566703796387</t>
+    <t xml:space="preserve">8.93566608428955</t>
   </si>
   <si>
     <t xml:space="preserve">10.3353385925293</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">10.9841938018799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0305414199829</t>
+    <t xml:space="preserve">11.0305404663086</t>
   </si>
   <si>
     <t xml:space="preserve">11.2159290313721</t>
@@ -605,22 +605,22 @@
     <t xml:space="preserve">11.540355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5867033004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6330499649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7257423400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9111309051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9574775695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1892118453979</t>
+    <t xml:space="preserve">11.5867023468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6330490112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7257442474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9111299514771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9574756622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1892108917236</t>
   </si>
   <si>
     <t xml:space="preserve">12.2819042205811</t>
@@ -629,25 +629,25 @@
     <t xml:space="preserve">12.3745985031128</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5136375427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3282518386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1428642272949</t>
+    <t xml:space="preserve">12.5136384963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3282527923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1428651809692</t>
   </si>
   <si>
     <t xml:space="preserve">12.0965185165405</t>
   </si>
   <si>
-    <t xml:space="preserve">12.555121421814</t>
+    <t xml:space="preserve">12.5551223754883</t>
   </si>
   <si>
     <t xml:space="preserve">12.5082750320435</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6488161087036</t>
+    <t xml:space="preserve">12.6488170623779</t>
   </si>
   <si>
     <t xml:space="preserve">12.4614267349243</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">12.2271900177002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1803417205811</t>
+    <t xml:space="preserve">12.1803426742554</t>
   </si>
   <si>
     <t xml:space="preserve">12.3208847045898</t>
@@ -677,25 +677,25 @@
     <t xml:space="preserve">12.8362064361572</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7893590927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6019687652588</t>
+    <t xml:space="preserve">12.7893581390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6019697189331</t>
   </si>
   <si>
     <t xml:space="preserve">12.9299011230469</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8830537796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0704431533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6794624328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8668518066406</t>
+    <t xml:space="preserve">12.8830547332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.07044506073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.679461479187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8668508529663</t>
   </si>
   <si>
     <t xml:space="preserve">14.0542411804199</t>
@@ -704,19 +704,19 @@
     <t xml:space="preserve">14.3353261947632</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5695629119873</t>
+    <t xml:space="preserve">14.5695638656616</t>
   </si>
   <si>
     <t xml:space="preserve">15.2254285812378</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1317319869995</t>
+    <t xml:space="preserve">15.1317329406738</t>
   </si>
   <si>
     <t xml:space="preserve">14.7569522857666</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0380363464355</t>
+    <t xml:space="preserve">15.0380382537842</t>
   </si>
   <si>
     <t xml:space="preserve">15.178581237793</t>
@@ -725,13 +725,13 @@
     <t xml:space="preserve">15.3191232681274</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8974952697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4596643447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4128189086914</t>
+    <t xml:space="preserve">14.8974943161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4596662521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4128179550171</t>
   </si>
   <si>
     <t xml:space="preserve">15.5533609390259</t>
@@ -740,13 +740,13 @@
     <t xml:space="preserve">16.0686817169189</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8650894165039</t>
+    <t xml:space="preserve">16.8650913238525</t>
   </si>
   <si>
     <t xml:space="preserve">17.0056324005127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7713928222656</t>
+    <t xml:space="preserve">16.7713947296143</t>
   </si>
   <si>
     <t xml:space="preserve">17.193021774292</t>
@@ -758,7 +758,7 @@
     <t xml:space="preserve">16.9587841033936</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7245464324951</t>
+    <t xml:space="preserve">16.7245483398438</t>
   </si>
   <si>
     <t xml:space="preserve">16.6308517456055</t>
@@ -767,25 +767,25 @@
     <t xml:space="preserve">16.5371570587158</t>
   </si>
   <si>
-    <t xml:space="preserve">16.584005355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2092227935791</t>
+    <t xml:space="preserve">16.5840034484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2092247009277</t>
   </si>
   <si>
     <t xml:space="preserve">16.2560710906982</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1461715698242</t>
+    <t xml:space="preserve">17.1461734771729</t>
   </si>
   <si>
     <t xml:space="preserve">16.396614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3029193878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8344440460205</t>
+    <t xml:space="preserve">16.3029174804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8344449996948</t>
   </si>
   <si>
     <t xml:space="preserve">16.1155300140381</t>
@@ -794,10 +794,10 @@
     <t xml:space="preserve">16.0218353271484</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1623764038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9749870300293</t>
+    <t xml:space="preserve">16.1623783111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.974986076355</t>
   </si>
   <si>
     <t xml:space="preserve">15.7407493591309</t>
@@ -806,31 +806,31 @@
     <t xml:space="preserve">16.4434604644775</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9119358062744</t>
+    <t xml:space="preserve">16.911937713623</t>
   </si>
   <si>
     <t xml:space="preserve">17.0993251800537</t>
   </si>
   <si>
-    <t xml:space="preserve">16.677698135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8182430267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2722749710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0848846435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.991189956665</t>
+    <t xml:space="preserve">16.6777000427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.818244934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.272274017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.084885597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9911909103394</t>
   </si>
   <si>
     <t xml:space="preserve">14.8038005828857</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4758672714233</t>
+    <t xml:space="preserve">14.4758682250977</t>
   </si>
   <si>
     <t xml:space="preserve">14.382173538208</t>
@@ -857,22 +857,22 @@
     <t xml:space="preserve">14.0073928833008</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7263078689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1479358673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4290208816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6164102554321</t>
+    <t xml:space="preserve">13.7263088226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1479368209839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4290199279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6164112091064</t>
   </si>
   <si>
     <t xml:space="preserve">13.7731561660767</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3515291213989</t>
+    <t xml:space="preserve">13.3515281677246</t>
   </si>
   <si>
     <t xml:space="preserve">13.3046808242798</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">12.3677320480347</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0866470336914</t>
+    <t xml:space="preserve">12.0866460800171</t>
   </si>
   <si>
     <t xml:space="preserve">11.9929523468018</t>
@@ -902,7 +902,7 @@
     <t xml:space="preserve">11.8992576599121</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0398006439209</t>
+    <t xml:space="preserve">12.0397987365723</t>
   </si>
   <si>
     <t xml:space="preserve">12.1334943771362</t>
@@ -911,31 +911,31 @@
     <t xml:space="preserve">11.4776306152344</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2433929443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3839349746704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6650190353394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4307832717896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9623079299927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7280693054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1965446472168</t>
+    <t xml:space="preserve">11.2433938980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3839340209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.665020942688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4307823181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9623069763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7280712127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1965456008911</t>
   </si>
   <si>
     <t xml:space="preserve">11.571325302124</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3370885848999</t>
+    <t xml:space="preserve">11.3370876312256</t>
   </si>
   <si>
     <t xml:space="preserve">11.2902402877808</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">11.7118673324585</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7587146759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8055629730225</t>
+    <t xml:space="preserve">11.7587156295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8055639266968</t>
   </si>
   <si>
     <t xml:space="preserve">11.0091552734375</t>
@@ -956,16 +956,16 @@
     <t xml:space="preserve">9.46318912506104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33884906768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57308578491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31074047088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45128440856934</t>
+    <t xml:space="preserve">8.3388500213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57308673858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31074142456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45128345489502</t>
   </si>
   <si>
     <t xml:space="preserve">8.61993408203125</t>
@@ -977,16 +977,16 @@
     <t xml:space="preserve">8.32948017120361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25452518463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43254470825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47002124786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32011032104492</t>
+    <t xml:space="preserve">8.25452423095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43254566192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47002220153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32011127471924</t>
   </si>
   <si>
     <t xml:space="preserve">8.20767688751221</t>
@@ -995,10 +995,10 @@
     <t xml:space="preserve">8.08587265014648</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78604984283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49559497833252</t>
+    <t xml:space="preserve">7.78604936599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49559545516968</t>
   </si>
   <si>
     <t xml:space="preserve">7.33631372451782</t>
@@ -1007,28 +1007,28 @@
     <t xml:space="preserve">7.23324918746948</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83289670944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9078516960144</t>
+    <t xml:space="preserve">7.83289623260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90785264968872</t>
   </si>
   <si>
     <t xml:space="preserve">7.50496482849121</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37379217147827</t>
+    <t xml:space="preserve">7.37379169464111</t>
   </si>
   <si>
     <t xml:space="preserve">7.12081527709961</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28009605407715</t>
+    <t xml:space="preserve">7.28009700775146</t>
   </si>
   <si>
     <t xml:space="preserve">6.98027324676514</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93342590332031</t>
+    <t xml:space="preserve">6.93342542648315</t>
   </si>
   <si>
     <t xml:space="preserve">7.06459808349609</t>
@@ -1037,28 +1037,28 @@
     <t xml:space="preserve">7.02712059020996</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34568357467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54244232177734</t>
+    <t xml:space="preserve">7.34568309783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5424427986145</t>
   </si>
   <si>
     <t xml:space="preserve">8.19830703735352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21704769134521</t>
+    <t xml:space="preserve">8.2170467376709</t>
   </si>
   <si>
     <t xml:space="preserve">8.65194320678711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46116161346436</t>
+    <t xml:space="preserve">8.46116256713867</t>
   </si>
   <si>
     <t xml:space="preserve">8.53747367858887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68056106567383</t>
+    <t xml:space="preserve">8.68056201934814</t>
   </si>
   <si>
     <t xml:space="preserve">8.77595138549805</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">8.84272575378418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72825527191162</t>
+    <t xml:space="preserve">8.72825622558594</t>
   </si>
   <si>
     <t xml:space="preserve">8.66148281097412</t>
@@ -1076,7 +1076,7 @@
     <t xml:space="preserve">8.49931812286377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42300605773926</t>
+    <t xml:space="preserve">8.42300510406494</t>
   </si>
   <si>
     <t xml:space="preserve">8.39438915252686</t>
@@ -1094,10 +1094,10 @@
     <t xml:space="preserve">8.12729454040527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89835596084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10821628570557</t>
+    <t xml:space="preserve">7.89835643768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10821723937988</t>
   </si>
   <si>
     <t xml:space="preserve">7.84112215042114</t>
@@ -1118,31 +1118,31 @@
     <t xml:space="preserve">8.07005977630615</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92697381973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98420763015747</t>
+    <t xml:space="preserve">7.92697429656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98420810699463</t>
   </si>
   <si>
     <t xml:space="preserve">8.30853748321533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26084136962891</t>
+    <t xml:space="preserve">8.26084041595459</t>
   </si>
   <si>
     <t xml:space="preserve">8.27038097381592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18452835083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03190326690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96513032913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86019945144653</t>
+    <t xml:space="preserve">8.18452930450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03190422058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96512985229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86020040512085</t>
   </si>
   <si>
     <t xml:space="preserve">7.86973905563354</t>
@@ -1157,40 +1157,40 @@
     <t xml:space="preserve">7.76480960845947</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72665357589722</t>
+    <t xml:space="preserve">7.72665309906006</t>
   </si>
   <si>
     <t xml:space="preserve">7.65034103393555</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63126182556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65987873077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16545104980469</t>
+    <t xml:space="preserve">7.63126230239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65987920761108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16545009613037</t>
   </si>
   <si>
     <t xml:space="preserve">8.32761383056641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11775588989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93651151657104</t>
+    <t xml:space="preserve">8.11775493621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9365119934082</t>
   </si>
   <si>
     <t xml:space="preserve">8.19406795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23222351074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31807708740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15591144561768</t>
+    <t xml:space="preserve">8.2322244644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31807613372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15591239929199</t>
   </si>
   <si>
     <t xml:space="preserve">8.22268486022949</t>
@@ -1208,28 +1208,28 @@
     <t xml:space="preserve">8.34669303894043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95559072494507</t>
+    <t xml:space="preserve">7.95559167861938</t>
   </si>
   <si>
     <t xml:space="preserve">7.77434825897217</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82204437255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97466897964478</t>
+    <t xml:space="preserve">7.82204389572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97466850280762</t>
   </si>
   <si>
     <t xml:space="preserve">8.01282501220703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05098056793213</t>
+    <t xml:space="preserve">8.05098152160645</t>
   </si>
   <si>
     <t xml:space="preserve">7.67895746231079</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73619174957275</t>
+    <t xml:space="preserve">7.73619222640991</t>
   </si>
   <si>
     <t xml:space="preserve">7.6980357170105</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">7.62172269821167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52633237838745</t>
+    <t xml:space="preserve">7.52633190155029</t>
   </si>
   <si>
     <t xml:space="preserve">7.34508991241455</t>
@@ -1259,10 +1259,10 @@
     <t xml:space="preserve">7.20200395584106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18292570114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14476871490479</t>
+    <t xml:space="preserve">7.18292617797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14476919174194</t>
   </si>
   <si>
     <t xml:space="preserve">7.12569093704224</t>
@@ -1274,16 +1274,16 @@
     <t xml:space="preserve">7.1543083190918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24969911575317</t>
+    <t xml:space="preserve">7.24969863891602</t>
   </si>
   <si>
     <t xml:space="preserve">7.24015998840332</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46909761428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41186285018921</t>
+    <t xml:space="preserve">7.46909809112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41186332702637</t>
   </si>
   <si>
     <t xml:space="preserve">7.45001983642578</t>
@@ -1295,10 +1295,10 @@
     <t xml:space="preserve">7.39278507232666</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33555126190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61218357086182</t>
+    <t xml:space="preserve">7.3355507850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61218452453613</t>
   </si>
   <si>
     <t xml:space="preserve">7.90789556503296</t>
@@ -1307,10 +1307,10 @@
     <t xml:space="preserve">7.94605112075806</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45955848693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70757436752319</t>
+    <t xml:space="preserve">7.45955896377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70757484436035</t>
   </si>
   <si>
     <t xml:space="preserve">7.8792781829834</t>
@@ -1322,28 +1322,28 @@
     <t xml:space="preserve">7.75527000427246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81250476837158</t>
+    <t xml:space="preserve">7.81250429153442</t>
   </si>
   <si>
     <t xml:space="preserve">7.79342699050903</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80296611785889</t>
+    <t xml:space="preserve">7.80296564102173</t>
   </si>
   <si>
     <t xml:space="preserve">7.85066032409668</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74573135375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83158254623413</t>
+    <t xml:space="preserve">7.74573087692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83158302307129</t>
   </si>
   <si>
     <t xml:space="preserve">7.66941833496094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60264539718628</t>
+    <t xml:space="preserve">7.60264444351196</t>
   </si>
   <si>
     <t xml:space="preserve">7.58356666564941</t>
@@ -1355,19 +1355,19 @@
     <t xml:space="preserve">8.00328636169434</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78388738632202</t>
+    <t xml:space="preserve">7.78388690948486</t>
   </si>
   <si>
     <t xml:space="preserve">7.3641676902771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10661315917969</t>
+    <t xml:space="preserve">7.10661268234253</t>
   </si>
   <si>
     <t xml:space="preserve">7.27831649780273</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08753490447998</t>
+    <t xml:space="preserve">7.08753442764282</t>
   </si>
   <si>
     <t xml:space="preserve">7.05891799926758</t>
@@ -2220,6 +2220,12 @@
   </si>
   <si>
     <t xml:space="preserve">9.30000019073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34000015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18000030517578</t>
   </si>
 </sst>
 </file>
@@ -62358,27 +62364,105 @@
     </row>
     <row r="2301">
       <c r="A2301" s="1" t="n">
-        <v>45968.6909953704</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B2301" t="n">
+        <v>12138</v>
+      </c>
+      <c r="C2301" t="n">
+        <v>9.38000011444092</v>
+      </c>
+      <c r="D2301" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="E2301" t="n">
+        <v>9.34000015258789</v>
+      </c>
+      <c r="F2301" t="n">
+        <v>9.34000015258789</v>
+      </c>
+      <c r="G2301" t="s">
+        <v>736</v>
+      </c>
+      <c r="H2301" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2302">
+      <c r="A2302" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B2302" t="n">
+        <v>31027</v>
+      </c>
+      <c r="C2302" t="n">
+        <v>9.39999961853027</v>
+      </c>
+      <c r="D2302" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="E2302" t="n">
+        <v>9.27999973297119</v>
+      </c>
+      <c r="F2302" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="G2302" t="s">
+        <v>731</v>
+      </c>
+      <c r="H2302" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2303">
+      <c r="A2303" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B2303" t="n">
         <v>15448</v>
       </c>
-      <c r="C2301" t="n">
+      <c r="C2303" t="n">
         <v>9.22000026702881</v>
       </c>
-      <c r="D2301" t="n">
+      <c r="D2303" t="n">
         <v>9.0600004196167</v>
       </c>
-      <c r="E2301" t="n">
+      <c r="E2303" t="n">
         <v>9.11999988555908</v>
       </c>
-      <c r="F2301" t="n">
+      <c r="F2303" t="n">
         <v>9.15999984741211</v>
       </c>
-      <c r="G2301" t="s">
+      <c r="G2303" t="s">
         <v>728</v>
       </c>
-      <c r="H2301" t="s">
+      <c r="H2303" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2304">
+      <c r="A2304" s="1" t="n">
+        <v>45971.6928472222</v>
+      </c>
+      <c r="B2304" t="n">
+        <v>21755</v>
+      </c>
+      <c r="C2304" t="n">
+        <v>9.23999977111816</v>
+      </c>
+      <c r="D2304" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="E2304" t="n">
+        <v>9.23999977111816</v>
+      </c>
+      <c r="F2304" t="n">
+        <v>9.18000030517578</v>
+      </c>
+      <c r="G2304" t="s">
+        <v>737</v>
+      </c>
+      <c r="H2304" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0764217376709</t>
+    <t xml:space="preserve">9.07642269134521</t>
   </si>
   <si>
     <t xml:space="preserve">FF.MI</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">8.98565673828125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08549785614014</t>
+    <t xml:space="preserve">9.08549880981445</t>
   </si>
   <si>
     <t xml:space="preserve">9.24887371063232</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">8.89943218231201</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89489269256592</t>
+    <t xml:space="preserve">8.89489364624023</t>
   </si>
   <si>
     <t xml:space="preserve">8.84951114654541</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">8.8676643371582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04919338226318</t>
+    <t xml:space="preserve">9.0491943359375</t>
   </si>
   <si>
     <t xml:space="preserve">9.23072147369385</t>
@@ -95,10 +95,10 @@
     <t xml:space="preserve">9.11272716522217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96750545501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91304683685303</t>
+    <t xml:space="preserve">8.96750450134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91304588317871</t>
   </si>
   <si>
     <t xml:space="preserve">8.92212390899658</t>
@@ -107,10 +107,10 @@
     <t xml:space="preserve">9.00381088256836</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15810775756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16718673706055</t>
+    <t xml:space="preserve">9.15810871124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16718769073486</t>
   </si>
   <si>
     <t xml:space="preserve">9.43947792053223</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">9.54839611053467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62100696563721</t>
+    <t xml:space="preserve">9.62100791931152</t>
   </si>
   <si>
     <t xml:space="preserve">9.80253601074219</t>
@@ -128,10 +128,10 @@
     <t xml:space="preserve">9.71177101135254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56654834747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58470249176025</t>
+    <t xml:space="preserve">9.56654930114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58470153808594</t>
   </si>
   <si>
     <t xml:space="preserve">9.5756254196167</t>
@@ -140,85 +140,85 @@
     <t xml:space="preserve">9.53024291992188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50301456451416</t>
+    <t xml:space="preserve">9.50301361083984</t>
   </si>
   <si>
     <t xml:space="preserve">9.60285472869873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63915920257568</t>
+    <t xml:space="preserve">9.63916015625</t>
   </si>
   <si>
     <t xml:space="preserve">9.79345989227295</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95683479309082</t>
+    <t xml:space="preserve">9.95683574676514</t>
   </si>
   <si>
     <t xml:space="preserve">9.93868255615234</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98406314849854</t>
+    <t xml:space="preserve">9.98406410217285</t>
   </si>
   <si>
     <t xml:space="preserve">9.73900032043457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76623058319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74807643890381</t>
+    <t xml:space="preserve">9.7662296295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74807739257812</t>
   </si>
   <si>
     <t xml:space="preserve">9.75715351104736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64823627471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82068729400635</t>
+    <t xml:space="preserve">9.64823722839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82068824768066</t>
   </si>
   <si>
     <t xml:space="preserve">9.70269393920898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72084617614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67546558380127</t>
+    <t xml:space="preserve">9.72084808349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67546463012695</t>
   </si>
   <si>
     <t xml:space="preserve">9.66638851165771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63008308410645</t>
+    <t xml:space="preserve">9.63008403778076</t>
   </si>
   <si>
     <t xml:space="preserve">9.65731239318848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68454265594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81161308288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82976531982422</t>
+    <t xml:space="preserve">9.68454170227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81161212921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8297643661499</t>
   </si>
   <si>
     <t xml:space="preserve">9.8479175567627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83884239196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72992420196533</t>
+    <t xml:space="preserve">9.83884143829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72992515563965</t>
   </si>
   <si>
     <t xml:space="preserve">9.78438282012939</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55747222900391</t>
+    <t xml:space="preserve">9.55747318267822</t>
   </si>
   <si>
     <t xml:space="preserve">9.34871482849121</t>
@@ -227,13 +227,13 @@
     <t xml:space="preserve">9.33963775634766</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27610397338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25794982910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19441413879395</t>
+    <t xml:space="preserve">9.27610301971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25795078277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19441509246826</t>
   </si>
   <si>
     <t xml:space="preserve">9.18533802032471</t>
@@ -242,28 +242,28 @@
     <t xml:space="preserve">9.4122486114502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22164440155029</t>
+    <t xml:space="preserve">9.22164535522461</t>
   </si>
   <si>
     <t xml:space="preserve">9.31240940093994</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26702785491943</t>
+    <t xml:space="preserve">9.26702690124512</t>
   </si>
   <si>
     <t xml:space="preserve">9.29425621032715</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28517818450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37594413757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36686706542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38502025604248</t>
+    <t xml:space="preserve">9.28517913818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37594509124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36686611175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3850212097168</t>
   </si>
   <si>
     <t xml:space="preserve">9.45763206481934</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">9.48486137390137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49393749237061</t>
+    <t xml:space="preserve">9.49393558502197</t>
   </si>
   <si>
     <t xml:space="preserve">9.44855499267578</t>
@@ -284,37 +284,37 @@
     <t xml:space="preserve">9.47578430175781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23979663848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14903163909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21256732940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20349311828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13088130950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1399564743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94027614593506</t>
+    <t xml:space="preserve">9.23979759216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14903259277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21256828308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20349216461182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13088035583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13995742797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94027423858643</t>
   </si>
   <si>
     <t xml:space="preserve">8.80412864685059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75874805450439</t>
+    <t xml:space="preserve">8.75874710083008</t>
   </si>
   <si>
     <t xml:space="preserve">8.66798400878906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62260055541992</t>
+    <t xml:space="preserve">8.62260150909424</t>
   </si>
   <si>
     <t xml:space="preserve">8.53183555603027</t>
@@ -323,10 +323,10 @@
     <t xml:space="preserve">8.35030841827393</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16877937316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98725032806396</t>
+    <t xml:space="preserve">8.16878032684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98725080490112</t>
   </si>
   <si>
     <t xml:space="preserve">8.03263378143311</t>
@@ -338,34 +338,34 @@
     <t xml:space="preserve">8.25954437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94186925888062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3049259185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21416091918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39568901062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5772180557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71336555480957</t>
+    <t xml:space="preserve">7.94186878204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30492496490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21416187286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39568996429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57721996307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71336650848389</t>
   </si>
   <si>
     <t xml:space="preserve">9.53202247619629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25706100463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44036960601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16540622711182</t>
+    <t xml:space="preserve">9.25706195831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44036865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16540718078613</t>
   </si>
   <si>
     <t xml:space="preserve">9.07375144958496</t>
@@ -377,13 +377,13 @@
     <t xml:space="preserve">8.98209857940674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02792549133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62367630004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80698394775391</t>
+    <t xml:space="preserve">9.02792453765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62367725372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80698490142822</t>
   </si>
   <si>
     <t xml:space="preserve">9.89863967895508</t>
@@ -401,19 +401,19 @@
     <t xml:space="preserve">10.3569107055664</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5402183532715</t>
+    <t xml:space="preserve">10.5402193069458</t>
   </si>
   <si>
     <t xml:space="preserve">10.631872177124</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8151798248291</t>
+    <t xml:space="preserve">10.8151788711548</t>
   </si>
   <si>
     <t xml:space="preserve">10.7235250473022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9068336486816</t>
+    <t xml:space="preserve">10.906834602356</t>
   </si>
   <si>
     <t xml:space="preserve">10.9984884262085</t>
@@ -425,37 +425,37 @@
     <t xml:space="preserve">11.1817960739136</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734498977661</t>
+    <t xml:space="preserve">11.2734508514404</t>
   </si>
   <si>
     <t xml:space="preserve">11.4567584991455</t>
   </si>
   <si>
-    <t xml:space="preserve">11.365104675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4485635757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71533107757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79878997802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24886608123779</t>
+    <t xml:space="preserve">11.3651037216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4485645294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79879188537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24886703491211</t>
   </si>
   <si>
     <t xml:space="preserve">9.2112340927124</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30288696289062</t>
+    <t xml:space="preserve">9.30288791656494</t>
   </si>
   <si>
     <t xml:space="preserve">9.03708934783936</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3945426940918</t>
+    <t xml:space="preserve">9.39454174041748</t>
   </si>
   <si>
     <t xml:space="preserve">9.76115703582764</t>
@@ -467,22 +467,22 @@
     <t xml:space="preserve">9.57785034179688</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0361194610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94446754455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82552433013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73283004760742</t>
+    <t xml:space="preserve">10.0361204147339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94446563720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82552528381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73283100128174</t>
   </si>
   <si>
     <t xml:space="preserve">9.59379005432129</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96456527709961</t>
+    <t xml:space="preserve">9.96456432342529</t>
   </si>
   <si>
     <t xml:space="preserve">9.91821670532227</t>
@@ -494,13 +494,13 @@
     <t xml:space="preserve">10.010910987854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1036043167114</t>
+    <t xml:space="preserve">10.1036052703857</t>
   </si>
   <si>
     <t xml:space="preserve">10.1499519348145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1962976455688</t>
+    <t xml:space="preserve">10.1962985992432</t>
   </si>
   <si>
     <t xml:space="preserve">9.77917766571045</t>
@@ -512,16 +512,16 @@
     <t xml:space="preserve">10.057258605957</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2889909744263</t>
+    <t xml:space="preserve">10.2889928817749</t>
   </si>
   <si>
     <t xml:space="preserve">10.4743795394897</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2426443099976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3816862106323</t>
+    <t xml:space="preserve">10.2426452636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.381685256958</t>
   </si>
   <si>
     <t xml:space="preserve">9.68648338317871</t>
@@ -563,13 +563,13 @@
     <t xml:space="preserve">8.97274303436279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17666721343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02835845947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95420455932617</t>
+    <t xml:space="preserve">9.17666816711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02835941314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95420360565186</t>
   </si>
   <si>
     <t xml:space="preserve">8.71320056915283</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">8.7688159942627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89858722686768</t>
+    <t xml:space="preserve">8.89858913421631</t>
   </si>
   <si>
     <t xml:space="preserve">8.93566608428955</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">10.3353385925293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9841947555542</t>
+    <t xml:space="preserve">10.9841938018799</t>
   </si>
   <si>
     <t xml:space="preserve">11.0305414199829</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">11.4940099716187</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5403566360474</t>
+    <t xml:space="preserve">11.540355682373</t>
   </si>
   <si>
     <t xml:space="preserve">11.5867033004761</t>
@@ -617,13 +617,13 @@
     <t xml:space="preserve">11.9111309051514</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9574756622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1892118453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2819051742554</t>
+    <t xml:space="preserve">11.9574775695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1892108917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2819042205811</t>
   </si>
   <si>
     <t xml:space="preserve">12.3745985031128</t>
@@ -632,13 +632,13 @@
     <t xml:space="preserve">12.5136394500732</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3282508850098</t>
+    <t xml:space="preserve">12.3282518386841</t>
   </si>
   <si>
     <t xml:space="preserve">12.1428651809692</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0965185165405</t>
+    <t xml:space="preserve">12.0965175628662</t>
   </si>
   <si>
     <t xml:space="preserve">12.555121421814</t>
@@ -653,7 +653,7 @@
     <t xml:space="preserve">12.4614267349243</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4145803451538</t>
+    <t xml:space="preserve">12.4145784378052</t>
   </si>
   <si>
     <t xml:space="preserve">12.7425127029419</t>
@@ -662,13 +662,13 @@
     <t xml:space="preserve">12.6956644058228</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2271909713745</t>
+    <t xml:space="preserve">12.2271900177002</t>
   </si>
   <si>
     <t xml:space="preserve">12.1803426742554</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3208847045898</t>
+    <t xml:space="preserve">12.3208837509155</t>
   </si>
   <si>
     <t xml:space="preserve">12.274037361145</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">12.9299011230469</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8830547332764</t>
+    <t xml:space="preserve">12.8830528259277</t>
   </si>
   <si>
     <t xml:space="preserve">13.0704441070557</t>
@@ -695,7 +695,7 @@
     <t xml:space="preserve">13.679461479187</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8668508529663</t>
+    <t xml:space="preserve">13.8668518066406</t>
   </si>
   <si>
     <t xml:space="preserve">14.0542411804199</t>
@@ -710,28 +710,28 @@
     <t xml:space="preserve">15.2254276275635</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1317329406738</t>
+    <t xml:space="preserve">15.1317319869995</t>
   </si>
   <si>
     <t xml:space="preserve">14.7569532394409</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0380382537842</t>
+    <t xml:space="preserve">15.0380373001099</t>
   </si>
   <si>
     <t xml:space="preserve">15.1785802841187</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3191223144531</t>
+    <t xml:space="preserve">15.3191242218018</t>
   </si>
   <si>
     <t xml:space="preserve">14.8974952697754</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4596652984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4128189086914</t>
+    <t xml:space="preserve">15.4596643447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4128179550171</t>
   </si>
   <si>
     <t xml:space="preserve">15.5533609390259</t>
@@ -740,7 +740,7 @@
     <t xml:space="preserve">16.0686817169189</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8650894165039</t>
+    <t xml:space="preserve">16.8650913238525</t>
   </si>
   <si>
     <t xml:space="preserve">17.0056324005127</t>
@@ -755,25 +755,25 @@
     <t xml:space="preserve">17.0524806976318</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9587821960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7245483398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6308517456055</t>
+    <t xml:space="preserve">16.9587860107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7245445251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6308498382568</t>
   </si>
   <si>
     <t xml:space="preserve">16.5371570587158</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5840034484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2092247009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2560710906982</t>
+    <t xml:space="preserve">16.584005355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2092227935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2560729980469</t>
   </si>
   <si>
     <t xml:space="preserve">17.1461734771729</t>
@@ -785,49 +785,49 @@
     <t xml:space="preserve">16.3029193878174</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8344430923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1155319213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0218353271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1623783111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.974986076355</t>
+    <t xml:space="preserve">15.8344440460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1155300140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0218372344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1623764038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9749870300293</t>
   </si>
   <si>
     <t xml:space="preserve">15.7407493591309</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4434585571289</t>
+    <t xml:space="preserve">16.4434623718262</t>
   </si>
   <si>
     <t xml:space="preserve">16.9119358062744</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0993251800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6777000427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.818244934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.272274017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.084885597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.991189956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8038015365601</t>
+    <t xml:space="preserve">17.0993270874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.677698135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8182430267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2722749710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0848846435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9911909103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8038005828857</t>
   </si>
   <si>
     <t xml:space="preserve">14.4758682250977</t>
@@ -836,67 +836,67 @@
     <t xml:space="preserve">14.382173538208</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1010875701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.288477897644</t>
+    <t xml:space="preserve">14.1010885238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2884769439697</t>
   </si>
   <si>
     <t xml:space="preserve">14.5227155685425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9605464935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2416315078735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1947832107544</t>
+    <t xml:space="preserve">13.960545539856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2416296005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1947822570801</t>
   </si>
   <si>
     <t xml:space="preserve">14.0073928833008</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7263088226318</t>
+    <t xml:space="preserve">13.7263069152832</t>
   </si>
   <si>
     <t xml:space="preserve">14.1479358673096</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4290199279785</t>
+    <t xml:space="preserve">14.4290208816528</t>
   </si>
   <si>
     <t xml:space="preserve">14.6164102554321</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7731561660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3515291213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3046817779541</t>
+    <t xml:space="preserve">13.7731552124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3515281677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3046808242798</t>
   </si>
   <si>
     <t xml:space="preserve">13.3983764648438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0235958099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1172904968262</t>
+    <t xml:space="preserve">13.0235967636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1172914505005</t>
   </si>
   <si>
     <t xml:space="preserve">12.976749420166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3677310943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0866460800171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9929523468018</t>
+    <t xml:space="preserve">12.3677320480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0866470336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9929513931274</t>
   </si>
   <si>
     <t xml:space="preserve">11.8992576599121</t>
@@ -911,10 +911,10 @@
     <t xml:space="preserve">11.4776296615601</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2433938980103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3839340209961</t>
+    <t xml:space="preserve">11.2433929443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3839349746704</t>
   </si>
   <si>
     <t xml:space="preserve">11.6650199890137</t>
@@ -926,13 +926,13 @@
     <t xml:space="preserve">10.9623079299927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7280712127686</t>
+    <t xml:space="preserve">10.7280702590942</t>
   </si>
   <si>
     <t xml:space="preserve">11.1965446472168</t>
   </si>
   <si>
-    <t xml:space="preserve">11.571325302124</t>
+    <t xml:space="preserve">11.5713243484497</t>
   </si>
   <si>
     <t xml:space="preserve">11.3370885848999</t>
@@ -953,10 +953,10 @@
     <t xml:space="preserve">11.0091552734375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46318817138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3388500213623</t>
+    <t xml:space="preserve">9.46318912506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33884906768799</t>
   </si>
   <si>
     <t xml:space="preserve">8.57308673858643</t>
@@ -965,25 +965,25 @@
     <t xml:space="preserve">8.31074142456055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45128345489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61993503570557</t>
+    <t xml:space="preserve">8.45128440856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61993408203125</t>
   </si>
   <si>
     <t xml:space="preserve">8.44191455841064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32948017120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25452518463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43254470825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47002124786377</t>
+    <t xml:space="preserve">8.32948112487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25452423095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43254566192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47002220153809</t>
   </si>
   <si>
     <t xml:space="preserve">8.32011032104492</t>
@@ -995,40 +995,40 @@
     <t xml:space="preserve">8.0858736038208</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78604936599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49559497833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33631324768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23324871063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83289670944214</t>
+    <t xml:space="preserve">7.78605031967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49559545516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33631372451782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23324918746948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83289623260498</t>
   </si>
   <si>
     <t xml:space="preserve">7.90785264968872</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50496530532837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37379217147827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12081575393677</t>
+    <t xml:space="preserve">7.50496482849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37379169464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12081480026245</t>
   </si>
   <si>
     <t xml:space="preserve">7.28009653091431</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98027324676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93342542648315</t>
+    <t xml:space="preserve">6.98027276992798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93342590332031</t>
   </si>
   <si>
     <t xml:space="preserve">7.06459808349609</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">7.34568309783936</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5424427986145</t>
+    <t xml:space="preserve">7.54244232177734</t>
   </si>
   <si>
     <t xml:space="preserve">8.19830703735352</t>
@@ -1049,10 +1049,10 @@
     <t xml:space="preserve">8.2170467376709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65194225311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46116161346436</t>
+    <t xml:space="preserve">8.65194320678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46116256713867</t>
   </si>
   <si>
     <t xml:space="preserve">8.53747367858887</t>
@@ -1070,7 +1070,7 @@
     <t xml:space="preserve">8.72825622558594</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6614818572998</t>
+    <t xml:space="preserve">8.66148281097412</t>
   </si>
   <si>
     <t xml:space="preserve">8.49931812286377</t>
@@ -1091,13 +1091,13 @@
     <t xml:space="preserve">8.29899787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12729358673096</t>
+    <t xml:space="preserve">8.12729454040527</t>
   </si>
   <si>
     <t xml:space="preserve">7.89835643768311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10821628570557</t>
+    <t xml:space="preserve">8.10821723937988</t>
   </si>
   <si>
     <t xml:space="preserve">7.84112215042114</t>
@@ -1112,13 +1112,13 @@
     <t xml:space="preserve">8.06052017211914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07959842681885</t>
+    <t xml:space="preserve">8.07959938049316</t>
   </si>
   <si>
     <t xml:space="preserve">8.07005977630615</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92697334289551</t>
+    <t xml:space="preserve">7.92697429656982</t>
   </si>
   <si>
     <t xml:space="preserve">7.98420810699463</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">8.30853748321533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26084136962891</t>
+    <t xml:space="preserve">8.26084041595459</t>
   </si>
   <si>
     <t xml:space="preserve">8.27038097381592</t>
@@ -1136,13 +1136,13 @@
     <t xml:space="preserve">8.18452930450439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03190326690674</t>
+    <t xml:space="preserve">8.03190422058105</t>
   </si>
   <si>
     <t xml:space="preserve">7.96512985229492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86019992828369</t>
+    <t xml:space="preserve">7.86020040512085</t>
   </si>
   <si>
     <t xml:space="preserve">7.86973905563354</t>
@@ -1166,10 +1166,10 @@
     <t xml:space="preserve">7.63126230239868</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65987873077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16545104980469</t>
+    <t xml:space="preserve">7.65987920761108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16545009613037</t>
   </si>
   <si>
     <t xml:space="preserve">8.32761383056641</t>
@@ -1181,13 +1181,13 @@
     <t xml:space="preserve">7.9365119934082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19406890869141</t>
+    <t xml:space="preserve">8.19406795501709</t>
   </si>
   <si>
     <t xml:space="preserve">8.2322244644165</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31807708740234</t>
+    <t xml:space="preserve">8.31807613372803</t>
   </si>
   <si>
     <t xml:space="preserve">8.15591239929199</t>
@@ -1208,7 +1208,7 @@
     <t xml:space="preserve">8.34669303894043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95559072494507</t>
+    <t xml:space="preserve">7.95559167861938</t>
   </si>
   <si>
     <t xml:space="preserve">7.77434825897217</t>
@@ -1223,13 +1223,13 @@
     <t xml:space="preserve">8.01282501220703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05098056793213</t>
+    <t xml:space="preserve">8.05098152160645</t>
   </si>
   <si>
     <t xml:space="preserve">7.67895746231079</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73619174957275</t>
+    <t xml:space="preserve">7.73619222640991</t>
   </si>
   <si>
     <t xml:space="preserve">7.6980357170105</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">7.62172269821167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52633237838745</t>
+    <t xml:space="preserve">7.52633190155029</t>
   </si>
   <si>
     <t xml:space="preserve">7.34508991241455</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">7.20200395584106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18292570114136</t>
+    <t xml:space="preserve">7.18292617797852</t>
   </si>
   <si>
     <t xml:space="preserve">7.14476919174194</t>
@@ -1274,13 +1274,13 @@
     <t xml:space="preserve">7.1543083190918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24969911575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24016046524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46909761428833</t>
+    <t xml:space="preserve">7.24969863891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24015998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46909809112549</t>
   </si>
   <si>
     <t xml:space="preserve">7.41186332702637</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">7.45001983642578</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28785562515259</t>
+    <t xml:space="preserve">7.28785514831543</t>
   </si>
   <si>
     <t xml:space="preserve">7.39278507232666</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">7.3355507850647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61218404769897</t>
+    <t xml:space="preserve">7.61218452453613</t>
   </si>
   <si>
     <t xml:space="preserve">7.90789556503296</t>
@@ -1307,28 +1307,28 @@
     <t xml:space="preserve">7.94605112075806</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45955848693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70757436752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87927865982056</t>
+    <t xml:space="preserve">7.45955896377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70757484436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8792781829834</t>
   </si>
   <si>
     <t xml:space="preserve">7.99374723434448</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75527048110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81250476837158</t>
+    <t xml:space="preserve">7.75527000427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81250429153442</t>
   </si>
   <si>
     <t xml:space="preserve">7.79342699050903</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80296611785889</t>
+    <t xml:space="preserve">7.80296564102173</t>
   </si>
   <si>
     <t xml:space="preserve">7.85066032409668</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">7.74573087692261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83158254623413</t>
+    <t xml:space="preserve">7.83158302307129</t>
   </si>
   <si>
     <t xml:space="preserve">7.66941833496094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60264492034912</t>
+    <t xml:space="preserve">7.60264444351196</t>
   </si>
   <si>
     <t xml:space="preserve">7.58356666564941</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">8.00328636169434</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78388738632202</t>
+    <t xml:space="preserve">7.78388690948486</t>
   </si>
   <si>
     <t xml:space="preserve">7.3641676902771</t>
@@ -62497,7 +62497,7 @@
     </row>
     <row r="2306">
       <c r="A2306" s="1" t="n">
-        <v>45973.6911574074</v>
+        <v>45973.3333333333</v>
       </c>
       <c r="B2306" t="n">
         <v>25837</v>
@@ -62518,6 +62518,32 @@
         <v>738</v>
       </c>
       <c r="H2306" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2307">
+      <c r="A2307" s="1" t="n">
+        <v>45974.6909837963</v>
+      </c>
+      <c r="B2307" t="n">
+        <v>45115</v>
+      </c>
+      <c r="C2307" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D2307" t="n">
+        <v>9.30000019073486</v>
+      </c>
+      <c r="E2307" t="n">
+        <v>9.4399995803833</v>
+      </c>
+      <c r="F2307" t="n">
+        <v>9.31999969482422</v>
+      </c>
+      <c r="G2307" t="s">
+        <v>726</v>
+      </c>
+      <c r="H2307" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07642269134521</t>
+    <t xml:space="preserve">9.0764217376709</t>
   </si>
   <si>
     <t xml:space="preserve">FF.MI</t>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">9.08549880981445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24887371063232</t>
+    <t xml:space="preserve">9.24887275695801</t>
   </si>
   <si>
     <t xml:space="preserve">9.09457492828369</t>
@@ -59,10 +59,10 @@
     <t xml:space="preserve">9.12180423736572</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03103923797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95389080047607</t>
+    <t xml:space="preserve">9.03104019165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95388984680176</t>
   </si>
   <si>
     <t xml:space="preserve">8.89943218231201</t>
@@ -71,10 +71,10 @@
     <t xml:space="preserve">8.89489364624023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84951114654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85858726501465</t>
+    <t xml:space="preserve">8.84951210021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85858821868896</t>
   </si>
   <si>
     <t xml:space="preserve">8.87674045562744</t>
@@ -83,46 +83,46 @@
     <t xml:space="preserve">8.76782321929932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8676643371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0491943359375</t>
+    <t xml:space="preserve">8.86766529083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04919147491455</t>
   </si>
   <si>
     <t xml:space="preserve">9.23072147369385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11272716522217</t>
+    <t xml:space="preserve">9.11272811889648</t>
   </si>
   <si>
     <t xml:space="preserve">8.96750450134277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91304588317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92212390899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00381088256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15810871124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16718769073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43947792053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54839611053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62100791931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80253601074219</t>
+    <t xml:space="preserve">8.91304683685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92212295532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00381183624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15810966491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16718578338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43947887420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54839706420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62100696563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80253410339355</t>
   </si>
   <si>
     <t xml:space="preserve">9.71177101135254</t>
@@ -143,19 +143,19 @@
     <t xml:space="preserve">9.50301361083984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60285472869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63916015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79345989227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95683574676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93868255615234</t>
+    <t xml:space="preserve">9.60285377502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63916110992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79345893859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9568338394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93868160247803</t>
   </si>
   <si>
     <t xml:space="preserve">9.98406410217285</t>
@@ -164,7 +164,7 @@
     <t xml:space="preserve">9.73900032043457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7662296295166</t>
+    <t xml:space="preserve">9.76623058319092</t>
   </si>
   <si>
     <t xml:space="preserve">9.74807739257812</t>
@@ -173,52 +173,52 @@
     <t xml:space="preserve">9.75715351104736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64823722839355</t>
+    <t xml:space="preserve">9.64823627471924</t>
   </si>
   <si>
     <t xml:space="preserve">9.82068824768066</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70269393920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72084808349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67546463012695</t>
+    <t xml:space="preserve">9.7026948928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72084903717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67546558380127</t>
   </si>
   <si>
     <t xml:space="preserve">9.66638851165771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63008403778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65731239318848</t>
+    <t xml:space="preserve">9.63008308410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65731334686279</t>
   </si>
   <si>
     <t xml:space="preserve">9.68454170227051</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81161212921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8297643661499</t>
+    <t xml:space="preserve">9.81161308288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82976531982422</t>
   </si>
   <si>
     <t xml:space="preserve">9.8479175567627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83884143829346</t>
+    <t xml:space="preserve">9.83884048461914</t>
   </si>
   <si>
     <t xml:space="preserve">9.72992515563965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78438282012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55747318267822</t>
+    <t xml:space="preserve">9.78438186645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55747222900391</t>
   </si>
   <si>
     <t xml:space="preserve">9.34871482849121</t>
@@ -227,79 +227,79 @@
     <t xml:space="preserve">9.33963775634766</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27610301971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25795078277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19441509246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18533802032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4122486114502</t>
+    <t xml:space="preserve">9.27610397338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25794982910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19441604614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18533992767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41224956512451</t>
   </si>
   <si>
     <t xml:space="preserve">9.22164535522461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31240940093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26702690124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29425621032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28517913818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37594509124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36686611175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3850212097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45763206481934</t>
+    <t xml:space="preserve">9.31240844726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2670259475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29425525665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28518009185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37594413757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.366868019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38502216339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45763111114502</t>
   </si>
   <si>
     <t xml:space="preserve">9.39409732818604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48486137390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49393558502197</t>
+    <t xml:space="preserve">9.48486042022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49393653869629</t>
   </si>
   <si>
     <t xml:space="preserve">9.44855499267578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47578430175781</t>
+    <t xml:space="preserve">9.4757833480835</t>
   </si>
   <si>
     <t xml:space="preserve">9.23979759216309</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14903259277344</t>
+    <t xml:space="preserve">9.14903163909912</t>
   </si>
   <si>
     <t xml:space="preserve">9.21256828308105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20349216461182</t>
+    <t xml:space="preserve">9.2034912109375</t>
   </si>
   <si>
     <t xml:space="preserve">9.13088035583496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13995742797852</t>
+    <t xml:space="preserve">9.13995552062988</t>
   </si>
   <si>
     <t xml:space="preserve">8.94027423858643</t>
@@ -311,13 +311,13 @@
     <t xml:space="preserve">8.75874710083008</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66798400878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62260150909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53183555603027</t>
+    <t xml:space="preserve">8.66798305511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62260055541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53183650970459</t>
   </si>
   <si>
     <t xml:space="preserve">8.35030841827393</t>
@@ -332,19 +332,19 @@
     <t xml:space="preserve">8.03263378143311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12339687347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25954437255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94186878204346</t>
+    <t xml:space="preserve">8.12339782714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25954341888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94186925888062</t>
   </si>
   <si>
     <t xml:space="preserve">8.30492496490479</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21416187286377</t>
+    <t xml:space="preserve">8.21416282653809</t>
   </si>
   <si>
     <t xml:space="preserve">8.39568996429443</t>
@@ -353,7 +353,7 @@
     <t xml:space="preserve">8.57721996307373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71336650848389</t>
+    <t xml:space="preserve">8.71336555480957</t>
   </si>
   <si>
     <t xml:space="preserve">9.53202247619629</t>
@@ -371,7 +371,7 @@
     <t xml:space="preserve">9.07375144958496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11957931518555</t>
+    <t xml:space="preserve">9.11958026885986</t>
   </si>
   <si>
     <t xml:space="preserve">8.98209857940674</t>
@@ -380,13 +380,13 @@
     <t xml:space="preserve">9.02792453765869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62367725372314</t>
+    <t xml:space="preserve">9.62367630004883</t>
   </si>
   <si>
     <t xml:space="preserve">9.80698490142822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89863967895508</t>
+    <t xml:space="preserve">9.89863872528076</t>
   </si>
   <si>
     <t xml:space="preserve">9.9902925491333</t>
@@ -395,37 +395,37 @@
     <t xml:space="preserve">10.1736011505127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2652549743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3569107055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5402193069458</t>
+    <t xml:space="preserve">10.2652559280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3569097518921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5402173995972</t>
   </si>
   <si>
     <t xml:space="preserve">10.631872177124</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8151788711548</t>
+    <t xml:space="preserve">10.8151807785034</t>
   </si>
   <si>
     <t xml:space="preserve">10.7235250473022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.906834602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9984884262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0901432037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1817960739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2734508514404</t>
+    <t xml:space="preserve">10.9068336486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9984893798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0901412963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1817941665649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2734498977661</t>
   </si>
   <si>
     <t xml:space="preserve">11.4567584991455</t>
@@ -434,10 +434,10 @@
     <t xml:space="preserve">11.3651037216187</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4485645294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71533203125</t>
+    <t xml:space="preserve">10.4485626220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71533107757568</t>
   </si>
   <si>
     <t xml:space="preserve">8.79879188537598</t>
@@ -452,19 +452,19 @@
     <t xml:space="preserve">9.30288791656494</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03708934783936</t>
+    <t xml:space="preserve">9.03709125518799</t>
   </si>
   <si>
     <t xml:space="preserve">9.39454174041748</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76115703582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66950416564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57785034179688</t>
+    <t xml:space="preserve">9.76115798950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6695032119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57784938812256</t>
   </si>
   <si>
     <t xml:space="preserve">10.0361204147339</t>
@@ -473,10 +473,10 @@
     <t xml:space="preserve">9.94446563720703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82552528381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73283100128174</t>
+    <t xml:space="preserve">9.82552433013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73283004760742</t>
   </si>
   <si>
     <t xml:space="preserve">9.59379005432129</t>
@@ -485,16 +485,16 @@
     <t xml:space="preserve">9.96456432342529</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91821670532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54744243621826</t>
+    <t xml:space="preserve">9.91821765899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54744338989258</t>
   </si>
   <si>
     <t xml:space="preserve">10.010910987854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1036052703857</t>
+    <t xml:space="preserve">10.1036043167114</t>
   </si>
   <si>
     <t xml:space="preserve">10.1499519348145</t>
@@ -503,16 +503,16 @@
     <t xml:space="preserve">10.1962985992432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77917766571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87187004089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.057258605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2889928817749</t>
+    <t xml:space="preserve">9.77917671203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87187099456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0572576522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2889919281006</t>
   </si>
   <si>
     <t xml:space="preserve">10.4743795394897</t>
@@ -521,13 +521,13 @@
     <t xml:space="preserve">10.2426452636719</t>
   </si>
   <si>
-    <t xml:space="preserve">10.381685256958</t>
+    <t xml:space="preserve">10.3816862106323</t>
   </si>
   <si>
     <t xml:space="preserve">9.68648338317871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64013576507568</t>
+    <t xml:space="preserve">9.64013671875</t>
   </si>
   <si>
     <t xml:space="preserve">9.50109672546387</t>
@@ -560,13 +560,13 @@
     <t xml:space="preserve">9.06543636322021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97274303436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17666816711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02835941314697</t>
+    <t xml:space="preserve">8.97274208068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17666721343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02835845947266</t>
   </si>
   <si>
     <t xml:space="preserve">8.95420360565186</t>
@@ -578,46 +578,46 @@
     <t xml:space="preserve">8.99128150939941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7688159942627</t>
+    <t xml:space="preserve">8.76881694793701</t>
   </si>
   <si>
     <t xml:space="preserve">8.89858913421631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93566608428955</t>
+    <t xml:space="preserve">8.93566513061523</t>
   </si>
   <si>
     <t xml:space="preserve">10.3353385925293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9841938018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0305414199829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2159290313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4940099716187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.540355682373</t>
+    <t xml:space="preserve">10.9841947555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0305404663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2159280776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4940090179443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5403566360474</t>
   </si>
   <si>
     <t xml:space="preserve">11.5867033004761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6330490112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7257423400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9111309051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9574775695801</t>
+    <t xml:space="preserve">11.6330499649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7257432937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9111299514771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9574756622314</t>
   </si>
   <si>
     <t xml:space="preserve">12.1892108917236</t>
@@ -626,10 +626,10 @@
     <t xml:space="preserve">12.2819042205811</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3745985031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5136394500732</t>
+    <t xml:space="preserve">12.3745994567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5136384963989</t>
   </si>
   <si>
     <t xml:space="preserve">12.3282518386841</t>
@@ -638,10 +638,10 @@
     <t xml:space="preserve">12.1428651809692</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0965175628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.555121421814</t>
+    <t xml:space="preserve">12.0965185165405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5551223754883</t>
   </si>
   <si>
     <t xml:space="preserve">12.5082750320435</t>
@@ -653,10 +653,10 @@
     <t xml:space="preserve">12.4614267349243</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4145784378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7425127029419</t>
+    <t xml:space="preserve">12.4145793914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7425117492676</t>
   </si>
   <si>
     <t xml:space="preserve">12.6956644058228</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">12.1803426742554</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3208837509155</t>
+    <t xml:space="preserve">12.3208847045898</t>
   </si>
   <si>
     <t xml:space="preserve">12.274037361145</t>
@@ -677,25 +677,25 @@
     <t xml:space="preserve">12.8362064361572</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7893590927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6019687652588</t>
+    <t xml:space="preserve">12.7893581390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6019697189331</t>
   </si>
   <si>
     <t xml:space="preserve">12.9299011230469</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8830528259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0704441070557</t>
+    <t xml:space="preserve">12.8830547332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.07044506073</t>
   </si>
   <si>
     <t xml:space="preserve">13.679461479187</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8668518066406</t>
+    <t xml:space="preserve">13.8668508529663</t>
   </si>
   <si>
     <t xml:space="preserve">14.0542411804199</t>
@@ -704,31 +704,31 @@
     <t xml:space="preserve">14.3353261947632</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5695629119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2254276275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1317319869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7569532394409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0380373001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1785802841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3191242218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8974952697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4596643447876</t>
+    <t xml:space="preserve">14.5695638656616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2254285812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1317329406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7569522857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0380382537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.178581237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3191232681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8974943161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4596662521362</t>
   </si>
   <si>
     <t xml:space="preserve">15.4128179550171</t>
@@ -746,34 +746,34 @@
     <t xml:space="preserve">17.0056324005127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7713928222656</t>
+    <t xml:space="preserve">16.7713947296143</t>
   </si>
   <si>
     <t xml:space="preserve">17.193021774292</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0524806976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9587860107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7245445251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6308498382568</t>
+    <t xml:space="preserve">17.0524787902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9587841033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7245483398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6308517456055</t>
   </si>
   <si>
     <t xml:space="preserve">16.5371570587158</t>
   </si>
   <si>
-    <t xml:space="preserve">16.584005355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2092227935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2560729980469</t>
+    <t xml:space="preserve">16.5840034484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2092247009277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2560710906982</t>
   </si>
   <si>
     <t xml:space="preserve">17.1461734771729</t>
@@ -782,46 +782,46 @@
     <t xml:space="preserve">16.396614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3029193878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8344440460205</t>
+    <t xml:space="preserve">16.3029174804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8344449996948</t>
   </si>
   <si>
     <t xml:space="preserve">16.1155300140381</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0218372344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1623764038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9749870300293</t>
+    <t xml:space="preserve">16.0218353271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1623783111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.974986076355</t>
   </si>
   <si>
     <t xml:space="preserve">15.7407493591309</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4434623718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9119358062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0993270874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.677698135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8182430267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2722749710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0848846435547</t>
+    <t xml:space="preserve">16.4434604644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.911937713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0993251800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6777000427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.818244934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.272274017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.084885597229</t>
   </si>
   <si>
     <t xml:space="preserve">14.9911909103394</t>
@@ -839,16 +839,16 @@
     <t xml:space="preserve">14.1010885238647</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2884769439697</t>
+    <t xml:space="preserve">14.288477897644</t>
   </si>
   <si>
     <t xml:space="preserve">14.5227155685425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.960545539856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2416296005249</t>
+    <t xml:space="preserve">13.9605464935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2416305541992</t>
   </si>
   <si>
     <t xml:space="preserve">14.1947822570801</t>
@@ -857,19 +857,19 @@
     <t xml:space="preserve">14.0073928833008</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7263069152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1479358673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4290208816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6164102554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7731552124023</t>
+    <t xml:space="preserve">13.7263088226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1479368209839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4290199279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6164112091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7731561660767</t>
   </si>
   <si>
     <t xml:space="preserve">13.3515281677246</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">13.3983764648438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0235967636108</t>
+    <t xml:space="preserve">13.0235958099365</t>
   </si>
   <si>
     <t xml:space="preserve">13.1172914505005</t>
@@ -893,49 +893,49 @@
     <t xml:space="preserve">12.3677320480347</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0866470336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9929513931274</t>
+    <t xml:space="preserve">12.0866460800171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9929523468018</t>
   </si>
   <si>
     <t xml:space="preserve">11.8992576599121</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0397996902466</t>
+    <t xml:space="preserve">12.0397987365723</t>
   </si>
   <si>
     <t xml:space="preserve">12.1334943771362</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4776296615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2433929443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3839349746704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6650199890137</t>
+    <t xml:space="preserve">11.4776306152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2433938980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3839340209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.665020942688</t>
   </si>
   <si>
     <t xml:space="preserve">11.4307823181152</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9623079299927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7280702590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1965446472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5713243484497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3370885848999</t>
+    <t xml:space="preserve">10.9623069763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7280712127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1965456008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.571325302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3370876312256</t>
   </si>
   <si>
     <t xml:space="preserve">11.2902402877808</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">11.7118673324585</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7587146759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8055629730225</t>
+    <t xml:space="preserve">11.7587156295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8055639266968</t>
   </si>
   <si>
     <t xml:space="preserve">11.0091552734375</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">9.46318912506104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33884906768799</t>
+    <t xml:space="preserve">8.3388500213623</t>
   </si>
   <si>
     <t xml:space="preserve">8.57308673858643</t>
@@ -965,7 +965,7 @@
     <t xml:space="preserve">8.31074142456055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45128440856934</t>
+    <t xml:space="preserve">8.45128345489502</t>
   </si>
   <si>
     <t xml:space="preserve">8.61993408203125</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">8.44191455841064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32948112487793</t>
+    <t xml:space="preserve">8.32948017120361</t>
   </si>
   <si>
     <t xml:space="preserve">8.25452423095703</t>
@@ -986,16 +986,16 @@
     <t xml:space="preserve">8.47002220153809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32011032104492</t>
+    <t xml:space="preserve">8.32011127471924</t>
   </si>
   <si>
     <t xml:space="preserve">8.20767688751221</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0858736038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78605031967163</t>
+    <t xml:space="preserve">8.08587265014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78604936599731</t>
   </si>
   <si>
     <t xml:space="preserve">7.49559545516968</t>
@@ -1019,16 +1019,16 @@
     <t xml:space="preserve">7.37379169464111</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12081480026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28009653091431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98027276992798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93342590332031</t>
+    <t xml:space="preserve">7.12081527709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28009700775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98027324676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93342542648315</t>
   </si>
   <si>
     <t xml:space="preserve">7.06459808349609</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">7.34568309783936</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54244232177734</t>
+    <t xml:space="preserve">7.5424427986145</t>
   </si>
   <si>
     <t xml:space="preserve">8.19830703735352</t>
@@ -62523,7 +62523,7 @@
     </row>
     <row r="2307">
       <c r="A2307" s="1" t="n">
-        <v>45974.6909837963</v>
+        <v>45974.3333333333</v>
       </c>
       <c r="B2307" t="n">
         <v>45115</v>
@@ -62544,6 +62544,32 @@
         <v>726</v>
       </c>
       <c r="H2307" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2308">
+      <c r="A2308" s="1" t="n">
+        <v>45975.6912268518</v>
+      </c>
+      <c r="B2308" t="n">
+        <v>20130</v>
+      </c>
+      <c r="C2308" t="n">
+        <v>9.38000011444092</v>
+      </c>
+      <c r="D2308" t="n">
+        <v>9.22000026702881</v>
+      </c>
+      <c r="E2308" t="n">
+        <v>9.34000015258789</v>
+      </c>
+      <c r="F2308" t="n">
+        <v>9.23999977111816</v>
+      </c>
+      <c r="G2308" t="s">
+        <v>722</v>
+      </c>
+      <c r="H2308" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -44,40 +44,40 @@
     <t xml:space="preserve">FF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98565673828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08549880981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24887275695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09457492828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12180423736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03104019165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95388984680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89943218231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89489364624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84951210021973</t>
+    <t xml:space="preserve">8.98565769195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08549785614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24887371063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09457588195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12180328369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03103828430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95389080047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8994312286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89489269256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84951114654541</t>
   </si>
   <si>
     <t xml:space="preserve">8.85858821868896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87674045562744</t>
+    <t xml:space="preserve">8.87673950195312</t>
   </si>
   <si>
     <t xml:space="preserve">8.76782321929932</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">8.86766529083252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04919147491455</t>
+    <t xml:space="preserve">9.04919338226318</t>
   </si>
   <si>
     <t xml:space="preserve">9.23072147369385</t>
@@ -104,34 +104,34 @@
     <t xml:space="preserve">8.92212295532227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00381183624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15810966491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16718578338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43947887420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54839706420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62100696563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80253410339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71177101135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56654930114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58470153808594</t>
+    <t xml:space="preserve">9.00381088256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15811061859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16718673706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43947792053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54839611053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62100791931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8025369644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71177196502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56654739379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58470249176025</t>
   </si>
   <si>
     <t xml:space="preserve">9.5756254196167</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">9.60285377502441</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63916110992432</t>
+    <t xml:space="preserve">9.63916015625</t>
   </si>
   <si>
     <t xml:space="preserve">9.79345893859863</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9568338394165</t>
+    <t xml:space="preserve">9.95683574676514</t>
   </si>
   <si>
     <t xml:space="preserve">9.93868160247803</t>
@@ -164,7 +164,7 @@
     <t xml:space="preserve">9.73900032043457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76623058319092</t>
+    <t xml:space="preserve">9.7662296295166</t>
   </si>
   <si>
     <t xml:space="preserve">9.74807739257812</t>
@@ -173,31 +173,31 @@
     <t xml:space="preserve">9.75715351104736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64823627471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82068824768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7026948928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72084903717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67546558380127</t>
+    <t xml:space="preserve">9.64823722839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82068729400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70269393920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72084617614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67546463012695</t>
   </si>
   <si>
     <t xml:space="preserve">9.66638851165771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63008308410645</t>
+    <t xml:space="preserve">9.63008213043213</t>
   </si>
   <si>
     <t xml:space="preserve">9.65731334686279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68454170227051</t>
+    <t xml:space="preserve">9.68454265594482</t>
   </si>
   <si>
     <t xml:space="preserve">9.81161308288574</t>
@@ -206,10 +206,10 @@
     <t xml:space="preserve">9.82976531982422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8479175567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83884048461914</t>
+    <t xml:space="preserve">9.84791851043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83884143829346</t>
   </si>
   <si>
     <t xml:space="preserve">9.72992515563965</t>
@@ -218,7 +218,7 @@
     <t xml:space="preserve">9.78438186645508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55747222900391</t>
+    <t xml:space="preserve">9.55747318267822</t>
   </si>
   <si>
     <t xml:space="preserve">9.34871482849121</t>
@@ -233,16 +233,16 @@
     <t xml:space="preserve">9.25794982910156</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19441604614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18533992767334</t>
+    <t xml:space="preserve">9.19441509246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18533897399902</t>
   </si>
   <si>
     <t xml:space="preserve">9.41224956512451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22164535522461</t>
+    <t xml:space="preserve">9.22164344787598</t>
   </si>
   <si>
     <t xml:space="preserve">9.31240844726562</t>
@@ -251,19 +251,19 @@
     <t xml:space="preserve">9.2670259475708</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29425525665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28518009185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37594413757324</t>
+    <t xml:space="preserve">9.29425621032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28517913818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37594318389893</t>
   </si>
   <si>
     <t xml:space="preserve">9.366868019104</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38502216339111</t>
+    <t xml:space="preserve">9.3850212097168</t>
   </si>
   <si>
     <t xml:space="preserve">9.45763111114502</t>
@@ -272,19 +272,19 @@
     <t xml:space="preserve">9.39409732818604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48486042022705</t>
+    <t xml:space="preserve">9.48486137390137</t>
   </si>
   <si>
     <t xml:space="preserve">9.49393653869629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44855499267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4757833480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23979759216309</t>
+    <t xml:space="preserve">9.44855403900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47578430175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2397985458374</t>
   </si>
   <si>
     <t xml:space="preserve">9.14903163909912</t>
@@ -293,46 +293,46 @@
     <t xml:space="preserve">9.21256828308105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2034912109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13088035583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13995552062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94027423858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80412864685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75874710083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66798305511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62260055541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53183650970459</t>
+    <t xml:space="preserve">9.20349216461182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13087940216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13995742797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94027519226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80412769317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75874614715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66798210144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62259960174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53183555603027</t>
   </si>
   <si>
     <t xml:space="preserve">8.35030841827393</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16878032684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98725080490112</t>
+    <t xml:space="preserve">8.16877937316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98725128173828</t>
   </si>
   <si>
     <t xml:space="preserve">8.03263378143311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12339782714844</t>
+    <t xml:space="preserve">8.12339878082275</t>
   </si>
   <si>
     <t xml:space="preserve">8.25954341888428</t>
@@ -344,22 +344,22 @@
     <t xml:space="preserve">8.30492496490479</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21416282653809</t>
+    <t xml:space="preserve">8.21416187286377</t>
   </si>
   <si>
     <t xml:space="preserve">8.39568996429443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57721996307373</t>
+    <t xml:space="preserve">8.5772180557251</t>
   </si>
   <si>
     <t xml:space="preserve">8.71336555480957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53202247619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25706195831299</t>
+    <t xml:space="preserve">9.53202342987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25706100463867</t>
   </si>
   <si>
     <t xml:space="preserve">9.44036865234375</t>
@@ -368,16 +368,16 @@
     <t xml:space="preserve">9.16540718078613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07375144958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11958026885986</t>
+    <t xml:space="preserve">9.07375240325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11957931518555</t>
   </si>
   <si>
     <t xml:space="preserve">8.98209857940674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02792453765869</t>
+    <t xml:space="preserve">9.02792549133301</t>
   </si>
   <si>
     <t xml:space="preserve">9.62367630004883</t>
@@ -386,13 +386,13 @@
     <t xml:space="preserve">9.80698490142822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89863872528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9902925491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1736011505127</t>
+    <t xml:space="preserve">9.89863967895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99029350280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.173602104187</t>
   </si>
   <si>
     <t xml:space="preserve">10.2652559280396</t>
@@ -404,7 +404,7 @@
     <t xml:space="preserve">10.5402173995972</t>
   </si>
   <si>
-    <t xml:space="preserve">10.631872177124</t>
+    <t xml:space="preserve">10.6318712234497</t>
   </si>
   <si>
     <t xml:space="preserve">10.8151807785034</t>
@@ -413,22 +413,22 @@
     <t xml:space="preserve">10.7235250473022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9068336486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9984893798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0901412963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1817941665649</t>
+    <t xml:space="preserve">10.9068326950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9984884262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.090142250061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1817960739136</t>
   </si>
   <si>
     <t xml:space="preserve">11.2734498977661</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4567584991455</t>
+    <t xml:space="preserve">11.4567594528198</t>
   </si>
   <si>
     <t xml:space="preserve">11.3651037216187</t>
@@ -437,40 +437,40 @@
     <t xml:space="preserve">10.4485626220703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71533107757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79879188537598</t>
+    <t xml:space="preserve">9.71533012390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79879093170166</t>
   </si>
   <si>
     <t xml:space="preserve">8.24886703491211</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2112340927124</t>
+    <t xml:space="preserve">9.21123313903809</t>
   </si>
   <si>
     <t xml:space="preserve">9.30288791656494</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03709125518799</t>
+    <t xml:space="preserve">9.03709030151367</t>
   </si>
   <si>
     <t xml:space="preserve">9.39454174041748</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76115798950195</t>
+    <t xml:space="preserve">9.76115703582764</t>
   </si>
   <si>
     <t xml:space="preserve">9.6695032119751</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57784938812256</t>
+    <t xml:space="preserve">9.57785034179688</t>
   </si>
   <si>
     <t xml:space="preserve">10.0361204147339</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94446563720703</t>
+    <t xml:space="preserve">9.94446659088135</t>
   </si>
   <si>
     <t xml:space="preserve">9.82552433013916</t>
@@ -62549,7 +62549,7 @@
     </row>
     <row r="2308">
       <c r="A2308" s="1" t="n">
-        <v>45975.6912268518</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B2308" t="n">
         <v>20130</v>
@@ -62570,6 +62570,32 @@
         <v>722</v>
       </c>
       <c r="H2308" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2309">
+      <c r="A2309" s="1" t="n">
+        <v>45978.6911921296</v>
+      </c>
+      <c r="B2309" t="n">
+        <v>24889</v>
+      </c>
+      <c r="C2309" t="n">
+        <v>9.34000015258789</v>
+      </c>
+      <c r="D2309" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="E2309" t="n">
+        <v>9.23999977111816</v>
+      </c>
+      <c r="F2309" t="n">
+        <v>9.26000022888184</v>
+      </c>
+      <c r="G2309" t="s">
+        <v>724</v>
+      </c>
+      <c r="H2309" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0764217376709</t>
+    <t xml:space="preserve">9.07642269134521</t>
   </si>
   <si>
     <t xml:space="preserve">FF.MI</t>
@@ -50,25 +50,25 @@
     <t xml:space="preserve">9.08549785614014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24887371063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09457588195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12180328369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03103828430176</t>
+    <t xml:space="preserve">9.24887275695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09457397460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12180423736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03104114532471</t>
   </si>
   <si>
     <t xml:space="preserve">8.95389080047607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8994312286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89489269256592</t>
+    <t xml:space="preserve">8.89943313598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89489364624023</t>
   </si>
   <si>
     <t xml:space="preserve">8.84951114654541</t>
@@ -83,13 +83,13 @@
     <t xml:space="preserve">8.76782321929932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86766529083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04919338226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23072147369385</t>
+    <t xml:space="preserve">8.8676643371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04919147491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23072052001953</t>
   </si>
   <si>
     <t xml:space="preserve">9.11272811889648</t>
@@ -101,34 +101,34 @@
     <t xml:space="preserve">8.91304683685303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92212295532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00381088256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15811061859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16718673706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43947792053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54839611053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62100791931152</t>
+    <t xml:space="preserve">8.92212200164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00380992889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15810966491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16718482971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43947887420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54839515686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62100696563721</t>
   </si>
   <si>
     <t xml:space="preserve">9.8025369644165</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71177196502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56654739379883</t>
+    <t xml:space="preserve">9.71177005767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56654930114746</t>
   </si>
   <si>
     <t xml:space="preserve">9.58470249176025</t>
@@ -140,22 +140,22 @@
     <t xml:space="preserve">9.53024291992188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50301361083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60285377502441</t>
+    <t xml:space="preserve">9.50301456451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60285472869873</t>
   </si>
   <si>
     <t xml:space="preserve">9.63916015625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79345893859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95683574676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93868160247803</t>
+    <t xml:space="preserve">9.79345798492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95683479309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93868064880371</t>
   </si>
   <si>
     <t xml:space="preserve">9.98406410217285</t>
@@ -164,46 +164,46 @@
     <t xml:space="preserve">9.73900032043457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7662296295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74807739257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75715351104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64823722839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82068729400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70269393920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72084617614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67546463012695</t>
+    <t xml:space="preserve">9.76623058319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74807548522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75715446472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64823627471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82068634033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7026948928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72084712982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67546558380127</t>
   </si>
   <si>
     <t xml:space="preserve">9.66638851165771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63008213043213</t>
+    <t xml:space="preserve">9.63008403778076</t>
   </si>
   <si>
     <t xml:space="preserve">9.65731334686279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68454265594482</t>
+    <t xml:space="preserve">9.68454360961914</t>
   </si>
   <si>
     <t xml:space="preserve">9.81161308288574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82976531982422</t>
+    <t xml:space="preserve">9.8297643661499</t>
   </si>
   <si>
     <t xml:space="preserve">9.84791851043701</t>
@@ -221,19 +221,19 @@
     <t xml:space="preserve">9.55747318267822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34871482849121</t>
+    <t xml:space="preserve">9.34871387481689</t>
   </si>
   <si>
     <t xml:space="preserve">9.33963775634766</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27610397338867</t>
+    <t xml:space="preserve">9.27610301971436</t>
   </si>
   <si>
     <t xml:space="preserve">9.25794982910156</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19441509246826</t>
+    <t xml:space="preserve">9.19441604614258</t>
   </si>
   <si>
     <t xml:space="preserve">9.18533897399902</t>
@@ -242,34 +242,34 @@
     <t xml:space="preserve">9.41224956512451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22164344787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31240844726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2670259475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29425621032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28517913818359</t>
+    <t xml:space="preserve">9.22164440155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31240940093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26702690124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29425525665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28518009185791</t>
   </si>
   <si>
     <t xml:space="preserve">9.37594318389893</t>
   </si>
   <si>
-    <t xml:space="preserve">9.366868019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3850212097168</t>
+    <t xml:space="preserve">9.36686706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38502025604248</t>
   </si>
   <si>
     <t xml:space="preserve">9.45763111114502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39409732818604</t>
+    <t xml:space="preserve">9.39409828186035</t>
   </si>
   <si>
     <t xml:space="preserve">9.48486137390137</t>
@@ -278,85 +278,85 @@
     <t xml:space="preserve">9.49393653869629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44855403900146</t>
+    <t xml:space="preserve">9.44855499267578</t>
   </si>
   <si>
     <t xml:space="preserve">9.47578430175781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2397985458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14903163909912</t>
+    <t xml:space="preserve">9.23979663848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14903354644775</t>
   </si>
   <si>
     <t xml:space="preserve">9.21256828308105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20349216461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13087940216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13995742797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94027519226074</t>
+    <t xml:space="preserve">9.20349311828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13088130950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1399564743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94027614593506</t>
   </si>
   <si>
     <t xml:space="preserve">8.80412769317627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75874614715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66798210144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62259960174561</t>
+    <t xml:space="preserve">8.75874710083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66798305511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62260150909424</t>
   </si>
   <si>
     <t xml:space="preserve">8.53183555603027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35030841827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16877937316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98725128173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03263378143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12339878082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25954341888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94186925888062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30492496490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21416187286377</t>
+    <t xml:space="preserve">8.35030746459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16878032684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98725175857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03263282775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12339687347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25954532623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94186878204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3049259185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21416282653809</t>
   </si>
   <si>
     <t xml:space="preserve">8.39568996429443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5772180557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71336555480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53202342987061</t>
+    <t xml:space="preserve">8.57721710205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71336650848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53202152252197</t>
   </si>
   <si>
     <t xml:space="preserve">9.25706100463867</t>
@@ -368,31 +368,31 @@
     <t xml:space="preserve">9.16540718078613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07375240325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11957931518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98209857940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02792549133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62367630004883</t>
+    <t xml:space="preserve">9.07375144958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11958026885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98209953308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02792644500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62367725372314</t>
   </si>
   <si>
     <t xml:space="preserve">9.80698490142822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89863967895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99029350280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.173602104187</t>
+    <t xml:space="preserve">9.89863872528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99029159545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1736011505127</t>
   </si>
   <si>
     <t xml:space="preserve">10.2652559280396</t>
@@ -401,52 +401,52 @@
     <t xml:space="preserve">10.3569097518921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5402173995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6318712234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8151807785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7235250473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9068326950073</t>
+    <t xml:space="preserve">10.5402183532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6318731307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8151798248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7235260009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9068336486816</t>
   </si>
   <si>
     <t xml:space="preserve">10.9984884262085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.090142250061</t>
+    <t xml:space="preserve">11.0901432037354</t>
   </si>
   <si>
     <t xml:space="preserve">11.1817960739136</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734498977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4567594528198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3651037216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4485626220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71533012390137</t>
+    <t xml:space="preserve">11.2734508514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4567584991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3651027679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4485635757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71533107757568</t>
   </si>
   <si>
     <t xml:space="preserve">8.79879093170166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24886703491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21123313903809</t>
+    <t xml:space="preserve">8.24886608123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2112340927124</t>
   </si>
   <si>
     <t xml:space="preserve">9.30288791656494</t>
@@ -455,13 +455,13 @@
     <t xml:space="preserve">9.03709030151367</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39454174041748</t>
+    <t xml:space="preserve">9.3945426940918</t>
   </si>
   <si>
     <t xml:space="preserve">9.76115703582764</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6695032119751</t>
+    <t xml:space="preserve">9.66950416564941</t>
   </si>
   <si>
     <t xml:space="preserve">9.57785034179688</t>
@@ -479,13 +479,13 @@
     <t xml:space="preserve">9.73283004760742</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59379005432129</t>
+    <t xml:space="preserve">9.59379100799561</t>
   </si>
   <si>
     <t xml:space="preserve">9.96456432342529</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91821765899658</t>
+    <t xml:space="preserve">9.91821670532227</t>
   </si>
   <si>
     <t xml:space="preserve">9.54744338989258</t>
@@ -497,22 +497,22 @@
     <t xml:space="preserve">10.1036043167114</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1499519348145</t>
+    <t xml:space="preserve">10.1499509811401</t>
   </si>
   <si>
     <t xml:space="preserve">10.1962985992432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77917671203613</t>
+    <t xml:space="preserve">9.77917766571045</t>
   </si>
   <si>
     <t xml:space="preserve">9.87187099456787</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0572576522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2889919281006</t>
+    <t xml:space="preserve">10.057258605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2889928817749</t>
   </si>
   <si>
     <t xml:space="preserve">10.4743795394897</t>
@@ -521,13 +521,13 @@
     <t xml:space="preserve">10.2426452636719</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3816862106323</t>
+    <t xml:space="preserve">10.381685256958</t>
   </si>
   <si>
     <t xml:space="preserve">9.68648338317871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64013671875</t>
+    <t xml:space="preserve">9.64013576507568</t>
   </si>
   <si>
     <t xml:space="preserve">9.50109672546387</t>
@@ -536,64 +536,64 @@
     <t xml:space="preserve">9.31570911407471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23228454589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1952075958252</t>
+    <t xml:space="preserve">9.23228549957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19520664215088</t>
   </si>
   <si>
     <t xml:space="preserve">9.25082302093506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.269362449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21374607086182</t>
+    <t xml:space="preserve">9.26936149597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2137451171875</t>
   </si>
   <si>
     <t xml:space="preserve">9.04689693450928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12105369567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06543636322021</t>
+    <t xml:space="preserve">9.12105274200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0654354095459</t>
   </si>
   <si>
     <t xml:space="preserve">8.97274208068848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17666721343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02835845947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95420360565186</t>
+    <t xml:space="preserve">9.17666816711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02835941314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95420265197754</t>
   </si>
   <si>
     <t xml:space="preserve">8.71320056915283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99128150939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76881694793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89858913421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93566513061523</t>
+    <t xml:space="preserve">8.9912805557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7688159942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89858818054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93566608428955</t>
   </si>
   <si>
     <t xml:space="preserve">10.3353385925293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9841947555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0305404663086</t>
+    <t xml:space="preserve">10.9841938018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0305414199829</t>
   </si>
   <si>
     <t xml:space="preserve">11.2159280776978</t>
@@ -602,37 +602,37 @@
     <t xml:space="preserve">11.4940090179443</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5403566360474</t>
+    <t xml:space="preserve">11.5403547286987</t>
   </si>
   <si>
     <t xml:space="preserve">11.5867033004761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6330499649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7257432937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9111299514771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9574756622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1892108917236</t>
+    <t xml:space="preserve">11.6330490112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7257423400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9111309051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9574766159058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1892118453979</t>
   </si>
   <si>
     <t xml:space="preserve">12.2819042205811</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3745994567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5136384963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3282518386841</t>
+    <t xml:space="preserve">12.3745985031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5136394500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3282527923584</t>
   </si>
   <si>
     <t xml:space="preserve">12.1428651809692</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">12.0965185165405</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5551223754883</t>
+    <t xml:space="preserve">12.5551204681396</t>
   </si>
   <si>
     <t xml:space="preserve">12.5082750320435</t>
@@ -656,13 +656,13 @@
     <t xml:space="preserve">12.4145793914795</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7425117492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6956644058228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2271900177002</t>
+    <t xml:space="preserve">12.7425127029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6956653594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2271909713745</t>
   </si>
   <si>
     <t xml:space="preserve">12.1803426742554</t>
@@ -677,25 +677,25 @@
     <t xml:space="preserve">12.8362064361572</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7893581390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6019697189331</t>
+    <t xml:space="preserve">12.7893600463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6019687652588</t>
   </si>
   <si>
     <t xml:space="preserve">12.9299011230469</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8830547332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.07044506073</t>
+    <t xml:space="preserve">12.8830537796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0704441070557</t>
   </si>
   <si>
     <t xml:space="preserve">13.679461479187</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8668508529663</t>
+    <t xml:space="preserve">13.8668518066406</t>
   </si>
   <si>
     <t xml:space="preserve">14.0542411804199</t>
@@ -704,61 +704,61 @@
     <t xml:space="preserve">14.3353261947632</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5695638656616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2254285812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1317329406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7569522857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0380382537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.178581237793</t>
+    <t xml:space="preserve">14.5695629119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2254276275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1317319869995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7569532394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0380373001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1785802841187</t>
   </si>
   <si>
     <t xml:space="preserve">15.3191232681274</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8974943161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4596662521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4128179550171</t>
+    <t xml:space="preserve">14.8974952697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4596643447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4128189086914</t>
   </si>
   <si>
     <t xml:space="preserve">15.5533609390259</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0686817169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8650913238525</t>
+    <t xml:space="preserve">16.0686798095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8650894165039</t>
   </si>
   <si>
     <t xml:space="preserve">17.0056324005127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7713947296143</t>
+    <t xml:space="preserve">16.7713928222656</t>
   </si>
   <si>
     <t xml:space="preserve">17.193021774292</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0524787902832</t>
+    <t xml:space="preserve">17.0524806976318</t>
   </si>
   <si>
     <t xml:space="preserve">16.9587841033936</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7245483398438</t>
+    <t xml:space="preserve">16.7245464324951</t>
   </si>
   <si>
     <t xml:space="preserve">16.6308517456055</t>
@@ -767,10 +767,10 @@
     <t xml:space="preserve">16.5371570587158</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5840034484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2092247009277</t>
+    <t xml:space="preserve">16.584005355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2092227935791</t>
   </si>
   <si>
     <t xml:space="preserve">16.2560710906982</t>
@@ -782,22 +782,22 @@
     <t xml:space="preserve">16.396614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3029174804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8344449996948</t>
+    <t xml:space="preserve">16.3029193878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8344440460205</t>
   </si>
   <si>
     <t xml:space="preserve">16.1155300140381</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0218353271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1623783111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.974986076355</t>
+    <t xml:space="preserve">16.0218372344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1623764038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9749870300293</t>
   </si>
   <si>
     <t xml:space="preserve">15.7407493591309</t>
@@ -806,22 +806,22 @@
     <t xml:space="preserve">16.4434604644775</t>
   </si>
   <si>
-    <t xml:space="preserve">16.911937713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0993251800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6777000427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.818244934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.272274017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.084885597229</t>
+    <t xml:space="preserve">16.9119358062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0993270874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.677698135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8182430267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2722749710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0848846435547</t>
   </si>
   <si>
     <t xml:space="preserve">14.9911909103394</t>
@@ -845,46 +845,46 @@
     <t xml:space="preserve">14.5227155685425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9605464935303</t>
+    <t xml:space="preserve">13.960545539856</t>
   </si>
   <si>
     <t xml:space="preserve">14.2416305541992</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1947822570801</t>
+    <t xml:space="preserve">14.1947832107544</t>
   </si>
   <si>
     <t xml:space="preserve">14.0073928833008</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7263088226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1479368209839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4290199279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6164112091064</t>
+    <t xml:space="preserve">13.7263078689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1479358673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4290208816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6164102554321</t>
   </si>
   <si>
     <t xml:space="preserve">13.7731561660767</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3515281677246</t>
+    <t xml:space="preserve">13.3515291213989</t>
   </si>
   <si>
     <t xml:space="preserve">13.3046808242798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3983764648438</t>
+    <t xml:space="preserve">13.3983755111694</t>
   </si>
   <si>
     <t xml:space="preserve">13.0235958099365</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1172914505005</t>
+    <t xml:space="preserve">13.1172904968262</t>
   </si>
   <si>
     <t xml:space="preserve">12.976749420166</t>
@@ -896,46 +896,46 @@
     <t xml:space="preserve">12.0866460800171</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9929523468018</t>
+    <t xml:space="preserve">11.9929513931274</t>
   </si>
   <si>
     <t xml:space="preserve">11.8992576599121</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0397987365723</t>
+    <t xml:space="preserve">12.0397996902466</t>
   </si>
   <si>
     <t xml:space="preserve">12.1334943771362</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4776306152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2433938980103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3839340209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.665020942688</t>
+    <t xml:space="preserve">11.4776296615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2433929443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3839349746704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6650199890137</t>
   </si>
   <si>
     <t xml:space="preserve">11.4307823181152</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9623069763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7280712127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1965456008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.571325302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3370876312256</t>
+    <t xml:space="preserve">10.9623079299927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7280702590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1965446472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5713243484497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3370885848999</t>
   </si>
   <si>
     <t xml:space="preserve">11.2902402877808</t>
@@ -944,28 +944,28 @@
     <t xml:space="preserve">11.7118673324585</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7587156295776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8055639266968</t>
+    <t xml:space="preserve">11.7587146759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8055629730225</t>
   </si>
   <si>
     <t xml:space="preserve">11.0091552734375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46318912506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3388500213623</t>
+    <t xml:space="preserve">9.46318817138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33884906768799</t>
   </si>
   <si>
     <t xml:space="preserve">8.57308673858643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31074142456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45128345489502</t>
+    <t xml:space="preserve">8.31074047088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45128440856934</t>
   </si>
   <si>
     <t xml:space="preserve">8.61993408203125</t>
@@ -974,25 +974,25 @@
     <t xml:space="preserve">8.44191455841064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32948017120361</t>
+    <t xml:space="preserve">8.32948112487793</t>
   </si>
   <si>
     <t xml:space="preserve">8.25452423095703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43254566192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47002220153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32011127471924</t>
+    <t xml:space="preserve">8.43254470825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47002124786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32011032104492</t>
   </si>
   <si>
     <t xml:space="preserve">8.20767688751221</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08587265014648</t>
+    <t xml:space="preserve">8.0858736038208</t>
   </si>
   <si>
     <t xml:space="preserve">7.78604936599731</t>
@@ -1010,25 +1010,25 @@
     <t xml:space="preserve">7.83289623260498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90785264968872</t>
+    <t xml:space="preserve">7.9078516960144</t>
   </si>
   <si>
     <t xml:space="preserve">7.50496482849121</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37379169464111</t>
+    <t xml:space="preserve">7.37379217147827</t>
   </si>
   <si>
     <t xml:space="preserve">7.12081527709961</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28009700775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98027324676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93342542648315</t>
+    <t xml:space="preserve">7.28009653091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98027276992798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93342590332031</t>
   </si>
   <si>
     <t xml:space="preserve">7.06459808349609</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">7.34568309783936</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5424427986145</t>
+    <t xml:space="preserve">7.54244232177734</t>
   </si>
   <si>
     <t xml:space="preserve">8.19830703735352</t>
@@ -1049,10 +1049,10 @@
     <t xml:space="preserve">8.2170467376709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65194320678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46116256713867</t>
+    <t xml:space="preserve">8.65194225311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46116161346436</t>
   </si>
   <si>
     <t xml:space="preserve">8.53747367858887</t>
@@ -1070,7 +1070,7 @@
     <t xml:space="preserve">8.72825622558594</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66148281097412</t>
+    <t xml:space="preserve">8.6614818572998</t>
   </si>
   <si>
     <t xml:space="preserve">8.49931812286377</t>
@@ -1091,13 +1091,13 @@
     <t xml:space="preserve">8.29899787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12729454040527</t>
+    <t xml:space="preserve">8.12729358673096</t>
   </si>
   <si>
     <t xml:space="preserve">7.89835643768311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10821723937988</t>
+    <t xml:space="preserve">8.10821628570557</t>
   </si>
   <si>
     <t xml:space="preserve">7.84112215042114</t>
@@ -1112,13 +1112,13 @@
     <t xml:space="preserve">8.06052017211914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07959938049316</t>
+    <t xml:space="preserve">8.07959842681885</t>
   </si>
   <si>
     <t xml:space="preserve">8.07005977630615</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92697429656982</t>
+    <t xml:space="preserve">7.92697334289551</t>
   </si>
   <si>
     <t xml:space="preserve">7.98420810699463</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">8.30853748321533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26084041595459</t>
+    <t xml:space="preserve">8.26084136962891</t>
   </si>
   <si>
     <t xml:space="preserve">8.27038097381592</t>
@@ -1136,13 +1136,13 @@
     <t xml:space="preserve">8.18452930450439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03190422058105</t>
+    <t xml:space="preserve">8.03190326690674</t>
   </si>
   <si>
     <t xml:space="preserve">7.96512985229492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86020040512085</t>
+    <t xml:space="preserve">7.86019992828369</t>
   </si>
   <si>
     <t xml:space="preserve">7.86973905563354</t>
@@ -1166,10 +1166,10 @@
     <t xml:space="preserve">7.63126230239868</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65987920761108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16545009613037</t>
+    <t xml:space="preserve">7.65987873077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16545104980469</t>
   </si>
   <si>
     <t xml:space="preserve">8.32761383056641</t>
@@ -1181,13 +1181,13 @@
     <t xml:space="preserve">7.9365119934082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19406795501709</t>
+    <t xml:space="preserve">8.19406890869141</t>
   </si>
   <si>
     <t xml:space="preserve">8.2322244644165</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31807613372803</t>
+    <t xml:space="preserve">8.31807708740234</t>
   </si>
   <si>
     <t xml:space="preserve">8.15591239929199</t>
@@ -1208,7 +1208,7 @@
     <t xml:space="preserve">8.34669303894043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95559167861938</t>
+    <t xml:space="preserve">7.95559072494507</t>
   </si>
   <si>
     <t xml:space="preserve">7.77434825897217</t>
@@ -1223,13 +1223,13 @@
     <t xml:space="preserve">8.01282501220703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05098152160645</t>
+    <t xml:space="preserve">8.05098056793213</t>
   </si>
   <si>
     <t xml:space="preserve">7.67895746231079</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73619222640991</t>
+    <t xml:space="preserve">7.73619174957275</t>
   </si>
   <si>
     <t xml:space="preserve">7.6980357170105</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">7.62172269821167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52633190155029</t>
+    <t xml:space="preserve">7.52633237838745</t>
   </si>
   <si>
     <t xml:space="preserve">7.34508991241455</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">7.20200395584106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18292617797852</t>
+    <t xml:space="preserve">7.18292570114136</t>
   </si>
   <si>
     <t xml:space="preserve">7.14476919174194</t>
@@ -1274,13 +1274,13 @@
     <t xml:space="preserve">7.1543083190918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24969863891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24015998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46909809112549</t>
+    <t xml:space="preserve">7.24969911575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24016046524048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46909761428833</t>
   </si>
   <si>
     <t xml:space="preserve">7.41186332702637</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">7.45001983642578</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28785514831543</t>
+    <t xml:space="preserve">7.28785562515259</t>
   </si>
   <si>
     <t xml:space="preserve">7.39278507232666</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">7.3355507850647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61218452453613</t>
+    <t xml:space="preserve">7.61218404769897</t>
   </si>
   <si>
     <t xml:space="preserve">7.90789556503296</t>
@@ -1307,28 +1307,28 @@
     <t xml:space="preserve">7.94605112075806</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45955896377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70757484436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8792781829834</t>
+    <t xml:space="preserve">7.45955848693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70757436752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87927865982056</t>
   </si>
   <si>
     <t xml:space="preserve">7.99374723434448</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75527000427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81250429153442</t>
+    <t xml:space="preserve">7.75527048110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81250476837158</t>
   </si>
   <si>
     <t xml:space="preserve">7.79342699050903</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80296564102173</t>
+    <t xml:space="preserve">7.80296611785889</t>
   </si>
   <si>
     <t xml:space="preserve">7.85066032409668</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">7.74573087692261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83158302307129</t>
+    <t xml:space="preserve">7.83158254623413</t>
   </si>
   <si>
     <t xml:space="preserve">7.66941833496094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60264444351196</t>
+    <t xml:space="preserve">7.60264492034912</t>
   </si>
   <si>
     <t xml:space="preserve">7.58356666564941</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">8.00328636169434</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78388690948486</t>
+    <t xml:space="preserve">7.78388738632202</t>
   </si>
   <si>
     <t xml:space="preserve">7.3641676902771</t>
@@ -62575,7 +62575,7 @@
     </row>
     <row r="2309">
       <c r="A2309" s="1" t="n">
-        <v>45978.6911921296</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B2309" t="n">
         <v>24889</v>
@@ -62596,6 +62596,32 @@
         <v>724</v>
       </c>
       <c r="H2309" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2310">
+      <c r="A2310" s="1" t="n">
+        <v>45979.6909837963</v>
+      </c>
+      <c r="B2310" t="n">
+        <v>60269</v>
+      </c>
+      <c r="C2310" t="n">
+        <v>9.26000022888184</v>
+      </c>
+      <c r="D2310" t="n">
+        <v>8.97999954223633</v>
+      </c>
+      <c r="E2310" t="n">
+        <v>9.23999977111816</v>
+      </c>
+      <c r="F2310" t="n">
+        <v>9.02000045776367</v>
+      </c>
+      <c r="G2310" t="s">
+        <v>730</v>
+      </c>
+      <c r="H2310" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="739">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="740">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07642269134521</t>
+    <t xml:space="preserve">9.0764217376709</t>
   </si>
   <si>
     <t xml:space="preserve">FF.MI</t>
@@ -53,13 +53,13 @@
     <t xml:space="preserve">9.24887275695801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09457397460938</t>
+    <t xml:space="preserve">9.09457588195801</t>
   </si>
   <si>
     <t xml:space="preserve">9.12180423736572</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03104114532471</t>
+    <t xml:space="preserve">9.03104019165039</t>
   </si>
   <si>
     <t xml:space="preserve">8.95389080047607</t>
@@ -71,16 +71,16 @@
     <t xml:space="preserve">8.89489364624023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84951114654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85858821868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87673950195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76782321929932</t>
+    <t xml:space="preserve">8.84951210021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85858726501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87674045562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.767822265625</t>
   </si>
   <si>
     <t xml:space="preserve">8.8676643371582</t>
@@ -92,55 +92,55 @@
     <t xml:space="preserve">9.23072052001953</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11272811889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96750450134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91304683685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92212200164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00380992889404</t>
+    <t xml:space="preserve">9.11272716522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96750354766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91304492950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9221248626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00381088256836</t>
   </si>
   <si>
     <t xml:space="preserve">9.15810966491699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16718482971191</t>
+    <t xml:space="preserve">9.16718673706055</t>
   </si>
   <si>
     <t xml:space="preserve">9.43947887420654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54839515686035</t>
+    <t xml:space="preserve">9.54839611053467</t>
   </si>
   <si>
     <t xml:space="preserve">9.62100696563721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8025369644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71177005767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56654930114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58470249176025</t>
+    <t xml:space="preserve">9.80253505706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71177101135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56654834747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58470058441162</t>
   </si>
   <si>
     <t xml:space="preserve">9.5756254196167</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53024291992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50301456451416</t>
+    <t xml:space="preserve">9.53024196624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50301551818848</t>
   </si>
   <si>
     <t xml:space="preserve">9.60285472869873</t>
@@ -149,40 +149,40 @@
     <t xml:space="preserve">9.63916015625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79345798492432</t>
+    <t xml:space="preserve">9.79345989227295</t>
   </si>
   <si>
     <t xml:space="preserve">9.95683479309082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93868064880371</t>
+    <t xml:space="preserve">9.93868160247803</t>
   </si>
   <si>
     <t xml:space="preserve">9.98406410217285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73900032043457</t>
+    <t xml:space="preserve">9.73900127410889</t>
   </si>
   <si>
     <t xml:space="preserve">9.76623058319092</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74807548522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75715446472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64823627471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82068634033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7026948928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72084712982178</t>
+    <t xml:space="preserve">9.74807643890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75715351104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64823722839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82068824768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70269393920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72084808349609</t>
   </si>
   <si>
     <t xml:space="preserve">9.67546558380127</t>
@@ -191,31 +191,31 @@
     <t xml:space="preserve">9.66638851165771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63008403778076</t>
+    <t xml:space="preserve">9.63008308410645</t>
   </si>
   <si>
     <t xml:space="preserve">9.65731334686279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68454360961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81161308288574</t>
+    <t xml:space="preserve">9.68454170227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81161212921143</t>
   </si>
   <si>
     <t xml:space="preserve">9.8297643661499</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84791851043701</t>
+    <t xml:space="preserve">9.8479175567627</t>
   </si>
   <si>
     <t xml:space="preserve">9.83884143829346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72992515563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78438186645508</t>
+    <t xml:space="preserve">9.72992420196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78438377380371</t>
   </si>
   <si>
     <t xml:space="preserve">9.55747318267822</t>
@@ -227,22 +227,22 @@
     <t xml:space="preserve">9.33963775634766</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27610301971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25794982910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19441604614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18533897399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41224956512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22164440155029</t>
+    <t xml:space="preserve">9.27610397338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25795078277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19441413879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18533802032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41225051879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22164535522461</t>
   </si>
   <si>
     <t xml:space="preserve">9.31240940093994</t>
@@ -251,10 +251,10 @@
     <t xml:space="preserve">9.26702690124512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29425525665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28518009185791</t>
+    <t xml:space="preserve">9.29425621032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28517818450928</t>
   </si>
   <si>
     <t xml:space="preserve">9.37594318389893</t>
@@ -263,28 +263,28 @@
     <t xml:space="preserve">9.36686706542969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38502025604248</t>
+    <t xml:space="preserve">9.3850212097168</t>
   </si>
   <si>
     <t xml:space="preserve">9.45763111114502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39409828186035</t>
+    <t xml:space="preserve">9.39409732818604</t>
   </si>
   <si>
     <t xml:space="preserve">9.48486137390137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49393653869629</t>
+    <t xml:space="preserve">9.49393749237061</t>
   </si>
   <si>
     <t xml:space="preserve">9.44855499267578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47578430175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23979663848877</t>
+    <t xml:space="preserve">9.4757833480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23979759216309</t>
   </si>
   <si>
     <t xml:space="preserve">9.14903354644775</t>
@@ -293,43 +293,43 @@
     <t xml:space="preserve">9.21256828308105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20349311828613</t>
+    <t xml:space="preserve">9.20349216461182</t>
   </si>
   <si>
     <t xml:space="preserve">9.13088130950928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1399564743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94027614593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80412769317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75874710083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66798305511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62260150909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53183555603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35030746459961</t>
+    <t xml:space="preserve">9.13995456695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94027709960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80412864685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75874805450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66798210144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62259960174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53183650970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35030841827393</t>
   </si>
   <si>
     <t xml:space="preserve">8.16878032684326</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98725175857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03263282775879</t>
+    <t xml:space="preserve">7.98725128173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03263378143311</t>
   </si>
   <si>
     <t xml:space="preserve">8.12339687347412</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">8.3049259185791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21416282653809</t>
+    <t xml:space="preserve">8.21416187286377</t>
   </si>
   <si>
     <t xml:space="preserve">8.39568996429443</t>
@@ -353,58 +353,58 @@
     <t xml:space="preserve">8.57721710205078</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71336650848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53202152252197</t>
+    <t xml:space="preserve">8.71336460113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53202342987061</t>
   </si>
   <si>
     <t xml:space="preserve">9.25706100463867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44036865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16540718078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07375144958496</t>
+    <t xml:space="preserve">9.44036960601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16540622711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07375240325928</t>
   </si>
   <si>
     <t xml:space="preserve">9.11958026885986</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98209953308105</t>
+    <t xml:space="preserve">8.98209857940674</t>
   </si>
   <si>
     <t xml:space="preserve">9.02792644500732</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62367725372314</t>
+    <t xml:space="preserve">9.62367630004883</t>
   </si>
   <si>
     <t xml:space="preserve">9.80698490142822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89863872528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99029159545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1736011505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2652559280396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3569097518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5402183532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6318731307983</t>
+    <t xml:space="preserve">9.89863777160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9902925491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.173602104187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2652568817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3569087982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5402173995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.631872177124</t>
   </si>
   <si>
     <t xml:space="preserve">10.8151798248291</t>
@@ -422,19 +422,19 @@
     <t xml:space="preserve">11.0901432037354</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1817960739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2734508514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4567584991455</t>
+    <t xml:space="preserve">11.1817970275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2734498977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4567575454712</t>
   </si>
   <si>
     <t xml:space="preserve">11.3651027679443</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4485635757446</t>
+    <t xml:space="preserve">10.4485626220703</t>
   </si>
   <si>
     <t xml:space="preserve">9.71533107757568</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">9.03709030151367</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3945426940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76115703582764</t>
+    <t xml:space="preserve">9.39454174041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76115798950195</t>
   </si>
   <si>
     <t xml:space="preserve">9.66950416564941</t>
@@ -479,13 +479,13 @@
     <t xml:space="preserve">9.73283004760742</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59379100799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96456432342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91821670532227</t>
+    <t xml:space="preserve">9.59379005432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96456527709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91821765899658</t>
   </si>
   <si>
     <t xml:space="preserve">9.54744338989258</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">10.1036043167114</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1499509811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1962985992432</t>
+    <t xml:space="preserve">10.1499519348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1962976455688</t>
   </si>
   <si>
     <t xml:space="preserve">9.77917766571045</t>
@@ -521,16 +521,16 @@
     <t xml:space="preserve">10.2426452636719</t>
   </si>
   <si>
-    <t xml:space="preserve">10.381685256958</t>
+    <t xml:space="preserve">10.3816871643066</t>
   </si>
   <si>
     <t xml:space="preserve">9.68648338317871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64013576507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50109672546387</t>
+    <t xml:space="preserve">9.64013671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50109577178955</t>
   </si>
   <si>
     <t xml:space="preserve">9.31570911407471</t>
@@ -539,10 +539,10 @@
     <t xml:space="preserve">9.23228549957275</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19520664215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25082302093506</t>
+    <t xml:space="preserve">9.1952075958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25082206726074</t>
   </si>
   <si>
     <t xml:space="preserve">9.26936149597168</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">9.17666816711426</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02835941314697</t>
+    <t xml:space="preserve">9.02835845947266</t>
   </si>
   <si>
     <t xml:space="preserve">8.95420265197754</t>
@@ -578,13 +578,13 @@
     <t xml:space="preserve">8.9912805557251</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7688159942627</t>
+    <t xml:space="preserve">8.76881694793701</t>
   </si>
   <si>
     <t xml:space="preserve">8.89858818054199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93566608428955</t>
+    <t xml:space="preserve">8.93566513061523</t>
   </si>
   <si>
     <t xml:space="preserve">10.3353385925293</t>
@@ -596,16 +596,16 @@
     <t xml:space="preserve">11.0305414199829</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2159280776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4940090179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5403547286987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5867033004761</t>
+    <t xml:space="preserve">11.2159290313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.49400806427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.540355682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5867023468018</t>
   </si>
   <si>
     <t xml:space="preserve">11.6330490112305</t>
@@ -614,25 +614,25 @@
     <t xml:space="preserve">11.7257423400879</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9111309051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9574766159058</t>
+    <t xml:space="preserve">11.9111299514771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9574775695801</t>
   </si>
   <si>
     <t xml:space="preserve">12.1892118453979</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2819042205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3745985031128</t>
+    <t xml:space="preserve">12.2819061279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3745994567871</t>
   </si>
   <si>
     <t xml:space="preserve">12.5136394500732</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3282527923584</t>
+    <t xml:space="preserve">12.3282518386841</t>
   </si>
   <si>
     <t xml:space="preserve">12.1428651809692</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">12.0965185165405</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5551204681396</t>
+    <t xml:space="preserve">12.555121421814</t>
   </si>
   <si>
     <t xml:space="preserve">12.5082750320435</t>
@@ -653,16 +653,16 @@
     <t xml:space="preserve">12.4614267349243</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4145793914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7425127029419</t>
+    <t xml:space="preserve">12.4145803451538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7425117492676</t>
   </si>
   <si>
     <t xml:space="preserve">12.6956653594971</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2271909713745</t>
+    <t xml:space="preserve">12.2271900177002</t>
   </si>
   <si>
     <t xml:space="preserve">12.1803426742554</t>
@@ -677,16 +677,16 @@
     <t xml:space="preserve">12.8362064361572</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7893600463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6019687652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9299011230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8830537796021</t>
+    <t xml:space="preserve">12.7893581390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6019697189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9299020767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8830547332764</t>
   </si>
   <si>
     <t xml:space="preserve">13.0704441070557</t>
@@ -707,37 +707,37 @@
     <t xml:space="preserve">14.5695629119873</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2254276275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1317319869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7569532394409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0380373001099</t>
+    <t xml:space="preserve">15.2254285812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1317338943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7569522857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0380382537842</t>
   </si>
   <si>
     <t xml:space="preserve">15.1785802841187</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3191232681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8974952697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4596643447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4128189086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5533609390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0686798095703</t>
+    <t xml:space="preserve">15.3191223144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8974943161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4596652984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4128179550171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5533618927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0686817169189</t>
   </si>
   <si>
     <t xml:space="preserve">16.8650894165039</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">17.0524806976318</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9587841033936</t>
+    <t xml:space="preserve">16.9587821960449</t>
   </si>
   <si>
     <t xml:space="preserve">16.7245464324951</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">16.584005355835</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2092227935791</t>
+    <t xml:space="preserve">16.2092247009277</t>
   </si>
   <si>
     <t xml:space="preserve">16.2560710906982</t>
@@ -782,25 +782,25 @@
     <t xml:space="preserve">16.396614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3029193878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8344440460205</t>
+    <t xml:space="preserve">16.3029174804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8344430923462</t>
   </si>
   <si>
     <t xml:space="preserve">16.1155300140381</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0218372344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1623764038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9749870300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7407493591309</t>
+    <t xml:space="preserve">16.0218353271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1623783111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.974986076355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7407503128052</t>
   </si>
   <si>
     <t xml:space="preserve">16.4434604644775</t>
@@ -812,28 +812,28 @@
     <t xml:space="preserve">17.0993270874023</t>
   </si>
   <si>
-    <t xml:space="preserve">16.677698135376</t>
+    <t xml:space="preserve">16.6777000427246</t>
   </si>
   <si>
     <t xml:space="preserve">16.8182430267334</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2722749710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0848846435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9911909103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8038005828857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4758682250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.382173538208</t>
+    <t xml:space="preserve">15.272274017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.084885597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.991189956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8038015365601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4758672714233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3821744918823</t>
   </si>
   <si>
     <t xml:space="preserve">14.1010885238647</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">14.5227155685425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.960545539856</t>
+    <t xml:space="preserve">13.9605464935303</t>
   </si>
   <si>
     <t xml:space="preserve">14.2416305541992</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1947832107544</t>
+    <t xml:space="preserve">14.1947822570801</t>
   </si>
   <si>
     <t xml:space="preserve">14.0073928833008</t>
@@ -860,13 +860,13 @@
     <t xml:space="preserve">13.7263078689575</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1479358673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4290208816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6164102554321</t>
+    <t xml:space="preserve">14.1479368209839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4290199279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6164112091064</t>
   </si>
   <si>
     <t xml:space="preserve">13.7731561660767</t>
@@ -878,25 +878,25 @@
     <t xml:space="preserve">13.3046808242798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3983755111694</t>
+    <t xml:space="preserve">13.3983764648438</t>
   </si>
   <si>
     <t xml:space="preserve">13.0235958099365</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1172904968262</t>
+    <t xml:space="preserve">13.1172914505005</t>
   </si>
   <si>
     <t xml:space="preserve">12.976749420166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3677320480347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0866460800171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9929513931274</t>
+    <t xml:space="preserve">12.3677310943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0866470336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9929523468018</t>
   </si>
   <si>
     <t xml:space="preserve">11.8992576599121</t>
@@ -908,37 +908,37 @@
     <t xml:space="preserve">12.1334943771362</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4776296615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2433929443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3839349746704</t>
+    <t xml:space="preserve">11.4776306152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2433938980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3839340209961</t>
   </si>
   <si>
     <t xml:space="preserve">11.6650199890137</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4307823181152</t>
+    <t xml:space="preserve">11.4307832717896</t>
   </si>
   <si>
     <t xml:space="preserve">10.9623079299927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7280702590942</t>
+    <t xml:space="preserve">10.7280712127686</t>
   </si>
   <si>
     <t xml:space="preserve">11.1965446472168</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5713243484497</t>
+    <t xml:space="preserve">11.571325302124</t>
   </si>
   <si>
     <t xml:space="preserve">11.3370885848999</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2902402877808</t>
+    <t xml:space="preserve">11.2902393341064</t>
   </si>
   <si>
     <t xml:space="preserve">11.7118673324585</t>
@@ -950,22 +950,22 @@
     <t xml:space="preserve">11.8055629730225</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0091552734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46318817138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33884906768799</t>
+    <t xml:space="preserve">11.0091562271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46318912506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3388500213623</t>
   </si>
   <si>
     <t xml:space="preserve">8.57308673858643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31074047088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45128440856934</t>
+    <t xml:space="preserve">8.31074142456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45128345489502</t>
   </si>
   <si>
     <t xml:space="preserve">8.61993408203125</t>
@@ -974,43 +974,43 @@
     <t xml:space="preserve">8.44191455841064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32948112487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25452423095703</t>
+    <t xml:space="preserve">8.32948017120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25452518463135</t>
   </si>
   <si>
     <t xml:space="preserve">8.43254470825195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47002124786377</t>
+    <t xml:space="preserve">8.47002220153809</t>
   </si>
   <si>
     <t xml:space="preserve">8.32011032104492</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20767688751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0858736038208</t>
+    <t xml:space="preserve">8.20767593383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08587265014648</t>
   </si>
   <si>
     <t xml:space="preserve">7.78604936599731</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49559545516968</t>
+    <t xml:space="preserve">7.49559497833252</t>
   </si>
   <si>
     <t xml:space="preserve">7.33631372451782</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23324918746948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83289623260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9078516960144</t>
+    <t xml:space="preserve">7.23324871063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8328971862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90785264968872</t>
   </si>
   <si>
     <t xml:space="preserve">7.50496482849121</t>
@@ -1022,10 +1022,10 @@
     <t xml:space="preserve">7.12081527709961</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28009653091431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98027276992798</t>
+    <t xml:space="preserve">7.28009700775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98027324676514</t>
   </si>
   <si>
     <t xml:space="preserve">6.93342590332031</t>
@@ -1037,10 +1037,10 @@
     <t xml:space="preserve">7.02712059020996</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34568309783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54244232177734</t>
+    <t xml:space="preserve">7.34568357467651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5424427986145</t>
   </si>
   <si>
     <t xml:space="preserve">8.19830703735352</t>
@@ -2229,6 +2229,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.39999961853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03999996185303</t>
   </si>
 </sst>
 </file>
@@ -62601,7 +62604,7 @@
     </row>
     <row r="2310">
       <c r="A2310" s="1" t="n">
-        <v>45979.6909837963</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B2310" t="n">
         <v>60269</v>
@@ -62622,6 +62625,32 @@
         <v>730</v>
       </c>
       <c r="H2310" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2311">
+      <c r="A2311" s="1" t="n">
+        <v>45980.6909953704</v>
+      </c>
+      <c r="B2311" t="n">
+        <v>45124</v>
+      </c>
+      <c r="C2311" t="n">
+        <v>9.15999984741211</v>
+      </c>
+      <c r="D2311" t="n">
+        <v>9</v>
+      </c>
+      <c r="E2311" t="n">
+        <v>9.07999992370605</v>
+      </c>
+      <c r="F2311" t="n">
+        <v>9.03999996185303</v>
+      </c>
+      <c r="G2311" t="s">
+        <v>739</v>
+      </c>
+      <c r="H2311" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0764217376709</t>
+    <t xml:space="preserve">9.07642078399658</t>
   </si>
   <si>
     <t xml:space="preserve">FF.MI</t>
@@ -47,40 +47,40 @@
     <t xml:space="preserve">8.98565769195557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08549785614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24887275695801</t>
+    <t xml:space="preserve">9.08549880981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24887371063232</t>
   </si>
   <si>
     <t xml:space="preserve">9.09457588195801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12180423736572</t>
+    <t xml:space="preserve">9.12180519104004</t>
   </si>
   <si>
     <t xml:space="preserve">9.03104019165039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95389080047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89943313598633</t>
+    <t xml:space="preserve">8.95388889312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89943218231201</t>
   </si>
   <si>
     <t xml:space="preserve">8.89489364624023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84951210021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85858726501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87674045562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.767822265625</t>
+    <t xml:space="preserve">8.84951114654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85858821868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87674140930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76782417297363</t>
   </si>
   <si>
     <t xml:space="preserve">8.8676643371582</t>
@@ -89,22 +89,22 @@
     <t xml:space="preserve">9.04919147491455</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23072052001953</t>
+    <t xml:space="preserve">9.23072147369385</t>
   </si>
   <si>
     <t xml:space="preserve">9.11272716522217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96750354766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91304492950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9221248626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00381088256836</t>
+    <t xml:space="preserve">8.96750545501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91304683685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92212295532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00380992889404</t>
   </si>
   <si>
     <t xml:space="preserve">9.15810966491699</t>
@@ -113,37 +113,37 @@
     <t xml:space="preserve">9.16718673706055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43947887420654</t>
+    <t xml:space="preserve">9.43947792053223</t>
   </si>
   <si>
     <t xml:space="preserve">9.54839611053467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62100696563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80253505706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71177101135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56654834747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58470058441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5756254196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53024196624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50301551818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60285472869873</t>
+    <t xml:space="preserve">9.62100791931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80253601074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71177196502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56654930114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58470153808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57562637329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53024291992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50301456451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60285568237305</t>
   </si>
   <si>
     <t xml:space="preserve">9.63916015625</t>
@@ -152,16 +152,16 @@
     <t xml:space="preserve">9.79345989227295</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95683479309082</t>
+    <t xml:space="preserve">9.95683574676514</t>
   </si>
   <si>
     <t xml:space="preserve">9.93868160247803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98406410217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73900127410889</t>
+    <t xml:space="preserve">9.98406505584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73900032043457</t>
   </si>
   <si>
     <t xml:space="preserve">9.76623058319092</t>
@@ -170,10 +170,10 @@
     <t xml:space="preserve">9.74807643890381</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75715351104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64823722839355</t>
+    <t xml:space="preserve">9.75715255737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64823627471924</t>
   </si>
   <si>
     <t xml:space="preserve">9.82068824768066</t>
@@ -182,19 +182,19 @@
     <t xml:space="preserve">9.70269393920898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72084808349609</t>
+    <t xml:space="preserve">9.72084712982178</t>
   </si>
   <si>
     <t xml:space="preserve">9.67546558380127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66638851165771</t>
+    <t xml:space="preserve">9.66638946533203</t>
   </si>
   <si>
     <t xml:space="preserve">9.63008308410645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65731334686279</t>
+    <t xml:space="preserve">9.65731239318848</t>
   </si>
   <si>
     <t xml:space="preserve">9.68454170227051</t>
@@ -209,61 +209,61 @@
     <t xml:space="preserve">9.8479175567627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83884143829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72992420196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78438377380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55747318267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34871387481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33963775634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27610397338867</t>
+    <t xml:space="preserve">9.83884048461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72992324829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78438186645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55747127532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34871578216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33963680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27610301971436</t>
   </si>
   <si>
     <t xml:space="preserve">9.25795078277588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19441413879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18533802032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41225051879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22164535522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31240940093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26702690124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29425621032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28517818450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37594318389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36686706542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3850212097168</t>
+    <t xml:space="preserve">9.19441509246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18533897399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4122486114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22164440155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31241035461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2670259475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29425525665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28518009185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37594413757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36686611175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38502025604248</t>
   </si>
   <si>
     <t xml:space="preserve">9.45763111114502</t>
@@ -272,16 +272,16 @@
     <t xml:space="preserve">9.39409732818604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48486137390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49393749237061</t>
+    <t xml:space="preserve">9.48486042022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49393844604492</t>
   </si>
   <si>
     <t xml:space="preserve">9.44855499267578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4757833480835</t>
+    <t xml:space="preserve">9.47578430175781</t>
   </si>
   <si>
     <t xml:space="preserve">9.23979759216309</t>
@@ -290,43 +290,43 @@
     <t xml:space="preserve">9.14903354644775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21256828308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20349216461182</t>
+    <t xml:space="preserve">9.21256923675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20349311828613</t>
   </si>
   <si>
     <t xml:space="preserve">9.13088130950928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13995456695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94027709960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80412864685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75874805450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66798210144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62259960174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53183650970459</t>
+    <t xml:space="preserve">9.13995552062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94027519226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8041296005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75874519348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66798305511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62260055541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53183555603027</t>
   </si>
   <si>
     <t xml:space="preserve">8.35030841827393</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16878032684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98725128173828</t>
+    <t xml:space="preserve">8.16877841949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98725032806396</t>
   </si>
   <si>
     <t xml:space="preserve">8.03263378143311</t>
@@ -335,16 +335,16 @@
     <t xml:space="preserve">8.12339687347412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25954532623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94186878204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3049259185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21416187286377</t>
+    <t xml:space="preserve">8.25954437255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94186925888062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30492496490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21416091918945</t>
   </si>
   <si>
     <t xml:space="preserve">8.39568996429443</t>
@@ -353,40 +353,40 @@
     <t xml:space="preserve">8.57721710205078</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71336460113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53202342987061</t>
+    <t xml:space="preserve">8.71336555480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53202247619629</t>
   </si>
   <si>
     <t xml:space="preserve">9.25706100463867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44036960601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16540622711182</t>
+    <t xml:space="preserve">9.44036865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16540718078613</t>
   </si>
   <si>
     <t xml:space="preserve">9.07375240325928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11958026885986</t>
+    <t xml:space="preserve">9.11957836151123</t>
   </si>
   <si>
     <t xml:space="preserve">8.98209857940674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02792644500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62367630004883</t>
+    <t xml:space="preserve">9.02792453765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62367725372314</t>
   </si>
   <si>
     <t xml:space="preserve">9.80698490142822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89863777160645</t>
+    <t xml:space="preserve">9.89863967895508</t>
   </si>
   <si>
     <t xml:space="preserve">9.9902925491333</t>
@@ -395,19 +395,19 @@
     <t xml:space="preserve">10.173602104187</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2652568817139</t>
+    <t xml:space="preserve">10.2652559280396</t>
   </si>
   <si>
     <t xml:space="preserve">10.3569087982178</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5402173995972</t>
+    <t xml:space="preserve">10.5402164459229</t>
   </si>
   <si>
     <t xml:space="preserve">10.631872177124</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8151798248291</t>
+    <t xml:space="preserve">10.8151807785034</t>
   </si>
   <si>
     <t xml:space="preserve">10.7235260009766</t>
@@ -431,19 +431,19 @@
     <t xml:space="preserve">11.4567575454712</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3651027679443</t>
+    <t xml:space="preserve">11.3651037216187</t>
   </si>
   <si>
     <t xml:space="preserve">10.4485626220703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71533107757568</t>
+    <t xml:space="preserve">9.71533203125</t>
   </si>
   <si>
     <t xml:space="preserve">8.79879093170166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24886608123779</t>
+    <t xml:space="preserve">8.24886512756348</t>
   </si>
   <si>
     <t xml:space="preserve">9.2112340927124</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">9.03709030151367</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39454174041748</t>
+    <t xml:space="preserve">9.3945426940918</t>
   </si>
   <si>
     <t xml:space="preserve">9.76115798950195</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">9.57785034179688</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0361204147339</t>
+    <t xml:space="preserve">10.0361194610596</t>
   </si>
   <si>
     <t xml:space="preserve">9.94446659088135</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">9.96456527709961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91821765899658</t>
+    <t xml:space="preserve">9.9182186126709</t>
   </si>
   <si>
     <t xml:space="preserve">9.54744338989258</t>
@@ -494,13 +494,13 @@
     <t xml:space="preserve">10.010910987854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1036043167114</t>
+    <t xml:space="preserve">10.1036052703857</t>
   </si>
   <si>
     <t xml:space="preserve">10.1499519348145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1962976455688</t>
+    <t xml:space="preserve">10.1962985992432</t>
   </si>
   <si>
     <t xml:space="preserve">9.77917766571045</t>
@@ -509,19 +509,19 @@
     <t xml:space="preserve">9.87187099456787</t>
   </si>
   <si>
-    <t xml:space="preserve">10.057258605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2889928817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4743795394897</t>
+    <t xml:space="preserve">10.0572576522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2889919281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4743804931641</t>
   </si>
   <si>
     <t xml:space="preserve">10.2426452636719</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3816871643066</t>
+    <t xml:space="preserve">10.381685256958</t>
   </si>
   <si>
     <t xml:space="preserve">9.68648338317871</t>
@@ -536,34 +536,34 @@
     <t xml:space="preserve">9.31570911407471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23228549957275</t>
+    <t xml:space="preserve">9.23228359222412</t>
   </si>
   <si>
     <t xml:space="preserve">9.1952075958252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25082206726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26936149597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2137451171875</t>
+    <t xml:space="preserve">9.25082302093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.269362449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21374607086182</t>
   </si>
   <si>
     <t xml:space="preserve">9.04689693450928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12105274200439</t>
+    <t xml:space="preserve">9.12105369567871</t>
   </si>
   <si>
     <t xml:space="preserve">9.0654354095459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97274208068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17666816711426</t>
+    <t xml:space="preserve">8.97274303436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17666912078857</t>
   </si>
   <si>
     <t xml:space="preserve">9.02835845947266</t>
@@ -575,13 +575,13 @@
     <t xml:space="preserve">8.71320056915283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9912805557251</t>
+    <t xml:space="preserve">8.99128150939941</t>
   </si>
   <si>
     <t xml:space="preserve">8.76881694793701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89858818054199</t>
+    <t xml:space="preserve">8.89858722686768</t>
   </si>
   <si>
     <t xml:space="preserve">8.93566513061523</t>
@@ -593,40 +593,40 @@
     <t xml:space="preserve">10.9841938018799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0305414199829</t>
+    <t xml:space="preserve">11.0305404663086</t>
   </si>
   <si>
     <t xml:space="preserve">11.2159290313721</t>
   </si>
   <si>
-    <t xml:space="preserve">11.49400806427</t>
+    <t xml:space="preserve">11.4940090179443</t>
   </si>
   <si>
     <t xml:space="preserve">11.540355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5867023468018</t>
+    <t xml:space="preserve">11.5867033004761</t>
   </si>
   <si>
     <t xml:space="preserve">11.6330490112305</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7257423400879</t>
+    <t xml:space="preserve">11.7257413864136</t>
   </si>
   <si>
     <t xml:space="preserve">11.9111299514771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9574775695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1892118453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2819061279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3745994567871</t>
+    <t xml:space="preserve">11.9574766159058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1892099380493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2819042205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3745985031128</t>
   </si>
   <si>
     <t xml:space="preserve">12.5136394500732</t>
@@ -638,10 +638,10 @@
     <t xml:space="preserve">12.1428651809692</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0965185165405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.555121421814</t>
+    <t xml:space="preserve">12.0965175628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5551223754883</t>
   </si>
   <si>
     <t xml:space="preserve">12.5082750320435</t>
@@ -650,70 +650,70 @@
     <t xml:space="preserve">12.6488170623779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4614267349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4145803451538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7425117492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6956653594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2271900177002</t>
+    <t xml:space="preserve">12.4614276885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4145793914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7425127029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6956644058228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2271890640259</t>
   </si>
   <si>
     <t xml:space="preserve">12.1803426742554</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3208847045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.274037361145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8362064361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7893581390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6019697189331</t>
+    <t xml:space="preserve">12.3208837509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2740383148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8362073898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7893590927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6019687652588</t>
   </si>
   <si>
     <t xml:space="preserve">12.9299020767212</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8830547332764</t>
+    <t xml:space="preserve">12.8830537796021</t>
   </si>
   <si>
     <t xml:space="preserve">13.0704441070557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.679461479187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8668518066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0542411804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3353261947632</t>
+    <t xml:space="preserve">13.6794605255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8668508529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0542402267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3353252410889</t>
   </si>
   <si>
     <t xml:space="preserve">14.5695629119873</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2254285812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1317338943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7569522857666</t>
+    <t xml:space="preserve">15.2254276275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1317329406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7569532394409</t>
   </si>
   <si>
     <t xml:space="preserve">15.0380382537842</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">15.1785802841187</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3191223144531</t>
+    <t xml:space="preserve">15.3191242218018</t>
   </si>
   <si>
     <t xml:space="preserve">14.8974943161011</t>
@@ -734,37 +734,37 @@
     <t xml:space="preserve">15.4128179550171</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5533618927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0686817169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8650894165039</t>
+    <t xml:space="preserve">15.5533609390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0686836242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8650875091553</t>
   </si>
   <si>
     <t xml:space="preserve">17.0056324005127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7713928222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.193021774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0524806976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9587821960449</t>
+    <t xml:space="preserve">16.7713947296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1930236816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0524787902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9587841033936</t>
   </si>
   <si>
     <t xml:space="preserve">16.7245464324951</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6308517456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5371570587158</t>
+    <t xml:space="preserve">16.6308536529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5371551513672</t>
   </si>
   <si>
     <t xml:space="preserve">16.584005355835</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">16.2092247009277</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2560710906982</t>
+    <t xml:space="preserve">16.2560749053955</t>
   </si>
   <si>
     <t xml:space="preserve">17.1461734771729</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">16.3029174804688</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8344430923462</t>
+    <t xml:space="preserve">15.8344440460205</t>
   </si>
   <si>
     <t xml:space="preserve">16.1155300140381</t>
@@ -794,7 +794,7 @@
     <t xml:space="preserve">16.0218353271484</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1623783111572</t>
+    <t xml:space="preserve">16.1623764038086</t>
   </si>
   <si>
     <t xml:space="preserve">15.974986076355</t>
@@ -803,37 +803,37 @@
     <t xml:space="preserve">15.7407503128052</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4434604644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9119358062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0993270874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6777000427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8182430267334</t>
+    <t xml:space="preserve">16.4434623718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9119338989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0993251800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.677698135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.818244934082</t>
   </si>
   <si>
     <t xml:space="preserve">15.272274017334</t>
   </si>
   <si>
-    <t xml:space="preserve">15.084885597229</t>
+    <t xml:space="preserve">15.0848846435547</t>
   </si>
   <si>
     <t xml:space="preserve">14.991189956665</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8038015365601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4758672714233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3821744918823</t>
+    <t xml:space="preserve">14.8037996292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4758682250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.382173538208</t>
   </si>
   <si>
     <t xml:space="preserve">14.1010885238647</t>
@@ -842,16 +842,16 @@
     <t xml:space="preserve">14.288477897644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5227155685425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9605464935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2416305541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1947822570801</t>
+    <t xml:space="preserve">14.5227146148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9605445861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2416296005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1947832107544</t>
   </si>
   <si>
     <t xml:space="preserve">14.0073928833008</t>
@@ -860,64 +860,64 @@
     <t xml:space="preserve">13.7263078689575</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1479368209839</t>
+    <t xml:space="preserve">14.1479358673096</t>
   </si>
   <si>
     <t xml:space="preserve">14.4290199279785</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6164112091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7731561660767</t>
+    <t xml:space="preserve">14.6164102554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7731552124023</t>
   </si>
   <si>
     <t xml:space="preserve">13.3515291213989</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3046808242798</t>
+    <t xml:space="preserve">13.3046817779541</t>
   </si>
   <si>
     <t xml:space="preserve">13.3983764648438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0235958099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1172914505005</t>
+    <t xml:space="preserve">13.0235967636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1172924041748</t>
   </si>
   <si>
     <t xml:space="preserve">12.976749420166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3677310943604</t>
+    <t xml:space="preserve">12.3677320480347</t>
   </si>
   <si>
     <t xml:space="preserve">12.0866470336914</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9929523468018</t>
+    <t xml:space="preserve">11.9929533004761</t>
   </si>
   <si>
     <t xml:space="preserve">11.8992576599121</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0397996902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1334943771362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4776306152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2433938980103</t>
+    <t xml:space="preserve">12.0397987365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1334934234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4776287078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2433929443359</t>
   </si>
   <si>
     <t xml:space="preserve">11.3839340209961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6650199890137</t>
+    <t xml:space="preserve">11.6650190353394</t>
   </si>
   <si>
     <t xml:space="preserve">11.4307832717896</t>
@@ -926,13 +926,13 @@
     <t xml:space="preserve">10.9623079299927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7280712127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1965446472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.571325302124</t>
+    <t xml:space="preserve">10.7280702590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1965436935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5713243484497</t>
   </si>
   <si>
     <t xml:space="preserve">11.3370885848999</t>
@@ -941,22 +941,22 @@
     <t xml:space="preserve">11.2902393341064</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7118673324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7587146759033</t>
+    <t xml:space="preserve">11.7118682861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.758713722229</t>
   </si>
   <si>
     <t xml:space="preserve">11.8055629730225</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0091562271118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46318912506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3388500213623</t>
+    <t xml:space="preserve">11.0091543197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46319007873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33884906768799</t>
   </si>
   <si>
     <t xml:space="preserve">8.57308673858643</t>
@@ -971,76 +971,76 @@
     <t xml:space="preserve">8.61993408203125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44191455841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32948017120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25452518463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43254470825195</t>
+    <t xml:space="preserve">8.44191360473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32948112487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25452423095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43254375457764</t>
   </si>
   <si>
     <t xml:space="preserve">8.47002220153809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32011032104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20767593383789</t>
+    <t xml:space="preserve">8.32011127471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20767688751221</t>
   </si>
   <si>
     <t xml:space="preserve">8.08587265014648</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78604936599731</t>
+    <t xml:space="preserve">7.78605031967163</t>
   </si>
   <si>
     <t xml:space="preserve">7.49559497833252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33631372451782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23324871063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8328971862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90785264968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50496482849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37379217147827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12081527709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28009700775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98027324676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93342590332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06459808349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02712059020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34568357467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5424427986145</t>
+    <t xml:space="preserve">7.33631420135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23324918746948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83289670944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90785217285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50496530532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37379169464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12081480026245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28009653091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98027229309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93342542648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06459856033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0271201133728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34568309783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54244232177734</t>
   </si>
   <si>
     <t xml:space="preserve">8.19830703735352</t>
@@ -1049,28 +1049,28 @@
     <t xml:space="preserve">8.2170467376709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65194225311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46116161346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53747367858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68056201934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77595138549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84272575378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825622558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6614818572998</t>
+    <t xml:space="preserve">8.65194320678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46116256713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53747463226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68056106567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77595233917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8427267074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825527191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66148281097412</t>
   </si>
   <si>
     <t xml:space="preserve">8.49931812286377</t>
@@ -1082,16 +1082,16 @@
     <t xml:space="preserve">8.39438915252686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60424900054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48977851867676</t>
+    <t xml:space="preserve">8.604248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48977947235107</t>
   </si>
   <si>
     <t xml:space="preserve">8.29899787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12729358673096</t>
+    <t xml:space="preserve">8.12729454040527</t>
   </si>
   <si>
     <t xml:space="preserve">7.89835643768311</t>
@@ -1112,19 +1112,19 @@
     <t xml:space="preserve">8.06052017211914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07959842681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07005977630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92697334289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98420810699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30853748321533</t>
+    <t xml:space="preserve">8.07959938049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07005882263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92697429656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98420858383179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30853652954102</t>
   </si>
   <si>
     <t xml:space="preserve">8.26084136962891</t>
@@ -1133,13 +1133,13 @@
     <t xml:space="preserve">8.27038097381592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18452930450439</t>
+    <t xml:space="preserve">8.18452835083008</t>
   </si>
   <si>
     <t xml:space="preserve">8.03190326690674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96512985229492</t>
+    <t xml:space="preserve">7.96513080596924</t>
   </si>
   <si>
     <t xml:space="preserve">7.86019992828369</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">7.91743516921997</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76480960845947</t>
+    <t xml:space="preserve">7.76481008529663</t>
   </si>
   <si>
     <t xml:space="preserve">7.72665309906006</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">7.63126230239868</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65987873077393</t>
+    <t xml:space="preserve">7.65987968444824</t>
   </si>
   <si>
     <t xml:space="preserve">8.16545104980469</t>
@@ -1175,22 +1175,22 @@
     <t xml:space="preserve">8.32761383056641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11775493621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9365119934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19406890869141</t>
+    <t xml:space="preserve">8.11775588989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93651247024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19406795501709</t>
   </si>
   <si>
     <t xml:space="preserve">8.2322244644165</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31807708740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15591239929199</t>
+    <t xml:space="preserve">8.31807518005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15591144561768</t>
   </si>
   <si>
     <t xml:space="preserve">8.22268486022949</t>
@@ -1199,16 +1199,16 @@
     <t xml:space="preserve">8.25130176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35623264312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2417631149292</t>
+    <t xml:space="preserve">8.35623168945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24176406860352</t>
   </si>
   <si>
     <t xml:space="preserve">8.34669303894043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95559072494507</t>
+    <t xml:space="preserve">7.95559167861938</t>
   </si>
   <si>
     <t xml:space="preserve">7.77434825897217</t>
@@ -1220,10 +1220,10 @@
     <t xml:space="preserve">7.97466850280762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01282501220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05098056793213</t>
+    <t xml:space="preserve">8.01282596588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05098152160645</t>
   </si>
   <si>
     <t xml:space="preserve">7.67895746231079</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">7.73619174957275</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6980357170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5167932510376</t>
+    <t xml:space="preserve">7.69803524017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51679372787476</t>
   </si>
   <si>
     <t xml:space="preserve">7.59310626983643</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">7.62172269821167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52633237838745</t>
+    <t xml:space="preserve">7.52633190155029</t>
   </si>
   <si>
     <t xml:space="preserve">7.34508991241455</t>
@@ -1262,25 +1262,25 @@
     <t xml:space="preserve">7.18292570114136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14476919174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12569093704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23062086105347</t>
+    <t xml:space="preserve">7.14476871490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12569046020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23062133789062</t>
   </si>
   <si>
     <t xml:space="preserve">7.1543083190918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24969911575317</t>
+    <t xml:space="preserve">7.24969863891602</t>
   </si>
   <si>
     <t xml:space="preserve">7.24016046524048</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46909761428833</t>
+    <t xml:space="preserve">7.46909809112549</t>
   </si>
   <si>
     <t xml:space="preserve">7.41186332702637</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">7.45001983642578</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28785562515259</t>
+    <t xml:space="preserve">7.28785514831543</t>
   </si>
   <si>
     <t xml:space="preserve">7.39278507232666</t>
@@ -1304,25 +1304,25 @@
     <t xml:space="preserve">7.90789556503296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94605112075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45955848693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70757436752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87927865982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99374723434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75527048110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81250476837158</t>
+    <t xml:space="preserve">7.94605159759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45955896377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70757484436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8792781829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99374771118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75527000427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81250381469727</t>
   </si>
   <si>
     <t xml:space="preserve">7.79342699050903</t>
@@ -1331,16 +1331,16 @@
     <t xml:space="preserve">7.80296611785889</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85066032409668</t>
+    <t xml:space="preserve">7.85065984725952</t>
   </si>
   <si>
     <t xml:space="preserve">7.74573087692261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83158254623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66941833496094</t>
+    <t xml:space="preserve">7.83158302307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66941785812378</t>
   </si>
   <si>
     <t xml:space="preserve">7.60264492034912</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">7.58356666564941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88881778717041</t>
+    <t xml:space="preserve">7.88881826400757</t>
   </si>
   <si>
     <t xml:space="preserve">8.00328636169434</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">7.27831649780273</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08753442764282</t>
+    <t xml:space="preserve">7.08753490447998</t>
   </si>
   <si>
     <t xml:space="preserve">7.05891799926758</t>
@@ -1376,10 +1376,10 @@
     <t xml:space="preserve">7.50372648239136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98721361160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02589321136475</t>
+    <t xml:space="preserve">7.98721408843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02589225769043</t>
   </si>
   <si>
     <t xml:space="preserve">8.04523086547852</t>
@@ -1391,25 +1391,25 @@
     <t xml:space="preserve">8.07424163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12259006500244</t>
+    <t xml:space="preserve">8.12258911132812</t>
   </si>
   <si>
     <t xml:space="preserve">8.05490112304688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94853448867798</t>
+    <t xml:space="preserve">7.94853496551514</t>
   </si>
   <si>
     <t xml:space="preserve">8.06457138061523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08391094207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97754383087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93886423110962</t>
+    <t xml:space="preserve">8.08390998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97754430770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93886518478394</t>
   </si>
   <si>
     <t xml:space="preserve">7.79381895065308</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">7.68745088577271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63910245895386</t>
+    <t xml:space="preserve">7.63910293579102</t>
   </si>
   <si>
     <t xml:space="preserve">7.73579978942871</t>
@@ -1436,10 +1436,10 @@
     <t xml:space="preserve">7.90985584259033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85183715820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83249807357788</t>
+    <t xml:space="preserve">7.85183668136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83249759674072</t>
   </si>
   <si>
     <t xml:space="preserve">7.81315755844116</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">7.80348825454712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78414869308472</t>
+    <t xml:space="preserve">7.78414916992188</t>
   </si>
   <si>
     <t xml:space="preserve">7.6681113243103</t>
@@ -1460,13 +1460,13 @@
     <t xml:space="preserve">7.71646022796631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75514030456543</t>
+    <t xml:space="preserve">7.75513982772827</t>
   </si>
   <si>
     <t xml:space="preserve">7.74547004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86150646209717</t>
+    <t xml:space="preserve">7.86150693893433</t>
   </si>
   <si>
     <t xml:space="preserve">7.89051580429077</t>
@@ -1484,10 +1484,10 @@
     <t xml:space="preserve">8.09358024597168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1322603225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15159893035889</t>
+    <t xml:space="preserve">8.13225936889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1515998840332</t>
   </si>
   <si>
     <t xml:space="preserve">8.1129207611084</t>
@@ -1496,10 +1496,10 @@
     <t xml:space="preserve">8.03556251525879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92919540405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69712114334106</t>
+    <t xml:space="preserve">7.92919492721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69712066650391</t>
   </si>
   <si>
     <t xml:space="preserve">7.60042381286621</t>
@@ -1508,10 +1508,10 @@
     <t xml:space="preserve">7.88084602355957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55207490921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40702867507935</t>
+    <t xml:space="preserve">7.55207443237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40702819824219</t>
   </si>
   <si>
     <t xml:space="preserve">7.34900999069214</t>
@@ -1520,16 +1520,16 @@
     <t xml:space="preserve">7.37801933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43603801727295</t>
+    <t xml:space="preserve">7.43603754043579</t>
   </si>
   <si>
     <t xml:space="preserve">7.41669797897339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5230655670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36834907531738</t>
+    <t xml:space="preserve">7.52306604385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36834955215454</t>
   </si>
   <si>
     <t xml:space="preserve">7.542405128479</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">7.4843864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70679092407227</t>
+    <t xml:space="preserve">7.70679044723511</t>
   </si>
   <si>
     <t xml:space="preserve">7.64877223968506</t>
@@ -1556,10 +1556,10 @@
     <t xml:space="preserve">7.59075355529785</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95820331573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96787357330322</t>
+    <t xml:space="preserve">7.95820426940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96787405014038</t>
   </si>
   <si>
     <t xml:space="preserve">7.90018606185913</t>
@@ -1577,10 +1577,10 @@
     <t xml:space="preserve">8.19027900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29664516448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45136070251465</t>
+    <t xml:space="preserve">8.29664611816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45136165618896</t>
   </si>
   <si>
     <t xml:space="preserve">8.48037147521973</t>
@@ -1607,19 +1607,19 @@
     <t xml:space="preserve">8.50938034057617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42235279083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54805850982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55772876739502</t>
+    <t xml:space="preserve">8.4223518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54805946350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55772972106934</t>
   </si>
   <si>
     <t xml:space="preserve">8.52871990203857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68343544006348</t>
+    <t xml:space="preserve">8.68343448638916</t>
   </si>
   <si>
     <t xml:space="preserve">8.76079368591309</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">8.65442562103271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75112342834473</t>
+    <t xml:space="preserve">8.75112438201904</t>
   </si>
   <si>
     <t xml:space="preserve">8.70277500152588</t>
@@ -1652,10 +1652,10 @@
     <t xml:space="preserve">8.63508701324463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32565498352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31598567962646</t>
+    <t xml:space="preserve">8.32565402984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31598472595215</t>
   </si>
   <si>
     <t xml:space="preserve">8.30631542205811</t>
@@ -62630,7 +62630,7 @@
     </row>
     <row r="2311">
       <c r="A2311" s="1" t="n">
-        <v>45980.6909953704</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B2311" t="n">
         <v>45124</v>
@@ -62651,6 +62651,32 @@
         <v>739</v>
       </c>
       <c r="H2311" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2312">
+      <c r="A2312" s="1" t="n">
+        <v>45981.6912152778</v>
+      </c>
+      <c r="B2312" t="n">
+        <v>46124</v>
+      </c>
+      <c r="C2312" t="n">
+        <v>9.15999984741211</v>
+      </c>
+      <c r="D2312" t="n">
+        <v>9</v>
+      </c>
+      <c r="E2312" t="n">
+        <v>9.11999988555908</v>
+      </c>
+      <c r="F2312" t="n">
+        <v>9.03999996185303</v>
+      </c>
+      <c r="G2312" t="s">
+        <v>739</v>
+      </c>
+      <c r="H2312" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="741">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="742">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07642269134521</t>
+    <t xml:space="preserve">9.0764217376709</t>
   </si>
   <si>
     <t xml:space="preserve">FF.MI</t>
@@ -47,46 +47,46 @@
     <t xml:space="preserve">8.98565769195557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08549785614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24887371063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09457397460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12180328369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03103923797607</t>
+    <t xml:space="preserve">9.08549880981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24887275695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09457492828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12180423736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03104019165039</t>
   </si>
   <si>
     <t xml:space="preserve">8.95388984680176</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89943218231201</t>
+    <t xml:space="preserve">8.8994312286377</t>
   </si>
   <si>
     <t xml:space="preserve">8.89489364624023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84951210021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85858726501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87674045562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76782321929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86766529083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04919338226318</t>
+    <t xml:space="preserve">8.84951019287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85858631134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87673950195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.767822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8676643371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04919242858887</t>
   </si>
   <si>
     <t xml:space="preserve">9.23072147369385</t>
@@ -98,19 +98,19 @@
     <t xml:space="preserve">8.96750450134277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91304588317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92212295532227</t>
+    <t xml:space="preserve">8.91304683685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92212390899658</t>
   </si>
   <si>
     <t xml:space="preserve">9.00380992889404</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15810871124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16718673706055</t>
+    <t xml:space="preserve">9.15811061859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16718769073486</t>
   </si>
   <si>
     <t xml:space="preserve">9.43947792053223</t>
@@ -125,19 +125,19 @@
     <t xml:space="preserve">9.80253601074219</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71177291870117</t>
+    <t xml:space="preserve">9.71177196502686</t>
   </si>
   <si>
     <t xml:space="preserve">9.56654930114746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58470153808594</t>
+    <t xml:space="preserve">9.58470058441162</t>
   </si>
   <si>
     <t xml:space="preserve">9.57562446594238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53024291992188</t>
+    <t xml:space="preserve">9.53024196624756</t>
   </si>
   <si>
     <t xml:space="preserve">9.50301361083984</t>
@@ -146,25 +146,25 @@
     <t xml:space="preserve">9.60285377502441</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63916015625</t>
+    <t xml:space="preserve">9.63915920257568</t>
   </si>
   <si>
     <t xml:space="preserve">9.79345893859863</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95683479309082</t>
+    <t xml:space="preserve">9.95683574676514</t>
   </si>
   <si>
     <t xml:space="preserve">9.93868160247803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98406410217285</t>
+    <t xml:space="preserve">9.98406505584717</t>
   </si>
   <si>
     <t xml:space="preserve">9.73900127410889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76623058319092</t>
+    <t xml:space="preserve">9.7662296295166</t>
   </si>
   <si>
     <t xml:space="preserve">9.74807739257812</t>
@@ -173,16 +173,16 @@
     <t xml:space="preserve">9.75715255737305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64823722839355</t>
+    <t xml:space="preserve">9.64823627471924</t>
   </si>
   <si>
     <t xml:space="preserve">9.82068729400635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70269393920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72084712982178</t>
+    <t xml:space="preserve">9.7026948928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72084808349609</t>
   </si>
   <si>
     <t xml:space="preserve">9.67546558380127</t>
@@ -191,31 +191,31 @@
     <t xml:space="preserve">9.66638946533203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63008308410645</t>
+    <t xml:space="preserve">9.63008213043213</t>
   </si>
   <si>
     <t xml:space="preserve">9.65731239318848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68454074859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81161212921143</t>
+    <t xml:space="preserve">9.68454265594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81161308288574</t>
   </si>
   <si>
     <t xml:space="preserve">9.8297643661499</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84791851043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83884239196777</t>
+    <t xml:space="preserve">9.8479175567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83884143829346</t>
   </si>
   <si>
     <t xml:space="preserve">9.72992420196533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78438186645508</t>
+    <t xml:space="preserve">9.78438091278076</t>
   </si>
   <si>
     <t xml:space="preserve">9.55747222900391</t>
@@ -227,13 +227,13 @@
     <t xml:space="preserve">9.33963680267334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27610206604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25795078277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19441509246826</t>
+    <t xml:space="preserve">9.27610301971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25794982910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19441699981689</t>
   </si>
   <si>
     <t xml:space="preserve">9.18533992767334</t>
@@ -242,13 +242,13 @@
     <t xml:space="preserve">9.41224956512451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22164344787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31240844726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26702785491943</t>
+    <t xml:space="preserve">9.22164440155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31240940093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2670259475708</t>
   </si>
   <si>
     <t xml:space="preserve">9.29425621032715</t>
@@ -257,19 +257,19 @@
     <t xml:space="preserve">9.28518009185791</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37594318389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36686706542969</t>
+    <t xml:space="preserve">9.37594413757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36686611175537</t>
   </si>
   <si>
     <t xml:space="preserve">9.38502025604248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45763206481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39409828186035</t>
+    <t xml:space="preserve">9.45763111114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3940954208374</t>
   </si>
   <si>
     <t xml:space="preserve">9.48486042022705</t>
@@ -284,34 +284,34 @@
     <t xml:space="preserve">9.47578430175781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23979759216309</t>
+    <t xml:space="preserve">9.23979663848877</t>
   </si>
   <si>
     <t xml:space="preserve">9.14903259277344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21256732940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20349311828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13088035583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13995742797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94027519226074</t>
+    <t xml:space="preserve">9.21256828308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20349407196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13088130950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1399564743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94027614593506</t>
   </si>
   <si>
     <t xml:space="preserve">8.8041296005249</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75874614715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66798400878906</t>
+    <t xml:space="preserve">8.75874519348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66798305511475</t>
   </si>
   <si>
     <t xml:space="preserve">8.62260150909424</t>
@@ -320,22 +320,22 @@
     <t xml:space="preserve">8.53183650970459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35030841827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16878032684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98725318908691</t>
+    <t xml:space="preserve">8.35030937194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16877937316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98725128173828</t>
   </si>
   <si>
     <t xml:space="preserve">8.03263473510742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12339782714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25954341888428</t>
+    <t xml:space="preserve">8.12339687347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25954437255859</t>
   </si>
   <si>
     <t xml:space="preserve">7.9418683052063</t>
@@ -353,37 +353,37 @@
     <t xml:space="preserve">8.5772180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71336460113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53202247619629</t>
+    <t xml:space="preserve">8.71336555480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53202342987061</t>
   </si>
   <si>
     <t xml:space="preserve">9.25706100463867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44036960601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16540718078613</t>
+    <t xml:space="preserve">9.44036865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16540813446045</t>
   </si>
   <si>
     <t xml:space="preserve">9.07375240325928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11957931518555</t>
+    <t xml:space="preserve">9.11957836151123</t>
   </si>
   <si>
     <t xml:space="preserve">8.98209953308105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02792549133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62367725372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80698585510254</t>
+    <t xml:space="preserve">9.02792644500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62367630004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80698490142822</t>
   </si>
   <si>
     <t xml:space="preserve">9.89863967895508</t>
@@ -392,13 +392,13 @@
     <t xml:space="preserve">9.9902925491333</t>
   </si>
   <si>
-    <t xml:space="preserve">10.173602104187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2652549743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3569107055664</t>
+    <t xml:space="preserve">10.1736011505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2652559280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3569097518921</t>
   </si>
   <si>
     <t xml:space="preserve">10.5402173995972</t>
@@ -410,58 +410,58 @@
     <t xml:space="preserve">10.8151807785034</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7235260009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9068326950073</t>
+    <t xml:space="preserve">10.7235250473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9068336486816</t>
   </si>
   <si>
     <t xml:space="preserve">10.9984884262085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.090142250061</t>
+    <t xml:space="preserve">11.0901432037354</t>
   </si>
   <si>
     <t xml:space="preserve">11.1817970275879</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734498977661</t>
+    <t xml:space="preserve">11.2734508514404</t>
   </si>
   <si>
     <t xml:space="preserve">11.4567584991455</t>
   </si>
   <si>
-    <t xml:space="preserve">11.365104675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4485626220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71533107757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79878997802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24886703491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21123313903809</t>
+    <t xml:space="preserve">11.3651037216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4485635757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71533298492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79879093170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24886608123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2112340927124</t>
   </si>
   <si>
     <t xml:space="preserve">9.30288696289062</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03708934783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39454078674316</t>
+    <t xml:space="preserve">9.03709030151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39454174041748</t>
   </si>
   <si>
     <t xml:space="preserve">9.76115798950195</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6695032119751</t>
+    <t xml:space="preserve">9.66950416564941</t>
   </si>
   <si>
     <t xml:space="preserve">9.57784938812256</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">10.0361194610596</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94446754455566</t>
+    <t xml:space="preserve">9.94446659088135</t>
   </si>
   <si>
     <t xml:space="preserve">9.82552433013916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73283100128174</t>
+    <t xml:space="preserve">9.73283004760742</t>
   </si>
   <si>
     <t xml:space="preserve">9.59379005432129</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96456432342529</t>
+    <t xml:space="preserve">9.96456527709961</t>
   </si>
   <si>
     <t xml:space="preserve">9.9182186126709</t>
@@ -494,40 +494,40 @@
     <t xml:space="preserve">10.010910987854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1036043167114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1499509811401</t>
+    <t xml:space="preserve">10.1036052703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1499519348145</t>
   </si>
   <si>
     <t xml:space="preserve">10.1962985992432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77917671203613</t>
+    <t xml:space="preserve">9.77917766571045</t>
   </si>
   <si>
     <t xml:space="preserve">9.87187099456787</t>
   </si>
   <si>
-    <t xml:space="preserve">10.057258605957</t>
+    <t xml:space="preserve">10.0572576522827</t>
   </si>
   <si>
     <t xml:space="preserve">10.2889919281006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4743795394897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2426443099976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3816862106323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68648242950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64013576507568</t>
+    <t xml:space="preserve">10.4743804931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2426452636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.381685256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68648338317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64013671875</t>
   </si>
   <si>
     <t xml:space="preserve">9.50109577178955</t>
@@ -539,16 +539,16 @@
     <t xml:space="preserve">9.23228359222412</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19520664215088</t>
+    <t xml:space="preserve">9.1952075958252</t>
   </si>
   <si>
     <t xml:space="preserve">9.25082302093506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26936340332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2137451171875</t>
+    <t xml:space="preserve">9.269362449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21374607086182</t>
   </si>
   <si>
     <t xml:space="preserve">9.04689693450928</t>
@@ -563,13 +563,13 @@
     <t xml:space="preserve">8.97274303436279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17666816711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02835750579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95420455932617</t>
+    <t xml:space="preserve">9.17666912078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02835845947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95420265197754</t>
   </si>
   <si>
     <t xml:space="preserve">8.71320056915283</t>
@@ -581,25 +581,25 @@
     <t xml:space="preserve">8.76881694793701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89858818054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93566608428955</t>
+    <t xml:space="preserve">8.89858722686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93566513061523</t>
   </si>
   <si>
     <t xml:space="preserve">10.3353385925293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9841947555542</t>
+    <t xml:space="preserve">10.9841938018799</t>
   </si>
   <si>
     <t xml:space="preserve">11.0305404663086</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2159280776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4940099716187</t>
+    <t xml:space="preserve">11.2159290313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4940090179443</t>
   </si>
   <si>
     <t xml:space="preserve">11.540355682373</t>
@@ -608,10 +608,10 @@
     <t xml:space="preserve">11.5867033004761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6330499649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7257423400879</t>
+    <t xml:space="preserve">11.6330490112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7257413864136</t>
   </si>
   <si>
     <t xml:space="preserve">11.9111299514771</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">11.9574766159058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1892108917236</t>
+    <t xml:space="preserve">12.1892099380493</t>
   </si>
   <si>
     <t xml:space="preserve">12.2819042205811</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">12.6488170623779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4614267349243</t>
+    <t xml:space="preserve">12.4614276885986</t>
   </si>
   <si>
     <t xml:space="preserve">12.4145793914795</t>
@@ -662,7 +662,7 @@
     <t xml:space="preserve">12.6956644058228</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2271900177002</t>
+    <t xml:space="preserve">12.2271890640259</t>
   </si>
   <si>
     <t xml:space="preserve">12.1803426742554</t>
@@ -671,19 +671,19 @@
     <t xml:space="preserve">12.3208837509155</t>
   </si>
   <si>
-    <t xml:space="preserve">12.274037361145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8362064361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7893581390381</t>
+    <t xml:space="preserve">12.2740383148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8362073898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7893590927124</t>
   </si>
   <si>
     <t xml:space="preserve">12.6019687652588</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9299011230469</t>
+    <t xml:space="preserve">12.9299020767212</t>
   </si>
   <si>
     <t xml:space="preserve">12.8830537796021</t>
@@ -692,16 +692,16 @@
     <t xml:space="preserve">13.0704441070557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.679461479187</t>
+    <t xml:space="preserve">13.6794605255127</t>
   </si>
   <si>
     <t xml:space="preserve">13.8668508529663</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0542411804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3353261947632</t>
+    <t xml:space="preserve">14.0542402267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3353252410889</t>
   </si>
   <si>
     <t xml:space="preserve">14.5695629119873</t>
@@ -722,10 +722,10 @@
     <t xml:space="preserve">15.1785802841187</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3191232681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8974952697754</t>
+    <t xml:space="preserve">15.3191242218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8974943161011</t>
   </si>
   <si>
     <t xml:space="preserve">15.4596652984619</t>
@@ -740,19 +740,19 @@
     <t xml:space="preserve">16.0686836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8650913238525</t>
+    <t xml:space="preserve">16.8650875091553</t>
   </si>
   <si>
     <t xml:space="preserve">17.0056324005127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7713928222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.193021774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0524806976318</t>
+    <t xml:space="preserve">16.7713947296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1930236816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0524787902832</t>
   </si>
   <si>
     <t xml:space="preserve">16.9587841033936</t>
@@ -761,19 +761,19 @@
     <t xml:space="preserve">16.7245464324951</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6308498382568</t>
+    <t xml:space="preserve">16.6308536529541</t>
   </si>
   <si>
     <t xml:space="preserve">16.5371551513672</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5840034484863</t>
+    <t xml:space="preserve">16.584005355835</t>
   </si>
   <si>
     <t xml:space="preserve">16.2092247009277</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2560729980469</t>
+    <t xml:space="preserve">16.2560749053955</t>
   </si>
   <si>
     <t xml:space="preserve">17.1461734771729</t>
@@ -782,37 +782,37 @@
     <t xml:space="preserve">16.396614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3029193878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8344430923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1155319213867</t>
+    <t xml:space="preserve">16.3029174804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8344440460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1155300140381</t>
   </si>
   <si>
     <t xml:space="preserve">16.0218353271484</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1623783111572</t>
+    <t xml:space="preserve">16.1623764038086</t>
   </si>
   <si>
     <t xml:space="preserve">15.974986076355</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7407493591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4434604644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9119358062744</t>
+    <t xml:space="preserve">15.7407503128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4434623718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9119338989258</t>
   </si>
   <si>
     <t xml:space="preserve">17.0993251800537</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6777000427246</t>
+    <t xml:space="preserve">16.677698135376</t>
   </si>
   <si>
     <t xml:space="preserve">16.818244934082</t>
@@ -821,13 +821,13 @@
     <t xml:space="preserve">15.272274017334</t>
   </si>
   <si>
-    <t xml:space="preserve">15.084885597229</t>
+    <t xml:space="preserve">15.0848846435547</t>
   </si>
   <si>
     <t xml:space="preserve">14.991189956665</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8038015365601</t>
+    <t xml:space="preserve">14.8037996292114</t>
   </si>
   <si>
     <t xml:space="preserve">14.4758682250977</t>
@@ -836,22 +836,22 @@
     <t xml:space="preserve">14.382173538208</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1010875701904</t>
+    <t xml:space="preserve">14.1010885238647</t>
   </si>
   <si>
     <t xml:space="preserve">14.288477897644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5227155685425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9605464935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2416305541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1947822570801</t>
+    <t xml:space="preserve">14.5227146148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9605445861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2416296005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1947832107544</t>
   </si>
   <si>
     <t xml:space="preserve">14.0073928833008</t>
@@ -872,127 +872,127 @@
     <t xml:space="preserve">13.7731552124023</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3515281677246</t>
+    <t xml:space="preserve">13.3515291213989</t>
   </si>
   <si>
     <t xml:space="preserve">13.3046817779541</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3983774185181</t>
+    <t xml:space="preserve">13.3983764648438</t>
   </si>
   <si>
     <t xml:space="preserve">13.0235967636108</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1172914505005</t>
+    <t xml:space="preserve">13.1172924041748</t>
   </si>
   <si>
     <t xml:space="preserve">12.976749420166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3677310943604</t>
+    <t xml:space="preserve">12.3677320480347</t>
   </si>
   <si>
     <t xml:space="preserve">12.0866470336914</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9929523468018</t>
+    <t xml:space="preserve">11.9929533004761</t>
   </si>
   <si>
     <t xml:space="preserve">11.8992576599121</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0397996902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1334943771362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4776296615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2433938980103</t>
+    <t xml:space="preserve">12.0397987365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1334934234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4776287078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2433929443359</t>
   </si>
   <si>
     <t xml:space="preserve">11.3839340209961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6650199890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4307823181152</t>
+    <t xml:space="preserve">11.6650190353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4307832717896</t>
   </si>
   <si>
     <t xml:space="preserve">10.9623079299927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7280712127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1965446472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.571325302124</t>
+    <t xml:space="preserve">10.7280702590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1965436935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5713243484497</t>
   </si>
   <si>
     <t xml:space="preserve">11.3370885848999</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2902402877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7118673324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7587146759033</t>
+    <t xml:space="preserve">11.2902393341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7118682861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.758713722229</t>
   </si>
   <si>
     <t xml:space="preserve">11.8055629730225</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0091552734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46318912506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3388500213623</t>
+    <t xml:space="preserve">11.0091543197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46319007873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33884906768799</t>
   </si>
   <si>
     <t xml:space="preserve">8.57308673858643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31074237823486</t>
+    <t xml:space="preserve">8.31074142456055</t>
   </si>
   <si>
     <t xml:space="preserve">8.45128345489502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61993503570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44191455841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32948017120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25452518463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43254566192627</t>
+    <t xml:space="preserve">8.61993408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44191360473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32948112487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25452423095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43254375457764</t>
   </si>
   <si>
     <t xml:space="preserve">8.47002220153809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32011032104492</t>
+    <t xml:space="preserve">8.32011127471924</t>
   </si>
   <si>
     <t xml:space="preserve">8.20767688751221</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0858736038208</t>
+    <t xml:space="preserve">8.08587265014648</t>
   </si>
   <si>
     <t xml:space="preserve">7.78605031967163</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">7.49559497833252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33631372451782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23324871063232</t>
+    <t xml:space="preserve">7.33631420135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23324918746948</t>
   </si>
   <si>
     <t xml:space="preserve">7.83289670944214</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90785264968872</t>
+    <t xml:space="preserve">7.90785217285156</t>
   </si>
   <si>
     <t xml:space="preserve">7.50496530532837</t>
@@ -1019,28 +1019,28 @@
     <t xml:space="preserve">7.37379169464111</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12081527709961</t>
+    <t xml:space="preserve">7.12081480026245</t>
   </si>
   <si>
     <t xml:space="preserve">7.28009653091431</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98027324676514</t>
+    <t xml:space="preserve">6.98027229309082</t>
   </si>
   <si>
     <t xml:space="preserve">6.93342542648315</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06459808349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02712059020996</t>
+    <t xml:space="preserve">7.06459856033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0271201133728</t>
   </si>
   <si>
     <t xml:space="preserve">7.34568309783936</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5424427986145</t>
+    <t xml:space="preserve">7.54244232177734</t>
   </si>
   <si>
     <t xml:space="preserve">8.19830703735352</t>
@@ -1055,19 +1055,19 @@
     <t xml:space="preserve">8.46116256713867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53747367858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68056201934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77595138549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84272575378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825622558594</t>
+    <t xml:space="preserve">8.53747463226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68056106567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77595233917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8427267074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825527191162</t>
   </si>
   <si>
     <t xml:space="preserve">8.66148281097412</t>
@@ -1082,10 +1082,10 @@
     <t xml:space="preserve">8.39438915252686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60424900054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48977851867676</t>
+    <t xml:space="preserve">8.604248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48977947235107</t>
   </si>
   <si>
     <t xml:space="preserve">8.29899787902832</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">7.89835643768311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10821723937988</t>
+    <t xml:space="preserve">8.10821628570557</t>
   </si>
   <si>
     <t xml:space="preserve">7.84112215042114</t>
@@ -1115,34 +1115,34 @@
     <t xml:space="preserve">8.07959938049316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07005977630615</t>
+    <t xml:space="preserve">8.07005882263184</t>
   </si>
   <si>
     <t xml:space="preserve">7.92697429656982</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98420810699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30853748321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26084041595459</t>
+    <t xml:space="preserve">7.98420858383179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30853652954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26084136962891</t>
   </si>
   <si>
     <t xml:space="preserve">8.27038097381592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18452930450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03190422058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96512985229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86020040512085</t>
+    <t xml:space="preserve">8.18452835083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03190326690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96513080596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86019992828369</t>
   </si>
   <si>
     <t xml:space="preserve">7.86973905563354</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">7.91743516921997</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76480960845947</t>
+    <t xml:space="preserve">7.76481008529663</t>
   </si>
   <si>
     <t xml:space="preserve">7.72665309906006</t>
@@ -1166,19 +1166,19 @@
     <t xml:space="preserve">7.63126230239868</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65987920761108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16545009613037</t>
+    <t xml:space="preserve">7.65987968444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16545104980469</t>
   </si>
   <si>
     <t xml:space="preserve">8.32761383056641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11775493621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9365119934082</t>
+    <t xml:space="preserve">8.11775588989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93651247024536</t>
   </si>
   <si>
     <t xml:space="preserve">8.19406795501709</t>
@@ -1187,10 +1187,10 @@
     <t xml:space="preserve">8.2322244644165</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31807613372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15591239929199</t>
+    <t xml:space="preserve">8.31807518005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15591144561768</t>
   </si>
   <si>
     <t xml:space="preserve">8.22268486022949</t>
@@ -1199,10 +1199,10 @@
     <t xml:space="preserve">8.25130176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35623264312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2417631149292</t>
+    <t xml:space="preserve">8.35623168945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24176406860352</t>
   </si>
   <si>
     <t xml:space="preserve">8.34669303894043</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">7.97466850280762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01282501220703</t>
+    <t xml:space="preserve">8.01282596588135</t>
   </si>
   <si>
     <t xml:space="preserve">8.05098152160645</t>
@@ -1229,13 +1229,13 @@
     <t xml:space="preserve">7.67895746231079</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73619222640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6980357170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5167932510376</t>
+    <t xml:space="preserve">7.73619174957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69803524017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51679372787476</t>
   </si>
   <si>
     <t xml:space="preserve">7.59310626983643</t>
@@ -1259,16 +1259,16 @@
     <t xml:space="preserve">7.20200395584106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18292617797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14476919174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12569093704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23062086105347</t>
+    <t xml:space="preserve">7.18292570114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14476871490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12569046020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23062133789062</t>
   </si>
   <si>
     <t xml:space="preserve">7.1543083190918</t>
@@ -1277,7 +1277,7 @@
     <t xml:space="preserve">7.24969863891602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24015998840332</t>
+    <t xml:space="preserve">7.24016046524048</t>
   </si>
   <si>
     <t xml:space="preserve">7.46909809112549</t>
@@ -1298,13 +1298,13 @@
     <t xml:space="preserve">7.3355507850647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61218452453613</t>
+    <t xml:space="preserve">7.61218404769897</t>
   </si>
   <si>
     <t xml:space="preserve">7.90789556503296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94605112075806</t>
+    <t xml:space="preserve">7.94605159759521</t>
   </si>
   <si>
     <t xml:space="preserve">7.45955896377563</t>
@@ -1316,22 +1316,22 @@
     <t xml:space="preserve">7.8792781829834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99374723434448</t>
+    <t xml:space="preserve">7.99374771118164</t>
   </si>
   <si>
     <t xml:space="preserve">7.75527000427246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81250429153442</t>
+    <t xml:space="preserve">7.81250381469727</t>
   </si>
   <si>
     <t xml:space="preserve">7.79342699050903</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80296564102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85066032409668</t>
+    <t xml:space="preserve">7.80296611785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85065984725952</t>
   </si>
   <si>
     <t xml:space="preserve">7.74573087692261</t>
@@ -1340,22 +1340,22 @@
     <t xml:space="preserve">7.83158302307129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66941833496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60264444351196</t>
+    <t xml:space="preserve">7.66941785812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60264492034912</t>
   </si>
   <si>
     <t xml:space="preserve">7.58356666564941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88881778717041</t>
+    <t xml:space="preserve">7.88881826400757</t>
   </si>
   <si>
     <t xml:space="preserve">8.00328636169434</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78388690948486</t>
+    <t xml:space="preserve">7.78388738632202</t>
   </si>
   <si>
     <t xml:space="preserve">7.3641676902771</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">7.27831649780273</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08753442764282</t>
+    <t xml:space="preserve">7.08753490447998</t>
   </si>
   <si>
     <t xml:space="preserve">7.05891799926758</t>
@@ -1376,10 +1376,10 @@
     <t xml:space="preserve">7.50372648239136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98721361160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02589321136475</t>
+    <t xml:space="preserve">7.98721408843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02589225769043</t>
   </si>
   <si>
     <t xml:space="preserve">8.04523086547852</t>
@@ -1391,25 +1391,25 @@
     <t xml:space="preserve">8.07424163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12259006500244</t>
+    <t xml:space="preserve">8.12258911132812</t>
   </si>
   <si>
     <t xml:space="preserve">8.05490112304688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94853448867798</t>
+    <t xml:space="preserve">7.94853496551514</t>
   </si>
   <si>
     <t xml:space="preserve">8.06457138061523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08391094207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97754383087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93886423110962</t>
+    <t xml:space="preserve">8.08390998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97754430770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93886518478394</t>
   </si>
   <si>
     <t xml:space="preserve">7.79381895065308</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">7.68745088577271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63910245895386</t>
+    <t xml:space="preserve">7.63910293579102</t>
   </si>
   <si>
     <t xml:space="preserve">7.73579978942871</t>
@@ -1436,10 +1436,10 @@
     <t xml:space="preserve">7.90985584259033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85183715820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83249807357788</t>
+    <t xml:space="preserve">7.85183668136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83249759674072</t>
   </si>
   <si>
     <t xml:space="preserve">7.81315755844116</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">7.80348825454712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78414869308472</t>
+    <t xml:space="preserve">7.78414916992188</t>
   </si>
   <si>
     <t xml:space="preserve">7.6681113243103</t>
@@ -1460,13 +1460,13 @@
     <t xml:space="preserve">7.71646022796631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75514030456543</t>
+    <t xml:space="preserve">7.75513982772827</t>
   </si>
   <si>
     <t xml:space="preserve">7.74547004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86150646209717</t>
+    <t xml:space="preserve">7.86150693893433</t>
   </si>
   <si>
     <t xml:space="preserve">7.89051580429077</t>
@@ -1484,10 +1484,10 @@
     <t xml:space="preserve">8.09358024597168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1322603225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15159893035889</t>
+    <t xml:space="preserve">8.13225936889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1515998840332</t>
   </si>
   <si>
     <t xml:space="preserve">8.1129207611084</t>
@@ -1496,10 +1496,10 @@
     <t xml:space="preserve">8.03556251525879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92919540405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69712114334106</t>
+    <t xml:space="preserve">7.92919492721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69712066650391</t>
   </si>
   <si>
     <t xml:space="preserve">7.60042381286621</t>
@@ -1508,10 +1508,10 @@
     <t xml:space="preserve">7.88084602355957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55207490921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40702867507935</t>
+    <t xml:space="preserve">7.55207443237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40702819824219</t>
   </si>
   <si>
     <t xml:space="preserve">7.34900999069214</t>
@@ -1520,16 +1520,16 @@
     <t xml:space="preserve">7.37801933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43603801727295</t>
+    <t xml:space="preserve">7.43603754043579</t>
   </si>
   <si>
     <t xml:space="preserve">7.41669797897339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5230655670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36834907531738</t>
+    <t xml:space="preserve">7.52306604385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36834955215454</t>
   </si>
   <si>
     <t xml:space="preserve">7.542405128479</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">7.4843864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70679092407227</t>
+    <t xml:space="preserve">7.70679044723511</t>
   </si>
   <si>
     <t xml:space="preserve">7.64877223968506</t>
@@ -1556,10 +1556,10 @@
     <t xml:space="preserve">7.59075355529785</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95820331573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96787357330322</t>
+    <t xml:space="preserve">7.95820426940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96787405014038</t>
   </si>
   <si>
     <t xml:space="preserve">7.90018606185913</t>
@@ -1577,10 +1577,10 @@
     <t xml:space="preserve">8.19027900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29664516448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45136070251465</t>
+    <t xml:space="preserve">8.29664611816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45136165618896</t>
   </si>
   <si>
     <t xml:space="preserve">8.48037147521973</t>
@@ -1607,19 +1607,19 @@
     <t xml:space="preserve">8.50938034057617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42235279083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54805850982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55772876739502</t>
+    <t xml:space="preserve">8.4223518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54805946350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55772972106934</t>
   </si>
   <si>
     <t xml:space="preserve">8.52871990203857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68343544006348</t>
+    <t xml:space="preserve">8.68343448638916</t>
   </si>
   <si>
     <t xml:space="preserve">8.76079368591309</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">8.65442562103271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75112342834473</t>
+    <t xml:space="preserve">8.75112438201904</t>
   </si>
   <si>
     <t xml:space="preserve">8.70277500152588</t>
@@ -1652,10 +1652,10 @@
     <t xml:space="preserve">8.63508701324463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32565498352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31598567962646</t>
+    <t xml:space="preserve">8.32565402984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31598472595215</t>
   </si>
   <si>
     <t xml:space="preserve">8.30631542205811</t>
@@ -2235,6 +2235,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.07999992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5600004196167</t>
   </si>
 </sst>
 </file>
@@ -62711,7 +62714,7 @@
     </row>
     <row r="2314">
       <c r="A2314" s="1" t="n">
-        <v>45985.6912962963</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B2314" t="n">
         <v>24843</v>
@@ -62732,6 +62735,32 @@
         <v>735</v>
       </c>
       <c r="H2314" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2315">
+      <c r="A2315" s="1" t="n">
+        <v>45986.6912847222</v>
+      </c>
+      <c r="B2315" t="n">
+        <v>27799</v>
+      </c>
+      <c r="C2315" t="n">
+        <v>9.47999954223633</v>
+      </c>
+      <c r="D2315" t="n">
+        <v>9.18000030517578</v>
+      </c>
+      <c r="E2315" t="n">
+        <v>9.30000019073486</v>
+      </c>
+      <c r="F2315" t="n">
+        <v>9.5600004196167</v>
+      </c>
+      <c r="G2315" t="s">
+        <v>741</v>
+      </c>
+      <c r="H2315" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="742">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="743">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,19 +44,19 @@
     <t xml:space="preserve">FF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98565769195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08549880981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24887275695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09457492828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12180423736572</t>
+    <t xml:space="preserve">8.98565673828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08549785614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24887466430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09457588195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12180328369141</t>
   </si>
   <si>
     <t xml:space="preserve">9.03104019165039</t>
@@ -68,52 +68,52 @@
     <t xml:space="preserve">8.8994312286377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89489364624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84951019287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85858631134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87673950195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.767822265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8676643371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04919242858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23072147369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11272811889648</t>
+    <t xml:space="preserve">8.89489269256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84951114654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85858917236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87674045562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76782417297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86766529083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04919338226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23072242736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1127290725708</t>
   </si>
   <si>
     <t xml:space="preserve">8.96750450134277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91304683685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92212390899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00380992889404</t>
+    <t xml:space="preserve">8.91304588317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92212295532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00381088256836</t>
   </si>
   <si>
     <t xml:space="preserve">9.15811061859131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16718769073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43947792053223</t>
+    <t xml:space="preserve">9.16718578338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43947887420654</t>
   </si>
   <si>
     <t xml:space="preserve">9.54839611053467</t>
@@ -128,25 +128,25 @@
     <t xml:space="preserve">9.71177196502686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56654930114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58470058441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57562446594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53024196624756</t>
+    <t xml:space="preserve">9.56654834747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58470153808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5756254196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53024387359619</t>
   </si>
   <si>
     <t xml:space="preserve">9.50301361083984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60285377502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63915920257568</t>
+    <t xml:space="preserve">9.60285472869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63916015625</t>
   </si>
   <si>
     <t xml:space="preserve">9.79345893859863</t>
@@ -155,28 +155,28 @@
     <t xml:space="preserve">9.95683574676514</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93868160247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98406505584717</t>
+    <t xml:space="preserve">9.93868255615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98406410217285</t>
   </si>
   <si>
     <t xml:space="preserve">9.73900127410889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7662296295166</t>
+    <t xml:space="preserve">9.76623058319092</t>
   </si>
   <si>
     <t xml:space="preserve">9.74807739257812</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75715255737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64823627471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82068729400635</t>
+    <t xml:space="preserve">9.75715351104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64823818206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82068920135498</t>
   </si>
   <si>
     <t xml:space="preserve">9.7026948928833</t>
@@ -185,13 +185,13 @@
     <t xml:space="preserve">9.72084808349609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67546558380127</t>
+    <t xml:space="preserve">9.67546463012695</t>
   </si>
   <si>
     <t xml:space="preserve">9.66638946533203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63008213043213</t>
+    <t xml:space="preserve">9.63008308410645</t>
   </si>
   <si>
     <t xml:space="preserve">9.65731239318848</t>
@@ -200,55 +200,55 @@
     <t xml:space="preserve">9.68454265594482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81161308288574</t>
+    <t xml:space="preserve">9.81161212921143</t>
   </si>
   <si>
     <t xml:space="preserve">9.8297643661499</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8479175567627</t>
+    <t xml:space="preserve">9.84791851043701</t>
   </si>
   <si>
     <t xml:space="preserve">9.83884143829346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72992420196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78438091278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55747222900391</t>
+    <t xml:space="preserve">9.72992515563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78438282012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55747318267822</t>
   </si>
   <si>
     <t xml:space="preserve">9.34871482849121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33963680267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27610301971436</t>
+    <t xml:space="preserve">9.33963871002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27610397338867</t>
   </si>
   <si>
     <t xml:space="preserve">9.25794982910156</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19441699981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18533992767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41224956512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22164440155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31240940093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2670259475708</t>
+    <t xml:space="preserve">9.19441604614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18534088134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41225051879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22164344787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31240844726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26702690124512</t>
   </si>
   <si>
     <t xml:space="preserve">9.29425621032715</t>
@@ -260,16 +260,16 @@
     <t xml:space="preserve">9.37594413757324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36686611175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38502025604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45763111114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3940954208374</t>
+    <t xml:space="preserve">9.36686897277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3850212097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45763206481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39409732818604</t>
   </si>
   <si>
     <t xml:space="preserve">9.48486042022705</t>
@@ -278,85 +278,85 @@
     <t xml:space="preserve">9.49393749237061</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44855499267578</t>
+    <t xml:space="preserve">9.44855403900146</t>
   </si>
   <si>
     <t xml:space="preserve">9.47578430175781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23979663848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14903259277344</t>
+    <t xml:space="preserve">9.2397985458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14903354644775</t>
   </si>
   <si>
     <t xml:space="preserve">9.21256828308105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20349407196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13088130950928</t>
+    <t xml:space="preserve">9.20349311828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13088035583496</t>
   </si>
   <si>
     <t xml:space="preserve">9.1399564743042</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94027614593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8041296005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75874519348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66798305511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62260150909424</t>
+    <t xml:space="preserve">8.94027519226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80412864685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75874614715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66798400878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62260055541992</t>
   </si>
   <si>
     <t xml:space="preserve">8.53183650970459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35030937194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16877937316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98725128173828</t>
+    <t xml:space="preserve">8.35030841827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16878128051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98725271224976</t>
   </si>
   <si>
     <t xml:space="preserve">8.03263473510742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12339687347412</t>
+    <t xml:space="preserve">8.12339782714844</t>
   </si>
   <si>
     <t xml:space="preserve">8.25954437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9418683052063</t>
+    <t xml:space="preserve">7.94187021255493</t>
   </si>
   <si>
     <t xml:space="preserve">8.3049259185791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21416187286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39568996429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5772180557251</t>
+    <t xml:space="preserve">8.21416282653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39569091796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57721900939941</t>
   </si>
   <si>
     <t xml:space="preserve">8.71336555480957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53202342987061</t>
+    <t xml:space="preserve">9.53202152252197</t>
   </si>
   <si>
     <t xml:space="preserve">9.25706100463867</t>
@@ -365,34 +365,34 @@
     <t xml:space="preserve">9.44036865234375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16540813446045</t>
+    <t xml:space="preserve">9.16540622711182</t>
   </si>
   <si>
     <t xml:space="preserve">9.07375240325928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11957836151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98209953308105</t>
+    <t xml:space="preserve">9.11957931518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98209857940674</t>
   </si>
   <si>
     <t xml:space="preserve">9.02792644500732</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62367630004883</t>
+    <t xml:space="preserve">9.62367725372314</t>
   </si>
   <si>
     <t xml:space="preserve">9.80698490142822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89863967895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9902925491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1736011505127</t>
+    <t xml:space="preserve">9.89863872528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99029350280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.173602104187</t>
   </si>
   <si>
     <t xml:space="preserve">10.2652559280396</t>
@@ -404,28 +404,28 @@
     <t xml:space="preserve">10.5402173995972</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6318731307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8151807785034</t>
+    <t xml:space="preserve">10.6318712234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8151798248291</t>
   </si>
   <si>
     <t xml:space="preserve">10.7235250473022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9068336486816</t>
+    <t xml:space="preserve">10.906834602356</t>
   </si>
   <si>
     <t xml:space="preserve">10.9984884262085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0901432037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1817970275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2734508514404</t>
+    <t xml:space="preserve">11.0901412963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1817960739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2734498977661</t>
   </si>
   <si>
     <t xml:space="preserve">11.4567584991455</t>
@@ -434,10 +434,10 @@
     <t xml:space="preserve">11.3651037216187</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4485635757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71533298492432</t>
+    <t xml:space="preserve">10.4485626220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71533107757568</t>
   </si>
   <si>
     <t xml:space="preserve">8.79879093170166</t>
@@ -446,22 +446,22 @@
     <t xml:space="preserve">8.24886608123779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2112340927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30288696289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03709030151367</t>
+    <t xml:space="preserve">9.21123504638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30288887023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03709125518799</t>
   </si>
   <si>
     <t xml:space="preserve">9.39454174041748</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76115798950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66950416564941</t>
+    <t xml:space="preserve">9.76115608215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6695032119751</t>
   </si>
   <si>
     <t xml:space="preserve">9.57784938812256</t>
@@ -470,22 +470,22 @@
     <t xml:space="preserve">10.0361194610596</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94446659088135</t>
+    <t xml:space="preserve">9.94446563720703</t>
   </si>
   <si>
     <t xml:space="preserve">9.82552433013916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73283004760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59379005432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96456527709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9182186126709</t>
+    <t xml:space="preserve">9.73283100128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59379100799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96456432342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91821765899658</t>
   </si>
   <si>
     <t xml:space="preserve">9.54744338989258</t>
@@ -497,46 +497,46 @@
     <t xml:space="preserve">10.1036052703857</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1499519348145</t>
+    <t xml:space="preserve">10.1499509811401</t>
   </si>
   <si>
     <t xml:space="preserve">10.1962985992432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77917766571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87187099456787</t>
+    <t xml:space="preserve">9.77917671203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87186908721924</t>
   </si>
   <si>
     <t xml:space="preserve">10.0572576522827</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2889919281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4743804931641</t>
+    <t xml:space="preserve">10.2889928817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4743795394897</t>
   </si>
   <si>
     <t xml:space="preserve">10.2426452636719</t>
   </si>
   <si>
-    <t xml:space="preserve">10.381685256958</t>
+    <t xml:space="preserve">10.3816862106323</t>
   </si>
   <si>
     <t xml:space="preserve">9.68648338317871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64013671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50109577178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31570911407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23228359222412</t>
+    <t xml:space="preserve">9.64013576507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50109672546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31571006774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23228454589844</t>
   </si>
   <si>
     <t xml:space="preserve">9.1952075958252</t>
@@ -545,43 +545,43 @@
     <t xml:space="preserve">9.25082302093506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.269362449646</t>
+    <t xml:space="preserve">9.26936149597168</t>
   </si>
   <si>
     <t xml:space="preserve">9.21374607086182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04689693450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12105369567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0654354095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97274303436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17666912078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02835845947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95420265197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71320056915283</t>
+    <t xml:space="preserve">9.04689788818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12105274200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06543445587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97274208068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17666816711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02835941314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95420360565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71319961547852</t>
   </si>
   <si>
     <t xml:space="preserve">8.99128150939941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76881694793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89858722686768</t>
+    <t xml:space="preserve">8.76881790161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89858818054199</t>
   </si>
   <si>
     <t xml:space="preserve">8.93566513061523</t>
@@ -590,19 +590,19 @@
     <t xml:space="preserve">10.3353385925293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9841938018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0305404663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2159290313721</t>
+    <t xml:space="preserve">10.9841947555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0305414199829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2159280776978</t>
   </si>
   <si>
     <t xml:space="preserve">11.4940090179443</t>
   </si>
   <si>
-    <t xml:space="preserve">11.540355682373</t>
+    <t xml:space="preserve">11.5403547286987</t>
   </si>
   <si>
     <t xml:space="preserve">11.5867033004761</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">11.6330490112305</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7257413864136</t>
+    <t xml:space="preserve">11.7257432937622</t>
   </si>
   <si>
     <t xml:space="preserve">11.9111299514771</t>
@@ -620,19 +620,19 @@
     <t xml:space="preserve">11.9574766159058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1892099380493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2819042205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3745985031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5136394500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3282518386841</t>
+    <t xml:space="preserve">12.1892108917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2819051742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3745994567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5136384963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3282527923584</t>
   </si>
   <si>
     <t xml:space="preserve">12.1428651809692</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">12.0965175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5551223754883</t>
+    <t xml:space="preserve">12.555121421814</t>
   </si>
   <si>
     <t xml:space="preserve">12.5082750320435</t>
@@ -662,7 +662,7 @@
     <t xml:space="preserve">12.6956644058228</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2271890640259</t>
+    <t xml:space="preserve">12.2271900177002</t>
   </si>
   <si>
     <t xml:space="preserve">12.1803426742554</t>
@@ -674,13 +674,13 @@
     <t xml:space="preserve">12.2740383148193</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8362073898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7893590927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6019687652588</t>
+    <t xml:space="preserve">12.8362064361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7893581390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6019697189331</t>
   </si>
   <si>
     <t xml:space="preserve">12.9299020767212</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">13.0704441070557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6794605255127</t>
+    <t xml:space="preserve">13.679461479187</t>
   </si>
   <si>
     <t xml:space="preserve">13.8668508529663</t>
@@ -704,10 +704,10 @@
     <t xml:space="preserve">14.3353252410889</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5695629119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2254276275635</t>
+    <t xml:space="preserve">14.5695638656616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2254285812378</t>
   </si>
   <si>
     <t xml:space="preserve">15.1317329406738</t>
@@ -716,31 +716,31 @@
     <t xml:space="preserve">14.7569532394409</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0380382537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1785802841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3191242218018</t>
+    <t xml:space="preserve">15.0380373001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.178581237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3191232681274</t>
   </si>
   <si>
     <t xml:space="preserve">14.8974943161011</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4596652984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4128179550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5533609390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0686836242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8650875091553</t>
+    <t xml:space="preserve">15.4596662521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4128189086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5533599853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0686817169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8650894165039</t>
   </si>
   <si>
     <t xml:space="preserve">17.0056324005127</t>
@@ -749,16 +749,16 @@
     <t xml:space="preserve">16.7713947296143</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1930236816406</t>
+    <t xml:space="preserve">17.193021774292</t>
   </si>
   <si>
     <t xml:space="preserve">17.0524787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9587841033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7245464324951</t>
+    <t xml:space="preserve">16.9587860107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7245483398438</t>
   </si>
   <si>
     <t xml:space="preserve">16.6308536529541</t>
@@ -770,13 +770,13 @@
     <t xml:space="preserve">16.584005355835</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2092247009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2560749053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1461734771729</t>
+    <t xml:space="preserve">16.2092227935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2560729980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1461715698242</t>
   </si>
   <si>
     <t xml:space="preserve">16.396614074707</t>
@@ -800,13 +800,13 @@
     <t xml:space="preserve">15.974986076355</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7407503128052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4434623718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9119338989258</t>
+    <t xml:space="preserve">15.7407484054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4434604644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9119358062744</t>
   </si>
   <si>
     <t xml:space="preserve">17.0993251800537</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">15.272274017334</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0848846435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.991189956665</t>
+    <t xml:space="preserve">15.084885597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9911909103394</t>
   </si>
   <si>
     <t xml:space="preserve">14.8037996292114</t>
@@ -842,22 +842,22 @@
     <t xml:space="preserve">14.288477897644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5227146148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9605445861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2416296005249</t>
+    <t xml:space="preserve">14.5227155685425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.960545539856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2416305541992</t>
   </si>
   <si>
     <t xml:space="preserve">14.1947832107544</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0073928833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7263078689575</t>
+    <t xml:space="preserve">14.0073938369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7263088226318</t>
   </si>
   <si>
     <t xml:space="preserve">14.1479358673096</t>
@@ -866,16 +866,16 @@
     <t xml:space="preserve">14.4290199279785</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6164102554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7731552124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3515291213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3046817779541</t>
+    <t xml:space="preserve">14.6164112091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7731561660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3515281677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3046808242798</t>
   </si>
   <si>
     <t xml:space="preserve">13.3983764648438</t>
@@ -893,10 +893,10 @@
     <t xml:space="preserve">12.3677320480347</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0866470336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9929533004761</t>
+    <t xml:space="preserve">12.0866460800171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9929523468018</t>
   </si>
   <si>
     <t xml:space="preserve">11.8992576599121</t>
@@ -905,61 +905,61 @@
     <t xml:space="preserve">12.0397987365723</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1334934234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4776287078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2433929443359</t>
+    <t xml:space="preserve">12.1334943771362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4776296615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2433938980103</t>
   </si>
   <si>
     <t xml:space="preserve">11.3839340209961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6650190353394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4307832717896</t>
+    <t xml:space="preserve">11.6650199890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4307823181152</t>
   </si>
   <si>
     <t xml:space="preserve">10.9623079299927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7280702590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1965436935425</t>
+    <t xml:space="preserve">10.7280712127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1965456008911</t>
   </si>
   <si>
     <t xml:space="preserve">11.5713243484497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3370885848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2902393341064</t>
+    <t xml:space="preserve">11.3370876312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2902402877808</t>
   </si>
   <si>
     <t xml:space="preserve">11.7118682861328</t>
   </si>
   <si>
-    <t xml:space="preserve">11.758713722229</t>
+    <t xml:space="preserve">11.7587156295776</t>
   </si>
   <si>
     <t xml:space="preserve">11.8055629730225</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0091543197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46319007873535</t>
+    <t xml:space="preserve">11.0091552734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46318912506104</t>
   </si>
   <si>
     <t xml:space="preserve">8.33884906768799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57308673858643</t>
+    <t xml:space="preserve">8.57308578491211</t>
   </si>
   <si>
     <t xml:space="preserve">8.31074142456055</t>
@@ -968,19 +968,19 @@
     <t xml:space="preserve">8.45128345489502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61993408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44191360473633</t>
+    <t xml:space="preserve">8.61993312835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44191455841064</t>
   </si>
   <si>
     <t xml:space="preserve">8.32948112487793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25452423095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43254375457764</t>
+    <t xml:space="preserve">8.25452327728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43254470825195</t>
   </si>
   <si>
     <t xml:space="preserve">8.47002220153809</t>
@@ -989,43 +989,43 @@
     <t xml:space="preserve">8.32011127471924</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20767688751221</t>
+    <t xml:space="preserve">8.20767784118652</t>
   </si>
   <si>
     <t xml:space="preserve">8.08587265014648</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78605031967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49559497833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33631420135498</t>
+    <t xml:space="preserve">7.78604936599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49559545516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33631372451782</t>
   </si>
   <si>
     <t xml:space="preserve">7.23324918746948</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83289670944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90785217285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50496530532837</t>
+    <t xml:space="preserve">7.83289623260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90785312652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50496482849121</t>
   </si>
   <si>
     <t xml:space="preserve">7.37379169464111</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12081480026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28009653091431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98027229309082</t>
+    <t xml:space="preserve">7.12081527709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28009700775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98027276992798</t>
   </si>
   <si>
     <t xml:space="preserve">6.93342542648315</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">7.34568309783936</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54244232177734</t>
+    <t xml:space="preserve">7.5424427986145</t>
   </si>
   <si>
     <t xml:space="preserve">8.19830703735352</t>
@@ -2238,6 +2238,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.5600004196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53999996185303</t>
   </si>
 </sst>
 </file>
@@ -62740,13 +62743,13 @@
     </row>
     <row r="2315">
       <c r="A2315" s="1" t="n">
-        <v>45986.6912847222</v>
+        <v>45986.3333333333</v>
       </c>
       <c r="B2315" t="n">
         <v>27799</v>
       </c>
       <c r="C2315" t="n">
-        <v>9.47999954223633</v>
+        <v>9.5600004196167</v>
       </c>
       <c r="D2315" t="n">
         <v>9.18000030517578</v>
@@ -62761,6 +62764,32 @@
         <v>741</v>
       </c>
       <c r="H2315" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2316">
+      <c r="A2316" s="1" t="n">
+        <v>45987.6912152778</v>
+      </c>
+      <c r="B2316" t="n">
+        <v>44787</v>
+      </c>
+      <c r="C2316" t="n">
+        <v>9.65999984741211</v>
+      </c>
+      <c r="D2316" t="n">
+        <v>9.4399995803833</v>
+      </c>
+      <c r="E2316" t="n">
+        <v>9.4399995803833</v>
+      </c>
+      <c r="F2316" t="n">
+        <v>9.53999996185303</v>
+      </c>
+      <c r="G2316" t="s">
+        <v>742</v>
+      </c>
+      <c r="H2316" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="743">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="744">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,22 +44,22 @@
     <t xml:space="preserve">FF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98565673828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08549785614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24887466430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09457588195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12180328369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03104019165039</t>
+    <t xml:space="preserve">8.98565578460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08549880981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24887275695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09457397460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12180423736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03103923797607</t>
   </si>
   <si>
     <t xml:space="preserve">8.95388984680176</t>
@@ -68,19 +68,19 @@
     <t xml:space="preserve">8.8994312286377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89489269256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84951114654541</t>
+    <t xml:space="preserve">8.89489364624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84951210021973</t>
   </si>
   <si>
     <t xml:space="preserve">8.85858917236328</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87674045562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76782417297363</t>
+    <t xml:space="preserve">8.87674140930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.767822265625</t>
   </si>
   <si>
     <t xml:space="preserve">8.86766529083252</t>
@@ -89,28 +89,28 @@
     <t xml:space="preserve">9.04919338226318</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23072242736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1127290725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96750450134277</t>
+    <t xml:space="preserve">9.23072147369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11272811889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96750259399414</t>
   </si>
   <si>
     <t xml:space="preserve">8.91304588317871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92212295532227</t>
+    <t xml:space="preserve">8.92212200164795</t>
   </si>
   <si>
     <t xml:space="preserve">9.00381088256836</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15811061859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16718578338623</t>
+    <t xml:space="preserve">9.15810871124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16718673706055</t>
   </si>
   <si>
     <t xml:space="preserve">9.43947887420654</t>
@@ -119,82 +119,82 @@
     <t xml:space="preserve">9.54839611053467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62100791931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80253601074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71177196502686</t>
+    <t xml:space="preserve">9.62100696563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80253505706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71177101135254</t>
   </si>
   <si>
     <t xml:space="preserve">9.56654834747314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58470153808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5756254196167</t>
+    <t xml:space="preserve">9.58470058441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57562351226807</t>
   </si>
   <si>
     <t xml:space="preserve">9.53024387359619</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50301361083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60285472869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63916015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79345893859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95683574676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93868255615234</t>
+    <t xml:space="preserve">9.50301456451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60285377502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63915920257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79345989227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95683479309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93868160247803</t>
   </si>
   <si>
     <t xml:space="preserve">9.98406410217285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73900127410889</t>
+    <t xml:space="preserve">9.73900032043457</t>
   </si>
   <si>
     <t xml:space="preserve">9.76623058319092</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74807739257812</t>
+    <t xml:space="preserve">9.74807834625244</t>
   </si>
   <si>
     <t xml:space="preserve">9.75715351104736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64823818206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82068920135498</t>
+    <t xml:space="preserve">9.64823532104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82068729400635</t>
   </si>
   <si>
     <t xml:space="preserve">9.7026948928833</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72084808349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67546463012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66638946533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63008308410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65731239318848</t>
+    <t xml:space="preserve">9.72084903717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67546558380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66638851165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63008213043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65731430053711</t>
   </si>
   <si>
     <t xml:space="preserve">9.68454265594482</t>
@@ -209,7 +209,7 @@
     <t xml:space="preserve">9.84791851043701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83884143829346</t>
+    <t xml:space="preserve">9.83884048461914</t>
   </si>
   <si>
     <t xml:space="preserve">9.72992515563965</t>
@@ -218,31 +218,31 @@
     <t xml:space="preserve">9.78438282012939</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55747318267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34871482849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33963871002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27610397338867</t>
+    <t xml:space="preserve">9.55747222900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34871578216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33963680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27610301971436</t>
   </si>
   <si>
     <t xml:space="preserve">9.25794982910156</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19441604614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18534088134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41225051879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22164344787598</t>
+    <t xml:space="preserve">9.19441509246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18533897399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41224956512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22164440155029</t>
   </si>
   <si>
     <t xml:space="preserve">9.31240844726562</t>
@@ -254,16 +254,16 @@
     <t xml:space="preserve">9.29425621032715</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28518009185791</t>
+    <t xml:space="preserve">9.28517913818359</t>
   </si>
   <si>
     <t xml:space="preserve">9.37594413757324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36686897277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3850212097168</t>
+    <t xml:space="preserve">9.36686706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38501930236816</t>
   </si>
   <si>
     <t xml:space="preserve">9.45763206481934</t>
@@ -272,13 +272,13 @@
     <t xml:space="preserve">9.39409732818604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48486042022705</t>
+    <t xml:space="preserve">9.48486137390137</t>
   </si>
   <si>
     <t xml:space="preserve">9.49393749237061</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44855403900146</t>
+    <t xml:space="preserve">9.44855499267578</t>
   </si>
   <si>
     <t xml:space="preserve">9.47578430175781</t>
@@ -287,13 +287,13 @@
     <t xml:space="preserve">9.2397985458374</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14903354644775</t>
+    <t xml:space="preserve">9.14903259277344</t>
   </si>
   <si>
     <t xml:space="preserve">9.21256828308105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20349311828613</t>
+    <t xml:space="preserve">9.20349216461182</t>
   </si>
   <si>
     <t xml:space="preserve">9.13088035583496</t>
@@ -305,7 +305,7 @@
     <t xml:space="preserve">8.94027519226074</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80412864685059</t>
+    <t xml:space="preserve">8.8041296005249</t>
   </si>
   <si>
     <t xml:space="preserve">8.75874614715576</t>
@@ -320,43 +320,43 @@
     <t xml:space="preserve">8.53183650970459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35030841827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16878128051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98725271224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03263473510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12339782714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25954437255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94187021255493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3049259185791</t>
+    <t xml:space="preserve">8.35030746459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16878032684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98725080490112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03263378143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12339687347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25954341888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94186925888062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30492496490479</t>
   </si>
   <si>
     <t xml:space="preserve">8.21416282653809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39569091796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57721900939941</t>
+    <t xml:space="preserve">8.39568996429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5772180557251</t>
   </si>
   <si>
     <t xml:space="preserve">8.71336555480957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53202152252197</t>
+    <t xml:space="preserve">9.53202247619629</t>
   </si>
   <si>
     <t xml:space="preserve">9.25706100463867</t>
@@ -368,16 +368,16 @@
     <t xml:space="preserve">9.16540622711182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07375240325928</t>
+    <t xml:space="preserve">9.07375144958496</t>
   </si>
   <si>
     <t xml:space="preserve">9.11957931518555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98209857940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02792644500732</t>
+    <t xml:space="preserve">8.98209953308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02792549133301</t>
   </si>
   <si>
     <t xml:space="preserve">9.62367725372314</t>
@@ -389,28 +389,28 @@
     <t xml:space="preserve">9.89863872528076</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99029350280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.173602104187</t>
+    <t xml:space="preserve">9.9902925491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1736011505127</t>
   </si>
   <si>
     <t xml:space="preserve">10.2652559280396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3569097518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5402173995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6318712234497</t>
+    <t xml:space="preserve">10.3569087982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5402183532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6318731307983</t>
   </si>
   <si>
     <t xml:space="preserve">10.8151798248291</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7235250473022</t>
+    <t xml:space="preserve">10.7235260009766</t>
   </si>
   <si>
     <t xml:space="preserve">10.906834602356</t>
@@ -419,13 +419,13 @@
     <t xml:space="preserve">10.9984884262085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0901412963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1817960739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2734498977661</t>
+    <t xml:space="preserve">11.090142250061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1817941665649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2734489440918</t>
   </si>
   <si>
     <t xml:space="preserve">11.4567584991455</t>
@@ -449,25 +449,25 @@
     <t xml:space="preserve">9.21123504638672</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30288887023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03709125518799</t>
+    <t xml:space="preserve">9.30288791656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03709030151367</t>
   </si>
   <si>
     <t xml:space="preserve">9.39454174041748</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76115608215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6695032119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57784938812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0361194610596</t>
+    <t xml:space="preserve">9.76115703582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66950225830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57785034179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0361204147339</t>
   </si>
   <si>
     <t xml:space="preserve">9.94446563720703</t>
@@ -479,7 +479,7 @@
     <t xml:space="preserve">9.73283100128174</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59379100799561</t>
+    <t xml:space="preserve">9.59379005432129</t>
   </si>
   <si>
     <t xml:space="preserve">9.96456432342529</t>
@@ -494,28 +494,28 @@
     <t xml:space="preserve">10.010910987854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1036052703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1499509811401</t>
+    <t xml:space="preserve">10.1036043167114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1499519348145</t>
   </si>
   <si>
     <t xml:space="preserve">10.1962985992432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77917671203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87186908721924</t>
+    <t xml:space="preserve">9.77917575836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87187004089355</t>
   </si>
   <si>
     <t xml:space="preserve">10.0572576522827</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2889928817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4743795394897</t>
+    <t xml:space="preserve">10.2889919281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4743785858154</t>
   </si>
   <si>
     <t xml:space="preserve">10.2426452636719</t>
@@ -524,10 +524,10 @@
     <t xml:space="preserve">10.3816862106323</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68648338317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64013576507568</t>
+    <t xml:space="preserve">9.68648433685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64013671875</t>
   </si>
   <si>
     <t xml:space="preserve">9.50109672546387</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">9.23228454589844</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1952075958252</t>
+    <t xml:space="preserve">9.19520854949951</t>
   </si>
   <si>
     <t xml:space="preserve">9.25082302093506</t>
@@ -557,28 +557,28 @@
     <t xml:space="preserve">9.12105274200439</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06543445587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97274208068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17666816711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02835941314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95420360565186</t>
+    <t xml:space="preserve">9.06543636322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97274303436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17666721343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02835845947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95420265197754</t>
   </si>
   <si>
     <t xml:space="preserve">8.71319961547852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99128150939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76881790161133</t>
+    <t xml:space="preserve">8.99128246307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76881694793701</t>
   </si>
   <si>
     <t xml:space="preserve">8.89858818054199</t>
@@ -587,28 +587,28 @@
     <t xml:space="preserve">8.93566513061523</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3353385925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9841947555542</t>
+    <t xml:space="preserve">10.3353395462036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9841957092285</t>
   </si>
   <si>
     <t xml:space="preserve">11.0305414199829</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2159280776978</t>
+    <t xml:space="preserve">11.2159290313721</t>
   </si>
   <si>
     <t xml:space="preserve">11.4940090179443</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5403547286987</t>
+    <t xml:space="preserve">11.540355682373</t>
   </si>
   <si>
     <t xml:space="preserve">11.5867033004761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6330490112305</t>
+    <t xml:space="preserve">11.6330499649048</t>
   </si>
   <si>
     <t xml:space="preserve">11.7257432937622</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">11.9574766159058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1892108917236</t>
+    <t xml:space="preserve">12.1892118453979</t>
   </si>
   <si>
     <t xml:space="preserve">12.2819051742554</t>
@@ -629,19 +629,19 @@
     <t xml:space="preserve">12.3745994567871</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5136384963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3282527923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1428651809692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0965175628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.555121421814</t>
+    <t xml:space="preserve">12.5136394500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3282518386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1428642272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0965185165405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5551223754883</t>
   </si>
   <si>
     <t xml:space="preserve">12.5082750320435</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">12.6488170623779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4614276885986</t>
+    <t xml:space="preserve">12.4614267349243</t>
   </si>
   <si>
     <t xml:space="preserve">12.4145793914795</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7425127029419</t>
+    <t xml:space="preserve">12.7425117492676</t>
   </si>
   <si>
     <t xml:space="preserve">12.6956644058228</t>
@@ -671,13 +671,13 @@
     <t xml:space="preserve">12.3208837509155</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2740383148193</t>
+    <t xml:space="preserve">12.274037361145</t>
   </si>
   <si>
     <t xml:space="preserve">12.8362064361572</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7893581390381</t>
+    <t xml:space="preserve">12.7893590927124</t>
   </si>
   <si>
     <t xml:space="preserve">12.6019697189331</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">12.9299020767212</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8830537796021</t>
+    <t xml:space="preserve">12.8830547332764</t>
   </si>
   <si>
     <t xml:space="preserve">13.0704441070557</t>
@@ -695,25 +695,25 @@
     <t xml:space="preserve">13.679461479187</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8668508529663</t>
+    <t xml:space="preserve">13.8668518066406</t>
   </si>
   <si>
     <t xml:space="preserve">14.0542402267456</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3353252410889</t>
+    <t xml:space="preserve">14.3353261947632</t>
   </si>
   <si>
     <t xml:space="preserve">14.5695638656616</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2254285812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1317329406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7569532394409</t>
+    <t xml:space="preserve">15.2254276275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1317319869995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7569522857666</t>
   </si>
   <si>
     <t xml:space="preserve">15.0380373001099</t>
@@ -725,19 +725,19 @@
     <t xml:space="preserve">15.3191232681274</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8974943161011</t>
+    <t xml:space="preserve">14.8974952697754</t>
   </si>
   <si>
     <t xml:space="preserve">15.4596662521362</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4128189086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5533599853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0686817169189</t>
+    <t xml:space="preserve">15.4128198623657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5533618927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0686798095703</t>
   </si>
   <si>
     <t xml:space="preserve">16.8650894165039</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">17.0056324005127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7713947296143</t>
+    <t xml:space="preserve">16.7713928222656</t>
   </si>
   <si>
     <t xml:space="preserve">17.193021774292</t>
@@ -761,31 +761,31 @@
     <t xml:space="preserve">16.7245483398438</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6308536529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5371551513672</t>
+    <t xml:space="preserve">16.6308517456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5371570587158</t>
   </si>
   <si>
     <t xml:space="preserve">16.584005355835</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2092227935791</t>
+    <t xml:space="preserve">16.2092247009277</t>
   </si>
   <si>
     <t xml:space="preserve">16.2560729980469</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1461715698242</t>
+    <t xml:space="preserve">17.1461734771729</t>
   </si>
   <si>
     <t xml:space="preserve">16.396614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3029174804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8344440460205</t>
+    <t xml:space="preserve">16.3029193878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8344430923462</t>
   </si>
   <si>
     <t xml:space="preserve">16.1155300140381</t>
@@ -794,7 +794,7 @@
     <t xml:space="preserve">16.0218353271484</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1623764038086</t>
+    <t xml:space="preserve">16.16237449646</t>
   </si>
   <si>
     <t xml:space="preserve">15.974986076355</t>
@@ -803,10 +803,10 @@
     <t xml:space="preserve">15.7407484054565</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4434604644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9119358062744</t>
+    <t xml:space="preserve">16.4434623718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.911937713623</t>
   </si>
   <si>
     <t xml:space="preserve">17.0993251800537</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">16.677698135376</t>
   </si>
   <si>
-    <t xml:space="preserve">16.818244934082</t>
+    <t xml:space="preserve">16.8182430267334</t>
   </si>
   <si>
     <t xml:space="preserve">15.272274017334</t>
@@ -824,10 +824,10 @@
     <t xml:space="preserve">15.084885597229</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9911909103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8037996292114</t>
+    <t xml:space="preserve">14.991189956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8038015365601</t>
   </si>
   <si>
     <t xml:space="preserve">14.4758682250977</t>
@@ -848,13 +848,13 @@
     <t xml:space="preserve">13.960545539856</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2416305541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1947832107544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0073938369751</t>
+    <t xml:space="preserve">14.2416315078735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1947822570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0073928833008</t>
   </si>
   <si>
     <t xml:space="preserve">13.7263088226318</t>
@@ -881,19 +881,19 @@
     <t xml:space="preserve">13.3983764648438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0235967636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1172924041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.976749420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3677320480347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0866460800171</t>
+    <t xml:space="preserve">13.0235958099365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1172914505005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9767484664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3677310943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0866470336914</t>
   </si>
   <si>
     <t xml:space="preserve">11.9929523468018</t>
@@ -902,22 +902,22 @@
     <t xml:space="preserve">11.8992576599121</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0397987365723</t>
+    <t xml:space="preserve">12.0397996902466</t>
   </si>
   <si>
     <t xml:space="preserve">12.1334943771362</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4776296615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2433938980103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3839340209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6650199890137</t>
+    <t xml:space="preserve">11.4776306152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2433929443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3839349746704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6650190353394</t>
   </si>
   <si>
     <t xml:space="preserve">11.4307823181152</t>
@@ -926,28 +926,28 @@
     <t xml:space="preserve">10.9623079299927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7280712127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1965456008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5713243484497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3370876312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2902402877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7118682861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7587156295776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8055629730225</t>
+    <t xml:space="preserve">10.7280702590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1965446472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5713262557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3370885848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2902393341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7118673324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7587146759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8055620193481</t>
   </si>
   <si>
     <t xml:space="preserve">11.0091552734375</t>
@@ -959,25 +959,25 @@
     <t xml:space="preserve">8.33884906768799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57308578491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31074142456055</t>
+    <t xml:space="preserve">8.57308673858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31074047088623</t>
   </si>
   <si>
     <t xml:space="preserve">8.45128345489502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61993312835693</t>
+    <t xml:space="preserve">8.61993408203125</t>
   </si>
   <si>
     <t xml:space="preserve">8.44191455841064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32948112487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25452327728271</t>
+    <t xml:space="preserve">8.32948017120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25452423095703</t>
   </si>
   <si>
     <t xml:space="preserve">8.43254470825195</t>
@@ -986,19 +986,19 @@
     <t xml:space="preserve">8.47002220153809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32011127471924</t>
+    <t xml:space="preserve">8.32011222839355</t>
   </si>
   <si>
     <t xml:space="preserve">8.20767784118652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08587265014648</t>
+    <t xml:space="preserve">8.0858736038208</t>
   </si>
   <si>
     <t xml:space="preserve">7.78604936599731</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49559545516968</t>
+    <t xml:space="preserve">7.49559497833252</t>
   </si>
   <si>
     <t xml:space="preserve">7.33631372451782</t>
@@ -1007,7 +1007,7 @@
     <t xml:space="preserve">7.23324918746948</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83289623260498</t>
+    <t xml:space="preserve">7.83289670944214</t>
   </si>
   <si>
     <t xml:space="preserve">7.90785312652588</t>
@@ -1019,7 +1019,7 @@
     <t xml:space="preserve">7.37379169464111</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12081527709961</t>
+    <t xml:space="preserve">7.12081575393677</t>
   </si>
   <si>
     <t xml:space="preserve">7.28009700775146</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">6.98027276992798</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93342542648315</t>
+    <t xml:space="preserve">6.93342590332031</t>
   </si>
   <si>
     <t xml:space="preserve">7.06459856033325</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">7.0271201133728</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34568309783936</t>
+    <t xml:space="preserve">7.34568357467651</t>
   </si>
   <si>
     <t xml:space="preserve">7.5424427986145</t>
@@ -1046,25 +1046,25 @@
     <t xml:space="preserve">8.19830703735352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2170467376709</t>
+    <t xml:space="preserve">8.21704578399658</t>
   </si>
   <si>
     <t xml:space="preserve">8.65194320678711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46116256713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53747463226318</t>
+    <t xml:space="preserve">8.46116161346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53747367858887</t>
   </si>
   <si>
     <t xml:space="preserve">8.68056106567383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77595233917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8427267074585</t>
+    <t xml:space="preserve">8.77595138549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84272575378418</t>
   </si>
   <si>
     <t xml:space="preserve">8.72825527191162</t>
@@ -1076,16 +1076,16 @@
     <t xml:space="preserve">8.49931812286377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42300510406494</t>
+    <t xml:space="preserve">8.42300605773926</t>
   </si>
   <si>
     <t xml:space="preserve">8.39438915252686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.604248046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48977947235107</t>
+    <t xml:space="preserve">8.60424900054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48977851867676</t>
   </si>
   <si>
     <t xml:space="preserve">8.29899787902832</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">8.12729454040527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89835643768311</t>
+    <t xml:space="preserve">7.89835596084595</t>
   </si>
   <si>
     <t xml:space="preserve">8.10821628570557</t>
@@ -1115,16 +1115,16 @@
     <t xml:space="preserve">8.07959938049316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07005882263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92697429656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98420858383179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30853652954102</t>
+    <t xml:space="preserve">8.07005977630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92697381973267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98420763015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30853748321533</t>
   </si>
   <si>
     <t xml:space="preserve">8.26084136962891</t>
@@ -1139,10 +1139,10 @@
     <t xml:space="preserve">8.03190326690674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96513080596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86019992828369</t>
+    <t xml:space="preserve">7.96513032913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86019945144653</t>
   </si>
   <si>
     <t xml:space="preserve">7.86973905563354</t>
@@ -1154,19 +1154,19 @@
     <t xml:space="preserve">7.91743516921997</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76481008529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72665309906006</t>
+    <t xml:space="preserve">7.76480960845947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72665357589722</t>
   </si>
   <si>
     <t xml:space="preserve">7.65034103393555</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63126230239868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65987968444824</t>
+    <t xml:space="preserve">7.63126182556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65987873077393</t>
   </si>
   <si>
     <t xml:space="preserve">8.16545104980469</t>
@@ -1178,16 +1178,16 @@
     <t xml:space="preserve">8.11775588989258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93651247024536</t>
+    <t xml:space="preserve">7.93651151657104</t>
   </si>
   <si>
     <t xml:space="preserve">8.19406795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2322244644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31807518005371</t>
+    <t xml:space="preserve">8.23222351074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31807708740234</t>
   </si>
   <si>
     <t xml:space="preserve">8.15591144561768</t>
@@ -1199,31 +1199,31 @@
     <t xml:space="preserve">8.25130176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35623168945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24176406860352</t>
+    <t xml:space="preserve">8.35623264312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2417631149292</t>
   </si>
   <si>
     <t xml:space="preserve">8.34669303894043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95559167861938</t>
+    <t xml:space="preserve">7.95559072494507</t>
   </si>
   <si>
     <t xml:space="preserve">7.77434825897217</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82204389572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97466850280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01282596588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05098152160645</t>
+    <t xml:space="preserve">7.82204437255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97466897964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01282501220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05098056793213</t>
   </si>
   <si>
     <t xml:space="preserve">7.67895746231079</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">7.73619174957275</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69803524017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51679372787476</t>
+    <t xml:space="preserve">7.6980357170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5167932510376</t>
   </si>
   <si>
     <t xml:space="preserve">7.59310626983643</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">7.62172269821167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52633190155029</t>
+    <t xml:space="preserve">7.52633237838745</t>
   </si>
   <si>
     <t xml:space="preserve">7.34508991241455</t>
@@ -1265,25 +1265,25 @@
     <t xml:space="preserve">7.14476871490479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12569046020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23062133789062</t>
+    <t xml:space="preserve">7.12569093704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23062086105347</t>
   </si>
   <si>
     <t xml:space="preserve">7.1543083190918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24969863891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24016046524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46909809112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41186332702637</t>
+    <t xml:space="preserve">7.24969911575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24015998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46909761428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41186285018921</t>
   </si>
   <si>
     <t xml:space="preserve">7.45001983642578</t>
@@ -1295,34 +1295,34 @@
     <t xml:space="preserve">7.39278507232666</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3355507850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61218404769897</t>
+    <t xml:space="preserve">7.33555126190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61218357086182</t>
   </si>
   <si>
     <t xml:space="preserve">7.90789556503296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94605159759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45955896377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70757484436035</t>
+    <t xml:space="preserve">7.94605112075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45955848693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70757436752319</t>
   </si>
   <si>
     <t xml:space="preserve">7.8792781829834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99374771118164</t>
+    <t xml:space="preserve">7.99374723434448</t>
   </si>
   <si>
     <t xml:space="preserve">7.75527000427246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81250381469727</t>
+    <t xml:space="preserve">7.81250476837158</t>
   </si>
   <si>
     <t xml:space="preserve">7.79342699050903</t>
@@ -1331,25 +1331,25 @@
     <t xml:space="preserve">7.80296611785889</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85065984725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74573087692261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83158302307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66941785812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60264492034912</t>
+    <t xml:space="preserve">7.85066032409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74573135375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83158254623413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66941833496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60264539718628</t>
   </si>
   <si>
     <t xml:space="preserve">7.58356666564941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88881826400757</t>
+    <t xml:space="preserve">7.88881778717041</t>
   </si>
   <si>
     <t xml:space="preserve">8.00328636169434</t>
@@ -1361,7 +1361,7 @@
     <t xml:space="preserve">7.3641676902771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10661268234253</t>
+    <t xml:space="preserve">7.10661315917969</t>
   </si>
   <si>
     <t xml:space="preserve">7.27831649780273</t>
@@ -1376,10 +1376,10 @@
     <t xml:space="preserve">7.50372648239136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98721408843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02589225769043</t>
+    <t xml:space="preserve">7.98721361160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02589321136475</t>
   </si>
   <si>
     <t xml:space="preserve">8.04523086547852</t>
@@ -1391,25 +1391,25 @@
     <t xml:space="preserve">8.07424163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12258911132812</t>
+    <t xml:space="preserve">8.12259006500244</t>
   </si>
   <si>
     <t xml:space="preserve">8.05490112304688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94853496551514</t>
+    <t xml:space="preserve">7.94853448867798</t>
   </si>
   <si>
     <t xml:space="preserve">8.06457138061523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08390998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97754430770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93886518478394</t>
+    <t xml:space="preserve">8.08391094207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97754383087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93886423110962</t>
   </si>
   <si>
     <t xml:space="preserve">7.79381895065308</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">7.68745088577271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63910293579102</t>
+    <t xml:space="preserve">7.63910245895386</t>
   </si>
   <si>
     <t xml:space="preserve">7.73579978942871</t>
@@ -1436,10 +1436,10 @@
     <t xml:space="preserve">7.90985584259033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85183668136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83249759674072</t>
+    <t xml:space="preserve">7.85183715820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83249807357788</t>
   </si>
   <si>
     <t xml:space="preserve">7.81315755844116</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">7.80348825454712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78414916992188</t>
+    <t xml:space="preserve">7.78414869308472</t>
   </si>
   <si>
     <t xml:space="preserve">7.6681113243103</t>
@@ -1460,13 +1460,13 @@
     <t xml:space="preserve">7.71646022796631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75513982772827</t>
+    <t xml:space="preserve">7.75514030456543</t>
   </si>
   <si>
     <t xml:space="preserve">7.74547004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86150693893433</t>
+    <t xml:space="preserve">7.86150646209717</t>
   </si>
   <si>
     <t xml:space="preserve">7.89051580429077</t>
@@ -1484,10 +1484,10 @@
     <t xml:space="preserve">8.09358024597168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13225936889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1515998840332</t>
+    <t xml:space="preserve">8.1322603225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15159893035889</t>
   </si>
   <si>
     <t xml:space="preserve">8.1129207611084</t>
@@ -1496,10 +1496,10 @@
     <t xml:space="preserve">8.03556251525879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92919492721558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69712066650391</t>
+    <t xml:space="preserve">7.92919540405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69712114334106</t>
   </si>
   <si>
     <t xml:space="preserve">7.60042381286621</t>
@@ -1508,10 +1508,10 @@
     <t xml:space="preserve">7.88084602355957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55207443237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40702819824219</t>
+    <t xml:space="preserve">7.55207490921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40702867507935</t>
   </si>
   <si>
     <t xml:space="preserve">7.34900999069214</t>
@@ -1520,16 +1520,16 @@
     <t xml:space="preserve">7.37801933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43603754043579</t>
+    <t xml:space="preserve">7.43603801727295</t>
   </si>
   <si>
     <t xml:space="preserve">7.41669797897339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52306604385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36834955215454</t>
+    <t xml:space="preserve">7.5230655670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36834907531738</t>
   </si>
   <si>
     <t xml:space="preserve">7.542405128479</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">7.4843864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70679044723511</t>
+    <t xml:space="preserve">7.70679092407227</t>
   </si>
   <si>
     <t xml:space="preserve">7.64877223968506</t>
@@ -1556,10 +1556,10 @@
     <t xml:space="preserve">7.59075355529785</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95820426940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96787405014038</t>
+    <t xml:space="preserve">7.95820331573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96787357330322</t>
   </si>
   <si>
     <t xml:space="preserve">7.90018606185913</t>
@@ -1577,10 +1577,10 @@
     <t xml:space="preserve">8.19027900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29664611816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45136165618896</t>
+    <t xml:space="preserve">8.29664516448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45136070251465</t>
   </si>
   <si>
     <t xml:space="preserve">8.48037147521973</t>
@@ -1607,19 +1607,19 @@
     <t xml:space="preserve">8.50938034057617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4223518371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54805946350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55772972106934</t>
+    <t xml:space="preserve">8.42235279083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54805850982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55772876739502</t>
   </si>
   <si>
     <t xml:space="preserve">8.52871990203857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68343448638916</t>
+    <t xml:space="preserve">8.68343544006348</t>
   </si>
   <si>
     <t xml:space="preserve">8.76079368591309</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">8.65442562103271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75112438201904</t>
+    <t xml:space="preserve">8.75112342834473</t>
   </si>
   <si>
     <t xml:space="preserve">8.70277500152588</t>
@@ -1652,10 +1652,10 @@
     <t xml:space="preserve">8.63508701324463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32565402984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31598472595215</t>
+    <t xml:space="preserve">8.32565498352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31598567962646</t>
   </si>
   <si>
     <t xml:space="preserve">8.30631542205811</t>
@@ -2241,6 +2241,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.53999996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52000045776367</t>
   </si>
 </sst>
 </file>
@@ -62769,7 +62772,7 @@
     </row>
     <row r="2316">
       <c r="A2316" s="1" t="n">
-        <v>45987.6912152778</v>
+        <v>45987.3333333333</v>
       </c>
       <c r="B2316" t="n">
         <v>44787</v>
@@ -62790,6 +62793,32 @@
         <v>742</v>
       </c>
       <c r="H2316" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2317">
+      <c r="A2317" s="1" t="n">
+        <v>45988.6912037037</v>
+      </c>
+      <c r="B2317" t="n">
+        <v>21252</v>
+      </c>
+      <c r="C2317" t="n">
+        <v>9.64000034332275</v>
+      </c>
+      <c r="D2317" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E2317" t="n">
+        <v>9.61999988555908</v>
+      </c>
+      <c r="F2317" t="n">
+        <v>9.52000045776367</v>
+      </c>
+      <c r="G2317" t="s">
+        <v>743</v>
+      </c>
+      <c r="H2317" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -44,16 +44,16 @@
     <t xml:space="preserve">FF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98565578460693</t>
+    <t xml:space="preserve">8.98565769195557</t>
   </si>
   <si>
     <t xml:space="preserve">9.08549880981445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24887275695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09457397460938</t>
+    <t xml:space="preserve">9.24887371063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09457683563232</t>
   </si>
   <si>
     <t xml:space="preserve">9.12180423736572</t>
@@ -62,46 +62,46 @@
     <t xml:space="preserve">9.03103923797607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95388984680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8994312286377</t>
+    <t xml:space="preserve">8.95389080047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89943313598633</t>
   </si>
   <si>
     <t xml:space="preserve">8.89489364624023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84951210021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85858917236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87674140930176</t>
+    <t xml:space="preserve">8.84951019287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85858821868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87674045562744</t>
   </si>
   <si>
     <t xml:space="preserve">8.767822265625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86766529083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04919338226318</t>
+    <t xml:space="preserve">8.8676643371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04919242858887</t>
   </si>
   <si>
     <t xml:space="preserve">9.23072147369385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11272811889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96750259399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91304588317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92212200164795</t>
+    <t xml:space="preserve">9.11272716522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96750354766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91304683685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92212390899658</t>
   </si>
   <si>
     <t xml:space="preserve">9.00381088256836</t>
@@ -113,7 +113,7 @@
     <t xml:space="preserve">9.16718673706055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43947887420654</t>
+    <t xml:space="preserve">9.43947696685791</t>
   </si>
   <si>
     <t xml:space="preserve">9.54839611053467</t>
@@ -125,64 +125,64 @@
     <t xml:space="preserve">9.80253505706787</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71177101135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56654834747314</t>
+    <t xml:space="preserve">9.71177196502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56654930114746</t>
   </si>
   <si>
     <t xml:space="preserve">9.58470058441162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57562351226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53024387359619</t>
+    <t xml:space="preserve">9.5756254196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53024196624756</t>
   </si>
   <si>
     <t xml:space="preserve">9.50301456451416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60285377502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63915920257568</t>
+    <t xml:space="preserve">9.60285472869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63916015625</t>
   </si>
   <si>
     <t xml:space="preserve">9.79345989227295</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95683479309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93868160247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98406410217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73900032043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76623058319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74807834625244</t>
+    <t xml:space="preserve">9.9568338394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93868255615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98406505584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7390022277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76622867584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74807739257812</t>
   </si>
   <si>
     <t xml:space="preserve">9.75715351104736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64823532104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82068729400635</t>
+    <t xml:space="preserve">9.64823722839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82068824768066</t>
   </si>
   <si>
     <t xml:space="preserve">9.7026948928833</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72084903717041</t>
+    <t xml:space="preserve">9.72084808349609</t>
   </si>
   <si>
     <t xml:space="preserve">9.67546558380127</t>
@@ -191,13 +191,13 @@
     <t xml:space="preserve">9.66638851165771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63008213043213</t>
+    <t xml:space="preserve">9.63008308410645</t>
   </si>
   <si>
     <t xml:space="preserve">9.65731430053711</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68454265594482</t>
+    <t xml:space="preserve">9.68454074859619</t>
   </si>
   <si>
     <t xml:space="preserve">9.81161212921143</t>
@@ -206,13 +206,13 @@
     <t xml:space="preserve">9.8297643661499</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84791851043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83884048461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72992515563965</t>
+    <t xml:space="preserve">9.8479175567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83884143829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72992420196533</t>
   </si>
   <si>
     <t xml:space="preserve">9.78438282012939</t>
@@ -221,34 +221,34 @@
     <t xml:space="preserve">9.55747222900391</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34871578216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33963680267334</t>
+    <t xml:space="preserve">9.34871292114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33963871002197</t>
   </si>
   <si>
     <t xml:space="preserve">9.27610301971436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25794982910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19441509246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18533897399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41224956512451</t>
+    <t xml:space="preserve">9.2579517364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19441413879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18533802032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41225051879883</t>
   </si>
   <si>
     <t xml:space="preserve">9.22164440155029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31240844726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26702690124512</t>
+    <t xml:space="preserve">9.31240940093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2670259475708</t>
   </si>
   <si>
     <t xml:space="preserve">9.29425621032715</t>
@@ -266,16 +266,16 @@
     <t xml:space="preserve">9.38501930236816</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45763206481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39409732818604</t>
+    <t xml:space="preserve">9.45763111114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39409637451172</t>
   </si>
   <si>
     <t xml:space="preserve">9.48486137390137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49393749237061</t>
+    <t xml:space="preserve">9.49393653869629</t>
   </si>
   <si>
     <t xml:space="preserve">9.44855499267578</t>
@@ -293,28 +293,28 @@
     <t xml:space="preserve">9.21256828308105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20349216461182</t>
+    <t xml:space="preserve">9.2034912109375</t>
   </si>
   <si>
     <t xml:space="preserve">9.13088035583496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1399564743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94027519226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8041296005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75874614715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66798400878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62260055541992</t>
+    <t xml:space="preserve">9.13995742797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94027614593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80412769317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75874710083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66798305511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62259960174561</t>
   </si>
   <si>
     <t xml:space="preserve">8.53183650970459</t>
@@ -326,73 +326,73 @@
     <t xml:space="preserve">8.16878032684326</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98725080490112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03263378143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12339687347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25954341888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94186925888062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30492496490479</t>
+    <t xml:space="preserve">7.98725128173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03263473510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12339782714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25954532623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94186878204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3049259185791</t>
   </si>
   <si>
     <t xml:space="preserve">8.21416282653809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39568996429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5772180557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71336555480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53202247619629</t>
+    <t xml:space="preserve">8.39569091796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57721710205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71336460113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53202342987061</t>
   </si>
   <si>
     <t xml:space="preserve">9.25706100463867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44036865234375</t>
+    <t xml:space="preserve">9.44036960601807</t>
   </si>
   <si>
     <t xml:space="preserve">9.16540622711182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07375144958496</t>
+    <t xml:space="preserve">9.07375240325928</t>
   </si>
   <si>
     <t xml:space="preserve">9.11957931518555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98209953308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02792549133301</t>
+    <t xml:space="preserve">8.98209857940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02792644500732</t>
   </si>
   <si>
     <t xml:space="preserve">9.62367725372314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80698490142822</t>
+    <t xml:space="preserve">9.80698585510254</t>
   </si>
   <si>
     <t xml:space="preserve">9.89863872528076</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9902925491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1736011505127</t>
+    <t xml:space="preserve">9.99029350280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.173602104187</t>
   </si>
   <si>
     <t xml:space="preserve">10.2652559280396</t>
@@ -404,7 +404,7 @@
     <t xml:space="preserve">10.5402183532715</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6318731307983</t>
+    <t xml:space="preserve">10.631872177124</t>
   </si>
   <si>
     <t xml:space="preserve">10.8151798248291</t>
@@ -413,7 +413,7 @@
     <t xml:space="preserve">10.7235260009766</t>
   </si>
   <si>
-    <t xml:space="preserve">10.906834602356</t>
+    <t xml:space="preserve">10.9068326950073</t>
   </si>
   <si>
     <t xml:space="preserve">10.9984884262085</t>
@@ -422,10 +422,10 @@
     <t xml:space="preserve">11.090142250061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1817941665649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2734489440918</t>
+    <t xml:space="preserve">11.1817970275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2734518051147</t>
   </si>
   <si>
     <t xml:space="preserve">11.4567584991455</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">10.4485626220703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71533107757568</t>
+    <t xml:space="preserve">9.71533203125</t>
   </si>
   <si>
     <t xml:space="preserve">8.79879093170166</t>
@@ -446,7 +446,7 @@
     <t xml:space="preserve">8.24886608123779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21123504638672</t>
+    <t xml:space="preserve">9.2112340927124</t>
   </si>
   <si>
     <t xml:space="preserve">9.30288791656494</t>
@@ -458,10 +458,10 @@
     <t xml:space="preserve">9.39454174041748</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76115703582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66950225830078</t>
+    <t xml:space="preserve">9.76115798950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66950416564941</t>
   </si>
   <si>
     <t xml:space="preserve">9.57785034179688</t>
@@ -470,13 +470,13 @@
     <t xml:space="preserve">10.0361204147339</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94446563720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82552433013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73283100128174</t>
+    <t xml:space="preserve">9.94446659088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82552528381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73283004760742</t>
   </si>
   <si>
     <t xml:space="preserve">9.59379005432129</t>
@@ -485,16 +485,16 @@
     <t xml:space="preserve">9.96456432342529</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91821765899658</t>
+    <t xml:space="preserve">9.9182186126709</t>
   </si>
   <si>
     <t xml:space="preserve">9.54744338989258</t>
   </si>
   <si>
-    <t xml:space="preserve">10.010910987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1036043167114</t>
+    <t xml:space="preserve">10.0109119415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1036052703857</t>
   </si>
   <si>
     <t xml:space="preserve">10.1499519348145</t>
@@ -503,19 +503,19 @@
     <t xml:space="preserve">10.1962985992432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77917575836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87187004089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0572576522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2889919281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4743785858154</t>
+    <t xml:space="preserve">9.77917766571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87187099456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.057258605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2889928817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4743795394897</t>
   </si>
   <si>
     <t xml:space="preserve">10.2426452636719</t>
@@ -524,25 +524,25 @@
     <t xml:space="preserve">10.3816862106323</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68648433685303</t>
+    <t xml:space="preserve">9.68648338317871</t>
   </si>
   <si>
     <t xml:space="preserve">9.64013671875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50109672546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31571006774902</t>
+    <t xml:space="preserve">9.50109577178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31570911407471</t>
   </si>
   <si>
     <t xml:space="preserve">9.23228454589844</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19520854949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25082302093506</t>
+    <t xml:space="preserve">9.1952075958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25082206726074</t>
   </si>
   <si>
     <t xml:space="preserve">9.26936149597168</t>
@@ -563,19 +563,19 @@
     <t xml:space="preserve">8.97274303436279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17666721343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02835845947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95420265197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71319961547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99128246307373</t>
+    <t xml:space="preserve">9.17666816711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02835941314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95420360565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71320056915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9912805557251</t>
   </si>
   <si>
     <t xml:space="preserve">8.76881694793701</t>
@@ -584,43 +584,43 @@
     <t xml:space="preserve">8.89858818054199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93566513061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3353395462036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9841957092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0305414199829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2159290313721</t>
+    <t xml:space="preserve">8.93566608428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3353385925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9841938018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0305404663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2159280776978</t>
   </si>
   <si>
     <t xml:space="preserve">11.4940090179443</t>
   </si>
   <si>
-    <t xml:space="preserve">11.540355682373</t>
+    <t xml:space="preserve">11.5403547286987</t>
   </si>
   <si>
     <t xml:space="preserve">11.5867033004761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6330499649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7257432937622</t>
+    <t xml:space="preserve">11.6330490112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7257413864136</t>
   </si>
   <si>
     <t xml:space="preserve">11.9111299514771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9574766159058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1892118453979</t>
+    <t xml:space="preserve">11.9574775695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1892108917236</t>
   </si>
   <si>
     <t xml:space="preserve">12.2819051742554</t>
@@ -632,16 +632,16 @@
     <t xml:space="preserve">12.5136394500732</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3282518386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1428642272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0965185165405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5551223754883</t>
+    <t xml:space="preserve">12.3282527923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1428661346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0965175628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.555121421814</t>
   </si>
   <si>
     <t xml:space="preserve">12.5082750320435</t>
@@ -650,19 +650,19 @@
     <t xml:space="preserve">12.6488170623779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4614267349243</t>
+    <t xml:space="preserve">12.4614276885986</t>
   </si>
   <si>
     <t xml:space="preserve">12.4145793914795</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7425117492676</t>
+    <t xml:space="preserve">12.7425127029419</t>
   </si>
   <si>
     <t xml:space="preserve">12.6956644058228</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2271900177002</t>
+    <t xml:space="preserve">12.2271890640259</t>
   </si>
   <si>
     <t xml:space="preserve">12.1803426742554</t>
@@ -671,49 +671,49 @@
     <t xml:space="preserve">12.3208837509155</t>
   </si>
   <si>
-    <t xml:space="preserve">12.274037361145</t>
+    <t xml:space="preserve">12.2740383148193</t>
   </si>
   <si>
     <t xml:space="preserve">12.8362064361572</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7893590927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6019697189331</t>
+    <t xml:space="preserve">12.7893581390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6019687652588</t>
   </si>
   <si>
     <t xml:space="preserve">12.9299020767212</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8830547332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0704441070557</t>
+    <t xml:space="preserve">12.8830537796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0704431533813</t>
   </si>
   <si>
     <t xml:space="preserve">13.679461479187</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8668518066406</t>
+    <t xml:space="preserve">13.8668508529663</t>
   </si>
   <si>
     <t xml:space="preserve">14.0542402267456</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3353261947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5695638656616</t>
+    <t xml:space="preserve">14.3353252410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5695629119873</t>
   </si>
   <si>
     <t xml:space="preserve">15.2254276275635</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1317319869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7569522857666</t>
+    <t xml:space="preserve">15.1317329406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7569532394409</t>
   </si>
   <si>
     <t xml:space="preserve">15.0380373001099</t>
@@ -728,16 +728,16 @@
     <t xml:space="preserve">14.8974952697754</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4596662521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4128198623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5533618927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0686798095703</t>
+    <t xml:space="preserve">15.4596652984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4128179550171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5533599853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0686817169189</t>
   </si>
   <si>
     <t xml:space="preserve">16.8650894165039</t>
@@ -749,34 +749,34 @@
     <t xml:space="preserve">16.7713928222656</t>
   </si>
   <si>
-    <t xml:space="preserve">17.193021774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0524787902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9587860107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7245483398438</t>
+    <t xml:space="preserve">17.1930236816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0524806976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9587841033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7245464324951</t>
   </si>
   <si>
     <t xml:space="preserve">16.6308517456055</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5371570587158</t>
+    <t xml:space="preserve">16.5371551513672</t>
   </si>
   <si>
     <t xml:space="preserve">16.584005355835</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2092247009277</t>
+    <t xml:space="preserve">16.2092227935791</t>
   </si>
   <si>
     <t xml:space="preserve">16.2560729980469</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1461734771729</t>
+    <t xml:space="preserve">17.1461715698242</t>
   </si>
   <si>
     <t xml:space="preserve">16.396614074707</t>
@@ -785,16 +785,16 @@
     <t xml:space="preserve">16.3029193878174</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8344430923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1155300140381</t>
+    <t xml:space="preserve">15.8344440460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1155319213867</t>
   </si>
   <si>
     <t xml:space="preserve">16.0218353271484</t>
   </si>
   <si>
-    <t xml:space="preserve">16.16237449646</t>
+    <t xml:space="preserve">16.1623764038086</t>
   </si>
   <si>
     <t xml:space="preserve">15.974986076355</t>
@@ -803,10 +803,10 @@
     <t xml:space="preserve">15.7407484054565</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4434623718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.911937713623</t>
+    <t xml:space="preserve">16.4434604644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9119338989258</t>
   </si>
   <si>
     <t xml:space="preserve">17.0993251800537</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">16.677698135376</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8182430267334</t>
+    <t xml:space="preserve">16.818244934082</t>
   </si>
   <si>
     <t xml:space="preserve">15.272274017334</t>
@@ -824,10 +824,10 @@
     <t xml:space="preserve">15.084885597229</t>
   </si>
   <si>
-    <t xml:space="preserve">14.991189956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8038015365601</t>
+    <t xml:space="preserve">14.9911909103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8037996292114</t>
   </si>
   <si>
     <t xml:space="preserve">14.4758682250977</t>
@@ -842,22 +842,22 @@
     <t xml:space="preserve">14.288477897644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5227155685425</t>
+    <t xml:space="preserve">14.5227146148682</t>
   </si>
   <si>
     <t xml:space="preserve">13.960545539856</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2416315078735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1947822570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0073928833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7263088226318</t>
+    <t xml:space="preserve">14.2416305541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1947832107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0073938369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7263078689575</t>
   </si>
   <si>
     <t xml:space="preserve">14.1479358673096</t>
@@ -866,7 +866,7 @@
     <t xml:space="preserve">14.4290199279785</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6164112091064</t>
+    <t xml:space="preserve">14.6164102554321</t>
   </si>
   <si>
     <t xml:space="preserve">13.7731561660767</t>
@@ -875,79 +875,79 @@
     <t xml:space="preserve">13.3515281677246</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3046808242798</t>
+    <t xml:space="preserve">13.3046817779541</t>
   </si>
   <si>
     <t xml:space="preserve">13.3983764648438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0235958099365</t>
+    <t xml:space="preserve">13.0235967636108</t>
   </si>
   <si>
     <t xml:space="preserve">13.1172914505005</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9767484664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3677310943604</t>
+    <t xml:space="preserve">12.976749420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3677320480347</t>
   </si>
   <si>
     <t xml:space="preserve">12.0866470336914</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9929523468018</t>
+    <t xml:space="preserve">11.9929533004761</t>
   </si>
   <si>
     <t xml:space="preserve">11.8992576599121</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0397996902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1334943771362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4776306152344</t>
+    <t xml:space="preserve">12.0397987365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1334934234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4776296615601</t>
   </si>
   <si>
     <t xml:space="preserve">11.2433929443359</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3839349746704</t>
+    <t xml:space="preserve">11.3839340209961</t>
   </si>
   <si>
     <t xml:space="preserve">11.6650190353394</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4307823181152</t>
+    <t xml:space="preserve">11.4307832717896</t>
   </si>
   <si>
     <t xml:space="preserve">10.9623079299927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7280702590942</t>
+    <t xml:space="preserve">10.7280712127686</t>
   </si>
   <si>
     <t xml:space="preserve">11.1965446472168</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5713262557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3370885848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2902393341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7118673324585</t>
+    <t xml:space="preserve">11.5713243484497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3370876312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2902402877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7118682861328</t>
   </si>
   <si>
     <t xml:space="preserve">11.7587146759033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8055620193481</t>
+    <t xml:space="preserve">11.8055629730225</t>
   </si>
   <si>
     <t xml:space="preserve">11.0091552734375</t>
@@ -959,10 +959,10 @@
     <t xml:space="preserve">8.33884906768799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57308673858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31074047088623</t>
+    <t xml:space="preserve">8.57308578491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31074142456055</t>
   </si>
   <si>
     <t xml:space="preserve">8.45128345489502</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">8.44191455841064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32948017120361</t>
+    <t xml:space="preserve">8.32948112487793</t>
   </si>
   <si>
     <t xml:space="preserve">8.25452423095703</t>
@@ -986,19 +986,19 @@
     <t xml:space="preserve">8.47002220153809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32011222839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20767784118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0858736038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78604936599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49559497833252</t>
+    <t xml:space="preserve">8.32011127471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20767688751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08587265014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78605031967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49559545516968</t>
   </si>
   <si>
     <t xml:space="preserve">7.33631372451782</t>
@@ -1007,19 +1007,19 @@
     <t xml:space="preserve">7.23324918746948</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83289670944214</t>
+    <t xml:space="preserve">7.83289623260498</t>
   </si>
   <si>
     <t xml:space="preserve">7.90785312652588</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50496482849121</t>
+    <t xml:space="preserve">7.50496530532837</t>
   </si>
   <si>
     <t xml:space="preserve">7.37379169464111</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12081575393677</t>
+    <t xml:space="preserve">7.12081527709961</t>
   </si>
   <si>
     <t xml:space="preserve">7.28009700775146</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">6.98027276992798</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93342590332031</t>
+    <t xml:space="preserve">6.93342542648315</t>
   </si>
   <si>
     <t xml:space="preserve">7.06459856033325</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">7.0271201133728</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34568357467651</t>
+    <t xml:space="preserve">7.34568309783936</t>
   </si>
   <si>
     <t xml:space="preserve">7.5424427986145</t>
@@ -1046,25 +1046,25 @@
     <t xml:space="preserve">8.19830703735352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21704578399658</t>
+    <t xml:space="preserve">8.2170467376709</t>
   </si>
   <si>
     <t xml:space="preserve">8.65194320678711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46116161346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53747367858887</t>
+    <t xml:space="preserve">8.46116256713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53747463226318</t>
   </si>
   <si>
     <t xml:space="preserve">8.68056106567383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77595138549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84272575378418</t>
+    <t xml:space="preserve">8.77595233917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8427267074585</t>
   </si>
   <si>
     <t xml:space="preserve">8.72825527191162</t>
@@ -1076,16 +1076,16 @@
     <t xml:space="preserve">8.49931812286377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42300605773926</t>
+    <t xml:space="preserve">8.42300510406494</t>
   </si>
   <si>
     <t xml:space="preserve">8.39438915252686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60424900054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48977851867676</t>
+    <t xml:space="preserve">8.604248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48977947235107</t>
   </si>
   <si>
     <t xml:space="preserve">8.29899787902832</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">8.12729454040527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89835596084595</t>
+    <t xml:space="preserve">7.89835643768311</t>
   </si>
   <si>
     <t xml:space="preserve">8.10821628570557</t>
@@ -1115,16 +1115,16 @@
     <t xml:space="preserve">8.07959938049316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07005977630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92697381973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98420763015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30853748321533</t>
+    <t xml:space="preserve">8.07005882263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92697429656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98420858383179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30853652954102</t>
   </si>
   <si>
     <t xml:space="preserve">8.26084136962891</t>
@@ -1139,10 +1139,10 @@
     <t xml:space="preserve">8.03190326690674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96513032913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86019945144653</t>
+    <t xml:space="preserve">7.96513080596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86019992828369</t>
   </si>
   <si>
     <t xml:space="preserve">7.86973905563354</t>
@@ -1154,19 +1154,19 @@
     <t xml:space="preserve">7.91743516921997</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76480960845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72665357589722</t>
+    <t xml:space="preserve">7.76481008529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72665309906006</t>
   </si>
   <si>
     <t xml:space="preserve">7.65034103393555</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63126182556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65987873077393</t>
+    <t xml:space="preserve">7.63126230239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65987968444824</t>
   </si>
   <si>
     <t xml:space="preserve">8.16545104980469</t>
@@ -1178,16 +1178,16 @@
     <t xml:space="preserve">8.11775588989258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93651151657104</t>
+    <t xml:space="preserve">7.93651247024536</t>
   </si>
   <si>
     <t xml:space="preserve">8.19406795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23222351074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31807708740234</t>
+    <t xml:space="preserve">8.2322244644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31807518005371</t>
   </si>
   <si>
     <t xml:space="preserve">8.15591144561768</t>
@@ -1199,31 +1199,31 @@
     <t xml:space="preserve">8.25130176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35623264312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2417631149292</t>
+    <t xml:space="preserve">8.35623168945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24176406860352</t>
   </si>
   <si>
     <t xml:space="preserve">8.34669303894043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95559072494507</t>
+    <t xml:space="preserve">7.95559167861938</t>
   </si>
   <si>
     <t xml:space="preserve">7.77434825897217</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82204437255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97466897964478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01282501220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05098056793213</t>
+    <t xml:space="preserve">7.82204389572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97466850280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01282596588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05098152160645</t>
   </si>
   <si>
     <t xml:space="preserve">7.67895746231079</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">7.73619174957275</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6980357170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5167932510376</t>
+    <t xml:space="preserve">7.69803524017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51679372787476</t>
   </si>
   <si>
     <t xml:space="preserve">7.59310626983643</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">7.62172269821167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52633237838745</t>
+    <t xml:space="preserve">7.52633190155029</t>
   </si>
   <si>
     <t xml:space="preserve">7.34508991241455</t>
@@ -1265,25 +1265,25 @@
     <t xml:space="preserve">7.14476871490479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12569093704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23062086105347</t>
+    <t xml:space="preserve">7.12569046020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23062133789062</t>
   </si>
   <si>
     <t xml:space="preserve">7.1543083190918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24969911575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24015998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46909761428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41186285018921</t>
+    <t xml:space="preserve">7.24969863891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24016046524048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46909809112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41186332702637</t>
   </si>
   <si>
     <t xml:space="preserve">7.45001983642578</t>
@@ -1295,34 +1295,34 @@
     <t xml:space="preserve">7.39278507232666</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33555126190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61218357086182</t>
+    <t xml:space="preserve">7.3355507850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61218404769897</t>
   </si>
   <si>
     <t xml:space="preserve">7.90789556503296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94605112075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45955848693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70757436752319</t>
+    <t xml:space="preserve">7.94605159759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45955896377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70757484436035</t>
   </si>
   <si>
     <t xml:space="preserve">7.8792781829834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99374723434448</t>
+    <t xml:space="preserve">7.99374771118164</t>
   </si>
   <si>
     <t xml:space="preserve">7.75527000427246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81250476837158</t>
+    <t xml:space="preserve">7.81250381469727</t>
   </si>
   <si>
     <t xml:space="preserve">7.79342699050903</t>
@@ -1331,25 +1331,25 @@
     <t xml:space="preserve">7.80296611785889</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85066032409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74573135375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83158254623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66941833496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60264539718628</t>
+    <t xml:space="preserve">7.85065984725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74573087692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83158302307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66941785812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60264492034912</t>
   </si>
   <si>
     <t xml:space="preserve">7.58356666564941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88881778717041</t>
+    <t xml:space="preserve">7.88881826400757</t>
   </si>
   <si>
     <t xml:space="preserve">8.00328636169434</t>
@@ -1361,7 +1361,7 @@
     <t xml:space="preserve">7.3641676902771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10661315917969</t>
+    <t xml:space="preserve">7.10661268234253</t>
   </si>
   <si>
     <t xml:space="preserve">7.27831649780273</t>
@@ -1376,10 +1376,10 @@
     <t xml:space="preserve">7.50372648239136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98721361160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02589321136475</t>
+    <t xml:space="preserve">7.98721408843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02589225769043</t>
   </si>
   <si>
     <t xml:space="preserve">8.04523086547852</t>
@@ -1391,25 +1391,25 @@
     <t xml:space="preserve">8.07424163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12259006500244</t>
+    <t xml:space="preserve">8.12258911132812</t>
   </si>
   <si>
     <t xml:space="preserve">8.05490112304688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94853448867798</t>
+    <t xml:space="preserve">7.94853496551514</t>
   </si>
   <si>
     <t xml:space="preserve">8.06457138061523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08391094207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97754383087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93886423110962</t>
+    <t xml:space="preserve">8.08390998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97754430770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93886518478394</t>
   </si>
   <si>
     <t xml:space="preserve">7.79381895065308</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">7.68745088577271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63910245895386</t>
+    <t xml:space="preserve">7.63910293579102</t>
   </si>
   <si>
     <t xml:space="preserve">7.73579978942871</t>
@@ -1436,10 +1436,10 @@
     <t xml:space="preserve">7.90985584259033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85183715820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83249807357788</t>
+    <t xml:space="preserve">7.85183668136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83249759674072</t>
   </si>
   <si>
     <t xml:space="preserve">7.81315755844116</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">7.80348825454712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78414869308472</t>
+    <t xml:space="preserve">7.78414916992188</t>
   </si>
   <si>
     <t xml:space="preserve">7.6681113243103</t>
@@ -1460,13 +1460,13 @@
     <t xml:space="preserve">7.71646022796631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75514030456543</t>
+    <t xml:space="preserve">7.75513982772827</t>
   </si>
   <si>
     <t xml:space="preserve">7.74547004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86150646209717</t>
+    <t xml:space="preserve">7.86150693893433</t>
   </si>
   <si>
     <t xml:space="preserve">7.89051580429077</t>
@@ -1484,10 +1484,10 @@
     <t xml:space="preserve">8.09358024597168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1322603225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15159893035889</t>
+    <t xml:space="preserve">8.13225936889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1515998840332</t>
   </si>
   <si>
     <t xml:space="preserve">8.1129207611084</t>
@@ -1496,10 +1496,10 @@
     <t xml:space="preserve">8.03556251525879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92919540405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69712114334106</t>
+    <t xml:space="preserve">7.92919492721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69712066650391</t>
   </si>
   <si>
     <t xml:space="preserve">7.60042381286621</t>
@@ -1508,10 +1508,10 @@
     <t xml:space="preserve">7.88084602355957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55207490921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40702867507935</t>
+    <t xml:space="preserve">7.55207443237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40702819824219</t>
   </si>
   <si>
     <t xml:space="preserve">7.34900999069214</t>
@@ -1520,16 +1520,16 @@
     <t xml:space="preserve">7.37801933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43603801727295</t>
+    <t xml:space="preserve">7.43603754043579</t>
   </si>
   <si>
     <t xml:space="preserve">7.41669797897339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5230655670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36834907531738</t>
+    <t xml:space="preserve">7.52306604385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36834955215454</t>
   </si>
   <si>
     <t xml:space="preserve">7.542405128479</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">7.4843864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70679092407227</t>
+    <t xml:space="preserve">7.70679044723511</t>
   </si>
   <si>
     <t xml:space="preserve">7.64877223968506</t>
@@ -1556,10 +1556,10 @@
     <t xml:space="preserve">7.59075355529785</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95820331573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96787357330322</t>
+    <t xml:space="preserve">7.95820426940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96787405014038</t>
   </si>
   <si>
     <t xml:space="preserve">7.90018606185913</t>
@@ -1577,10 +1577,10 @@
     <t xml:space="preserve">8.19027900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29664516448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45136070251465</t>
+    <t xml:space="preserve">8.29664611816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45136165618896</t>
   </si>
   <si>
     <t xml:space="preserve">8.48037147521973</t>
@@ -1607,19 +1607,19 @@
     <t xml:space="preserve">8.50938034057617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42235279083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54805850982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55772876739502</t>
+    <t xml:space="preserve">8.4223518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54805946350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55772972106934</t>
   </si>
   <si>
     <t xml:space="preserve">8.52871990203857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68343544006348</t>
+    <t xml:space="preserve">8.68343448638916</t>
   </si>
   <si>
     <t xml:space="preserve">8.76079368591309</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">8.65442562103271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75112342834473</t>
+    <t xml:space="preserve">8.75112438201904</t>
   </si>
   <si>
     <t xml:space="preserve">8.70277500152588</t>
@@ -1652,10 +1652,10 @@
     <t xml:space="preserve">8.63508701324463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32565498352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31598567962646</t>
+    <t xml:space="preserve">8.32565402984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31598472595215</t>
   </si>
   <si>
     <t xml:space="preserve">8.30631542205811</t>
@@ -62798,7 +62798,7 @@
     </row>
     <row r="2317">
       <c r="A2317" s="1" t="n">
-        <v>45988.6912037037</v>
+        <v>45988.3333333333</v>
       </c>
       <c r="B2317" t="n">
         <v>21252</v>
@@ -62819,6 +62819,32 @@
         <v>743</v>
       </c>
       <c r="H2317" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2318">
+      <c r="A2318" s="1" t="n">
+        <v>45989.6909722222</v>
+      </c>
+      <c r="B2318" t="n">
+        <v>24039</v>
+      </c>
+      <c r="C2318" t="n">
+        <v>9.53999996185303</v>
+      </c>
+      <c r="D2318" t="n">
+        <v>9.4399995803833</v>
+      </c>
+      <c r="E2318" t="n">
+        <v>9.53999996185303</v>
+      </c>
+      <c r="F2318" t="n">
+        <v>9.53999996185303</v>
+      </c>
+      <c r="G2318" t="s">
+        <v>742</v>
+      </c>
+      <c r="H2318" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -44,28 +44,28 @@
     <t xml:space="preserve">FF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98565864562988</t>
+    <t xml:space="preserve">8.98565769195557</t>
   </si>
   <si>
     <t xml:space="preserve">9.08549785614014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24887275695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09457588195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12180328369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03104019165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95388984680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89943218231201</t>
+    <t xml:space="preserve">9.24887371063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09457492828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12180423736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03103923797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95388889312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89943313598633</t>
   </si>
   <si>
     <t xml:space="preserve">8.89489269256592</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">8.85858821868896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87674045562744</t>
+    <t xml:space="preserve">8.87674140930176</t>
   </si>
   <si>
     <t xml:space="preserve">8.76782321929932</t>
@@ -92,34 +92,34 @@
     <t xml:space="preserve">9.23072052001953</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11272811889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96750354766846</t>
+    <t xml:space="preserve">9.11272716522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96750545501709</t>
   </si>
   <si>
     <t xml:space="preserve">8.91304588317871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92212200164795</t>
+    <t xml:space="preserve">8.92212295532227</t>
   </si>
   <si>
     <t xml:space="preserve">9.00380992889404</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15810871124268</t>
+    <t xml:space="preserve">9.15810966491699</t>
   </si>
   <si>
     <t xml:space="preserve">9.16718578338623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43947887420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54839706420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62100696563721</t>
+    <t xml:space="preserve">9.43947696685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54839611053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62100791931152</t>
   </si>
   <si>
     <t xml:space="preserve">9.80253601074219</t>
@@ -128,46 +128,46 @@
     <t xml:space="preserve">9.71177101135254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56654930114746</t>
+    <t xml:space="preserve">9.56654834747314</t>
   </si>
   <si>
     <t xml:space="preserve">9.58470249176025</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5756254196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53024196624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50301456451416</t>
+    <t xml:space="preserve">9.57562637329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53024387359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50301361083984</t>
   </si>
   <si>
     <t xml:space="preserve">9.60285472869873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63915920257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79345798492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95683479309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93868255615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98406314849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73900032043457</t>
+    <t xml:space="preserve">9.63916015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79345893859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95683574676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93868160247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98406505584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73900127410889</t>
   </si>
   <si>
     <t xml:space="preserve">9.76623058319092</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74807643890381</t>
+    <t xml:space="preserve">9.74807548522949</t>
   </si>
   <si>
     <t xml:space="preserve">9.75715351104736</t>
@@ -182,16 +182,16 @@
     <t xml:space="preserve">9.70269393920898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72084712982178</t>
+    <t xml:space="preserve">9.72084808349609</t>
   </si>
   <si>
     <t xml:space="preserve">9.67546558380127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66639041900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63008308410645</t>
+    <t xml:space="preserve">9.66638946533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63008403778076</t>
   </si>
   <si>
     <t xml:space="preserve">9.65731334686279</t>
@@ -200,79 +200,79 @@
     <t xml:space="preserve">9.68454265594482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81161308288574</t>
+    <t xml:space="preserve">9.81161212921143</t>
   </si>
   <si>
     <t xml:space="preserve">9.8297643661499</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8479175567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83884048461914</t>
+    <t xml:space="preserve">9.84791851043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83884143829346</t>
   </si>
   <si>
     <t xml:space="preserve">9.72992420196533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78438377380371</t>
+    <t xml:space="preserve">9.78438186645508</t>
   </si>
   <si>
     <t xml:space="preserve">9.55747222900391</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34871578216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33963871002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27610397338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25794982910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19441604614258</t>
+    <t xml:space="preserve">9.34871482849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33963775634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27610206604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25795078277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19441509246826</t>
   </si>
   <si>
     <t xml:space="preserve">9.18533897399902</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41224956512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22164535522461</t>
+    <t xml:space="preserve">9.4122486114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22164344787598</t>
   </si>
   <si>
     <t xml:space="preserve">9.31240940093994</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26702690124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29425621032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28517818450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37594413757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36686611175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38502025604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45763206481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39409732818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48486137390137</t>
+    <t xml:space="preserve">9.2670259475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29425525665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28518009185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37594318389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36686706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38501930236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45763111114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39409828186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48486042022705</t>
   </si>
   <si>
     <t xml:space="preserve">9.49393749237061</t>
@@ -281,64 +281,64 @@
     <t xml:space="preserve">9.44855499267578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47578239440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23979568481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14903354644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21256828308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20349311828613</t>
+    <t xml:space="preserve">9.47578430175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23979759216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14903450012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21256923675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20349216461182</t>
   </si>
   <si>
     <t xml:space="preserve">9.13088035583496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13995552062988</t>
+    <t xml:space="preserve">9.1399564743042</t>
   </si>
   <si>
     <t xml:space="preserve">8.94027614593506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80412769317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75874710083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66798210144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62260150909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53183650970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35030841827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16877841949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98725175857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03263473510742</t>
+    <t xml:space="preserve">8.80412864685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75874614715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66798305511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62260055541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53183555603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35030746459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16877937316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98725032806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03263378143311</t>
   </si>
   <si>
     <t xml:space="preserve">8.12339687347412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25954532623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9418683052063</t>
+    <t xml:space="preserve">8.25954437255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94186878204346</t>
   </si>
   <si>
     <t xml:space="preserve">8.3049259185791</t>
@@ -347,46 +347,46 @@
     <t xml:space="preserve">8.21416091918945</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39569091796875</t>
+    <t xml:space="preserve">8.39568996429443</t>
   </si>
   <si>
     <t xml:space="preserve">8.57721710205078</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71336555480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53202247619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25706100463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44036769866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16540718078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07375240325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11958026885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98209857940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02792549133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62367630004883</t>
+    <t xml:space="preserve">8.71336460113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53202342987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25706195831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44036865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16540622711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07375144958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11957931518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98209762573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02792453765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62367725372314</t>
   </si>
   <si>
     <t xml:space="preserve">9.80698490142822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89863872528076</t>
+    <t xml:space="preserve">9.89863967895508</t>
   </si>
   <si>
     <t xml:space="preserve">9.9902925491333</t>
@@ -395,10 +395,10 @@
     <t xml:space="preserve">10.1736011505127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2652559280396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3569097518921</t>
+    <t xml:space="preserve">10.2652549743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3569107055664</t>
   </si>
   <si>
     <t xml:space="preserve">10.5402183532715</t>
@@ -407,19 +407,19 @@
     <t xml:space="preserve">10.631872177124</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8151788711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7235260009766</t>
+    <t xml:space="preserve">10.8151798248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7235250473022</t>
   </si>
   <si>
     <t xml:space="preserve">10.9068336486816</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9984884262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.090142250061</t>
+    <t xml:space="preserve">10.9984874725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0901432037354</t>
   </si>
   <si>
     <t xml:space="preserve">11.1817960739136</t>
@@ -428,25 +428,25 @@
     <t xml:space="preserve">11.2734508514404</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4567594528198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.365104675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4485635757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71533107757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79878997802734</t>
+    <t xml:space="preserve">11.4567575454712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3651027679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4485645294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79879093170166</t>
   </si>
   <si>
     <t xml:space="preserve">8.24886608123779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21123313903809</t>
+    <t xml:space="preserve">9.2112340927124</t>
   </si>
   <si>
     <t xml:space="preserve">9.30288791656494</t>
@@ -458,16 +458,16 @@
     <t xml:space="preserve">9.39454174041748</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76115798950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66950416564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57785034179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0361213684082</t>
+    <t xml:space="preserve">9.76115703582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66950511932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57785129547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0361204147339</t>
   </si>
   <si>
     <t xml:space="preserve">9.94446659088135</t>
@@ -476,16 +476,16 @@
     <t xml:space="preserve">9.82552433013916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73282909393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59379005432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96456432342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91821765899658</t>
+    <t xml:space="preserve">9.73283004760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59379100799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96456527709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91821575164795</t>
   </si>
   <si>
     <t xml:space="preserve">9.54744243621826</t>
@@ -497,43 +497,43 @@
     <t xml:space="preserve">10.1036043167114</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1499528884888</t>
+    <t xml:space="preserve">10.1499519348145</t>
   </si>
   <si>
     <t xml:space="preserve">10.1962976455688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77917671203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87187099456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.057258605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2889909744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4743804931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2426443099976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3816862106323</t>
+    <t xml:space="preserve">9.77917766571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87187004089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0572595596313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2889919281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4743795394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2426452636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.381685256958</t>
   </si>
   <si>
     <t xml:space="preserve">9.68648338317871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64013671875</t>
+    <t xml:space="preserve">9.64013576507568</t>
   </si>
   <si>
     <t xml:space="preserve">9.50109672546387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31571006774902</t>
+    <t xml:space="preserve">9.31570911407471</t>
   </si>
   <si>
     <t xml:space="preserve">9.23228549957275</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">9.17666816711426</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02835845947266</t>
+    <t xml:space="preserve">9.02835941314697</t>
   </si>
   <si>
     <t xml:space="preserve">8.95420360565186</t>
@@ -575,13 +575,13 @@
     <t xml:space="preserve">8.71320056915283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9912805557251</t>
+    <t xml:space="preserve">8.99128150939941</t>
   </si>
   <si>
     <t xml:space="preserve">8.7688159942627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89858722686768</t>
+    <t xml:space="preserve">8.89858818054199</t>
   </si>
   <si>
     <t xml:space="preserve">8.93566608428955</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">10.3353385925293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9841947555542</t>
+    <t xml:space="preserve">10.9841938018799</t>
   </si>
   <si>
     <t xml:space="preserve">11.0305414199829</t>
@@ -605,10 +605,10 @@
     <t xml:space="preserve">11.540355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5867023468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6330480575562</t>
+    <t xml:space="preserve">11.5867033004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6330490112305</t>
   </si>
   <si>
     <t xml:space="preserve">11.7257423400879</t>
@@ -620,13 +620,13 @@
     <t xml:space="preserve">11.9574766159058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1892108917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2819051742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3745994567871</t>
+    <t xml:space="preserve">12.1892118453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2819042205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3745985031128</t>
   </si>
   <si>
     <t xml:space="preserve">12.5136394500732</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">12.3282518386841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1428642272949</t>
+    <t xml:space="preserve">12.1428651809692</t>
   </si>
   <si>
     <t xml:space="preserve">12.0965185165405</t>
   </si>
   <si>
-    <t xml:space="preserve">12.555121421814</t>
+    <t xml:space="preserve">12.5551204681396</t>
   </si>
   <si>
     <t xml:space="preserve">12.5082750320435</t>
@@ -656,19 +656,19 @@
     <t xml:space="preserve">12.4145793914795</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7425117492676</t>
+    <t xml:space="preserve">12.7425127029419</t>
   </si>
   <si>
     <t xml:space="preserve">12.6956653594971</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2271900177002</t>
+    <t xml:space="preserve">12.2271909713745</t>
   </si>
   <si>
     <t xml:space="preserve">12.1803426742554</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3208837509155</t>
+    <t xml:space="preserve">12.3208847045898</t>
   </si>
   <si>
     <t xml:space="preserve">12.274037361145</t>
@@ -677,16 +677,16 @@
     <t xml:space="preserve">12.8362064361572</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7893590927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6019697189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9299020767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8830547332764</t>
+    <t xml:space="preserve">12.7893600463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6019687652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9299011230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8830537796021</t>
   </si>
   <si>
     <t xml:space="preserve">13.0704441070557</t>
@@ -710,10 +710,10 @@
     <t xml:space="preserve">15.2254276275635</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1317329406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7569522857666</t>
+    <t xml:space="preserve">15.1317319869995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7569532394409</t>
   </si>
   <si>
     <t xml:space="preserve">15.0380373001099</t>
@@ -722,19 +722,19 @@
     <t xml:space="preserve">15.1785802841187</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3191223144531</t>
+    <t xml:space="preserve">15.3191232681274</t>
   </si>
   <si>
     <t xml:space="preserve">14.8974952697754</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4596652984619</t>
+    <t xml:space="preserve">15.4596643447876</t>
   </si>
   <si>
     <t xml:space="preserve">15.4128189086914</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5533618927002</t>
+    <t xml:space="preserve">15.5533609390259</t>
   </si>
   <si>
     <t xml:space="preserve">16.0686798095703</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">17.0056324005127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.771390914917</t>
+    <t xml:space="preserve">16.7713928222656</t>
   </si>
   <si>
     <t xml:space="preserve">17.193021774292</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">16.7245464324951</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6308536529541</t>
+    <t xml:space="preserve">16.6308517456055</t>
   </si>
   <si>
     <t xml:space="preserve">16.5371570587158</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">16.584005355835</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2092247009277</t>
+    <t xml:space="preserve">16.2092227935791</t>
   </si>
   <si>
     <t xml:space="preserve">16.2560710906982</t>
@@ -785,22 +785,22 @@
     <t xml:space="preserve">16.3029193878174</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8344430923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1155319213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0218353271484</t>
+    <t xml:space="preserve">15.8344440460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1155300140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0218372344971</t>
   </si>
   <si>
     <t xml:space="preserve">16.1623764038086</t>
   </si>
   <si>
-    <t xml:space="preserve">15.974986076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7407503128052</t>
+    <t xml:space="preserve">15.9749870300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7407493591309</t>
   </si>
   <si>
     <t xml:space="preserve">16.4434604644775</t>
@@ -818,19 +818,19 @@
     <t xml:space="preserve">16.8182430267334</t>
   </si>
   <si>
-    <t xml:space="preserve">15.272274017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.084885597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.991189956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8038015365601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4758672714233</t>
+    <t xml:space="preserve">15.2722749710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0848846435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9911909103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8038005828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4758682250977</t>
   </si>
   <si>
     <t xml:space="preserve">14.382173538208</t>
@@ -848,10 +848,10 @@
     <t xml:space="preserve">13.960545539856</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2416315078735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1947822570801</t>
+    <t xml:space="preserve">14.2416305541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1947832107544</t>
   </si>
   <si>
     <t xml:space="preserve">14.0073928833008</t>
@@ -860,13 +860,13 @@
     <t xml:space="preserve">13.7263078689575</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1479368209839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4290199279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6164112091064</t>
+    <t xml:space="preserve">14.1479358673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4290208816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6164102554321</t>
   </si>
   <si>
     <t xml:space="preserve">13.7731561660767</t>
@@ -878,37 +878,37 @@
     <t xml:space="preserve">13.3046808242798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3983764648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0235948562622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1172914505005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9767484664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3677310943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0866470336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9929523468018</t>
+    <t xml:space="preserve">13.3983755111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0235958099365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1172904968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.976749420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3677320480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0866460800171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9929513931274</t>
   </si>
   <si>
     <t xml:space="preserve">11.8992576599121</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0398006439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1334953308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4776306152344</t>
+    <t xml:space="preserve">12.0397996902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1334943771362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4776296615601</t>
   </si>
   <si>
     <t xml:space="preserve">11.2433929443359</t>
@@ -917,10 +917,10 @@
     <t xml:space="preserve">11.3839349746704</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6650190353394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4307832717896</t>
+    <t xml:space="preserve">11.6650199890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4307823181152</t>
   </si>
   <si>
     <t xml:space="preserve">10.9623079299927</t>
@@ -932,28 +932,28 @@
     <t xml:space="preserve">11.1965446472168</t>
   </si>
   <si>
-    <t xml:space="preserve">11.571325302124</t>
+    <t xml:space="preserve">11.5713243484497</t>
   </si>
   <si>
     <t xml:space="preserve">11.3370885848999</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2902393341064</t>
+    <t xml:space="preserve">11.2902402877808</t>
   </si>
   <si>
     <t xml:space="preserve">11.7118673324585</t>
   </si>
   <si>
-    <t xml:space="preserve">11.758713722229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8055620193481</t>
+    <t xml:space="preserve">11.7587146759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8055629730225</t>
   </si>
   <si>
     <t xml:space="preserve">11.0091552734375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46318912506104</t>
+    <t xml:space="preserve">9.46318817138672</t>
   </si>
   <si>
     <t xml:space="preserve">8.33884906768799</t>
@@ -965,7 +965,7 @@
     <t xml:space="preserve">8.31074047088623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45128345489502</t>
+    <t xml:space="preserve">8.45128440856934</t>
   </si>
   <si>
     <t xml:space="preserve">8.61993408203125</t>
@@ -974,31 +974,31 @@
     <t xml:space="preserve">8.44191455841064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32948017120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25452518463135</t>
+    <t xml:space="preserve">8.32948112487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25452423095703</t>
   </si>
   <si>
     <t xml:space="preserve">8.43254470825195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47002220153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32011127471924</t>
+    <t xml:space="preserve">8.47002124786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32011032104492</t>
   </si>
   <si>
     <t xml:space="preserve">8.20767688751221</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08587265014648</t>
+    <t xml:space="preserve">8.0858736038208</t>
   </si>
   <si>
     <t xml:space="preserve">7.78604936599731</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49559497833252</t>
+    <t xml:space="preserve">7.49559545516968</t>
   </si>
   <si>
     <t xml:space="preserve">7.33631372451782</t>
@@ -1007,22 +1007,22 @@
     <t xml:space="preserve">7.23324918746948</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83289670944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90785217285156</t>
+    <t xml:space="preserve">7.83289623260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9078516960144</t>
   </si>
   <si>
     <t xml:space="preserve">7.50496482849121</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37379169464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12081575393677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28009700775146</t>
+    <t xml:space="preserve">7.37379217147827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12081527709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28009653091431</t>
   </si>
   <si>
     <t xml:space="preserve">6.98027276992798</t>
@@ -1031,25 +1031,25 @@
     <t xml:space="preserve">6.93342590332031</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06459856033325</t>
+    <t xml:space="preserve">7.06459808349609</t>
   </si>
   <si>
     <t xml:space="preserve">7.02712059020996</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34568357467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5424427986145</t>
+    <t xml:space="preserve">7.34568309783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54244232177734</t>
   </si>
   <si>
     <t xml:space="preserve">8.19830703735352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21704578399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65194320678711</t>
+    <t xml:space="preserve">8.2170467376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65194225311279</t>
   </si>
   <si>
     <t xml:space="preserve">8.46116161346436</t>
@@ -1058,7 +1058,7 @@
     <t xml:space="preserve">8.53747367858887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68056106567383</t>
+    <t xml:space="preserve">8.68056201934814</t>
   </si>
   <si>
     <t xml:space="preserve">8.77595138549805</t>
@@ -1067,16 +1067,16 @@
     <t xml:space="preserve">8.84272575378418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72825527191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66148281097412</t>
+    <t xml:space="preserve">8.72825622558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6614818572998</t>
   </si>
   <si>
     <t xml:space="preserve">8.49931812286377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42300605773926</t>
+    <t xml:space="preserve">8.42300510406494</t>
   </si>
   <si>
     <t xml:space="preserve">8.39438915252686</t>
@@ -1091,10 +1091,10 @@
     <t xml:space="preserve">8.29899787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12729454040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89835596084595</t>
+    <t xml:space="preserve">8.12729358673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89835643768311</t>
   </si>
   <si>
     <t xml:space="preserve">8.10821628570557</t>
@@ -1112,16 +1112,16 @@
     <t xml:space="preserve">8.06052017211914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07959938049316</t>
+    <t xml:space="preserve">8.07959842681885</t>
   </si>
   <si>
     <t xml:space="preserve">8.07005977630615</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92697381973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98420763015747</t>
+    <t xml:space="preserve">7.92697334289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98420810699463</t>
   </si>
   <si>
     <t xml:space="preserve">8.30853748321533</t>
@@ -1133,16 +1133,16 @@
     <t xml:space="preserve">8.27038097381592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18452835083008</t>
+    <t xml:space="preserve">8.18452930450439</t>
   </si>
   <si>
     <t xml:space="preserve">8.03190326690674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96513032913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86019945144653</t>
+    <t xml:space="preserve">7.96512985229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86019992828369</t>
   </si>
   <si>
     <t xml:space="preserve">7.86973905563354</t>
@@ -1157,13 +1157,13 @@
     <t xml:space="preserve">7.76480960845947</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72665357589722</t>
+    <t xml:space="preserve">7.72665309906006</t>
   </si>
   <si>
     <t xml:space="preserve">7.65034103393555</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63126182556152</t>
+    <t xml:space="preserve">7.63126230239868</t>
   </si>
   <si>
     <t xml:space="preserve">7.65987873077393</t>
@@ -1175,22 +1175,22 @@
     <t xml:space="preserve">8.32761383056641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11775588989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93651151657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19406795501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23222351074219</t>
+    <t xml:space="preserve">8.11775493621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9365119934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19406890869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2322244644165</t>
   </si>
   <si>
     <t xml:space="preserve">8.31807708740234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15591144561768</t>
+    <t xml:space="preserve">8.15591239929199</t>
   </si>
   <si>
     <t xml:space="preserve">8.22268486022949</t>
@@ -1214,10 +1214,10 @@
     <t xml:space="preserve">7.77434825897217</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82204437255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97466897964478</t>
+    <t xml:space="preserve">7.82204389572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97466850280762</t>
   </si>
   <si>
     <t xml:space="preserve">8.01282501220703</t>
@@ -1262,7 +1262,7 @@
     <t xml:space="preserve">7.18292570114136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14476871490479</t>
+    <t xml:space="preserve">7.14476919174194</t>
   </si>
   <si>
     <t xml:space="preserve">7.12569093704224</t>
@@ -1277,28 +1277,28 @@
     <t xml:space="preserve">7.24969911575317</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24015998840332</t>
+    <t xml:space="preserve">7.24016046524048</t>
   </si>
   <si>
     <t xml:space="preserve">7.46909761428833</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41186285018921</t>
+    <t xml:space="preserve">7.41186332702637</t>
   </si>
   <si>
     <t xml:space="preserve">7.45001983642578</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28785514831543</t>
+    <t xml:space="preserve">7.28785562515259</t>
   </si>
   <si>
     <t xml:space="preserve">7.39278507232666</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33555126190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61218357086182</t>
+    <t xml:space="preserve">7.3355507850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61218404769897</t>
   </si>
   <si>
     <t xml:space="preserve">7.90789556503296</t>
@@ -1313,13 +1313,13 @@
     <t xml:space="preserve">7.70757436752319</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8792781829834</t>
+    <t xml:space="preserve">7.87927865982056</t>
   </si>
   <si>
     <t xml:space="preserve">7.99374723434448</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75527000427246</t>
+    <t xml:space="preserve">7.75527048110962</t>
   </si>
   <si>
     <t xml:space="preserve">7.81250476837158</t>
@@ -1334,7 +1334,7 @@
     <t xml:space="preserve">7.85066032409668</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74573135375977</t>
+    <t xml:space="preserve">7.74573087692261</t>
   </si>
   <si>
     <t xml:space="preserve">7.83158254623413</t>
@@ -1343,7 +1343,7 @@
     <t xml:space="preserve">7.66941833496094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60264539718628</t>
+    <t xml:space="preserve">7.60264492034912</t>
   </si>
   <si>
     <t xml:space="preserve">7.58356666564941</t>
@@ -1361,13 +1361,13 @@
     <t xml:space="preserve">7.3641676902771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10661315917969</t>
+    <t xml:space="preserve">7.10661268234253</t>
   </si>
   <si>
     <t xml:space="preserve">7.27831649780273</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08753490447998</t>
+    <t xml:space="preserve">7.08753442764282</t>
   </si>
   <si>
     <t xml:space="preserve">7.05891799926758</t>
@@ -62879,7 +62879,7 @@
     </row>
     <row r="2320">
       <c r="A2320" s="1" t="n">
-        <v>45993.6909722222</v>
+        <v>45993.3333333333</v>
       </c>
       <c r="B2320" t="n">
         <v>18119</v>
@@ -62900,6 +62900,32 @@
         <v>744</v>
       </c>
       <c r="H2320" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2321">
+      <c r="A2321" s="1" t="n">
+        <v>45994.6910416667</v>
+      </c>
+      <c r="B2321" t="n">
+        <v>17710</v>
+      </c>
+      <c r="C2321" t="n">
+        <v>9.5600004196167</v>
+      </c>
+      <c r="D2321" t="n">
+        <v>9.35999965667725</v>
+      </c>
+      <c r="E2321" t="n">
+        <v>9.46000003814697</v>
+      </c>
+      <c r="F2321" t="n">
+        <v>9.34000015258789</v>
+      </c>
+      <c r="G2321" t="s">
+        <v>736</v>
+      </c>
+      <c r="H2321" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">FF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98565769195557</t>
+    <t xml:space="preserve">8.98565673828125</t>
   </si>
   <si>
     <t xml:space="preserve">9.08549785614014</t>
@@ -53,67 +53,67 @@
     <t xml:space="preserve">9.24887371063232</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09457492828369</t>
+    <t xml:space="preserve">9.09457588195801</t>
   </si>
   <si>
     <t xml:space="preserve">9.12180423736572</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03103923797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95388889312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89943313598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89489269256592</t>
+    <t xml:space="preserve">9.03104019165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95388984680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8994312286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8948917388916</t>
   </si>
   <si>
     <t xml:space="preserve">8.84951114654541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85858821868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87674140930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76782321929932</t>
+    <t xml:space="preserve">8.85858917236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87674045562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76782417297363</t>
   </si>
   <si>
     <t xml:space="preserve">8.8676643371582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04919242858887</t>
+    <t xml:space="preserve">9.04919338226318</t>
   </si>
   <si>
     <t xml:space="preserve">9.23072052001953</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11272716522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96750545501709</t>
+    <t xml:space="preserve">9.11272621154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96750354766846</t>
   </si>
   <si>
     <t xml:space="preserve">8.91304588317871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92212295532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00380992889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15810966491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16718578338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43947696685791</t>
+    <t xml:space="preserve">8.92212200164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00381183624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15810871124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16718673706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43947887420654</t>
   </si>
   <si>
     <t xml:space="preserve">9.54839611053467</t>
@@ -125,19 +125,19 @@
     <t xml:space="preserve">9.80253601074219</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71177101135254</t>
+    <t xml:space="preserve">9.71177196502686</t>
   </si>
   <si>
     <t xml:space="preserve">9.56654834747314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58470249176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57562637329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53024387359619</t>
+    <t xml:space="preserve">9.58470153808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5756254196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53024196624756</t>
   </si>
   <si>
     <t xml:space="preserve">9.50301361083984</t>
@@ -146,76 +146,76 @@
     <t xml:space="preserve">9.60285472869873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63916015625</t>
+    <t xml:space="preserve">9.63916110992432</t>
   </si>
   <si>
     <t xml:space="preserve">9.79345893859863</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95683574676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93868160247803</t>
+    <t xml:space="preserve">9.95683479309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93868064880371</t>
   </si>
   <si>
     <t xml:space="preserve">9.98406505584717</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73900127410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76623058319092</t>
+    <t xml:space="preserve">9.73900032043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7662296295166</t>
   </si>
   <si>
     <t xml:space="preserve">9.74807548522949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75715351104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64823627471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82068824768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70269393920898</t>
+    <t xml:space="preserve">9.75715255737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64823722839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82068729400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7026948928833</t>
   </si>
   <si>
     <t xml:space="preserve">9.72084808349609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67546558380127</t>
+    <t xml:space="preserve">9.67546463012695</t>
   </si>
   <si>
     <t xml:space="preserve">9.66638946533203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63008403778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65731334686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68454265594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81161212921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8297643661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84791851043701</t>
+    <t xml:space="preserve">9.63008308410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65731239318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68454170227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81161308288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82976531982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8479175567627</t>
   </si>
   <si>
     <t xml:space="preserve">9.83884143829346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72992420196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78438186645508</t>
+    <t xml:space="preserve">9.72992324829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78438472747803</t>
   </si>
   <si>
     <t xml:space="preserve">9.55747222900391</t>
@@ -227,82 +227,82 @@
     <t xml:space="preserve">9.33963775634766</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27610206604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25795078277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19441509246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18533897399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4122486114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22164344787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31240940093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2670259475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29425525665283</t>
+    <t xml:space="preserve">9.27610397338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25794982910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19441604614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18533802032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41224956512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22164440155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31240749359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26702690124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29425621032715</t>
   </si>
   <si>
     <t xml:space="preserve">9.28518009185791</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37594318389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36686706542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38501930236816</t>
+    <t xml:space="preserve">9.37594413757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.366868019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3850212097168</t>
   </si>
   <si>
     <t xml:space="preserve">9.45763111114502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39409828186035</t>
+    <t xml:space="preserve">9.39409637451172</t>
   </si>
   <si>
     <t xml:space="preserve">9.48486042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49393749237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44855499267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47578430175781</t>
+    <t xml:space="preserve">9.49393653869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4485559463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4757833480835</t>
   </si>
   <si>
     <t xml:space="preserve">9.23979759216309</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14903450012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21256923675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20349216461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13088035583496</t>
+    <t xml:space="preserve">9.14903354644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21256828308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20349311828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13087940216064</t>
   </si>
   <si>
     <t xml:space="preserve">9.1399564743042</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94027614593506</t>
+    <t xml:space="preserve">8.94027519226074</t>
   </si>
   <si>
     <t xml:space="preserve">8.80412864685059</t>
@@ -311,7 +311,7 @@
     <t xml:space="preserve">8.75874614715576</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66798305511475</t>
+    <t xml:space="preserve">8.66798400878906</t>
   </si>
   <si>
     <t xml:space="preserve">8.62260055541992</t>
@@ -323,28 +323,28 @@
     <t xml:space="preserve">8.35030746459961</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16877937316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98725032806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03263378143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12339687347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25954437255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94186878204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3049259185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21416091918945</t>
+    <t xml:space="preserve">8.16878032684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98725175857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03263473510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12339782714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25954627990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9418683052063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30492687225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21416187286377</t>
   </si>
   <si>
     <t xml:space="preserve">8.39568996429443</t>
@@ -359,22 +359,22 @@
     <t xml:space="preserve">9.53202342987061</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25706195831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44036865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16540622711182</t>
+    <t xml:space="preserve">9.25706100463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44036960601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16540718078613</t>
   </si>
   <si>
     <t xml:space="preserve">9.07375144958496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11957931518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98209762573242</t>
+    <t xml:space="preserve">9.11958026885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98209857940674</t>
   </si>
   <si>
     <t xml:space="preserve">9.02792453765869</t>
@@ -383,43 +383,43 @@
     <t xml:space="preserve">9.62367725372314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80698490142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89863967895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9902925491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1736011505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2652549743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3569107055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5402183532715</t>
+    <t xml:space="preserve">9.80698585510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89863872528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99029350280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1736030578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2652540206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3569097518921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5402173995972</t>
   </si>
   <si>
     <t xml:space="preserve">10.631872177124</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8151798248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7235250473022</t>
+    <t xml:space="preserve">10.8151788711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7235260009766</t>
   </si>
   <si>
     <t xml:space="preserve">10.9068336486816</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9984874725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0901432037354</t>
+    <t xml:space="preserve">10.9984884262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0901412963867</t>
   </si>
   <si>
     <t xml:space="preserve">11.1817960739136</t>
@@ -428,13 +428,13 @@
     <t xml:space="preserve">11.2734508514404</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4567575454712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3651027679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4485645294189</t>
+    <t xml:space="preserve">11.4567584991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3651037216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4485635757446</t>
   </si>
   <si>
     <t xml:space="preserve">9.71533203125</t>
@@ -443,16 +443,16 @@
     <t xml:space="preserve">8.79879093170166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24886608123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2112340927124</t>
+    <t xml:space="preserve">8.24886512756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21123313903809</t>
   </si>
   <si>
     <t xml:space="preserve">9.30288791656494</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03709030151367</t>
+    <t xml:space="preserve">9.03709125518799</t>
   </si>
   <si>
     <t xml:space="preserve">9.39454174041748</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">9.66950511932373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57785129547119</t>
+    <t xml:space="preserve">9.57784938812256</t>
   </si>
   <si>
     <t xml:space="preserve">10.0361204147339</t>
@@ -473,25 +473,25 @@
     <t xml:space="preserve">9.94446659088135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82552433013916</t>
+    <t xml:space="preserve">9.82552528381348</t>
   </si>
   <si>
     <t xml:space="preserve">9.73283004760742</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59379100799561</t>
+    <t xml:space="preserve">9.59378910064697</t>
   </si>
   <si>
     <t xml:space="preserve">9.96456527709961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91821575164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54744243621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.010910987854</t>
+    <t xml:space="preserve">9.91821670532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54744338989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0109119415283</t>
   </si>
   <si>
     <t xml:space="preserve">10.1036043167114</t>
@@ -500,22 +500,22 @@
     <t xml:space="preserve">10.1499519348145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1962976455688</t>
+    <t xml:space="preserve">10.1962985992432</t>
   </si>
   <si>
     <t xml:space="preserve">9.77917766571045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87187004089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0572595596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2889919281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4743795394897</t>
+    <t xml:space="preserve">9.87186908721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.057258605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2889928817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4743804931641</t>
   </si>
   <si>
     <t xml:space="preserve">10.2426452636719</t>
@@ -527,25 +527,25 @@
     <t xml:space="preserve">9.68648338317871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64013576507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50109672546387</t>
+    <t xml:space="preserve">9.64013671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50109767913818</t>
   </si>
   <si>
     <t xml:space="preserve">9.31570911407471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23228549957275</t>
+    <t xml:space="preserve">9.23228454589844</t>
   </si>
   <si>
     <t xml:space="preserve">9.1952075958252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25082302093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26936149597168</t>
+    <t xml:space="preserve">9.25082397460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.269362449646</t>
   </si>
   <si>
     <t xml:space="preserve">9.21374607086182</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">9.04689693450928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12105369567871</t>
+    <t xml:space="preserve">9.12105178833008</t>
   </si>
   <si>
     <t xml:space="preserve">9.06543636322021</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">8.7688159942627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89858818054199</t>
+    <t xml:space="preserve">8.89858722686768</t>
   </si>
   <si>
     <t xml:space="preserve">8.93566608428955</t>
@@ -590,31 +590,31 @@
     <t xml:space="preserve">10.3353385925293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9841938018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0305414199829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2159290313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4940099716187</t>
+    <t xml:space="preserve">10.9841947555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0305404663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2159280776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4940090179443</t>
   </si>
   <si>
     <t xml:space="preserve">11.540355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5867033004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6330490112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7257423400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9111309051514</t>
+    <t xml:space="preserve">11.5867023468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6330499649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7257432937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9111318588257</t>
   </si>
   <si>
     <t xml:space="preserve">11.9574766159058</t>
@@ -623,10 +623,10 @@
     <t xml:space="preserve">12.1892118453979</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2819042205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3745985031128</t>
+    <t xml:space="preserve">12.2819032669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3745994567871</t>
   </si>
   <si>
     <t xml:space="preserve">12.5136394500732</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">12.3282518386841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1428651809692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0965185165405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5551204681396</t>
+    <t xml:space="preserve">12.1428642272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0965175628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.555121421814</t>
   </si>
   <si>
     <t xml:space="preserve">12.5082750320435</t>
@@ -653,22 +653,22 @@
     <t xml:space="preserve">12.4614267349243</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4145793914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7425127029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6956653594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2271909713745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1803426742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3208847045898</t>
+    <t xml:space="preserve">12.4145784378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7425117492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6956644058228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2271890640259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1803417205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3208837509155</t>
   </si>
   <si>
     <t xml:space="preserve">12.274037361145</t>
@@ -677,13 +677,13 @@
     <t xml:space="preserve">12.8362064361572</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7893600463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6019687652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9299011230469</t>
+    <t xml:space="preserve">12.7893590927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6019697189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9299020767212</t>
   </si>
   <si>
     <t xml:space="preserve">12.8830537796021</t>
@@ -692,19 +692,19 @@
     <t xml:space="preserve">13.0704441070557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.679461479187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8668518066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0542411804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3353261947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5695629119873</t>
+    <t xml:space="preserve">13.6794624328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8668508529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0542402267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3353252410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5695638656616</t>
   </si>
   <si>
     <t xml:space="preserve">15.2254276275635</t>
@@ -722,40 +722,40 @@
     <t xml:space="preserve">15.1785802841187</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3191232681274</t>
+    <t xml:space="preserve">15.3191223144531</t>
   </si>
   <si>
     <t xml:space="preserve">14.8974952697754</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4596643447876</t>
+    <t xml:space="preserve">15.4596662521362</t>
   </si>
   <si>
     <t xml:space="preserve">15.4128189086914</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5533609390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0686798095703</t>
+    <t xml:space="preserve">15.5533599853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0686817169189</t>
   </si>
   <si>
     <t xml:space="preserve">16.8650894165039</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0056324005127</t>
+    <t xml:space="preserve">17.0056304931641</t>
   </si>
   <si>
     <t xml:space="preserve">16.7713928222656</t>
   </si>
   <si>
-    <t xml:space="preserve">17.193021774292</t>
+    <t xml:space="preserve">17.1930198669434</t>
   </si>
   <si>
     <t xml:space="preserve">17.0524806976318</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9587841033936</t>
+    <t xml:space="preserve">16.9587860107422</t>
   </si>
   <si>
     <t xml:space="preserve">16.7245464324951</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">16.2092227935791</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2560710906982</t>
+    <t xml:space="preserve">16.2560729980469</t>
   </si>
   <si>
     <t xml:space="preserve">17.1461734771729</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">16.3029193878174</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8344440460205</t>
+    <t xml:space="preserve">15.8344430923462</t>
   </si>
   <si>
     <t xml:space="preserve">16.1155300140381</t>
@@ -797,13 +797,13 @@
     <t xml:space="preserve">16.1623764038086</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9749870300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7407493591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4434604644775</t>
+    <t xml:space="preserve">15.9749879837036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7407484054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4434623718262</t>
   </si>
   <si>
     <t xml:space="preserve">16.9119358062744</t>
@@ -818,16 +818,16 @@
     <t xml:space="preserve">16.8182430267334</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2722749710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0848846435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9911909103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8038005828857</t>
+    <t xml:space="preserve">15.272274017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0848865509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.991189956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8038015365601</t>
   </si>
   <si>
     <t xml:space="preserve">14.4758682250977</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">14.1010885238647</t>
   </si>
   <si>
-    <t xml:space="preserve">14.288477897644</t>
+    <t xml:space="preserve">14.2884788513184</t>
   </si>
   <si>
     <t xml:space="preserve">14.5227155685425</t>
@@ -848,16 +848,16 @@
     <t xml:space="preserve">13.960545539856</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2416305541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1947832107544</t>
+    <t xml:space="preserve">14.2416315078735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1947822570801</t>
   </si>
   <si>
     <t xml:space="preserve">14.0073928833008</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7263078689575</t>
+    <t xml:space="preserve">13.7263088226318</t>
   </si>
   <si>
     <t xml:space="preserve">14.1479358673096</t>
@@ -878,37 +878,37 @@
     <t xml:space="preserve">13.3046808242798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3983755111694</t>
+    <t xml:space="preserve">13.3983764648438</t>
   </si>
   <si>
     <t xml:space="preserve">13.0235958099365</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1172904968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.976749420166</t>
+    <t xml:space="preserve">13.1172924041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9767484664917</t>
   </si>
   <si>
     <t xml:space="preserve">12.3677320480347</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0866460800171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9929513931274</t>
+    <t xml:space="preserve">12.0866470336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9929523468018</t>
   </si>
   <si>
     <t xml:space="preserve">11.8992576599121</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0397996902466</t>
+    <t xml:space="preserve">12.0398006439209</t>
   </si>
   <si>
     <t xml:space="preserve">12.1334943771362</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4776296615601</t>
+    <t xml:space="preserve">11.4776306152344</t>
   </si>
   <si>
     <t xml:space="preserve">11.2433929443359</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">11.3839349746704</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6650199890137</t>
+    <t xml:space="preserve">11.6650190353394</t>
   </si>
   <si>
     <t xml:space="preserve">11.4307823181152</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">11.1965446472168</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5713243484497</t>
+    <t xml:space="preserve">11.5713262557983</t>
   </si>
   <si>
     <t xml:space="preserve">11.3370885848999</t>
@@ -950,10 +950,10 @@
     <t xml:space="preserve">11.8055629730225</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0091552734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46318817138672</t>
+    <t xml:space="preserve">11.0091562271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46318912506104</t>
   </si>
   <si>
     <t xml:space="preserve">8.33884906768799</t>
@@ -962,10 +962,10 @@
     <t xml:space="preserve">8.57308673858643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31074047088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45128440856934</t>
+    <t xml:space="preserve">8.31074142456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45128345489502</t>
   </si>
   <si>
     <t xml:space="preserve">8.61993408203125</t>
@@ -974,16 +974,16 @@
     <t xml:space="preserve">8.44191455841064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32948112487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25452423095703</t>
+    <t xml:space="preserve">8.32948017120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25452518463135</t>
   </si>
   <si>
     <t xml:space="preserve">8.43254470825195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47002124786377</t>
+    <t xml:space="preserve">8.47002220153809</t>
   </si>
   <si>
     <t xml:space="preserve">8.32011032104492</t>
@@ -992,55 +992,55 @@
     <t xml:space="preserve">8.20767688751221</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0858736038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78604936599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49559545516968</t>
+    <t xml:space="preserve">8.08587265014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78604984283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49559497833252</t>
   </si>
   <si>
     <t xml:space="preserve">7.33631372451782</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23324918746948</t>
+    <t xml:space="preserve">7.23324966430664</t>
   </si>
   <si>
     <t xml:space="preserve">7.83289623260498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9078516960144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50496482849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37379217147827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12081527709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28009653091431</t>
+    <t xml:space="preserve">7.90785217285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50496530532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37379169464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12081575393677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28009700775146</t>
   </si>
   <si>
     <t xml:space="preserve">6.98027276992798</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93342590332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06459808349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02712059020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34568309783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54244232177734</t>
+    <t xml:space="preserve">6.93342542648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06459856033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0271201133728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34568357467651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54244327545166</t>
   </si>
   <si>
     <t xml:space="preserve">8.19830703735352</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">8.2170467376709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65194225311279</t>
+    <t xml:space="preserve">8.65194320678711</t>
   </si>
   <si>
     <t xml:space="preserve">8.46116161346436</t>
@@ -1058,7 +1058,7 @@
     <t xml:space="preserve">8.53747367858887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68056201934814</t>
+    <t xml:space="preserve">8.68056106567383</t>
   </si>
   <si>
     <t xml:space="preserve">8.77595138549805</t>
@@ -1070,19 +1070,19 @@
     <t xml:space="preserve">8.72825622558594</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6614818572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49931812286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42300510406494</t>
+    <t xml:space="preserve">8.66148281097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49931716918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42300605773926</t>
   </si>
   <si>
     <t xml:space="preserve">8.39438915252686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60424900054932</t>
+    <t xml:space="preserve">8.604248046875</t>
   </si>
   <si>
     <t xml:space="preserve">8.48977851867676</t>
@@ -1091,46 +1091,46 @@
     <t xml:space="preserve">8.29899787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12729358673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89835643768311</t>
+    <t xml:space="preserve">8.12729454040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89835596084595</t>
   </si>
   <si>
     <t xml:space="preserve">8.10821628570557</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84112215042114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33715343475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2036075592041</t>
+    <t xml:space="preserve">7.8411226272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33715438842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20360660552979</t>
   </si>
   <si>
     <t xml:space="preserve">8.06052017211914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07959842681885</t>
+    <t xml:space="preserve">8.07959938049316</t>
   </si>
   <si>
     <t xml:space="preserve">8.07005977630615</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92697334289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98420810699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30853748321533</t>
+    <t xml:space="preserve">7.92697381973267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98420763015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30853652954102</t>
   </si>
   <si>
     <t xml:space="preserve">8.26084136962891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27038097381592</t>
+    <t xml:space="preserve">8.2703800201416</t>
   </si>
   <si>
     <t xml:space="preserve">8.18452930450439</t>
@@ -1139,19 +1139,19 @@
     <t xml:space="preserve">8.03190326690674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96512985229492</t>
+    <t xml:space="preserve">7.96513032913208</t>
   </si>
   <si>
     <t xml:space="preserve">7.86019992828369</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86973905563354</t>
+    <t xml:space="preserve">7.8697395324707</t>
   </si>
   <si>
     <t xml:space="preserve">7.71711397171021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91743516921997</t>
+    <t xml:space="preserve">7.91743421554565</t>
   </si>
   <si>
     <t xml:space="preserve">7.76480960845947</t>
@@ -1160,34 +1160,34 @@
     <t xml:space="preserve">7.72665309906006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65034103393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63126230239868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65987873077393</t>
+    <t xml:space="preserve">7.65034055709839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63126182556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65987920761108</t>
   </si>
   <si>
     <t xml:space="preserve">8.16545104980469</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32761383056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11775493621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9365119934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19406890869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2322244644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31807708740234</t>
+    <t xml:space="preserve">8.32761478424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11775588989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93651151657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19406795501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23222351074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31807613372803</t>
   </si>
   <si>
     <t xml:space="preserve">8.15591239929199</t>
@@ -1217,16 +1217,16 @@
     <t xml:space="preserve">7.82204389572144</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97466850280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01282501220703</t>
+    <t xml:space="preserve">7.97466802597046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01282405853271</t>
   </si>
   <si>
     <t xml:space="preserve">8.05098056793213</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67895746231079</t>
+    <t xml:space="preserve">7.67895793914795</t>
   </si>
   <si>
     <t xml:space="preserve">7.73619174957275</t>
@@ -1235,16 +1235,16 @@
     <t xml:space="preserve">7.6980357170105</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5167932510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59310626983643</t>
+    <t xml:space="preserve">7.51679372787476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59310579299927</t>
   </si>
   <si>
     <t xml:space="preserve">7.44048070907593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5358715057373</t>
+    <t xml:space="preserve">7.53587198257446</t>
   </si>
   <si>
     <t xml:space="preserve">7.62172269821167</t>
@@ -1271,7 +1271,7 @@
     <t xml:space="preserve">7.23062086105347</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1543083190918</t>
+    <t xml:space="preserve">7.15430784225464</t>
   </si>
   <si>
     <t xml:space="preserve">7.24969911575317</t>
@@ -1286,10 +1286,10 @@
     <t xml:space="preserve">7.41186332702637</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45001983642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28785562515259</t>
+    <t xml:space="preserve">7.45001935958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28785514831543</t>
   </si>
   <si>
     <t xml:space="preserve">7.39278507232666</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">7.3355507850647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61218404769897</t>
+    <t xml:space="preserve">7.61218357086182</t>
   </si>
   <si>
     <t xml:space="preserve">7.90789556503296</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">7.94605112075806</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45955848693848</t>
+    <t xml:space="preserve">7.45955896377563</t>
   </si>
   <si>
     <t xml:space="preserve">7.70757436752319</t>
@@ -1331,13 +1331,13 @@
     <t xml:space="preserve">7.80296611785889</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85066032409668</t>
+    <t xml:space="preserve">7.85066080093384</t>
   </si>
   <si>
     <t xml:space="preserve">7.74573087692261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83158254623413</t>
+    <t xml:space="preserve">7.83158349990845</t>
   </si>
   <si>
     <t xml:space="preserve">7.66941833496094</t>
@@ -1358,28 +1358,28 @@
     <t xml:space="preserve">7.78388738632202</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3641676902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10661268234253</t>
+    <t xml:space="preserve">7.36416816711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10661315917969</t>
   </si>
   <si>
     <t xml:space="preserve">7.27831649780273</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08753442764282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05891799926758</t>
+    <t xml:space="preserve">7.08753490447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05891752243042</t>
   </si>
   <si>
     <t xml:space="preserve">7.50372648239136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98721361160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02589321136475</t>
+    <t xml:space="preserve">7.98721408843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02589225769043</t>
   </si>
   <si>
     <t xml:space="preserve">8.04523086547852</t>
@@ -1391,25 +1391,25 @@
     <t xml:space="preserve">8.07424163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12259006500244</t>
+    <t xml:space="preserve">8.12258911132812</t>
   </si>
   <si>
     <t xml:space="preserve">8.05490112304688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94853448867798</t>
+    <t xml:space="preserve">7.94853496551514</t>
   </si>
   <si>
     <t xml:space="preserve">8.06457138061523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08391094207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97754383087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93886423110962</t>
+    <t xml:space="preserve">8.08390998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97754430770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93886518478394</t>
   </si>
   <si>
     <t xml:space="preserve">7.79381895065308</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">7.68745088577271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63910245895386</t>
+    <t xml:space="preserve">7.63910293579102</t>
   </si>
   <si>
     <t xml:space="preserve">7.73579978942871</t>
@@ -1436,10 +1436,10 @@
     <t xml:space="preserve">7.90985584259033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85183715820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83249807357788</t>
+    <t xml:space="preserve">7.85183668136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83249759674072</t>
   </si>
   <si>
     <t xml:space="preserve">7.81315755844116</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">7.80348825454712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78414869308472</t>
+    <t xml:space="preserve">7.78414916992188</t>
   </si>
   <si>
     <t xml:space="preserve">7.6681113243103</t>
@@ -1460,13 +1460,13 @@
     <t xml:space="preserve">7.71646022796631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75514030456543</t>
+    <t xml:space="preserve">7.75513982772827</t>
   </si>
   <si>
     <t xml:space="preserve">7.74547004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86150646209717</t>
+    <t xml:space="preserve">7.86150693893433</t>
   </si>
   <si>
     <t xml:space="preserve">7.89051580429077</t>
@@ -1484,10 +1484,10 @@
     <t xml:space="preserve">8.09358024597168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1322603225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15159893035889</t>
+    <t xml:space="preserve">8.13225936889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1515998840332</t>
   </si>
   <si>
     <t xml:space="preserve">8.1129207611084</t>
@@ -1496,10 +1496,10 @@
     <t xml:space="preserve">8.03556251525879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92919540405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69712114334106</t>
+    <t xml:space="preserve">7.92919492721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69712066650391</t>
   </si>
   <si>
     <t xml:space="preserve">7.60042381286621</t>
@@ -1508,10 +1508,10 @@
     <t xml:space="preserve">7.88084602355957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55207490921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40702867507935</t>
+    <t xml:space="preserve">7.55207443237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40702819824219</t>
   </si>
   <si>
     <t xml:space="preserve">7.34900999069214</t>
@@ -1520,16 +1520,16 @@
     <t xml:space="preserve">7.37801933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43603801727295</t>
+    <t xml:space="preserve">7.43603754043579</t>
   </si>
   <si>
     <t xml:space="preserve">7.41669797897339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5230655670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36834907531738</t>
+    <t xml:space="preserve">7.52306604385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36834955215454</t>
   </si>
   <si>
     <t xml:space="preserve">7.542405128479</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">7.4843864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70679092407227</t>
+    <t xml:space="preserve">7.70679044723511</t>
   </si>
   <si>
     <t xml:space="preserve">7.64877223968506</t>
@@ -1556,10 +1556,10 @@
     <t xml:space="preserve">7.59075355529785</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95820331573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96787357330322</t>
+    <t xml:space="preserve">7.95820426940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96787405014038</t>
   </si>
   <si>
     <t xml:space="preserve">7.90018606185913</t>
@@ -1577,10 +1577,10 @@
     <t xml:space="preserve">8.19027900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29664516448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45136070251465</t>
+    <t xml:space="preserve">8.29664611816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45136165618896</t>
   </si>
   <si>
     <t xml:space="preserve">8.48037147521973</t>
@@ -1607,19 +1607,19 @@
     <t xml:space="preserve">8.50938034057617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42235279083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54805850982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55772876739502</t>
+    <t xml:space="preserve">8.4223518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54805946350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55772972106934</t>
   </si>
   <si>
     <t xml:space="preserve">8.52871990203857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68343544006348</t>
+    <t xml:space="preserve">8.68343448638916</t>
   </si>
   <si>
     <t xml:space="preserve">8.76079368591309</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">8.65442562103271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75112342834473</t>
+    <t xml:space="preserve">8.75112438201904</t>
   </si>
   <si>
     <t xml:space="preserve">8.70277500152588</t>
@@ -1652,10 +1652,10 @@
     <t xml:space="preserve">8.63508701324463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32565498352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31598567962646</t>
+    <t xml:space="preserve">8.32565402984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31598472595215</t>
   </si>
   <si>
     <t xml:space="preserve">8.30631542205811</t>
@@ -62905,7 +62905,7 @@
     </row>
     <row r="2321">
       <c r="A2321" s="1" t="n">
-        <v>45994.6910416667</v>
+        <v>45994.3333333333</v>
       </c>
       <c r="B2321" t="n">
         <v>17710</v>
@@ -62914,7 +62914,7 @@
         <v>9.5600004196167</v>
       </c>
       <c r="D2321" t="n">
-        <v>9.35999965667725</v>
+        <v>9.31999969482422</v>
       </c>
       <c r="E2321" t="n">
         <v>9.46000003814697</v>
@@ -62926,6 +62926,32 @@
         <v>736</v>
       </c>
       <c r="H2321" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2322">
+      <c r="A2322" s="1" t="n">
+        <v>45995.6912152778</v>
+      </c>
+      <c r="B2322" t="n">
+        <v>18395</v>
+      </c>
+      <c r="C2322" t="n">
+        <v>9.4399995803833</v>
+      </c>
+      <c r="D2322" t="n">
+        <v>9.30000019073486</v>
+      </c>
+      <c r="E2322" t="n">
+        <v>9.34000015258789</v>
+      </c>
+      <c r="F2322" t="n">
+        <v>9.39999961853027</v>
+      </c>
+      <c r="G2322" t="s">
+        <v>738</v>
+      </c>
+      <c r="H2322" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -38,34 +38,34 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07642269134521</t>
+    <t xml:space="preserve">9.0764217376709</t>
   </si>
   <si>
     <t xml:space="preserve">FF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98565769195557</t>
+    <t xml:space="preserve">8.98565578460693</t>
   </si>
   <si>
     <t xml:space="preserve">9.08549880981445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24887275695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09457492828369</t>
+    <t xml:space="preserve">9.24887371063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09457397460938</t>
   </si>
   <si>
     <t xml:space="preserve">9.12180328369141</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03104019165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95388889312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89943218231201</t>
+    <t xml:space="preserve">9.03103828430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95388984680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8994312286377</t>
   </si>
   <si>
     <t xml:space="preserve">8.89489364624023</t>
@@ -77,28 +77,28 @@
     <t xml:space="preserve">8.85858821868896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87673950195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76782417297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86766338348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04919147491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23072147369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11272716522217</t>
+    <t xml:space="preserve">8.87674045562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76782321929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86766624450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04919338226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23072242736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11272811889648</t>
   </si>
   <si>
     <t xml:space="preserve">8.96750450134277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91304588317871</t>
+    <t xml:space="preserve">8.91304683685303</t>
   </si>
   <si>
     <t xml:space="preserve">8.92212200164795</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">9.00381088256836</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15810871124268</t>
+    <t xml:space="preserve">9.15810966491699</t>
   </si>
   <si>
     <t xml:space="preserve">9.16718578338623</t>
@@ -116,13 +116,13 @@
     <t xml:space="preserve">9.43947792053223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54839611053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62100791931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80253601074219</t>
+    <t xml:space="preserve">9.54839706420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62100696563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80253505706787</t>
   </si>
   <si>
     <t xml:space="preserve">9.71177101135254</t>
@@ -134,22 +134,22 @@
     <t xml:space="preserve">9.58470249176025</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5756254196167</t>
+    <t xml:space="preserve">9.57562446594238</t>
   </si>
   <si>
     <t xml:space="preserve">9.53024291992188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50301456451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60285568237305</t>
+    <t xml:space="preserve">9.50301361083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60285472869873</t>
   </si>
   <si>
     <t xml:space="preserve">9.63915920257568</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79345989227295</t>
+    <t xml:space="preserve">9.79346084594727</t>
   </si>
   <si>
     <t xml:space="preserve">9.95683479309082</t>
@@ -164,43 +164,43 @@
     <t xml:space="preserve">9.73900032043457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7662296295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74807643890381</t>
+    <t xml:space="preserve">9.76623058319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74807739257812</t>
   </si>
   <si>
     <t xml:space="preserve">9.75715255737305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64823532104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82068824768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70269393920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72084712982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67546558380127</t>
+    <t xml:space="preserve">9.64823627471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82068729400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7026948928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72084903717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67546463012695</t>
   </si>
   <si>
     <t xml:space="preserve">9.66638851165771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63008213043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65731334686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68454170227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81161403656006</t>
+    <t xml:space="preserve">9.63008403778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65731430053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68454265594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81161212921143</t>
   </si>
   <si>
     <t xml:space="preserve">9.8297643661499</t>
@@ -224,13 +224,13 @@
     <t xml:space="preserve">9.34871578216553</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33963775634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27610397338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25794887542725</t>
+    <t xml:space="preserve">9.33963680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27610206604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25794982910156</t>
   </si>
   <si>
     <t xml:space="preserve">9.19441509246826</t>
@@ -239,31 +239,31 @@
     <t xml:space="preserve">9.18533992767334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4122486114502</t>
+    <t xml:space="preserve">9.41224956512451</t>
   </si>
   <si>
     <t xml:space="preserve">9.22164440155029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31241035461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2670259475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29425525665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28517913818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37594318389893</t>
+    <t xml:space="preserve">9.31240940093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26702690124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29425621032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28518009185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37594509124756</t>
   </si>
   <si>
     <t xml:space="preserve">9.36686706542969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38501930236816</t>
+    <t xml:space="preserve">9.38502025604248</t>
   </si>
   <si>
     <t xml:space="preserve">9.45763111114502</t>
@@ -275,28 +275,28 @@
     <t xml:space="preserve">9.48486042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49393749237061</t>
+    <t xml:space="preserve">9.49393653869629</t>
   </si>
   <si>
     <t xml:space="preserve">9.44855499267578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4757833480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23979759216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14903354644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21256828308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20349311828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13088130950928</t>
+    <t xml:space="preserve">9.47578430175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2397985458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14903259277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21256732940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20349216461182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13088035583496</t>
   </si>
   <si>
     <t xml:space="preserve">9.1399564743042</t>
@@ -311,7 +311,7 @@
     <t xml:space="preserve">8.75874614715576</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66798210144043</t>
+    <t xml:space="preserve">8.66798400878906</t>
   </si>
   <si>
     <t xml:space="preserve">8.62260055541992</t>
@@ -320,19 +320,19 @@
     <t xml:space="preserve">8.53183650970459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35030937194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16877841949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98725128173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03263473510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12339782714844</t>
+    <t xml:space="preserve">8.35030746459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16878032684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98725175857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03263378143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12339878082275</t>
   </si>
   <si>
     <t xml:space="preserve">8.25954437255859</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">7.94186925888062</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30492496490479</t>
+    <t xml:space="preserve">8.3049259185791</t>
   </si>
   <si>
     <t xml:space="preserve">8.21416187286377</t>
@@ -350,31 +350,31 @@
     <t xml:space="preserve">8.39569091796875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57721900939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71336555480957</t>
+    <t xml:space="preserve">8.5772180557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71336460113525</t>
   </si>
   <si>
     <t xml:space="preserve">9.53202247619629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34871387481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25706005096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44037055969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16540718078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07375335693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11957931518555</t>
+    <t xml:space="preserve">9.34871482849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25706100463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44036865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16540622711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07375144958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11957836151123</t>
   </si>
   <si>
     <t xml:space="preserve">8.98209857940674</t>
@@ -383,7 +383,7 @@
     <t xml:space="preserve">9.02792549133301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62367725372314</t>
+    <t xml:space="preserve">9.62367630004883</t>
   </si>
   <si>
     <t xml:space="preserve">9.80698394775391</t>
@@ -392,31 +392,31 @@
     <t xml:space="preserve">9.89863872528076</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99029350280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.173602104187</t>
+    <t xml:space="preserve">9.9902925491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1736011505127</t>
   </si>
   <si>
     <t xml:space="preserve">10.2652559280396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3569087982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5402164459229</t>
+    <t xml:space="preserve">10.3569097518921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5402183532715</t>
   </si>
   <si>
     <t xml:space="preserve">10.631872177124</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8151798248291</t>
+    <t xml:space="preserve">10.8151807785034</t>
   </si>
   <si>
     <t xml:space="preserve">10.7235260009766</t>
   </si>
   <si>
-    <t xml:space="preserve">10.906831741333</t>
+    <t xml:space="preserve">10.906834602356</t>
   </si>
   <si>
     <t xml:space="preserve">10.9984884262085</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">11.090142250061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1817960739136</t>
+    <t xml:space="preserve">11.1817951202393</t>
   </si>
   <si>
     <t xml:space="preserve">11.2734498977661</t>
@@ -434,22 +434,22 @@
     <t xml:space="preserve">11.4567575454712</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3651027679443</t>
+    <t xml:space="preserve">11.365104675293</t>
   </si>
   <si>
     <t xml:space="preserve">10.4485626220703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71533203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79879093170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24886512756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21123218536377</t>
+    <t xml:space="preserve">9.71533107757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79878997802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24886608123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2112340927124</t>
   </si>
   <si>
     <t xml:space="preserve">9.30288696289062</t>
@@ -458,64 +458,64 @@
     <t xml:space="preserve">9.03709030151367</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39454174041748</t>
+    <t xml:space="preserve">9.39454078674316</t>
   </si>
   <si>
     <t xml:space="preserve">9.76115703582764</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66950416564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57784843444824</t>
+    <t xml:space="preserve">9.66950225830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57784938812256</t>
   </si>
   <si>
     <t xml:space="preserve">10.0361204147339</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94446659088135</t>
+    <t xml:space="preserve">9.94446563720703</t>
   </si>
   <si>
     <t xml:space="preserve">9.82552433013916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73283100128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59379100799561</t>
+    <t xml:space="preserve">9.73283004760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59379005432129</t>
   </si>
   <si>
     <t xml:space="preserve">9.96456432342529</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91821765899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54744434356689</t>
+    <t xml:space="preserve">9.91821670532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54744338989258</t>
   </si>
   <si>
     <t xml:space="preserve">10.010910987854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1036062240601</t>
+    <t xml:space="preserve">10.1036043167114</t>
   </si>
   <si>
     <t xml:space="preserve">10.1499519348145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1962976455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77917861938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87186908721924</t>
+    <t xml:space="preserve">10.1962985992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77917575836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87187004089355</t>
   </si>
   <si>
     <t xml:space="preserve">10.0572576522827</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2889928817749</t>
+    <t xml:space="preserve">10.2889919281006</t>
   </si>
   <si>
     <t xml:space="preserve">10.4743795394897</t>
@@ -524,55 +524,55 @@
     <t xml:space="preserve">10.2426452636719</t>
   </si>
   <si>
-    <t xml:space="preserve">10.381685256958</t>
+    <t xml:space="preserve">10.3816862106323</t>
   </si>
   <si>
     <t xml:space="preserve">9.68648338317871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64013576507568</t>
+    <t xml:space="preserve">9.64013671875</t>
   </si>
   <si>
     <t xml:space="preserve">9.50109577178955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31570816040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23228454589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1952075958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25082397460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.269362449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21374702453613</t>
+    <t xml:space="preserve">9.31570911407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23228549957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19520854949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25082302093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26936149597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21374607086182</t>
   </si>
   <si>
     <t xml:space="preserve">9.04689693450928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12105178833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0654354095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97274303436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17666912078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02835941314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95420455932617</t>
+    <t xml:space="preserve">9.12105274200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06543636322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97274208068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17666721343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02835845947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95420360565186</t>
   </si>
   <si>
     <t xml:space="preserve">8.71320056915283</t>
@@ -587,31 +587,31 @@
     <t xml:space="preserve">8.89858722686768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93566513061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3353395462036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9841938018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0305404663086</t>
+    <t xml:space="preserve">8.93566608428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3353385925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9841957092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0305414199829</t>
   </si>
   <si>
     <t xml:space="preserve">11.2159290313721</t>
   </si>
   <si>
-    <t xml:space="preserve">11.49400806427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.540355682373</t>
+    <t xml:space="preserve">11.4940099716187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5403566360474</t>
   </si>
   <si>
     <t xml:space="preserve">11.5867023468018</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6330509185791</t>
+    <t xml:space="preserve">11.6330499649048</t>
   </si>
   <si>
     <t xml:space="preserve">11.7257432937622</t>
@@ -629,34 +629,34 @@
     <t xml:space="preserve">12.2819042205811</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3745985031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5136394500732</t>
+    <t xml:space="preserve">12.3745994567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5136384963989</t>
   </si>
   <si>
     <t xml:space="preserve">12.3282518386841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1428651809692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0965175628662</t>
+    <t xml:space="preserve">12.1428642272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0965185165405</t>
   </si>
   <si>
     <t xml:space="preserve">12.555121421814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5082740783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6488170623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4614276885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4145793914795</t>
+    <t xml:space="preserve">12.5082750320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6488161087036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4614267349243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4145784378052</t>
   </si>
   <si>
     <t xml:space="preserve">12.7425117492676</t>
@@ -665,31 +665,31 @@
     <t xml:space="preserve">12.6956634521484</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2271890640259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1803417205811</t>
+    <t xml:space="preserve">12.2271900177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1803426742554</t>
   </si>
   <si>
     <t xml:space="preserve">12.3208847045898</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2740383148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8362073898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7893590927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6019687652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9299030303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8830547332764</t>
+    <t xml:space="preserve">12.274037361145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8362054824829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7893581390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6019697189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9299011230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8830537796021</t>
   </si>
   <si>
     <t xml:space="preserve">13.0704441070557</t>
@@ -698,13 +698,13 @@
     <t xml:space="preserve">13.679461479187</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8668508529663</t>
+    <t xml:space="preserve">13.8668518066406</t>
   </si>
   <si>
     <t xml:space="preserve">14.0542402267456</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3353252410889</t>
+    <t xml:space="preserve">14.3353261947632</t>
   </si>
   <si>
     <t xml:space="preserve">14.5695638656616</t>
@@ -713,16 +713,16 @@
     <t xml:space="preserve">15.2254276275635</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1317319869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7569532394409</t>
+    <t xml:space="preserve">15.1317329406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7569522857666</t>
   </si>
   <si>
     <t xml:space="preserve">15.0380373001099</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1785802841187</t>
+    <t xml:space="preserve">15.178581237793</t>
   </si>
   <si>
     <t xml:space="preserve">15.3191232681274</t>
@@ -737,37 +737,37 @@
     <t xml:space="preserve">15.4128198623657</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5533590316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0686836242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8650875091553</t>
+    <t xml:space="preserve">15.5533618927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0686798095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8650913238525</t>
   </si>
   <si>
     <t xml:space="preserve">17.0056324005127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7713928222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.193021774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0524787902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9587841033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7245464324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6308498382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5371551513672</t>
+    <t xml:space="preserve">16.7713947296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1930198669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0524806976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9587860107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7245483398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6308517456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5371570587158</t>
   </si>
   <si>
     <t xml:space="preserve">16.584005355835</t>
@@ -782,13 +782,13 @@
     <t xml:space="preserve">17.1461734771729</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3966159820557</t>
+    <t xml:space="preserve">16.396614074707</t>
   </si>
   <si>
     <t xml:space="preserve">16.3029193878174</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8344440460205</t>
+    <t xml:space="preserve">15.8344430923462</t>
   </si>
   <si>
     <t xml:space="preserve">16.1155300140381</t>
@@ -800,7 +800,7 @@
     <t xml:space="preserve">16.1623764038086</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9749879837036</t>
+    <t xml:space="preserve">15.974986076355</t>
   </si>
   <si>
     <t xml:space="preserve">15.7407484054565</t>
@@ -812,22 +812,22 @@
     <t xml:space="preserve">16.9119358062744</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0993270874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6776962280273</t>
+    <t xml:space="preserve">17.0993251800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.677698135376</t>
   </si>
   <si>
     <t xml:space="preserve">16.8182430267334</t>
   </si>
   <si>
-    <t xml:space="preserve">15.272274017334</t>
+    <t xml:space="preserve">15.2722749710083</t>
   </si>
   <si>
     <t xml:space="preserve">15.084885597229</t>
   </si>
   <si>
-    <t xml:space="preserve">14.991189956665</t>
+    <t xml:space="preserve">14.9911909103394</t>
   </si>
   <si>
     <t xml:space="preserve">14.8038005828857</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">14.382173538208</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1010885238647</t>
+    <t xml:space="preserve">14.1010875701904</t>
   </si>
   <si>
     <t xml:space="preserve">14.2884788513184</t>
@@ -854,46 +854,46 @@
     <t xml:space="preserve">14.2416305541992</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1947832107544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0073938369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7263078689575</t>
+    <t xml:space="preserve">14.1947822570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0073928833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7263088226318</t>
   </si>
   <si>
     <t xml:space="preserve">14.1479358673096</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4290199279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6164102554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.773154258728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3515291213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3046817779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3983764648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0235967636108</t>
+    <t xml:space="preserve">14.4290208816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6164112091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7731561660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3515281677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3046808242798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3983755111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0235958099365</t>
   </si>
   <si>
     <t xml:space="preserve">13.1172914505005</t>
   </si>
   <si>
-    <t xml:space="preserve">12.976749420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.367733001709</t>
+    <t xml:space="preserve">12.9767484664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3677320480347</t>
   </si>
   <si>
     <t xml:space="preserve">12.0866470336914</t>
@@ -902,25 +902,25 @@
     <t xml:space="preserve">11.9929523468018</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8992567062378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0397996902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1334934234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4776296615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2433938980103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3839340209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6650190353394</t>
+    <t xml:space="preserve">11.8992586135864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0398006439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1334943771362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4776306152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2433929443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3839349746704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6650199890137</t>
   </si>
   <si>
     <t xml:space="preserve">11.4307823181152</t>
@@ -929,19 +929,19 @@
     <t xml:space="preserve">10.9623079299927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7280712127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1965446472168</t>
+    <t xml:space="preserve">10.7280702590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1965456008911</t>
   </si>
   <si>
     <t xml:space="preserve">11.571325302124</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3370876312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2902402877808</t>
+    <t xml:space="preserve">11.3370885848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2902393341064</t>
   </si>
   <si>
     <t xml:space="preserve">11.7118673324585</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">11.7587156295776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8055639266968</t>
+    <t xml:space="preserve">11.8055629730225</t>
   </si>
   <si>
     <t xml:space="preserve">11.0091552734375</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">9.46318817138672</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33884811401367</t>
+    <t xml:space="preserve">8.33884906768799</t>
   </si>
   <si>
     <t xml:space="preserve">8.57308673858643</t>
@@ -977,13 +977,13 @@
     <t xml:space="preserve">8.44191360473633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32948112487793</t>
+    <t xml:space="preserve">8.32948017120361</t>
   </si>
   <si>
     <t xml:space="preserve">8.25452423095703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43254375457764</t>
+    <t xml:space="preserve">8.43254566192627</t>
   </si>
   <si>
     <t xml:space="preserve">8.47002220153809</t>
@@ -992,16 +992,16 @@
     <t xml:space="preserve">8.32011127471924</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20767688751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08587265014648</t>
+    <t xml:space="preserve">8.20767784118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0858736038208</t>
   </si>
   <si>
     <t xml:space="preserve">7.78604936599731</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49559497833252</t>
+    <t xml:space="preserve">7.49559545516968</t>
   </si>
   <si>
     <t xml:space="preserve">7.33631372451782</t>
@@ -1031,7 +1031,7 @@
     <t xml:space="preserve">6.98027276992798</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93342542648315</t>
+    <t xml:space="preserve">6.93342590332031</t>
   </si>
   <si>
     <t xml:space="preserve">7.06459856033325</t>
@@ -1040,13 +1040,13 @@
     <t xml:space="preserve">7.0271201133728</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34568309783936</t>
+    <t xml:space="preserve">7.34568357467651</t>
   </si>
   <si>
     <t xml:space="preserve">7.5424427986145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19830799102783</t>
+    <t xml:space="preserve">8.19830703735352</t>
   </si>
   <si>
     <t xml:space="preserve">8.2170467376709</t>
@@ -1055,7 +1055,7 @@
     <t xml:space="preserve">8.65194320678711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46116256713867</t>
+    <t xml:space="preserve">8.46116161346436</t>
   </si>
   <si>
     <t xml:space="preserve">8.53747367858887</t>
@@ -1070,7 +1070,7 @@
     <t xml:space="preserve">8.84272575378418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72825527191162</t>
+    <t xml:space="preserve">8.72825622558594</t>
   </si>
   <si>
     <t xml:space="preserve">8.66148281097412</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">8.39438915252686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60424900054932</t>
+    <t xml:space="preserve">8.604248046875</t>
   </si>
   <si>
     <t xml:space="preserve">8.48977851867676</t>
@@ -1094,10 +1094,10 @@
     <t xml:space="preserve">8.29899787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12729549407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89835643768311</t>
+    <t xml:space="preserve">8.12729454040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89835596084595</t>
   </si>
   <si>
     <t xml:space="preserve">8.10821628570557</t>
@@ -1106,7 +1106,7 @@
     <t xml:space="preserve">7.8411226272583</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33715343475342</t>
+    <t xml:space="preserve">8.33715438842773</t>
   </si>
   <si>
     <t xml:space="preserve">8.20360660552979</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">8.07005977630615</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92697334289551</t>
+    <t xml:space="preserve">7.92697381973267</t>
   </si>
   <si>
     <t xml:space="preserve">7.98420763015747</t>
@@ -1136,19 +1136,19 @@
     <t xml:space="preserve">8.2703800201416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18452835083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03190422058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96512985229492</t>
+    <t xml:space="preserve">8.18452930450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03190326690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96513032913208</t>
   </si>
   <si>
     <t xml:space="preserve">7.86019992828369</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86973905563354</t>
+    <t xml:space="preserve">7.8697395324707</t>
   </si>
   <si>
     <t xml:space="preserve">7.71711397171021</t>
@@ -1163,16 +1163,16 @@
     <t xml:space="preserve">7.72665309906006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65034103393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63126230239868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65987968444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.165452003479</t>
+    <t xml:space="preserve">7.65034055709839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63126182556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65987920761108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16545104980469</t>
   </si>
   <si>
     <t xml:space="preserve">8.32761478424072</t>
@@ -1181,25 +1181,25 @@
     <t xml:space="preserve">8.11775588989258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93651247024536</t>
+    <t xml:space="preserve">7.93651151657104</t>
   </si>
   <si>
     <t xml:space="preserve">8.19406795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2322244644165</t>
+    <t xml:space="preserve">8.23222351074219</t>
   </si>
   <si>
     <t xml:space="preserve">8.31807613372803</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15591144561768</t>
+    <t xml:space="preserve">8.15591239929199</t>
   </si>
   <si>
     <t xml:space="preserve">8.22268486022949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25130081176758</t>
+    <t xml:space="preserve">8.25130176544189</t>
   </si>
   <si>
     <t xml:space="preserve">8.35623264312744</t>
@@ -1220,19 +1220,19 @@
     <t xml:space="preserve">7.82204389572144</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97466850280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01282501220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05098152160645</t>
+    <t xml:space="preserve">7.97466802597046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01282405853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05098056793213</t>
   </si>
   <si>
     <t xml:space="preserve">7.67895793914795</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7361912727356</t>
+    <t xml:space="preserve">7.73619174957275</t>
   </si>
   <si>
     <t xml:space="preserve">7.6980357170105</t>
@@ -1262,7 +1262,7 @@
     <t xml:space="preserve">7.20200395584106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1829252243042</t>
+    <t xml:space="preserve">7.18292570114136</t>
   </si>
   <si>
     <t xml:space="preserve">7.14476919174194</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">7.23062086105347</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1543083190918</t>
+    <t xml:space="preserve">7.15430784225464</t>
   </si>
   <si>
     <t xml:space="preserve">7.24969911575317</t>
@@ -1283,10 +1283,10 @@
     <t xml:space="preserve">7.24016046524048</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46909809112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41186380386353</t>
+    <t xml:space="preserve">7.46909761428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41186332702637</t>
   </si>
   <si>
     <t xml:space="preserve">7.45001935958862</t>
@@ -1295,40 +1295,40 @@
     <t xml:space="preserve">7.28785514831543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39278554916382</t>
+    <t xml:space="preserve">7.39278507232666</t>
   </si>
   <si>
     <t xml:space="preserve">7.3355507850647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61218404769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90789604187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94605159759521</t>
+    <t xml:space="preserve">7.61218357086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90789556503296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94605112075806</t>
   </si>
   <si>
     <t xml:space="preserve">7.45955896377563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70757484436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87927913665771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99374675750732</t>
+    <t xml:space="preserve">7.70757436752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87927865982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99374723434448</t>
   </si>
   <si>
     <t xml:space="preserve">7.75527048110962</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81250429153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79342651367188</t>
+    <t xml:space="preserve">7.81250476837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79342699050903</t>
   </si>
   <si>
     <t xml:space="preserve">7.80296611785889</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">7.74573087692261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83158302307129</t>
+    <t xml:space="preserve">7.83158349990845</t>
   </si>
   <si>
     <t xml:space="preserve">7.66941833496094</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">7.58356666564941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88881826400757</t>
+    <t xml:space="preserve">7.88881778717041</t>
   </si>
   <si>
     <t xml:space="preserve">8.00328636169434</t>
@@ -1361,7 +1361,7 @@
     <t xml:space="preserve">7.78388738632202</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3641676902771</t>
+    <t xml:space="preserve">7.36416816711426</t>
   </si>
   <si>
     <t xml:space="preserve">7.10661315917969</t>
@@ -1370,10 +1370,10 @@
     <t xml:space="preserve">7.27831649780273</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08753442764282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05891799926758</t>
+    <t xml:space="preserve">7.08753490447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05891752243042</t>
   </si>
   <si>
     <t xml:space="preserve">7.50372648239136</t>
@@ -62960,7 +62960,7 @@
     </row>
     <row r="2323">
       <c r="A2323" s="1" t="n">
-        <v>45996.6911574074</v>
+        <v>45996.3333333333</v>
       </c>
       <c r="B2323" t="n">
         <v>24520</v>
@@ -62981,6 +62981,32 @@
         <v>737</v>
       </c>
       <c r="H2323" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2324">
+      <c r="A2324" s="1" t="n">
+        <v>45999.6911226852</v>
+      </c>
+      <c r="B2324" t="n">
+        <v>16957</v>
+      </c>
+      <c r="C2324" t="n">
+        <v>9.42000007629395</v>
+      </c>
+      <c r="D2324" t="n">
+        <v>9.30000019073486</v>
+      </c>
+      <c r="E2324" t="n">
+        <v>9.31999969482422</v>
+      </c>
+      <c r="F2324" t="n">
+        <v>9.30000019073486</v>
+      </c>
+      <c r="G2324" t="s">
+        <v>736</v>
+      </c>
+      <c r="H2324" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="746">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="747">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,22 +44,22 @@
     <t xml:space="preserve">FF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98565578460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08549880981445</t>
+    <t xml:space="preserve">8.98565769195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08549785614014</t>
   </si>
   <si>
     <t xml:space="preserve">9.24887371063232</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09457397460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12180328369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03103828430176</t>
+    <t xml:space="preserve">9.09457588195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12180519104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03104019165039</t>
   </si>
   <si>
     <t xml:space="preserve">8.95388984680176</t>
@@ -68,10 +68,10 @@
     <t xml:space="preserve">8.8994312286377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89489364624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84951114654541</t>
+    <t xml:space="preserve">8.8948917388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84951019287109</t>
   </si>
   <si>
     <t xml:space="preserve">8.85858821868896</t>
@@ -80,25 +80,25 @@
     <t xml:space="preserve">8.87674045562744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76782321929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86766624450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04919338226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23072242736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11272811889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96750450134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91304683685303</t>
+    <t xml:space="preserve">8.76782512664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86766242980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04919242858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23072052001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11272621154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96750354766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91304588317871</t>
   </si>
   <si>
     <t xml:space="preserve">8.92212200164795</t>
@@ -107,106 +107,106 @@
     <t xml:space="preserve">9.00381088256836</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15810966491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16718578338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43947792053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54839706420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62100696563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80253505706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71177101135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56654930114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58470249176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57562446594238</t>
+    <t xml:space="preserve">9.15810871124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16718673706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43947887420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54839611053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62100791931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80253601074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71177291870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56654834747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58470153808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5756254196167</t>
   </si>
   <si>
     <t xml:space="preserve">9.53024291992188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50301361083984</t>
+    <t xml:space="preserve">9.50301265716553</t>
   </si>
   <si>
     <t xml:space="preserve">9.60285472869873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63915920257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79346084594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95683479309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93868160247803</t>
+    <t xml:space="preserve">9.63916015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79345893859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95683670043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93868064880371</t>
   </si>
   <si>
     <t xml:space="preserve">9.98406410217285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73900032043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76623058319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74807739257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75715255737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64823627471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82068729400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7026948928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72084903717041</t>
+    <t xml:space="preserve">9.73900127410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7662296295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74807548522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75715351104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64823532104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82068824768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70269393920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72084712982178</t>
   </si>
   <si>
     <t xml:space="preserve">9.67546463012695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66638851165771</t>
+    <t xml:space="preserve">9.66638946533203</t>
   </si>
   <si>
     <t xml:space="preserve">9.63008403778076</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65731430053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68454265594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81161212921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8297643661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8479175567627</t>
+    <t xml:space="preserve">9.65731239318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68454170227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81161403656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82976531982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84791851043701</t>
   </si>
   <si>
     <t xml:space="preserve">9.83884048461914</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">9.72992420196533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78438282012939</t>
+    <t xml:space="preserve">9.78438377380371</t>
   </si>
   <si>
     <t xml:space="preserve">9.55747222900391</t>
@@ -224,22 +224,22 @@
     <t xml:space="preserve">9.34871578216553</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33963680267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27610206604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25794982910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19441509246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18533992767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41224956512451</t>
+    <t xml:space="preserve">9.33963871002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27610397338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25795078277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19441604614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18533706665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4122486114502</t>
   </si>
   <si>
     <t xml:space="preserve">9.22164440155029</t>
@@ -257,10 +257,10 @@
     <t xml:space="preserve">9.28518009185791</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37594509124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36686706542969</t>
+    <t xml:space="preserve">9.37594318389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.366868019104</t>
   </si>
   <si>
     <t xml:space="preserve">9.38502025604248</t>
@@ -275,40 +275,40 @@
     <t xml:space="preserve">9.48486042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49393653869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44855499267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47578430175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2397985458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14903259277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21256732940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20349216461182</t>
+    <t xml:space="preserve">9.49393749237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4485559463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47578239440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23979759216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14903354644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21256828308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20349311828613</t>
   </si>
   <si>
     <t xml:space="preserve">9.13088035583496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1399564743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94027519226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80412864685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75874614715576</t>
+    <t xml:space="preserve">9.13995552062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94027423858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80412769317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75874710083008</t>
   </si>
   <si>
     <t xml:space="preserve">8.66798400878906</t>
@@ -317,13 +317,13 @@
     <t xml:space="preserve">8.62260055541992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53183650970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35030746459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16878032684326</t>
+    <t xml:space="preserve">8.53183555603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35030651092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16877937316895</t>
   </si>
   <si>
     <t xml:space="preserve">7.98725175857544</t>
@@ -332,31 +332,31 @@
     <t xml:space="preserve">8.03263378143311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12339878082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25954437255859</t>
+    <t xml:space="preserve">8.12339687347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25954627990723</t>
   </si>
   <si>
     <t xml:space="preserve">7.94186925888062</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3049259185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21416187286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39569091796875</t>
+    <t xml:space="preserve">8.30492687225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21416091918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39568996429443</t>
   </si>
   <si>
     <t xml:space="preserve">8.5772180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71336460113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53202247619629</t>
+    <t xml:space="preserve">8.71336555480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53202342987061</t>
   </si>
   <si>
     <t xml:space="preserve">9.34871482849121</t>
@@ -365,106 +365,106 @@
     <t xml:space="preserve">9.25706100463867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44036865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16540622711182</t>
+    <t xml:space="preserve">9.44036960601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16540718078613</t>
   </si>
   <si>
     <t xml:space="preserve">9.07375144958496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11957836151123</t>
+    <t xml:space="preserve">9.11958026885986</t>
   </si>
   <si>
     <t xml:space="preserve">8.98209857940674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02792549133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62367630004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80698394775391</t>
+    <t xml:space="preserve">9.02792453765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62367725372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80698585510254</t>
   </si>
   <si>
     <t xml:space="preserve">9.89863872528076</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9902925491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1736011505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2652559280396</t>
+    <t xml:space="preserve">9.99029350280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1736030578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2652540206909</t>
   </si>
   <si>
     <t xml:space="preserve">10.3569097518921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5402183532715</t>
+    <t xml:space="preserve">10.5402173995972</t>
   </si>
   <si>
     <t xml:space="preserve">10.631872177124</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8151807785034</t>
+    <t xml:space="preserve">10.8151788711548</t>
   </si>
   <si>
     <t xml:space="preserve">10.7235260009766</t>
   </si>
   <si>
-    <t xml:space="preserve">10.906834602356</t>
+    <t xml:space="preserve">10.9068336486816</t>
   </si>
   <si>
     <t xml:space="preserve">10.9984884262085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.090142250061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1817951202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2734498977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4567575454712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.365104675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4485626220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71533107757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79878997802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24886608123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2112340927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30288696289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03709030151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39454078674316</t>
+    <t xml:space="preserve">11.0901412963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1817960739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2734508514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4567584991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3651037216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4485635757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79879093170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24886512756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21123313903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30288791656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03709125518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39454174041748</t>
   </si>
   <si>
     <t xml:space="preserve">9.76115703582764</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66950225830078</t>
+    <t xml:space="preserve">9.66950511932373</t>
   </si>
   <si>
     <t xml:space="preserve">9.57784938812256</t>
@@ -473,19 +473,19 @@
     <t xml:space="preserve">10.0361204147339</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94446563720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82552433013916</t>
+    <t xml:space="preserve">9.94446659088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82552528381348</t>
   </si>
   <si>
     <t xml:space="preserve">9.73283004760742</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59379005432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96456432342529</t>
+    <t xml:space="preserve">9.59378910064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96456527709961</t>
   </si>
   <si>
     <t xml:space="preserve">9.91821670532227</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">9.54744338989258</t>
   </si>
   <si>
-    <t xml:space="preserve">10.010910987854</t>
+    <t xml:space="preserve">10.0109119415283</t>
   </si>
   <si>
     <t xml:space="preserve">10.1036043167114</t>
@@ -506,25 +506,25 @@
     <t xml:space="preserve">10.1962985992432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77917575836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87187004089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0572576522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2889919281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4743795394897</t>
+    <t xml:space="preserve">9.77917766571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87186908721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.057258605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2889928817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4743804931641</t>
   </si>
   <si>
     <t xml:space="preserve">10.2426452636719</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3816862106323</t>
+    <t xml:space="preserve">10.381685256958</t>
   </si>
   <si>
     <t xml:space="preserve">9.68648338317871</t>
@@ -533,22 +533,22 @@
     <t xml:space="preserve">9.64013671875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50109577178955</t>
+    <t xml:space="preserve">9.50109767913818</t>
   </si>
   <si>
     <t xml:space="preserve">9.31570911407471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23228549957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19520854949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25082302093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26936149597168</t>
+    <t xml:space="preserve">9.23228454589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1952075958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25082397460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.269362449646</t>
   </si>
   <si>
     <t xml:space="preserve">9.21374607086182</t>
@@ -557,19 +557,19 @@
     <t xml:space="preserve">9.04689693450928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12105274200439</t>
+    <t xml:space="preserve">9.12105178833008</t>
   </si>
   <si>
     <t xml:space="preserve">9.06543636322021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97274208068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17666721343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02835845947266</t>
+    <t xml:space="preserve">8.97274303436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17666816711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02835941314697</t>
   </si>
   <si>
     <t xml:space="preserve">8.95420360565186</t>
@@ -593,19 +593,19 @@
     <t xml:space="preserve">10.3353385925293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9841957092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0305414199829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2159290313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4940099716187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5403566360474</t>
+    <t xml:space="preserve">10.9841947555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0305404663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2159280776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4940090179443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.540355682373</t>
   </si>
   <si>
     <t xml:space="preserve">11.5867023468018</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">11.7257432937622</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9111309051514</t>
+    <t xml:space="preserve">11.9111318588257</t>
   </si>
   <si>
     <t xml:space="preserve">11.9574766159058</t>
@@ -626,13 +626,13 @@
     <t xml:space="preserve">12.1892118453979</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2819042205811</t>
+    <t xml:space="preserve">12.2819032669067</t>
   </si>
   <si>
     <t xml:space="preserve">12.3745994567871</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5136384963989</t>
+    <t xml:space="preserve">12.5136394500732</t>
   </si>
   <si>
     <t xml:space="preserve">12.3282518386841</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">12.1428642272949</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0965185165405</t>
+    <t xml:space="preserve">12.0965175628662</t>
   </si>
   <si>
     <t xml:space="preserve">12.555121421814</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">12.5082750320435</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6488161087036</t>
+    <t xml:space="preserve">12.6488170623779</t>
   </si>
   <si>
     <t xml:space="preserve">12.4614267349243</t>
@@ -662,31 +662,31 @@
     <t xml:space="preserve">12.7425117492676</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6956634521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2271900177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1803426742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3208847045898</t>
+    <t xml:space="preserve">12.6956644058228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2271890640259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1803417205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3208837509155</t>
   </si>
   <si>
     <t xml:space="preserve">12.274037361145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8362054824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7893581390381</t>
+    <t xml:space="preserve">12.8362064361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7893590927124</t>
   </si>
   <si>
     <t xml:space="preserve">12.6019697189331</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9299011230469</t>
+    <t xml:space="preserve">12.9299020767212</t>
   </si>
   <si>
     <t xml:space="preserve">12.8830537796021</t>
@@ -695,16 +695,16 @@
     <t xml:space="preserve">13.0704441070557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.679461479187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8668518066406</t>
+    <t xml:space="preserve">13.6794624328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8668508529663</t>
   </si>
   <si>
     <t xml:space="preserve">14.0542402267456</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3353261947632</t>
+    <t xml:space="preserve">14.3353252410889</t>
   </si>
   <si>
     <t xml:space="preserve">14.5695638656616</t>
@@ -713,19 +713,19 @@
     <t xml:space="preserve">15.2254276275635</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1317329406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7569522857666</t>
+    <t xml:space="preserve">15.1317319869995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7569532394409</t>
   </si>
   <si>
     <t xml:space="preserve">15.0380373001099</t>
   </si>
   <si>
-    <t xml:space="preserve">15.178581237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3191232681274</t>
+    <t xml:space="preserve">15.1785802841187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3191223144531</t>
   </si>
   <si>
     <t xml:space="preserve">14.8974952697754</t>
@@ -734,22 +734,22 @@
     <t xml:space="preserve">15.4596662521362</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4128198623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5533618927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0686798095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8650913238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0056324005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7713947296143</t>
+    <t xml:space="preserve">15.4128189086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5533599853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0686817169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8650894165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0056304931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7713928222656</t>
   </si>
   <si>
     <t xml:space="preserve">17.1930198669434</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">16.9587860107422</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7245483398438</t>
+    <t xml:space="preserve">16.7245464324951</t>
   </si>
   <si>
     <t xml:space="preserve">16.6308517456055</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">16.584005355835</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2092247009277</t>
+    <t xml:space="preserve">16.2092227935791</t>
   </si>
   <si>
     <t xml:space="preserve">16.2560729980469</t>
@@ -794,13 +794,13 @@
     <t xml:space="preserve">16.1155300140381</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0218353271484</t>
+    <t xml:space="preserve">16.0218372344971</t>
   </si>
   <si>
     <t xml:space="preserve">16.1623764038086</t>
   </si>
   <si>
-    <t xml:space="preserve">15.974986076355</t>
+    <t xml:space="preserve">15.9749879837036</t>
   </si>
   <si>
     <t xml:space="preserve">15.7407484054565</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">16.9119358062744</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0993251800537</t>
+    <t xml:space="preserve">17.0993270874023</t>
   </si>
   <si>
     <t xml:space="preserve">16.677698135376</t>
@@ -821,16 +821,16 @@
     <t xml:space="preserve">16.8182430267334</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2722749710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.084885597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9911909103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8038005828857</t>
+    <t xml:space="preserve">15.272274017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0848865509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.991189956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8038015365601</t>
   </si>
   <si>
     <t xml:space="preserve">14.4758682250977</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">14.382173538208</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1010875701904</t>
+    <t xml:space="preserve">14.1010885238647</t>
   </si>
   <si>
     <t xml:space="preserve">14.2884788513184</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">13.960545539856</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2416305541992</t>
+    <t xml:space="preserve">14.2416315078735</t>
   </si>
   <si>
     <t xml:space="preserve">14.1947822570801</t>
@@ -869,25 +869,25 @@
     <t xml:space="preserve">14.4290208816528</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6164112091064</t>
+    <t xml:space="preserve">14.6164102554321</t>
   </si>
   <si>
     <t xml:space="preserve">13.7731561660767</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3515281677246</t>
+    <t xml:space="preserve">13.3515291213989</t>
   </si>
   <si>
     <t xml:space="preserve">13.3046808242798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3983755111694</t>
+    <t xml:space="preserve">13.3983764648438</t>
   </si>
   <si>
     <t xml:space="preserve">13.0235958099365</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1172914505005</t>
+    <t xml:space="preserve">13.1172924041748</t>
   </si>
   <si>
     <t xml:space="preserve">12.9767484664917</t>
@@ -902,7 +902,7 @@
     <t xml:space="preserve">11.9929523468018</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8992586135864</t>
+    <t xml:space="preserve">11.8992576599121</t>
   </si>
   <si>
     <t xml:space="preserve">12.0398006439209</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">11.3839349746704</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6650199890137</t>
+    <t xml:space="preserve">11.6650190353394</t>
   </si>
   <si>
     <t xml:space="preserve">11.4307823181152</t>
@@ -932,31 +932,31 @@
     <t xml:space="preserve">10.7280702590942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1965456008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.571325302124</t>
+    <t xml:space="preserve">11.1965446472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5713262557983</t>
   </si>
   <si>
     <t xml:space="preserve">11.3370885848999</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2902393341064</t>
+    <t xml:space="preserve">11.2902402877808</t>
   </si>
   <si>
     <t xml:space="preserve">11.7118673324585</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7587156295776</t>
+    <t xml:space="preserve">11.7587146759033</t>
   </si>
   <si>
     <t xml:space="preserve">11.8055629730225</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0091552734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46318817138672</t>
+    <t xml:space="preserve">11.0091562271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46318912506104</t>
   </si>
   <si>
     <t xml:space="preserve">8.33884906768799</t>
@@ -968,46 +968,46 @@
     <t xml:space="preserve">8.31074142456055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45128440856934</t>
+    <t xml:space="preserve">8.45128345489502</t>
   </si>
   <si>
     <t xml:space="preserve">8.61993408203125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44191360473633</t>
+    <t xml:space="preserve">8.44191455841064</t>
   </si>
   <si>
     <t xml:space="preserve">8.32948017120361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25452423095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43254566192627</t>
+    <t xml:space="preserve">8.25452518463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43254470825195</t>
   </si>
   <si>
     <t xml:space="preserve">8.47002220153809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32011127471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20767784118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0858736038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78604936599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49559545516968</t>
+    <t xml:space="preserve">8.32011032104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20767688751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08587265014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78604984283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49559497833252</t>
   </si>
   <si>
     <t xml:space="preserve">7.33631372451782</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23324918746948</t>
+    <t xml:space="preserve">7.23324966430664</t>
   </si>
   <si>
     <t xml:space="preserve">7.83289623260498</t>
@@ -1016,13 +1016,13 @@
     <t xml:space="preserve">7.90785217285156</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50496482849121</t>
+    <t xml:space="preserve">7.50496530532837</t>
   </si>
   <si>
     <t xml:space="preserve">7.37379169464111</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12081527709961</t>
+    <t xml:space="preserve">7.12081575393677</t>
   </si>
   <si>
     <t xml:space="preserve">7.28009700775146</t>
@@ -1031,7 +1031,7 @@
     <t xml:space="preserve">6.98027276992798</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93342590332031</t>
+    <t xml:space="preserve">6.93342542648315</t>
   </si>
   <si>
     <t xml:space="preserve">7.06459856033325</t>
@@ -1043,7 +1043,7 @@
     <t xml:space="preserve">7.34568357467651</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5424427986145</t>
+    <t xml:space="preserve">7.54244327545166</t>
   </si>
   <si>
     <t xml:space="preserve">8.19830703735352</t>
@@ -2250,6 +2250,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.42000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65999984741211</t>
   </si>
 </sst>
 </file>
@@ -62986,7 +62989,7 @@
     </row>
     <row r="2324">
       <c r="A2324" s="1" t="n">
-        <v>45999.6911226852</v>
+        <v>45999.3333333333</v>
       </c>
       <c r="B2324" t="n">
         <v>16957</v>
@@ -62998,7 +63001,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="E2324" t="n">
-        <v>9.31999969482422</v>
+        <v>9.30000019073486</v>
       </c>
       <c r="F2324" t="n">
         <v>9.30000019073486</v>
@@ -63007,6 +63010,32 @@
         <v>736</v>
       </c>
       <c r="H2324" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2325">
+      <c r="A2325" s="1" t="n">
+        <v>46000.6911921296</v>
+      </c>
+      <c r="B2325" t="n">
+        <v>47618</v>
+      </c>
+      <c r="C2325" t="n">
+        <v>9.65999984741211</v>
+      </c>
+      <c r="D2325" t="n">
+        <v>9.31999969482422</v>
+      </c>
+      <c r="E2325" t="n">
+        <v>9.39999961853027</v>
+      </c>
+      <c r="F2325" t="n">
+        <v>9.65999984741211</v>
+      </c>
+      <c r="G2325" t="s">
+        <v>746</v>
+      </c>
+      <c r="H2325" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="747" uniqueCount="747">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="748">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,46 +44,46 @@
     <t xml:space="preserve">FF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98565673828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08549976348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24887371063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09457588195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12180328369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03104019165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95388889312744</t>
+    <t xml:space="preserve">8.98565769195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08549880981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24887275695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09457492828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12180423736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03104114532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95388984680176</t>
   </si>
   <si>
     <t xml:space="preserve">8.89943218231201</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89489459991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84951114654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85858631134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87673950195312</t>
+    <t xml:space="preserve">8.89489269256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84951019287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85858821868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87674045562744</t>
   </si>
   <si>
     <t xml:space="preserve">8.76782321929932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8676643371582</t>
+    <t xml:space="preserve">8.86766529083252</t>
   </si>
   <si>
     <t xml:space="preserve">9.04919242858887</t>
@@ -92,10 +92,10 @@
     <t xml:space="preserve">9.23072147369385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11272811889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96750354766846</t>
+    <t xml:space="preserve">9.11272716522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96750450134277</t>
   </si>
   <si>
     <t xml:space="preserve">8.91304588317871</t>
@@ -104,10 +104,10 @@
     <t xml:space="preserve">8.92212295532227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00380992889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15810871124268</t>
+    <t xml:space="preserve">9.00381183624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15810966491699</t>
   </si>
   <si>
     <t xml:space="preserve">9.16718578338623</t>
@@ -116,13 +116,13 @@
     <t xml:space="preserve">9.43947792053223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54839611053467</t>
+    <t xml:space="preserve">9.54839515686035</t>
   </si>
   <si>
     <t xml:space="preserve">9.62100791931152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80253601074219</t>
+    <t xml:space="preserve">9.8025369644165</t>
   </si>
   <si>
     <t xml:space="preserve">9.71177101135254</t>
@@ -134,49 +134,49 @@
     <t xml:space="preserve">9.58470153808594</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5756254196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53024291992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50301456451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60285377502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63916015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79345893859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95683574676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93868160247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98406410217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73899936676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76623058319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74807643890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75715255737305</t>
+    <t xml:space="preserve">9.57562446594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53024196624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50301361083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60285472869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63915920257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79345989227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95683479309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93868255615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98406219482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73900032043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7662296295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74807739257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75715351104736</t>
   </si>
   <si>
     <t xml:space="preserve">9.64823627471924</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82068824768066</t>
+    <t xml:space="preserve">9.82068729400635</t>
   </si>
   <si>
     <t xml:space="preserve">9.7026948928833</t>
@@ -185,19 +185,19 @@
     <t xml:space="preserve">9.72084712982178</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67546653747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66638946533203</t>
+    <t xml:space="preserve">9.67546558380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66638851165771</t>
   </si>
   <si>
     <t xml:space="preserve">9.63008308410645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65731239318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68454265594482</t>
+    <t xml:space="preserve">9.65731430053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68454170227051</t>
   </si>
   <si>
     <t xml:space="preserve">9.81161308288574</t>
@@ -206,10 +206,10 @@
     <t xml:space="preserve">9.8297643661499</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84791851043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83884143829346</t>
+    <t xml:space="preserve">9.8479175567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83884048461914</t>
   </si>
   <si>
     <t xml:space="preserve">9.72992420196533</t>
@@ -224,22 +224,22 @@
     <t xml:space="preserve">9.34871482849121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33963775634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27610301971436</t>
+    <t xml:space="preserve">9.33963871002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27610397338867</t>
   </si>
   <si>
     <t xml:space="preserve">9.25794982910156</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19441604614258</t>
+    <t xml:space="preserve">9.19441509246826</t>
   </si>
   <si>
     <t xml:space="preserve">9.18533897399902</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4122486114502</t>
+    <t xml:space="preserve">9.41224956512451</t>
   </si>
   <si>
     <t xml:space="preserve">9.22164440155029</t>
@@ -248,10 +248,10 @@
     <t xml:space="preserve">9.31240844726562</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26702690124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29425525665283</t>
+    <t xml:space="preserve">9.2670259475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29425621032715</t>
   </si>
   <si>
     <t xml:space="preserve">9.28517913818359</t>
@@ -260,10 +260,10 @@
     <t xml:space="preserve">9.37594413757324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36686706542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3850212097168</t>
+    <t xml:space="preserve">9.366868019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38501930236816</t>
   </si>
   <si>
     <t xml:space="preserve">9.45763111114502</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">9.39409732818604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48486042022705</t>
+    <t xml:space="preserve">9.48486137390137</t>
   </si>
   <si>
     <t xml:space="preserve">9.49393749237061</t>
@@ -284,13 +284,13 @@
     <t xml:space="preserve">9.47578430175781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23979759216309</t>
+    <t xml:space="preserve">9.23979663848877</t>
   </si>
   <si>
     <t xml:space="preserve">9.14903259277344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21256828308105</t>
+    <t xml:space="preserve">9.21256732940674</t>
   </si>
   <si>
     <t xml:space="preserve">9.20349216461182</t>
@@ -299,22 +299,22 @@
     <t xml:space="preserve">9.13088130950928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13995552062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94027614593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8041296005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75874519348145</t>
+    <t xml:space="preserve">9.1399564743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94027519226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80412864685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75874614715576</t>
   </si>
   <si>
     <t xml:space="preserve">8.66798305511475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62260055541992</t>
+    <t xml:space="preserve">8.62259960174561</t>
   </si>
   <si>
     <t xml:space="preserve">8.53183650970459</t>
@@ -326,13 +326,13 @@
     <t xml:space="preserve">8.16877937316895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98725128173828</t>
+    <t xml:space="preserve">7.9872522354126</t>
   </si>
   <si>
     <t xml:space="preserve">8.03263473510742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1233959197998</t>
+    <t xml:space="preserve">8.12339782714844</t>
   </si>
   <si>
     <t xml:space="preserve">8.25954341888428</t>
@@ -341,19 +341,19 @@
     <t xml:space="preserve">7.9418683052063</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3049259185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2141637802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39568996429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5772180557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71336650848389</t>
+    <t xml:space="preserve">8.30492496490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21416187286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39569187164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57721710205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71336555480957</t>
   </si>
   <si>
     <t xml:space="preserve">9.53202342987061</t>
@@ -365,55 +365,55 @@
     <t xml:space="preserve">9.44036865234375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16540813446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07375144958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11957836151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98209953308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02792644500732</t>
+    <t xml:space="preserve">9.16540718078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07375240325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11957931518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98209857940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02792453765869</t>
   </si>
   <si>
     <t xml:space="preserve">9.62367725372314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80698394775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89863967895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99029159545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.173602104187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2652559280396</t>
+    <t xml:space="preserve">9.80698490142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89863872528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99029350280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1736011505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2652549743652</t>
   </si>
   <si>
     <t xml:space="preserve">10.3569087982178</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5402173995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.631872177124</t>
+    <t xml:space="preserve">10.5402183532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6318712234497</t>
   </si>
   <si>
     <t xml:space="preserve">10.8151807785034</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7235250473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9068336486816</t>
+    <t xml:space="preserve">10.7235260009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9068326950073</t>
   </si>
   <si>
     <t xml:space="preserve">10.9984874725342</t>
@@ -425,22 +425,22 @@
     <t xml:space="preserve">11.1817960739136</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734508514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4567575454712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3651037216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4485635757446</t>
+    <t xml:space="preserve">11.2734518051147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4567584991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3651027679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4485626220703</t>
   </si>
   <si>
     <t xml:space="preserve">9.71533203125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79879093170166</t>
+    <t xml:space="preserve">8.79878997802734</t>
   </si>
   <si>
     <t xml:space="preserve">8.24886608123779</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">9.21123313903809</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30288696289062</t>
+    <t xml:space="preserve">9.30288791656494</t>
   </si>
   <si>
     <t xml:space="preserve">9.03709030151367</t>
@@ -473,16 +473,16 @@
     <t xml:space="preserve">9.94446754455566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82552337646484</t>
+    <t xml:space="preserve">9.82552433013916</t>
   </si>
   <si>
     <t xml:space="preserve">9.73283100128174</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59379005432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96456432342529</t>
+    <t xml:space="preserve">9.59379100799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96456527709961</t>
   </si>
   <si>
     <t xml:space="preserve">9.91821765899658</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">10.010910987854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1036043167114</t>
+    <t xml:space="preserve">10.1036052703857</t>
   </si>
   <si>
     <t xml:space="preserve">10.1499519348145</t>
@@ -512,16 +512,16 @@
     <t xml:space="preserve">10.057258605957</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2889928817749</t>
+    <t xml:space="preserve">10.2889919281006</t>
   </si>
   <si>
     <t xml:space="preserve">10.4743795394897</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2426452636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.381685256958</t>
+    <t xml:space="preserve">10.2426443099976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3816843032837</t>
   </si>
   <si>
     <t xml:space="preserve">9.68648338317871</t>
@@ -536,7 +536,7 @@
     <t xml:space="preserve">9.31570816040039</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23228454589844</t>
+    <t xml:space="preserve">9.23228359222412</t>
   </si>
   <si>
     <t xml:space="preserve">9.1952075958252</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">9.269362449646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21374607086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04689693450928</t>
+    <t xml:space="preserve">9.2137451171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04689788818359</t>
   </si>
   <si>
     <t xml:space="preserve">9.12105274200439</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0654354095459</t>
+    <t xml:space="preserve">9.06543636322021</t>
   </si>
   <si>
     <t xml:space="preserve">8.97274398803711</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">9.17666816711426</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02835845947266</t>
+    <t xml:space="preserve">9.02835750579834</t>
   </si>
   <si>
     <t xml:space="preserve">8.95420360565186</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">8.71319961547852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99128246307373</t>
+    <t xml:space="preserve">8.99128150939941</t>
   </si>
   <si>
     <t xml:space="preserve">8.76881694793701</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">8.89858722686768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93566608428955</t>
+    <t xml:space="preserve">8.93566513061523</t>
   </si>
   <si>
     <t xml:space="preserve">10.3353395462036</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">11.0305404663086</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2159280776978</t>
+    <t xml:space="preserve">11.2159290313721</t>
   </si>
   <si>
     <t xml:space="preserve">11.4940090179443</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">11.5403566360474</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5867023468018</t>
+    <t xml:space="preserve">11.5867033004761</t>
   </si>
   <si>
     <t xml:space="preserve">11.6330499649048</t>
@@ -617,10 +617,10 @@
     <t xml:space="preserve">11.9111299514771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9574766159058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1892108917236</t>
+    <t xml:space="preserve">11.9574756622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1892099380493</t>
   </si>
   <si>
     <t xml:space="preserve">12.2819051742554</t>
@@ -632,16 +632,16 @@
     <t xml:space="preserve">12.5136384963989</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3282527923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1428651809692</t>
+    <t xml:space="preserve">12.3282518386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1428642272949</t>
   </si>
   <si>
     <t xml:space="preserve">12.0965175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5551223754883</t>
+    <t xml:space="preserve">12.555121421814</t>
   </si>
   <si>
     <t xml:space="preserve">12.5082750320435</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">12.6488170623779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4614276885986</t>
+    <t xml:space="preserve">12.4614267349243</t>
   </si>
   <si>
     <t xml:space="preserve">12.4145793914795</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7425127029419</t>
+    <t xml:space="preserve">12.7425117492676</t>
   </si>
   <si>
     <t xml:space="preserve">12.6956644058228</t>
@@ -665,34 +665,34 @@
     <t xml:space="preserve">12.2271890640259</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1803426742554</t>
+    <t xml:space="preserve">12.1803417205811</t>
   </si>
   <si>
     <t xml:space="preserve">12.3208837509155</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2740383148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8362073898315</t>
+    <t xml:space="preserve">12.274037361145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8362064361572</t>
   </si>
   <si>
     <t xml:space="preserve">12.7893590927124</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6019687652588</t>
+    <t xml:space="preserve">12.6019697189331</t>
   </si>
   <si>
     <t xml:space="preserve">12.9299020767212</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8830537796021</t>
+    <t xml:space="preserve">12.8830547332764</t>
   </si>
   <si>
     <t xml:space="preserve">13.0704441070557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6794605255127</t>
+    <t xml:space="preserve">13.679461479187</t>
   </si>
   <si>
     <t xml:space="preserve">13.8668508529663</t>
@@ -704,25 +704,25 @@
     <t xml:space="preserve">14.3353252410889</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5695629119873</t>
+    <t xml:space="preserve">14.5695638656616</t>
   </si>
   <si>
     <t xml:space="preserve">15.2254276275635</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1317329406738</t>
+    <t xml:space="preserve">15.1317319869995</t>
   </si>
   <si>
     <t xml:space="preserve">14.7569532394409</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0380382537842</t>
+    <t xml:space="preserve">15.0380373001099</t>
   </si>
   <si>
     <t xml:space="preserve">15.1785802841187</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3191242218018</t>
+    <t xml:space="preserve">15.3191232681274</t>
   </si>
   <si>
     <t xml:space="preserve">14.8974943161011</t>
@@ -731,10 +731,10 @@
     <t xml:space="preserve">15.4596652984619</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4128179550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5533609390259</t>
+    <t xml:space="preserve">15.4128189086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5533599853516</t>
   </si>
   <si>
     <t xml:space="preserve">16.0686836242676</t>
@@ -746,10 +746,10 @@
     <t xml:space="preserve">17.0056324005127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7713947296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1930236816406</t>
+    <t xml:space="preserve">16.7713928222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.193021774292</t>
   </si>
   <si>
     <t xml:space="preserve">17.0524787902832</t>
@@ -761,19 +761,19 @@
     <t xml:space="preserve">16.7245464324951</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6308536529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5371551513672</t>
+    <t xml:space="preserve">16.6308517456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5371570587158</t>
   </si>
   <si>
     <t xml:space="preserve">16.584005355835</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2092247009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2560749053955</t>
+    <t xml:space="preserve">16.2092227935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2560729980469</t>
   </si>
   <si>
     <t xml:space="preserve">17.1461734771729</t>
@@ -797,37 +797,37 @@
     <t xml:space="preserve">16.1623764038086</t>
   </si>
   <si>
-    <t xml:space="preserve">15.974986076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7407503128052</t>
+    <t xml:space="preserve">15.9749879837036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7407484054565</t>
   </si>
   <si>
     <t xml:space="preserve">16.4434623718262</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9119338989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0993251800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.677698135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.818244934082</t>
+    <t xml:space="preserve">16.9119358062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0993270874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6776962280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8182430267334</t>
   </si>
   <si>
     <t xml:space="preserve">15.272274017334</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0848846435547</t>
+    <t xml:space="preserve">15.084885597229</t>
   </si>
   <si>
     <t xml:space="preserve">14.991189956665</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8037996292114</t>
+    <t xml:space="preserve">14.8038005828857</t>
   </si>
   <si>
     <t xml:space="preserve">14.4758682250977</t>
@@ -839,25 +839,25 @@
     <t xml:space="preserve">14.1010885238647</t>
   </si>
   <si>
-    <t xml:space="preserve">14.288477897644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5227146148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9605445861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2416296005249</t>
+    <t xml:space="preserve">14.2884788513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5227155685425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.960545539856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2416305541992</t>
   </si>
   <si>
     <t xml:space="preserve">14.1947832107544</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0073928833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7263078689575</t>
+    <t xml:space="preserve">14.0073938369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7263088226318</t>
   </si>
   <si>
     <t xml:space="preserve">14.1479358673096</t>
@@ -896,19 +896,19 @@
     <t xml:space="preserve">12.0866470336914</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9929533004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8992576599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0397987365723</t>
+    <t xml:space="preserve">11.9929523468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8992567062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0397996902466</t>
   </si>
   <si>
     <t xml:space="preserve">12.1334934234619</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4776287078857</t>
+    <t xml:space="preserve">11.4776296615601</t>
   </si>
   <si>
     <t xml:space="preserve">11.2433929443359</t>
@@ -920,43 +920,43 @@
     <t xml:space="preserve">11.6650190353394</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4307832717896</t>
+    <t xml:space="preserve">11.4307823181152</t>
   </si>
   <si>
     <t xml:space="preserve">10.9623079299927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7280702590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1965436935425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5713243484497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3370885848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2902393341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7118682861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.758713722229</t>
+    <t xml:space="preserve">10.7280712127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1965446472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.571325302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3370876312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2902402877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7118673324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7587146759033</t>
   </si>
   <si>
     <t xml:space="preserve">11.8055629730225</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0091543197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46319007873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33884906768799</t>
+    <t xml:space="preserve">11.0091552734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46318912506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33884811401367</t>
   </si>
   <si>
     <t xml:space="preserve">8.57308673858643</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">8.31074142456055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45128345489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61993408203125</t>
+    <t xml:space="preserve">8.45128440856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61993312835693</t>
   </si>
   <si>
     <t xml:space="preserve">8.44191360473633</t>
@@ -986,16 +986,16 @@
     <t xml:space="preserve">8.47002220153809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32011127471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20767688751221</t>
+    <t xml:space="preserve">8.32011032104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20767784118652</t>
   </si>
   <si>
     <t xml:space="preserve">8.08587265014648</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78605031967163</t>
+    <t xml:space="preserve">7.78604936599731</t>
   </si>
   <si>
     <t xml:space="preserve">7.49559497833252</t>
@@ -1013,19 +1013,19 @@
     <t xml:space="preserve">7.90785217285156</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50496530532837</t>
+    <t xml:space="preserve">7.50496482849121</t>
   </si>
   <si>
     <t xml:space="preserve">7.37379169464111</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12081480026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28009653091431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98027229309082</t>
+    <t xml:space="preserve">7.12081527709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28009700775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98027276992798</t>
   </si>
   <si>
     <t xml:space="preserve">6.93342542648315</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">7.34568309783936</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54244232177734</t>
+    <t xml:space="preserve">7.5424427986145</t>
   </si>
   <si>
     <t xml:space="preserve">8.19830703735352</t>
@@ -1055,16 +1055,16 @@
     <t xml:space="preserve">8.46116256713867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53747463226318</t>
+    <t xml:space="preserve">8.53747367858887</t>
   </si>
   <si>
     <t xml:space="preserve">8.68056106567383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77595233917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8427267074585</t>
+    <t xml:space="preserve">8.77595138549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84272575378418</t>
   </si>
   <si>
     <t xml:space="preserve">8.72825527191162</t>
@@ -1073,25 +1073,25 @@
     <t xml:space="preserve">8.66148281097412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49931812286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42300510406494</t>
+    <t xml:space="preserve">8.49931716918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42300605773926</t>
   </si>
   <si>
     <t xml:space="preserve">8.39438915252686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.604248046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48977947235107</t>
+    <t xml:space="preserve">8.60424900054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48977851867676</t>
   </si>
   <si>
     <t xml:space="preserve">8.29899787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12729454040527</t>
+    <t xml:space="preserve">8.12729549407959</t>
   </si>
   <si>
     <t xml:space="preserve">7.89835643768311</t>
@@ -1100,13 +1100,13 @@
     <t xml:space="preserve">8.10821628570557</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84112215042114</t>
+    <t xml:space="preserve">7.8411226272583</t>
   </si>
   <si>
     <t xml:space="preserve">8.33715343475342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2036075592041</t>
+    <t xml:space="preserve">8.20360660552979</t>
   </si>
   <si>
     <t xml:space="preserve">8.06052017211914</t>
@@ -1115,13 +1115,13 @@
     <t xml:space="preserve">8.07959938049316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07005882263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92697429656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98420858383179</t>
+    <t xml:space="preserve">8.07005977630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92697334289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98420763015747</t>
   </si>
   <si>
     <t xml:space="preserve">8.30853652954102</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">8.26084136962891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27038097381592</t>
+    <t xml:space="preserve">8.2703800201416</t>
   </si>
   <si>
     <t xml:space="preserve">8.18452835083008</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03190326690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96513080596924</t>
+    <t xml:space="preserve">8.03190422058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96512985229492</t>
   </si>
   <si>
     <t xml:space="preserve">7.86019992828369</t>
@@ -1151,10 +1151,10 @@
     <t xml:space="preserve">7.71711397171021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91743516921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76481008529663</t>
+    <t xml:space="preserve">7.91743421554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76480960845947</t>
   </si>
   <si>
     <t xml:space="preserve">7.72665309906006</t>
@@ -1169,10 +1169,10 @@
     <t xml:space="preserve">7.65987968444824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16545104980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32761383056641</t>
+    <t xml:space="preserve">8.165452003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32761478424072</t>
   </si>
   <si>
     <t xml:space="preserve">8.11775588989258</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">8.2322244644165</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31807518005371</t>
+    <t xml:space="preserve">8.31807613372803</t>
   </si>
   <si>
     <t xml:space="preserve">8.15591144561768</t>
@@ -1196,19 +1196,19 @@
     <t xml:space="preserve">8.22268486022949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25130176544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35623168945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24176406860352</t>
+    <t xml:space="preserve">8.25130081176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35623264312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2417631149292</t>
   </si>
   <si>
     <t xml:space="preserve">8.34669303894043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95559167861938</t>
+    <t xml:space="preserve">7.95559072494507</t>
   </si>
   <si>
     <t xml:space="preserve">7.77434825897217</t>
@@ -1220,37 +1220,37 @@
     <t xml:space="preserve">7.97466850280762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01282596588135</t>
+    <t xml:space="preserve">8.01282501220703</t>
   </si>
   <si>
     <t xml:space="preserve">8.05098152160645</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67895746231079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73619174957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69803524017334</t>
+    <t xml:space="preserve">7.67895793914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7361912727356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6980357170105</t>
   </si>
   <si>
     <t xml:space="preserve">7.51679372787476</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59310626983643</t>
+    <t xml:space="preserve">7.59310579299927</t>
   </si>
   <si>
     <t xml:space="preserve">7.44048070907593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5358715057373</t>
+    <t xml:space="preserve">7.53587198257446</t>
   </si>
   <si>
     <t xml:space="preserve">7.62172269821167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52633190155029</t>
+    <t xml:space="preserve">7.52633237838745</t>
   </si>
   <si>
     <t xml:space="preserve">7.34508991241455</t>
@@ -1259,22 +1259,22 @@
     <t xml:space="preserve">7.20200395584106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18292570114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14476871490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12569046020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23062133789062</t>
+    <t xml:space="preserve">7.1829252243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14476919174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12569093704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23062086105347</t>
   </si>
   <si>
     <t xml:space="preserve">7.1543083190918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24969863891602</t>
+    <t xml:space="preserve">7.24969911575317</t>
   </si>
   <si>
     <t xml:space="preserve">7.24016046524048</t>
@@ -1283,16 +1283,16 @@
     <t xml:space="preserve">7.46909809112549</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41186332702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45001983642578</t>
+    <t xml:space="preserve">7.41186380386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45001935958862</t>
   </si>
   <si>
     <t xml:space="preserve">7.28785514831543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39278507232666</t>
+    <t xml:space="preserve">7.39278554916382</t>
   </si>
   <si>
     <t xml:space="preserve">7.3355507850647</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">7.61218404769897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90789556503296</t>
+    <t xml:space="preserve">7.90789604187012</t>
   </si>
   <si>
     <t xml:space="preserve">7.94605159759521</t>
@@ -1313,25 +1313,25 @@
     <t xml:space="preserve">7.70757484436035</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8792781829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99374771118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75527000427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81250381469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79342699050903</t>
+    <t xml:space="preserve">7.87927913665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99374675750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75527048110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81250429153442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79342651367188</t>
   </si>
   <si>
     <t xml:space="preserve">7.80296611785889</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85065984725952</t>
+    <t xml:space="preserve">7.85066080093384</t>
   </si>
   <si>
     <t xml:space="preserve">7.74573087692261</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">7.83158302307129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66941785812378</t>
+    <t xml:space="preserve">7.66941833496094</t>
   </si>
   <si>
     <t xml:space="preserve">7.60264492034912</t>
@@ -1361,13 +1361,13 @@
     <t xml:space="preserve">7.3641676902771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10661268234253</t>
+    <t xml:space="preserve">7.10661315917969</t>
   </si>
   <si>
     <t xml:space="preserve">7.27831649780273</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08753490447998</t>
+    <t xml:space="preserve">7.08753442764282</t>
   </si>
   <si>
     <t xml:space="preserve">7.05891799926758</t>
@@ -2253,6 +2253,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.68000030517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64000034332275</t>
   </si>
 </sst>
 </file>
@@ -63041,7 +63044,7 @@
     </row>
     <row r="2326">
       <c r="A2326" s="1" t="n">
-        <v>46001.6910185185</v>
+        <v>46001.3333333333</v>
       </c>
       <c r="B2326" t="n">
         <v>52226</v>
@@ -63062,6 +63065,32 @@
         <v>746</v>
       </c>
       <c r="H2326" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2327">
+      <c r="A2327" s="1" t="n">
+        <v>46002.6911226852</v>
+      </c>
+      <c r="B2327" t="n">
+        <v>20292</v>
+      </c>
+      <c r="C2327" t="n">
+        <v>9.68000030517578</v>
+      </c>
+      <c r="D2327" t="n">
+        <v>9.52000045776367</v>
+      </c>
+      <c r="E2327" t="n">
+        <v>9.52000045776367</v>
+      </c>
+      <c r="F2327" t="n">
+        <v>9.64000034332275</v>
+      </c>
+      <c r="G2327" t="s">
+        <v>747</v>
+      </c>
+      <c r="H2327" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="748">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="749">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,34 +44,34 @@
     <t xml:space="preserve">FF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98565769195557</t>
+    <t xml:space="preserve">8.98565864562988</t>
   </si>
   <si>
     <t xml:space="preserve">9.08549880981445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24887275695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09457492828369</t>
+    <t xml:space="preserve">9.24887371063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09457397460938</t>
   </si>
   <si>
     <t xml:space="preserve">9.12180423736572</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03104114532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95388984680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89943218231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89489269256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84951019287109</t>
+    <t xml:space="preserve">9.03104019165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95389080047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8994312286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8948917388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84951210021973</t>
   </si>
   <si>
     <t xml:space="preserve">8.85858821868896</t>
@@ -80,13 +80,13 @@
     <t xml:space="preserve">8.87674045562744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76782321929932</t>
+    <t xml:space="preserve">8.76782417297363</t>
   </si>
   <si>
     <t xml:space="preserve">8.86766529083252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04919242858887</t>
+    <t xml:space="preserve">9.04919338226318</t>
   </si>
   <si>
     <t xml:space="preserve">9.23072147369385</t>
@@ -95,7 +95,7 @@
     <t xml:space="preserve">9.11272716522217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96750450134277</t>
+    <t xml:space="preserve">8.96750545501709</t>
   </si>
   <si>
     <t xml:space="preserve">8.91304588317871</t>
@@ -104,19 +104,19 @@
     <t xml:space="preserve">8.92212295532227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00381183624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15810966491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16718578338623</t>
+    <t xml:space="preserve">9.00381088256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15810871124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16718673706055</t>
   </si>
   <si>
     <t xml:space="preserve">9.43947792053223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54839515686035</t>
+    <t xml:space="preserve">9.54839611053467</t>
   </si>
   <si>
     <t xml:space="preserve">9.62100791931152</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">9.57562446594238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53024196624756</t>
+    <t xml:space="preserve">9.53024291992188</t>
   </si>
   <si>
     <t xml:space="preserve">9.50301361083984</t>
@@ -158,25 +158,25 @@
     <t xml:space="preserve">9.93868255615234</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98406219482422</t>
+    <t xml:space="preserve">9.98406314849854</t>
   </si>
   <si>
     <t xml:space="preserve">9.73900032043457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7662296295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74807739257812</t>
+    <t xml:space="preserve">9.76623153686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74807643890381</t>
   </si>
   <si>
     <t xml:space="preserve">9.75715351104736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64823627471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82068729400635</t>
+    <t xml:space="preserve">9.64823722839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82068824768066</t>
   </si>
   <si>
     <t xml:space="preserve">9.7026948928833</t>
@@ -185,49 +185,49 @@
     <t xml:space="preserve">9.72084712982178</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67546558380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66638851165771</t>
+    <t xml:space="preserve">9.67546463012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66639041900635</t>
   </si>
   <si>
     <t xml:space="preserve">9.63008308410645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65731430053711</t>
+    <t xml:space="preserve">9.65731334686279</t>
   </si>
   <si>
     <t xml:space="preserve">9.68454170227051</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81161308288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8297643661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8479175567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83884048461914</t>
+    <t xml:space="preserve">9.81161212921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82976531982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84791660308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83884143829346</t>
   </si>
   <si>
     <t xml:space="preserve">9.72992420196533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78438282012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55747222900391</t>
+    <t xml:space="preserve">9.78438186645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55747318267822</t>
   </si>
   <si>
     <t xml:space="preserve">9.34871482849121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33963871002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27610397338867</t>
+    <t xml:space="preserve">9.33963775634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27610301971436</t>
   </si>
   <si>
     <t xml:space="preserve">9.25794982910156</t>
@@ -236,70 +236,70 @@
     <t xml:space="preserve">9.19441509246826</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18533897399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41224956512451</t>
+    <t xml:space="preserve">9.18533992767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4122486114502</t>
   </si>
   <si>
     <t xml:space="preserve">9.22164440155029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31240844726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2670259475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29425621032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28517913818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37594413757324</t>
+    <t xml:space="preserve">9.31240749359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26702690124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29425525665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28518009185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37594318389893</t>
   </si>
   <si>
     <t xml:space="preserve">9.366868019104</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38501930236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45763111114502</t>
+    <t xml:space="preserve">9.3850212097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45763206481934</t>
   </si>
   <si>
     <t xml:space="preserve">9.39409732818604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48486137390137</t>
+    <t xml:space="preserve">9.48486042022705</t>
   </si>
   <si>
     <t xml:space="preserve">9.49393749237061</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44855403900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47578430175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23979663848877</t>
+    <t xml:space="preserve">9.44855499267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4757833480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2397985458374</t>
   </si>
   <si>
     <t xml:space="preserve">9.14903259277344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21256732940674</t>
+    <t xml:space="preserve">9.21256637573242</t>
   </si>
   <si>
     <t xml:space="preserve">9.20349216461182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13088130950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1399564743042</t>
+    <t xml:space="preserve">9.13088035583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13995742797852</t>
   </si>
   <si>
     <t xml:space="preserve">8.94027519226074</t>
@@ -311,19 +311,19 @@
     <t xml:space="preserve">8.75874614715576</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66798305511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62259960174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53183650970459</t>
+    <t xml:space="preserve">8.66798400878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62260055541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53183555603027</t>
   </si>
   <si>
     <t xml:space="preserve">8.35030937194824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16877937316895</t>
+    <t xml:space="preserve">8.16878032684326</t>
   </si>
   <si>
     <t xml:space="preserve">7.9872522354126</t>
@@ -338,37 +338,37 @@
     <t xml:space="preserve">8.25954341888428</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9418683052063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30492496490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21416187286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39569187164307</t>
+    <t xml:space="preserve">7.94186925888062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30492687225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21416282653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39568996429443</t>
   </si>
   <si>
     <t xml:space="preserve">8.57721710205078</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71336555480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53202342987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25706005096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44036865234375</t>
+    <t xml:space="preserve">8.71336460113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53202247619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25706100463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44036960601807</t>
   </si>
   <si>
     <t xml:space="preserve">9.16540718078613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07375240325928</t>
+    <t xml:space="preserve">9.07375144958496</t>
   </si>
   <si>
     <t xml:space="preserve">9.11957931518555</t>
@@ -377,34 +377,34 @@
     <t xml:space="preserve">8.98209857940674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02792453765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62367725372314</t>
+    <t xml:space="preserve">9.02792549133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62367630004883</t>
   </si>
   <si>
     <t xml:space="preserve">9.80698490142822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89863872528076</t>
+    <t xml:space="preserve">9.89863967895508</t>
   </si>
   <si>
     <t xml:space="preserve">9.99029350280762</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1736011505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2652549743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3569087982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5402183532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6318712234497</t>
+    <t xml:space="preserve">10.173602104187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2652559280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3569097518921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5402173995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.631872177124</t>
   </si>
   <si>
     <t xml:space="preserve">10.8151807785034</t>
@@ -413,31 +413,31 @@
     <t xml:space="preserve">10.7235260009766</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9068326950073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9984874725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.090142250061</t>
+    <t xml:space="preserve">10.9068336486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9984884262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0901432037354</t>
   </si>
   <si>
     <t xml:space="preserve">11.1817960739136</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734518051147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4567584991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3651027679443</t>
+    <t xml:space="preserve">11.2734489440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4567575454712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3651037216187</t>
   </si>
   <si>
     <t xml:space="preserve">10.4485626220703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71533203125</t>
+    <t xml:space="preserve">9.71533107757568</t>
   </si>
   <si>
     <t xml:space="preserve">8.79878997802734</t>
@@ -449,22 +449,22 @@
     <t xml:space="preserve">9.21123313903809</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30288791656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03709030151367</t>
+    <t xml:space="preserve">9.30288696289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03709125518799</t>
   </si>
   <si>
     <t xml:space="preserve">9.39454174041748</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76115798950195</t>
+    <t xml:space="preserve">9.76115703582764</t>
   </si>
   <si>
     <t xml:space="preserve">9.66950416564941</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57784938812256</t>
+    <t xml:space="preserve">9.57785034179688</t>
   </si>
   <si>
     <t xml:space="preserve">10.0361194610596</t>
@@ -479,31 +479,31 @@
     <t xml:space="preserve">9.73283100128174</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59379100799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96456527709961</t>
+    <t xml:space="preserve">9.59379005432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96456432342529</t>
   </si>
   <si>
     <t xml:space="preserve">9.91821765899658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54744338989258</t>
+    <t xml:space="preserve">9.54744243621826</t>
   </si>
   <si>
     <t xml:space="preserve">10.010910987854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1036052703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1499519348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1962976455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77917766571045</t>
+    <t xml:space="preserve">10.1036033630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1499509811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1962985992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77917671203613</t>
   </si>
   <si>
     <t xml:space="preserve">9.87187099456787</t>
@@ -521,55 +521,55 @@
     <t xml:space="preserve">10.2426443099976</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3816843032837</t>
+    <t xml:space="preserve">10.3816862106323</t>
   </si>
   <si>
     <t xml:space="preserve">9.68648338317871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64013671875</t>
+    <t xml:space="preserve">9.64013576507568</t>
   </si>
   <si>
     <t xml:space="preserve">9.50109577178955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31570816040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23228359222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1952075958252</t>
+    <t xml:space="preserve">9.31570911407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23228454589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19520664215088</t>
   </si>
   <si>
     <t xml:space="preserve">9.25082302093506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.269362449646</t>
+    <t xml:space="preserve">9.26936340332031</t>
   </si>
   <si>
     <t xml:space="preserve">9.2137451171875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04689788818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12105274200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06543636322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97274398803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17666816711426</t>
+    <t xml:space="preserve">9.04689693450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12105369567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0654354095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97274303436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17666721343994</t>
   </si>
   <si>
     <t xml:space="preserve">9.02835750579834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95420360565186</t>
+    <t xml:space="preserve">8.95420455932617</t>
   </si>
   <si>
     <t xml:space="preserve">8.71319961547852</t>
@@ -584,22 +584,22 @@
     <t xml:space="preserve">8.89858722686768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93566513061523</t>
+    <t xml:space="preserve">8.93566608428955</t>
   </si>
   <si>
     <t xml:space="preserve">10.3353395462036</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9841938018799</t>
+    <t xml:space="preserve">10.9841947555542</t>
   </si>
   <si>
     <t xml:space="preserve">11.0305404663086</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2159290313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4940090179443</t>
+    <t xml:space="preserve">11.2159280776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4940099716187</t>
   </si>
   <si>
     <t xml:space="preserve">11.5403566360474</t>
@@ -611,16 +611,16 @@
     <t xml:space="preserve">11.6330499649048</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7257423400879</t>
+    <t xml:space="preserve">11.7257432937622</t>
   </si>
   <si>
     <t xml:space="preserve">11.9111299514771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9574756622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1892099380493</t>
+    <t xml:space="preserve">11.9574766159058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1892108917236</t>
   </si>
   <si>
     <t xml:space="preserve">12.2819051742554</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">12.3282518386841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1428642272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0965175628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.555121421814</t>
+    <t xml:space="preserve">12.1428651809692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0965185165405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5551223754883</t>
   </si>
   <si>
     <t xml:space="preserve">12.5082750320435</t>
@@ -656,16 +656,16 @@
     <t xml:space="preserve">12.4145793914795</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7425117492676</t>
+    <t xml:space="preserve">12.7425127029419</t>
   </si>
   <si>
     <t xml:space="preserve">12.6956644058228</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2271890640259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1803417205811</t>
+    <t xml:space="preserve">12.2271900177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1803426742554</t>
   </si>
   <si>
     <t xml:space="preserve">12.3208837509155</t>
@@ -677,16 +677,16 @@
     <t xml:space="preserve">12.8362064361572</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7893590927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6019697189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9299020767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8830547332764</t>
+    <t xml:space="preserve">12.7893581390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6019687652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9299011230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8830537796021</t>
   </si>
   <si>
     <t xml:space="preserve">13.0704441070557</t>
@@ -698,25 +698,25 @@
     <t xml:space="preserve">13.8668508529663</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0542402267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3353252410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5695638656616</t>
+    <t xml:space="preserve">14.0542411804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3353261947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5695629119873</t>
   </si>
   <si>
     <t xml:space="preserve">15.2254276275635</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1317319869995</t>
+    <t xml:space="preserve">15.1317329406738</t>
   </si>
   <si>
     <t xml:space="preserve">14.7569532394409</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0380373001099</t>
+    <t xml:space="preserve">15.0380382537842</t>
   </si>
   <si>
     <t xml:space="preserve">15.1785802841187</t>
@@ -725,22 +725,22 @@
     <t xml:space="preserve">15.3191232681274</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8974943161011</t>
+    <t xml:space="preserve">14.8974952697754</t>
   </si>
   <si>
     <t xml:space="preserve">15.4596652984619</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4128189086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5533599853516</t>
+    <t xml:space="preserve">15.4128179550171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5533609390259</t>
   </si>
   <si>
     <t xml:space="preserve">16.0686836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8650875091553</t>
+    <t xml:space="preserve">16.8650913238525</t>
   </si>
   <si>
     <t xml:space="preserve">17.0056324005127</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">17.193021774292</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0524787902832</t>
+    <t xml:space="preserve">17.0524806976318</t>
   </si>
   <si>
     <t xml:space="preserve">16.9587841033936</t>
@@ -761,16 +761,16 @@
     <t xml:space="preserve">16.7245464324951</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6308517456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5371570587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.584005355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2092227935791</t>
+    <t xml:space="preserve">16.6308498382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5371551513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5840034484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2092247009277</t>
   </si>
   <si>
     <t xml:space="preserve">16.2560729980469</t>
@@ -782,40 +782,40 @@
     <t xml:space="preserve">16.396614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3029174804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8344440460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1155300140381</t>
+    <t xml:space="preserve">16.3029193878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8344430923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1155319213867</t>
   </si>
   <si>
     <t xml:space="preserve">16.0218353271484</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1623764038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9749879837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7407484054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4434623718262</t>
+    <t xml:space="preserve">16.1623783111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.974986076355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7407493591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4434604644775</t>
   </si>
   <si>
     <t xml:space="preserve">16.9119358062744</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0993270874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6776962280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8182430267334</t>
+    <t xml:space="preserve">17.0993251800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6777000427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.818244934082</t>
   </si>
   <si>
     <t xml:space="preserve">15.272274017334</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">14.991189956665</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8038005828857</t>
+    <t xml:space="preserve">14.8038015365601</t>
   </si>
   <si>
     <t xml:space="preserve">14.4758682250977</t>
@@ -836,28 +836,28 @@
     <t xml:space="preserve">14.382173538208</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1010885238647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2884788513184</t>
+    <t xml:space="preserve">14.1010875701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.288477897644</t>
   </si>
   <si>
     <t xml:space="preserve">14.5227155685425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.960545539856</t>
+    <t xml:space="preserve">13.9605464935303</t>
   </si>
   <si>
     <t xml:space="preserve">14.2416305541992</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1947832107544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0073938369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7263088226318</t>
+    <t xml:space="preserve">14.1947822570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0073928833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7263078689575</t>
   </si>
   <si>
     <t xml:space="preserve">14.1479358673096</t>
@@ -872,25 +872,25 @@
     <t xml:space="preserve">13.7731552124023</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3515291213989</t>
+    <t xml:space="preserve">13.3515281677246</t>
   </si>
   <si>
     <t xml:space="preserve">13.3046817779541</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3983764648438</t>
+    <t xml:space="preserve">13.3983774185181</t>
   </si>
   <si>
     <t xml:space="preserve">13.0235967636108</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1172924041748</t>
+    <t xml:space="preserve">13.1172914505005</t>
   </si>
   <si>
     <t xml:space="preserve">12.976749420166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3677320480347</t>
+    <t xml:space="preserve">12.3677310943604</t>
   </si>
   <si>
     <t xml:space="preserve">12.0866470336914</t>
@@ -899,25 +899,25 @@
     <t xml:space="preserve">11.9929523468018</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8992567062378</t>
+    <t xml:space="preserve">11.8992576599121</t>
   </si>
   <si>
     <t xml:space="preserve">12.0397996902466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1334934234619</t>
+    <t xml:space="preserve">12.1334943771362</t>
   </si>
   <si>
     <t xml:space="preserve">11.4776296615601</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2433929443359</t>
+    <t xml:space="preserve">11.2433938980103</t>
   </si>
   <si>
     <t xml:space="preserve">11.3839340209961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6650190353394</t>
+    <t xml:space="preserve">11.6650199890137</t>
   </si>
   <si>
     <t xml:space="preserve">11.4307823181152</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">11.571325302124</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3370876312256</t>
+    <t xml:space="preserve">11.3370885848999</t>
   </si>
   <si>
     <t xml:space="preserve">11.2902402877808</t>
@@ -956,31 +956,31 @@
     <t xml:space="preserve">9.46318912506104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33884811401367</t>
+    <t xml:space="preserve">8.3388500213623</t>
   </si>
   <si>
     <t xml:space="preserve">8.57308673858643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31074142456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45128440856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61993312835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44191360473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32948112487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25452423095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43254375457764</t>
+    <t xml:space="preserve">8.31074237823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45128345489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61993503570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44191455841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32948017120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25452518463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43254566192627</t>
   </si>
   <si>
     <t xml:space="preserve">8.47002220153809</t>
@@ -989,31 +989,31 @@
     <t xml:space="preserve">8.32011032104492</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20767784118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08587265014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78604936599731</t>
+    <t xml:space="preserve">8.20767688751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0858736038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78605031967163</t>
   </si>
   <si>
     <t xml:space="preserve">7.49559497833252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33631420135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23324918746948</t>
+    <t xml:space="preserve">7.33631372451782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23324871063232</t>
   </si>
   <si>
     <t xml:space="preserve">7.83289670944214</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90785217285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50496482849121</t>
+    <t xml:space="preserve">7.90785264968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50496530532837</t>
   </si>
   <si>
     <t xml:space="preserve">7.37379169464111</t>
@@ -1022,19 +1022,19 @@
     <t xml:space="preserve">7.12081527709961</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28009700775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98027276992798</t>
+    <t xml:space="preserve">7.28009653091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98027324676514</t>
   </si>
   <si>
     <t xml:space="preserve">6.93342542648315</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06459856033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0271201133728</t>
+    <t xml:space="preserve">7.06459808349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02712059020996</t>
   </si>
   <si>
     <t xml:space="preserve">7.34568309783936</t>
@@ -1058,7 +1058,7 @@
     <t xml:space="preserve">8.53747367858887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68056106567383</t>
+    <t xml:space="preserve">8.68056201934814</t>
   </si>
   <si>
     <t xml:space="preserve">8.77595138549805</t>
@@ -1067,16 +1067,16 @@
     <t xml:space="preserve">8.84272575378418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72825527191162</t>
+    <t xml:space="preserve">8.72825622558594</t>
   </si>
   <si>
     <t xml:space="preserve">8.66148281097412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49931716918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42300605773926</t>
+    <t xml:space="preserve">8.49931812286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42300510406494</t>
   </si>
   <si>
     <t xml:space="preserve">8.39438915252686</t>
@@ -1091,22 +1091,22 @@
     <t xml:space="preserve">8.29899787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12729549407959</t>
+    <t xml:space="preserve">8.12729454040527</t>
   </si>
   <si>
     <t xml:space="preserve">7.89835643768311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10821628570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8411226272583</t>
+    <t xml:space="preserve">8.10821723937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84112215042114</t>
   </si>
   <si>
     <t xml:space="preserve">8.33715343475342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20360660552979</t>
+    <t xml:space="preserve">8.2036075592041</t>
   </si>
   <si>
     <t xml:space="preserve">8.06052017211914</t>
@@ -1118,22 +1118,22 @@
     <t xml:space="preserve">8.07005977630615</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92697334289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98420763015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30853652954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26084136962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2703800201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18452835083008</t>
+    <t xml:space="preserve">7.92697429656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98420810699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30853748321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26084041595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27038097381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18452930450439</t>
   </si>
   <si>
     <t xml:space="preserve">8.03190422058105</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">7.96512985229492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86019992828369</t>
+    <t xml:space="preserve">7.86020040512085</t>
   </si>
   <si>
     <t xml:space="preserve">7.86973905563354</t>
@@ -1151,7 +1151,7 @@
     <t xml:space="preserve">7.71711397171021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91743421554565</t>
+    <t xml:space="preserve">7.91743516921997</t>
   </si>
   <si>
     <t xml:space="preserve">7.76480960845947</t>
@@ -1166,19 +1166,19 @@
     <t xml:space="preserve">7.63126230239868</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65987968444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.165452003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32761478424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11775588989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93651247024536</t>
+    <t xml:space="preserve">7.65987920761108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16545009613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32761383056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11775493621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9365119934082</t>
   </si>
   <si>
     <t xml:space="preserve">8.19406795501709</t>
@@ -1190,13 +1190,13 @@
     <t xml:space="preserve">8.31807613372803</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15591144561768</t>
+    <t xml:space="preserve">8.15591239929199</t>
   </si>
   <si>
     <t xml:space="preserve">8.22268486022949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25130081176758</t>
+    <t xml:space="preserve">8.25130176544189</t>
   </si>
   <si>
     <t xml:space="preserve">8.35623264312744</t>
@@ -1208,7 +1208,7 @@
     <t xml:space="preserve">8.34669303894043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95559072494507</t>
+    <t xml:space="preserve">7.95559167861938</t>
   </si>
   <si>
     <t xml:space="preserve">7.77434825897217</t>
@@ -1226,31 +1226,31 @@
     <t xml:space="preserve">8.05098152160645</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67895793914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7361912727356</t>
+    <t xml:space="preserve">7.67895746231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73619222640991</t>
   </si>
   <si>
     <t xml:space="preserve">7.6980357170105</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51679372787476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59310579299927</t>
+    <t xml:space="preserve">7.5167932510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59310626983643</t>
   </si>
   <si>
     <t xml:space="preserve">7.44048070907593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53587198257446</t>
+    <t xml:space="preserve">7.5358715057373</t>
   </si>
   <si>
     <t xml:space="preserve">7.62172269821167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52633237838745</t>
+    <t xml:space="preserve">7.52633190155029</t>
   </si>
   <si>
     <t xml:space="preserve">7.34508991241455</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">7.20200395584106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1829252243042</t>
+    <t xml:space="preserve">7.18292617797852</t>
   </si>
   <si>
     <t xml:space="preserve">7.14476919174194</t>
@@ -1274,37 +1274,37 @@
     <t xml:space="preserve">7.1543083190918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24969911575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24016046524048</t>
+    <t xml:space="preserve">7.24969863891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24015998840332</t>
   </si>
   <si>
     <t xml:space="preserve">7.46909809112549</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41186380386353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45001935958862</t>
+    <t xml:space="preserve">7.41186332702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45001983642578</t>
   </si>
   <si>
     <t xml:space="preserve">7.28785514831543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39278554916382</t>
+    <t xml:space="preserve">7.39278507232666</t>
   </si>
   <si>
     <t xml:space="preserve">7.3355507850647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61218404769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90789604187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94605159759521</t>
+    <t xml:space="preserve">7.61218452453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90789556503296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94605112075806</t>
   </si>
   <si>
     <t xml:space="preserve">7.45955896377563</t>
@@ -1313,25 +1313,25 @@
     <t xml:space="preserve">7.70757484436035</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87927913665771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99374675750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75527048110962</t>
+    <t xml:space="preserve">7.8792781829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99374723434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75527000427246</t>
   </si>
   <si>
     <t xml:space="preserve">7.81250429153442</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79342651367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80296611785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85066080093384</t>
+    <t xml:space="preserve">7.79342699050903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80296564102173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85066032409668</t>
   </si>
   <si>
     <t xml:space="preserve">7.74573087692261</t>
@@ -1343,25 +1343,25 @@
     <t xml:space="preserve">7.66941833496094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60264492034912</t>
+    <t xml:space="preserve">7.60264444351196</t>
   </si>
   <si>
     <t xml:space="preserve">7.58356666564941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88881826400757</t>
+    <t xml:space="preserve">7.88881778717041</t>
   </si>
   <si>
     <t xml:space="preserve">8.00328636169434</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78388738632202</t>
+    <t xml:space="preserve">7.78388690948486</t>
   </si>
   <si>
     <t xml:space="preserve">7.3641676902771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10661315917969</t>
+    <t xml:space="preserve">7.10661268234253</t>
   </si>
   <si>
     <t xml:space="preserve">7.27831649780273</t>
@@ -1376,10 +1376,10 @@
     <t xml:space="preserve">7.50372648239136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98721408843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02589225769043</t>
+    <t xml:space="preserve">7.98721361160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02589321136475</t>
   </si>
   <si>
     <t xml:space="preserve">8.04523086547852</t>
@@ -1391,25 +1391,25 @@
     <t xml:space="preserve">8.07424163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12258911132812</t>
+    <t xml:space="preserve">8.12259006500244</t>
   </si>
   <si>
     <t xml:space="preserve">8.05490112304688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94853496551514</t>
+    <t xml:space="preserve">7.94853448867798</t>
   </si>
   <si>
     <t xml:space="preserve">8.06457138061523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08390998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97754430770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93886518478394</t>
+    <t xml:space="preserve">8.08391094207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97754383087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93886423110962</t>
   </si>
   <si>
     <t xml:space="preserve">7.79381895065308</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">7.68745088577271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63910293579102</t>
+    <t xml:space="preserve">7.63910245895386</t>
   </si>
   <si>
     <t xml:space="preserve">7.73579978942871</t>
@@ -1436,10 +1436,10 @@
     <t xml:space="preserve">7.90985584259033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85183668136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83249759674072</t>
+    <t xml:space="preserve">7.85183715820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83249807357788</t>
   </si>
   <si>
     <t xml:space="preserve">7.81315755844116</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">7.80348825454712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78414916992188</t>
+    <t xml:space="preserve">7.78414869308472</t>
   </si>
   <si>
     <t xml:space="preserve">7.6681113243103</t>
@@ -1460,13 +1460,13 @@
     <t xml:space="preserve">7.71646022796631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75513982772827</t>
+    <t xml:space="preserve">7.75514030456543</t>
   </si>
   <si>
     <t xml:space="preserve">7.74547004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86150693893433</t>
+    <t xml:space="preserve">7.86150646209717</t>
   </si>
   <si>
     <t xml:space="preserve">7.89051580429077</t>
@@ -1484,10 +1484,10 @@
     <t xml:space="preserve">8.09358024597168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13225936889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1515998840332</t>
+    <t xml:space="preserve">8.1322603225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15159893035889</t>
   </si>
   <si>
     <t xml:space="preserve">8.1129207611084</t>
@@ -1496,10 +1496,10 @@
     <t xml:space="preserve">8.03556251525879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92919492721558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69712066650391</t>
+    <t xml:space="preserve">7.92919540405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69712114334106</t>
   </si>
   <si>
     <t xml:space="preserve">7.60042381286621</t>
@@ -1508,10 +1508,10 @@
     <t xml:space="preserve">7.88084602355957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55207443237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40702819824219</t>
+    <t xml:space="preserve">7.55207490921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40702867507935</t>
   </si>
   <si>
     <t xml:space="preserve">7.34900999069214</t>
@@ -1520,16 +1520,16 @@
     <t xml:space="preserve">7.37801933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43603754043579</t>
+    <t xml:space="preserve">7.43603801727295</t>
   </si>
   <si>
     <t xml:space="preserve">7.41669797897339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52306604385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36834955215454</t>
+    <t xml:space="preserve">7.5230655670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36834907531738</t>
   </si>
   <si>
     <t xml:space="preserve">7.542405128479</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">7.4843864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70679044723511</t>
+    <t xml:space="preserve">7.70679092407227</t>
   </si>
   <si>
     <t xml:space="preserve">7.64877223968506</t>
@@ -1556,10 +1556,10 @@
     <t xml:space="preserve">7.59075355529785</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95820426940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96787405014038</t>
+    <t xml:space="preserve">7.95820331573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96787357330322</t>
   </si>
   <si>
     <t xml:space="preserve">7.90018606185913</t>
@@ -1577,10 +1577,10 @@
     <t xml:space="preserve">8.19027900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29664611816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45136165618896</t>
+    <t xml:space="preserve">8.29664516448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45136070251465</t>
   </si>
   <si>
     <t xml:space="preserve">8.48037147521973</t>
@@ -1607,19 +1607,19 @@
     <t xml:space="preserve">8.50938034057617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4223518371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54805946350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55772972106934</t>
+    <t xml:space="preserve">8.42235279083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54805850982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55772876739502</t>
   </si>
   <si>
     <t xml:space="preserve">8.52871990203857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68343448638916</t>
+    <t xml:space="preserve">8.68343544006348</t>
   </si>
   <si>
     <t xml:space="preserve">8.76079368591309</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">8.65442562103271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75112438201904</t>
+    <t xml:space="preserve">8.75112342834473</t>
   </si>
   <si>
     <t xml:space="preserve">8.70277500152588</t>
@@ -1652,10 +1652,10 @@
     <t xml:space="preserve">8.63508701324463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32565402984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31598472595215</t>
+    <t xml:space="preserve">8.32565498352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31598567962646</t>
   </si>
   <si>
     <t xml:space="preserve">8.30631542205811</t>
@@ -2256,6 +2256,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.64000034332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84000015258789</t>
   </si>
 </sst>
 </file>
@@ -63070,7 +63073,7 @@
     </row>
     <row r="2327">
       <c r="A2327" s="1" t="n">
-        <v>46002.6911226852</v>
+        <v>46002.3333333333</v>
       </c>
       <c r="B2327" t="n">
         <v>20292</v>
@@ -63091,6 +63094,32 @@
         <v>747</v>
       </c>
       <c r="H2327" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2328">
+      <c r="A2328" s="1" t="n">
+        <v>46003.6911574074</v>
+      </c>
+      <c r="B2328" t="n">
+        <v>45168</v>
+      </c>
+      <c r="C2328" t="n">
+        <v>9.85999965667725</v>
+      </c>
+      <c r="D2328" t="n">
+        <v>9.68000030517578</v>
+      </c>
+      <c r="E2328" t="n">
+        <v>9.69999980926514</v>
+      </c>
+      <c r="F2328" t="n">
+        <v>9.84000015258789</v>
+      </c>
+      <c r="G2328" t="s">
+        <v>748</v>
+      </c>
+      <c r="H2328" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="749" uniqueCount="749">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="750">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">FF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98565864562988</t>
+    <t xml:space="preserve">8.98565673828125</t>
   </si>
   <si>
     <t xml:space="preserve">9.08549880981445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24887371063232</t>
+    <t xml:space="preserve">9.24887275695801</t>
   </si>
   <si>
     <t xml:space="preserve">9.09457397460938</t>
@@ -59,31 +59,31 @@
     <t xml:space="preserve">9.12180423736572</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03104019165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95389080047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8994312286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8948917388916</t>
+    <t xml:space="preserve">9.03103923797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95388984680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89943218231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89489459991455</t>
   </si>
   <si>
     <t xml:space="preserve">8.84951210021973</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85858821868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87674045562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76782417297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86766529083252</t>
+    <t xml:space="preserve">8.85858917236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87673950195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.767822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8676643371582</t>
   </si>
   <si>
     <t xml:space="preserve">9.04919338226318</t>
@@ -92,10 +92,10 @@
     <t xml:space="preserve">9.23072147369385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11272716522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96750545501709</t>
+    <t xml:space="preserve">9.11272811889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96750450134277</t>
   </si>
   <si>
     <t xml:space="preserve">8.91304588317871</t>
@@ -104,10 +104,10 @@
     <t xml:space="preserve">8.92212295532227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00381088256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15810871124268</t>
+    <t xml:space="preserve">9.00381183624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15811157226562</t>
   </si>
   <si>
     <t xml:space="preserve">9.16718673706055</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">9.58470153808594</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57562446594238</t>
+    <t xml:space="preserve">9.5756254196167</t>
   </si>
   <si>
     <t xml:space="preserve">9.53024291992188</t>
@@ -146,28 +146,28 @@
     <t xml:space="preserve">9.60285472869873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63915920257568</t>
+    <t xml:space="preserve">9.63916015625</t>
   </si>
   <si>
     <t xml:space="preserve">9.79345989227295</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95683479309082</t>
+    <t xml:space="preserve">9.95683574676514</t>
   </si>
   <si>
     <t xml:space="preserve">9.93868255615234</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98406314849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73900032043457</t>
+    <t xml:space="preserve">9.98406410217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73899936676025</t>
   </si>
   <si>
     <t xml:space="preserve">9.76623153686523</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74807643890381</t>
+    <t xml:space="preserve">9.74807834625244</t>
   </si>
   <si>
     <t xml:space="preserve">9.75715351104736</t>
@@ -176,19 +176,19 @@
     <t xml:space="preserve">9.64823722839355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82068824768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7026948928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72084712982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67546463012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66639041900635</t>
+    <t xml:space="preserve">9.82068729400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70269393920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72084808349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67546558380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6663875579834</t>
   </si>
   <si>
     <t xml:space="preserve">9.63008308410645</t>
@@ -197,10 +197,10 @@
     <t xml:space="preserve">9.65731334686279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68454170227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81161212921143</t>
+    <t xml:space="preserve">9.68454360961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81161308288574</t>
   </si>
   <si>
     <t xml:space="preserve">9.82976531982422</t>
@@ -209,7 +209,7 @@
     <t xml:space="preserve">9.84791660308838</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83884143829346</t>
+    <t xml:space="preserve">9.83884239196777</t>
   </si>
   <si>
     <t xml:space="preserve">9.72992420196533</t>
@@ -218,7 +218,7 @@
     <t xml:space="preserve">9.78438186645508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55747318267822</t>
+    <t xml:space="preserve">9.55747127532959</t>
   </si>
   <si>
     <t xml:space="preserve">9.34871482849121</t>
@@ -233,10 +233,10 @@
     <t xml:space="preserve">9.25794982910156</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19441509246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18533992767334</t>
+    <t xml:space="preserve">9.19441604614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18533897399902</t>
   </si>
   <si>
     <t xml:space="preserve">9.4122486114502</t>
@@ -245,16 +245,16 @@
     <t xml:space="preserve">9.22164440155029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31240749359131</t>
+    <t xml:space="preserve">9.31240844726562</t>
   </si>
   <si>
     <t xml:space="preserve">9.26702690124512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29425525665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28518009185791</t>
+    <t xml:space="preserve">9.29425621032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28517723083496</t>
   </si>
   <si>
     <t xml:space="preserve">9.37594318389893</t>
@@ -263,16 +263,16 @@
     <t xml:space="preserve">9.366868019104</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3850212097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45763206481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39409732818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48486042022705</t>
+    <t xml:space="preserve">9.38502025604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45763301849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39409637451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48486137390137</t>
   </si>
   <si>
     <t xml:space="preserve">9.49393749237061</t>
@@ -281,16 +281,16 @@
     <t xml:space="preserve">9.44855499267578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4757833480835</t>
+    <t xml:space="preserve">9.47578430175781</t>
   </si>
   <si>
     <t xml:space="preserve">9.2397985458374</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14903259277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21256637573242</t>
+    <t xml:space="preserve">9.14903354644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21256732940674</t>
   </si>
   <si>
     <t xml:space="preserve">9.20349216461182</t>
@@ -299,19 +299,19 @@
     <t xml:space="preserve">9.13088035583496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13995742797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94027519226074</t>
+    <t xml:space="preserve">9.1399564743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94027614593506</t>
   </si>
   <si>
     <t xml:space="preserve">8.80412864685059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75874614715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66798400878906</t>
+    <t xml:space="preserve">8.75874710083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66798305511475</t>
   </si>
   <si>
     <t xml:space="preserve">8.62260055541992</t>
@@ -320,13 +320,13 @@
     <t xml:space="preserve">8.53183555603027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35030937194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16878032684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9872522354126</t>
+    <t xml:space="preserve">8.35030746459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16877937316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98725128173828</t>
   </si>
   <si>
     <t xml:space="preserve">8.03263473510742</t>
@@ -335,13 +335,13 @@
     <t xml:space="preserve">8.12339782714844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25954341888428</t>
+    <t xml:space="preserve">8.25954437255859</t>
   </si>
   <si>
     <t xml:space="preserve">7.94186925888062</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30492687225342</t>
+    <t xml:space="preserve">8.30492401123047</t>
   </si>
   <si>
     <t xml:space="preserve">8.21416282653809</t>
@@ -350,22 +350,22 @@
     <t xml:space="preserve">8.39568996429443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57721710205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71336460113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53202247619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25706100463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44036960601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16540718078613</t>
+    <t xml:space="preserve">8.5772180557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71336650848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53202342987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25706005096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44036865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16540622711182</t>
   </si>
   <si>
     <t xml:space="preserve">9.07375144958496</t>
@@ -374,13 +374,13 @@
     <t xml:space="preserve">9.11957931518555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98209857940674</t>
+    <t xml:space="preserve">8.98209953308105</t>
   </si>
   <si>
     <t xml:space="preserve">9.02792549133301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62367630004883</t>
+    <t xml:space="preserve">9.62367725372314</t>
   </si>
   <si>
     <t xml:space="preserve">9.80698490142822</t>
@@ -392,7 +392,7 @@
     <t xml:space="preserve">9.99029350280762</t>
   </si>
   <si>
-    <t xml:space="preserve">10.173602104187</t>
+    <t xml:space="preserve">10.1736011505127</t>
   </si>
   <si>
     <t xml:space="preserve">10.2652559280396</t>
@@ -404,7 +404,7 @@
     <t xml:space="preserve">10.5402173995972</t>
   </si>
   <si>
-    <t xml:space="preserve">10.631872177124</t>
+    <t xml:space="preserve">10.6318712234497</t>
   </si>
   <si>
     <t xml:space="preserve">10.8151807785034</t>
@@ -425,34 +425,34 @@
     <t xml:space="preserve">11.1817960739136</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734489440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4567575454712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3651037216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4485626220703</t>
+    <t xml:space="preserve">11.2734508514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4567584991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3651027679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.448561668396</t>
   </si>
   <si>
     <t xml:space="preserve">9.71533107757568</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79878997802734</t>
+    <t xml:space="preserve">8.79879093170166</t>
   </si>
   <si>
     <t xml:space="preserve">8.24886608123779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21123313903809</t>
+    <t xml:space="preserve">9.2112340927124</t>
   </si>
   <si>
     <t xml:space="preserve">9.30288696289062</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03709125518799</t>
+    <t xml:space="preserve">9.03709030151367</t>
   </si>
   <si>
     <t xml:space="preserve">9.39454174041748</t>
@@ -470,13 +470,13 @@
     <t xml:space="preserve">10.0361194610596</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94446754455566</t>
+    <t xml:space="preserve">9.94446659088135</t>
   </si>
   <si>
     <t xml:space="preserve">9.82552433013916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73283100128174</t>
+    <t xml:space="preserve">9.73283004760742</t>
   </si>
   <si>
     <t xml:space="preserve">9.59379005432129</t>
@@ -488,16 +488,16 @@
     <t xml:space="preserve">9.91821765899658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54744243621826</t>
+    <t xml:space="preserve">9.54744338989258</t>
   </si>
   <si>
     <t xml:space="preserve">10.010910987854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1036033630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1499509811401</t>
+    <t xml:space="preserve">10.1036043167114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1499519348145</t>
   </si>
   <si>
     <t xml:space="preserve">10.1962985992432</t>
@@ -506,109 +506,109 @@
     <t xml:space="preserve">9.77917671203613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87187099456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.057258605957</t>
+    <t xml:space="preserve">9.87187004089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0572576522827</t>
   </si>
   <si>
     <t xml:space="preserve">10.2889919281006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4743795394897</t>
+    <t xml:space="preserve">10.4743785858154</t>
   </si>
   <si>
     <t xml:space="preserve">10.2426443099976</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3816862106323</t>
+    <t xml:space="preserve">10.3816871643066</t>
   </si>
   <si>
     <t xml:space="preserve">9.68648338317871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64013576507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50109577178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31570911407471</t>
+    <t xml:space="preserve">9.64013671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50109672546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31571006774902</t>
   </si>
   <si>
     <t xml:space="preserve">9.23228454589844</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19520664215088</t>
+    <t xml:space="preserve">9.1952075958252</t>
   </si>
   <si>
     <t xml:space="preserve">9.25082302093506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26936340332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2137451171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04689693450928</t>
+    <t xml:space="preserve">9.269362449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21374607086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04689788818359</t>
   </si>
   <si>
     <t xml:space="preserve">9.12105369567871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0654354095459</t>
+    <t xml:space="preserve">9.06543636322021</t>
   </si>
   <si>
     <t xml:space="preserve">8.97274303436279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17666721343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02835750579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95420455932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71319961547852</t>
+    <t xml:space="preserve">9.17666625976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02835845947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95420360565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71320056915283</t>
   </si>
   <si>
     <t xml:space="preserve">8.99128150939941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76881694793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89858722686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93566608428955</t>
+    <t xml:space="preserve">8.76881790161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89858818054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93566513061523</t>
   </si>
   <si>
     <t xml:space="preserve">10.3353395462036</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9841947555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0305404663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2159280776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4940099716187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5403566360474</t>
+    <t xml:space="preserve">10.9841957092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0305414199829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2159290313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4940090179443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.540355682373</t>
   </si>
   <si>
     <t xml:space="preserve">11.5867033004761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6330499649048</t>
+    <t xml:space="preserve">11.6330509185791</t>
   </si>
   <si>
     <t xml:space="preserve">11.7257432937622</t>
@@ -629,10 +629,10 @@
     <t xml:space="preserve">12.3745985031128</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5136384963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3282518386841</t>
+    <t xml:space="preserve">12.5136394500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3282527923584</t>
   </si>
   <si>
     <t xml:space="preserve">12.1428651809692</t>
@@ -653,10 +653,10 @@
     <t xml:space="preserve">12.4614267349243</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4145793914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7425127029419</t>
+    <t xml:space="preserve">12.4145803451538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7425117492676</t>
   </si>
   <si>
     <t xml:space="preserve">12.6956644058228</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">12.1803426742554</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3208837509155</t>
+    <t xml:space="preserve">12.3208847045898</t>
   </si>
   <si>
     <t xml:space="preserve">12.274037361145</t>
@@ -680,13 +680,13 @@
     <t xml:space="preserve">12.7893581390381</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6019687652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9299011230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8830537796021</t>
+    <t xml:space="preserve">12.6019697189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9299020767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8830547332764</t>
   </si>
   <si>
     <t xml:space="preserve">13.0704441070557</t>
@@ -695,79 +695,79 @@
     <t xml:space="preserve">13.679461479187</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8668508529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0542411804199</t>
+    <t xml:space="preserve">13.8668518066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0542402267456</t>
   </si>
   <si>
     <t xml:space="preserve">14.3353261947632</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5695629119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2254276275635</t>
+    <t xml:space="preserve">14.5695638656616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2254285812378</t>
   </si>
   <si>
     <t xml:space="preserve">15.1317329406738</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7569532394409</t>
+    <t xml:space="preserve">14.7569522857666</t>
   </si>
   <si>
     <t xml:space="preserve">15.0380382537842</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1785802841187</t>
+    <t xml:space="preserve">15.178581237793</t>
   </si>
   <si>
     <t xml:space="preserve">15.3191232681274</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8974952697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4596652984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4128179550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5533609390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0686836242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8650913238525</t>
+    <t xml:space="preserve">14.8974943161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4596662521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4128189086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5533618927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0686817169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8650894165039</t>
   </si>
   <si>
     <t xml:space="preserve">17.0056324005127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7713928222656</t>
+    <t xml:space="preserve">16.7713947296143</t>
   </si>
   <si>
     <t xml:space="preserve">17.193021774292</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0524806976318</t>
+    <t xml:space="preserve">17.0524787902832</t>
   </si>
   <si>
     <t xml:space="preserve">16.9587841033936</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7245464324951</t>
+    <t xml:space="preserve">16.7245483398438</t>
   </si>
   <si>
     <t xml:space="preserve">16.6308498382568</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5371551513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5840034484863</t>
+    <t xml:space="preserve">16.5371570587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.584005355835</t>
   </si>
   <si>
     <t xml:space="preserve">16.2092247009277</t>
@@ -782,31 +782,31 @@
     <t xml:space="preserve">16.396614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3029193878174</t>
+    <t xml:space="preserve">16.3029174804688</t>
   </si>
   <si>
     <t xml:space="preserve">15.8344430923462</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1155319213867</t>
+    <t xml:space="preserve">16.1155281066895</t>
   </si>
   <si>
     <t xml:space="preserve">16.0218353271484</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1623783111572</t>
+    <t xml:space="preserve">16.1623764038086</t>
   </si>
   <si>
     <t xml:space="preserve">15.974986076355</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7407493591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4434604644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9119358062744</t>
+    <t xml:space="preserve">15.7407484054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4434623718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.911937713623</t>
   </si>
   <si>
     <t xml:space="preserve">17.0993251800537</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">16.6777000427246</t>
   </si>
   <si>
-    <t xml:space="preserve">16.818244934082</t>
+    <t xml:space="preserve">16.8182430267334</t>
   </si>
   <si>
     <t xml:space="preserve">15.272274017334</t>
@@ -833,10 +833,10 @@
     <t xml:space="preserve">14.4758682250977</t>
   </si>
   <si>
-    <t xml:space="preserve">14.382173538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1010875701904</t>
+    <t xml:space="preserve">14.3821744918823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1010885238647</t>
   </si>
   <si>
     <t xml:space="preserve">14.288477897644</t>
@@ -857,7 +857,7 @@
     <t xml:space="preserve">14.0073928833008</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7263078689575</t>
+    <t xml:space="preserve">13.7263088226318</t>
   </si>
   <si>
     <t xml:space="preserve">14.1479358673096</t>
@@ -866,19 +866,19 @@
     <t xml:space="preserve">14.4290199279785</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6164102554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7731552124023</t>
+    <t xml:space="preserve">14.6164112091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7731561660767</t>
   </si>
   <si>
     <t xml:space="preserve">13.3515281677246</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3046817779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3983774185181</t>
+    <t xml:space="preserve">13.3046808242798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3983764648438</t>
   </si>
   <si>
     <t xml:space="preserve">13.0235967636108</t>
@@ -902,13 +902,13 @@
     <t xml:space="preserve">11.8992576599121</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0397996902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1334943771362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4776296615601</t>
+    <t xml:space="preserve">12.0397987365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1334934234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4776306152344</t>
   </si>
   <si>
     <t xml:space="preserve">11.2433938980103</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">11.4307823181152</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9623079299927</t>
+    <t xml:space="preserve">10.9623069763184</t>
   </si>
   <si>
     <t xml:space="preserve">10.7280712127686</t>
@@ -932,25 +932,25 @@
     <t xml:space="preserve">11.1965446472168</t>
   </si>
   <si>
-    <t xml:space="preserve">11.571325302124</t>
+    <t xml:space="preserve">11.5713262557983</t>
   </si>
   <si>
     <t xml:space="preserve">11.3370885848999</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2902402877808</t>
+    <t xml:space="preserve">11.2902393341064</t>
   </si>
   <si>
     <t xml:space="preserve">11.7118673324585</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7587146759033</t>
+    <t xml:space="preserve">11.7587156295776</t>
   </si>
   <si>
     <t xml:space="preserve">11.8055629730225</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0091552734375</t>
+    <t xml:space="preserve">11.0091562271118</t>
   </si>
   <si>
     <t xml:space="preserve">9.46318912506104</t>
@@ -962,13 +962,13 @@
     <t xml:space="preserve">8.57308673858643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31074237823486</t>
+    <t xml:space="preserve">8.31074142456055</t>
   </si>
   <si>
     <t xml:space="preserve">8.45128345489502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61993503570557</t>
+    <t xml:space="preserve">8.61993408203125</t>
   </si>
   <si>
     <t xml:space="preserve">8.44191455841064</t>
@@ -977,16 +977,16 @@
     <t xml:space="preserve">8.32948017120361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25452518463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43254566192627</t>
+    <t xml:space="preserve">8.25452423095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43254470825195</t>
   </si>
   <si>
     <t xml:space="preserve">8.47002220153809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32011032104492</t>
+    <t xml:space="preserve">8.32011127471924</t>
   </si>
   <si>
     <t xml:space="preserve">8.20767688751221</t>
@@ -995,7 +995,7 @@
     <t xml:space="preserve">8.0858736038208</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78605031967163</t>
+    <t xml:space="preserve">7.78604936599731</t>
   </si>
   <si>
     <t xml:space="preserve">7.49559497833252</t>
@@ -1007,37 +1007,37 @@
     <t xml:space="preserve">7.23324871063232</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83289670944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90785264968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50496530532837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37379169464111</t>
+    <t xml:space="preserve">7.8328971862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90785360336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50496482849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37379217147827</t>
   </si>
   <si>
     <t xml:space="preserve">7.12081527709961</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28009653091431</t>
+    <t xml:space="preserve">7.28009700775146</t>
   </si>
   <si>
     <t xml:space="preserve">6.98027324676514</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93342542648315</t>
+    <t xml:space="preserve">6.93342590332031</t>
   </si>
   <si>
     <t xml:space="preserve">7.06459808349609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02712059020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34568309783936</t>
+    <t xml:space="preserve">7.0271201133728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34568357467651</t>
   </si>
   <si>
     <t xml:space="preserve">7.5424427986145</t>
@@ -1049,10 +1049,10 @@
     <t xml:space="preserve">8.2170467376709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65194320678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46116256713867</t>
+    <t xml:space="preserve">8.65194225311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46116161346436</t>
   </si>
   <si>
     <t xml:space="preserve">8.53747367858887</t>
@@ -1070,7 +1070,7 @@
     <t xml:space="preserve">8.72825622558594</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66148281097412</t>
+    <t xml:space="preserve">8.6614818572998</t>
   </si>
   <si>
     <t xml:space="preserve">8.49931812286377</t>
@@ -1091,13 +1091,13 @@
     <t xml:space="preserve">8.29899787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12729454040527</t>
+    <t xml:space="preserve">8.12729358673096</t>
   </si>
   <si>
     <t xml:space="preserve">7.89835643768311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10821723937988</t>
+    <t xml:space="preserve">8.10821628570557</t>
   </si>
   <si>
     <t xml:space="preserve">7.84112215042114</t>
@@ -1112,13 +1112,13 @@
     <t xml:space="preserve">8.06052017211914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07959938049316</t>
+    <t xml:space="preserve">8.07959842681885</t>
   </si>
   <si>
     <t xml:space="preserve">8.07005977630615</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92697429656982</t>
+    <t xml:space="preserve">7.92697334289551</t>
   </si>
   <si>
     <t xml:space="preserve">7.98420810699463</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">8.30853748321533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26084041595459</t>
+    <t xml:space="preserve">8.26084136962891</t>
   </si>
   <si>
     <t xml:space="preserve">8.27038097381592</t>
@@ -1136,13 +1136,13 @@
     <t xml:space="preserve">8.18452930450439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03190422058105</t>
+    <t xml:space="preserve">8.03190326690674</t>
   </si>
   <si>
     <t xml:space="preserve">7.96512985229492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86020040512085</t>
+    <t xml:space="preserve">7.86019992828369</t>
   </si>
   <si>
     <t xml:space="preserve">7.86973905563354</t>
@@ -1166,10 +1166,10 @@
     <t xml:space="preserve">7.63126230239868</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65987920761108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16545009613037</t>
+    <t xml:space="preserve">7.65987873077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16545104980469</t>
   </si>
   <si>
     <t xml:space="preserve">8.32761383056641</t>
@@ -1181,13 +1181,13 @@
     <t xml:space="preserve">7.9365119934082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19406795501709</t>
+    <t xml:space="preserve">8.19406890869141</t>
   </si>
   <si>
     <t xml:space="preserve">8.2322244644165</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31807613372803</t>
+    <t xml:space="preserve">8.31807708740234</t>
   </si>
   <si>
     <t xml:space="preserve">8.15591239929199</t>
@@ -1208,7 +1208,7 @@
     <t xml:space="preserve">8.34669303894043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95559167861938</t>
+    <t xml:space="preserve">7.95559072494507</t>
   </si>
   <si>
     <t xml:space="preserve">7.77434825897217</t>
@@ -1223,13 +1223,13 @@
     <t xml:space="preserve">8.01282501220703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05098152160645</t>
+    <t xml:space="preserve">8.05098056793213</t>
   </si>
   <si>
     <t xml:space="preserve">7.67895746231079</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73619222640991</t>
+    <t xml:space="preserve">7.73619174957275</t>
   </si>
   <si>
     <t xml:space="preserve">7.6980357170105</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">7.62172269821167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52633190155029</t>
+    <t xml:space="preserve">7.52633237838745</t>
   </si>
   <si>
     <t xml:space="preserve">7.34508991241455</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">7.20200395584106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18292617797852</t>
+    <t xml:space="preserve">7.18292570114136</t>
   </si>
   <si>
     <t xml:space="preserve">7.14476919174194</t>
@@ -1274,13 +1274,13 @@
     <t xml:space="preserve">7.1543083190918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24969863891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24015998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46909809112549</t>
+    <t xml:space="preserve">7.24969911575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24016046524048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46909761428833</t>
   </si>
   <si>
     <t xml:space="preserve">7.41186332702637</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">7.45001983642578</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28785514831543</t>
+    <t xml:space="preserve">7.28785562515259</t>
   </si>
   <si>
     <t xml:space="preserve">7.39278507232666</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">7.3355507850647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61218452453613</t>
+    <t xml:space="preserve">7.61218404769897</t>
   </si>
   <si>
     <t xml:space="preserve">7.90789556503296</t>
@@ -1307,28 +1307,28 @@
     <t xml:space="preserve">7.94605112075806</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45955896377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70757484436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8792781829834</t>
+    <t xml:space="preserve">7.45955848693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70757436752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87927865982056</t>
   </si>
   <si>
     <t xml:space="preserve">7.99374723434448</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75527000427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81250429153442</t>
+    <t xml:space="preserve">7.75527048110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81250476837158</t>
   </si>
   <si>
     <t xml:space="preserve">7.79342699050903</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80296564102173</t>
+    <t xml:space="preserve">7.80296611785889</t>
   </si>
   <si>
     <t xml:space="preserve">7.85066032409668</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">7.74573087692261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83158302307129</t>
+    <t xml:space="preserve">7.83158254623413</t>
   </si>
   <si>
     <t xml:space="preserve">7.66941833496094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60264444351196</t>
+    <t xml:space="preserve">7.60264492034912</t>
   </si>
   <si>
     <t xml:space="preserve">7.58356666564941</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">8.00328636169434</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78388690948486</t>
+    <t xml:space="preserve">7.78388738632202</t>
   </si>
   <si>
     <t xml:space="preserve">7.3641676902771</t>
@@ -2259,6 +2259,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.84000015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76000022888184</t>
   </si>
 </sst>
 </file>
@@ -63099,7 +63102,7 @@
     </row>
     <row r="2328">
       <c r="A2328" s="1" t="n">
-        <v>46003.6911574074</v>
+        <v>46003.3333333333</v>
       </c>
       <c r="B2328" t="n">
         <v>45168</v>
@@ -63120,6 +63123,32 @@
         <v>748</v>
       </c>
       <c r="H2328" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2329">
+      <c r="A2329" s="1" t="n">
+        <v>46006.6911111111</v>
+      </c>
+      <c r="B2329" t="n">
+        <v>52344</v>
+      </c>
+      <c r="C2329" t="n">
+        <v>10.0500001907349</v>
+      </c>
+      <c r="D2329" t="n">
+        <v>9.69999980926514</v>
+      </c>
+      <c r="E2329" t="n">
+        <v>9.89999961853027</v>
+      </c>
+      <c r="F2329" t="n">
+        <v>9.76000022888184</v>
+      </c>
+      <c r="G2329" t="s">
+        <v>749</v>
+      </c>
+      <c r="H2329" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="750">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="751">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0764217376709</t>
+    <t xml:space="preserve">9.07642078399658</t>
   </si>
   <si>
     <t xml:space="preserve">FF.MI</t>
@@ -50,40 +50,40 @@
     <t xml:space="preserve">9.08549880981445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24887275695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09457397460938</t>
+    <t xml:space="preserve">9.24887371063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09457588195801</t>
   </si>
   <si>
     <t xml:space="preserve">9.12180423736572</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03103923797607</t>
+    <t xml:space="preserve">9.03104019165039</t>
   </si>
   <si>
     <t xml:space="preserve">8.95388984680176</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89943218231201</t>
+    <t xml:space="preserve">8.8994312286377</t>
   </si>
   <si>
     <t xml:space="preserve">8.89489459991455</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84951210021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85858917236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87673950195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.767822265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8676643371582</t>
+    <t xml:space="preserve">8.84951114654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85858726501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87674045562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76782321929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86766338348389</t>
   </si>
   <si>
     <t xml:space="preserve">9.04919338226318</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">9.23072147369385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11272811889648</t>
+    <t xml:space="preserve">9.11272716522217</t>
   </si>
   <si>
     <t xml:space="preserve">8.96750450134277</t>
@@ -101,16 +101,16 @@
     <t xml:space="preserve">8.91304588317871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92212295532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00381183624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15811157226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16718673706055</t>
+    <t xml:space="preserve">8.92212200164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00380992889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15810871124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16718578338623</t>
   </si>
   <si>
     <t xml:space="preserve">9.43947792053223</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">9.62100791931152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8025369644165</t>
+    <t xml:space="preserve">9.80253601074219</t>
   </si>
   <si>
     <t xml:space="preserve">9.71177101135254</t>
@@ -131,16 +131,16 @@
     <t xml:space="preserve">9.56654834747314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58470153808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5756254196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53024291992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50301361083984</t>
+    <t xml:space="preserve">9.58470344543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57562446594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53024196624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50301456451416</t>
   </si>
   <si>
     <t xml:space="preserve">9.60285472869873</t>
@@ -152,28 +152,28 @@
     <t xml:space="preserve">9.79345989227295</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95683574676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93868255615234</t>
+    <t xml:space="preserve">9.95683479309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93868160247803</t>
   </si>
   <si>
     <t xml:space="preserve">9.98406410217285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73899936676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76623153686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74807834625244</t>
+    <t xml:space="preserve">9.73900032043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76623058319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74807548522949</t>
   </si>
   <si>
     <t xml:space="preserve">9.75715351104736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64823722839355</t>
+    <t xml:space="preserve">9.64823532104492</t>
   </si>
   <si>
     <t xml:space="preserve">9.82068729400635</t>
@@ -182,37 +182,37 @@
     <t xml:space="preserve">9.70269393920898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72084808349609</t>
+    <t xml:space="preserve">9.72084712982178</t>
   </si>
   <si>
     <t xml:space="preserve">9.67546558380127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6663875579834</t>
+    <t xml:space="preserve">9.66638851165771</t>
   </si>
   <si>
     <t xml:space="preserve">9.63008308410645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65731334686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68454360961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81161308288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82976531982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84791660308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83884239196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72992420196533</t>
+    <t xml:space="preserve">9.65731239318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68454265594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81161403656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8297643661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84791851043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83884143829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72992324829102</t>
   </si>
   <si>
     <t xml:space="preserve">9.78438186645508</t>
@@ -221,10 +221,10 @@
     <t xml:space="preserve">9.55747127532959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34871482849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33963775634766</t>
+    <t xml:space="preserve">9.34871387481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33963871002197</t>
   </si>
   <si>
     <t xml:space="preserve">9.27610301971436</t>
@@ -239,49 +239,49 @@
     <t xml:space="preserve">9.18533897399902</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4122486114502</t>
+    <t xml:space="preserve">9.41224956512451</t>
   </si>
   <si>
     <t xml:space="preserve">9.22164440155029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31240844726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26702690124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29425621032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28517723083496</t>
+    <t xml:space="preserve">9.31240940093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2670259475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29425716400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28518009185791</t>
   </si>
   <si>
     <t xml:space="preserve">9.37594318389893</t>
   </si>
   <si>
-    <t xml:space="preserve">9.366868019104</t>
+    <t xml:space="preserve">9.36686706542969</t>
   </si>
   <si>
     <t xml:space="preserve">9.38502025604248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45763301849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39409637451172</t>
+    <t xml:space="preserve">9.45763111114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39409732818604</t>
   </si>
   <si>
     <t xml:space="preserve">9.48486137390137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49393749237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44855499267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47578430175781</t>
+    <t xml:space="preserve">9.49393844604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44855403900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4757833480835</t>
   </si>
   <si>
     <t xml:space="preserve">9.2397985458374</t>
@@ -302,22 +302,22 @@
     <t xml:space="preserve">9.1399564743042</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94027614593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80412864685059</t>
+    <t xml:space="preserve">8.94027519226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8041296005249</t>
   </si>
   <si>
     <t xml:space="preserve">8.75874710083008</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66798305511475</t>
+    <t xml:space="preserve">8.66798210144043</t>
   </si>
   <si>
     <t xml:space="preserve">8.62260055541992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53183555603027</t>
+    <t xml:space="preserve">8.53183650970459</t>
   </si>
   <si>
     <t xml:space="preserve">8.35030746459961</t>
@@ -329,61 +329,61 @@
     <t xml:space="preserve">7.98725128173828</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03263473510742</t>
+    <t xml:space="preserve">8.03263568878174</t>
   </si>
   <si>
     <t xml:space="preserve">8.12339782714844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25954437255859</t>
+    <t xml:space="preserve">8.25954246520996</t>
   </si>
   <si>
     <t xml:space="preserve">7.94186925888062</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30492401123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21416282653809</t>
+    <t xml:space="preserve">8.3049259185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21416091918945</t>
   </si>
   <si>
     <t xml:space="preserve">8.39568996429443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5772180557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71336650848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53202342987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25706005096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44036865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16540622711182</t>
+    <t xml:space="preserve">8.57721900939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71336555480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53202247619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25705909729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44036960601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16540813446045</t>
   </si>
   <si>
     <t xml:space="preserve">9.07375144958496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11957931518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98209953308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02792549133301</t>
+    <t xml:space="preserve">9.11957836151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98209762573242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02792644500732</t>
   </si>
   <si>
     <t xml:space="preserve">9.62367725372314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80698490142822</t>
+    <t xml:space="preserve">9.80698394775391</t>
   </si>
   <si>
     <t xml:space="preserve">9.89863967895508</t>
@@ -392,7 +392,7 @@
     <t xml:space="preserve">9.99029350280762</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1736011505127</t>
+    <t xml:space="preserve">10.1736030578613</t>
   </si>
   <si>
     <t xml:space="preserve">10.2652559280396</t>
@@ -404,10 +404,10 @@
     <t xml:space="preserve">10.5402173995972</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6318712234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8151807785034</t>
+    <t xml:space="preserve">10.631872177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8151798248291</t>
   </si>
   <si>
     <t xml:space="preserve">10.7235260009766</t>
@@ -416,49 +416,49 @@
     <t xml:space="preserve">10.9068336486816</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9984884262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0901432037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1817960739136</t>
+    <t xml:space="preserve">10.9984874725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.090142250061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1817951202393</t>
   </si>
   <si>
     <t xml:space="preserve">11.2734508514404</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4567584991455</t>
+    <t xml:space="preserve">11.4567575454712</t>
   </si>
   <si>
     <t xml:space="preserve">11.3651027679443</t>
   </si>
   <si>
-    <t xml:space="preserve">10.448561668396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71533107757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79879093170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24886608123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2112340927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30288696289062</t>
+    <t xml:space="preserve">10.4485626220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79878997802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24886512756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21123313903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30288791656494</t>
   </si>
   <si>
     <t xml:space="preserve">9.03709030151367</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39454174041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76115703582764</t>
+    <t xml:space="preserve">9.3945426940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76115798950195</t>
   </si>
   <si>
     <t xml:space="preserve">9.66950416564941</t>
@@ -470,79 +470,79 @@
     <t xml:space="preserve">10.0361194610596</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94446659088135</t>
+    <t xml:space="preserve">9.94446754455566</t>
   </si>
   <si>
     <t xml:space="preserve">9.82552433013916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73283004760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59379005432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96456432342529</t>
+    <t xml:space="preserve">9.73283100128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59379100799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96456527709961</t>
   </si>
   <si>
     <t xml:space="preserve">9.91821765899658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54744338989258</t>
+    <t xml:space="preserve">9.54744434356689</t>
   </si>
   <si>
     <t xml:space="preserve">10.010910987854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1036043167114</t>
+    <t xml:space="preserve">10.1036052703857</t>
   </si>
   <si>
     <t xml:space="preserve">10.1499519348145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1962985992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77917671203613</t>
+    <t xml:space="preserve">10.1962976455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77917861938477</t>
   </si>
   <si>
     <t xml:space="preserve">9.87187004089355</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0572576522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2889919281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4743785858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2426443099976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3816871643066</t>
+    <t xml:space="preserve">10.057258605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2889928817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4743795394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2426452636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.381685256958</t>
   </si>
   <si>
     <t xml:space="preserve">9.68648338317871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64013671875</t>
+    <t xml:space="preserve">9.64013576507568</t>
   </si>
   <si>
     <t xml:space="preserve">9.50109672546387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31571006774902</t>
+    <t xml:space="preserve">9.31570911407471</t>
   </si>
   <si>
     <t xml:space="preserve">9.23228454589844</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1952075958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25082302093506</t>
+    <t xml:space="preserve">9.19520854949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25082206726074</t>
   </si>
   <si>
     <t xml:space="preserve">9.269362449646</t>
@@ -551,37 +551,37 @@
     <t xml:space="preserve">9.21374607086182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04689788818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12105369567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06543636322021</t>
+    <t xml:space="preserve">9.04689693450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12105178833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06543445587158</t>
   </si>
   <si>
     <t xml:space="preserve">8.97274303436279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17666625976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02835845947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95420360565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71320056915283</t>
+    <t xml:space="preserve">9.17666912078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02835941314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95420455932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71319961547852</t>
   </si>
   <si>
     <t xml:space="preserve">8.99128150939941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76881790161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89858818054199</t>
+    <t xml:space="preserve">8.76881694793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89858722686768</t>
   </si>
   <si>
     <t xml:space="preserve">8.93566513061523</t>
@@ -590,28 +590,28 @@
     <t xml:space="preserve">10.3353395462036</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9841957092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0305414199829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2159290313721</t>
+    <t xml:space="preserve">10.9841938018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0305404663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2159280776978</t>
   </si>
   <si>
     <t xml:space="preserve">11.4940090179443</t>
   </si>
   <si>
-    <t xml:space="preserve">11.540355682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5867033004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6330509185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7257432937622</t>
+    <t xml:space="preserve">11.5403547286987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5867023468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6330499649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7257423400879</t>
   </si>
   <si>
     <t xml:space="preserve">11.9111299514771</t>
@@ -623,25 +623,25 @@
     <t xml:space="preserve">12.1892108917236</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2819051742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3745985031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5136394500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3282527923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1428651809692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0965185165405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5551223754883</t>
+    <t xml:space="preserve">12.2819042205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3745994567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5136384963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3282508850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1428642272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0965166091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.555121421814</t>
   </si>
   <si>
     <t xml:space="preserve">12.5082750320435</t>
@@ -653,7 +653,7 @@
     <t xml:space="preserve">12.4614267349243</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4145803451538</t>
+    <t xml:space="preserve">12.4145793914795</t>
   </si>
   <si>
     <t xml:space="preserve">12.7425117492676</t>
@@ -662,13 +662,13 @@
     <t xml:space="preserve">12.6956644058228</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2271900177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1803426742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3208847045898</t>
+    <t xml:space="preserve">12.2271890640259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1803417205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3208837509155</t>
   </si>
   <si>
     <t xml:space="preserve">12.274037361145</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">12.8362064361572</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7893581390381</t>
+    <t xml:space="preserve">12.7893590927124</t>
   </si>
   <si>
     <t xml:space="preserve">12.6019697189331</t>
@@ -695,31 +695,31 @@
     <t xml:space="preserve">13.679461479187</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8668518066406</t>
+    <t xml:space="preserve">13.8668508529663</t>
   </si>
   <si>
     <t xml:space="preserve">14.0542402267456</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3353261947632</t>
+    <t xml:space="preserve">14.3353252410889</t>
   </si>
   <si>
     <t xml:space="preserve">14.5695638656616</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2254285812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1317329406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7569522857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0380382537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.178581237793</t>
+    <t xml:space="preserve">15.2254276275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1317319869995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7569532394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0380373001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1785802841187</t>
   </si>
   <si>
     <t xml:space="preserve">15.3191232681274</t>
@@ -728,25 +728,25 @@
     <t xml:space="preserve">14.8974943161011</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4596662521362</t>
+    <t xml:space="preserve">15.4596652984619</t>
   </si>
   <si>
     <t xml:space="preserve">15.4128189086914</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5533618927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0686817169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8650894165039</t>
+    <t xml:space="preserve">15.5533599853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0686836242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8650875091553</t>
   </si>
   <si>
     <t xml:space="preserve">17.0056324005127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7713947296143</t>
+    <t xml:space="preserve">16.7713928222656</t>
   </si>
   <si>
     <t xml:space="preserve">17.193021774292</t>
@@ -758,10 +758,10 @@
     <t xml:space="preserve">16.9587841033936</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7245483398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6308498382568</t>
+    <t xml:space="preserve">16.7245464324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6308517456055</t>
   </si>
   <si>
     <t xml:space="preserve">16.5371570587158</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">16.584005355835</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2092247009277</t>
+    <t xml:space="preserve">16.2092227935791</t>
   </si>
   <si>
     <t xml:space="preserve">16.2560729980469</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">16.3029174804688</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8344430923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1155281066895</t>
+    <t xml:space="preserve">15.8344440460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1155300140381</t>
   </si>
   <si>
     <t xml:space="preserve">16.0218353271484</t>
@@ -797,7 +797,7 @@
     <t xml:space="preserve">16.1623764038086</t>
   </si>
   <si>
-    <t xml:space="preserve">15.974986076355</t>
+    <t xml:space="preserve">15.9749879837036</t>
   </si>
   <si>
     <t xml:space="preserve">15.7407484054565</t>
@@ -806,13 +806,13 @@
     <t xml:space="preserve">16.4434623718262</t>
   </si>
   <si>
-    <t xml:space="preserve">16.911937713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0993251800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6777000427246</t>
+    <t xml:space="preserve">16.9119358062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0993270874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6776962280273</t>
   </si>
   <si>
     <t xml:space="preserve">16.8182430267334</t>
@@ -827,34 +827,34 @@
     <t xml:space="preserve">14.991189956665</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8038015365601</t>
+    <t xml:space="preserve">14.8038005828857</t>
   </si>
   <si>
     <t xml:space="preserve">14.4758682250977</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3821744918823</t>
+    <t xml:space="preserve">14.382173538208</t>
   </si>
   <si>
     <t xml:space="preserve">14.1010885238647</t>
   </si>
   <si>
-    <t xml:space="preserve">14.288477897644</t>
+    <t xml:space="preserve">14.2884788513184</t>
   </si>
   <si>
     <t xml:space="preserve">14.5227155685425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9605464935303</t>
+    <t xml:space="preserve">13.960545539856</t>
   </si>
   <si>
     <t xml:space="preserve">14.2416305541992</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1947822570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0073928833008</t>
+    <t xml:space="preserve">14.1947832107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0073938369751</t>
   </si>
   <si>
     <t xml:space="preserve">13.7263088226318</t>
@@ -866,16 +866,16 @@
     <t xml:space="preserve">14.4290199279785</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6164112091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7731561660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3515281677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3046808242798</t>
+    <t xml:space="preserve">14.6164102554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7731552124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3515291213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3046817779541</t>
   </si>
   <si>
     <t xml:space="preserve">13.3983764648438</t>
@@ -884,13 +884,13 @@
     <t xml:space="preserve">13.0235967636108</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1172914505005</t>
+    <t xml:space="preserve">13.1172924041748</t>
   </si>
   <si>
     <t xml:space="preserve">12.976749420166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3677310943604</t>
+    <t xml:space="preserve">12.3677320480347</t>
   </si>
   <si>
     <t xml:space="preserve">12.0866470336914</t>
@@ -899,31 +899,31 @@
     <t xml:space="preserve">11.9929523468018</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8992576599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0397987365723</t>
+    <t xml:space="preserve">11.8992567062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0397996902466</t>
   </si>
   <si>
     <t xml:space="preserve">12.1334934234619</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4776306152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2433938980103</t>
+    <t xml:space="preserve">11.4776296615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2433929443359</t>
   </si>
   <si>
     <t xml:space="preserve">11.3839340209961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6650199890137</t>
+    <t xml:space="preserve">11.6650190353394</t>
   </si>
   <si>
     <t xml:space="preserve">11.4307823181152</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9623069763184</t>
+    <t xml:space="preserve">10.9623079299927</t>
   </si>
   <si>
     <t xml:space="preserve">10.7280712127686</t>
@@ -932,31 +932,31 @@
     <t xml:space="preserve">11.1965446472168</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5713262557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3370885848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2902393341064</t>
+    <t xml:space="preserve">11.571325302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3370876312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2902402877808</t>
   </si>
   <si>
     <t xml:space="preserve">11.7118673324585</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7587156295776</t>
+    <t xml:space="preserve">11.7587146759033</t>
   </si>
   <si>
     <t xml:space="preserve">11.8055629730225</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0091562271118</t>
+    <t xml:space="preserve">11.0091552734375</t>
   </si>
   <si>
     <t xml:space="preserve">9.46318912506104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3388500213623</t>
+    <t xml:space="preserve">8.33884811401367</t>
   </si>
   <si>
     <t xml:space="preserve">8.57308673858643</t>
@@ -965,34 +965,34 @@
     <t xml:space="preserve">8.31074142456055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45128345489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61993408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44191455841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32948017120361</t>
+    <t xml:space="preserve">8.45128440856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61993312835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44191360473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32948112487793</t>
   </si>
   <si>
     <t xml:space="preserve">8.25452423095703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43254470825195</t>
+    <t xml:space="preserve">8.43254375457764</t>
   </si>
   <si>
     <t xml:space="preserve">8.47002220153809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32011127471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20767688751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0858736038208</t>
+    <t xml:space="preserve">8.32011032104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20767784118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08587265014648</t>
   </si>
   <si>
     <t xml:space="preserve">7.78604936599731</t>
@@ -1001,22 +1001,22 @@
     <t xml:space="preserve">7.49559497833252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33631372451782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23324871063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8328971862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90785360336304</t>
+    <t xml:space="preserve">7.33631420135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23324918746948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83289670944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90785217285156</t>
   </si>
   <si>
     <t xml:space="preserve">7.50496482849121</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37379217147827</t>
+    <t xml:space="preserve">7.37379169464111</t>
   </si>
   <si>
     <t xml:space="preserve">7.12081527709961</t>
@@ -1025,19 +1025,19 @@
     <t xml:space="preserve">7.28009700775146</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98027324676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93342590332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06459808349609</t>
+    <t xml:space="preserve">6.98027276992798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93342542648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06459856033325</t>
   </si>
   <si>
     <t xml:space="preserve">7.0271201133728</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34568357467651</t>
+    <t xml:space="preserve">7.34568309783936</t>
   </si>
   <si>
     <t xml:space="preserve">7.5424427986145</t>
@@ -1049,16 +1049,16 @@
     <t xml:space="preserve">8.2170467376709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65194225311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46116161346436</t>
+    <t xml:space="preserve">8.65194320678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46116256713867</t>
   </si>
   <si>
     <t xml:space="preserve">8.53747367858887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68056201934814</t>
+    <t xml:space="preserve">8.68056106567383</t>
   </si>
   <si>
     <t xml:space="preserve">8.77595138549805</t>
@@ -1067,16 +1067,16 @@
     <t xml:space="preserve">8.84272575378418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72825622558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6614818572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49931812286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42300510406494</t>
+    <t xml:space="preserve">8.72825527191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66148281097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49931716918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42300605773926</t>
   </si>
   <si>
     <t xml:space="preserve">8.39438915252686</t>
@@ -1091,7 +1091,7 @@
     <t xml:space="preserve">8.29899787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12729358673096</t>
+    <t xml:space="preserve">8.12729549407959</t>
   </si>
   <si>
     <t xml:space="preserve">7.89835643768311</t>
@@ -1100,19 +1100,19 @@
     <t xml:space="preserve">8.10821628570557</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84112215042114</t>
+    <t xml:space="preserve">7.8411226272583</t>
   </si>
   <si>
     <t xml:space="preserve">8.33715343475342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2036075592041</t>
+    <t xml:space="preserve">8.20360660552979</t>
   </si>
   <si>
     <t xml:space="preserve">8.06052017211914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07959842681885</t>
+    <t xml:space="preserve">8.07959938049316</t>
   </si>
   <si>
     <t xml:space="preserve">8.07005977630615</t>
@@ -1121,22 +1121,22 @@
     <t xml:space="preserve">7.92697334289551</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98420810699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30853748321533</t>
+    <t xml:space="preserve">7.98420763015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30853652954102</t>
   </si>
   <si>
     <t xml:space="preserve">8.26084136962891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27038097381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18452930450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03190326690674</t>
+    <t xml:space="preserve">8.2703800201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18452835083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03190422058105</t>
   </si>
   <si>
     <t xml:space="preserve">7.96512985229492</t>
@@ -1151,7 +1151,7 @@
     <t xml:space="preserve">7.71711397171021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91743516921997</t>
+    <t xml:space="preserve">7.91743421554565</t>
   </si>
   <si>
     <t xml:space="preserve">7.76480960845947</t>
@@ -1166,37 +1166,37 @@
     <t xml:space="preserve">7.63126230239868</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65987873077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16545104980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32761383056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11775493621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9365119934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19406890869141</t>
+    <t xml:space="preserve">7.65987968444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.165452003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32761478424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11775588989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93651247024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19406795501709</t>
   </si>
   <si>
     <t xml:space="preserve">8.2322244644165</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31807708740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15591239929199</t>
+    <t xml:space="preserve">8.31807613372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15591144561768</t>
   </si>
   <si>
     <t xml:space="preserve">8.22268486022949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25130176544189</t>
+    <t xml:space="preserve">8.25130081176758</t>
   </si>
   <si>
     <t xml:space="preserve">8.35623264312744</t>
@@ -1223,28 +1223,28 @@
     <t xml:space="preserve">8.01282501220703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05098056793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67895746231079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73619174957275</t>
+    <t xml:space="preserve">8.05098152160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67895793914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7361912727356</t>
   </si>
   <si>
     <t xml:space="preserve">7.6980357170105</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5167932510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59310626983643</t>
+    <t xml:space="preserve">7.51679372787476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59310579299927</t>
   </si>
   <si>
     <t xml:space="preserve">7.44048070907593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5358715057373</t>
+    <t xml:space="preserve">7.53587198257446</t>
   </si>
   <si>
     <t xml:space="preserve">7.62172269821167</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">7.20200395584106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18292570114136</t>
+    <t xml:space="preserve">7.1829252243042</t>
   </si>
   <si>
     <t xml:space="preserve">7.14476919174194</t>
@@ -1280,19 +1280,19 @@
     <t xml:space="preserve">7.24016046524048</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46909761428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41186332702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45001983642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28785562515259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39278507232666</t>
+    <t xml:space="preserve">7.46909809112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41186380386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45001935958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28785514831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39278554916382</t>
   </si>
   <si>
     <t xml:space="preserve">7.3355507850647</t>
@@ -1301,43 +1301,43 @@
     <t xml:space="preserve">7.61218404769897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90789556503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94605112075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45955848693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70757436752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87927865982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99374723434448</t>
+    <t xml:space="preserve">7.90789604187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94605159759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45955896377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70757484436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87927913665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99374675750732</t>
   </si>
   <si>
     <t xml:space="preserve">7.75527048110962</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81250476837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79342699050903</t>
+    <t xml:space="preserve">7.81250429153442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79342651367188</t>
   </si>
   <si>
     <t xml:space="preserve">7.80296611785889</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85066032409668</t>
+    <t xml:space="preserve">7.85066080093384</t>
   </si>
   <si>
     <t xml:space="preserve">7.74573087692261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83158254623413</t>
+    <t xml:space="preserve">7.83158302307129</t>
   </si>
   <si>
     <t xml:space="preserve">7.66941833496094</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">7.58356666564941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88881778717041</t>
+    <t xml:space="preserve">7.88881826400757</t>
   </si>
   <si>
     <t xml:space="preserve">8.00328636169434</t>
@@ -1361,7 +1361,7 @@
     <t xml:space="preserve">7.3641676902771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10661268234253</t>
+    <t xml:space="preserve">7.10661315917969</t>
   </si>
   <si>
     <t xml:space="preserve">7.27831649780273</t>
@@ -1376,10 +1376,10 @@
     <t xml:space="preserve">7.50372648239136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98721361160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02589321136475</t>
+    <t xml:space="preserve">7.98721408843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02589225769043</t>
   </si>
   <si>
     <t xml:space="preserve">8.04523086547852</t>
@@ -1391,25 +1391,25 @@
     <t xml:space="preserve">8.07424163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12259006500244</t>
+    <t xml:space="preserve">8.12258911132812</t>
   </si>
   <si>
     <t xml:space="preserve">8.05490112304688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94853448867798</t>
+    <t xml:space="preserve">7.94853496551514</t>
   </si>
   <si>
     <t xml:space="preserve">8.06457138061523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08391094207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97754383087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93886423110962</t>
+    <t xml:space="preserve">8.08390998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97754430770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93886518478394</t>
   </si>
   <si>
     <t xml:space="preserve">7.79381895065308</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">7.68745088577271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63910245895386</t>
+    <t xml:space="preserve">7.63910293579102</t>
   </si>
   <si>
     <t xml:space="preserve">7.73579978942871</t>
@@ -1436,10 +1436,10 @@
     <t xml:space="preserve">7.90985584259033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85183715820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83249807357788</t>
+    <t xml:space="preserve">7.85183668136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83249759674072</t>
   </si>
   <si>
     <t xml:space="preserve">7.81315755844116</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">7.80348825454712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78414869308472</t>
+    <t xml:space="preserve">7.78414916992188</t>
   </si>
   <si>
     <t xml:space="preserve">7.6681113243103</t>
@@ -1460,13 +1460,13 @@
     <t xml:space="preserve">7.71646022796631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75514030456543</t>
+    <t xml:space="preserve">7.75513982772827</t>
   </si>
   <si>
     <t xml:space="preserve">7.74547004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86150646209717</t>
+    <t xml:space="preserve">7.86150693893433</t>
   </si>
   <si>
     <t xml:space="preserve">7.89051580429077</t>
@@ -1484,10 +1484,10 @@
     <t xml:space="preserve">8.09358024597168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1322603225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15159893035889</t>
+    <t xml:space="preserve">8.13225936889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1515998840332</t>
   </si>
   <si>
     <t xml:space="preserve">8.1129207611084</t>
@@ -1496,10 +1496,10 @@
     <t xml:space="preserve">8.03556251525879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92919540405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69712114334106</t>
+    <t xml:space="preserve">7.92919492721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69712066650391</t>
   </si>
   <si>
     <t xml:space="preserve">7.60042381286621</t>
@@ -1508,10 +1508,10 @@
     <t xml:space="preserve">7.88084602355957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55207490921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40702867507935</t>
+    <t xml:space="preserve">7.55207443237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40702819824219</t>
   </si>
   <si>
     <t xml:space="preserve">7.34900999069214</t>
@@ -1520,16 +1520,16 @@
     <t xml:space="preserve">7.37801933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43603801727295</t>
+    <t xml:space="preserve">7.43603754043579</t>
   </si>
   <si>
     <t xml:space="preserve">7.41669797897339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5230655670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36834907531738</t>
+    <t xml:space="preserve">7.52306604385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36834955215454</t>
   </si>
   <si>
     <t xml:space="preserve">7.542405128479</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">7.4843864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70679092407227</t>
+    <t xml:space="preserve">7.70679044723511</t>
   </si>
   <si>
     <t xml:space="preserve">7.64877223968506</t>
@@ -1556,10 +1556,10 @@
     <t xml:space="preserve">7.59075355529785</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95820331573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96787357330322</t>
+    <t xml:space="preserve">7.95820426940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96787405014038</t>
   </si>
   <si>
     <t xml:space="preserve">7.90018606185913</t>
@@ -1577,10 +1577,10 @@
     <t xml:space="preserve">8.19027900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29664516448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45136070251465</t>
+    <t xml:space="preserve">8.29664611816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45136165618896</t>
   </si>
   <si>
     <t xml:space="preserve">8.48037147521973</t>
@@ -1607,19 +1607,19 @@
     <t xml:space="preserve">8.50938034057617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42235279083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54805850982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55772876739502</t>
+    <t xml:space="preserve">8.4223518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54805946350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55772972106934</t>
   </si>
   <si>
     <t xml:space="preserve">8.52871990203857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68343544006348</t>
+    <t xml:space="preserve">8.68343448638916</t>
   </si>
   <si>
     <t xml:space="preserve">8.76079368591309</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">8.65442562103271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75112342834473</t>
+    <t xml:space="preserve">8.75112438201904</t>
   </si>
   <si>
     <t xml:space="preserve">8.70277500152588</t>
@@ -1652,10 +1652,10 @@
     <t xml:space="preserve">8.63508701324463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32565498352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31598567962646</t>
+    <t xml:space="preserve">8.32565402984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31598472595215</t>
   </si>
   <si>
     <t xml:space="preserve">8.30631542205811</t>
@@ -2262,6 +2262,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.76000022888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80000019073486</t>
   </si>
 </sst>
 </file>
@@ -63128,7 +63131,7 @@
     </row>
     <row r="2329">
       <c r="A2329" s="1" t="n">
-        <v>46006.6911111111</v>
+        <v>46006.3333333333</v>
       </c>
       <c r="B2329" t="n">
         <v>52344</v>
@@ -63149,6 +63152,32 @@
         <v>749</v>
       </c>
       <c r="H2329" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2330">
+      <c r="A2330" s="1" t="n">
+        <v>46007.6910300926</v>
+      </c>
+      <c r="B2330" t="n">
+        <v>46835</v>
+      </c>
+      <c r="C2330" t="n">
+        <v>9.97999954223633</v>
+      </c>
+      <c r="D2330" t="n">
+        <v>9.69999980926514</v>
+      </c>
+      <c r="E2330" t="n">
+        <v>9.88000011444092</v>
+      </c>
+      <c r="F2330" t="n">
+        <v>9.80000019073486</v>
+      </c>
+      <c r="G2330" t="s">
+        <v>750</v>
+      </c>
+      <c r="H2330" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07642078399658</t>
+    <t xml:space="preserve">9.0764217376709</t>
   </si>
   <si>
     <t xml:space="preserve">FF.MI</t>
@@ -50,46 +50,46 @@
     <t xml:space="preserve">9.08549880981445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24887371063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09457588195801</t>
+    <t xml:space="preserve">9.24887466430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09457397460938</t>
   </si>
   <si>
     <t xml:space="preserve">9.12180423736572</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03104019165039</t>
+    <t xml:space="preserve">9.03103923797607</t>
   </si>
   <si>
     <t xml:space="preserve">8.95388984680176</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8994312286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89489459991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84951114654541</t>
+    <t xml:space="preserve">8.89943313598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89489364624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84951210021973</t>
   </si>
   <si>
     <t xml:space="preserve">8.85858726501465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87674045562744</t>
+    <t xml:space="preserve">8.87673950195312</t>
   </si>
   <si>
     <t xml:space="preserve">8.76782321929932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86766338348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04919338226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23072147369385</t>
+    <t xml:space="preserve">8.86766529083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04919242858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23072052001953</t>
   </si>
   <si>
     <t xml:space="preserve">9.11272716522217</t>
@@ -101,16 +101,16 @@
     <t xml:space="preserve">8.91304588317871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92212200164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00380992889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15810871124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16718578338623</t>
+    <t xml:space="preserve">8.92212295532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00381088256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15810966491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16718673706055</t>
   </si>
   <si>
     <t xml:space="preserve">9.43947792053223</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">9.54839611053467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62100791931152</t>
+    <t xml:space="preserve">9.62100696563721</t>
   </si>
   <si>
     <t xml:space="preserve">9.80253601074219</t>
@@ -128,31 +128,31 @@
     <t xml:space="preserve">9.71177101135254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56654834747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58470344543457</t>
+    <t xml:space="preserve">9.56655025482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58470249176025</t>
   </si>
   <si>
     <t xml:space="preserve">9.57562446594238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53024196624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50301456451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60285472869873</t>
+    <t xml:space="preserve">9.53024291992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50301361083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60285568237305</t>
   </si>
   <si>
     <t xml:space="preserve">9.63916015625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79345989227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95683479309082</t>
+    <t xml:space="preserve">9.79345893859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9568338394165</t>
   </si>
   <si>
     <t xml:space="preserve">9.93868160247803</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">9.98406410217285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73900032043457</t>
+    <t xml:space="preserve">9.73899936676025</t>
   </si>
   <si>
     <t xml:space="preserve">9.76623058319092</t>
@@ -170,10 +170,10 @@
     <t xml:space="preserve">9.74807548522949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75715351104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64823532104492</t>
+    <t xml:space="preserve">9.75715255737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64823627471924</t>
   </si>
   <si>
     <t xml:space="preserve">9.82068729400635</t>
@@ -188,7 +188,7 @@
     <t xml:space="preserve">9.67546558380127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66638851165771</t>
+    <t xml:space="preserve">9.66638946533203</t>
   </si>
   <si>
     <t xml:space="preserve">9.63008308410645</t>
@@ -197,100 +197,100 @@
     <t xml:space="preserve">9.65731239318848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68454265594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81161403656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8297643661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84791851043701</t>
+    <t xml:space="preserve">9.68454170227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81161212921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82976341247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8479175567627</t>
   </si>
   <si>
     <t xml:space="preserve">9.83884143829346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72992324829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78438186645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55747127532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34871387481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33963871002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27610301971436</t>
+    <t xml:space="preserve">9.72992420196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78438282012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55747222900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34871482849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33963680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27610397338867</t>
   </si>
   <si>
     <t xml:space="preserve">9.25794982910156</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19441604614258</t>
+    <t xml:space="preserve">9.19441509246826</t>
   </si>
   <si>
     <t xml:space="preserve">9.18533897399902</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41224956512451</t>
+    <t xml:space="preserve">9.4122486114502</t>
   </si>
   <si>
     <t xml:space="preserve">9.22164440155029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31240940093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2670259475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29425716400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28518009185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37594318389893</t>
+    <t xml:space="preserve">9.31241035461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26702690124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29425621032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28517913818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37594413757324</t>
   </si>
   <si>
     <t xml:space="preserve">9.36686706542969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38502025604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45763111114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39409732818604</t>
+    <t xml:space="preserve">9.3850212097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45763301849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39409828186035</t>
   </si>
   <si>
     <t xml:space="preserve">9.48486137390137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49393844604492</t>
+    <t xml:space="preserve">9.49393749237061</t>
   </si>
   <si>
     <t xml:space="preserve">9.44855403900146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4757833480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2397985458374</t>
+    <t xml:space="preserve">9.47578525543213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23979759216309</t>
   </si>
   <si>
     <t xml:space="preserve">9.14903354644775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21256732940674</t>
+    <t xml:space="preserve">9.21256828308105</t>
   </si>
   <si>
     <t xml:space="preserve">9.20349216461182</t>
@@ -302,16 +302,16 @@
     <t xml:space="preserve">9.1399564743042</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94027519226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8041296005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75874710083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66798210144043</t>
+    <t xml:space="preserve">8.94027614593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80412864685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75874805450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66798305511475</t>
   </si>
   <si>
     <t xml:space="preserve">8.62260055541992</t>
@@ -320,31 +320,31 @@
     <t xml:space="preserve">8.53183650970459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35030746459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16877937316895</t>
+    <t xml:space="preserve">8.35030841827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16878032684326</t>
   </si>
   <si>
     <t xml:space="preserve">7.98725128173828</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03263568878174</t>
+    <t xml:space="preserve">8.03263378143311</t>
   </si>
   <si>
     <t xml:space="preserve">8.12339782714844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25954246520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94186925888062</t>
+    <t xml:space="preserve">8.25954532623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94186878204346</t>
   </si>
   <si>
     <t xml:space="preserve">8.3049259185791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21416091918945</t>
+    <t xml:space="preserve">8.21416187286377</t>
   </si>
   <si>
     <t xml:space="preserve">8.39568996429443</t>
@@ -353,58 +353,58 @@
     <t xml:space="preserve">8.57721900939941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71336555480957</t>
+    <t xml:space="preserve">8.71336460113525</t>
   </si>
   <si>
     <t xml:space="preserve">9.53202247619629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25705909729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44036960601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16540813446045</t>
+    <t xml:space="preserve">9.25706100463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44036865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16540622711182</t>
   </si>
   <si>
     <t xml:space="preserve">9.07375144958496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11957836151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98209762573242</t>
+    <t xml:space="preserve">9.11957931518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98209857940674</t>
   </si>
   <si>
     <t xml:space="preserve">9.02792644500732</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62367725372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80698394775391</t>
+    <t xml:space="preserve">9.62367630004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80698490142822</t>
   </si>
   <si>
     <t xml:space="preserve">9.89863967895508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99029350280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1736030578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2652559280396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3569097518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5402173995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.631872177124</t>
+    <t xml:space="preserve">9.99029159545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1736011505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2652549743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3569107055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5402183532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6318731307983</t>
   </si>
   <si>
     <t xml:space="preserve">10.8151798248291</t>
@@ -413,7 +413,7 @@
     <t xml:space="preserve">10.7235260009766</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9068336486816</t>
+    <t xml:space="preserve">10.906834602356</t>
   </si>
   <si>
     <t xml:space="preserve">10.9984874725342</t>
@@ -422,40 +422,40 @@
     <t xml:space="preserve">11.090142250061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1817951202393</t>
+    <t xml:space="preserve">11.1817960739136</t>
   </si>
   <si>
     <t xml:space="preserve">11.2734508514404</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4567575454712</t>
+    <t xml:space="preserve">11.4567584991455</t>
   </si>
   <si>
     <t xml:space="preserve">11.3651027679443</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4485626220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71533203125</t>
+    <t xml:space="preserve">10.4485635757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71533107757568</t>
   </si>
   <si>
     <t xml:space="preserve">8.79878997802734</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24886512756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21123313903809</t>
+    <t xml:space="preserve">8.24886608123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2112340927124</t>
   </si>
   <si>
     <t xml:space="preserve">9.30288791656494</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03709030151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3945426940918</t>
+    <t xml:space="preserve">9.03708934783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39454174041748</t>
   </si>
   <si>
     <t xml:space="preserve">9.76115798950195</t>
@@ -467,46 +467,46 @@
     <t xml:space="preserve">9.57785034179688</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0361194610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94446754455566</t>
+    <t xml:space="preserve">10.0361204147339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94446563720703</t>
   </si>
   <si>
     <t xml:space="preserve">9.82552433013916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73283100128174</t>
+    <t xml:space="preserve">9.73283004760742</t>
   </si>
   <si>
     <t xml:space="preserve">9.59379100799561</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96456527709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91821765899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54744434356689</t>
+    <t xml:space="preserve">9.96456432342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91821670532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54744338989258</t>
   </si>
   <si>
     <t xml:space="preserve">10.010910987854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1036052703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1499519348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1962976455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77917861938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87187004089355</t>
+    <t xml:space="preserve">10.1036043167114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1499509811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1962985992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77917766571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87187099456787</t>
   </si>
   <si>
     <t xml:space="preserve">10.057258605957</t>
@@ -536,64 +536,64 @@
     <t xml:space="preserve">9.31570911407471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23228454589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19520854949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25082206726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.269362449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21374607086182</t>
+    <t xml:space="preserve">9.23228549957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19520664215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25082302093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26936149597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2137451171875</t>
   </si>
   <si>
     <t xml:space="preserve">9.04689693450928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12105178833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06543445587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97274303436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17666912078857</t>
+    <t xml:space="preserve">9.12105274200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0654354095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97274208068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17666816711426</t>
   </si>
   <si>
     <t xml:space="preserve">9.02835941314697</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95420455932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71319961547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99128150939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76881694793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89858722686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93566513061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3353395462036</t>
+    <t xml:space="preserve">8.95420265197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71320056915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9912805557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7688159942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89858818054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93566608428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3353385925293</t>
   </si>
   <si>
     <t xml:space="preserve">10.9841938018799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0305404663086</t>
+    <t xml:space="preserve">11.0305414199829</t>
   </si>
   <si>
     <t xml:space="preserve">11.2159280776978</t>
@@ -605,43 +605,43 @@
     <t xml:space="preserve">11.5403547286987</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5867023468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6330499649048</t>
+    <t xml:space="preserve">11.5867033004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6330490112305</t>
   </si>
   <si>
     <t xml:space="preserve">11.7257423400879</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9111299514771</t>
+    <t xml:space="preserve">11.9111309051514</t>
   </si>
   <si>
     <t xml:space="preserve">11.9574766159058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1892108917236</t>
+    <t xml:space="preserve">12.1892118453979</t>
   </si>
   <si>
     <t xml:space="preserve">12.2819042205811</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3745994567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5136384963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3282508850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1428642272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0965166091919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.555121421814</t>
+    <t xml:space="preserve">12.3745985031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5136394500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3282527923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1428651809692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0965185165405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5551204681396</t>
   </si>
   <si>
     <t xml:space="preserve">12.5082750320435</t>
@@ -656,19 +656,19 @@
     <t xml:space="preserve">12.4145793914795</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7425117492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6956644058228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2271890640259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1803417205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3208837509155</t>
+    <t xml:space="preserve">12.7425127029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6956653594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2271909713745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1803426742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3208847045898</t>
   </si>
   <si>
     <t xml:space="preserve">12.274037361145</t>
@@ -677,16 +677,16 @@
     <t xml:space="preserve">12.8362064361572</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7893590927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6019697189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9299020767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8830547332764</t>
+    <t xml:space="preserve">12.7893600463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6019687652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9299011230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8830537796021</t>
   </si>
   <si>
     <t xml:space="preserve">13.0704441070557</t>
@@ -695,16 +695,16 @@
     <t xml:space="preserve">13.679461479187</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8668508529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0542402267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3353252410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5695638656616</t>
+    <t xml:space="preserve">13.8668518066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0542411804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3353261947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5695629119873</t>
   </si>
   <si>
     <t xml:space="preserve">15.2254276275635</t>
@@ -725,22 +725,22 @@
     <t xml:space="preserve">15.3191232681274</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8974943161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4596652984619</t>
+    <t xml:space="preserve">14.8974952697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4596643447876</t>
   </si>
   <si>
     <t xml:space="preserve">15.4128189086914</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5533599853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0686836242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8650875091553</t>
+    <t xml:space="preserve">15.5533609390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0686798095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8650894165039</t>
   </si>
   <si>
     <t xml:space="preserve">17.0056324005127</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">17.193021774292</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0524787902832</t>
+    <t xml:space="preserve">17.0524806976318</t>
   </si>
   <si>
     <t xml:space="preserve">16.9587841033936</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">16.2092227935791</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2560729980469</t>
+    <t xml:space="preserve">16.2560710906982</t>
   </si>
   <si>
     <t xml:space="preserve">17.1461734771729</t>
@@ -782,7 +782,7 @@
     <t xml:space="preserve">16.396614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3029174804688</t>
+    <t xml:space="preserve">16.3029193878174</t>
   </si>
   <si>
     <t xml:space="preserve">15.8344440460205</t>
@@ -791,19 +791,19 @@
     <t xml:space="preserve">16.1155300140381</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0218353271484</t>
+    <t xml:space="preserve">16.0218372344971</t>
   </si>
   <si>
     <t xml:space="preserve">16.1623764038086</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9749879837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7407484054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4434623718262</t>
+    <t xml:space="preserve">15.9749870300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7407493591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4434604644775</t>
   </si>
   <si>
     <t xml:space="preserve">16.9119358062744</t>
@@ -812,19 +812,19 @@
     <t xml:space="preserve">17.0993270874023</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6776962280273</t>
+    <t xml:space="preserve">16.677698135376</t>
   </si>
   <si>
     <t xml:space="preserve">16.8182430267334</t>
   </si>
   <si>
-    <t xml:space="preserve">15.272274017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.084885597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.991189956665</t>
+    <t xml:space="preserve">15.2722749710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0848846435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9911909103394</t>
   </si>
   <si>
     <t xml:space="preserve">14.8038005828857</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">14.1010885238647</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2884788513184</t>
+    <t xml:space="preserve">14.288477897644</t>
   </si>
   <si>
     <t xml:space="preserve">14.5227155685425</t>
@@ -854,37 +854,37 @@
     <t xml:space="preserve">14.1947832107544</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0073938369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7263088226318</t>
+    <t xml:space="preserve">14.0073928833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7263078689575</t>
   </si>
   <si>
     <t xml:space="preserve">14.1479358673096</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4290199279785</t>
+    <t xml:space="preserve">14.4290208816528</t>
   </si>
   <si>
     <t xml:space="preserve">14.6164102554321</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7731552124023</t>
+    <t xml:space="preserve">13.7731561660767</t>
   </si>
   <si>
     <t xml:space="preserve">13.3515291213989</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3046817779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3983764648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0235967636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1172924041748</t>
+    <t xml:space="preserve">13.3046808242798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3983755111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0235958099365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1172904968262</t>
   </si>
   <si>
     <t xml:space="preserve">12.976749420166</t>
@@ -893,19 +893,19 @@
     <t xml:space="preserve">12.3677320480347</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0866470336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9929523468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8992567062378</t>
+    <t xml:space="preserve">12.0866460800171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9929513931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8992576599121</t>
   </si>
   <si>
     <t xml:space="preserve">12.0397996902466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1334934234619</t>
+    <t xml:space="preserve">12.1334943771362</t>
   </si>
   <si>
     <t xml:space="preserve">11.4776296615601</t>
@@ -914,10 +914,10 @@
     <t xml:space="preserve">11.2433929443359</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3839340209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6650190353394</t>
+    <t xml:space="preserve">11.3839349746704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6650199890137</t>
   </si>
   <si>
     <t xml:space="preserve">11.4307823181152</t>
@@ -926,16 +926,16 @@
     <t xml:space="preserve">10.9623079299927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7280712127686</t>
+    <t xml:space="preserve">10.7280702590942</t>
   </si>
   <si>
     <t xml:space="preserve">11.1965446472168</t>
   </si>
   <si>
-    <t xml:space="preserve">11.571325302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3370876312256</t>
+    <t xml:space="preserve">11.5713243484497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3370885848999</t>
   </si>
   <si>
     <t xml:space="preserve">11.2902402877808</t>
@@ -953,25 +953,25 @@
     <t xml:space="preserve">11.0091552734375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46318912506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33884811401367</t>
+    <t xml:space="preserve">9.46318817138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33884906768799</t>
   </si>
   <si>
     <t xml:space="preserve">8.57308673858643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31074142456055</t>
+    <t xml:space="preserve">8.31074047088623</t>
   </si>
   <si>
     <t xml:space="preserve">8.45128440856934</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61993312835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44191360473633</t>
+    <t xml:space="preserve">8.61993408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44191455841064</t>
   </si>
   <si>
     <t xml:space="preserve">8.32948112487793</t>
@@ -980,67 +980,67 @@
     <t xml:space="preserve">8.25452423095703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43254375457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47002220153809</t>
+    <t xml:space="preserve">8.43254470825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47002124786377</t>
   </si>
   <si>
     <t xml:space="preserve">8.32011032104492</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20767784118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08587265014648</t>
+    <t xml:space="preserve">8.20767688751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0858736038208</t>
   </si>
   <si>
     <t xml:space="preserve">7.78604936599731</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49559497833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33631420135498</t>
+    <t xml:space="preserve">7.49559545516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33631372451782</t>
   </si>
   <si>
     <t xml:space="preserve">7.23324918746948</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83289670944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90785217285156</t>
+    <t xml:space="preserve">7.83289623260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9078516960144</t>
   </si>
   <si>
     <t xml:space="preserve">7.50496482849121</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37379169464111</t>
+    <t xml:space="preserve">7.37379217147827</t>
   </si>
   <si>
     <t xml:space="preserve">7.12081527709961</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28009700775146</t>
+    <t xml:space="preserve">7.28009653091431</t>
   </si>
   <si>
     <t xml:space="preserve">6.98027276992798</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93342542648315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06459856033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0271201133728</t>
+    <t xml:space="preserve">6.93342590332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06459808349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02712059020996</t>
   </si>
   <si>
     <t xml:space="preserve">7.34568309783936</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5424427986145</t>
+    <t xml:space="preserve">7.54244232177734</t>
   </si>
   <si>
     <t xml:space="preserve">8.19830703735352</t>
@@ -1049,16 +1049,16 @@
     <t xml:space="preserve">8.2170467376709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65194320678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46116256713867</t>
+    <t xml:space="preserve">8.65194225311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46116161346436</t>
   </si>
   <si>
     <t xml:space="preserve">8.53747367858887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68056106567383</t>
+    <t xml:space="preserve">8.68056201934814</t>
   </si>
   <si>
     <t xml:space="preserve">8.77595138549805</t>
@@ -1067,16 +1067,16 @@
     <t xml:space="preserve">8.84272575378418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72825527191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66148281097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49931716918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42300605773926</t>
+    <t xml:space="preserve">8.72825622558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6614818572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49931812286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42300510406494</t>
   </si>
   <si>
     <t xml:space="preserve">8.39438915252686</t>
@@ -1091,7 +1091,7 @@
     <t xml:space="preserve">8.29899787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12729549407959</t>
+    <t xml:space="preserve">8.12729358673096</t>
   </si>
   <si>
     <t xml:space="preserve">7.89835643768311</t>
@@ -1100,19 +1100,19 @@
     <t xml:space="preserve">8.10821628570557</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8411226272583</t>
+    <t xml:space="preserve">7.84112215042114</t>
   </si>
   <si>
     <t xml:space="preserve">8.33715343475342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20360660552979</t>
+    <t xml:space="preserve">8.2036075592041</t>
   </si>
   <si>
     <t xml:space="preserve">8.06052017211914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07959938049316</t>
+    <t xml:space="preserve">8.07959842681885</t>
   </si>
   <si>
     <t xml:space="preserve">8.07005977630615</t>
@@ -1121,22 +1121,22 @@
     <t xml:space="preserve">7.92697334289551</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98420763015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30853652954102</t>
+    <t xml:space="preserve">7.98420810699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30853748321533</t>
   </si>
   <si>
     <t xml:space="preserve">8.26084136962891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2703800201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18452835083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03190422058105</t>
+    <t xml:space="preserve">8.27038097381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18452930450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03190326690674</t>
   </si>
   <si>
     <t xml:space="preserve">7.96512985229492</t>
@@ -1151,7 +1151,7 @@
     <t xml:space="preserve">7.71711397171021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91743421554565</t>
+    <t xml:space="preserve">7.91743516921997</t>
   </si>
   <si>
     <t xml:space="preserve">7.76480960845947</t>
@@ -1166,37 +1166,37 @@
     <t xml:space="preserve">7.63126230239868</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65987968444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.165452003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32761478424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11775588989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93651247024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19406795501709</t>
+    <t xml:space="preserve">7.65987873077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16545104980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32761383056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11775493621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9365119934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19406890869141</t>
   </si>
   <si>
     <t xml:space="preserve">8.2322244644165</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31807613372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15591144561768</t>
+    <t xml:space="preserve">8.31807708740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15591239929199</t>
   </si>
   <si>
     <t xml:space="preserve">8.22268486022949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25130081176758</t>
+    <t xml:space="preserve">8.25130176544189</t>
   </si>
   <si>
     <t xml:space="preserve">8.35623264312744</t>
@@ -1223,28 +1223,28 @@
     <t xml:space="preserve">8.01282501220703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05098152160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67895793914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7361912727356</t>
+    <t xml:space="preserve">8.05098056793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67895746231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73619174957275</t>
   </si>
   <si>
     <t xml:space="preserve">7.6980357170105</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51679372787476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59310579299927</t>
+    <t xml:space="preserve">7.5167932510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59310626983643</t>
   </si>
   <si>
     <t xml:space="preserve">7.44048070907593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53587198257446</t>
+    <t xml:space="preserve">7.5358715057373</t>
   </si>
   <si>
     <t xml:space="preserve">7.62172269821167</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">7.20200395584106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1829252243042</t>
+    <t xml:space="preserve">7.18292570114136</t>
   </si>
   <si>
     <t xml:space="preserve">7.14476919174194</t>
@@ -1280,19 +1280,19 @@
     <t xml:space="preserve">7.24016046524048</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46909809112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41186380386353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45001935958862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28785514831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39278554916382</t>
+    <t xml:space="preserve">7.46909761428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41186332702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45001983642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28785562515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39278507232666</t>
   </si>
   <si>
     <t xml:space="preserve">7.3355507850647</t>
@@ -1301,43 +1301,43 @@
     <t xml:space="preserve">7.61218404769897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90789604187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94605159759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45955896377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70757484436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87927913665771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99374675750732</t>
+    <t xml:space="preserve">7.90789556503296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94605112075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45955848693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70757436752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87927865982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99374723434448</t>
   </si>
   <si>
     <t xml:space="preserve">7.75527048110962</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81250429153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79342651367188</t>
+    <t xml:space="preserve">7.81250476837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79342699050903</t>
   </si>
   <si>
     <t xml:space="preserve">7.80296611785889</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85066080093384</t>
+    <t xml:space="preserve">7.85066032409668</t>
   </si>
   <si>
     <t xml:space="preserve">7.74573087692261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83158302307129</t>
+    <t xml:space="preserve">7.83158254623413</t>
   </si>
   <si>
     <t xml:space="preserve">7.66941833496094</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">7.58356666564941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88881826400757</t>
+    <t xml:space="preserve">7.88881778717041</t>
   </si>
   <si>
     <t xml:space="preserve">8.00328636169434</t>
@@ -1361,7 +1361,7 @@
     <t xml:space="preserve">7.3641676902771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10661315917969</t>
+    <t xml:space="preserve">7.10661268234253</t>
   </si>
   <si>
     <t xml:space="preserve">7.27831649780273</t>
@@ -1376,10 +1376,10 @@
     <t xml:space="preserve">7.50372648239136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98721408843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02589225769043</t>
+    <t xml:space="preserve">7.98721361160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02589321136475</t>
   </si>
   <si>
     <t xml:space="preserve">8.04523086547852</t>
@@ -1391,25 +1391,25 @@
     <t xml:space="preserve">8.07424163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12258911132812</t>
+    <t xml:space="preserve">8.12259006500244</t>
   </si>
   <si>
     <t xml:space="preserve">8.05490112304688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94853496551514</t>
+    <t xml:space="preserve">7.94853448867798</t>
   </si>
   <si>
     <t xml:space="preserve">8.06457138061523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08390998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97754430770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93886518478394</t>
+    <t xml:space="preserve">8.08391094207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97754383087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93886423110962</t>
   </si>
   <si>
     <t xml:space="preserve">7.79381895065308</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">7.68745088577271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63910293579102</t>
+    <t xml:space="preserve">7.63910245895386</t>
   </si>
   <si>
     <t xml:space="preserve">7.73579978942871</t>
@@ -1436,10 +1436,10 @@
     <t xml:space="preserve">7.90985584259033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85183668136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83249759674072</t>
+    <t xml:space="preserve">7.85183715820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83249807357788</t>
   </si>
   <si>
     <t xml:space="preserve">7.81315755844116</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">7.80348825454712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78414916992188</t>
+    <t xml:space="preserve">7.78414869308472</t>
   </si>
   <si>
     <t xml:space="preserve">7.6681113243103</t>
@@ -1460,13 +1460,13 @@
     <t xml:space="preserve">7.71646022796631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75513982772827</t>
+    <t xml:space="preserve">7.75514030456543</t>
   </si>
   <si>
     <t xml:space="preserve">7.74547004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86150693893433</t>
+    <t xml:space="preserve">7.86150646209717</t>
   </si>
   <si>
     <t xml:space="preserve">7.89051580429077</t>
@@ -1484,10 +1484,10 @@
     <t xml:space="preserve">8.09358024597168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13225936889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1515998840332</t>
+    <t xml:space="preserve">8.1322603225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15159893035889</t>
   </si>
   <si>
     <t xml:space="preserve">8.1129207611084</t>
@@ -1496,10 +1496,10 @@
     <t xml:space="preserve">8.03556251525879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92919492721558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69712066650391</t>
+    <t xml:space="preserve">7.92919540405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69712114334106</t>
   </si>
   <si>
     <t xml:space="preserve">7.60042381286621</t>
@@ -1508,10 +1508,10 @@
     <t xml:space="preserve">7.88084602355957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55207443237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40702819824219</t>
+    <t xml:space="preserve">7.55207490921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40702867507935</t>
   </si>
   <si>
     <t xml:space="preserve">7.34900999069214</t>
@@ -1520,16 +1520,16 @@
     <t xml:space="preserve">7.37801933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43603754043579</t>
+    <t xml:space="preserve">7.43603801727295</t>
   </si>
   <si>
     <t xml:space="preserve">7.41669797897339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52306604385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36834955215454</t>
+    <t xml:space="preserve">7.5230655670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36834907531738</t>
   </si>
   <si>
     <t xml:space="preserve">7.542405128479</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">7.4843864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70679044723511</t>
+    <t xml:space="preserve">7.70679092407227</t>
   </si>
   <si>
     <t xml:space="preserve">7.64877223968506</t>
@@ -1556,10 +1556,10 @@
     <t xml:space="preserve">7.59075355529785</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95820426940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96787405014038</t>
+    <t xml:space="preserve">7.95820331573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96787357330322</t>
   </si>
   <si>
     <t xml:space="preserve">7.90018606185913</t>
@@ -1577,10 +1577,10 @@
     <t xml:space="preserve">8.19027900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29664611816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45136165618896</t>
+    <t xml:space="preserve">8.29664516448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45136070251465</t>
   </si>
   <si>
     <t xml:space="preserve">8.48037147521973</t>
@@ -1607,19 +1607,19 @@
     <t xml:space="preserve">8.50938034057617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4223518371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54805946350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55772972106934</t>
+    <t xml:space="preserve">8.42235279083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54805850982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55772876739502</t>
   </si>
   <si>
     <t xml:space="preserve">8.52871990203857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68343448638916</t>
+    <t xml:space="preserve">8.68343544006348</t>
   </si>
   <si>
     <t xml:space="preserve">8.76079368591309</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">8.65442562103271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75112438201904</t>
+    <t xml:space="preserve">8.75112342834473</t>
   </si>
   <si>
     <t xml:space="preserve">8.70277500152588</t>
@@ -1652,10 +1652,10 @@
     <t xml:space="preserve">8.63508701324463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32565402984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31598472595215</t>
+    <t xml:space="preserve">8.32565498352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31598567962646</t>
   </si>
   <si>
     <t xml:space="preserve">8.30631542205811</t>
@@ -63157,7 +63157,7 @@
     </row>
     <row r="2330">
       <c r="A2330" s="1" t="n">
-        <v>46007.6910300926</v>
+        <v>46007.3333333333</v>
       </c>
       <c r="B2330" t="n">
         <v>46835</v>
@@ -63178,6 +63178,32 @@
         <v>750</v>
       </c>
       <c r="H2330" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2331">
+      <c r="A2331" s="1" t="n">
+        <v>46008.6911226852</v>
+      </c>
+      <c r="B2331" t="n">
+        <v>52329</v>
+      </c>
+      <c r="C2331" t="n">
+        <v>9.80000019073486</v>
+      </c>
+      <c r="D2331" t="n">
+        <v>9.42000007629395</v>
+      </c>
+      <c r="E2331" t="n">
+        <v>9.80000019073486</v>
+      </c>
+      <c r="F2331" t="n">
+        <v>9.5600004196167</v>
+      </c>
+      <c r="G2331" t="s">
+        <v>741</v>
+      </c>
+      <c r="H2331" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="753">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="754">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,61 +38,61 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0764217376709</t>
+    <t xml:space="preserve">9.07642269134521</t>
   </si>
   <si>
     <t xml:space="preserve">FF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98565769195557</t>
+    <t xml:space="preserve">8.98565673828125</t>
   </si>
   <si>
     <t xml:space="preserve">9.08549785614014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24887275695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09457588195801</t>
+    <t xml:space="preserve">9.24887371063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09457397460938</t>
   </si>
   <si>
     <t xml:space="preserve">9.12180423736572</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03104019165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95389080047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89943408966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89489364624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84951210021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85858631134033</t>
+    <t xml:space="preserve">9.03103923797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95388984680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89943313598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89489459991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84951114654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85858726501465</t>
   </si>
   <si>
     <t xml:space="preserve">8.87674045562744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76782321929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86766338348389</t>
+    <t xml:space="preserve">8.76782417297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86766529083252</t>
   </si>
   <si>
     <t xml:space="preserve">9.04919242858887</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23071956634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11272811889648</t>
+    <t xml:space="preserve">9.23072147369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11272716522217</t>
   </si>
   <si>
     <t xml:space="preserve">8.96750450134277</t>
@@ -101,25 +101,25 @@
     <t xml:space="preserve">8.91304588317871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92212390899658</t>
+    <t xml:space="preserve">8.92212295532227</t>
   </si>
   <si>
     <t xml:space="preserve">9.00381088256836</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15810966491699</t>
+    <t xml:space="preserve">9.15810775756836</t>
   </si>
   <si>
     <t xml:space="preserve">9.16718673706055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43947887420654</t>
+    <t xml:space="preserve">9.43947792053223</t>
   </si>
   <si>
     <t xml:space="preserve">9.54839611053467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62100696563721</t>
+    <t xml:space="preserve">9.62100791931152</t>
   </si>
   <si>
     <t xml:space="preserve">9.80253601074219</t>
@@ -128,19 +128,19 @@
     <t xml:space="preserve">9.71177101135254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56654930114746</t>
+    <t xml:space="preserve">9.56654834747314</t>
   </si>
   <si>
     <t xml:space="preserve">9.58470153808594</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57562446594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53024196624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50301551818848</t>
+    <t xml:space="preserve">9.5756254196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53024387359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50301456451416</t>
   </si>
   <si>
     <t xml:space="preserve">9.60285472869873</t>
@@ -149,40 +149,40 @@
     <t xml:space="preserve">9.63915920257568</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79345798492432</t>
+    <t xml:space="preserve">9.79345893859863</t>
   </si>
   <si>
     <t xml:space="preserve">9.95683479309082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93868350982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98406314849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73900032043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76623058319092</t>
+    <t xml:space="preserve">9.93868255615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98406505584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73900127410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7662296295166</t>
   </si>
   <si>
     <t xml:space="preserve">9.74807643890381</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75715255737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64823627471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82068824768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70269298553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72084712982178</t>
+    <t xml:space="preserve">9.75715351104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64823722839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82068729400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70269393920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72084808349609</t>
   </si>
   <si>
     <t xml:space="preserve">9.67546558380127</t>
@@ -191,205 +191,205 @@
     <t xml:space="preserve">9.66638851165771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63008308410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65731430053711</t>
+    <t xml:space="preserve">9.63008403778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65731334686279</t>
   </si>
   <si>
     <t xml:space="preserve">9.68454265594482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81161212921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82976531982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84791946411133</t>
+    <t xml:space="preserve">9.81161308288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8297643661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8479175567627</t>
   </si>
   <si>
     <t xml:space="preserve">9.83884239196777</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72992324829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78438282012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55747222900391</t>
+    <t xml:space="preserve">9.72992420196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78438186645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55747318267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34871387481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33963775634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27610301971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25794982910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19441604614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18533897399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4122486114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22164344787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31240844726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26702690124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29425621032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28517913818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37594413757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36686706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38502025604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45763206481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39409732818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48486137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49393653869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44855499267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47578430175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23979663848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14903450012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21256828308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20349216461182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13087940216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13995742797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94027614593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8041296005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75874614715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66798305511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62260246276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53183650970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35030746459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16878032684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98725128173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03263378143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12339687347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25954627990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94186878204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3049259185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21416187286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39568901062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57721900939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71336555480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53202247619629</t>
   </si>
   <si>
     <t xml:space="preserve">9.34871482849121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33963775634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27610397338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25794982910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19441509246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18533897399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41225051879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22164535522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31240940093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26702690124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29425430297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28517913818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37594413757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36686706542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38502025604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45763206481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39409732818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48486137390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49393749237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44855499267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47578430175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23979663848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14903259277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21256828308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2034912109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13088130950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13995552062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94027709960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80412769317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75874805450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66798210144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62260055541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53183650970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35030841827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16877937316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9872522354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03263378143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12339687347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25954532623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94186878204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3049259185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21416187286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39568901062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57721710205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71336460113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53202342987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34871387481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25706100463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44036960601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16540622711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07375240325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11958026885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98209857940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02792739868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62367630004883</t>
+    <t xml:space="preserve">9.25706195831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44036769866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16540718078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07375144958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11957931518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98209953308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02792549133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62367725372314</t>
   </si>
   <si>
     <t xml:space="preserve">9.80698490142822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89863872528076</t>
+    <t xml:space="preserve">9.89863967895508</t>
   </si>
   <si>
     <t xml:space="preserve">9.9902925491333</t>
@@ -398,37 +398,37 @@
     <t xml:space="preserve">10.1736011505127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2652559280396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3569087982178</t>
+    <t xml:space="preserve">10.2652549743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3569107055664</t>
   </si>
   <si>
     <t xml:space="preserve">10.5402183532715</t>
   </si>
   <si>
-    <t xml:space="preserve">10.631872177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8151798248291</t>
+    <t xml:space="preserve">10.6318731307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8151788711548</t>
   </si>
   <si>
     <t xml:space="preserve">10.7235260009766</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9068336486816</t>
+    <t xml:space="preserve">10.906834602356</t>
   </si>
   <si>
     <t xml:space="preserve">10.9984884262085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.090142250061</t>
+    <t xml:space="preserve">11.0901432037354</t>
   </si>
   <si>
     <t xml:space="preserve">11.1817960739136</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734498977661</t>
+    <t xml:space="preserve">11.2734508514404</t>
   </si>
   <si>
     <t xml:space="preserve">11.4567584991455</t>
@@ -440,13 +440,13 @@
     <t xml:space="preserve">10.4485635757446</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71533107757568</t>
+    <t xml:space="preserve">9.71533203125</t>
   </si>
   <si>
     <t xml:space="preserve">8.79879093170166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24886608123779</t>
+    <t xml:space="preserve">8.24886703491211</t>
   </si>
   <si>
     <t xml:space="preserve">9.2112340927124</t>
@@ -458,10 +458,10 @@
     <t xml:space="preserve">9.03708934783936</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39454078674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76115798950195</t>
+    <t xml:space="preserve">9.39454174041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76115703582764</t>
   </si>
   <si>
     <t xml:space="preserve">9.66950416564941</t>
@@ -473,43 +473,43 @@
     <t xml:space="preserve">10.0361213684082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94446754455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82552433013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73283004760742</t>
+    <t xml:space="preserve">9.94446563720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82552528381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73283100128174</t>
   </si>
   <si>
     <t xml:space="preserve">9.59379005432129</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96456527709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91821765899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54744338989258</t>
+    <t xml:space="preserve">9.96456432342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91821670532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54744243621826</t>
   </si>
   <si>
     <t xml:space="preserve">10.010910987854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1036043167114</t>
+    <t xml:space="preserve">10.1036052703857</t>
   </si>
   <si>
     <t xml:space="preserve">10.1499519348145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1962976455688</t>
+    <t xml:space="preserve">10.1962985992432</t>
   </si>
   <si>
     <t xml:space="preserve">9.77917766571045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87187099456787</t>
+    <t xml:space="preserve">9.87187004089355</t>
   </si>
   <si>
     <t xml:space="preserve">10.057258605957</t>
@@ -524,70 +524,70 @@
     <t xml:space="preserve">10.2426452636719</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3816871643066</t>
+    <t xml:space="preserve">10.381685256958</t>
   </si>
   <si>
     <t xml:space="preserve">9.68648338317871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64013671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50109577178955</t>
+    <t xml:space="preserve">9.64013576507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50109672546387</t>
   </si>
   <si>
     <t xml:space="preserve">9.31570911407471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23228549957275</t>
+    <t xml:space="preserve">9.23228454589844</t>
   </si>
   <si>
     <t xml:space="preserve">9.1952075958252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25082206726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26936149597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2137451171875</t>
+    <t xml:space="preserve">9.25082302093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.269362449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21374607086182</t>
   </si>
   <si>
     <t xml:space="preserve">9.04689693450928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12105274200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0654354095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97274208068848</t>
+    <t xml:space="preserve">9.12105369567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06543636322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97274303436279</t>
   </si>
   <si>
     <t xml:space="preserve">9.17666816711426</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02835845947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95420265197754</t>
+    <t xml:space="preserve">9.02835941314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95420360565186</t>
   </si>
   <si>
     <t xml:space="preserve">8.71320056915283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9912805557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76881694793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89858818054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93566513061523</t>
+    <t xml:space="preserve">8.99128150939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7688159942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89858913421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93566608428955</t>
   </si>
   <si>
     <t xml:space="preserve">10.3353385925293</t>
@@ -602,13 +602,13 @@
     <t xml:space="preserve">11.2159290313721</t>
   </si>
   <si>
-    <t xml:space="preserve">11.49400806427</t>
+    <t xml:space="preserve">11.4940099716187</t>
   </si>
   <si>
     <t xml:space="preserve">11.540355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5867023468018</t>
+    <t xml:space="preserve">11.5867033004761</t>
   </si>
   <si>
     <t xml:space="preserve">11.6330490112305</t>
@@ -617,19 +617,19 @@
     <t xml:space="preserve">11.7257423400879</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9111299514771</t>
+    <t xml:space="preserve">11.9111309051514</t>
   </si>
   <si>
     <t xml:space="preserve">11.9574775695801</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1892118453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2819061279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3745994567871</t>
+    <t xml:space="preserve">12.1892108917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2819042205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3745985031128</t>
   </si>
   <si>
     <t xml:space="preserve">12.5136394500732</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">12.1428651809692</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0965185165405</t>
+    <t xml:space="preserve">12.0965175628662</t>
   </si>
   <si>
     <t xml:space="preserve">12.555121421814</t>
@@ -656,13 +656,13 @@
     <t xml:space="preserve">12.4614267349243</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4145803451538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7425117492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6956653594971</t>
+    <t xml:space="preserve">12.4145784378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7425127029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6956644058228</t>
   </si>
   <si>
     <t xml:space="preserve">12.2271900177002</t>
@@ -671,7 +671,7 @@
     <t xml:space="preserve">12.1803426742554</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3208847045898</t>
+    <t xml:space="preserve">12.3208837509155</t>
   </si>
   <si>
     <t xml:space="preserve">12.274037361145</t>
@@ -680,16 +680,16 @@
     <t xml:space="preserve">12.8362064361572</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7893581390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6019697189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9299020767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8830547332764</t>
+    <t xml:space="preserve">12.7893590927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6019687652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9299011230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8830528259277</t>
   </si>
   <si>
     <t xml:space="preserve">13.0704441070557</t>
@@ -710,40 +710,40 @@
     <t xml:space="preserve">14.5695629119873</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2254285812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1317338943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7569522857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0380382537842</t>
+    <t xml:space="preserve">15.2254276275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1317319869995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7569532394409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0380373001099</t>
   </si>
   <si>
     <t xml:space="preserve">15.1785802841187</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3191223144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8974943161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4596652984619</t>
+    <t xml:space="preserve">15.3191242218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8974952697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4596643447876</t>
   </si>
   <si>
     <t xml:space="preserve">15.4128179550171</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5533618927002</t>
+    <t xml:space="preserve">15.5533609390259</t>
   </si>
   <si>
     <t xml:space="preserve">16.0686817169189</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8650894165039</t>
+    <t xml:space="preserve">16.8650913238525</t>
   </si>
   <si>
     <t xml:space="preserve">17.0056324005127</t>
@@ -758,13 +758,13 @@
     <t xml:space="preserve">17.0524806976318</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9587821960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7245464324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6308517456055</t>
+    <t xml:space="preserve">16.9587860107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7245445251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6308498382568</t>
   </si>
   <si>
     <t xml:space="preserve">16.5371570587158</t>
@@ -773,10 +773,10 @@
     <t xml:space="preserve">16.584005355835</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2092247009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2560710906982</t>
+    <t xml:space="preserve">16.2092227935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2560729980469</t>
   </si>
   <si>
     <t xml:space="preserve">17.1461734771729</t>
@@ -785,28 +785,28 @@
     <t xml:space="preserve">16.396614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3029174804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8344430923462</t>
+    <t xml:space="preserve">16.3029193878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8344440460205</t>
   </si>
   <si>
     <t xml:space="preserve">16.1155300140381</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0218353271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1623783111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.974986076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7407503128052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4434604644775</t>
+    <t xml:space="preserve">16.0218372344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1623764038086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9749870300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7407493591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4434623718262</t>
   </si>
   <si>
     <t xml:space="preserve">16.9119358062744</t>
@@ -815,43 +815,43 @@
     <t xml:space="preserve">17.0993270874023</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6777000427246</t>
+    <t xml:space="preserve">16.677698135376</t>
   </si>
   <si>
     <t xml:space="preserve">16.8182430267334</t>
   </si>
   <si>
-    <t xml:space="preserve">15.272274017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.084885597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.991189956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8038015365601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4758672714233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3821744918823</t>
+    <t xml:space="preserve">15.2722749710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0848846435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9911909103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8038005828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4758682250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.382173538208</t>
   </si>
   <si>
     <t xml:space="preserve">14.1010885238647</t>
   </si>
   <si>
-    <t xml:space="preserve">14.288477897644</t>
+    <t xml:space="preserve">14.2884769439697</t>
   </si>
   <si>
     <t xml:space="preserve">14.5227155685425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9605464935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2416305541992</t>
+    <t xml:space="preserve">13.960545539856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2416296005249</t>
   </si>
   <si>
     <t xml:space="preserve">14.1947822570801</t>
@@ -860,22 +860,22 @@
     <t xml:space="preserve">14.0073928833008</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7263078689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1479368209839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4290199279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6164112091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7731561660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3515291213989</t>
+    <t xml:space="preserve">13.7263069152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1479358673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4290208816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6164102554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7731552124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3515281677246</t>
   </si>
   <si>
     <t xml:space="preserve">13.3046808242798</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">13.3983764648438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0235958099365</t>
+    <t xml:space="preserve">13.0235967636108</t>
   </si>
   <si>
     <t xml:space="preserve">13.1172914505005</t>
@@ -893,13 +893,13 @@
     <t xml:space="preserve">12.976749420166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3677310943604</t>
+    <t xml:space="preserve">12.3677320480347</t>
   </si>
   <si>
     <t xml:space="preserve">12.0866470336914</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9929523468018</t>
+    <t xml:space="preserve">11.9929513931274</t>
   </si>
   <si>
     <t xml:space="preserve">11.8992576599121</t>
@@ -911,37 +911,37 @@
     <t xml:space="preserve">12.1334943771362</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4776306152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2433938980103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3839340209961</t>
+    <t xml:space="preserve">11.4776296615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2433929443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3839349746704</t>
   </si>
   <si>
     <t xml:space="preserve">11.6650199890137</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4307832717896</t>
+    <t xml:space="preserve">11.4307823181152</t>
   </si>
   <si>
     <t xml:space="preserve">10.9623079299927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7280712127686</t>
+    <t xml:space="preserve">10.7280702590942</t>
   </si>
   <si>
     <t xml:space="preserve">11.1965446472168</t>
   </si>
   <si>
-    <t xml:space="preserve">11.571325302124</t>
+    <t xml:space="preserve">11.5713243484497</t>
   </si>
   <si>
     <t xml:space="preserve">11.3370885848999</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2902393341064</t>
+    <t xml:space="preserve">11.2902402877808</t>
   </si>
   <si>
     <t xml:space="preserve">11.7118673324585</t>
@@ -953,13 +953,13 @@
     <t xml:space="preserve">11.8055629730225</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0091562271118</t>
+    <t xml:space="preserve">11.0091552734375</t>
   </si>
   <si>
     <t xml:space="preserve">9.46318912506104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3388500213623</t>
+    <t xml:space="preserve">8.33884906768799</t>
   </si>
   <si>
     <t xml:space="preserve">8.57308673858643</t>
@@ -968,7 +968,7 @@
     <t xml:space="preserve">8.31074142456055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45128345489502</t>
+    <t xml:space="preserve">8.45128440856934</t>
   </si>
   <si>
     <t xml:space="preserve">8.61993408203125</t>
@@ -977,13 +977,13 @@
     <t xml:space="preserve">8.44191455841064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32948017120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25452518463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43254470825195</t>
+    <t xml:space="preserve">8.32948112487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25452423095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43254566192627</t>
   </si>
   <si>
     <t xml:space="preserve">8.47002220153809</t>
@@ -992,25 +992,25 @@
     <t xml:space="preserve">8.32011032104492</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20767593383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08587265014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78604936599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49559497833252</t>
+    <t xml:space="preserve">8.20767688751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0858736038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78605031967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49559545516968</t>
   </si>
   <si>
     <t xml:space="preserve">7.33631372451782</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23324871063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8328971862793</t>
+    <t xml:space="preserve">7.23324918746948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83289623260498</t>
   </si>
   <si>
     <t xml:space="preserve">7.90785264968872</t>
@@ -1019,16 +1019,16 @@
     <t xml:space="preserve">7.50496482849121</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37379217147827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12081527709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28009700775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98027324676514</t>
+    <t xml:space="preserve">7.37379169464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12081480026245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28009653091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98027276992798</t>
   </si>
   <si>
     <t xml:space="preserve">6.93342590332031</t>
@@ -1040,10 +1040,10 @@
     <t xml:space="preserve">7.02712059020996</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34568357467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5424427986145</t>
+    <t xml:space="preserve">7.34568309783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54244232177734</t>
   </si>
   <si>
     <t xml:space="preserve">8.19830703735352</t>
@@ -1052,10 +1052,10 @@
     <t xml:space="preserve">8.2170467376709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65194225311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46116161346436</t>
+    <t xml:space="preserve">8.65194320678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46116256713867</t>
   </si>
   <si>
     <t xml:space="preserve">8.53747367858887</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">8.72825622558594</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6614818572998</t>
+    <t xml:space="preserve">8.66148281097412</t>
   </si>
   <si>
     <t xml:space="preserve">8.49931812286377</t>
@@ -1094,13 +1094,13 @@
     <t xml:space="preserve">8.29899787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12729358673096</t>
+    <t xml:space="preserve">8.12729454040527</t>
   </si>
   <si>
     <t xml:space="preserve">7.89835643768311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10821628570557</t>
+    <t xml:space="preserve">8.10821723937988</t>
   </si>
   <si>
     <t xml:space="preserve">7.84112215042114</t>
@@ -1115,13 +1115,13 @@
     <t xml:space="preserve">8.06052017211914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07959842681885</t>
+    <t xml:space="preserve">8.07959938049316</t>
   </si>
   <si>
     <t xml:space="preserve">8.07005977630615</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92697334289551</t>
+    <t xml:space="preserve">7.92697429656982</t>
   </si>
   <si>
     <t xml:space="preserve">7.98420810699463</t>
@@ -1130,7 +1130,7 @@
     <t xml:space="preserve">8.30853748321533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26084136962891</t>
+    <t xml:space="preserve">8.26084041595459</t>
   </si>
   <si>
     <t xml:space="preserve">8.27038097381592</t>
@@ -1139,13 +1139,13 @@
     <t xml:space="preserve">8.18452930450439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03190326690674</t>
+    <t xml:space="preserve">8.03190422058105</t>
   </si>
   <si>
     <t xml:space="preserve">7.96512985229492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86019992828369</t>
+    <t xml:space="preserve">7.86020040512085</t>
   </si>
   <si>
     <t xml:space="preserve">7.86973905563354</t>
@@ -1169,10 +1169,10 @@
     <t xml:space="preserve">7.63126230239868</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65987873077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16545104980469</t>
+    <t xml:space="preserve">7.65987920761108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16545009613037</t>
   </si>
   <si>
     <t xml:space="preserve">8.32761383056641</t>
@@ -1184,13 +1184,13 @@
     <t xml:space="preserve">7.9365119934082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19406890869141</t>
+    <t xml:space="preserve">8.19406795501709</t>
   </si>
   <si>
     <t xml:space="preserve">8.2322244644165</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31807708740234</t>
+    <t xml:space="preserve">8.31807613372803</t>
   </si>
   <si>
     <t xml:space="preserve">8.15591239929199</t>
@@ -1211,7 +1211,7 @@
     <t xml:space="preserve">8.34669303894043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95559072494507</t>
+    <t xml:space="preserve">7.95559167861938</t>
   </si>
   <si>
     <t xml:space="preserve">7.77434825897217</t>
@@ -1226,13 +1226,13 @@
     <t xml:space="preserve">8.01282501220703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05098056793213</t>
+    <t xml:space="preserve">8.05098152160645</t>
   </si>
   <si>
     <t xml:space="preserve">7.67895746231079</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73619174957275</t>
+    <t xml:space="preserve">7.73619222640991</t>
   </si>
   <si>
     <t xml:space="preserve">7.6980357170105</t>
@@ -1253,7 +1253,7 @@
     <t xml:space="preserve">7.62172269821167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52633237838745</t>
+    <t xml:space="preserve">7.52633190155029</t>
   </si>
   <si>
     <t xml:space="preserve">7.34508991241455</t>
@@ -1262,7 +1262,7 @@
     <t xml:space="preserve">7.20200395584106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18292570114136</t>
+    <t xml:space="preserve">7.18292617797852</t>
   </si>
   <si>
     <t xml:space="preserve">7.14476919174194</t>
@@ -1277,13 +1277,13 @@
     <t xml:space="preserve">7.1543083190918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24969911575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24016046524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46909761428833</t>
+    <t xml:space="preserve">7.24969863891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24015998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46909809112549</t>
   </si>
   <si>
     <t xml:space="preserve">7.41186332702637</t>
@@ -1292,7 +1292,7 @@
     <t xml:space="preserve">7.45001983642578</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28785562515259</t>
+    <t xml:space="preserve">7.28785514831543</t>
   </si>
   <si>
     <t xml:space="preserve">7.39278507232666</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">7.3355507850647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61218404769897</t>
+    <t xml:space="preserve">7.61218452453613</t>
   </si>
   <si>
     <t xml:space="preserve">7.90789556503296</t>
@@ -1310,28 +1310,28 @@
     <t xml:space="preserve">7.94605112075806</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45955848693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70757436752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87927865982056</t>
+    <t xml:space="preserve">7.45955896377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70757484436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8792781829834</t>
   </si>
   <si>
     <t xml:space="preserve">7.99374723434448</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75527048110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81250476837158</t>
+    <t xml:space="preserve">7.75527000427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81250429153442</t>
   </si>
   <si>
     <t xml:space="preserve">7.79342699050903</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80296611785889</t>
+    <t xml:space="preserve">7.80296564102173</t>
   </si>
   <si>
     <t xml:space="preserve">7.85066032409668</t>
@@ -1340,13 +1340,13 @@
     <t xml:space="preserve">7.74573087692261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83158254623413</t>
+    <t xml:space="preserve">7.83158302307129</t>
   </si>
   <si>
     <t xml:space="preserve">7.66941833496094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60264492034912</t>
+    <t xml:space="preserve">7.60264444351196</t>
   </si>
   <si>
     <t xml:space="preserve">7.58356666564941</t>
@@ -1358,7 +1358,7 @@
     <t xml:space="preserve">8.00328636169434</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78388738632202</t>
+    <t xml:space="preserve">7.78388690948486</t>
   </si>
   <si>
     <t xml:space="preserve">7.3641676902771</t>
@@ -2271,6 +2271,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.57999992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47999954223633</t>
   </si>
 </sst>
 </file>
@@ -63267,7 +63270,7 @@
     </row>
     <row r="2334">
       <c r="A2334" s="1" t="n">
-        <v>46013.6911226852</v>
+        <v>46013.3333333333</v>
       </c>
       <c r="B2334" t="n">
         <v>8788</v>
@@ -63288,6 +63291,32 @@
         <v>752</v>
       </c>
       <c r="H2334" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2335">
+      <c r="A2335" s="1" t="n">
+        <v>46014.6911111111</v>
+      </c>
+      <c r="B2335" t="n">
+        <v>10780</v>
+      </c>
+      <c r="C2335" t="n">
+        <v>9.57999992370605</v>
+      </c>
+      <c r="D2335" t="n">
+        <v>9.46000003814697</v>
+      </c>
+      <c r="E2335" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="F2335" t="n">
+        <v>9.47999954223633</v>
+      </c>
+      <c r="G2335" t="s">
+        <v>753</v>
+      </c>
+      <c r="H2335" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07642269134521</t>
+    <t xml:space="preserve">9.0764217376709</t>
   </si>
   <si>
     <t xml:space="preserve">FF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98565673828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08549785614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24887371063232</t>
+    <t xml:space="preserve">8.98565769195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08549880981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24887275695801</t>
   </si>
   <si>
     <t xml:space="preserve">9.09457397460938</t>
@@ -62,43 +62,43 @@
     <t xml:space="preserve">9.03103923797607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95388984680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89943313598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89489459991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84951114654541</t>
+    <t xml:space="preserve">8.95389175415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89943218231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89489364624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84951210021973</t>
   </si>
   <si>
     <t xml:space="preserve">8.85858726501465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87674045562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76782417297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86766529083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04919242858887</t>
+    <t xml:space="preserve">8.87674140930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76782321929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8676643371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04919338226318</t>
   </si>
   <si>
     <t xml:space="preserve">9.23072147369385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11272716522217</t>
+    <t xml:space="preserve">9.11272811889648</t>
   </si>
   <si>
     <t xml:space="preserve">8.96750450134277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91304588317871</t>
+    <t xml:space="preserve">8.91304492950439</t>
   </si>
   <si>
     <t xml:space="preserve">8.92212295532227</t>
@@ -107,70 +107,70 @@
     <t xml:space="preserve">9.00381088256836</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15810775756836</t>
+    <t xml:space="preserve">9.15810871124268</t>
   </si>
   <si>
     <t xml:space="preserve">9.16718673706055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43947792053223</t>
+    <t xml:space="preserve">9.43947887420654</t>
   </si>
   <si>
     <t xml:space="preserve">9.54839611053467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62100791931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80253601074219</t>
+    <t xml:space="preserve">9.62100696563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80253505706787</t>
   </si>
   <si>
     <t xml:space="preserve">9.71177101135254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56654834747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58470153808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5756254196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53024387359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50301456451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60285472869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63915920257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79345893859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95683479309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93868255615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98406505584717</t>
+    <t xml:space="preserve">9.56654930114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58470249176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57562446594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53024291992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50301361083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60285377502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63916110992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79345989227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9568338394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93868350982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98406410217285</t>
   </si>
   <si>
     <t xml:space="preserve">9.73900127410889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7662296295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74807643890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75715351104736</t>
+    <t xml:space="preserve">9.76623058319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74807739257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75715255737305</t>
   </si>
   <si>
     <t xml:space="preserve">9.64823722839355</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">9.70269393920898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72084808349609</t>
+    <t xml:space="preserve">9.72084712982178</t>
   </si>
   <si>
     <t xml:space="preserve">9.67546558380127</t>
@@ -200,37 +200,37 @@
     <t xml:space="preserve">9.68454265594482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81161308288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8297643661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8479175567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83884239196777</t>
+    <t xml:space="preserve">9.81161212921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82976531982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84791851043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83884143829346</t>
   </si>
   <si>
     <t xml:space="preserve">9.72992420196533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78438186645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55747318267822</t>
+    <t xml:space="preserve">9.78438282012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55747127532959</t>
   </si>
   <si>
     <t xml:space="preserve">9.34871387481689</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33963775634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27610301971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25794982910156</t>
+    <t xml:space="preserve">9.33963871002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27610397338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25794887542725</t>
   </si>
   <si>
     <t xml:space="preserve">9.19441604614258</t>
@@ -242,19 +242,19 @@
     <t xml:space="preserve">9.4122486114502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22164344787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31240844726562</t>
+    <t xml:space="preserve">9.22164535522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31240940093994</t>
   </si>
   <si>
     <t xml:space="preserve">9.26702690124512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29425621032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28517913818359</t>
+    <t xml:space="preserve">9.29425525665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28518009185791</t>
   </si>
   <si>
     <t xml:space="preserve">9.37594413757324</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">9.39409732818604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48486137390137</t>
+    <t xml:space="preserve">9.48486232757568</t>
   </si>
   <si>
     <t xml:space="preserve">9.49393653869629</t>
@@ -287,34 +287,34 @@
     <t xml:space="preserve">9.23979663848877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14903450012207</t>
+    <t xml:space="preserve">9.14903259277344</t>
   </si>
   <si>
     <t xml:space="preserve">9.21256828308105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20349216461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13087940216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13995742797852</t>
+    <t xml:space="preserve">9.2034912109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13088226318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1399564743042</t>
   </si>
   <si>
     <t xml:space="preserve">8.94027614593506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8041296005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75874614715576</t>
+    <t xml:space="preserve">8.80412864685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75874710083008</t>
   </si>
   <si>
     <t xml:space="preserve">8.66798305511475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62260246276855</t>
+    <t xml:space="preserve">8.62260055541992</t>
   </si>
   <si>
     <t xml:space="preserve">8.53183650970459</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">8.35030746459961</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16878032684326</t>
+    <t xml:space="preserve">8.16877937316895</t>
   </si>
   <si>
     <t xml:space="preserve">7.98725128173828</t>
@@ -332,10 +332,10 @@
     <t xml:space="preserve">8.03263378143311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12339687347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25954627990723</t>
+    <t xml:space="preserve">8.12339782714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25954437255859</t>
   </si>
   <si>
     <t xml:space="preserve">7.94186878204346</t>
@@ -344,40 +344,40 @@
     <t xml:space="preserve">8.3049259185791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21416187286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39568901062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57721900939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71336555480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53202247619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34871482849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25706195831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44036769866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16540718078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07375144958496</t>
+    <t xml:space="preserve">8.21416282653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39568996429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5772180557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71336460113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53202342987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34871292114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25706100463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44036865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16540622711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07375240325928</t>
   </si>
   <si>
     <t xml:space="preserve">9.11957931518555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98209953308105</t>
+    <t xml:space="preserve">8.98209857940674</t>
   </si>
   <si>
     <t xml:space="preserve">9.02792549133301</t>
@@ -389,40 +389,40 @@
     <t xml:space="preserve">9.80698490142822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89863967895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9902925491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1736011505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2652549743652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3569107055664</t>
+    <t xml:space="preserve">9.89863777160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99029350280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.173602104187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2652559280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3569078445435</t>
   </si>
   <si>
     <t xml:space="preserve">10.5402183532715</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6318731307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8151788711548</t>
+    <t xml:space="preserve">10.631872177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8151798248291</t>
   </si>
   <si>
     <t xml:space="preserve">10.7235260009766</t>
   </si>
   <si>
-    <t xml:space="preserve">10.906834602356</t>
+    <t xml:space="preserve">10.9068326950073</t>
   </si>
   <si>
     <t xml:space="preserve">10.9984884262085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0901432037354</t>
+    <t xml:space="preserve">11.090142250061</t>
   </si>
   <si>
     <t xml:space="preserve">11.1817960739136</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">11.4567584991455</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3651037216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4485635757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71533203125</t>
+    <t xml:space="preserve">11.3651027679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4485626220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71533107757568</t>
   </si>
   <si>
     <t xml:space="preserve">8.79879093170166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24886703491211</t>
+    <t xml:space="preserve">8.24886608123779</t>
   </si>
   <si>
     <t xml:space="preserve">9.2112340927124</t>
@@ -455,31 +455,31 @@
     <t xml:space="preserve">9.30288791656494</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03708934783936</t>
+    <t xml:space="preserve">9.03709030151367</t>
   </si>
   <si>
     <t xml:space="preserve">9.39454174041748</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76115703582764</t>
+    <t xml:space="preserve">9.76115798950195</t>
   </si>
   <si>
     <t xml:space="preserve">9.66950416564941</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57785034179688</t>
+    <t xml:space="preserve">9.57785129547119</t>
   </si>
   <si>
     <t xml:space="preserve">10.0361213684082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94446563720703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82552528381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73283100128174</t>
+    <t xml:space="preserve">9.94446659088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82552433013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73283004760742</t>
   </si>
   <si>
     <t xml:space="preserve">9.59379005432129</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">9.96456432342529</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91821670532227</t>
+    <t xml:space="preserve">9.91821765899658</t>
   </si>
   <si>
     <t xml:space="preserve">9.54744243621826</t>
@@ -500,7 +500,7 @@
     <t xml:space="preserve">10.1036052703857</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1499519348145</t>
+    <t xml:space="preserve">10.1499528884888</t>
   </si>
   <si>
     <t xml:space="preserve">10.1962985992432</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">9.77917766571045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87187004089355</t>
+    <t xml:space="preserve">9.87187099456787</t>
   </si>
   <si>
     <t xml:space="preserve">10.057258605957</t>
@@ -518,22 +518,22 @@
     <t xml:space="preserve">10.2889928817749</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4743795394897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2426452636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.381685256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68648338317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64013576507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50109672546387</t>
+    <t xml:space="preserve">10.4743785858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2426462173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3816862106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68648433685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64013671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50109577178955</t>
   </si>
   <si>
     <t xml:space="preserve">9.31570911407471</t>
@@ -545,31 +545,31 @@
     <t xml:space="preserve">9.1952075958252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25082302093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.269362449646</t>
+    <t xml:space="preserve">9.25082206726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26936149597168</t>
   </si>
   <si>
     <t xml:space="preserve">9.21374607086182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04689693450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12105369567871</t>
+    <t xml:space="preserve">9.04689788818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12105274200439</t>
   </si>
   <si>
     <t xml:space="preserve">9.06543636322021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97274303436279</t>
+    <t xml:space="preserve">8.97274208068848</t>
   </si>
   <si>
     <t xml:space="preserve">9.17666816711426</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02835941314697</t>
+    <t xml:space="preserve">9.02835845947266</t>
   </si>
   <si>
     <t xml:space="preserve">8.95420360565186</t>
@@ -578,31 +578,31 @@
     <t xml:space="preserve">8.71320056915283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99128150939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7688159942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89858913421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93566608428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3353385925293</t>
+    <t xml:space="preserve">8.9912805557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76881694793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89858818054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93566513061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3353395462036</t>
   </si>
   <si>
     <t xml:space="preserve">10.9841938018799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0305414199829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2159290313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4940099716187</t>
+    <t xml:space="preserve">11.0305404663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2159280776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.49400806427</t>
   </si>
   <si>
     <t xml:space="preserve">11.540355682373</t>
@@ -611,37 +611,37 @@
     <t xml:space="preserve">11.5867033004761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6330490112305</t>
+    <t xml:space="preserve">11.6330499649048</t>
   </si>
   <si>
     <t xml:space="preserve">11.7257423400879</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9111309051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9574775695801</t>
+    <t xml:space="preserve">11.9111299514771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9574766159058</t>
   </si>
   <si>
     <t xml:space="preserve">12.1892108917236</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2819042205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3745985031128</t>
+    <t xml:space="preserve">12.2819051742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3745994567871</t>
   </si>
   <si>
     <t xml:space="preserve">12.5136394500732</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3282518386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1428651809692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0965175628662</t>
+    <t xml:space="preserve">12.3282527923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1428661346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0965185165405</t>
   </si>
   <si>
     <t xml:space="preserve">12.555121421814</t>
@@ -653,10 +653,10 @@
     <t xml:space="preserve">12.6488170623779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4614267349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4145784378052</t>
+    <t xml:space="preserve">12.4614276885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4145793914795</t>
   </si>
   <si>
     <t xml:space="preserve">12.7425127029419</t>
@@ -674,22 +674,22 @@
     <t xml:space="preserve">12.3208837509155</t>
   </si>
   <si>
-    <t xml:space="preserve">12.274037361145</t>
+    <t xml:space="preserve">12.2740383148193</t>
   </si>
   <si>
     <t xml:space="preserve">12.8362064361572</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7893590927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6019687652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9299011230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8830528259277</t>
+    <t xml:space="preserve">12.7893581390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6019697189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9299020767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8830537796021</t>
   </si>
   <si>
     <t xml:space="preserve">13.0704441070557</t>
@@ -698,22 +698,22 @@
     <t xml:space="preserve">13.679461479187</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8668518066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0542411804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3353261947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5695629119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2254276275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1317319869995</t>
+    <t xml:space="preserve">13.8668508529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0542402267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3353252410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5695638656616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2254285812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1317329406738</t>
   </si>
   <si>
     <t xml:space="preserve">14.7569532394409</t>
@@ -722,52 +722,52 @@
     <t xml:space="preserve">15.0380373001099</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1785802841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3191242218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8974952697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4596643447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4128179550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5533609390259</t>
+    <t xml:space="preserve">15.178581237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3191232681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8974943161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4596662521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4128189086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5533599853516</t>
   </si>
   <si>
     <t xml:space="preserve">16.0686817169189</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8650913238525</t>
+    <t xml:space="preserve">16.8650894165039</t>
   </si>
   <si>
     <t xml:space="preserve">17.0056324005127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7713928222656</t>
+    <t xml:space="preserve">16.7713947296143</t>
   </si>
   <si>
     <t xml:space="preserve">17.193021774292</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0524806976318</t>
+    <t xml:space="preserve">17.0524787902832</t>
   </si>
   <si>
     <t xml:space="preserve">16.9587860107422</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7245445251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6308498382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5371570587158</t>
+    <t xml:space="preserve">16.7245483398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6308536529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5371551513672</t>
   </si>
   <si>
     <t xml:space="preserve">16.584005355835</t>
@@ -779,13 +779,13 @@
     <t xml:space="preserve">16.2560729980469</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1461734771729</t>
+    <t xml:space="preserve">17.1461715698242</t>
   </si>
   <si>
     <t xml:space="preserve">16.396614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3029193878174</t>
+    <t xml:space="preserve">16.3029174804688</t>
   </si>
   <si>
     <t xml:space="preserve">15.8344440460205</t>
@@ -794,43 +794,43 @@
     <t xml:space="preserve">16.1155300140381</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0218372344971</t>
+    <t xml:space="preserve">16.0218353271484</t>
   </si>
   <si>
     <t xml:space="preserve">16.1623764038086</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9749870300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7407493591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4434623718262</t>
+    <t xml:space="preserve">15.974986076355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7407484054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4434604644775</t>
   </si>
   <si>
     <t xml:space="preserve">16.9119358062744</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0993270874023</t>
+    <t xml:space="preserve">17.0993251800537</t>
   </si>
   <si>
     <t xml:space="preserve">16.677698135376</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8182430267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2722749710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0848846435547</t>
+    <t xml:space="preserve">16.818244934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.272274017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.084885597229</t>
   </si>
   <si>
     <t xml:space="preserve">14.9911909103394</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8038005828857</t>
+    <t xml:space="preserve">14.8037996292114</t>
   </si>
   <si>
     <t xml:space="preserve">14.4758682250977</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">14.1010885238647</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2884769439697</t>
+    <t xml:space="preserve">14.288477897644</t>
   </si>
   <si>
     <t xml:space="preserve">14.5227155685425</t>
@@ -851,28 +851,28 @@
     <t xml:space="preserve">13.960545539856</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2416296005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1947822570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0073928833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7263069152832</t>
+    <t xml:space="preserve">14.2416305541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1947832107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0073938369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7263088226318</t>
   </si>
   <si>
     <t xml:space="preserve">14.1479358673096</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4290208816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6164102554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7731552124023</t>
+    <t xml:space="preserve">14.4290199279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6164112091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7731561660767</t>
   </si>
   <si>
     <t xml:space="preserve">13.3515281677246</t>
@@ -887,7 +887,7 @@
     <t xml:space="preserve">13.0235967636108</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1172914505005</t>
+    <t xml:space="preserve">13.1172924041748</t>
   </si>
   <si>
     <t xml:space="preserve">12.976749420166</t>
@@ -896,16 +896,16 @@
     <t xml:space="preserve">12.3677320480347</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0866470336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9929513931274</t>
+    <t xml:space="preserve">12.0866460800171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9929523468018</t>
   </si>
   <si>
     <t xml:space="preserve">11.8992576599121</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0397996902466</t>
+    <t xml:space="preserve">12.0397987365723</t>
   </si>
   <si>
     <t xml:space="preserve">12.1334943771362</t>
@@ -914,10 +914,10 @@
     <t xml:space="preserve">11.4776296615601</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2433929443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3839349746704</t>
+    <t xml:space="preserve">11.2433938980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3839340209961</t>
   </si>
   <si>
     <t xml:space="preserve">11.6650199890137</t>
@@ -929,25 +929,25 @@
     <t xml:space="preserve">10.9623079299927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7280702590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1965446472168</t>
+    <t xml:space="preserve">10.7280712127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1965456008911</t>
   </si>
   <si>
     <t xml:space="preserve">11.5713243484497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3370885848999</t>
+    <t xml:space="preserve">11.3370876312256</t>
   </si>
   <si>
     <t xml:space="preserve">11.2902402877808</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7118673324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7587146759033</t>
+    <t xml:space="preserve">11.7118682861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7587156295776</t>
   </si>
   <si>
     <t xml:space="preserve">11.8055629730225</t>
@@ -962,16 +962,16 @@
     <t xml:space="preserve">8.33884906768799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57308673858643</t>
+    <t xml:space="preserve">8.57308578491211</t>
   </si>
   <si>
     <t xml:space="preserve">8.31074142456055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45128440856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61993408203125</t>
+    <t xml:space="preserve">8.45128345489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61993312835693</t>
   </si>
   <si>
     <t xml:space="preserve">8.44191455841064</t>
@@ -980,25 +980,25 @@
     <t xml:space="preserve">8.32948112487793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25452423095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43254566192627</t>
+    <t xml:space="preserve">8.25452327728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43254470825195</t>
   </si>
   <si>
     <t xml:space="preserve">8.47002220153809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32011032104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20767688751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0858736038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78605031967163</t>
+    <t xml:space="preserve">8.32011127471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20767784118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08587265014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78604936599731</t>
   </si>
   <si>
     <t xml:space="preserve">7.49559545516968</t>
@@ -1013,7 +1013,7 @@
     <t xml:space="preserve">7.83289623260498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90785264968872</t>
+    <t xml:space="preserve">7.90785312652588</t>
   </si>
   <si>
     <t xml:space="preserve">7.50496482849121</t>
@@ -1022,28 +1022,28 @@
     <t xml:space="preserve">7.37379169464111</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12081480026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28009653091431</t>
+    <t xml:space="preserve">7.12081527709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28009700775146</t>
   </si>
   <si>
     <t xml:space="preserve">6.98027276992798</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93342590332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06459808349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02712059020996</t>
+    <t xml:space="preserve">6.93342542648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06459856033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0271201133728</t>
   </si>
   <si>
     <t xml:space="preserve">7.34568309783936</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54244232177734</t>
+    <t xml:space="preserve">7.5424427986145</t>
   </si>
   <si>
     <t xml:space="preserve">8.19830703735352</t>
@@ -1058,19 +1058,19 @@
     <t xml:space="preserve">8.46116256713867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53747367858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68056201934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77595138549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84272575378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825622558594</t>
+    <t xml:space="preserve">8.53747463226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68056106567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77595233917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8427267074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825527191162</t>
   </si>
   <si>
     <t xml:space="preserve">8.66148281097412</t>
@@ -1085,10 +1085,10 @@
     <t xml:space="preserve">8.39438915252686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60424900054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48977851867676</t>
+    <t xml:space="preserve">8.604248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48977947235107</t>
   </si>
   <si>
     <t xml:space="preserve">8.29899787902832</t>
@@ -1100,7 +1100,7 @@
     <t xml:space="preserve">7.89835643768311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10821723937988</t>
+    <t xml:space="preserve">8.10821628570557</t>
   </si>
   <si>
     <t xml:space="preserve">7.84112215042114</t>
@@ -1118,34 +1118,34 @@
     <t xml:space="preserve">8.07959938049316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07005977630615</t>
+    <t xml:space="preserve">8.07005882263184</t>
   </si>
   <si>
     <t xml:space="preserve">7.92697429656982</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98420810699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30853748321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26084041595459</t>
+    <t xml:space="preserve">7.98420858383179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30853652954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26084136962891</t>
   </si>
   <si>
     <t xml:space="preserve">8.27038097381592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18452930450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03190422058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96512985229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86020040512085</t>
+    <t xml:space="preserve">8.18452835083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03190326690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96513080596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86019992828369</t>
   </si>
   <si>
     <t xml:space="preserve">7.86973905563354</t>
@@ -1157,7 +1157,7 @@
     <t xml:space="preserve">7.91743516921997</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76480960845947</t>
+    <t xml:space="preserve">7.76481008529663</t>
   </si>
   <si>
     <t xml:space="preserve">7.72665309906006</t>
@@ -1169,19 +1169,19 @@
     <t xml:space="preserve">7.63126230239868</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65987920761108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16545009613037</t>
+    <t xml:space="preserve">7.65987968444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16545104980469</t>
   </si>
   <si>
     <t xml:space="preserve">8.32761383056641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11775493621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9365119934082</t>
+    <t xml:space="preserve">8.11775588989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93651247024536</t>
   </si>
   <si>
     <t xml:space="preserve">8.19406795501709</t>
@@ -1190,10 +1190,10 @@
     <t xml:space="preserve">8.2322244644165</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31807613372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15591239929199</t>
+    <t xml:space="preserve">8.31807518005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15591144561768</t>
   </si>
   <si>
     <t xml:space="preserve">8.22268486022949</t>
@@ -1202,10 +1202,10 @@
     <t xml:space="preserve">8.25130176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35623264312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2417631149292</t>
+    <t xml:space="preserve">8.35623168945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24176406860352</t>
   </si>
   <si>
     <t xml:space="preserve">8.34669303894043</t>
@@ -1223,7 +1223,7 @@
     <t xml:space="preserve">7.97466850280762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01282501220703</t>
+    <t xml:space="preserve">8.01282596588135</t>
   </si>
   <si>
     <t xml:space="preserve">8.05098152160645</t>
@@ -1232,13 +1232,13 @@
     <t xml:space="preserve">7.67895746231079</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73619222640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6980357170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5167932510376</t>
+    <t xml:space="preserve">7.73619174957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69803524017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51679372787476</t>
   </si>
   <si>
     <t xml:space="preserve">7.59310626983643</t>
@@ -1262,16 +1262,16 @@
     <t xml:space="preserve">7.20200395584106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18292617797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14476919174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12569093704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23062086105347</t>
+    <t xml:space="preserve">7.18292570114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14476871490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12569046020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23062133789062</t>
   </si>
   <si>
     <t xml:space="preserve">7.1543083190918</t>
@@ -1280,7 +1280,7 @@
     <t xml:space="preserve">7.24969863891602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24015998840332</t>
+    <t xml:space="preserve">7.24016046524048</t>
   </si>
   <si>
     <t xml:space="preserve">7.46909809112549</t>
@@ -1301,13 +1301,13 @@
     <t xml:space="preserve">7.3355507850647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61218452453613</t>
+    <t xml:space="preserve">7.61218404769897</t>
   </si>
   <si>
     <t xml:space="preserve">7.90789556503296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94605112075806</t>
+    <t xml:space="preserve">7.94605159759521</t>
   </si>
   <si>
     <t xml:space="preserve">7.45955896377563</t>
@@ -1319,22 +1319,22 @@
     <t xml:space="preserve">7.8792781829834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99374723434448</t>
+    <t xml:space="preserve">7.99374771118164</t>
   </si>
   <si>
     <t xml:space="preserve">7.75527000427246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81250429153442</t>
+    <t xml:space="preserve">7.81250381469727</t>
   </si>
   <si>
     <t xml:space="preserve">7.79342699050903</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80296564102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85066032409668</t>
+    <t xml:space="preserve">7.80296611785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85065984725952</t>
   </si>
   <si>
     <t xml:space="preserve">7.74573087692261</t>
@@ -1343,22 +1343,22 @@
     <t xml:space="preserve">7.83158302307129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66941833496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60264444351196</t>
+    <t xml:space="preserve">7.66941785812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60264492034912</t>
   </si>
   <si>
     <t xml:space="preserve">7.58356666564941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88881778717041</t>
+    <t xml:space="preserve">7.88881826400757</t>
   </si>
   <si>
     <t xml:space="preserve">8.00328636169434</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78388690948486</t>
+    <t xml:space="preserve">7.78388738632202</t>
   </si>
   <si>
     <t xml:space="preserve">7.3641676902771</t>
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">7.27831649780273</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08753442764282</t>
+    <t xml:space="preserve">7.08753490447998</t>
   </si>
   <si>
     <t xml:space="preserve">7.05891799926758</t>
@@ -1379,10 +1379,10 @@
     <t xml:space="preserve">7.50372648239136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98721361160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02589321136475</t>
+    <t xml:space="preserve">7.98721408843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02589225769043</t>
   </si>
   <si>
     <t xml:space="preserve">8.04523086547852</t>
@@ -1394,25 +1394,25 @@
     <t xml:space="preserve">8.07424163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12259006500244</t>
+    <t xml:space="preserve">8.12258911132812</t>
   </si>
   <si>
     <t xml:space="preserve">8.05490112304688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94853448867798</t>
+    <t xml:space="preserve">7.94853496551514</t>
   </si>
   <si>
     <t xml:space="preserve">8.06457138061523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08391094207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97754383087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93886423110962</t>
+    <t xml:space="preserve">8.08390998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97754430770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93886518478394</t>
   </si>
   <si>
     <t xml:space="preserve">7.79381895065308</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">7.68745088577271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63910245895386</t>
+    <t xml:space="preserve">7.63910293579102</t>
   </si>
   <si>
     <t xml:space="preserve">7.73579978942871</t>
@@ -1439,10 +1439,10 @@
     <t xml:space="preserve">7.90985584259033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85183715820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83249807357788</t>
+    <t xml:space="preserve">7.85183668136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83249759674072</t>
   </si>
   <si>
     <t xml:space="preserve">7.81315755844116</t>
@@ -1451,7 +1451,7 @@
     <t xml:space="preserve">7.80348825454712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78414869308472</t>
+    <t xml:space="preserve">7.78414916992188</t>
   </si>
   <si>
     <t xml:space="preserve">7.6681113243103</t>
@@ -1463,13 +1463,13 @@
     <t xml:space="preserve">7.71646022796631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75514030456543</t>
+    <t xml:space="preserve">7.75513982772827</t>
   </si>
   <si>
     <t xml:space="preserve">7.74547004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86150646209717</t>
+    <t xml:space="preserve">7.86150693893433</t>
   </si>
   <si>
     <t xml:space="preserve">7.89051580429077</t>
@@ -1487,10 +1487,10 @@
     <t xml:space="preserve">8.09358024597168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1322603225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15159893035889</t>
+    <t xml:space="preserve">8.13225936889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1515998840332</t>
   </si>
   <si>
     <t xml:space="preserve">8.1129207611084</t>
@@ -1499,10 +1499,10 @@
     <t xml:space="preserve">8.03556251525879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92919540405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69712114334106</t>
+    <t xml:space="preserve">7.92919492721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69712066650391</t>
   </si>
   <si>
     <t xml:space="preserve">7.60042381286621</t>
@@ -1511,10 +1511,10 @@
     <t xml:space="preserve">7.88084602355957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55207490921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40702867507935</t>
+    <t xml:space="preserve">7.55207443237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40702819824219</t>
   </si>
   <si>
     <t xml:space="preserve">7.34900999069214</t>
@@ -1523,16 +1523,16 @@
     <t xml:space="preserve">7.37801933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43603801727295</t>
+    <t xml:space="preserve">7.43603754043579</t>
   </si>
   <si>
     <t xml:space="preserve">7.41669797897339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5230655670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36834907531738</t>
+    <t xml:space="preserve">7.52306604385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36834955215454</t>
   </si>
   <si>
     <t xml:space="preserve">7.542405128479</t>
@@ -1541,7 +1541,7 @@
     <t xml:space="preserve">7.4843864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70679092407227</t>
+    <t xml:space="preserve">7.70679044723511</t>
   </si>
   <si>
     <t xml:space="preserve">7.64877223968506</t>
@@ -1559,10 +1559,10 @@
     <t xml:space="preserve">7.59075355529785</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95820331573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96787357330322</t>
+    <t xml:space="preserve">7.95820426940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96787405014038</t>
   </si>
   <si>
     <t xml:space="preserve">7.90018606185913</t>
@@ -1580,10 +1580,10 @@
     <t xml:space="preserve">8.19027900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29664516448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45136070251465</t>
+    <t xml:space="preserve">8.29664611816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45136165618896</t>
   </si>
   <si>
     <t xml:space="preserve">8.48037147521973</t>
@@ -1610,19 +1610,19 @@
     <t xml:space="preserve">8.50938034057617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42235279083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54805850982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55772876739502</t>
+    <t xml:space="preserve">8.4223518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54805946350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55772972106934</t>
   </si>
   <si>
     <t xml:space="preserve">8.52871990203857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68343544006348</t>
+    <t xml:space="preserve">8.68343448638916</t>
   </si>
   <si>
     <t xml:space="preserve">8.76079368591309</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">8.65442562103271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75112342834473</t>
+    <t xml:space="preserve">8.75112438201904</t>
   </si>
   <si>
     <t xml:space="preserve">8.70277500152588</t>
@@ -1655,10 +1655,10 @@
     <t xml:space="preserve">8.63508701324463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32565498352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31598567962646</t>
+    <t xml:space="preserve">8.32565402984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31598472595215</t>
   </si>
   <si>
     <t xml:space="preserve">8.30631542205811</t>
@@ -63296,7 +63296,7 @@
     </row>
     <row r="2335">
       <c r="A2335" s="1" t="n">
-        <v>46014.6911111111</v>
+        <v>46014.3333333333</v>
       </c>
       <c r="B2335" t="n">
         <v>10780</v>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -44,25 +44,25 @@
     <t xml:space="preserve">FF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98565769195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08549880981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24887275695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09457397460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12180423736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03103923797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95389175415039</t>
+    <t xml:space="preserve">8.98565673828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08549785614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24887371063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09457588195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12180519104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03103828430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95388984680176</t>
   </si>
   <si>
     <t xml:space="preserve">8.89943218231201</t>
@@ -71,13 +71,13 @@
     <t xml:space="preserve">8.89489364624023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84951210021973</t>
+    <t xml:space="preserve">8.84951114654541</t>
   </si>
   <si>
     <t xml:space="preserve">8.85858726501465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87674140930176</t>
+    <t xml:space="preserve">8.87674045562744</t>
   </si>
   <si>
     <t xml:space="preserve">8.76782321929932</t>
@@ -86,16 +86,16 @@
     <t xml:space="preserve">8.8676643371582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04919338226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23072147369385</t>
+    <t xml:space="preserve">9.04919242858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23072052001953</t>
   </si>
   <si>
     <t xml:space="preserve">9.11272811889648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96750450134277</t>
+    <t xml:space="preserve">8.96750545501709</t>
   </si>
   <si>
     <t xml:space="preserve">8.91304492950439</t>
@@ -107,13 +107,13 @@
     <t xml:space="preserve">9.00381088256836</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15810871124268</t>
+    <t xml:space="preserve">9.15810966491699</t>
   </si>
   <si>
     <t xml:space="preserve">9.16718673706055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43947887420654</t>
+    <t xml:space="preserve">9.43947792053223</t>
   </si>
   <si>
     <t xml:space="preserve">9.54839611053467</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">9.62100696563721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80253505706787</t>
+    <t xml:space="preserve">9.80253601074219</t>
   </si>
   <si>
     <t xml:space="preserve">9.71177101135254</t>
@@ -131,55 +131,55 @@
     <t xml:space="preserve">9.56654930114746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58470249176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57562446594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53024291992188</t>
+    <t xml:space="preserve">9.58470153808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5756254196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53024387359619</t>
   </si>
   <si>
     <t xml:space="preserve">9.50301361083984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60285377502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63916110992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79345989227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9568338394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93868350982666</t>
+    <t xml:space="preserve">9.60285472869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63915920257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79345893859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95683479309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93868255615234</t>
   </si>
   <si>
     <t xml:space="preserve">9.98406410217285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73900127410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76623058319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74807739257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75715255737305</t>
+    <t xml:space="preserve">9.73900032043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7662296295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74807643890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75715446472168</t>
   </si>
   <si>
     <t xml:space="preserve">9.64823722839355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82068729400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70269393920898</t>
+    <t xml:space="preserve">9.82068920135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7026948928833</t>
   </si>
   <si>
     <t xml:space="preserve">9.72084712982178</t>
@@ -191,16 +191,16 @@
     <t xml:space="preserve">9.66638851165771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63008403778076</t>
+    <t xml:space="preserve">9.63008308410645</t>
   </si>
   <si>
     <t xml:space="preserve">9.65731334686279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68454265594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81161212921143</t>
+    <t xml:space="preserve">9.68454074859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81161308288574</t>
   </si>
   <si>
     <t xml:space="preserve">9.82976531982422</t>
@@ -215,52 +215,52 @@
     <t xml:space="preserve">9.72992420196533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78438282012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55747127532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34871387481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33963871002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27610397338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25794887542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19441604614258</t>
+    <t xml:space="preserve">9.78438186645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55747222900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34871482849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33963775634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27610206604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25795078277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19441413879395</t>
   </si>
   <si>
     <t xml:space="preserve">9.18533897399902</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4122486114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22164535522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31240940093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26702690124512</t>
+    <t xml:space="preserve">9.41224956512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22164344787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31240844726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2670259475708</t>
   </si>
   <si>
     <t xml:space="preserve">9.29425525665283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28518009185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37594413757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36686706542969</t>
+    <t xml:space="preserve">9.28517913818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37594318389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36686611175537</t>
   </si>
   <si>
     <t xml:space="preserve">9.38502025604248</t>
@@ -275,19 +275,19 @@
     <t xml:space="preserve">9.48486232757568</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49393653869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44855499267578</t>
+    <t xml:space="preserve">9.49393749237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44855403900146</t>
   </si>
   <si>
     <t xml:space="preserve">9.47578430175781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23979663848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14903259277344</t>
+    <t xml:space="preserve">9.2397985458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14903450012207</t>
   </si>
   <si>
     <t xml:space="preserve">9.21256828308105</t>
@@ -296,7 +296,7 @@
     <t xml:space="preserve">9.2034912109375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13088226318359</t>
+    <t xml:space="preserve">9.13088130950928</t>
   </si>
   <si>
     <t xml:space="preserve">9.1399564743042</t>
@@ -305,34 +305,34 @@
     <t xml:space="preserve">8.94027614593506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80412864685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75874710083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66798305511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62260055541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53183650970459</t>
+    <t xml:space="preserve">8.80412769317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75874614715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66798210144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62259960174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53183555603027</t>
   </si>
   <si>
     <t xml:space="preserve">8.35030746459961</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16877937316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98725128173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03263378143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12339782714844</t>
+    <t xml:space="preserve">8.16878032684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98725032806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03263187408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12339687347412</t>
   </si>
   <si>
     <t xml:space="preserve">8.25954437255859</t>
@@ -344,25 +344,25 @@
     <t xml:space="preserve">8.3049259185791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21416282653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39568996429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5772180557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71336460113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53202342987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34871292114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25706100463867</t>
+    <t xml:space="preserve">8.21416187286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39568901062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57721900939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71336555480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53202247619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34871578216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25706195831299</t>
   </si>
   <si>
     <t xml:space="preserve">9.44036865234375</t>
@@ -371,13 +371,13 @@
     <t xml:space="preserve">9.16540622711182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07375240325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11957931518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98209857940674</t>
+    <t xml:space="preserve">9.07375144958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11957836151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98209953308105</t>
   </si>
   <si>
     <t xml:space="preserve">9.02792549133301</t>
@@ -389,22 +389,22 @@
     <t xml:space="preserve">9.80698490142822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89863777160645</t>
+    <t xml:space="preserve">9.89863967895508</t>
   </si>
   <si>
     <t xml:space="preserve">9.99029350280762</t>
   </si>
   <si>
-    <t xml:space="preserve">10.173602104187</t>
+    <t xml:space="preserve">10.1736011505127</t>
   </si>
   <si>
     <t xml:space="preserve">10.2652559280396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3569078445435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5402183532715</t>
+    <t xml:space="preserve">10.3569097518921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5402173995972</t>
   </si>
   <si>
     <t xml:space="preserve">10.631872177124</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">10.7235260009766</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9068326950073</t>
+    <t xml:space="preserve">10.9068336486816</t>
   </si>
   <si>
     <t xml:space="preserve">10.9984884262085</t>
@@ -425,13 +425,13 @@
     <t xml:space="preserve">11.090142250061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1817960739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2734508514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4567584991455</t>
+    <t xml:space="preserve">11.1817951202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2734498977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4567575454712</t>
   </si>
   <si>
     <t xml:space="preserve">11.3651027679443</t>
@@ -455,43 +455,43 @@
     <t xml:space="preserve">9.30288791656494</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03709030151367</t>
+    <t xml:space="preserve">9.03709125518799</t>
   </si>
   <si>
     <t xml:space="preserve">9.39454174041748</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76115798950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66950416564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57785129547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0361213684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94446659088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82552433013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73283004760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59379005432129</t>
+    <t xml:space="preserve">9.76115703582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66950511932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57785034179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0361204147339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94446563720703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82552528381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73283100128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59379100799561</t>
   </si>
   <si>
     <t xml:space="preserve">9.96456432342529</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91821765899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54744243621826</t>
+    <t xml:space="preserve">9.91821670532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54744338989258</t>
   </si>
   <si>
     <t xml:space="preserve">10.010910987854</t>
@@ -500,7 +500,7 @@
     <t xml:space="preserve">10.1036052703857</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1499528884888</t>
+    <t xml:space="preserve">10.1499519348145</t>
   </si>
   <si>
     <t xml:space="preserve">10.1962985992432</t>
@@ -521,19 +521,19 @@
     <t xml:space="preserve">10.4743785858154</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2426462173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3816862106323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68648433685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64013671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50109577178955</t>
+    <t xml:space="preserve">10.2426452636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.381685256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68648338317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64013576507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50109672546387</t>
   </si>
   <si>
     <t xml:space="preserve">9.31570911407471</t>
@@ -545,16 +545,16 @@
     <t xml:space="preserve">9.1952075958252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25082206726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26936149597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21374607086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04689788818359</t>
+    <t xml:space="preserve">9.25082302093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26936340332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2137451171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04689693450928</t>
   </si>
   <si>
     <t xml:space="preserve">9.12105274200439</t>
@@ -563,13 +563,13 @@
     <t xml:space="preserve">9.06543636322021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97274208068848</t>
+    <t xml:space="preserve">8.97274303436279</t>
   </si>
   <si>
     <t xml:space="preserve">9.17666816711426</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02835845947266</t>
+    <t xml:space="preserve">9.02835941314697</t>
   </si>
   <si>
     <t xml:space="preserve">8.95420360565186</t>
@@ -578,31 +578,31 @@
     <t xml:space="preserve">8.71320056915283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9912805557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76881694793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89858818054199</t>
+    <t xml:space="preserve">8.99128150939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7688159942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89858913421631</t>
   </si>
   <si>
     <t xml:space="preserve">8.93566513061523</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3353395462036</t>
+    <t xml:space="preserve">10.3353385925293</t>
   </si>
   <si>
     <t xml:space="preserve">10.9841938018799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0305404663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2159280776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.49400806427</t>
+    <t xml:space="preserve">11.0305414199829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2159290313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4940099716187</t>
   </si>
   <si>
     <t xml:space="preserve">11.540355682373</t>
@@ -611,34 +611,34 @@
     <t xml:space="preserve">11.5867033004761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6330499649048</t>
+    <t xml:space="preserve">11.6330490112305</t>
   </si>
   <si>
     <t xml:space="preserve">11.7257423400879</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9111299514771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9574766159058</t>
+    <t xml:space="preserve">11.9111309051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9574775695801</t>
   </si>
   <si>
     <t xml:space="preserve">12.1892108917236</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2819051742554</t>
+    <t xml:space="preserve">12.2819042205811</t>
   </si>
   <si>
     <t xml:space="preserve">12.3745994567871</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5136394500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3282527923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1428661346436</t>
+    <t xml:space="preserve">12.5136384963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3282518386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1428642272949</t>
   </si>
   <si>
     <t xml:space="preserve">12.0965185165405</t>
@@ -653,10 +653,10 @@
     <t xml:space="preserve">12.6488170623779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4614276885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4145793914795</t>
+    <t xml:space="preserve">12.4614267349243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4145784378052</t>
   </si>
   <si>
     <t xml:space="preserve">12.7425127029419</t>
@@ -674,22 +674,22 @@
     <t xml:space="preserve">12.3208837509155</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2740383148193</t>
+    <t xml:space="preserve">12.274037361145</t>
   </si>
   <si>
     <t xml:space="preserve">12.8362064361572</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7893581390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6019697189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9299020767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8830537796021</t>
+    <t xml:space="preserve">12.7893590927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6019687652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9299011230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8830528259277</t>
   </si>
   <si>
     <t xml:space="preserve">13.0704441070557</t>
@@ -698,22 +698,22 @@
     <t xml:space="preserve">13.679461479187</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8668508529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0542402267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3353252410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5695638656616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2254285812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1317329406738</t>
+    <t xml:space="preserve">13.8668518066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0542411804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3353261947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5695629119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2254276275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1317319869995</t>
   </si>
   <si>
     <t xml:space="preserve">14.7569532394409</t>
@@ -722,52 +722,52 @@
     <t xml:space="preserve">15.0380373001099</t>
   </si>
   <si>
-    <t xml:space="preserve">15.178581237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3191232681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8974943161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4596662521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4128189086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5533599853516</t>
+    <t xml:space="preserve">15.1785802841187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3191242218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8974952697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4596643447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4128179550171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5533609390259</t>
   </si>
   <si>
     <t xml:space="preserve">16.0686817169189</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8650894165039</t>
+    <t xml:space="preserve">16.8650913238525</t>
   </si>
   <si>
     <t xml:space="preserve">17.0056324005127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7713947296143</t>
+    <t xml:space="preserve">16.7713928222656</t>
   </si>
   <si>
     <t xml:space="preserve">17.193021774292</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0524787902832</t>
+    <t xml:space="preserve">17.0524806976318</t>
   </si>
   <si>
     <t xml:space="preserve">16.9587860107422</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7245483398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6308536529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5371551513672</t>
+    <t xml:space="preserve">16.7245445251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6308498382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5371570587158</t>
   </si>
   <si>
     <t xml:space="preserve">16.584005355835</t>
@@ -779,13 +779,13 @@
     <t xml:space="preserve">16.2560729980469</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1461715698242</t>
+    <t xml:space="preserve">17.1461734771729</t>
   </si>
   <si>
     <t xml:space="preserve">16.396614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3029174804688</t>
+    <t xml:space="preserve">16.3029193878174</t>
   </si>
   <si>
     <t xml:space="preserve">15.8344440460205</t>
@@ -794,43 +794,43 @@
     <t xml:space="preserve">16.1155300140381</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0218353271484</t>
+    <t xml:space="preserve">16.0218372344971</t>
   </si>
   <si>
     <t xml:space="preserve">16.1623764038086</t>
   </si>
   <si>
-    <t xml:space="preserve">15.974986076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7407484054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4434604644775</t>
+    <t xml:space="preserve">15.9749870300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7407493591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4434623718262</t>
   </si>
   <si>
     <t xml:space="preserve">16.9119358062744</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0993251800537</t>
+    <t xml:space="preserve">17.0993270874023</t>
   </si>
   <si>
     <t xml:space="preserve">16.677698135376</t>
   </si>
   <si>
-    <t xml:space="preserve">16.818244934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.272274017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.084885597229</t>
+    <t xml:space="preserve">16.8182430267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2722749710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0848846435547</t>
   </si>
   <si>
     <t xml:space="preserve">14.9911909103394</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8037996292114</t>
+    <t xml:space="preserve">14.8038005828857</t>
   </si>
   <si>
     <t xml:space="preserve">14.4758682250977</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">14.1010885238647</t>
   </si>
   <si>
-    <t xml:space="preserve">14.288477897644</t>
+    <t xml:space="preserve">14.2884769439697</t>
   </si>
   <si>
     <t xml:space="preserve">14.5227155685425</t>
@@ -851,28 +851,28 @@
     <t xml:space="preserve">13.960545539856</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2416305541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1947832107544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0073938369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7263088226318</t>
+    <t xml:space="preserve">14.2416296005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1947822570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0073928833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7263069152832</t>
   </si>
   <si>
     <t xml:space="preserve">14.1479358673096</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4290199279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6164112091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7731561660767</t>
+    <t xml:space="preserve">14.4290208816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6164102554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7731552124023</t>
   </si>
   <si>
     <t xml:space="preserve">13.3515281677246</t>
@@ -887,7 +887,7 @@
     <t xml:space="preserve">13.0235967636108</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1172924041748</t>
+    <t xml:space="preserve">13.1172914505005</t>
   </si>
   <si>
     <t xml:space="preserve">12.976749420166</t>
@@ -896,16 +896,16 @@
     <t xml:space="preserve">12.3677320480347</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0866460800171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9929523468018</t>
+    <t xml:space="preserve">12.0866470336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9929513931274</t>
   </si>
   <si>
     <t xml:space="preserve">11.8992576599121</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0397987365723</t>
+    <t xml:space="preserve">12.0397996902466</t>
   </si>
   <si>
     <t xml:space="preserve">12.1334943771362</t>
@@ -914,10 +914,10 @@
     <t xml:space="preserve">11.4776296615601</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2433938980103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3839340209961</t>
+    <t xml:space="preserve">11.2433929443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3839349746704</t>
   </si>
   <si>
     <t xml:space="preserve">11.6650199890137</t>
@@ -929,25 +929,25 @@
     <t xml:space="preserve">10.9623079299927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7280712127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1965456008911</t>
+    <t xml:space="preserve">10.7280702590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1965446472168</t>
   </si>
   <si>
     <t xml:space="preserve">11.5713243484497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3370876312256</t>
+    <t xml:space="preserve">11.3370885848999</t>
   </si>
   <si>
     <t xml:space="preserve">11.2902402877808</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7118682861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7587156295776</t>
+    <t xml:space="preserve">11.7118673324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7587146759033</t>
   </si>
   <si>
     <t xml:space="preserve">11.8055629730225</t>
@@ -962,16 +962,16 @@
     <t xml:space="preserve">8.33884906768799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57308578491211</t>
+    <t xml:space="preserve">8.57308673858643</t>
   </si>
   <si>
     <t xml:space="preserve">8.31074142456055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45128345489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61993312835693</t>
+    <t xml:space="preserve">8.45128440856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61993408203125</t>
   </si>
   <si>
     <t xml:space="preserve">8.44191455841064</t>
@@ -980,25 +980,25 @@
     <t xml:space="preserve">8.32948112487793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25452327728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43254470825195</t>
+    <t xml:space="preserve">8.25452423095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43254566192627</t>
   </si>
   <si>
     <t xml:space="preserve">8.47002220153809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32011127471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20767784118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08587265014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78604936599731</t>
+    <t xml:space="preserve">8.32011032104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20767688751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0858736038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78605031967163</t>
   </si>
   <si>
     <t xml:space="preserve">7.49559545516968</t>
@@ -1013,7 +1013,7 @@
     <t xml:space="preserve">7.83289623260498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90785312652588</t>
+    <t xml:space="preserve">7.90785264968872</t>
   </si>
   <si>
     <t xml:space="preserve">7.50496482849121</t>
@@ -1022,28 +1022,28 @@
     <t xml:space="preserve">7.37379169464111</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12081527709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28009700775146</t>
+    <t xml:space="preserve">7.12081480026245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28009653091431</t>
   </si>
   <si>
     <t xml:space="preserve">6.98027276992798</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93342542648315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06459856033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0271201133728</t>
+    <t xml:space="preserve">6.93342590332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06459808349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02712059020996</t>
   </si>
   <si>
     <t xml:space="preserve">7.34568309783936</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5424427986145</t>
+    <t xml:space="preserve">7.54244232177734</t>
   </si>
   <si>
     <t xml:space="preserve">8.19830703735352</t>
@@ -1058,19 +1058,19 @@
     <t xml:space="preserve">8.46116256713867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53747463226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68056106567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77595233917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8427267074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825527191162</t>
+    <t xml:space="preserve">8.53747367858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68056201934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77595138549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84272575378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825622558594</t>
   </si>
   <si>
     <t xml:space="preserve">8.66148281097412</t>
@@ -1085,10 +1085,10 @@
     <t xml:space="preserve">8.39438915252686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.604248046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48977947235107</t>
+    <t xml:space="preserve">8.60424900054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48977851867676</t>
   </si>
   <si>
     <t xml:space="preserve">8.29899787902832</t>
@@ -1100,7 +1100,7 @@
     <t xml:space="preserve">7.89835643768311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10821628570557</t>
+    <t xml:space="preserve">8.10821723937988</t>
   </si>
   <si>
     <t xml:space="preserve">7.84112215042114</t>
@@ -1118,34 +1118,34 @@
     <t xml:space="preserve">8.07959938049316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07005882263184</t>
+    <t xml:space="preserve">8.07005977630615</t>
   </si>
   <si>
     <t xml:space="preserve">7.92697429656982</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98420858383179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30853652954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26084136962891</t>
+    <t xml:space="preserve">7.98420810699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30853748321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26084041595459</t>
   </si>
   <si>
     <t xml:space="preserve">8.27038097381592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18452835083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03190326690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96513080596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86019992828369</t>
+    <t xml:space="preserve">8.18452930450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03190422058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96512985229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86020040512085</t>
   </si>
   <si>
     <t xml:space="preserve">7.86973905563354</t>
@@ -1157,7 +1157,7 @@
     <t xml:space="preserve">7.91743516921997</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76481008529663</t>
+    <t xml:space="preserve">7.76480960845947</t>
   </si>
   <si>
     <t xml:space="preserve">7.72665309906006</t>
@@ -1169,19 +1169,19 @@
     <t xml:space="preserve">7.63126230239868</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65987968444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16545104980469</t>
+    <t xml:space="preserve">7.65987920761108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16545009613037</t>
   </si>
   <si>
     <t xml:space="preserve">8.32761383056641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11775588989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93651247024536</t>
+    <t xml:space="preserve">8.11775493621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9365119934082</t>
   </si>
   <si>
     <t xml:space="preserve">8.19406795501709</t>
@@ -1190,10 +1190,10 @@
     <t xml:space="preserve">8.2322244644165</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31807518005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15591144561768</t>
+    <t xml:space="preserve">8.31807613372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15591239929199</t>
   </si>
   <si>
     <t xml:space="preserve">8.22268486022949</t>
@@ -1202,10 +1202,10 @@
     <t xml:space="preserve">8.25130176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35623168945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24176406860352</t>
+    <t xml:space="preserve">8.35623264312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2417631149292</t>
   </si>
   <si>
     <t xml:space="preserve">8.34669303894043</t>
@@ -1223,7 +1223,7 @@
     <t xml:space="preserve">7.97466850280762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01282596588135</t>
+    <t xml:space="preserve">8.01282501220703</t>
   </si>
   <si>
     <t xml:space="preserve">8.05098152160645</t>
@@ -1232,13 +1232,13 @@
     <t xml:space="preserve">7.67895746231079</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73619174957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69803524017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51679372787476</t>
+    <t xml:space="preserve">7.73619222640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6980357170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5167932510376</t>
   </si>
   <si>
     <t xml:space="preserve">7.59310626983643</t>
@@ -1262,16 +1262,16 @@
     <t xml:space="preserve">7.20200395584106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18292570114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14476871490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12569046020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23062133789062</t>
+    <t xml:space="preserve">7.18292617797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14476919174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12569093704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23062086105347</t>
   </si>
   <si>
     <t xml:space="preserve">7.1543083190918</t>
@@ -1280,7 +1280,7 @@
     <t xml:space="preserve">7.24969863891602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24016046524048</t>
+    <t xml:space="preserve">7.24015998840332</t>
   </si>
   <si>
     <t xml:space="preserve">7.46909809112549</t>
@@ -1301,13 +1301,13 @@
     <t xml:space="preserve">7.3355507850647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61218404769897</t>
+    <t xml:space="preserve">7.61218452453613</t>
   </si>
   <si>
     <t xml:space="preserve">7.90789556503296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94605159759521</t>
+    <t xml:space="preserve">7.94605112075806</t>
   </si>
   <si>
     <t xml:space="preserve">7.45955896377563</t>
@@ -1319,22 +1319,22 @@
     <t xml:space="preserve">7.8792781829834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99374771118164</t>
+    <t xml:space="preserve">7.99374723434448</t>
   </si>
   <si>
     <t xml:space="preserve">7.75527000427246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81250381469727</t>
+    <t xml:space="preserve">7.81250429153442</t>
   </si>
   <si>
     <t xml:space="preserve">7.79342699050903</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80296611785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85065984725952</t>
+    <t xml:space="preserve">7.80296564102173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85066032409668</t>
   </si>
   <si>
     <t xml:space="preserve">7.74573087692261</t>
@@ -1343,22 +1343,22 @@
     <t xml:space="preserve">7.83158302307129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66941785812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60264492034912</t>
+    <t xml:space="preserve">7.66941833496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60264444351196</t>
   </si>
   <si>
     <t xml:space="preserve">7.58356666564941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88881826400757</t>
+    <t xml:space="preserve">7.88881778717041</t>
   </si>
   <si>
     <t xml:space="preserve">8.00328636169434</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78388738632202</t>
+    <t xml:space="preserve">7.78388690948486</t>
   </si>
   <si>
     <t xml:space="preserve">7.3641676902771</t>
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">7.27831649780273</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08753490447998</t>
+    <t xml:space="preserve">7.08753442764282</t>
   </si>
   <si>
     <t xml:space="preserve">7.05891799926758</t>
@@ -1379,10 +1379,10 @@
     <t xml:space="preserve">7.50372648239136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98721408843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02589225769043</t>
+    <t xml:space="preserve">7.98721361160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02589321136475</t>
   </si>
   <si>
     <t xml:space="preserve">8.04523086547852</t>
@@ -1394,25 +1394,25 @@
     <t xml:space="preserve">8.07424163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12258911132812</t>
+    <t xml:space="preserve">8.12259006500244</t>
   </si>
   <si>
     <t xml:space="preserve">8.05490112304688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94853496551514</t>
+    <t xml:space="preserve">7.94853448867798</t>
   </si>
   <si>
     <t xml:space="preserve">8.06457138061523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08390998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97754430770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93886518478394</t>
+    <t xml:space="preserve">8.08391094207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97754383087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93886423110962</t>
   </si>
   <si>
     <t xml:space="preserve">7.79381895065308</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">7.68745088577271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63910293579102</t>
+    <t xml:space="preserve">7.63910245895386</t>
   </si>
   <si>
     <t xml:space="preserve">7.73579978942871</t>
@@ -1439,10 +1439,10 @@
     <t xml:space="preserve">7.90985584259033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85183668136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83249759674072</t>
+    <t xml:space="preserve">7.85183715820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83249807357788</t>
   </si>
   <si>
     <t xml:space="preserve">7.81315755844116</t>
@@ -1451,7 +1451,7 @@
     <t xml:space="preserve">7.80348825454712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78414916992188</t>
+    <t xml:space="preserve">7.78414869308472</t>
   </si>
   <si>
     <t xml:space="preserve">7.6681113243103</t>
@@ -1463,13 +1463,13 @@
     <t xml:space="preserve">7.71646022796631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75513982772827</t>
+    <t xml:space="preserve">7.75514030456543</t>
   </si>
   <si>
     <t xml:space="preserve">7.74547004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86150693893433</t>
+    <t xml:space="preserve">7.86150646209717</t>
   </si>
   <si>
     <t xml:space="preserve">7.89051580429077</t>
@@ -1487,10 +1487,10 @@
     <t xml:space="preserve">8.09358024597168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13225936889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1515998840332</t>
+    <t xml:space="preserve">8.1322603225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15159893035889</t>
   </si>
   <si>
     <t xml:space="preserve">8.1129207611084</t>
@@ -1499,10 +1499,10 @@
     <t xml:space="preserve">8.03556251525879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92919492721558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69712066650391</t>
+    <t xml:space="preserve">7.92919540405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69712114334106</t>
   </si>
   <si>
     <t xml:space="preserve">7.60042381286621</t>
@@ -1511,10 +1511,10 @@
     <t xml:space="preserve">7.88084602355957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55207443237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40702819824219</t>
+    <t xml:space="preserve">7.55207490921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40702867507935</t>
   </si>
   <si>
     <t xml:space="preserve">7.34900999069214</t>
@@ -1523,16 +1523,16 @@
     <t xml:space="preserve">7.37801933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43603754043579</t>
+    <t xml:space="preserve">7.43603801727295</t>
   </si>
   <si>
     <t xml:space="preserve">7.41669797897339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52306604385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36834955215454</t>
+    <t xml:space="preserve">7.5230655670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36834907531738</t>
   </si>
   <si>
     <t xml:space="preserve">7.542405128479</t>
@@ -1541,7 +1541,7 @@
     <t xml:space="preserve">7.4843864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70679044723511</t>
+    <t xml:space="preserve">7.70679092407227</t>
   </si>
   <si>
     <t xml:space="preserve">7.64877223968506</t>
@@ -1559,10 +1559,10 @@
     <t xml:space="preserve">7.59075355529785</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95820426940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96787405014038</t>
+    <t xml:space="preserve">7.95820331573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96787357330322</t>
   </si>
   <si>
     <t xml:space="preserve">7.90018606185913</t>
@@ -1580,10 +1580,10 @@
     <t xml:space="preserve">8.19027900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29664611816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45136165618896</t>
+    <t xml:space="preserve">8.29664516448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45136070251465</t>
   </si>
   <si>
     <t xml:space="preserve">8.48037147521973</t>
@@ -1610,19 +1610,19 @@
     <t xml:space="preserve">8.50938034057617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4223518371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54805946350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55772972106934</t>
+    <t xml:space="preserve">8.42235279083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54805850982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55772876739502</t>
   </si>
   <si>
     <t xml:space="preserve">8.52871990203857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68343448638916</t>
+    <t xml:space="preserve">8.68343544006348</t>
   </si>
   <si>
     <t xml:space="preserve">8.76079368591309</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">8.65442562103271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75112438201904</t>
+    <t xml:space="preserve">8.75112342834473</t>
   </si>
   <si>
     <t xml:space="preserve">8.70277500152588</t>
@@ -1655,10 +1655,10 @@
     <t xml:space="preserve">8.63508701324463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32565402984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31598472595215</t>
+    <t xml:space="preserve">8.32565498352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31598567962646</t>
   </si>
   <si>
     <t xml:space="preserve">8.30631542205811</t>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="753">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="754">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0764217376709</t>
+    <t xml:space="preserve">9.07642269134521</t>
   </si>
   <si>
     <t xml:space="preserve">FF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98565769195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08549880981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24887466430664</t>
+    <t xml:space="preserve">8.98565673828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08549785614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24887275695801</t>
   </si>
   <si>
     <t xml:space="preserve">9.09457492828369</t>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">9.03104019165039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95388984680176</t>
+    <t xml:space="preserve">8.95388889312744</t>
   </si>
   <si>
     <t xml:space="preserve">8.89943218231201</t>
@@ -71,16 +71,16 @@
     <t xml:space="preserve">8.89489364624023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84951114654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85858821868896</t>
+    <t xml:space="preserve">8.84951019287109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85858917236328</t>
   </si>
   <si>
     <t xml:space="preserve">8.87674045562744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76782417297363</t>
+    <t xml:space="preserve">8.76782321929932</t>
   </si>
   <si>
     <t xml:space="preserve">8.8676643371582</t>
@@ -89,16 +89,16 @@
     <t xml:space="preserve">9.04919242858887</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23072052001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1127290725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96750450134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91304588317871</t>
+    <t xml:space="preserve">9.23072147369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11272621154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96750545501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91304492950439</t>
   </si>
   <si>
     <t xml:space="preserve">8.92212295532227</t>
@@ -107,82 +107,82 @@
     <t xml:space="preserve">9.00380992889404</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15810966491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16718578338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43947887420654</t>
+    <t xml:space="preserve">9.15810871124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16718673706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43947792053223</t>
   </si>
   <si>
     <t xml:space="preserve">9.54839611053467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62100696563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8025369644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71177005767822</t>
+    <t xml:space="preserve">9.62100791931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80253601074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71177196502686</t>
   </si>
   <si>
     <t xml:space="preserve">9.56654834747314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58470153808594</t>
+    <t xml:space="preserve">9.58470058441162</t>
   </si>
   <si>
     <t xml:space="preserve">9.5756254196167</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53024387359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50301456451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60285472869873</t>
+    <t xml:space="preserve">9.53024291992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50301361083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60285568237305</t>
   </si>
   <si>
     <t xml:space="preserve">9.63916015625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79345893859863</t>
+    <t xml:space="preserve">9.79345798492432</t>
   </si>
   <si>
     <t xml:space="preserve">9.95683479309082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93868064880371</t>
+    <t xml:space="preserve">9.93868160247803</t>
   </si>
   <si>
     <t xml:space="preserve">9.98406505584717</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73899936676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7662296295166</t>
+    <t xml:space="preserve">9.73900127410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76622867584229</t>
   </si>
   <si>
     <t xml:space="preserve">9.74807548522949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75715446472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64823627471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82068729400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70269584655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72084808349609</t>
+    <t xml:space="preserve">9.75715351104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64823722839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82068920135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7026948928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72084712982178</t>
   </si>
   <si>
     <t xml:space="preserve">9.67546558380127</t>
@@ -191,37 +191,37 @@
     <t xml:space="preserve">9.66638946533203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63008308410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65731334686279</t>
+    <t xml:space="preserve">9.63008213043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65731239318848</t>
   </si>
   <si>
     <t xml:space="preserve">9.68454170227051</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81161308288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8297643661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84791851043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83884239196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72992515563965</t>
+    <t xml:space="preserve">9.81161212921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82976531982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84791946411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83884143829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72992420196533</t>
   </si>
   <si>
     <t xml:space="preserve">9.78438282012939</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55747222900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34871387481689</t>
+    <t xml:space="preserve">9.55747318267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34871482849121</t>
   </si>
   <si>
     <t xml:space="preserve">9.33963775634766</t>
@@ -230,40 +230,40 @@
     <t xml:space="preserve">9.27610301971436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25794982910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19441509246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18533992767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41224956512451</t>
+    <t xml:space="preserve">9.25794887542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19441604614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18533897399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4122486114502</t>
   </si>
   <si>
     <t xml:space="preserve">9.22164440155029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31240844726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26702499389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29425430297852</t>
+    <t xml:space="preserve">9.31241035461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26702690124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29425525665283</t>
   </si>
   <si>
     <t xml:space="preserve">9.28517913818359</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37594318389893</t>
+    <t xml:space="preserve">9.37594413757324</t>
   </si>
   <si>
     <t xml:space="preserve">9.36686706542969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3850212097168</t>
+    <t xml:space="preserve">9.38502025604248</t>
   </si>
   <si>
     <t xml:space="preserve">9.45763111114502</t>
@@ -278,13 +278,13 @@
     <t xml:space="preserve">9.49393749237061</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44855403900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47578430175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23979759216309</t>
+    <t xml:space="preserve">9.44855499267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4757833480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2397985458374</t>
   </si>
   <si>
     <t xml:space="preserve">9.14903354644775</t>
@@ -293,10 +293,10 @@
     <t xml:space="preserve">9.21256828308105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2034912109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13088035583496</t>
+    <t xml:space="preserve">9.20349216461182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13088130950928</t>
   </si>
   <si>
     <t xml:space="preserve">9.1399564743042</t>
@@ -305,13 +305,13 @@
     <t xml:space="preserve">8.94027614593506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80412864685059</t>
+    <t xml:space="preserve">8.80412769317627</t>
   </si>
   <si>
     <t xml:space="preserve">8.75874710083008</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66798400878906</t>
+    <t xml:space="preserve">8.66798210144043</t>
   </si>
   <si>
     <t xml:space="preserve">8.62260055541992</t>
@@ -320,7 +320,7 @@
     <t xml:space="preserve">8.53183555603027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35030841827393</t>
+    <t xml:space="preserve">8.35030746459961</t>
   </si>
   <si>
     <t xml:space="preserve">8.16877937316895</t>
@@ -329,52 +329,52 @@
     <t xml:space="preserve">7.98725128173828</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03263282775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12339782714844</t>
+    <t xml:space="preserve">8.03263378143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1233959197998</t>
   </si>
   <si>
     <t xml:space="preserve">8.25954437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94186878204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30492496490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21416282653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39568901062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5772180557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71336555480957</t>
+    <t xml:space="preserve">7.94186973571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3049259185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21416091918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39568996429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57721900939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71336460113525</t>
   </si>
   <si>
     <t xml:space="preserve">9.53202247619629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25706100463867</t>
+    <t xml:space="preserve">9.25706005096436</t>
   </si>
   <si>
     <t xml:space="preserve">9.44036865234375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16540622711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07375240325928</t>
+    <t xml:space="preserve">9.16540718078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07375144958496</t>
   </si>
   <si>
     <t xml:space="preserve">9.11957931518555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98209953308105</t>
+    <t xml:space="preserve">8.98209857940674</t>
   </si>
   <si>
     <t xml:space="preserve">9.02792549133301</t>
@@ -386,7 +386,7 @@
     <t xml:space="preserve">9.80698394775391</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89863967895508</t>
+    <t xml:space="preserve">9.89863872528076</t>
   </si>
   <si>
     <t xml:space="preserve">9.9902925491333</t>
@@ -395,49 +395,49 @@
     <t xml:space="preserve">10.1736011505127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2652540206909</t>
+    <t xml:space="preserve">10.2652559280396</t>
   </si>
   <si>
     <t xml:space="preserve">10.3569097518921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5402183532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6318731307983</t>
+    <t xml:space="preserve">10.5402193069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.631872177124</t>
   </si>
   <si>
     <t xml:space="preserve">10.8151798248291</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7235250473022</t>
+    <t xml:space="preserve">10.7235260009766</t>
   </si>
   <si>
     <t xml:space="preserve">10.9068336486816</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9984874725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0901432037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1817951202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2734518051147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4567575454712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.36510181427</t>
+    <t xml:space="preserve">10.9984884262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.090142250061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1817960739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2734508514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4567584991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3651027679443</t>
   </si>
   <si>
     <t xml:space="preserve">10.4485635757446</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71533107757568</t>
+    <t xml:space="preserve">9.71533203125</t>
   </si>
   <si>
     <t xml:space="preserve">8.79879093170166</t>
@@ -455,25 +455,25 @@
     <t xml:space="preserve">9.03709030151367</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3945426940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76115703582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66950416564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57785034179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0361204147339</t>
+    <t xml:space="preserve">9.39454174041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76115798950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66950511932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57784938812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0361194610596</t>
   </si>
   <si>
     <t xml:space="preserve">9.94446659088135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82552433013916</t>
+    <t xml:space="preserve">9.82552528381348</t>
   </si>
   <si>
     <t xml:space="preserve">9.73283100128174</t>
@@ -497,7 +497,7 @@
     <t xml:space="preserve">10.1036043167114</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1499509811401</t>
+    <t xml:space="preserve">10.1499519348145</t>
   </si>
   <si>
     <t xml:space="preserve">10.1962985992432</t>
@@ -506,10 +506,10 @@
     <t xml:space="preserve">9.77917671203613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87187099456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0572595596313</t>
+    <t xml:space="preserve">9.87187004089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.057258605957</t>
   </si>
   <si>
     <t xml:space="preserve">10.2889928817749</t>
@@ -518,10 +518,10 @@
     <t xml:space="preserve">10.4743795394897</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2426452636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.381685256958</t>
+    <t xml:space="preserve">10.2426443099976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3816843032837</t>
   </si>
   <si>
     <t xml:space="preserve">9.68648338317871</t>
@@ -530,10 +530,10 @@
     <t xml:space="preserve">9.64013576507568</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50109672546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31570911407471</t>
+    <t xml:space="preserve">9.50109577178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31570816040039</t>
   </si>
   <si>
     <t xml:space="preserve">9.23228454589844</t>
@@ -542,61 +542,61 @@
     <t xml:space="preserve">9.19520664215088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25082302093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26936149597168</t>
+    <t xml:space="preserve">9.25082397460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26936340332031</t>
   </si>
   <si>
     <t xml:space="preserve">9.2137451171875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04689693450928</t>
+    <t xml:space="preserve">9.04689788818359</t>
   </si>
   <si>
     <t xml:space="preserve">9.12105274200439</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0654354095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97274303436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17666816711426</t>
+    <t xml:space="preserve">9.06543636322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97274208068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17666721343994</t>
   </si>
   <si>
     <t xml:space="preserve">9.02835845947266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95420265197754</t>
+    <t xml:space="preserve">8.95420360565186</t>
   </si>
   <si>
     <t xml:space="preserve">8.71319961547852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99128150939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7688159942627</t>
+    <t xml:space="preserve">8.9912805557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76881694793701</t>
   </si>
   <si>
     <t xml:space="preserve">8.89858818054199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93566513061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3353385925293</t>
+    <t xml:space="preserve">8.93566608428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3353395462036</t>
   </si>
   <si>
     <t xml:space="preserve">10.9841938018799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0305404663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2159280776978</t>
+    <t xml:space="preserve">11.0305414199829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2159290313721</t>
   </si>
   <si>
     <t xml:space="preserve">11.4940090179443</t>
@@ -605,10 +605,10 @@
     <t xml:space="preserve">11.540355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5867023468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6330499649048</t>
+    <t xml:space="preserve">11.5867033004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6330490112305</t>
   </si>
   <si>
     <t xml:space="preserve">11.7257432937622</t>
@@ -617,31 +617,31 @@
     <t xml:space="preserve">11.9111299514771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9574766159058</t>
+    <t xml:space="preserve">11.9574775695801</t>
   </si>
   <si>
     <t xml:space="preserve">12.1892108917236</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2819042205811</t>
+    <t xml:space="preserve">12.2819051742554</t>
   </si>
   <si>
     <t xml:space="preserve">12.3745985031128</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5136394500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3282527923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1428651809692</t>
+    <t xml:space="preserve">12.5136375427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3282518386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1428642272949</t>
   </si>
   <si>
     <t xml:space="preserve">12.0965175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5551204681396</t>
+    <t xml:space="preserve">12.555121421814</t>
   </si>
   <si>
     <t xml:space="preserve">12.5082750320435</t>
@@ -653,19 +653,19 @@
     <t xml:space="preserve">12.4614267349243</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4145793914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7425127029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6956653594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2271909713745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1803426742554</t>
+    <t xml:space="preserve">12.4145784378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7425117492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6956644058228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2271890640259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1803417205811</t>
   </si>
   <si>
     <t xml:space="preserve">12.3208847045898</t>
@@ -674,37 +674,37 @@
     <t xml:space="preserve">12.274037361145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8362064361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7893600463867</t>
+    <t xml:space="preserve">12.8362073898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7893590927124</t>
   </si>
   <si>
     <t xml:space="preserve">12.6019687652588</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9299011230469</t>
+    <t xml:space="preserve">12.9299020767212</t>
   </si>
   <si>
     <t xml:space="preserve">12.8830537796021</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0704441070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.679461479187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8668518066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0542411804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3353261947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5695629119873</t>
+    <t xml:space="preserve">13.0704431533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6794624328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8668508529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0542402267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3353252410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5695638656616</t>
   </si>
   <si>
     <t xml:space="preserve">15.2254276275635</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">14.7569532394409</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0380373001099</t>
+    <t xml:space="preserve">15.0380363464355</t>
   </si>
   <si>
     <t xml:space="preserve">15.1785802841187</t>
@@ -728,16 +728,16 @@
     <t xml:space="preserve">14.8974952697754</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4596643447876</t>
+    <t xml:space="preserve">15.4596652984619</t>
   </si>
   <si>
     <t xml:space="preserve">15.4128189086914</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5533609390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0686798095703</t>
+    <t xml:space="preserve">15.5533590316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0686836242676</t>
   </si>
   <si>
     <t xml:space="preserve">16.8650894165039</t>
@@ -749,25 +749,25 @@
     <t xml:space="preserve">16.7713928222656</t>
   </si>
   <si>
-    <t xml:space="preserve">17.193021774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0524806976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9587841033936</t>
+    <t xml:space="preserve">17.1930198669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0524787902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9587860107422</t>
   </si>
   <si>
     <t xml:space="preserve">16.7245464324951</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6308517456055</t>
+    <t xml:space="preserve">16.6308498382568</t>
   </si>
   <si>
     <t xml:space="preserve">16.5371570587158</t>
   </si>
   <si>
-    <t xml:space="preserve">16.584005355835</t>
+    <t xml:space="preserve">16.5840072631836</t>
   </si>
   <si>
     <t xml:space="preserve">16.2092227935791</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">15.8344440460205</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1155300140381</t>
+    <t xml:space="preserve">16.1155281066895</t>
   </si>
   <si>
     <t xml:space="preserve">16.0218372344971</t>
@@ -800,10 +800,10 @@
     <t xml:space="preserve">15.9749870300293</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7407493591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4434604644775</t>
+    <t xml:space="preserve">15.7407474517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4434623718262</t>
   </si>
   <si>
     <t xml:space="preserve">16.9119358062744</t>
@@ -821,13 +821,13 @@
     <t xml:space="preserve">15.2722749710083</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0848846435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9911909103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8038005828857</t>
+    <t xml:space="preserve">15.084885597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.991189956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8038015365601</t>
   </si>
   <si>
     <t xml:space="preserve">14.4758682250977</t>
@@ -839,19 +839,19 @@
     <t xml:space="preserve">14.1010885238647</t>
   </si>
   <si>
-    <t xml:space="preserve">14.288477897644</t>
+    <t xml:space="preserve">14.2884788513184</t>
   </si>
   <si>
     <t xml:space="preserve">14.5227155685425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.960545539856</t>
+    <t xml:space="preserve">13.9605464935303</t>
   </si>
   <si>
     <t xml:space="preserve">14.2416305541992</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1947832107544</t>
+    <t xml:space="preserve">14.1947822570801</t>
   </si>
   <si>
     <t xml:space="preserve">14.0073928833008</t>
@@ -869,7 +869,7 @@
     <t xml:space="preserve">14.6164102554321</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7731561660767</t>
+    <t xml:space="preserve">13.7731552124023</t>
   </si>
   <si>
     <t xml:space="preserve">13.3515291213989</t>
@@ -878,37 +878,37 @@
     <t xml:space="preserve">13.3046808242798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3983755111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0235958099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1172904968262</t>
+    <t xml:space="preserve">13.3983764648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0235967636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1172914505005</t>
   </si>
   <si>
     <t xml:space="preserve">12.976749420166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3677320480347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0866460800171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9929513931274</t>
+    <t xml:space="preserve">12.367733001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0866470336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9929523468018</t>
   </si>
   <si>
     <t xml:space="preserve">11.8992576599121</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0397996902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1334943771362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4776296615601</t>
+    <t xml:space="preserve">12.0398006439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1334934234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4776306152344</t>
   </si>
   <si>
     <t xml:space="preserve">11.2433929443359</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">11.3839349746704</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6650199890137</t>
+    <t xml:space="preserve">11.6650190353394</t>
   </si>
   <si>
     <t xml:space="preserve">11.4307823181152</t>
@@ -932,10 +932,10 @@
     <t xml:space="preserve">11.1965446472168</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5713243484497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3370885848999</t>
+    <t xml:space="preserve">11.5713262557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3370876312256</t>
   </si>
   <si>
     <t xml:space="preserve">11.2902402877808</t>
@@ -950,10 +950,10 @@
     <t xml:space="preserve">11.8055629730225</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0091552734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46318817138672</t>
+    <t xml:space="preserve">11.0091562271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46318912506104</t>
   </si>
   <si>
     <t xml:space="preserve">8.33884906768799</t>
@@ -965,7 +965,7 @@
     <t xml:space="preserve">8.31074047088623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45128440856934</t>
+    <t xml:space="preserve">8.45128345489502</t>
   </si>
   <si>
     <t xml:space="preserve">8.61993408203125</t>
@@ -974,40 +974,40 @@
     <t xml:space="preserve">8.44191455841064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32948112487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25452423095703</t>
+    <t xml:space="preserve">8.32948017120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25452518463135</t>
   </si>
   <si>
     <t xml:space="preserve">8.43254470825195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47002124786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32011032104492</t>
+    <t xml:space="preserve">8.47002220153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32010936737061</t>
   </si>
   <si>
     <t xml:space="preserve">8.20767688751221</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0858736038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78604936599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49559545516968</t>
+    <t xml:space="preserve">8.08587265014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78604984283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49559497833252</t>
   </si>
   <si>
     <t xml:space="preserve">7.33631372451782</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23324918746948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83289623260498</t>
+    <t xml:space="preserve">7.23324966430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83289575576782</t>
   </si>
   <si>
     <t xml:space="preserve">7.9078516960144</t>
@@ -1016,7 +1016,7 @@
     <t xml:space="preserve">7.50496482849121</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37379217147827</t>
+    <t xml:space="preserve">7.37379169464111</t>
   </si>
   <si>
     <t xml:space="preserve">7.12081527709961</t>
@@ -1025,31 +1025,31 @@
     <t xml:space="preserve">7.28009653091431</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98027276992798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93342590332031</t>
+    <t xml:space="preserve">6.98027324676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93342542648315</t>
   </si>
   <si>
     <t xml:space="preserve">7.06459808349609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02712059020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34568309783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54244232177734</t>
+    <t xml:space="preserve">7.0271201133728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34568357467651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5424427986145</t>
   </si>
   <si>
     <t xml:space="preserve">8.19830703735352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2170467376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65194225311279</t>
+    <t xml:space="preserve">8.21704769134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65194320678711</t>
   </si>
   <si>
     <t xml:space="preserve">8.46116161346436</t>
@@ -1058,7 +1058,7 @@
     <t xml:space="preserve">8.53747367858887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68056201934814</t>
+    <t xml:space="preserve">8.68056106567383</t>
   </si>
   <si>
     <t xml:space="preserve">8.77595138549805</t>
@@ -1070,19 +1070,19 @@
     <t xml:space="preserve">8.72825622558594</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6614818572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49931812286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42300510406494</t>
+    <t xml:space="preserve">8.66148281097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49931716918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42300605773926</t>
   </si>
   <si>
     <t xml:space="preserve">8.39438915252686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60424900054932</t>
+    <t xml:space="preserve">8.604248046875</t>
   </si>
   <si>
     <t xml:space="preserve">8.48977851867676</t>
@@ -1091,46 +1091,46 @@
     <t xml:space="preserve">8.29899787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12729358673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89835643768311</t>
+    <t xml:space="preserve">8.12729454040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89835596084595</t>
   </si>
   <si>
     <t xml:space="preserve">8.10821628570557</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84112215042114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33715343475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2036075592041</t>
+    <t xml:space="preserve">7.8411226272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33715438842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20360660552979</t>
   </si>
   <si>
     <t xml:space="preserve">8.06052017211914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07959842681885</t>
+    <t xml:space="preserve">8.07959938049316</t>
   </si>
   <si>
     <t xml:space="preserve">8.07005977630615</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92697334289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98420810699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30853748321533</t>
+    <t xml:space="preserve">7.92697381973267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98420763015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30853652954102</t>
   </si>
   <si>
     <t xml:space="preserve">8.26084136962891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27038097381592</t>
+    <t xml:space="preserve">8.2703800201416</t>
   </si>
   <si>
     <t xml:space="preserve">8.18452930450439</t>
@@ -1139,19 +1139,19 @@
     <t xml:space="preserve">8.03190326690674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96512985229492</t>
+    <t xml:space="preserve">7.96513032913208</t>
   </si>
   <si>
     <t xml:space="preserve">7.86019992828369</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86973905563354</t>
+    <t xml:space="preserve">7.8697395324707</t>
   </si>
   <si>
     <t xml:space="preserve">7.71711397171021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91743516921997</t>
+    <t xml:space="preserve">7.91743421554565</t>
   </si>
   <si>
     <t xml:space="preserve">7.76480960845947</t>
@@ -1160,34 +1160,34 @@
     <t xml:space="preserve">7.72665309906006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65034103393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63126230239868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65987873077393</t>
+    <t xml:space="preserve">7.65034055709839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63126182556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65987920761108</t>
   </si>
   <si>
     <t xml:space="preserve">8.16545104980469</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32761383056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11775493621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9365119934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19406890869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2322244644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31807708740234</t>
+    <t xml:space="preserve">8.32761478424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11775588989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93651151657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19406795501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23222351074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31807613372803</t>
   </si>
   <si>
     <t xml:space="preserve">8.15591239929199</t>
@@ -1217,16 +1217,16 @@
     <t xml:space="preserve">7.82204389572144</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97466850280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01282501220703</t>
+    <t xml:space="preserve">7.97466802597046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01282405853271</t>
   </si>
   <si>
     <t xml:space="preserve">8.05098056793213</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67895746231079</t>
+    <t xml:space="preserve">7.67895793914795</t>
   </si>
   <si>
     <t xml:space="preserve">7.73619174957275</t>
@@ -1235,16 +1235,16 @@
     <t xml:space="preserve">7.6980357170105</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5167932510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59310626983643</t>
+    <t xml:space="preserve">7.51679372787476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59310579299927</t>
   </si>
   <si>
     <t xml:space="preserve">7.44048070907593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5358715057373</t>
+    <t xml:space="preserve">7.53587198257446</t>
   </si>
   <si>
     <t xml:space="preserve">7.62172269821167</t>
@@ -1271,7 +1271,7 @@
     <t xml:space="preserve">7.23062086105347</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1543083190918</t>
+    <t xml:space="preserve">7.15430784225464</t>
   </si>
   <si>
     <t xml:space="preserve">7.24969911575317</t>
@@ -1286,10 +1286,10 @@
     <t xml:space="preserve">7.41186332702637</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45001983642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28785562515259</t>
+    <t xml:space="preserve">7.45001935958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28785514831543</t>
   </si>
   <si>
     <t xml:space="preserve">7.39278507232666</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">7.3355507850647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61218404769897</t>
+    <t xml:space="preserve">7.61218357086182</t>
   </si>
   <si>
     <t xml:space="preserve">7.90789556503296</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">7.94605112075806</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45955848693848</t>
+    <t xml:space="preserve">7.45955896377563</t>
   </si>
   <si>
     <t xml:space="preserve">7.70757436752319</t>
@@ -1331,13 +1331,13 @@
     <t xml:space="preserve">7.80296611785889</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85066032409668</t>
+    <t xml:space="preserve">7.85066080093384</t>
   </si>
   <si>
     <t xml:space="preserve">7.74573087692261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83158254623413</t>
+    <t xml:space="preserve">7.83158349990845</t>
   </si>
   <si>
     <t xml:space="preserve">7.66941833496094</t>
@@ -1358,28 +1358,28 @@
     <t xml:space="preserve">7.78388738632202</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3641676902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10661268234253</t>
+    <t xml:space="preserve">7.36416816711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10661315917969</t>
   </si>
   <si>
     <t xml:space="preserve">7.27831649780273</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08753442764282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05891799926758</t>
+    <t xml:space="preserve">7.08753490447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05891752243042</t>
   </si>
   <si>
     <t xml:space="preserve">7.50372648239136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98721361160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02589321136475</t>
+    <t xml:space="preserve">7.98721408843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02589225769043</t>
   </si>
   <si>
     <t xml:space="preserve">8.04523086547852</t>
@@ -1391,25 +1391,25 @@
     <t xml:space="preserve">8.07424163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12259006500244</t>
+    <t xml:space="preserve">8.12258911132812</t>
   </si>
   <si>
     <t xml:space="preserve">8.05490112304688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94853448867798</t>
+    <t xml:space="preserve">7.94853496551514</t>
   </si>
   <si>
     <t xml:space="preserve">8.06457138061523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08391094207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97754383087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93886423110962</t>
+    <t xml:space="preserve">8.08390998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97754430770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93886518478394</t>
   </si>
   <si>
     <t xml:space="preserve">7.79381895065308</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">7.68745088577271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63910245895386</t>
+    <t xml:space="preserve">7.63910293579102</t>
   </si>
   <si>
     <t xml:space="preserve">7.73579978942871</t>
@@ -1436,10 +1436,10 @@
     <t xml:space="preserve">7.90985584259033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85183715820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83249807357788</t>
+    <t xml:space="preserve">7.85183668136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83249759674072</t>
   </si>
   <si>
     <t xml:space="preserve">7.81315755844116</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">7.80348825454712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78414869308472</t>
+    <t xml:space="preserve">7.78414916992188</t>
   </si>
   <si>
     <t xml:space="preserve">7.6681113243103</t>
@@ -1460,13 +1460,13 @@
     <t xml:space="preserve">7.71646022796631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75514030456543</t>
+    <t xml:space="preserve">7.75513982772827</t>
   </si>
   <si>
     <t xml:space="preserve">7.74547004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86150646209717</t>
+    <t xml:space="preserve">7.86150693893433</t>
   </si>
   <si>
     <t xml:space="preserve">7.89051580429077</t>
@@ -1484,10 +1484,10 @@
     <t xml:space="preserve">8.09358024597168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1322603225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15159893035889</t>
+    <t xml:space="preserve">8.13225936889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1515998840332</t>
   </si>
   <si>
     <t xml:space="preserve">8.1129207611084</t>
@@ -1496,10 +1496,10 @@
     <t xml:space="preserve">8.03556251525879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92919540405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69712114334106</t>
+    <t xml:space="preserve">7.92919492721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69712066650391</t>
   </si>
   <si>
     <t xml:space="preserve">7.60042381286621</t>
@@ -1508,10 +1508,10 @@
     <t xml:space="preserve">7.88084602355957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55207490921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40702867507935</t>
+    <t xml:space="preserve">7.55207443237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40702819824219</t>
   </si>
   <si>
     <t xml:space="preserve">7.34900999069214</t>
@@ -1520,16 +1520,16 @@
     <t xml:space="preserve">7.37801933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43603801727295</t>
+    <t xml:space="preserve">7.43603754043579</t>
   </si>
   <si>
     <t xml:space="preserve">7.41669797897339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5230655670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36834907531738</t>
+    <t xml:space="preserve">7.52306604385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36834955215454</t>
   </si>
   <si>
     <t xml:space="preserve">7.542405128479</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">7.4843864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70679092407227</t>
+    <t xml:space="preserve">7.70679044723511</t>
   </si>
   <si>
     <t xml:space="preserve">7.64877223968506</t>
@@ -1556,10 +1556,10 @@
     <t xml:space="preserve">7.59075355529785</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95820331573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96787357330322</t>
+    <t xml:space="preserve">7.95820426940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96787405014038</t>
   </si>
   <si>
     <t xml:space="preserve">7.90018606185913</t>
@@ -1577,10 +1577,10 @@
     <t xml:space="preserve">8.19027900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29664516448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45136070251465</t>
+    <t xml:space="preserve">8.29664611816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45136165618896</t>
   </si>
   <si>
     <t xml:space="preserve">8.48037147521973</t>
@@ -1607,19 +1607,19 @@
     <t xml:space="preserve">8.50938034057617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42235279083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54805850982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55772876739502</t>
+    <t xml:space="preserve">8.4223518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54805946350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55772972106934</t>
   </si>
   <si>
     <t xml:space="preserve">8.52871990203857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68343544006348</t>
+    <t xml:space="preserve">8.68343448638916</t>
   </si>
   <si>
     <t xml:space="preserve">8.76079368591309</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">8.65442562103271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75112342834473</t>
+    <t xml:space="preserve">8.75112438201904</t>
   </si>
   <si>
     <t xml:space="preserve">8.70277500152588</t>
@@ -1652,10 +1652,10 @@
     <t xml:space="preserve">8.63508701324463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32565498352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31598567962646</t>
+    <t xml:space="preserve">8.32565402984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31598472595215</t>
   </si>
   <si>
     <t xml:space="preserve">8.30631542205811</t>
@@ -2271,6 +2271,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.47999954223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5</t>
   </si>
 </sst>
 </file>
@@ -63317,6 +63320,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2336">
+      <c r="A2336" s="1" t="n">
+        <v>46020.6911921296</v>
+      </c>
+      <c r="B2336" t="n">
+        <v>13929</v>
+      </c>
+      <c r="C2336" t="n">
+        <v>9.5600004196167</v>
+      </c>
+      <c r="D2336" t="n">
+        <v>9.46000003814697</v>
+      </c>
+      <c r="E2336" t="n">
+        <v>9.53999996185303</v>
+      </c>
+      <c r="F2336" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G2336" t="s">
+        <v>753</v>
+      </c>
+      <c r="H2336" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07642269134521</t>
+    <t xml:space="preserve">9.0764217376709</t>
   </si>
   <si>
     <t xml:space="preserve">FF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98565673828125</t>
+    <t xml:space="preserve">8.98565769195557</t>
   </si>
   <si>
     <t xml:space="preserve">9.08549785614014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24887275695801</t>
+    <t xml:space="preserve">9.24887180328369</t>
   </si>
   <si>
     <t xml:space="preserve">9.09457492828369</t>
@@ -59,31 +59,31 @@
     <t xml:space="preserve">9.12180328369141</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03104019165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95388889312744</t>
+    <t xml:space="preserve">9.03103923797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95389080047607</t>
   </si>
   <si>
     <t xml:space="preserve">8.89943218231201</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89489364624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84951019287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85858917236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87674045562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76782321929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8676643371582</t>
+    <t xml:space="preserve">8.89489269256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84951114654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85858726501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87674140930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.767822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86766529083252</t>
   </si>
   <si>
     <t xml:space="preserve">9.04919242858887</t>
@@ -92,121 +92,121 @@
     <t xml:space="preserve">9.23072147369385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11272621154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96750545501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91304492950439</t>
+    <t xml:space="preserve">9.11272811889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96750450134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91304683685303</t>
   </si>
   <si>
     <t xml:space="preserve">8.92212295532227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00380992889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15810871124268</t>
+    <t xml:space="preserve">9.00381183624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15811061859131</t>
   </si>
   <si>
     <t xml:space="preserve">9.16718673706055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43947792053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54839611053467</t>
+    <t xml:space="preserve">9.43947887420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54839706420898</t>
   </si>
   <si>
     <t xml:space="preserve">9.62100791931152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80253601074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71177196502686</t>
+    <t xml:space="preserve">9.80253505706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71177101135254</t>
   </si>
   <si>
     <t xml:space="preserve">9.56654834747314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58470058441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5756254196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53024291992188</t>
+    <t xml:space="preserve">9.58470249176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57562446594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53024196624756</t>
   </si>
   <si>
     <t xml:space="preserve">9.50301361083984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60285568237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63916015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79345798492432</t>
+    <t xml:space="preserve">9.60285377502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63916110992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79345893859863</t>
   </si>
   <si>
     <t xml:space="preserve">9.95683479309082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93868160247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98406505584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73900127410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76622867584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74807548522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75715351104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64823722839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82068920135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7026948928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72084712982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67546558380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66638946533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63008213043213</t>
+    <t xml:space="preserve">9.93868255615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98406410217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73900032043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76623058319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74807739257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75715160369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64823627471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82068729400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70269393920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72084808349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67546653747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66638851165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63008308410645</t>
   </si>
   <si>
     <t xml:space="preserve">9.65731239318848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68454170227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81161212921143</t>
+    <t xml:space="preserve">9.68454360961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81161308288574</t>
   </si>
   <si>
     <t xml:space="preserve">9.82976531982422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84791946411133</t>
+    <t xml:space="preserve">9.8479175567627</t>
   </si>
   <si>
     <t xml:space="preserve">9.83884143829346</t>
@@ -215,13 +215,13 @@
     <t xml:space="preserve">9.72992420196533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78438282012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55747318267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34871482849121</t>
+    <t xml:space="preserve">9.78438186645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55747222900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34871387481689</t>
   </si>
   <si>
     <t xml:space="preserve">9.33963775634766</t>
@@ -230,31 +230,31 @@
     <t xml:space="preserve">9.27610301971436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25794887542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19441604614258</t>
+    <t xml:space="preserve">9.25795078277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19441509246826</t>
   </si>
   <si>
     <t xml:space="preserve">9.18533897399902</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4122486114502</t>
+    <t xml:space="preserve">9.41224956512451</t>
   </si>
   <si>
     <t xml:space="preserve">9.22164440155029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31241035461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26702690124512</t>
+    <t xml:space="preserve">9.31240844726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26702785491943</t>
   </si>
   <si>
     <t xml:space="preserve">9.29425525665283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28517913818359</t>
+    <t xml:space="preserve">9.28518009185791</t>
   </si>
   <si>
     <t xml:space="preserve">9.37594413757324</t>
@@ -263,19 +263,19 @@
     <t xml:space="preserve">9.36686706542969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38502025604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45763111114502</t>
+    <t xml:space="preserve">9.3850212097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45763206481934</t>
   </si>
   <si>
     <t xml:space="preserve">9.39409732818604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48486042022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49393749237061</t>
+    <t xml:space="preserve">9.48486137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49393844604492</t>
   </si>
   <si>
     <t xml:space="preserve">9.44855499267578</t>
@@ -284,85 +284,85 @@
     <t xml:space="preserve">9.4757833480835</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2397985458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14903354644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21256828308105</t>
+    <t xml:space="preserve">9.23979759216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14903259277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21256732940674</t>
   </si>
   <si>
     <t xml:space="preserve">9.20349216461182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13088130950928</t>
+    <t xml:space="preserve">9.13088035583496</t>
   </si>
   <si>
     <t xml:space="preserve">9.1399564743042</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94027614593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80412769317627</t>
+    <t xml:space="preserve">8.94027519226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80412864685059</t>
   </si>
   <si>
     <t xml:space="preserve">8.75874710083008</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66798210144043</t>
+    <t xml:space="preserve">8.66798305511475</t>
   </si>
   <si>
     <t xml:space="preserve">8.62260055541992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53183555603027</t>
+    <t xml:space="preserve">8.53183650970459</t>
   </si>
   <si>
     <t xml:space="preserve">8.35030746459961</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16877937316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98725128173828</t>
+    <t xml:space="preserve">8.16878032684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98725032806396</t>
   </si>
   <si>
     <t xml:space="preserve">8.03263378143311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1233959197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25954437255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94186973571777</t>
+    <t xml:space="preserve">8.12339782714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25954341888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94186925888062</t>
   </si>
   <si>
     <t xml:space="preserve">8.3049259185791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21416091918945</t>
+    <t xml:space="preserve">8.21416187286377</t>
   </si>
   <si>
     <t xml:space="preserve">8.39568996429443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57721900939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71336460113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53202247619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25706005096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44036865234375</t>
+    <t xml:space="preserve">8.5772180557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71336555480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53202342987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25706100463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44036960601807</t>
   </si>
   <si>
     <t xml:space="preserve">9.16540718078613</t>
@@ -371,7 +371,7 @@
     <t xml:space="preserve">9.07375144958496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11957931518555</t>
+    <t xml:space="preserve">9.11958026885986</t>
   </si>
   <si>
     <t xml:space="preserve">8.98209857940674</t>
@@ -383,37 +383,37 @@
     <t xml:space="preserve">9.62367725372314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80698394775391</t>
+    <t xml:space="preserve">9.80698490142822</t>
   </si>
   <si>
     <t xml:space="preserve">9.89863872528076</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9902925491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1736011505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2652559280396</t>
+    <t xml:space="preserve">9.99029445648193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.173602104187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2652568817139</t>
   </si>
   <si>
     <t xml:space="preserve">10.3569097518921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5402193069458</t>
+    <t xml:space="preserve">10.5402173995972</t>
   </si>
   <si>
     <t xml:space="preserve">10.631872177124</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8151798248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7235260009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9068336486816</t>
+    <t xml:space="preserve">10.8151807785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7235250473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9068326950073</t>
   </si>
   <si>
     <t xml:space="preserve">10.9984884262085</t>
@@ -425,46 +425,46 @@
     <t xml:space="preserve">11.1817960739136</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734508514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4567584991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3651027679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4485635757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71533203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79879093170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24886608123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2112340927124</t>
+    <t xml:space="preserve">11.2734489440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4567594528198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3651037216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.448561668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71533107757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79878997802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24886703491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21123313903809</t>
   </si>
   <si>
     <t xml:space="preserve">9.30288791656494</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03709030151367</t>
+    <t xml:space="preserve">9.03708934783936</t>
   </si>
   <si>
     <t xml:space="preserve">9.39454174041748</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76115798950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66950511932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57784938812256</t>
+    <t xml:space="preserve">9.76115703582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6695032119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57785034179688</t>
   </si>
   <si>
     <t xml:space="preserve">10.0361194610596</t>
@@ -473,19 +473,19 @@
     <t xml:space="preserve">9.94446659088135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82552528381348</t>
+    <t xml:space="preserve">9.82552433013916</t>
   </si>
   <si>
     <t xml:space="preserve">9.73283100128174</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59379100799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96456432342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91821670532227</t>
+    <t xml:space="preserve">9.59379005432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96456336975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91821765899658</t>
   </si>
   <si>
     <t xml:space="preserve">9.54744338989258</t>
@@ -494,22 +494,22 @@
     <t xml:space="preserve">10.010910987854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1036043167114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1499519348145</t>
+    <t xml:space="preserve">10.1036052703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1499509811401</t>
   </si>
   <si>
     <t xml:space="preserve">10.1962985992432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77917671203613</t>
+    <t xml:space="preserve">9.77917766571045</t>
   </si>
   <si>
     <t xml:space="preserve">9.87187004089355</t>
   </si>
   <si>
-    <t xml:space="preserve">10.057258605957</t>
+    <t xml:space="preserve">10.0572576522827</t>
   </si>
   <si>
     <t xml:space="preserve">10.2889928817749</t>
@@ -518,52 +518,52 @@
     <t xml:space="preserve">10.4743795394897</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2426443099976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3816843032837</t>
+    <t xml:space="preserve">10.2426452636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3816862106323</t>
   </si>
   <si>
     <t xml:space="preserve">9.68648338317871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64013576507568</t>
+    <t xml:space="preserve">9.64013671875</t>
   </si>
   <si>
     <t xml:space="preserve">9.50109577178955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31570816040039</t>
+    <t xml:space="preserve">9.31570911407471</t>
   </si>
   <si>
     <t xml:space="preserve">9.23228454589844</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19520664215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25082397460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26936340332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2137451171875</t>
+    <t xml:space="preserve">9.1952075958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25082302093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.269362449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21374702453613</t>
   </si>
   <si>
     <t xml:space="preserve">9.04689788818359</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12105274200439</t>
+    <t xml:space="preserve">9.12105369567871</t>
   </si>
   <si>
     <t xml:space="preserve">9.06543636322021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97274208068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17666721343994</t>
+    <t xml:space="preserve">8.97274303436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17666816711426</t>
   </si>
   <si>
     <t xml:space="preserve">9.02835845947266</t>
@@ -572,10 +572,10 @@
     <t xml:space="preserve">8.95420360565186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71319961547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9912805557251</t>
+    <t xml:space="preserve">8.71320152282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99128150939941</t>
   </si>
   <si>
     <t xml:space="preserve">8.76881694793701</t>
@@ -584,64 +584,64 @@
     <t xml:space="preserve">8.89858818054199</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93566608428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3353395462036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9841938018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0305414199829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2159290313721</t>
+    <t xml:space="preserve">8.93566513061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3353385925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9841947555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0305404663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2159280776978</t>
   </si>
   <si>
     <t xml:space="preserve">11.4940090179443</t>
   </si>
   <si>
-    <t xml:space="preserve">11.540355682373</t>
+    <t xml:space="preserve">11.5403566360474</t>
   </si>
   <si>
     <t xml:space="preserve">11.5867033004761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6330490112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7257432937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9111299514771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9574775695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1892108917236</t>
+    <t xml:space="preserve">11.6330499649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7257423400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9111289978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9574756622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1892118453979</t>
   </si>
   <si>
     <t xml:space="preserve">12.2819051742554</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3745985031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5136375427246</t>
+    <t xml:space="preserve">12.3745994567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5136384963989</t>
   </si>
   <si>
     <t xml:space="preserve">12.3282518386841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1428642272949</t>
+    <t xml:space="preserve">12.1428651809692</t>
   </si>
   <si>
     <t xml:space="preserve">12.0965175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">12.555121421814</t>
+    <t xml:space="preserve">12.5551223754883</t>
   </si>
   <si>
     <t xml:space="preserve">12.5082750320435</t>
@@ -653,7 +653,7 @@
     <t xml:space="preserve">12.4614267349243</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4145784378052</t>
+    <t xml:space="preserve">12.4145793914795</t>
   </si>
   <si>
     <t xml:space="preserve">12.7425117492676</t>
@@ -662,10 +662,10 @@
     <t xml:space="preserve">12.6956644058228</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2271890640259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1803417205811</t>
+    <t xml:space="preserve">12.2271900177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1803426742554</t>
   </si>
   <si>
     <t xml:space="preserve">12.3208847045898</t>
@@ -674,103 +674,103 @@
     <t xml:space="preserve">12.274037361145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8362073898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7893590927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6019687652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9299020767212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8830537796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0704431533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6794624328613</t>
+    <t xml:space="preserve">12.8362064361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7893581390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6019697189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9299011230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8830547332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.07044506073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.679461479187</t>
   </si>
   <si>
     <t xml:space="preserve">13.8668508529663</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0542402267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3353252410889</t>
+    <t xml:space="preserve">14.0542411804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3353261947632</t>
   </si>
   <si>
     <t xml:space="preserve">14.5695638656616</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2254276275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1317319869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7569532394409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0380363464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1785802841187</t>
+    <t xml:space="preserve">15.2254285812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1317329406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7569522857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0380382537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.178581237793</t>
   </si>
   <si>
     <t xml:space="preserve">15.3191232681274</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8974952697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4596652984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4128189086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5533590316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0686836242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8650894165039</t>
+    <t xml:space="preserve">14.8974943161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4596662521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4128179550171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5533609390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0686817169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8650913238525</t>
   </si>
   <si>
     <t xml:space="preserve">17.0056324005127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7713928222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1930198669434</t>
+    <t xml:space="preserve">16.7713947296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.193021774292</t>
   </si>
   <si>
     <t xml:space="preserve">17.0524787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9587860107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7245464324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6308498382568</t>
+    <t xml:space="preserve">16.9587841033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7245483398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6308517456055</t>
   </si>
   <si>
     <t xml:space="preserve">16.5371570587158</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5840072631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2092227935791</t>
+    <t xml:space="preserve">16.5840034484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2092247009277</t>
   </si>
   <si>
     <t xml:space="preserve">16.2560710906982</t>
@@ -782,52 +782,52 @@
     <t xml:space="preserve">16.396614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3029193878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8344440460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1155281066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0218372344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1623764038086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9749870300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7407474517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4434623718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9119358062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0993270874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.677698135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8182430267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2722749710083</t>
+    <t xml:space="preserve">16.3029174804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8344449996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1155300140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0218353271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1623783111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.974986076355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7407493591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4434604644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.911937713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0993251800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6777000427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.818244934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.272274017334</t>
   </si>
   <si>
     <t xml:space="preserve">15.084885597229</t>
   </si>
   <si>
-    <t xml:space="preserve">14.991189956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8038015365601</t>
+    <t xml:space="preserve">14.9911909103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8038005828857</t>
   </si>
   <si>
     <t xml:space="preserve">14.4758682250977</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">14.1010885238647</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2884788513184</t>
+    <t xml:space="preserve">14.288477897644</t>
   </si>
   <si>
     <t xml:space="preserve">14.5227155685425</t>
@@ -857,22 +857,22 @@
     <t xml:space="preserve">14.0073928833008</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7263078689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1479358673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4290208816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6164102554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7731552124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3515291213989</t>
+    <t xml:space="preserve">13.7263088226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1479368209839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4290199279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6164112091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7731561660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3515281677246</t>
   </si>
   <si>
     <t xml:space="preserve">13.3046808242798</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">13.3983764648438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0235967636108</t>
+    <t xml:space="preserve">13.0235958099365</t>
   </si>
   <si>
     <t xml:space="preserve">13.1172914505005</t>
@@ -890,10 +890,10 @@
     <t xml:space="preserve">12.976749420166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.367733001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0866470336914</t>
+    <t xml:space="preserve">12.3677320480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0866460800171</t>
   </si>
   <si>
     <t xml:space="preserve">11.9929523468018</t>
@@ -902,37 +902,37 @@
     <t xml:space="preserve">11.8992576599121</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0398006439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1334934234619</t>
+    <t xml:space="preserve">12.0397987365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1334943771362</t>
   </si>
   <si>
     <t xml:space="preserve">11.4776306152344</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2433929443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3839349746704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6650190353394</t>
+    <t xml:space="preserve">11.2433938980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3839340209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.665020942688</t>
   </si>
   <si>
     <t xml:space="preserve">11.4307823181152</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9623079299927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7280702590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1965446472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5713262557983</t>
+    <t xml:space="preserve">10.9623069763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7280712127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1965456008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.571325302124</t>
   </si>
   <si>
     <t xml:space="preserve">11.3370876312256</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">11.7118673324585</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7587146759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8055629730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0091562271118</t>
+    <t xml:space="preserve">11.7587156295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8055639266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0091552734375</t>
   </si>
   <si>
     <t xml:space="preserve">9.46318912506104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33884906768799</t>
+    <t xml:space="preserve">8.3388500213623</t>
   </si>
   <si>
     <t xml:space="preserve">8.57308673858643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31074047088623</t>
+    <t xml:space="preserve">8.31074142456055</t>
   </si>
   <si>
     <t xml:space="preserve">8.45128345489502</t>
@@ -977,16 +977,16 @@
     <t xml:space="preserve">8.32948017120361</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25452518463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43254470825195</t>
+    <t xml:space="preserve">8.25452423095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43254566192627</t>
   </si>
   <si>
     <t xml:space="preserve">8.47002220153809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32010936737061</t>
+    <t xml:space="preserve">8.32011127471924</t>
   </si>
   <si>
     <t xml:space="preserve">8.20767688751221</t>
@@ -995,22 +995,22 @@
     <t xml:space="preserve">8.08587265014648</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78604984283447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49559497833252</t>
+    <t xml:space="preserve">7.78604936599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49559545516968</t>
   </si>
   <si>
     <t xml:space="preserve">7.33631372451782</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23324966430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83289575576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9078516960144</t>
+    <t xml:space="preserve">7.23324918746948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83289623260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90785264968872</t>
   </si>
   <si>
     <t xml:space="preserve">7.50496482849121</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">7.12081527709961</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28009653091431</t>
+    <t xml:space="preserve">7.28009700775146</t>
   </si>
   <si>
     <t xml:space="preserve">6.98027324676514</t>
@@ -1034,10 +1034,10 @@
     <t xml:space="preserve">7.06459808349609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0271201133728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34568357467651</t>
+    <t xml:space="preserve">7.02712059020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34568309783936</t>
   </si>
   <si>
     <t xml:space="preserve">7.5424427986145</t>
@@ -1046,19 +1046,19 @@
     <t xml:space="preserve">8.19830703735352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21704769134521</t>
+    <t xml:space="preserve">8.2170467376709</t>
   </si>
   <si>
     <t xml:space="preserve">8.65194320678711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46116161346436</t>
+    <t xml:space="preserve">8.46116256713867</t>
   </si>
   <si>
     <t xml:space="preserve">8.53747367858887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68056106567383</t>
+    <t xml:space="preserve">8.68056201934814</t>
   </si>
   <si>
     <t xml:space="preserve">8.77595138549805</t>
@@ -1073,16 +1073,16 @@
     <t xml:space="preserve">8.66148281097412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49931716918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42300605773926</t>
+    <t xml:space="preserve">8.49931812286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42300510406494</t>
   </si>
   <si>
     <t xml:space="preserve">8.39438915252686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.604248046875</t>
+    <t xml:space="preserve">8.60424900054932</t>
   </si>
   <si>
     <t xml:space="preserve">8.48977851867676</t>
@@ -1094,19 +1094,19 @@
     <t xml:space="preserve">8.12729454040527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89835596084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10821628570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8411226272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33715438842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20360660552979</t>
+    <t xml:space="preserve">7.89835643768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10821723937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84112215042114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33715343475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2036075592041</t>
   </si>
   <si>
     <t xml:space="preserve">8.06052017211914</t>
@@ -1118,40 +1118,40 @@
     <t xml:space="preserve">8.07005977630615</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92697381973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98420763015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30853652954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26084136962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2703800201416</t>
+    <t xml:space="preserve">7.92697429656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98420810699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30853748321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26084041595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27038097381592</t>
   </si>
   <si>
     <t xml:space="preserve">8.18452930450439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03190326690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96513032913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86019992828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8697395324707</t>
+    <t xml:space="preserve">8.03190422058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96512985229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86020040512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86973905563354</t>
   </si>
   <si>
     <t xml:space="preserve">7.71711397171021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91743421554565</t>
+    <t xml:space="preserve">7.91743516921997</t>
   </si>
   <si>
     <t xml:space="preserve">7.76480960845947</t>
@@ -1160,31 +1160,31 @@
     <t xml:space="preserve">7.72665309906006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65034055709839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63126182556152</t>
+    <t xml:space="preserve">7.65034103393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63126230239868</t>
   </si>
   <si>
     <t xml:space="preserve">7.65987920761108</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16545104980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32761478424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11775588989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93651151657104</t>
+    <t xml:space="preserve">8.16545009613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32761383056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11775493621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9365119934082</t>
   </si>
   <si>
     <t xml:space="preserve">8.19406795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23222351074219</t>
+    <t xml:space="preserve">8.2322244644165</t>
   </si>
   <si>
     <t xml:space="preserve">8.31807613372803</t>
@@ -1208,7 +1208,7 @@
     <t xml:space="preserve">8.34669303894043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95559072494507</t>
+    <t xml:space="preserve">7.95559167861938</t>
   </si>
   <si>
     <t xml:space="preserve">7.77434825897217</t>
@@ -1217,40 +1217,40 @@
     <t xml:space="preserve">7.82204389572144</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97466802597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01282405853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05098056793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67895793914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73619174957275</t>
+    <t xml:space="preserve">7.97466850280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01282501220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05098152160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67895746231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73619222640991</t>
   </si>
   <si>
     <t xml:space="preserve">7.6980357170105</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51679372787476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59310579299927</t>
+    <t xml:space="preserve">7.5167932510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59310626983643</t>
   </si>
   <si>
     <t xml:space="preserve">7.44048070907593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53587198257446</t>
+    <t xml:space="preserve">7.5358715057373</t>
   </si>
   <si>
     <t xml:space="preserve">7.62172269821167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52633237838745</t>
+    <t xml:space="preserve">7.52633190155029</t>
   </si>
   <si>
     <t xml:space="preserve">7.34508991241455</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">7.20200395584106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18292570114136</t>
+    <t xml:space="preserve">7.18292617797852</t>
   </si>
   <si>
     <t xml:space="preserve">7.14476919174194</t>
@@ -1271,22 +1271,22 @@
     <t xml:space="preserve">7.23062086105347</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15430784225464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24969911575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24016046524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46909761428833</t>
+    <t xml:space="preserve">7.1543083190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24969863891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24015998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46909809112549</t>
   </si>
   <si>
     <t xml:space="preserve">7.41186332702637</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45001935958862</t>
+    <t xml:space="preserve">7.45001983642578</t>
   </si>
   <si>
     <t xml:space="preserve">7.28785514831543</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">7.3355507850647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61218357086182</t>
+    <t xml:space="preserve">7.61218452453613</t>
   </si>
   <si>
     <t xml:space="preserve">7.90789556503296</t>
@@ -1310,40 +1310,40 @@
     <t xml:space="preserve">7.45955896377563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70757436752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87927865982056</t>
+    <t xml:space="preserve">7.70757484436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8792781829834</t>
   </si>
   <si>
     <t xml:space="preserve">7.99374723434448</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75527048110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81250476837158</t>
+    <t xml:space="preserve">7.75527000427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81250429153442</t>
   </si>
   <si>
     <t xml:space="preserve">7.79342699050903</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80296611785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85066080093384</t>
+    <t xml:space="preserve">7.80296564102173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85066032409668</t>
   </si>
   <si>
     <t xml:space="preserve">7.74573087692261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83158349990845</t>
+    <t xml:space="preserve">7.83158302307129</t>
   </si>
   <si>
     <t xml:space="preserve">7.66941833496094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60264492034912</t>
+    <t xml:space="preserve">7.60264444351196</t>
   </si>
   <si>
     <t xml:space="preserve">7.58356666564941</t>
@@ -1355,31 +1355,31 @@
     <t xml:space="preserve">8.00328636169434</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78388738632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36416816711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10661315917969</t>
+    <t xml:space="preserve">7.78388690948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3641676902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10661268234253</t>
   </si>
   <si>
     <t xml:space="preserve">7.27831649780273</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08753490447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05891752243042</t>
+    <t xml:space="preserve">7.08753442764282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05891799926758</t>
   </si>
   <si>
     <t xml:space="preserve">7.50372648239136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98721408843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02589225769043</t>
+    <t xml:space="preserve">7.98721361160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02589321136475</t>
   </si>
   <si>
     <t xml:space="preserve">8.04523086547852</t>
@@ -1391,25 +1391,25 @@
     <t xml:space="preserve">8.07424163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12258911132812</t>
+    <t xml:space="preserve">8.12259006500244</t>
   </si>
   <si>
     <t xml:space="preserve">8.05490112304688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94853496551514</t>
+    <t xml:space="preserve">7.94853448867798</t>
   </si>
   <si>
     <t xml:space="preserve">8.06457138061523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08390998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97754430770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93886518478394</t>
+    <t xml:space="preserve">8.08391094207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97754383087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93886423110962</t>
   </si>
   <si>
     <t xml:space="preserve">7.79381895065308</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">7.68745088577271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63910293579102</t>
+    <t xml:space="preserve">7.63910245895386</t>
   </si>
   <si>
     <t xml:space="preserve">7.73579978942871</t>
@@ -1436,10 +1436,10 @@
     <t xml:space="preserve">7.90985584259033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85183668136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83249759674072</t>
+    <t xml:space="preserve">7.85183715820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83249807357788</t>
   </si>
   <si>
     <t xml:space="preserve">7.81315755844116</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">7.80348825454712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78414916992188</t>
+    <t xml:space="preserve">7.78414869308472</t>
   </si>
   <si>
     <t xml:space="preserve">7.6681113243103</t>
@@ -1460,13 +1460,13 @@
     <t xml:space="preserve">7.71646022796631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75513982772827</t>
+    <t xml:space="preserve">7.75514030456543</t>
   </si>
   <si>
     <t xml:space="preserve">7.74547004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86150693893433</t>
+    <t xml:space="preserve">7.86150646209717</t>
   </si>
   <si>
     <t xml:space="preserve">7.89051580429077</t>
@@ -1484,10 +1484,10 @@
     <t xml:space="preserve">8.09358024597168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13225936889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1515998840332</t>
+    <t xml:space="preserve">8.1322603225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15159893035889</t>
   </si>
   <si>
     <t xml:space="preserve">8.1129207611084</t>
@@ -1496,10 +1496,10 @@
     <t xml:space="preserve">8.03556251525879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92919492721558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69712066650391</t>
+    <t xml:space="preserve">7.92919540405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69712114334106</t>
   </si>
   <si>
     <t xml:space="preserve">7.60042381286621</t>
@@ -1508,10 +1508,10 @@
     <t xml:space="preserve">7.88084602355957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55207443237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40702819824219</t>
+    <t xml:space="preserve">7.55207490921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40702867507935</t>
   </si>
   <si>
     <t xml:space="preserve">7.34900999069214</t>
@@ -1520,16 +1520,16 @@
     <t xml:space="preserve">7.37801933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43603754043579</t>
+    <t xml:space="preserve">7.43603801727295</t>
   </si>
   <si>
     <t xml:space="preserve">7.41669797897339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52306604385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36834955215454</t>
+    <t xml:space="preserve">7.5230655670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36834907531738</t>
   </si>
   <si>
     <t xml:space="preserve">7.542405128479</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">7.4843864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70679044723511</t>
+    <t xml:space="preserve">7.70679092407227</t>
   </si>
   <si>
     <t xml:space="preserve">7.64877223968506</t>
@@ -1556,10 +1556,10 @@
     <t xml:space="preserve">7.59075355529785</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95820426940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96787405014038</t>
+    <t xml:space="preserve">7.95820331573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96787357330322</t>
   </si>
   <si>
     <t xml:space="preserve">7.90018606185913</t>
@@ -1577,10 +1577,10 @@
     <t xml:space="preserve">8.19027900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29664611816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45136165618896</t>
+    <t xml:space="preserve">8.29664516448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45136070251465</t>
   </si>
   <si>
     <t xml:space="preserve">8.48037147521973</t>
@@ -1607,19 +1607,19 @@
     <t xml:space="preserve">8.50938034057617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4223518371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54805946350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55772972106934</t>
+    <t xml:space="preserve">8.42235279083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54805850982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55772876739502</t>
   </si>
   <si>
     <t xml:space="preserve">8.52871990203857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68343448638916</t>
+    <t xml:space="preserve">8.68343544006348</t>
   </si>
   <si>
     <t xml:space="preserve">8.76079368591309</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">8.65442562103271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75112438201904</t>
+    <t xml:space="preserve">8.75112342834473</t>
   </si>
   <si>
     <t xml:space="preserve">8.70277500152588</t>
@@ -1652,10 +1652,10 @@
     <t xml:space="preserve">8.63508701324463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32565402984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31598472595215</t>
+    <t xml:space="preserve">8.32565498352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31598567962646</t>
   </si>
   <si>
     <t xml:space="preserve">8.30631542205811</t>
@@ -63322,7 +63322,7 @@
     </row>
     <row r="2336">
       <c r="A2336" s="1" t="n">
-        <v>46020.6911921296</v>
+        <v>46020.3333333333</v>
       </c>
       <c r="B2336" t="n">
         <v>13929</v>
@@ -63343,6 +63343,32 @@
         <v>753</v>
       </c>
       <c r="H2336" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2337">
+      <c r="A2337" s="1" t="n">
+        <v>46021.6913078704</v>
+      </c>
+      <c r="B2337" t="n">
+        <v>10714</v>
+      </c>
+      <c r="C2337" t="n">
+        <v>9.60000038146973</v>
+      </c>
+      <c r="D2337" t="n">
+        <v>9.4399995803833</v>
+      </c>
+      <c r="E2337" t="n">
+        <v>9.46000003814697</v>
+      </c>
+      <c r="F2337" t="n">
+        <v>9.57999992370605</v>
+      </c>
+      <c r="G2337" t="s">
+        <v>751</v>
+      </c>
+      <c r="H2337" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -44,13 +44,13 @@
     <t xml:space="preserve">FF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98565769195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08549785614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24887180328369</t>
+    <t xml:space="preserve">8.98565673828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08549880981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24887371063232</t>
   </si>
   <si>
     <t xml:space="preserve">9.09457492828369</t>
@@ -59,16 +59,16 @@
     <t xml:space="preserve">9.12180328369141</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03103923797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95389080047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89943218231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89489269256592</t>
+    <t xml:space="preserve">9.03104019165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95388984680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8994312286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89489364624023</t>
   </si>
   <si>
     <t xml:space="preserve">8.84951114654541</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">8.85858726501465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87674140930176</t>
+    <t xml:space="preserve">8.87674045562744</t>
   </si>
   <si>
     <t xml:space="preserve">8.767822265625</t>
@@ -86,10 +86,10 @@
     <t xml:space="preserve">8.86766529083252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04919242858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23072147369385</t>
+    <t xml:space="preserve">9.04919338226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23072242736816</t>
   </si>
   <si>
     <t xml:space="preserve">9.11272811889648</t>
@@ -101,10 +101,10 @@
     <t xml:space="preserve">8.91304683685303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92212295532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00381183624268</t>
+    <t xml:space="preserve">8.92212390899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00380992889404</t>
   </si>
   <si>
     <t xml:space="preserve">9.15811061859131</t>
@@ -116,22 +116,22 @@
     <t xml:space="preserve">9.43947887420654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54839706420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62100791931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80253505706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71177101135254</t>
+    <t xml:space="preserve">9.54839611053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62100696563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80253601074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71177196502686</t>
   </si>
   <si>
     <t xml:space="preserve">9.56654834747314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58470249176025</t>
+    <t xml:space="preserve">9.58470153808594</t>
   </si>
   <si>
     <t xml:space="preserve">9.57562446594238</t>
@@ -140,19 +140,19 @@
     <t xml:space="preserve">9.53024196624756</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50301361083984</t>
+    <t xml:space="preserve">9.50301265716553</t>
   </si>
   <si>
     <t xml:space="preserve">9.60285377502441</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63916110992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79345893859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95683479309082</t>
+    <t xml:space="preserve">9.63915920257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79345798492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95683574676514</t>
   </si>
   <si>
     <t xml:space="preserve">9.93868255615234</t>
@@ -161,31 +161,31 @@
     <t xml:space="preserve">9.98406410217285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73900032043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76623058319092</t>
+    <t xml:space="preserve">9.73900127410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7662296295166</t>
   </si>
   <si>
     <t xml:space="preserve">9.74807739257812</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75715160369873</t>
+    <t xml:space="preserve">9.75715351104736</t>
   </si>
   <si>
     <t xml:space="preserve">9.64823627471924</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82068729400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70269393920898</t>
+    <t xml:space="preserve">9.82068824768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7026948928833</t>
   </si>
   <si>
     <t xml:space="preserve">9.72084808349609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67546653747559</t>
+    <t xml:space="preserve">9.67546558380127</t>
   </si>
   <si>
     <t xml:space="preserve">9.66638851165771</t>
@@ -197,61 +197,61 @@
     <t xml:space="preserve">9.65731239318848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68454360961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81161308288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82976531982422</t>
+    <t xml:space="preserve">9.68454265594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81161212921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8297643661499</t>
   </si>
   <si>
     <t xml:space="preserve">9.8479175567627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83884143829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72992420196533</t>
+    <t xml:space="preserve">9.83884048461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72992515563965</t>
   </si>
   <si>
     <t xml:space="preserve">9.78438186645508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55747222900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34871387481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33963775634766</t>
+    <t xml:space="preserve">9.55747318267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34871482849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33963680267334</t>
   </si>
   <si>
     <t xml:space="preserve">9.27610301971436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25795078277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19441509246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18533897399902</t>
+    <t xml:space="preserve">9.25794982910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19441699981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18533992767334</t>
   </si>
   <si>
     <t xml:space="preserve">9.41224956512451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22164440155029</t>
+    <t xml:space="preserve">9.22164535522461</t>
   </si>
   <si>
     <t xml:space="preserve">9.31240844726562</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26702785491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29425525665283</t>
+    <t xml:space="preserve">9.2670259475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29425621032715</t>
   </si>
   <si>
     <t xml:space="preserve">9.28518009185791</t>
@@ -263,19 +263,19 @@
     <t xml:space="preserve">9.36686706542969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3850212097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45763206481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39409732818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48486137390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49393844604492</t>
+    <t xml:space="preserve">9.38501930236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45763111114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39409637451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48486042022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49393653869629</t>
   </si>
   <si>
     <t xml:space="preserve">9.44855499267578</t>
@@ -290,10 +290,10 @@
     <t xml:space="preserve">9.14903259277344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21256732940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20349216461182</t>
+    <t xml:space="preserve">9.21256828308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20349407196045</t>
   </si>
   <si>
     <t xml:space="preserve">9.13088035583496</t>
@@ -302,40 +302,40 @@
     <t xml:space="preserve">9.1399564743042</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94027519226074</t>
+    <t xml:space="preserve">8.94027614593506</t>
   </si>
   <si>
     <t xml:space="preserve">8.80412864685059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75874710083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66798305511475</t>
+    <t xml:space="preserve">8.75874614715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66798400878906</t>
   </si>
   <si>
     <t xml:space="preserve">8.62260055541992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53183650970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35030746459961</t>
+    <t xml:space="preserve">8.53183746337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35030937194824</t>
   </si>
   <si>
     <t xml:space="preserve">8.16878032684326</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98725032806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03263378143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12339782714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25954341888428</t>
+    <t xml:space="preserve">7.98725175857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03263473510742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12339687347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25954437255859</t>
   </si>
   <si>
     <t xml:space="preserve">7.94186925888062</t>
@@ -347,73 +347,73 @@
     <t xml:space="preserve">8.21416187286377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39568996429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5772180557251</t>
+    <t xml:space="preserve">8.39569091796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57721900939941</t>
   </si>
   <si>
     <t xml:space="preserve">8.71336555480957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53202342987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25706100463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44036960601807</t>
+    <t xml:space="preserve">9.53202247619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25706195831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44036865234375</t>
   </si>
   <si>
     <t xml:space="preserve">9.16540718078613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07375144958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11958026885986</t>
+    <t xml:space="preserve">9.07375335693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11957931518555</t>
   </si>
   <si>
     <t xml:space="preserve">8.98209857940674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02792549133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62367725372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80698490142822</t>
+    <t xml:space="preserve">9.02792644500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62367630004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80698585510254</t>
   </si>
   <si>
     <t xml:space="preserve">9.89863872528076</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99029445648193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.173602104187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2652568817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3569097518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5402173995972</t>
+    <t xml:space="preserve">9.99029350280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1736011505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2652549743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3569107055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5402183532715</t>
   </si>
   <si>
     <t xml:space="preserve">10.631872177124</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8151807785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7235250473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9068326950073</t>
+    <t xml:space="preserve">10.8151798248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7235260009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9068336486816</t>
   </si>
   <si>
     <t xml:space="preserve">10.9984884262085</t>
@@ -422,19 +422,19 @@
     <t xml:space="preserve">11.090142250061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1817960739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2734489440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4567594528198</t>
+    <t xml:space="preserve">11.1817970275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2734498977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4567584991455</t>
   </si>
   <si>
     <t xml:space="preserve">11.3651037216187</t>
   </si>
   <si>
-    <t xml:space="preserve">10.448561668396</t>
+    <t xml:space="preserve">10.4485635757446</t>
   </si>
   <si>
     <t xml:space="preserve">9.71533107757568</t>
@@ -443,49 +443,49 @@
     <t xml:space="preserve">8.79878997802734</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24886703491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21123313903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30288791656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03708934783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39454174041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76115703582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6695032119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57785034179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0361194610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94446659088135</t>
+    <t xml:space="preserve">8.24886512756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2112340927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30288887023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03709125518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39454078674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76115798950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66950416564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57784938812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0361204147339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94446563720703</t>
   </si>
   <si>
     <t xml:space="preserve">9.82552433013916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73283100128174</t>
+    <t xml:space="preserve">9.73283004760742</t>
   </si>
   <si>
     <t xml:space="preserve">9.59379005432129</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96456336975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91821765899658</t>
+    <t xml:space="preserve">9.96456527709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9182186126709</t>
   </si>
   <si>
     <t xml:space="preserve">9.54744338989258</t>
@@ -497,7 +497,7 @@
     <t xml:space="preserve">10.1036052703857</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1499509811401</t>
+    <t xml:space="preserve">10.1499519348145</t>
   </si>
   <si>
     <t xml:space="preserve">10.1962985992432</t>
@@ -506,22 +506,22 @@
     <t xml:space="preserve">9.77917766571045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87187004089355</t>
+    <t xml:space="preserve">9.87187099456787</t>
   </si>
   <si>
     <t xml:space="preserve">10.0572576522827</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2889928817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4743795394897</t>
+    <t xml:space="preserve">10.2889919281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4743804931641</t>
   </si>
   <si>
     <t xml:space="preserve">10.2426452636719</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3816862106323</t>
+    <t xml:space="preserve">10.381685256958</t>
   </si>
   <si>
     <t xml:space="preserve">9.68648338317871</t>
@@ -536,7 +536,7 @@
     <t xml:space="preserve">9.31570911407471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23228454589844</t>
+    <t xml:space="preserve">9.23228359222412</t>
   </si>
   <si>
     <t xml:space="preserve">9.1952075958252</t>
@@ -548,31 +548,31 @@
     <t xml:space="preserve">9.269362449646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21374702453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04689788818359</t>
+    <t xml:space="preserve">9.21374607086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04689693450928</t>
   </si>
   <si>
     <t xml:space="preserve">9.12105369567871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06543636322021</t>
+    <t xml:space="preserve">9.0654354095459</t>
   </si>
   <si>
     <t xml:space="preserve">8.97274303436279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17666816711426</t>
+    <t xml:space="preserve">9.17666912078857</t>
   </si>
   <si>
     <t xml:space="preserve">9.02835845947266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95420360565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71320152282715</t>
+    <t xml:space="preserve">8.95420265197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71320056915283</t>
   </si>
   <si>
     <t xml:space="preserve">8.99128150939941</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">8.76881694793701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89858818054199</t>
+    <t xml:space="preserve">8.89858722686768</t>
   </si>
   <si>
     <t xml:space="preserve">8.93566513061523</t>
@@ -590,46 +590,46 @@
     <t xml:space="preserve">10.3353385925293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9841947555542</t>
+    <t xml:space="preserve">10.9841938018799</t>
   </si>
   <si>
     <t xml:space="preserve">11.0305404663086</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2159280776978</t>
+    <t xml:space="preserve">11.2159290313721</t>
   </si>
   <si>
     <t xml:space="preserve">11.4940090179443</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5403566360474</t>
+    <t xml:space="preserve">11.540355682373</t>
   </si>
   <si>
     <t xml:space="preserve">11.5867033004761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6330499649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7257423400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9111289978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9574756622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1892118453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2819051742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3745994567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5136384963989</t>
+    <t xml:space="preserve">11.6330490112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7257413864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9111299514771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9574766159058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1892099380493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2819042205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3745985031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5136394500732</t>
   </si>
   <si>
     <t xml:space="preserve">12.3282518386841</t>
@@ -650,85 +650,85 @@
     <t xml:space="preserve">12.6488170623779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4614267349243</t>
+    <t xml:space="preserve">12.4614276885986</t>
   </si>
   <si>
     <t xml:space="preserve">12.4145793914795</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7425117492676</t>
+    <t xml:space="preserve">12.7425127029419</t>
   </si>
   <si>
     <t xml:space="preserve">12.6956644058228</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2271900177002</t>
+    <t xml:space="preserve">12.2271890640259</t>
   </si>
   <si>
     <t xml:space="preserve">12.1803426742554</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3208847045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.274037361145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8362064361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7893581390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6019697189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9299011230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8830547332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.07044506073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.679461479187</t>
+    <t xml:space="preserve">12.3208837509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2740383148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8362073898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7893590927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6019687652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9299020767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8830537796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0704441070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6794605255127</t>
   </si>
   <si>
     <t xml:space="preserve">13.8668508529663</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0542411804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3353261947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5695638656616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2254285812378</t>
+    <t xml:space="preserve">14.0542402267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3353252410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5695629119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2254276275635</t>
   </si>
   <si>
     <t xml:space="preserve">15.1317329406738</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7569522857666</t>
+    <t xml:space="preserve">14.7569532394409</t>
   </si>
   <si>
     <t xml:space="preserve">15.0380382537842</t>
   </si>
   <si>
-    <t xml:space="preserve">15.178581237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3191232681274</t>
+    <t xml:space="preserve">15.1785802841187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3191242218018</t>
   </si>
   <si>
     <t xml:space="preserve">14.8974943161011</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4596662521362</t>
+    <t xml:space="preserve">15.4596652984619</t>
   </si>
   <si>
     <t xml:space="preserve">15.4128179550171</t>
@@ -737,10 +737,10 @@
     <t xml:space="preserve">15.5533609390259</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0686817169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8650913238525</t>
+    <t xml:space="preserve">16.0686836242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8650875091553</t>
   </si>
   <si>
     <t xml:space="preserve">17.0056324005127</t>
@@ -749,7 +749,7 @@
     <t xml:space="preserve">16.7713947296143</t>
   </si>
   <si>
-    <t xml:space="preserve">17.193021774292</t>
+    <t xml:space="preserve">17.1930236816406</t>
   </si>
   <si>
     <t xml:space="preserve">17.0524787902832</t>
@@ -758,22 +758,22 @@
     <t xml:space="preserve">16.9587841033936</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7245483398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6308517456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5371570587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5840034484863</t>
+    <t xml:space="preserve">16.7245464324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6308536529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5371551513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.584005355835</t>
   </si>
   <si>
     <t xml:space="preserve">16.2092247009277</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2560710906982</t>
+    <t xml:space="preserve">16.2560749053955</t>
   </si>
   <si>
     <t xml:space="preserve">17.1461734771729</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">16.3029174804688</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8344449996948</t>
+    <t xml:space="preserve">15.8344440460205</t>
   </si>
   <si>
     <t xml:space="preserve">16.1155300140381</t>
@@ -794,25 +794,25 @@
     <t xml:space="preserve">16.0218353271484</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1623783111572</t>
+    <t xml:space="preserve">16.1623764038086</t>
   </si>
   <si>
     <t xml:space="preserve">15.974986076355</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7407493591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4434604644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.911937713623</t>
+    <t xml:space="preserve">15.7407503128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4434623718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9119338989258</t>
   </si>
   <si>
     <t xml:space="preserve">17.0993251800537</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6777000427246</t>
+    <t xml:space="preserve">16.677698135376</t>
   </si>
   <si>
     <t xml:space="preserve">16.818244934082</t>
@@ -821,13 +821,13 @@
     <t xml:space="preserve">15.272274017334</t>
   </si>
   <si>
-    <t xml:space="preserve">15.084885597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9911909103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8038005828857</t>
+    <t xml:space="preserve">15.0848846435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.991189956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8037996292114</t>
   </si>
   <si>
     <t xml:space="preserve">14.4758682250977</t>
@@ -842,49 +842,49 @@
     <t xml:space="preserve">14.288477897644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5227155685425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9605464935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2416305541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1947822570801</t>
+    <t xml:space="preserve">14.5227146148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9605445861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2416296005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1947832107544</t>
   </si>
   <si>
     <t xml:space="preserve">14.0073928833008</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7263088226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1479368209839</t>
+    <t xml:space="preserve">13.7263078689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1479358673096</t>
   </si>
   <si>
     <t xml:space="preserve">14.4290199279785</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6164112091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7731561660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3515281677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3046808242798</t>
+    <t xml:space="preserve">14.6164102554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7731552124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3515291213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3046817779541</t>
   </si>
   <si>
     <t xml:space="preserve">13.3983764648438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0235958099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1172914505005</t>
+    <t xml:space="preserve">13.0235967636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1172924041748</t>
   </si>
   <si>
     <t xml:space="preserve">12.976749420166</t>
@@ -893,10 +893,10 @@
     <t xml:space="preserve">12.3677320480347</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0866460800171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9929523468018</t>
+    <t xml:space="preserve">12.0866470336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9929533004761</t>
   </si>
   <si>
     <t xml:space="preserve">11.8992576599121</t>
@@ -905,58 +905,58 @@
     <t xml:space="preserve">12.0397987365723</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1334943771362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4776306152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2433938980103</t>
+    <t xml:space="preserve">12.1334934234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4776287078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2433929443359</t>
   </si>
   <si>
     <t xml:space="preserve">11.3839340209961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.665020942688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4307823181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9623069763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7280712127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1965456008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.571325302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3370876312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2902402877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7118673324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7587156295776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8055639266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0091552734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46318912506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3388500213623</t>
+    <t xml:space="preserve">11.6650190353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4307832717896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9623079299927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7280702590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1965436935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5713243484497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3370885848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2902393341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7118682861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.758713722229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8055629730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0091543197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46319007873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33884906768799</t>
   </si>
   <si>
     <t xml:space="preserve">8.57308673858643</t>
@@ -971,16 +971,16 @@
     <t xml:space="preserve">8.61993408203125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44191455841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32948017120361</t>
+    <t xml:space="preserve">8.44191360473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32948112487793</t>
   </si>
   <si>
     <t xml:space="preserve">8.25452423095703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43254566192627</t>
+    <t xml:space="preserve">8.43254375457764</t>
   </si>
   <si>
     <t xml:space="preserve">8.47002220153809</t>
@@ -995,52 +995,52 @@
     <t xml:space="preserve">8.08587265014648</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78604936599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49559545516968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33631372451782</t>
+    <t xml:space="preserve">7.78605031967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49559497833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33631420135498</t>
   </si>
   <si>
     <t xml:space="preserve">7.23324918746948</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83289623260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90785264968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50496482849121</t>
+    <t xml:space="preserve">7.83289670944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90785217285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50496530532837</t>
   </si>
   <si>
     <t xml:space="preserve">7.37379169464111</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12081527709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28009700775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98027324676514</t>
+    <t xml:space="preserve">7.12081480026245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28009653091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98027229309082</t>
   </si>
   <si>
     <t xml:space="preserve">6.93342542648315</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06459808349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02712059020996</t>
+    <t xml:space="preserve">7.06459856033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0271201133728</t>
   </si>
   <si>
     <t xml:space="preserve">7.34568309783936</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5424427986145</t>
+    <t xml:space="preserve">7.54244232177734</t>
   </si>
   <si>
     <t xml:space="preserve">8.19830703735352</t>
@@ -1055,19 +1055,19 @@
     <t xml:space="preserve">8.46116256713867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53747367858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68056201934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77595138549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84272575378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825622558594</t>
+    <t xml:space="preserve">8.53747463226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68056106567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77595233917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8427267074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825527191162</t>
   </si>
   <si>
     <t xml:space="preserve">8.66148281097412</t>
@@ -1082,10 +1082,10 @@
     <t xml:space="preserve">8.39438915252686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60424900054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48977851867676</t>
+    <t xml:space="preserve">8.604248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48977947235107</t>
   </si>
   <si>
     <t xml:space="preserve">8.29899787902832</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">7.89835643768311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10821723937988</t>
+    <t xml:space="preserve">8.10821628570557</t>
   </si>
   <si>
     <t xml:space="preserve">7.84112215042114</t>
@@ -1115,34 +1115,34 @@
     <t xml:space="preserve">8.07959938049316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07005977630615</t>
+    <t xml:space="preserve">8.07005882263184</t>
   </si>
   <si>
     <t xml:space="preserve">7.92697429656982</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98420810699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30853748321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26084041595459</t>
+    <t xml:space="preserve">7.98420858383179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30853652954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26084136962891</t>
   </si>
   <si>
     <t xml:space="preserve">8.27038097381592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18452930450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03190422058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96512985229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86020040512085</t>
+    <t xml:space="preserve">8.18452835083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03190326690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96513080596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86019992828369</t>
   </si>
   <si>
     <t xml:space="preserve">7.86973905563354</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">7.91743516921997</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76480960845947</t>
+    <t xml:space="preserve">7.76481008529663</t>
   </si>
   <si>
     <t xml:space="preserve">7.72665309906006</t>
@@ -1166,19 +1166,19 @@
     <t xml:space="preserve">7.63126230239868</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65987920761108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16545009613037</t>
+    <t xml:space="preserve">7.65987968444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16545104980469</t>
   </si>
   <si>
     <t xml:space="preserve">8.32761383056641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11775493621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9365119934082</t>
+    <t xml:space="preserve">8.11775588989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93651247024536</t>
   </si>
   <si>
     <t xml:space="preserve">8.19406795501709</t>
@@ -1187,10 +1187,10 @@
     <t xml:space="preserve">8.2322244644165</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31807613372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15591239929199</t>
+    <t xml:space="preserve">8.31807518005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15591144561768</t>
   </si>
   <si>
     <t xml:space="preserve">8.22268486022949</t>
@@ -1199,10 +1199,10 @@
     <t xml:space="preserve">8.25130176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35623264312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2417631149292</t>
+    <t xml:space="preserve">8.35623168945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24176406860352</t>
   </si>
   <si>
     <t xml:space="preserve">8.34669303894043</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">7.97466850280762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01282501220703</t>
+    <t xml:space="preserve">8.01282596588135</t>
   </si>
   <si>
     <t xml:space="preserve">8.05098152160645</t>
@@ -1229,13 +1229,13 @@
     <t xml:space="preserve">7.67895746231079</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73619222640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6980357170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5167932510376</t>
+    <t xml:space="preserve">7.73619174957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69803524017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51679372787476</t>
   </si>
   <si>
     <t xml:space="preserve">7.59310626983643</t>
@@ -1259,16 +1259,16 @@
     <t xml:space="preserve">7.20200395584106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18292617797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14476919174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12569093704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23062086105347</t>
+    <t xml:space="preserve">7.18292570114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14476871490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12569046020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23062133789062</t>
   </si>
   <si>
     <t xml:space="preserve">7.1543083190918</t>
@@ -1277,7 +1277,7 @@
     <t xml:space="preserve">7.24969863891602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24015998840332</t>
+    <t xml:space="preserve">7.24016046524048</t>
   </si>
   <si>
     <t xml:space="preserve">7.46909809112549</t>
@@ -1298,13 +1298,13 @@
     <t xml:space="preserve">7.3355507850647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61218452453613</t>
+    <t xml:space="preserve">7.61218404769897</t>
   </si>
   <si>
     <t xml:space="preserve">7.90789556503296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94605112075806</t>
+    <t xml:space="preserve">7.94605159759521</t>
   </si>
   <si>
     <t xml:space="preserve">7.45955896377563</t>
@@ -1316,22 +1316,22 @@
     <t xml:space="preserve">7.8792781829834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99374723434448</t>
+    <t xml:space="preserve">7.99374771118164</t>
   </si>
   <si>
     <t xml:space="preserve">7.75527000427246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81250429153442</t>
+    <t xml:space="preserve">7.81250381469727</t>
   </si>
   <si>
     <t xml:space="preserve">7.79342699050903</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80296564102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85066032409668</t>
+    <t xml:space="preserve">7.80296611785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85065984725952</t>
   </si>
   <si>
     <t xml:space="preserve">7.74573087692261</t>
@@ -1340,22 +1340,22 @@
     <t xml:space="preserve">7.83158302307129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66941833496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60264444351196</t>
+    <t xml:space="preserve">7.66941785812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60264492034912</t>
   </si>
   <si>
     <t xml:space="preserve">7.58356666564941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88881778717041</t>
+    <t xml:space="preserve">7.88881826400757</t>
   </si>
   <si>
     <t xml:space="preserve">8.00328636169434</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78388690948486</t>
+    <t xml:space="preserve">7.78388738632202</t>
   </si>
   <si>
     <t xml:space="preserve">7.3641676902771</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">7.27831649780273</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08753442764282</t>
+    <t xml:space="preserve">7.08753490447998</t>
   </si>
   <si>
     <t xml:space="preserve">7.05891799926758</t>
@@ -1376,10 +1376,10 @@
     <t xml:space="preserve">7.50372648239136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98721361160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02589321136475</t>
+    <t xml:space="preserve">7.98721408843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02589225769043</t>
   </si>
   <si>
     <t xml:space="preserve">8.04523086547852</t>
@@ -1391,25 +1391,25 @@
     <t xml:space="preserve">8.07424163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12259006500244</t>
+    <t xml:space="preserve">8.12258911132812</t>
   </si>
   <si>
     <t xml:space="preserve">8.05490112304688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94853448867798</t>
+    <t xml:space="preserve">7.94853496551514</t>
   </si>
   <si>
     <t xml:space="preserve">8.06457138061523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08391094207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97754383087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93886423110962</t>
+    <t xml:space="preserve">8.08390998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97754430770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93886518478394</t>
   </si>
   <si>
     <t xml:space="preserve">7.79381895065308</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">7.68745088577271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63910245895386</t>
+    <t xml:space="preserve">7.63910293579102</t>
   </si>
   <si>
     <t xml:space="preserve">7.73579978942871</t>
@@ -1436,10 +1436,10 @@
     <t xml:space="preserve">7.90985584259033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85183715820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83249807357788</t>
+    <t xml:space="preserve">7.85183668136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83249759674072</t>
   </si>
   <si>
     <t xml:space="preserve">7.81315755844116</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">7.80348825454712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78414869308472</t>
+    <t xml:space="preserve">7.78414916992188</t>
   </si>
   <si>
     <t xml:space="preserve">7.6681113243103</t>
@@ -1460,13 +1460,13 @@
     <t xml:space="preserve">7.71646022796631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75514030456543</t>
+    <t xml:space="preserve">7.75513982772827</t>
   </si>
   <si>
     <t xml:space="preserve">7.74547004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86150646209717</t>
+    <t xml:space="preserve">7.86150693893433</t>
   </si>
   <si>
     <t xml:space="preserve">7.89051580429077</t>
@@ -1484,10 +1484,10 @@
     <t xml:space="preserve">8.09358024597168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1322603225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15159893035889</t>
+    <t xml:space="preserve">8.13225936889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1515998840332</t>
   </si>
   <si>
     <t xml:space="preserve">8.1129207611084</t>
@@ -1496,10 +1496,10 @@
     <t xml:space="preserve">8.03556251525879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92919540405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69712114334106</t>
+    <t xml:space="preserve">7.92919492721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69712066650391</t>
   </si>
   <si>
     <t xml:space="preserve">7.60042381286621</t>
@@ -1508,10 +1508,10 @@
     <t xml:space="preserve">7.88084602355957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55207490921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40702867507935</t>
+    <t xml:space="preserve">7.55207443237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40702819824219</t>
   </si>
   <si>
     <t xml:space="preserve">7.34900999069214</t>
@@ -1520,16 +1520,16 @@
     <t xml:space="preserve">7.37801933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43603801727295</t>
+    <t xml:space="preserve">7.43603754043579</t>
   </si>
   <si>
     <t xml:space="preserve">7.41669797897339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5230655670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36834907531738</t>
+    <t xml:space="preserve">7.52306604385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36834955215454</t>
   </si>
   <si>
     <t xml:space="preserve">7.542405128479</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">7.4843864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70679092407227</t>
+    <t xml:space="preserve">7.70679044723511</t>
   </si>
   <si>
     <t xml:space="preserve">7.64877223968506</t>
@@ -1556,10 +1556,10 @@
     <t xml:space="preserve">7.59075355529785</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95820331573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96787357330322</t>
+    <t xml:space="preserve">7.95820426940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96787405014038</t>
   </si>
   <si>
     <t xml:space="preserve">7.90018606185913</t>
@@ -1577,10 +1577,10 @@
     <t xml:space="preserve">8.19027900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29664516448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45136070251465</t>
+    <t xml:space="preserve">8.29664611816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45136165618896</t>
   </si>
   <si>
     <t xml:space="preserve">8.48037147521973</t>
@@ -1607,19 +1607,19 @@
     <t xml:space="preserve">8.50938034057617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42235279083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54805850982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55772876739502</t>
+    <t xml:space="preserve">8.4223518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54805946350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55772972106934</t>
   </si>
   <si>
     <t xml:space="preserve">8.52871990203857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68343544006348</t>
+    <t xml:space="preserve">8.68343448638916</t>
   </si>
   <si>
     <t xml:space="preserve">8.76079368591309</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">8.65442562103271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75112342834473</t>
+    <t xml:space="preserve">8.75112438201904</t>
   </si>
   <si>
     <t xml:space="preserve">8.70277500152588</t>
@@ -1652,10 +1652,10 @@
     <t xml:space="preserve">8.63508701324463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32565498352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31598567962646</t>
+    <t xml:space="preserve">8.32565402984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31598472595215</t>
   </si>
   <si>
     <t xml:space="preserve">8.30631542205811</t>
@@ -63348,7 +63348,7 @@
     </row>
     <row r="2337">
       <c r="A2337" s="1" t="n">
-        <v>46021.6913078704</v>
+        <v>46021.3333333333</v>
       </c>
       <c r="B2337" t="n">
         <v>10714</v>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -44,19 +44,19 @@
     <t xml:space="preserve">FF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98565673828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08549880981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24887371063232</t>
+    <t xml:space="preserve">8.98565578460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08549785614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24887275695801</t>
   </si>
   <si>
     <t xml:space="preserve">9.09457492828369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12180328369141</t>
+    <t xml:space="preserve">9.12180423736572</t>
   </si>
   <si>
     <t xml:space="preserve">9.03104019165039</t>
@@ -68,19 +68,19 @@
     <t xml:space="preserve">8.8994312286377</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89489364624023</t>
+    <t xml:space="preserve">8.89489269256592</t>
   </si>
   <si>
     <t xml:space="preserve">8.84951114654541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85858726501465</t>
+    <t xml:space="preserve">8.85858821868896</t>
   </si>
   <si>
     <t xml:space="preserve">8.87674045562744</t>
   </si>
   <si>
-    <t xml:space="preserve">8.767822265625</t>
+    <t xml:space="preserve">8.76782321929932</t>
   </si>
   <si>
     <t xml:space="preserve">8.86766529083252</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">9.04919338226318</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23072242736816</t>
+    <t xml:space="preserve">9.23072147369385</t>
   </si>
   <si>
     <t xml:space="preserve">9.11272811889648</t>
@@ -98,34 +98,34 @@
     <t xml:space="preserve">8.96750450134277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91304683685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92212390899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00380992889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15811061859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16718673706055</t>
+    <t xml:space="preserve">8.91304588317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92212295532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00381183624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15810966491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16718578338623</t>
   </si>
   <si>
     <t xml:space="preserve">9.43947887420654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54839611053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62100696563721</t>
+    <t xml:space="preserve">9.54839515686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62100791931152</t>
   </si>
   <si>
     <t xml:space="preserve">9.80253601074219</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71177196502686</t>
+    <t xml:space="preserve">9.71177101135254</t>
   </si>
   <si>
     <t xml:space="preserve">9.56654834747314</t>
@@ -134,25 +134,25 @@
     <t xml:space="preserve">9.58470153808594</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57562446594238</t>
+    <t xml:space="preserve">9.57562637329102</t>
   </si>
   <si>
     <t xml:space="preserve">9.53024196624756</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50301265716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60285377502441</t>
+    <t xml:space="preserve">9.50301361083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60285472869873</t>
   </si>
   <si>
     <t xml:space="preserve">9.63915920257568</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79345798492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95683574676514</t>
+    <t xml:space="preserve">9.79345989227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95683479309082</t>
   </si>
   <si>
     <t xml:space="preserve">9.93868255615234</t>
@@ -161,34 +161,34 @@
     <t xml:space="preserve">9.98406410217285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73900127410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7662296295166</t>
+    <t xml:space="preserve">9.73900032043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76623058319092</t>
   </si>
   <si>
     <t xml:space="preserve">9.74807739257812</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75715351104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64823627471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82068824768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7026948928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72084808349609</t>
+    <t xml:space="preserve">9.75715446472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64823532104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82068729400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70269584655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72084712982178</t>
   </si>
   <si>
     <t xml:space="preserve">9.67546558380127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66638851165771</t>
+    <t xml:space="preserve">9.6663875579834</t>
   </si>
   <si>
     <t xml:space="preserve">9.63008308410645</t>
@@ -200,109 +200,109 @@
     <t xml:space="preserve">9.68454265594482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81161212921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8297643661499</t>
+    <t xml:space="preserve">9.81161308288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82976531982422</t>
   </si>
   <si>
     <t xml:space="preserve">9.8479175567627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83884048461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72992515563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78438186645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55747318267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34871482849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33963680267334</t>
+    <t xml:space="preserve">9.83884143829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72992420196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78438377380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55747127532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34871387481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33963775634766</t>
   </si>
   <si>
     <t xml:space="preserve">9.27610301971436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25794982910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19441699981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18533992767334</t>
+    <t xml:space="preserve">9.25795078277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19441604614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18533897399902</t>
   </si>
   <si>
     <t xml:space="preserve">9.41224956512451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22164535522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31240844726562</t>
+    <t xml:space="preserve">9.22164440155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31240940093994</t>
   </si>
   <si>
     <t xml:space="preserve">9.2670259475708</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29425621032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28518009185791</t>
+    <t xml:space="preserve">9.29425525665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28517913818359</t>
   </si>
   <si>
     <t xml:space="preserve">9.37594413757324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36686706542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38501930236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45763111114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39409637451172</t>
+    <t xml:space="preserve">9.366868019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3850212097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4576301574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39409732818604</t>
   </si>
   <si>
     <t xml:space="preserve">9.48486042022705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49393653869629</t>
+    <t xml:space="preserve">9.49393749237061</t>
   </si>
   <si>
     <t xml:space="preserve">9.44855499267578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4757833480835</t>
+    <t xml:space="preserve">9.47578430175781</t>
   </si>
   <si>
     <t xml:space="preserve">9.23979759216309</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14903259277344</t>
+    <t xml:space="preserve">9.14903163909912</t>
   </si>
   <si>
     <t xml:space="preserve">9.21256828308105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20349407196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13088035583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1399564743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94027614593506</t>
+    <t xml:space="preserve">9.20349216461182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13088130950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13995552062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94027519226074</t>
   </si>
   <si>
     <t xml:space="preserve">8.80412864685059</t>
@@ -311,34 +311,34 @@
     <t xml:space="preserve">8.75874614715576</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66798400878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62260055541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53183746337891</t>
+    <t xml:space="preserve">8.66798305511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62259960174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53183555603027</t>
   </si>
   <si>
     <t xml:space="preserve">8.35030937194824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16878032684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98725175857544</t>
+    <t xml:space="preserve">8.16877937316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9872522354126</t>
   </si>
   <si>
     <t xml:space="preserve">8.03263473510742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12339687347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25954437255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94186925888062</t>
+    <t xml:space="preserve">8.12339782714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25954341888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9418683052063</t>
   </si>
   <si>
     <t xml:space="preserve">8.3049259185791</t>
@@ -350,7 +350,7 @@
     <t xml:space="preserve">8.39569091796875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57721900939941</t>
+    <t xml:space="preserve">8.57721710205078</t>
   </si>
   <si>
     <t xml:space="preserve">8.71336555480957</t>
@@ -359,76 +359,76 @@
     <t xml:space="preserve">9.53202247619629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25706195831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44036865234375</t>
+    <t xml:space="preserve">9.25706005096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44036769866943</t>
   </si>
   <si>
     <t xml:space="preserve">9.16540718078613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07375335693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11957931518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98209857940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02792644500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62367630004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80698585510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89863872528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99029350280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1736011505127</t>
+    <t xml:space="preserve">9.07375240325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11957836151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98209953308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02792549133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62367820739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80698490142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89863967895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99029159545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.173602104187</t>
   </si>
   <si>
     <t xml:space="preserve">10.2652549743652</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3569107055664</t>
+    <t xml:space="preserve">10.3569097518921</t>
   </si>
   <si>
     <t xml:space="preserve">10.5402183532715</t>
   </si>
   <si>
-    <t xml:space="preserve">10.631872177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8151798248291</t>
+    <t xml:space="preserve">10.6318712234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8151807785034</t>
   </si>
   <si>
     <t xml:space="preserve">10.7235260009766</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9068336486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9984884262085</t>
+    <t xml:space="preserve">10.9068326950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9984874725342</t>
   </si>
   <si>
     <t xml:space="preserve">11.090142250061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1817970275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2734498977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4567584991455</t>
+    <t xml:space="preserve">11.1817951202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2734508514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4567575454712</t>
   </si>
   <si>
     <t xml:space="preserve">11.3651037216187</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">10.4485635757446</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71533107757568</t>
+    <t xml:space="preserve">9.71533203125</t>
   </si>
   <si>
     <t xml:space="preserve">8.79878997802734</t>
@@ -449,43 +449,43 @@
     <t xml:space="preserve">9.2112340927124</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30288887023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03709125518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39454078674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76115798950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66950416564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57784938812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0361204147339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94446563720703</t>
+    <t xml:space="preserve">9.30288791656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03709030151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39454174041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76115703582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6695032119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57785034179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0361194610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94446659088135</t>
   </si>
   <si>
     <t xml:space="preserve">9.82552433013916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73283004760742</t>
+    <t xml:space="preserve">9.73283100128174</t>
   </si>
   <si>
     <t xml:space="preserve">9.59379005432129</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96456527709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9182186126709</t>
+    <t xml:space="preserve">9.96456432342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91821765899658</t>
   </si>
   <si>
     <t xml:space="preserve">9.54744338989258</t>
@@ -494,10 +494,10 @@
     <t xml:space="preserve">10.010910987854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1036052703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1499519348145</t>
+    <t xml:space="preserve">10.1036043167114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1499509811401</t>
   </si>
   <si>
     <t xml:space="preserve">10.1962985992432</t>
@@ -506,13 +506,13 @@
     <t xml:space="preserve">9.77917766571045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87187099456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0572576522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2889919281006</t>
+    <t xml:space="preserve">9.87187004089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.057258605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2889928817749</t>
   </si>
   <si>
     <t xml:space="preserve">10.4743804931641</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">9.68648338317871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64013671875</t>
+    <t xml:space="preserve">9.64013576507568</t>
   </si>
   <si>
     <t xml:space="preserve">9.50109577178955</t>
@@ -536,10 +536,10 @@
     <t xml:space="preserve">9.31570911407471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23228359222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1952075958252</t>
+    <t xml:space="preserve">9.23228454589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19520664215088</t>
   </si>
   <si>
     <t xml:space="preserve">9.25082302093506</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">9.04689693450928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12105369567871</t>
+    <t xml:space="preserve">9.12105274200439</t>
   </si>
   <si>
     <t xml:space="preserve">9.0654354095459</t>
@@ -563,19 +563,19 @@
     <t xml:space="preserve">8.97274303436279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17666912078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02835845947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95420265197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71320056915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99128150939941</t>
+    <t xml:space="preserve">9.17666816711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02835941314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95420360565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7131986618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99128246307373</t>
   </si>
   <si>
     <t xml:space="preserve">8.76881694793701</t>
@@ -584,34 +584,34 @@
     <t xml:space="preserve">8.89858722686768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93566513061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3353385925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9841938018799</t>
+    <t xml:space="preserve">8.93566608428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3353395462036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9841947555542</t>
   </si>
   <si>
     <t xml:space="preserve">11.0305404663086</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2159290313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4940090179443</t>
+    <t xml:space="preserve">11.2159280776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4940099716187</t>
   </si>
   <si>
     <t xml:space="preserve">11.540355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5867033004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6330490112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7257413864136</t>
+    <t xml:space="preserve">11.5867023468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6330499649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7257423400879</t>
   </si>
   <si>
     <t xml:space="preserve">11.9111299514771</t>
@@ -620,28 +620,28 @@
     <t xml:space="preserve">11.9574766159058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1892099380493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2819042205811</t>
+    <t xml:space="preserve">12.1892108917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2819051742554</t>
   </si>
   <si>
     <t xml:space="preserve">12.3745985031128</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5136394500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3282518386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1428651809692</t>
+    <t xml:space="preserve">12.5136375427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3282527923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1428661346436</t>
   </si>
   <si>
     <t xml:space="preserve">12.0965175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5551223754883</t>
+    <t xml:space="preserve">12.555121421814</t>
   </si>
   <si>
     <t xml:space="preserve">12.5082750320435</t>
@@ -674,10 +674,10 @@
     <t xml:space="preserve">12.2740383148193</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8362073898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7893590927124</t>
+    <t xml:space="preserve">12.8362064361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7893581390381</t>
   </si>
   <si>
     <t xml:space="preserve">12.6019687652588</t>
@@ -689,10 +689,10 @@
     <t xml:space="preserve">12.8830537796021</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0704441070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6794605255127</t>
+    <t xml:space="preserve">13.0704431533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.679461479187</t>
   </si>
   <si>
     <t xml:space="preserve">13.8668508529663</t>
@@ -716,16 +716,16 @@
     <t xml:space="preserve">14.7569532394409</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0380382537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1785802841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3191242218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8974943161011</t>
+    <t xml:space="preserve">15.0380373001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.178581237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3191232681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8974952697754</t>
   </si>
   <si>
     <t xml:space="preserve">15.4596652984619</t>
@@ -734,25 +734,25 @@
     <t xml:space="preserve">15.4128179550171</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5533609390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0686836242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8650875091553</t>
+    <t xml:space="preserve">15.5533599853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0686817169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8650894165039</t>
   </si>
   <si>
     <t xml:space="preserve">17.0056324005127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7713947296143</t>
+    <t xml:space="preserve">16.7713928222656</t>
   </si>
   <si>
     <t xml:space="preserve">17.1930236816406</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0524787902832</t>
+    <t xml:space="preserve">17.0524806976318</t>
   </si>
   <si>
     <t xml:space="preserve">16.9587841033936</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">16.7245464324951</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6308536529541</t>
+    <t xml:space="preserve">16.6308517456055</t>
   </si>
   <si>
     <t xml:space="preserve">16.5371551513672</t>
@@ -770,25 +770,25 @@
     <t xml:space="preserve">16.584005355835</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2092247009277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2560749053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1461734771729</t>
+    <t xml:space="preserve">16.2092227935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2560729980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1461715698242</t>
   </si>
   <si>
     <t xml:space="preserve">16.396614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3029174804688</t>
+    <t xml:space="preserve">16.3029193878174</t>
   </si>
   <si>
     <t xml:space="preserve">15.8344440460205</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1155300140381</t>
+    <t xml:space="preserve">16.1155319213867</t>
   </si>
   <si>
     <t xml:space="preserve">16.0218353271484</t>
@@ -800,10 +800,10 @@
     <t xml:space="preserve">15.974986076355</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7407503128052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4434623718262</t>
+    <t xml:space="preserve">15.7407484054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4434604644775</t>
   </si>
   <si>
     <t xml:space="preserve">16.9119338989258</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">15.272274017334</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0848846435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.991189956665</t>
+    <t xml:space="preserve">15.084885597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9911909103394</t>
   </si>
   <si>
     <t xml:space="preserve">14.8037996292114</t>
@@ -845,16 +845,16 @@
     <t xml:space="preserve">14.5227146148682</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9605445861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2416296005249</t>
+    <t xml:space="preserve">13.960545539856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2416305541992</t>
   </si>
   <si>
     <t xml:space="preserve">14.1947832107544</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0073928833008</t>
+    <t xml:space="preserve">14.0073938369751</t>
   </si>
   <si>
     <t xml:space="preserve">13.7263078689575</t>
@@ -869,10 +869,10 @@
     <t xml:space="preserve">14.6164102554321</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7731552124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3515291213989</t>
+    <t xml:space="preserve">13.7731561660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3515281677246</t>
   </si>
   <si>
     <t xml:space="preserve">13.3046817779541</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">13.0235967636108</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1172924041748</t>
+    <t xml:space="preserve">13.1172914505005</t>
   </si>
   <si>
     <t xml:space="preserve">12.976749420166</t>
@@ -908,7 +908,7 @@
     <t xml:space="preserve">12.1334934234619</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4776287078857</t>
+    <t xml:space="preserve">11.4776296615601</t>
   </si>
   <si>
     <t xml:space="preserve">11.2433929443359</t>
@@ -926,40 +926,40 @@
     <t xml:space="preserve">10.9623079299927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7280702590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1965436935425</t>
+    <t xml:space="preserve">10.7280712127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1965446472168</t>
   </si>
   <si>
     <t xml:space="preserve">11.5713243484497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3370885848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2902393341064</t>
+    <t xml:space="preserve">11.3370876312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2902402877808</t>
   </si>
   <si>
     <t xml:space="preserve">11.7118682861328</t>
   </si>
   <si>
-    <t xml:space="preserve">11.758713722229</t>
+    <t xml:space="preserve">11.7587146759033</t>
   </si>
   <si>
     <t xml:space="preserve">11.8055629730225</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0091543197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46319007873535</t>
+    <t xml:space="preserve">11.0091552734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46318912506104</t>
   </si>
   <si>
     <t xml:space="preserve">8.33884906768799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57308673858643</t>
+    <t xml:space="preserve">8.57308578491211</t>
   </si>
   <si>
     <t xml:space="preserve">8.31074142456055</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">8.61993408203125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44191360473633</t>
+    <t xml:space="preserve">8.44191455841064</t>
   </si>
   <si>
     <t xml:space="preserve">8.32948112487793</t>
@@ -980,7 +980,7 @@
     <t xml:space="preserve">8.25452423095703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43254375457764</t>
+    <t xml:space="preserve">8.43254470825195</t>
   </si>
   <si>
     <t xml:space="preserve">8.47002220153809</t>
@@ -998,19 +998,19 @@
     <t xml:space="preserve">7.78605031967163</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49559497833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33631420135498</t>
+    <t xml:space="preserve">7.49559545516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33631372451782</t>
   </si>
   <si>
     <t xml:space="preserve">7.23324918746948</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83289670944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90785217285156</t>
+    <t xml:space="preserve">7.83289623260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90785312652588</t>
   </si>
   <si>
     <t xml:space="preserve">7.50496530532837</t>
@@ -1019,13 +1019,13 @@
     <t xml:space="preserve">7.37379169464111</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12081480026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28009653091431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98027229309082</t>
+    <t xml:space="preserve">7.12081527709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28009700775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98027276992798</t>
   </si>
   <si>
     <t xml:space="preserve">6.93342542648315</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">7.34568309783936</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54244232177734</t>
+    <t xml:space="preserve">7.5424427986145</t>
   </si>
   <si>
     <t xml:space="preserve">8.19830703735352</t>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07642078399658</t>
+    <t xml:space="preserve">9.0764217376709</t>
   </si>
   <si>
     <t xml:space="preserve">FF.MI</t>
@@ -47,85 +47,85 @@
     <t xml:space="preserve">8.98565769195557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08549880981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24887371063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09457492828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12180519104004</t>
+    <t xml:space="preserve">9.08549976348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24887180328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09457588195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12180328369141</t>
   </si>
   <si>
     <t xml:space="preserve">9.03104019165039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95388984680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8994312286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89489269256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84951210021973</t>
+    <t xml:space="preserve">8.95389080047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89943313598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89489364624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84951114654541</t>
   </si>
   <si>
     <t xml:space="preserve">8.85858821868896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87674045562744</t>
+    <t xml:space="preserve">8.87673950195312</t>
   </si>
   <si>
     <t xml:space="preserve">8.76782321929932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86766529083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04919338226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23072147369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11272716522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96750450134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91304588317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92212295532227</t>
+    <t xml:space="preserve">8.86766338348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04919147491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23072052001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11272811889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96750354766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91304683685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92212390899658</t>
   </si>
   <si>
     <t xml:space="preserve">9.00381088256836</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15810871124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16718578338623</t>
+    <t xml:space="preserve">9.15810966491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16718673706055</t>
   </si>
   <si>
     <t xml:space="preserve">9.43947792053223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54839515686035</t>
+    <t xml:space="preserve">9.54839706420898</t>
   </si>
   <si>
     <t xml:space="preserve">9.62100791931152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8025369644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71177101135254</t>
+    <t xml:space="preserve">9.80253601074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71177005767822</t>
   </si>
   <si>
     <t xml:space="preserve">9.56654930114746</t>
@@ -134,61 +134,61 @@
     <t xml:space="preserve">9.58470153808594</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5756254196167</t>
+    <t xml:space="preserve">9.57562637329102</t>
   </si>
   <si>
     <t xml:space="preserve">9.53024196624756</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50301361083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60285472869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63915920257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79345989227295</t>
+    <t xml:space="preserve">9.50301551818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60285377502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63916015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79345893859863</t>
   </si>
   <si>
     <t xml:space="preserve">9.95683574676514</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93868255615234</t>
+    <t xml:space="preserve">9.93868160247803</t>
   </si>
   <si>
     <t xml:space="preserve">9.98406410217285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73899936676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76623153686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74807643890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75715446472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64823627471924</t>
+    <t xml:space="preserve">9.73900127410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7662296295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74807739257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75715351104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64823722839355</t>
   </si>
   <si>
     <t xml:space="preserve">9.82068824768066</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7026948928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72084712982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67546463012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66638946533203</t>
+    <t xml:space="preserve">9.70269393920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72084808349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67546558380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66638851165771</t>
   </si>
   <si>
     <t xml:space="preserve">9.63008308410645</t>
@@ -197,76 +197,76 @@
     <t xml:space="preserve">9.65731334686279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68454170227051</t>
+    <t xml:space="preserve">9.68454265594482</t>
   </si>
   <si>
     <t xml:space="preserve">9.81161212921143</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82976531982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84791660308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83884048461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72992324829102</t>
+    <t xml:space="preserve">9.8297643661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84791851043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83884143829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72992420196533</t>
   </si>
   <si>
     <t xml:space="preserve">9.78438282012939</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55747222900391</t>
+    <t xml:space="preserve">9.55747318267822</t>
   </si>
   <si>
     <t xml:space="preserve">9.34871387481689</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33963680267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27610301971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25795078277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19441604614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18533992767334</t>
+    <t xml:space="preserve">9.33963775634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27610397338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2579517364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19441509246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18533802032471</t>
   </si>
   <si>
     <t xml:space="preserve">9.41224956512451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22164535522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31240844726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2670259475708</t>
+    <t xml:space="preserve">9.22164440155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31240940093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26702690124512</t>
   </si>
   <si>
     <t xml:space="preserve">9.29425525665283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28518009185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37594413757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36686706542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38502216339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45763111114502</t>
+    <t xml:space="preserve">9.28517913818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37594509124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36686611175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3850212097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45763206481934</t>
   </si>
   <si>
     <t xml:space="preserve">9.39409732818604</t>
@@ -278,43 +278,43 @@
     <t xml:space="preserve">9.49393749237061</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44855499267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4757833480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23979759216309</t>
+    <t xml:space="preserve">9.4485559463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47578430175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23979663848877</t>
   </si>
   <si>
     <t xml:space="preserve">9.14903259277344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21256732940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20349216461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13088035583496</t>
+    <t xml:space="preserve">9.21256828308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20349311828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13088130950928</t>
   </si>
   <si>
     <t xml:space="preserve">9.13995552062988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94027519226074</t>
+    <t xml:space="preserve">8.94027614593506</t>
   </si>
   <si>
     <t xml:space="preserve">8.80412864685059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75874519348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66798305511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62260055541992</t>
+    <t xml:space="preserve">8.75874710083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66798210144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62259960174561</t>
   </si>
   <si>
     <t xml:space="preserve">8.53183650970459</t>
@@ -326,10 +326,10 @@
     <t xml:space="preserve">8.16878032684326</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9872522354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03263473510742</t>
+    <t xml:space="preserve">7.98725032806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03263378143311</t>
   </si>
   <si>
     <t xml:space="preserve">8.12339782714844</t>
@@ -338,22 +338,22 @@
     <t xml:space="preserve">8.25954341888428</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9418683052063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30492687225342</t>
+    <t xml:space="preserve">7.94186973571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30492496490479</t>
   </si>
   <si>
     <t xml:space="preserve">8.21416282653809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39568996429443</t>
+    <t xml:space="preserve">8.39569091796875</t>
   </si>
   <si>
     <t xml:space="preserve">8.57721710205078</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71336460113525</t>
+    <t xml:space="preserve">8.71336555480957</t>
   </si>
   <si>
     <t xml:space="preserve">9.53202247619629</t>
@@ -362,37 +362,37 @@
     <t xml:space="preserve">9.25706005096436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44036865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16540718078613</t>
+    <t xml:space="preserve">9.44036960601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16540622711182</t>
   </si>
   <si>
     <t xml:space="preserve">9.07375240325928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11957836151123</t>
+    <t xml:space="preserve">9.11958026885986</t>
   </si>
   <si>
     <t xml:space="preserve">8.98209857940674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02792453765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62367725372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80698490142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89863967895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9902925491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.173602104187</t>
+    <t xml:space="preserve">9.02792644500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62367630004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80698394775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89863872528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99029350280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1736011505127</t>
   </si>
   <si>
     <t xml:space="preserve">10.2652559280396</t>
@@ -413,43 +413,43 @@
     <t xml:space="preserve">10.7235260009766</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9068336486816</t>
+    <t xml:space="preserve">10.9068326950073</t>
   </si>
   <si>
     <t xml:space="preserve">10.9984884262085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.090142250061</t>
+    <t xml:space="preserve">11.0901432037354</t>
   </si>
   <si>
     <t xml:space="preserve">11.1817960739136</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734498977661</t>
+    <t xml:space="preserve">11.2734508514404</t>
   </si>
   <si>
     <t xml:space="preserve">11.4567575454712</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3651027679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4485635757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71533203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79879093170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24886512756348</t>
+    <t xml:space="preserve">11.3651037216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4485626220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71533107757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79878997802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24886608123779</t>
   </si>
   <si>
     <t xml:space="preserve">9.2112340927124</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30288791656494</t>
+    <t xml:space="preserve">9.30288696289062</t>
   </si>
   <si>
     <t xml:space="preserve">9.03709030151367</t>
@@ -458,10 +458,10 @@
     <t xml:space="preserve">9.3945426940918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76115703582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6695032119751</t>
+    <t xml:space="preserve">9.76115798950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66950416564941</t>
   </si>
   <si>
     <t xml:space="preserve">9.57785034179688</t>
@@ -470,58 +470,58 @@
     <t xml:space="preserve">10.0361204147339</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94446659088135</t>
+    <t xml:space="preserve">9.94446754455566</t>
   </si>
   <si>
     <t xml:space="preserve">9.82552433013916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73283100128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59379005432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96456432342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91821765899658</t>
+    <t xml:space="preserve">9.73283004760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59379100799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96456527709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91821670532227</t>
   </si>
   <si>
     <t xml:space="preserve">9.54744338989258</t>
   </si>
   <si>
-    <t xml:space="preserve">10.010910987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1036043167114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1499509811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1962985992432</t>
+    <t xml:space="preserve">10.0109119415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1036052703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1499519348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1962976455688</t>
   </si>
   <si>
     <t xml:space="preserve">9.77917766571045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87187004089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.057258605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2889928817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4743804931641</t>
+    <t xml:space="preserve">9.87187099456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0572595596313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2889919281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4743795394897</t>
   </si>
   <si>
     <t xml:space="preserve">10.2426452636719</t>
   </si>
   <si>
-    <t xml:space="preserve">10.381685256958</t>
+    <t xml:space="preserve">10.3816862106323</t>
   </si>
   <si>
     <t xml:space="preserve">9.68648338317871</t>
@@ -530,25 +530,25 @@
     <t xml:space="preserve">9.64013576507568</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50109577178955</t>
+    <t xml:space="preserve">9.50109672546387</t>
   </si>
   <si>
     <t xml:space="preserve">9.31570911407471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23228454589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19520664215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25082302093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.269362449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21374607086182</t>
+    <t xml:space="preserve">9.23228549957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1952075958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25082206726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26936149597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2137451171875</t>
   </si>
   <si>
     <t xml:space="preserve">9.04689693450928</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">9.12105274200439</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0654354095459</t>
+    <t xml:space="preserve">9.06543636322021</t>
   </si>
   <si>
     <t xml:space="preserve">8.97274303436279</t>
@@ -572,22 +572,22 @@
     <t xml:space="preserve">8.95420360565186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7131986618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99128246307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76881694793701</t>
+    <t xml:space="preserve">8.71320056915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99128150939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7688159942627</t>
   </si>
   <si>
     <t xml:space="preserve">8.89858722686768</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93566608428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3353395462036</t>
+    <t xml:space="preserve">8.93566513061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3353385925293</t>
   </si>
   <si>
     <t xml:space="preserve">10.9841947555542</t>
@@ -596,10 +596,10 @@
     <t xml:space="preserve">11.0305404663086</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2159280776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4940099716187</t>
+    <t xml:space="preserve">11.2159290313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4940090179443</t>
   </si>
   <si>
     <t xml:space="preserve">11.540355682373</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">11.5867023468018</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6330499649048</t>
+    <t xml:space="preserve">11.6330490112305</t>
   </si>
   <si>
     <t xml:space="preserve">11.7257423400879</t>
@@ -620,28 +620,28 @@
     <t xml:space="preserve">11.9574766159058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1892108917236</t>
+    <t xml:space="preserve">12.1892118453979</t>
   </si>
   <si>
     <t xml:space="preserve">12.2819051742554</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3745985031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5136375427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3282527923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1428661346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0965175628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.555121421814</t>
+    <t xml:space="preserve">12.3745994567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5136394500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3282518386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1428651809692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0965194702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5551204681396</t>
   </si>
   <si>
     <t xml:space="preserve">12.5082750320435</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">12.6488170623779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4614276885986</t>
+    <t xml:space="preserve">12.4614267349243</t>
   </si>
   <si>
     <t xml:space="preserve">12.4145793914795</t>
@@ -659,49 +659,49 @@
     <t xml:space="preserve">12.7425127029419</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6956644058228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2271890640259</t>
+    <t xml:space="preserve">12.6956653594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2271909713745</t>
   </si>
   <si>
     <t xml:space="preserve">12.1803426742554</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3208837509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2740383148193</t>
+    <t xml:space="preserve">12.3208847045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.274037361145</t>
   </si>
   <si>
     <t xml:space="preserve">12.8362064361572</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7893581390381</t>
+    <t xml:space="preserve">12.7893600463867</t>
   </si>
   <si>
     <t xml:space="preserve">12.6019687652588</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9299020767212</t>
+    <t xml:space="preserve">12.9299011230469</t>
   </si>
   <si>
     <t xml:space="preserve">12.8830537796021</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0704431533813</t>
+    <t xml:space="preserve">13.0704441070557</t>
   </si>
   <si>
     <t xml:space="preserve">13.679461479187</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8668508529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0542402267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3353252410889</t>
+    <t xml:space="preserve">13.8668518066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0542411804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3353261947632</t>
   </si>
   <si>
     <t xml:space="preserve">14.5695629119873</t>
@@ -710,7 +710,7 @@
     <t xml:space="preserve">15.2254276275635</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1317329406738</t>
+    <t xml:space="preserve">15.1317319869995</t>
   </si>
   <si>
     <t xml:space="preserve">14.7569532394409</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">15.0380373001099</t>
   </si>
   <si>
-    <t xml:space="preserve">15.178581237793</t>
+    <t xml:space="preserve">15.1785802841187</t>
   </si>
   <si>
     <t xml:space="preserve">15.3191232681274</t>
@@ -728,16 +728,16 @@
     <t xml:space="preserve">14.8974952697754</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4596652984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4128179550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5533599853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0686817169189</t>
+    <t xml:space="preserve">15.4596643447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4128189086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5533609390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0686798095703</t>
   </si>
   <si>
     <t xml:space="preserve">16.8650894165039</t>
@@ -749,7 +749,7 @@
     <t xml:space="preserve">16.7713928222656</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1930236816406</t>
+    <t xml:space="preserve">17.193021774292</t>
   </si>
   <si>
     <t xml:space="preserve">17.0524806976318</t>
@@ -764,7 +764,7 @@
     <t xml:space="preserve">16.6308517456055</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5371551513672</t>
+    <t xml:space="preserve">16.5371570587158</t>
   </si>
   <si>
     <t xml:space="preserve">16.584005355835</t>
@@ -773,10 +773,10 @@
     <t xml:space="preserve">16.2092227935791</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2560729980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1461715698242</t>
+    <t xml:space="preserve">16.2560710906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1461734771729</t>
   </si>
   <si>
     <t xml:space="preserve">16.396614074707</t>
@@ -788,46 +788,46 @@
     <t xml:space="preserve">15.8344440460205</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1155319213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0218353271484</t>
+    <t xml:space="preserve">16.1155300140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0218372344971</t>
   </si>
   <si>
     <t xml:space="preserve">16.1623764038086</t>
   </si>
   <si>
-    <t xml:space="preserve">15.974986076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7407484054565</t>
+    <t xml:space="preserve">15.9749870300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7407493591309</t>
   </si>
   <si>
     <t xml:space="preserve">16.4434604644775</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9119338989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0993251800537</t>
+    <t xml:space="preserve">16.9119358062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0993270874023</t>
   </si>
   <si>
     <t xml:space="preserve">16.677698135376</t>
   </si>
   <si>
-    <t xml:space="preserve">16.818244934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.272274017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.084885597229</t>
+    <t xml:space="preserve">16.8182430267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2722749710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0848846435547</t>
   </si>
   <si>
     <t xml:space="preserve">14.9911909103394</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8037996292114</t>
+    <t xml:space="preserve">14.8038005828857</t>
   </si>
   <si>
     <t xml:space="preserve">14.4758682250977</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">14.288477897644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5227146148682</t>
+    <t xml:space="preserve">14.5227155685425</t>
   </si>
   <si>
     <t xml:space="preserve">13.960545539856</t>
@@ -854,7 +854,7 @@
     <t xml:space="preserve">14.1947832107544</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0073938369751</t>
+    <t xml:space="preserve">14.0073928833008</t>
   </si>
   <si>
     <t xml:space="preserve">13.7263078689575</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">14.1479358673096</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4290199279785</t>
+    <t xml:space="preserve">14.4290208816528</t>
   </si>
   <si>
     <t xml:space="preserve">14.6164102554321</t>
@@ -872,19 +872,19 @@
     <t xml:space="preserve">13.7731561660767</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3515281677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3046817779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3983764648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0235967636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1172914505005</t>
+    <t xml:space="preserve">13.3515291213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3046808242798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3983755111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0235958099365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1172904968262</t>
   </si>
   <si>
     <t xml:space="preserve">12.976749420166</t>
@@ -893,19 +893,19 @@
     <t xml:space="preserve">12.3677320480347</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0866470336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9929533004761</t>
+    <t xml:space="preserve">12.0866460800171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9929513931274</t>
   </si>
   <si>
     <t xml:space="preserve">11.8992576599121</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0397987365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1334934234619</t>
+    <t xml:space="preserve">12.0397996902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1334943771362</t>
   </si>
   <si>
     <t xml:space="preserve">11.4776296615601</t>
@@ -914,19 +914,19 @@
     <t xml:space="preserve">11.2433929443359</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3839340209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6650190353394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4307832717896</t>
+    <t xml:space="preserve">11.3839349746704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6650199890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4307823181152</t>
   </si>
   <si>
     <t xml:space="preserve">10.9623079299927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7280712127686</t>
+    <t xml:space="preserve">10.7280702590942</t>
   </si>
   <si>
     <t xml:space="preserve">11.1965446472168</t>
@@ -935,13 +935,13 @@
     <t xml:space="preserve">11.5713243484497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3370876312256</t>
+    <t xml:space="preserve">11.3370885848999</t>
   </si>
   <si>
     <t xml:space="preserve">11.2902402877808</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7118682861328</t>
+    <t xml:space="preserve">11.7118673324585</t>
   </si>
   <si>
     <t xml:space="preserve">11.7587146759033</t>
@@ -953,19 +953,19 @@
     <t xml:space="preserve">11.0091552734375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46318912506104</t>
+    <t xml:space="preserve">9.46318817138672</t>
   </si>
   <si>
     <t xml:space="preserve">8.33884906768799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57308578491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31074142456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45128345489502</t>
+    <t xml:space="preserve">8.57308673858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31074047088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45128440856934</t>
   </si>
   <si>
     <t xml:space="preserve">8.61993408203125</t>
@@ -983,19 +983,19 @@
     <t xml:space="preserve">8.43254470825195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47002220153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32011127471924</t>
+    <t xml:space="preserve">8.47002124786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32011032104492</t>
   </si>
   <si>
     <t xml:space="preserve">8.20767688751221</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08587265014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78605031967163</t>
+    <t xml:space="preserve">8.0858736038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78604936599731</t>
   </si>
   <si>
     <t xml:space="preserve">7.49559545516968</t>
@@ -1010,37 +1010,37 @@
     <t xml:space="preserve">7.83289623260498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90785312652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50496530532837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37379169464111</t>
+    <t xml:space="preserve">7.9078516960144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50496482849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37379217147827</t>
   </si>
   <si>
     <t xml:space="preserve">7.12081527709961</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28009700775146</t>
+    <t xml:space="preserve">7.28009653091431</t>
   </si>
   <si>
     <t xml:space="preserve">6.98027276992798</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93342542648315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06459856033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0271201133728</t>
+    <t xml:space="preserve">6.93342590332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06459808349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02712059020996</t>
   </si>
   <si>
     <t xml:space="preserve">7.34568309783936</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5424427986145</t>
+    <t xml:space="preserve">7.54244232177734</t>
   </si>
   <si>
     <t xml:space="preserve">8.19830703735352</t>
@@ -1049,28 +1049,28 @@
     <t xml:space="preserve">8.2170467376709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65194320678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46116256713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53747463226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68056106567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77595233917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8427267074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825527191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66148281097412</t>
+    <t xml:space="preserve">8.65194225311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46116161346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53747367858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68056201934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77595138549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84272575378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825622558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6614818572998</t>
   </si>
   <si>
     <t xml:space="preserve">8.49931812286377</t>
@@ -1082,16 +1082,16 @@
     <t xml:space="preserve">8.39438915252686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.604248046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48977947235107</t>
+    <t xml:space="preserve">8.60424900054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48977851867676</t>
   </si>
   <si>
     <t xml:space="preserve">8.29899787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12729454040527</t>
+    <t xml:space="preserve">8.12729358673096</t>
   </si>
   <si>
     <t xml:space="preserve">7.89835643768311</t>
@@ -1112,19 +1112,19 @@
     <t xml:space="preserve">8.06052017211914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07959938049316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07005882263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92697429656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98420858383179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30853652954102</t>
+    <t xml:space="preserve">8.07959842681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07005977630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92697334289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98420810699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30853748321533</t>
   </si>
   <si>
     <t xml:space="preserve">8.26084136962891</t>
@@ -1133,13 +1133,13 @@
     <t xml:space="preserve">8.27038097381592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18452835083008</t>
+    <t xml:space="preserve">8.18452930450439</t>
   </si>
   <si>
     <t xml:space="preserve">8.03190326690674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96513080596924</t>
+    <t xml:space="preserve">7.96512985229492</t>
   </si>
   <si>
     <t xml:space="preserve">7.86019992828369</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">7.91743516921997</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76481008529663</t>
+    <t xml:space="preserve">7.76480960845947</t>
   </si>
   <si>
     <t xml:space="preserve">7.72665309906006</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">7.63126230239868</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65987968444824</t>
+    <t xml:space="preserve">7.65987873077393</t>
   </si>
   <si>
     <t xml:space="preserve">8.16545104980469</t>
@@ -1175,22 +1175,22 @@
     <t xml:space="preserve">8.32761383056641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11775588989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93651247024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19406795501709</t>
+    <t xml:space="preserve">8.11775493621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9365119934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19406890869141</t>
   </si>
   <si>
     <t xml:space="preserve">8.2322244644165</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31807518005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15591144561768</t>
+    <t xml:space="preserve">8.31807708740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15591239929199</t>
   </si>
   <si>
     <t xml:space="preserve">8.22268486022949</t>
@@ -1199,16 +1199,16 @@
     <t xml:space="preserve">8.25130176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35623168945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24176406860352</t>
+    <t xml:space="preserve">8.35623264312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2417631149292</t>
   </si>
   <si>
     <t xml:space="preserve">8.34669303894043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95559167861938</t>
+    <t xml:space="preserve">7.95559072494507</t>
   </si>
   <si>
     <t xml:space="preserve">7.77434825897217</t>
@@ -1220,10 +1220,10 @@
     <t xml:space="preserve">7.97466850280762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01282596588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05098152160645</t>
+    <t xml:space="preserve">8.01282501220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05098056793213</t>
   </si>
   <si>
     <t xml:space="preserve">7.67895746231079</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">7.73619174957275</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69803524017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51679372787476</t>
+    <t xml:space="preserve">7.6980357170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5167932510376</t>
   </si>
   <si>
     <t xml:space="preserve">7.59310626983643</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">7.62172269821167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52633190155029</t>
+    <t xml:space="preserve">7.52633237838745</t>
   </si>
   <si>
     <t xml:space="preserve">7.34508991241455</t>
@@ -1262,25 +1262,25 @@
     <t xml:space="preserve">7.18292570114136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14476871490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12569046020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23062133789062</t>
+    <t xml:space="preserve">7.14476919174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12569093704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23062086105347</t>
   </si>
   <si>
     <t xml:space="preserve">7.1543083190918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24969863891602</t>
+    <t xml:space="preserve">7.24969911575317</t>
   </si>
   <si>
     <t xml:space="preserve">7.24016046524048</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46909809112549</t>
+    <t xml:space="preserve">7.46909761428833</t>
   </si>
   <si>
     <t xml:space="preserve">7.41186332702637</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">7.45001983642578</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28785514831543</t>
+    <t xml:space="preserve">7.28785562515259</t>
   </si>
   <si>
     <t xml:space="preserve">7.39278507232666</t>
@@ -1304,25 +1304,25 @@
     <t xml:space="preserve">7.90789556503296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94605159759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45955896377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70757484436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8792781829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99374771118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75527000427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81250381469727</t>
+    <t xml:space="preserve">7.94605112075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45955848693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70757436752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87927865982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99374723434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75527048110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81250476837158</t>
   </si>
   <si>
     <t xml:space="preserve">7.79342699050903</t>
@@ -1331,16 +1331,16 @@
     <t xml:space="preserve">7.80296611785889</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85065984725952</t>
+    <t xml:space="preserve">7.85066032409668</t>
   </si>
   <si>
     <t xml:space="preserve">7.74573087692261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83158302307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66941785812378</t>
+    <t xml:space="preserve">7.83158254623413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66941833496094</t>
   </si>
   <si>
     <t xml:space="preserve">7.60264492034912</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">7.58356666564941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88881826400757</t>
+    <t xml:space="preserve">7.88881778717041</t>
   </si>
   <si>
     <t xml:space="preserve">8.00328636169434</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">7.27831649780273</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08753490447998</t>
+    <t xml:space="preserve">7.08753442764282</t>
   </si>
   <si>
     <t xml:space="preserve">7.05891799926758</t>
@@ -1376,10 +1376,10 @@
     <t xml:space="preserve">7.50372648239136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98721408843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02589225769043</t>
+    <t xml:space="preserve">7.98721361160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02589321136475</t>
   </si>
   <si>
     <t xml:space="preserve">8.04523086547852</t>
@@ -1391,25 +1391,25 @@
     <t xml:space="preserve">8.07424163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12258911132812</t>
+    <t xml:space="preserve">8.12259006500244</t>
   </si>
   <si>
     <t xml:space="preserve">8.05490112304688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94853496551514</t>
+    <t xml:space="preserve">7.94853448867798</t>
   </si>
   <si>
     <t xml:space="preserve">8.06457138061523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08390998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97754430770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93886518478394</t>
+    <t xml:space="preserve">8.08391094207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97754383087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93886423110962</t>
   </si>
   <si>
     <t xml:space="preserve">7.79381895065308</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">7.68745088577271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63910293579102</t>
+    <t xml:space="preserve">7.63910245895386</t>
   </si>
   <si>
     <t xml:space="preserve">7.73579978942871</t>
@@ -1436,10 +1436,10 @@
     <t xml:space="preserve">7.90985584259033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85183668136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83249759674072</t>
+    <t xml:space="preserve">7.85183715820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83249807357788</t>
   </si>
   <si>
     <t xml:space="preserve">7.81315755844116</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">7.80348825454712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78414916992188</t>
+    <t xml:space="preserve">7.78414869308472</t>
   </si>
   <si>
     <t xml:space="preserve">7.6681113243103</t>
@@ -1460,13 +1460,13 @@
     <t xml:space="preserve">7.71646022796631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75513982772827</t>
+    <t xml:space="preserve">7.75514030456543</t>
   </si>
   <si>
     <t xml:space="preserve">7.74547004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86150693893433</t>
+    <t xml:space="preserve">7.86150646209717</t>
   </si>
   <si>
     <t xml:space="preserve">7.89051580429077</t>
@@ -1484,10 +1484,10 @@
     <t xml:space="preserve">8.09358024597168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13225936889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1515998840332</t>
+    <t xml:space="preserve">8.1322603225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15159893035889</t>
   </si>
   <si>
     <t xml:space="preserve">8.1129207611084</t>
@@ -1496,10 +1496,10 @@
     <t xml:space="preserve">8.03556251525879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92919492721558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69712066650391</t>
+    <t xml:space="preserve">7.92919540405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69712114334106</t>
   </si>
   <si>
     <t xml:space="preserve">7.60042381286621</t>
@@ -1508,10 +1508,10 @@
     <t xml:space="preserve">7.88084602355957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55207443237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40702819824219</t>
+    <t xml:space="preserve">7.55207490921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40702867507935</t>
   </si>
   <si>
     <t xml:space="preserve">7.34900999069214</t>
@@ -1520,16 +1520,16 @@
     <t xml:space="preserve">7.37801933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43603754043579</t>
+    <t xml:space="preserve">7.43603801727295</t>
   </si>
   <si>
     <t xml:space="preserve">7.41669797897339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52306604385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36834955215454</t>
+    <t xml:space="preserve">7.5230655670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36834907531738</t>
   </si>
   <si>
     <t xml:space="preserve">7.542405128479</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">7.4843864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70679044723511</t>
+    <t xml:space="preserve">7.70679092407227</t>
   </si>
   <si>
     <t xml:space="preserve">7.64877223968506</t>
@@ -1556,10 +1556,10 @@
     <t xml:space="preserve">7.59075355529785</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95820426940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96787405014038</t>
+    <t xml:space="preserve">7.95820331573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96787357330322</t>
   </si>
   <si>
     <t xml:space="preserve">7.90018606185913</t>
@@ -1577,10 +1577,10 @@
     <t xml:space="preserve">8.19027900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29664611816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45136165618896</t>
+    <t xml:space="preserve">8.29664516448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45136070251465</t>
   </si>
   <si>
     <t xml:space="preserve">8.48037147521973</t>
@@ -1607,19 +1607,19 @@
     <t xml:space="preserve">8.50938034057617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4223518371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54805946350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55772972106934</t>
+    <t xml:space="preserve">8.42235279083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54805850982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55772876739502</t>
   </si>
   <si>
     <t xml:space="preserve">8.52871990203857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68343448638916</t>
+    <t xml:space="preserve">8.68343544006348</t>
   </si>
   <si>
     <t xml:space="preserve">8.76079368591309</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">8.65442562103271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75112438201904</t>
+    <t xml:space="preserve">8.75112342834473</t>
   </si>
   <si>
     <t xml:space="preserve">8.70277500152588</t>
@@ -1652,10 +1652,10 @@
     <t xml:space="preserve">8.63508701324463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32565402984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31598472595215</t>
+    <t xml:space="preserve">8.32565498352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31598567962646</t>
   </si>
   <si>
     <t xml:space="preserve">8.30631542205811</t>
@@ -63400,7 +63400,7 @@
     </row>
     <row r="2339">
       <c r="A2339" s="1" t="n">
-        <v>46027.6911458333</v>
+        <v>46027.3333333333</v>
       </c>
       <c r="B2339" t="n">
         <v>10819</v>
@@ -63421,6 +63421,32 @@
         <v>744</v>
       </c>
       <c r="H2339" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2340">
+      <c r="A2340" s="1" t="n">
+        <v>46028.6910532407</v>
+      </c>
+      <c r="B2340" t="n">
+        <v>12870</v>
+      </c>
+      <c r="C2340" t="n">
+        <v>9.53999996185303</v>
+      </c>
+      <c r="D2340" t="n">
+        <v>9.35999965667725</v>
+      </c>
+      <c r="E2340" t="n">
+        <v>9.53999996185303</v>
+      </c>
+      <c r="F2340" t="n">
+        <v>9.38000011444092</v>
+      </c>
+      <c r="G2340" t="s">
+        <v>734</v>
+      </c>
+      <c r="H2340" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -44,67 +44,67 @@
     <t xml:space="preserve">FF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98565769195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08549976348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24887180328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09457588195801</t>
+    <t xml:space="preserve">8.98565673828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08549785614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24887275695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09457397460938</t>
   </si>
   <si>
     <t xml:space="preserve">9.12180328369141</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03104019165039</t>
+    <t xml:space="preserve">9.03103923797607</t>
   </si>
   <si>
     <t xml:space="preserve">8.95389080047607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89943313598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89489364624023</t>
+    <t xml:space="preserve">8.89943218231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89489459991455</t>
   </si>
   <si>
     <t xml:space="preserve">8.84951114654541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85858821868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87673950195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76782321929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86766338348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04919147491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23072052001953</t>
+    <t xml:space="preserve">8.85858726501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87674045562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.767822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86766529083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04919338226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23072147369385</t>
   </si>
   <si>
     <t xml:space="preserve">9.11272811889648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96750354766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91304683685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92212390899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00381088256836</t>
+    <t xml:space="preserve">8.96750450134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91304588317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92212295532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00380992889404</t>
   </si>
   <si>
     <t xml:space="preserve">9.15810966491699</t>
@@ -116,7 +116,7 @@
     <t xml:space="preserve">9.43947792053223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54839706420898</t>
+    <t xml:space="preserve">9.54839515686035</t>
   </si>
   <si>
     <t xml:space="preserve">9.62100791931152</t>
@@ -125,34 +125,34 @@
     <t xml:space="preserve">9.80253601074219</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71177005767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56654930114746</t>
+    <t xml:space="preserve">9.71177101135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56654834747314</t>
   </si>
   <si>
     <t xml:space="preserve">9.58470153808594</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57562637329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53024196624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50301551818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60285377502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63916015625</t>
+    <t xml:space="preserve">9.57562446594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53024291992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50301361083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60285472869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63915920257568</t>
   </si>
   <si>
     <t xml:space="preserve">9.79345893859863</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95683574676514</t>
+    <t xml:space="preserve">9.95683479309082</t>
   </si>
   <si>
     <t xml:space="preserve">9.93868160247803</t>
@@ -161,34 +161,34 @@
     <t xml:space="preserve">9.98406410217285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73900127410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7662296295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74807739257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75715351104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64823722839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82068824768066</t>
+    <t xml:space="preserve">9.73900032043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76623058319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74807643890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75715446472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64823627471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82068634033203</t>
   </si>
   <si>
     <t xml:space="preserve">9.70269393920898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72084808349609</t>
+    <t xml:space="preserve">9.72084712982178</t>
   </si>
   <si>
     <t xml:space="preserve">9.67546558380127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66638851165771</t>
+    <t xml:space="preserve">9.66639041900635</t>
   </si>
   <si>
     <t xml:space="preserve">9.63008308410645</t>
@@ -197,10 +197,10 @@
     <t xml:space="preserve">9.65731334686279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68454265594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81161212921143</t>
+    <t xml:space="preserve">9.68454360961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81161117553711</t>
   </si>
   <si>
     <t xml:space="preserve">9.8297643661499</t>
@@ -215,31 +215,31 @@
     <t xml:space="preserve">9.72992420196533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78438282012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55747318267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34871387481689</t>
+    <t xml:space="preserve">9.78438186645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55747222900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34871482849121</t>
   </si>
   <si>
     <t xml:space="preserve">9.33963775634766</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27610397338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2579517364502</t>
+    <t xml:space="preserve">9.27610301971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25794982910156</t>
   </si>
   <si>
     <t xml:space="preserve">9.19441509246826</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18533802032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41224956512451</t>
+    <t xml:space="preserve">9.18533897399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41225051879883</t>
   </si>
   <si>
     <t xml:space="preserve">9.22164440155029</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">9.31240940093994</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26702690124512</t>
+    <t xml:space="preserve">9.2670259475708</t>
   </si>
   <si>
     <t xml:space="preserve">9.29425525665283</t>
@@ -257,76 +257,76 @@
     <t xml:space="preserve">9.28517913818359</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37594509124756</t>
+    <t xml:space="preserve">9.37594318389893</t>
   </si>
   <si>
     <t xml:space="preserve">9.36686611175537</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3850212097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45763206481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39409732818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48486042022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49393749237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4485559463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47578430175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23979663848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14903259277344</t>
+    <t xml:space="preserve">9.38502025604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45763111114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39409828186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48486137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49393844604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44855499267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4757833480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23979759216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14903450012207</t>
   </si>
   <si>
     <t xml:space="preserve">9.21256828308105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20349311828613</t>
+    <t xml:space="preserve">9.20349216461182</t>
   </si>
   <si>
     <t xml:space="preserve">9.13088130950928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13995552062988</t>
+    <t xml:space="preserve">9.13995742797852</t>
   </si>
   <si>
     <t xml:space="preserve">8.94027614593506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80412864685059</t>
+    <t xml:space="preserve">8.8041296005249</t>
   </si>
   <si>
     <t xml:space="preserve">8.75874710083008</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66798210144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62259960174561</t>
+    <t xml:space="preserve">8.66798305511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62260150909424</t>
   </si>
   <si>
     <t xml:space="preserve">8.53183650970459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35030937194824</t>
+    <t xml:space="preserve">8.35030841827393</t>
   </si>
   <si>
     <t xml:space="preserve">8.16878032684326</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98725032806396</t>
+    <t xml:space="preserve">7.98725128173828</t>
   </si>
   <si>
     <t xml:space="preserve">8.03263378143311</t>
@@ -335,76 +335,76 @@
     <t xml:space="preserve">8.12339782714844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25954341888428</t>
+    <t xml:space="preserve">8.25954437255859</t>
   </si>
   <si>
     <t xml:space="preserve">7.94186973571777</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30492496490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21416282653809</t>
+    <t xml:space="preserve">8.3049259185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21416091918945</t>
   </si>
   <si>
     <t xml:space="preserve">8.39569091796875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57721710205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71336555480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53202247619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25706005096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44036960601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16540622711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07375240325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11958026885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98209857940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02792644500732</t>
+    <t xml:space="preserve">8.5772180557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71336460113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53202342987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25706100463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44036865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16540718078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07375144958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11957931518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98209953308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02792549133301</t>
   </si>
   <si>
     <t xml:space="preserve">9.62367630004883</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80698394775391</t>
+    <t xml:space="preserve">9.80698490142822</t>
   </si>
   <si>
     <t xml:space="preserve">9.89863872528076</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99029350280762</t>
+    <t xml:space="preserve">9.9902925491333</t>
   </si>
   <si>
     <t xml:space="preserve">10.1736011505127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2652559280396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3569087982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5402183532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.631872177124</t>
+    <t xml:space="preserve">10.2652549743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3569097518921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5402173995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6318731307983</t>
   </si>
   <si>
     <t xml:space="preserve">10.8151807785034</t>
@@ -413,7 +413,7 @@
     <t xml:space="preserve">10.7235260009766</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9068326950073</t>
+    <t xml:space="preserve">10.906834602356</t>
   </si>
   <si>
     <t xml:space="preserve">10.9984884262085</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">11.2734508514404</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4567575454712</t>
+    <t xml:space="preserve">11.4567594528198</t>
   </si>
   <si>
     <t xml:space="preserve">11.3651037216187</t>
@@ -437,25 +437,25 @@
     <t xml:space="preserve">10.4485626220703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71533107757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79878997802734</t>
+    <t xml:space="preserve">9.71533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79879093170166</t>
   </si>
   <si>
     <t xml:space="preserve">8.24886608123779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2112340927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30288696289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03709030151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3945426940918</t>
+    <t xml:space="preserve">9.21123313903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30288791656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03708934783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39454174041748</t>
   </si>
   <si>
     <t xml:space="preserve">9.76115798950195</t>
@@ -470,10 +470,10 @@
     <t xml:space="preserve">10.0361204147339</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94446754455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82552433013916</t>
+    <t xml:space="preserve">9.94446659088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82552528381348</t>
   </si>
   <si>
     <t xml:space="preserve">9.73283004760742</t>
@@ -485,67 +485,67 @@
     <t xml:space="preserve">9.96456527709961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91821670532227</t>
+    <t xml:space="preserve">9.91821765899658</t>
   </si>
   <si>
     <t xml:space="preserve">9.54744338989258</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0109119415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1036052703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1499519348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1962976455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77917766571045</t>
+    <t xml:space="preserve">10.010910987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1036043167114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1499509811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1962985992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77917671203613</t>
   </si>
   <si>
     <t xml:space="preserve">9.87187099456787</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0572595596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2889919281006</t>
+    <t xml:space="preserve">10.057258605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2889928817749</t>
   </si>
   <si>
     <t xml:space="preserve">10.4743795394897</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2426452636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3816862106323</t>
+    <t xml:space="preserve">10.2426462173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.381685256958</t>
   </si>
   <si>
     <t xml:space="preserve">9.68648338317871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64013576507568</t>
+    <t xml:space="preserve">9.64013671875</t>
   </si>
   <si>
     <t xml:space="preserve">9.50109672546387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31570911407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23228549957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1952075958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25082206726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26936149597168</t>
+    <t xml:space="preserve">9.31570816040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23228454589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19520664215088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25082302093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.269362449646</t>
   </si>
   <si>
     <t xml:space="preserve">9.2137451171875</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">9.04689693450928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12105274200439</t>
+    <t xml:space="preserve">9.12105369567871</t>
   </si>
   <si>
     <t xml:space="preserve">9.06543636322021</t>
@@ -566,10 +566,10 @@
     <t xml:space="preserve">9.17666816711426</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02835941314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95420360565186</t>
+    <t xml:space="preserve">9.02835845947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95420265197754</t>
   </si>
   <si>
     <t xml:space="preserve">8.71320056915283</t>
@@ -578,10 +578,10 @@
     <t xml:space="preserve">8.99128150939941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7688159942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89858722686768</t>
+    <t xml:space="preserve">8.76881694793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89858818054199</t>
   </si>
   <si>
     <t xml:space="preserve">8.93566513061523</t>
@@ -590,10 +590,10 @@
     <t xml:space="preserve">10.3353385925293</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9841947555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0305404663086</t>
+    <t xml:space="preserve">10.9841938018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0305414199829</t>
   </si>
   <si>
     <t xml:space="preserve">11.2159290313721</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">11.540355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5867023468018</t>
+    <t xml:space="preserve">11.5867042541504</t>
   </si>
   <si>
     <t xml:space="preserve">11.6330490112305</t>
@@ -620,16 +620,16 @@
     <t xml:space="preserve">11.9574766159058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1892118453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2819051742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3745994567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5136394500732</t>
+    <t xml:space="preserve">12.1892108917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2819042205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3745985031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5136384963989</t>
   </si>
   <si>
     <t xml:space="preserve">12.3282518386841</t>
@@ -638,13 +638,13 @@
     <t xml:space="preserve">12.1428651809692</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0965194702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5551204681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5082750320435</t>
+    <t xml:space="preserve">12.0965185165405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5551223754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5082740783691</t>
   </si>
   <si>
     <t xml:space="preserve">12.6488170623779</t>
@@ -653,31 +653,31 @@
     <t xml:space="preserve">12.4614267349243</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4145793914795</t>
+    <t xml:space="preserve">12.4145784378052</t>
   </si>
   <si>
     <t xml:space="preserve">12.7425127029419</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6956653594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2271909713745</t>
+    <t xml:space="preserve">12.6956644058228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2271900177002</t>
   </si>
   <si>
     <t xml:space="preserve">12.1803426742554</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3208847045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.274037361145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8362064361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7893600463867</t>
+    <t xml:space="preserve">12.3208837509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2740383148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8362073898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7893590927124</t>
   </si>
   <si>
     <t xml:space="preserve">12.6019687652588</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">12.9299011230469</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8830537796021</t>
+    <t xml:space="preserve">12.8830528259277</t>
   </si>
   <si>
     <t xml:space="preserve">13.0704441070557</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">15.1785802841187</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3191232681274</t>
+    <t xml:space="preserve">15.3191242218018</t>
   </si>
   <si>
     <t xml:space="preserve">14.8974952697754</t>
@@ -731,28 +731,28 @@
     <t xml:space="preserve">15.4596643447876</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4128189086914</t>
+    <t xml:space="preserve">15.4128179550171</t>
   </si>
   <si>
     <t xml:space="preserve">15.5533609390259</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0686798095703</t>
+    <t xml:space="preserve">16.0686817169189</t>
   </si>
   <si>
     <t xml:space="preserve">16.8650894165039</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0056324005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7713928222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.193021774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0524806976318</t>
+    <t xml:space="preserve">17.0056304931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7713947296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1930236816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0524787902832</t>
   </si>
   <si>
     <t xml:space="preserve">16.9587841033936</t>
@@ -773,10 +773,10 @@
     <t xml:space="preserve">16.2092227935791</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2560710906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1461734771729</t>
+    <t xml:space="preserve">16.2560729980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1461715698242</t>
   </si>
   <si>
     <t xml:space="preserve">16.396614074707</t>
@@ -791,28 +791,28 @@
     <t xml:space="preserve">16.1155300140381</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0218372344971</t>
+    <t xml:space="preserve">16.0218353271484</t>
   </si>
   <si>
     <t xml:space="preserve">16.1623764038086</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9749870300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7407493591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4434604644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9119358062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0993270874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.677698135376</t>
+    <t xml:space="preserve">15.9749851226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7407512664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4434623718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9119338989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0993251800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6777000427246</t>
   </si>
   <si>
     <t xml:space="preserve">16.8182430267334</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">14.1010885238647</t>
   </si>
   <si>
-    <t xml:space="preserve">14.288477897644</t>
+    <t xml:space="preserve">14.2884769439697</t>
   </si>
   <si>
     <t xml:space="preserve">14.5227155685425</t>
@@ -848,16 +848,16 @@
     <t xml:space="preserve">13.960545539856</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2416305541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1947832107544</t>
+    <t xml:space="preserve">14.2416296005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1947822570801</t>
   </si>
   <si>
     <t xml:space="preserve">14.0073928833008</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7263078689575</t>
+    <t xml:space="preserve">13.7263069152832</t>
   </si>
   <si>
     <t xml:space="preserve">14.1479358673096</t>
@@ -869,22 +869,22 @@
     <t xml:space="preserve">14.6164102554321</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7731561660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3515291213989</t>
+    <t xml:space="preserve">13.7731552124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3515281677246</t>
   </si>
   <si>
     <t xml:space="preserve">13.3046808242798</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3983755111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0235958099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1172904968262</t>
+    <t xml:space="preserve">13.3983764648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0235967636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1172924041748</t>
   </si>
   <si>
     <t xml:space="preserve">12.976749420166</t>
@@ -896,13 +896,13 @@
     <t xml:space="preserve">12.0866460800171</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9929513931274</t>
+    <t xml:space="preserve">11.9929523468018</t>
   </si>
   <si>
     <t xml:space="preserve">11.8992576599121</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0397996902466</t>
+    <t xml:space="preserve">12.0397987365723</t>
   </si>
   <si>
     <t xml:space="preserve">12.1334943771362</t>
@@ -920,16 +920,16 @@
     <t xml:space="preserve">11.6650199890137</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4307823181152</t>
+    <t xml:space="preserve">11.4307832717896</t>
   </si>
   <si>
     <t xml:space="preserve">10.9623079299927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7280702590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1965446472168</t>
+    <t xml:space="preserve">10.7280693054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1965436935425</t>
   </si>
   <si>
     <t xml:space="preserve">11.5713243484497</t>
@@ -941,7 +941,7 @@
     <t xml:space="preserve">11.2902402877808</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7118673324585</t>
+    <t xml:space="preserve">11.7118682861328</t>
   </si>
   <si>
     <t xml:space="preserve">11.7587146759033</t>
@@ -953,22 +953,22 @@
     <t xml:space="preserve">11.0091552734375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46318817138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33884906768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57308673858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31074047088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45128440856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61993408203125</t>
+    <t xml:space="preserve">9.46318912506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3388500213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57308578491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31074142456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45128345489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61993503570557</t>
   </si>
   <si>
     <t xml:space="preserve">8.44191455841064</t>
@@ -983,19 +983,19 @@
     <t xml:space="preserve">8.43254470825195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47002124786377</t>
+    <t xml:space="preserve">8.47002220153809</t>
   </si>
   <si>
     <t xml:space="preserve">8.32011032104492</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20767688751221</t>
+    <t xml:space="preserve">8.20767593383789</t>
   </si>
   <si>
     <t xml:space="preserve">8.0858736038208</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78604936599731</t>
+    <t xml:space="preserve">7.78605031967163</t>
   </si>
   <si>
     <t xml:space="preserve">7.49559545516968</t>
@@ -1010,16 +1010,16 @@
     <t xml:space="preserve">7.83289623260498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9078516960144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50496482849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37379217147827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12081527709961</t>
+    <t xml:space="preserve">7.90785264968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50496530532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37379169464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12081480026245</t>
   </si>
   <si>
     <t xml:space="preserve">7.28009653091431</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">7.02712059020996</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34568309783936</t>
+    <t xml:space="preserve">7.34568357467651</t>
   </si>
   <si>
     <t xml:space="preserve">7.54244232177734</t>
@@ -1049,28 +1049,28 @@
     <t xml:space="preserve">8.2170467376709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65194225311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46116161346436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53747367858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68056201934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77595138549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84272575378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825622558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6614818572998</t>
+    <t xml:space="preserve">8.65194320678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46116256713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53747463226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68056106567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77595233917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8427267074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825527191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66148281097412</t>
   </si>
   <si>
     <t xml:space="preserve">8.49931812286377</t>
@@ -1082,16 +1082,16 @@
     <t xml:space="preserve">8.39438915252686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60424900054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48977851867676</t>
+    <t xml:space="preserve">8.604248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48977947235107</t>
   </si>
   <si>
     <t xml:space="preserve">8.29899787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12729358673096</t>
+    <t xml:space="preserve">8.12729454040527</t>
   </si>
   <si>
     <t xml:space="preserve">7.89835643768311</t>
@@ -1112,19 +1112,19 @@
     <t xml:space="preserve">8.06052017211914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07959842681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07005977630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92697334289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98420810699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30853748321533</t>
+    <t xml:space="preserve">8.07959938049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07005882263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92697429656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98420858383179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30853652954102</t>
   </si>
   <si>
     <t xml:space="preserve">8.26084136962891</t>
@@ -1133,13 +1133,13 @@
     <t xml:space="preserve">8.27038097381592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18452930450439</t>
+    <t xml:space="preserve">8.18452835083008</t>
   </si>
   <si>
     <t xml:space="preserve">8.03190326690674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96512985229492</t>
+    <t xml:space="preserve">7.96513080596924</t>
   </si>
   <si>
     <t xml:space="preserve">7.86019992828369</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">7.91743516921997</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76480960845947</t>
+    <t xml:space="preserve">7.76481008529663</t>
   </si>
   <si>
     <t xml:space="preserve">7.72665309906006</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">7.63126230239868</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65987873077393</t>
+    <t xml:space="preserve">7.65987968444824</t>
   </si>
   <si>
     <t xml:space="preserve">8.16545104980469</t>
@@ -1175,22 +1175,22 @@
     <t xml:space="preserve">8.32761383056641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11775493621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9365119934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19406890869141</t>
+    <t xml:space="preserve">8.11775588989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93651247024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19406795501709</t>
   </si>
   <si>
     <t xml:space="preserve">8.2322244644165</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31807708740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15591239929199</t>
+    <t xml:space="preserve">8.31807518005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15591144561768</t>
   </si>
   <si>
     <t xml:space="preserve">8.22268486022949</t>
@@ -1199,16 +1199,16 @@
     <t xml:space="preserve">8.25130176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35623264312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2417631149292</t>
+    <t xml:space="preserve">8.35623168945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24176406860352</t>
   </si>
   <si>
     <t xml:space="preserve">8.34669303894043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95559072494507</t>
+    <t xml:space="preserve">7.95559167861938</t>
   </si>
   <si>
     <t xml:space="preserve">7.77434825897217</t>
@@ -1220,10 +1220,10 @@
     <t xml:space="preserve">7.97466850280762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01282501220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05098056793213</t>
+    <t xml:space="preserve">8.01282596588135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05098152160645</t>
   </si>
   <si>
     <t xml:space="preserve">7.67895746231079</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">7.73619174957275</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6980357170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5167932510376</t>
+    <t xml:space="preserve">7.69803524017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51679372787476</t>
   </si>
   <si>
     <t xml:space="preserve">7.59310626983643</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">7.62172269821167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52633237838745</t>
+    <t xml:space="preserve">7.52633190155029</t>
   </si>
   <si>
     <t xml:space="preserve">7.34508991241455</t>
@@ -1262,25 +1262,25 @@
     <t xml:space="preserve">7.18292570114136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14476919174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12569093704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23062086105347</t>
+    <t xml:space="preserve">7.14476871490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12569046020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23062133789062</t>
   </si>
   <si>
     <t xml:space="preserve">7.1543083190918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24969911575317</t>
+    <t xml:space="preserve">7.24969863891602</t>
   </si>
   <si>
     <t xml:space="preserve">7.24016046524048</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46909761428833</t>
+    <t xml:space="preserve">7.46909809112549</t>
   </si>
   <si>
     <t xml:space="preserve">7.41186332702637</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">7.45001983642578</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28785562515259</t>
+    <t xml:space="preserve">7.28785514831543</t>
   </si>
   <si>
     <t xml:space="preserve">7.39278507232666</t>
@@ -1304,25 +1304,25 @@
     <t xml:space="preserve">7.90789556503296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94605112075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45955848693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70757436752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87927865982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99374723434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75527048110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81250476837158</t>
+    <t xml:space="preserve">7.94605159759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45955896377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70757484436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8792781829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99374771118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75527000427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81250381469727</t>
   </si>
   <si>
     <t xml:space="preserve">7.79342699050903</t>
@@ -1331,16 +1331,16 @@
     <t xml:space="preserve">7.80296611785889</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85066032409668</t>
+    <t xml:space="preserve">7.85065984725952</t>
   </si>
   <si>
     <t xml:space="preserve">7.74573087692261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83158254623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66941833496094</t>
+    <t xml:space="preserve">7.83158302307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66941785812378</t>
   </si>
   <si>
     <t xml:space="preserve">7.60264492034912</t>
@@ -1349,7 +1349,7 @@
     <t xml:space="preserve">7.58356666564941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88881778717041</t>
+    <t xml:space="preserve">7.88881826400757</t>
   </si>
   <si>
     <t xml:space="preserve">8.00328636169434</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">7.27831649780273</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08753442764282</t>
+    <t xml:space="preserve">7.08753490447998</t>
   </si>
   <si>
     <t xml:space="preserve">7.05891799926758</t>
@@ -1376,10 +1376,10 @@
     <t xml:space="preserve">7.50372648239136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98721361160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02589321136475</t>
+    <t xml:space="preserve">7.98721408843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02589225769043</t>
   </si>
   <si>
     <t xml:space="preserve">8.04523086547852</t>
@@ -1391,25 +1391,25 @@
     <t xml:space="preserve">8.07424163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12259006500244</t>
+    <t xml:space="preserve">8.12258911132812</t>
   </si>
   <si>
     <t xml:space="preserve">8.05490112304688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94853448867798</t>
+    <t xml:space="preserve">7.94853496551514</t>
   </si>
   <si>
     <t xml:space="preserve">8.06457138061523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08391094207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97754383087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93886423110962</t>
+    <t xml:space="preserve">8.08390998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97754430770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93886518478394</t>
   </si>
   <si>
     <t xml:space="preserve">7.79381895065308</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">7.68745088577271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63910245895386</t>
+    <t xml:space="preserve">7.63910293579102</t>
   </si>
   <si>
     <t xml:space="preserve">7.73579978942871</t>
@@ -1436,10 +1436,10 @@
     <t xml:space="preserve">7.90985584259033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85183715820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83249807357788</t>
+    <t xml:space="preserve">7.85183668136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83249759674072</t>
   </si>
   <si>
     <t xml:space="preserve">7.81315755844116</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">7.80348825454712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78414869308472</t>
+    <t xml:space="preserve">7.78414916992188</t>
   </si>
   <si>
     <t xml:space="preserve">7.6681113243103</t>
@@ -1460,13 +1460,13 @@
     <t xml:space="preserve">7.71646022796631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75514030456543</t>
+    <t xml:space="preserve">7.75513982772827</t>
   </si>
   <si>
     <t xml:space="preserve">7.74547004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86150646209717</t>
+    <t xml:space="preserve">7.86150693893433</t>
   </si>
   <si>
     <t xml:space="preserve">7.89051580429077</t>
@@ -1484,10 +1484,10 @@
     <t xml:space="preserve">8.09358024597168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1322603225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15159893035889</t>
+    <t xml:space="preserve">8.13225936889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1515998840332</t>
   </si>
   <si>
     <t xml:space="preserve">8.1129207611084</t>
@@ -1496,10 +1496,10 @@
     <t xml:space="preserve">8.03556251525879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92919540405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69712114334106</t>
+    <t xml:space="preserve">7.92919492721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69712066650391</t>
   </si>
   <si>
     <t xml:space="preserve">7.60042381286621</t>
@@ -1508,10 +1508,10 @@
     <t xml:space="preserve">7.88084602355957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55207490921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40702867507935</t>
+    <t xml:space="preserve">7.55207443237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40702819824219</t>
   </si>
   <si>
     <t xml:space="preserve">7.34900999069214</t>
@@ -1520,16 +1520,16 @@
     <t xml:space="preserve">7.37801933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43603801727295</t>
+    <t xml:space="preserve">7.43603754043579</t>
   </si>
   <si>
     <t xml:space="preserve">7.41669797897339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5230655670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36834907531738</t>
+    <t xml:space="preserve">7.52306604385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36834955215454</t>
   </si>
   <si>
     <t xml:space="preserve">7.542405128479</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">7.4843864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70679092407227</t>
+    <t xml:space="preserve">7.70679044723511</t>
   </si>
   <si>
     <t xml:space="preserve">7.64877223968506</t>
@@ -1556,10 +1556,10 @@
     <t xml:space="preserve">7.59075355529785</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95820331573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96787357330322</t>
+    <t xml:space="preserve">7.95820426940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96787405014038</t>
   </si>
   <si>
     <t xml:space="preserve">7.90018606185913</t>
@@ -1577,10 +1577,10 @@
     <t xml:space="preserve">8.19027900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29664516448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45136070251465</t>
+    <t xml:space="preserve">8.29664611816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45136165618896</t>
   </si>
   <si>
     <t xml:space="preserve">8.48037147521973</t>
@@ -1607,19 +1607,19 @@
     <t xml:space="preserve">8.50938034057617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42235279083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54805850982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55772876739502</t>
+    <t xml:space="preserve">8.4223518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54805946350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55772972106934</t>
   </si>
   <si>
     <t xml:space="preserve">8.52871990203857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68343544006348</t>
+    <t xml:space="preserve">8.68343448638916</t>
   </si>
   <si>
     <t xml:space="preserve">8.76079368591309</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">8.65442562103271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75112342834473</t>
+    <t xml:space="preserve">8.75112438201904</t>
   </si>
   <si>
     <t xml:space="preserve">8.70277500152588</t>
@@ -1652,10 +1652,10 @@
     <t xml:space="preserve">8.63508701324463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32565498352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31598567962646</t>
+    <t xml:space="preserve">8.32565402984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31598472595215</t>
   </si>
   <si>
     <t xml:space="preserve">8.30631542205811</t>
@@ -63426,16 +63426,16 @@
     </row>
     <row r="2340">
       <c r="A2340" s="1" t="n">
-        <v>46028.6910532407</v>
+        <v>46028.3333333333</v>
       </c>
       <c r="B2340" t="n">
-        <v>12870</v>
+        <v>13716</v>
       </c>
       <c r="C2340" t="n">
         <v>9.53999996185303</v>
       </c>
       <c r="D2340" t="n">
-        <v>9.35999965667725</v>
+        <v>9.34000015258789</v>
       </c>
       <c r="E2340" t="n">
         <v>9.53999996185303</v>
@@ -63447,6 +63447,32 @@
         <v>734</v>
       </c>
       <c r="H2340" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2341">
+      <c r="A2341" s="1" t="n">
+        <v>46029.6912037037</v>
+      </c>
+      <c r="B2341" t="n">
+        <v>20919</v>
+      </c>
+      <c r="C2341" t="n">
+        <v>9.46000003814697</v>
+      </c>
+      <c r="D2341" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="E2341" t="n">
+        <v>9.42000007629395</v>
+      </c>
+      <c r="F2341" t="n">
+        <v>9.23999977111816</v>
+      </c>
+      <c r="G2341" t="s">
+        <v>722</v>
+      </c>
+      <c r="H2341" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0764217376709</t>
+    <t xml:space="preserve">9.07642078399658</t>
   </si>
   <si>
     <t xml:space="preserve">FF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98565673828125</t>
+    <t xml:space="preserve">8.98565769195557</t>
   </si>
   <si>
     <t xml:space="preserve">9.08549785614014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24887275695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09457397460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12180328369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03103923797607</t>
+    <t xml:space="preserve">9.24887371063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09457588195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12180423736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03104019165039</t>
   </si>
   <si>
     <t xml:space="preserve">8.95389080047607</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">8.89943218231201</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89489459991455</t>
+    <t xml:space="preserve">8.89489364624023</t>
   </si>
   <si>
     <t xml:space="preserve">8.84951114654541</t>
@@ -77,28 +77,28 @@
     <t xml:space="preserve">8.85858726501465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87674045562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.767822265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86766529083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04919338226318</t>
+    <t xml:space="preserve">8.87673950195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76782417297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8676643371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04919242858887</t>
   </si>
   <si>
     <t xml:space="preserve">9.23072147369385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11272811889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96750450134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91304588317871</t>
+    <t xml:space="preserve">9.1127290725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96750354766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91304683685303</t>
   </si>
   <si>
     <t xml:space="preserve">8.92212295532227</t>
@@ -107,16 +107,16 @@
     <t xml:space="preserve">9.00380992889404</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15810966491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16718673706055</t>
+    <t xml:space="preserve">9.15810871124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16718578338623</t>
   </si>
   <si>
     <t xml:space="preserve">9.43947792053223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54839515686035</t>
+    <t xml:space="preserve">9.54839706420898</t>
   </si>
   <si>
     <t xml:space="preserve">9.62100791931152</t>
@@ -128,19 +128,19 @@
     <t xml:space="preserve">9.71177101135254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56654834747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58470153808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57562446594238</t>
+    <t xml:space="preserve">9.56654739379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58470249176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5756254196167</t>
   </si>
   <si>
     <t xml:space="preserve">9.53024291992188</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50301361083984</t>
+    <t xml:space="preserve">9.50301456451416</t>
   </si>
   <si>
     <t xml:space="preserve">9.60285472869873</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">9.63915920257568</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79345893859863</t>
+    <t xml:space="preserve">9.79345989227295</t>
   </si>
   <si>
     <t xml:space="preserve">9.95683479309082</t>
@@ -161,52 +161,52 @@
     <t xml:space="preserve">9.98406410217285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73900032043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76623058319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74807643890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75715446472168</t>
+    <t xml:space="preserve">9.73899936676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7662296295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74807739257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75715255737305</t>
   </si>
   <si>
     <t xml:space="preserve">9.64823627471924</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82068634033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70269393920898</t>
+    <t xml:space="preserve">9.82068729400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7026948928833</t>
   </si>
   <si>
     <t xml:space="preserve">9.72084712982178</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67546558380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66639041900635</t>
+    <t xml:space="preserve">9.6754674911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66638946533203</t>
   </si>
   <si>
     <t xml:space="preserve">9.63008308410645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65731334686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68454360961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81161117553711</t>
+    <t xml:space="preserve">9.65731239318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68454170227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81161403656006</t>
   </si>
   <si>
     <t xml:space="preserve">9.8297643661499</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84791851043701</t>
+    <t xml:space="preserve">9.8479175567627</t>
   </si>
   <si>
     <t xml:space="preserve">9.83884143829346</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">9.72992420196533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78438186645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55747222900391</t>
+    <t xml:space="preserve">9.78438282012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55747127532959</t>
   </si>
   <si>
     <t xml:space="preserve">9.34871482849121</t>
@@ -227,34 +227,34 @@
     <t xml:space="preserve">9.33963775634766</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27610301971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25794982910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19441509246826</t>
+    <t xml:space="preserve">9.27610206604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25795078277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19441699981689</t>
   </si>
   <si>
     <t xml:space="preserve">9.18533897399902</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41225051879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22164440155029</t>
+    <t xml:space="preserve">9.4122486114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22164535522461</t>
   </si>
   <si>
     <t xml:space="preserve">9.31240940093994</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2670259475708</t>
+    <t xml:space="preserve">9.26702690124512</t>
   </si>
   <si>
     <t xml:space="preserve">9.29425525665283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28517913818359</t>
+    <t xml:space="preserve">9.28517818450928</t>
   </si>
   <si>
     <t xml:space="preserve">9.37594318389893</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">9.36686611175537</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38502025604248</t>
+    <t xml:space="preserve">9.38502216339111</t>
   </si>
   <si>
     <t xml:space="preserve">9.45763111114502</t>
@@ -272,46 +272,46 @@
     <t xml:space="preserve">9.39409828186035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48486137390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49393844604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44855499267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4757833480835</t>
+    <t xml:space="preserve">9.48486042022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49393749237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44855403900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47578430175781</t>
   </si>
   <si>
     <t xml:space="preserve">9.23979759216309</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14903450012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21256828308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20349216461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13088130950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13995742797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94027614593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8041296005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75874710083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66798305511475</t>
+    <t xml:space="preserve">9.14903354644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21256732940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2034912109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13087940216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13995552062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94027519226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80412864685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75874519348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66798400878906</t>
   </si>
   <si>
     <t xml:space="preserve">8.62260150909424</t>
@@ -320,10 +320,10 @@
     <t xml:space="preserve">8.53183650970459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35030841827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16878032684326</t>
+    <t xml:space="preserve">8.35030937194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16877841949463</t>
   </si>
   <si>
     <t xml:space="preserve">7.98725128173828</t>
@@ -332,58 +332,58 @@
     <t xml:space="preserve">8.03263378143311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12339782714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25954437255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94186973571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3049259185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21416091918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39569091796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5772180557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71336460113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53202342987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25706100463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44036865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16540718078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07375144958496</t>
+    <t xml:space="preserve">8.12339687347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25954341888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94186925888062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30492496490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21416282653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39568996429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57721900939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71336650848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53202247619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25706005096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44036960601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16540622711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07375240325928</t>
   </si>
   <si>
     <t xml:space="preserve">9.11957931518555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98209953308105</t>
+    <t xml:space="preserve">8.98209857940674</t>
   </si>
   <si>
     <t xml:space="preserve">9.02792549133301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62367630004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80698490142822</t>
+    <t xml:space="preserve">9.62367725372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80698394775391</t>
   </si>
   <si>
     <t xml:space="preserve">9.89863872528076</t>
@@ -392,7 +392,7 @@
     <t xml:space="preserve">9.9902925491333</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1736011505127</t>
+    <t xml:space="preserve">10.173602104187</t>
   </si>
   <si>
     <t xml:space="preserve">10.2652549743652</t>
@@ -404,19 +404,19 @@
     <t xml:space="preserve">10.5402173995972</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6318731307983</t>
+    <t xml:space="preserve">10.631872177124</t>
   </si>
   <si>
     <t xml:space="preserve">10.8151807785034</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7235260009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.906834602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9984884262085</t>
+    <t xml:space="preserve">10.7235250473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9068326950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9984865188599</t>
   </si>
   <si>
     <t xml:space="preserve">11.0901432037354</t>
@@ -428,13 +428,13 @@
     <t xml:space="preserve">11.2734508514404</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4567594528198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3651037216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4485626220703</t>
+    <t xml:space="preserve">11.4567575454712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3651027679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4485635757446</t>
   </si>
   <si>
     <t xml:space="preserve">9.71533203125</t>
@@ -443,19 +443,19 @@
     <t xml:space="preserve">8.79879093170166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24886608123779</t>
+    <t xml:space="preserve">8.24886512756348</t>
   </si>
   <si>
     <t xml:space="preserve">9.21123313903809</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30288791656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03708934783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39454174041748</t>
+    <t xml:space="preserve">9.30288696289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03709030151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3945426940918</t>
   </si>
   <si>
     <t xml:space="preserve">9.76115798950195</t>
@@ -464,19 +464,19 @@
     <t xml:space="preserve">9.66950416564941</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57785034179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0361204147339</t>
+    <t xml:space="preserve">9.57784938812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0361194610596</t>
   </si>
   <si>
     <t xml:space="preserve">9.94446659088135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82552528381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73283004760742</t>
+    <t xml:space="preserve">9.82552433013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73283100128174</t>
   </si>
   <si>
     <t xml:space="preserve">9.59379100799561</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">9.91821765899658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54744338989258</t>
+    <t xml:space="preserve">9.54744434356689</t>
   </si>
   <si>
     <t xml:space="preserve">10.010910987854</t>
@@ -497,16 +497,16 @@
     <t xml:space="preserve">10.1036043167114</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1499509811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1962985992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77917671203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87187099456787</t>
+    <t xml:space="preserve">10.1499519348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1962976455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77917766571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87187004089355</t>
   </si>
   <si>
     <t xml:space="preserve">10.057258605957</t>
@@ -515,46 +515,46 @@
     <t xml:space="preserve">10.2889928817749</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4743795394897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2426462173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.381685256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68648338317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64013671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50109672546387</t>
+    <t xml:space="preserve">10.4743804931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2426443099976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3816843032837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68648242950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64013576507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50109577178955</t>
   </si>
   <si>
     <t xml:space="preserve">9.31570816040039</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23228454589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19520664215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25082302093506</t>
+    <t xml:space="preserve">9.23228359222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1952075958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25082397460938</t>
   </si>
   <si>
     <t xml:space="preserve">9.269362449646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2137451171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04689693450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12105369567871</t>
+    <t xml:space="preserve">9.21374607086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04689788818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12105274200439</t>
   </si>
   <si>
     <t xml:space="preserve">9.06543636322021</t>
@@ -569,16 +569,16 @@
     <t xml:space="preserve">9.02835845947266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95420265197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71320056915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99128150939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76881694793701</t>
+    <t xml:space="preserve">8.95420455932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71319961547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99128246307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7688159942627</t>
   </si>
   <si>
     <t xml:space="preserve">8.89858818054199</t>
@@ -587,7 +587,7 @@
     <t xml:space="preserve">8.93566513061523</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3353385925293</t>
+    <t xml:space="preserve">10.3353395462036</t>
   </si>
   <si>
     <t xml:space="preserve">10.9841938018799</t>
@@ -602,28 +602,28 @@
     <t xml:space="preserve">11.4940090179443</t>
   </si>
   <si>
-    <t xml:space="preserve">11.540355682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5867042541504</t>
+    <t xml:space="preserve">11.5403566360474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5867033004761</t>
   </si>
   <si>
     <t xml:space="preserve">11.6330490112305</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7257423400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9111299514771</t>
+    <t xml:space="preserve">11.7257432937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9111309051514</t>
   </si>
   <si>
     <t xml:space="preserve">11.9574766159058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1892108917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2819042205811</t>
+    <t xml:space="preserve">12.1892099380493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2819051742554</t>
   </si>
   <si>
     <t xml:space="preserve">12.3745985031128</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">12.3282518386841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1428651809692</t>
+    <t xml:space="preserve">12.1428642272949</t>
   </si>
   <si>
     <t xml:space="preserve">12.0965185165405</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5551223754883</t>
+    <t xml:space="preserve">12.555121421814</t>
   </si>
   <si>
     <t xml:space="preserve">12.5082740783691</t>
@@ -650,25 +650,25 @@
     <t xml:space="preserve">12.6488170623779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4614267349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4145784378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7425127029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6956644058228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2271900177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1803426742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3208837509155</t>
+    <t xml:space="preserve">12.4614276885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4145793914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7425117492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6956634521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2271890640259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1803417205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3208847045898</t>
   </si>
   <si>
     <t xml:space="preserve">12.2740383148193</t>
@@ -683,10 +683,10 @@
     <t xml:space="preserve">12.6019687652588</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9299011230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8830528259277</t>
+    <t xml:space="preserve">12.9299030303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8830547332764</t>
   </si>
   <si>
     <t xml:space="preserve">13.0704441070557</t>
@@ -695,16 +695,16 @@
     <t xml:space="preserve">13.679461479187</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8668518066406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0542411804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3353261947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5695629119873</t>
+    <t xml:space="preserve">13.8668508529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0542402267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3353252410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5695638656616</t>
   </si>
   <si>
     <t xml:space="preserve">15.2254276275635</t>
@@ -722,34 +722,34 @@
     <t xml:space="preserve">15.1785802841187</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3191242218018</t>
+    <t xml:space="preserve">15.3191232681274</t>
   </si>
   <si>
     <t xml:space="preserve">14.8974952697754</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4596643447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4128179550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5533609390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0686817169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8650894165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0056304931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7713947296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1930236816406</t>
+    <t xml:space="preserve">15.4596662521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4128198623657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5533590316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0686836242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8650875091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0056324005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7713928222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.193021774292</t>
   </si>
   <si>
     <t xml:space="preserve">17.0524787902832</t>
@@ -761,25 +761,25 @@
     <t xml:space="preserve">16.7245464324951</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6308517456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5371570587158</t>
+    <t xml:space="preserve">16.6308498382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5371551513672</t>
   </si>
   <si>
     <t xml:space="preserve">16.584005355835</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2092227935791</t>
+    <t xml:space="preserve">16.2092247009277</t>
   </si>
   <si>
     <t xml:space="preserve">16.2560729980469</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1461715698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.396614074707</t>
+    <t xml:space="preserve">17.1461734771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3966159820557</t>
   </si>
   <si>
     <t xml:space="preserve">16.3029193878174</t>
@@ -797,34 +797,34 @@
     <t xml:space="preserve">16.1623764038086</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9749851226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7407512664795</t>
+    <t xml:space="preserve">15.9749879837036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7407484054565</t>
   </si>
   <si>
     <t xml:space="preserve">16.4434623718262</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9119338989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0993251800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6777000427246</t>
+    <t xml:space="preserve">16.9119358062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0993270874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6776962280273</t>
   </si>
   <si>
     <t xml:space="preserve">16.8182430267334</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2722749710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0848846435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9911909103394</t>
+    <t xml:space="preserve">15.272274017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.084885597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.991189956665</t>
   </si>
   <si>
     <t xml:space="preserve">14.8038005828857</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">14.1010885238647</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2884769439697</t>
+    <t xml:space="preserve">14.2884788513184</t>
   </si>
   <si>
     <t xml:space="preserve">14.5227155685425</t>
@@ -848,34 +848,34 @@
     <t xml:space="preserve">13.960545539856</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2416296005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1947822570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0073928833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7263069152832</t>
+    <t xml:space="preserve">14.2416305541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1947832107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0073938369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7263078689575</t>
   </si>
   <si>
     <t xml:space="preserve">14.1479358673096</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4290208816528</t>
+    <t xml:space="preserve">14.4290199279785</t>
   </si>
   <si>
     <t xml:space="preserve">14.6164102554321</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7731552124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3515281677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3046808242798</t>
+    <t xml:space="preserve">13.773154258728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3515291213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3046817779541</t>
   </si>
   <si>
     <t xml:space="preserve">13.3983764648438</t>
@@ -884,94 +884,94 @@
     <t xml:space="preserve">13.0235967636108</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1172924041748</t>
+    <t xml:space="preserve">13.1172914505005</t>
   </si>
   <si>
     <t xml:space="preserve">12.976749420166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3677320480347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0866460800171</t>
+    <t xml:space="preserve">12.367733001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0866470336914</t>
   </si>
   <si>
     <t xml:space="preserve">11.9929523468018</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8992576599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0397987365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1334943771362</t>
+    <t xml:space="preserve">11.8992567062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0397996902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1334934234619</t>
   </si>
   <si>
     <t xml:space="preserve">11.4776296615601</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2433929443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3839349746704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6650199890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4307832717896</t>
+    <t xml:space="preserve">11.2433938980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3839340209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6650190353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4307823181152</t>
   </si>
   <si>
     <t xml:space="preserve">10.9623079299927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7280693054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1965436935425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5713243484497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3370885848999</t>
+    <t xml:space="preserve">10.7280712127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1965446472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.571325302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3370876312256</t>
   </si>
   <si>
     <t xml:space="preserve">11.2902402877808</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7118682861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7587146759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8055629730225</t>
+    <t xml:space="preserve">11.7118673324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7587156295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8055639266968</t>
   </si>
   <si>
     <t xml:space="preserve">11.0091552734375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46318912506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3388500213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57308578491211</t>
+    <t xml:space="preserve">9.46318817138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33884811401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57308673858643</t>
   </si>
   <si>
     <t xml:space="preserve">8.31074142456055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45128345489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61993503570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44191455841064</t>
+    <t xml:space="preserve">8.45128440856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61993408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44191360473633</t>
   </si>
   <si>
     <t xml:space="preserve">8.32948112487793</t>
@@ -980,25 +980,25 @@
     <t xml:space="preserve">8.25452423095703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43254470825195</t>
+    <t xml:space="preserve">8.43254375457764</t>
   </si>
   <si>
     <t xml:space="preserve">8.47002220153809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32011032104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20767593383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0858736038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78605031967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49559545516968</t>
+    <t xml:space="preserve">8.32011127471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20767688751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08587265014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78604936599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49559497833252</t>
   </si>
   <si>
     <t xml:space="preserve">7.33631372451782</t>
@@ -1010,40 +1010,40 @@
     <t xml:space="preserve">7.83289623260498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90785264968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50496530532837</t>
+    <t xml:space="preserve">7.90785217285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50496482849121</t>
   </si>
   <si>
     <t xml:space="preserve">7.37379169464111</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12081480026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28009653091431</t>
+    <t xml:space="preserve">7.12081527709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28009700775146</t>
   </si>
   <si>
     <t xml:space="preserve">6.98027276992798</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93342590332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06459808349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02712059020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34568357467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54244232177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19830703735352</t>
+    <t xml:space="preserve">6.93342542648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06459856033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0271201133728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34568309783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5424427986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19830799102783</t>
   </si>
   <si>
     <t xml:space="preserve">8.2170467376709</t>
@@ -1055,16 +1055,16 @@
     <t xml:space="preserve">8.46116256713867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53747463226318</t>
+    <t xml:space="preserve">8.53747367858887</t>
   </si>
   <si>
     <t xml:space="preserve">8.68056106567383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77595233917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8427267074585</t>
+    <t xml:space="preserve">8.77595138549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84272575378418</t>
   </si>
   <si>
     <t xml:space="preserve">8.72825527191162</t>
@@ -1073,25 +1073,25 @@
     <t xml:space="preserve">8.66148281097412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49931812286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42300510406494</t>
+    <t xml:space="preserve">8.49931716918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42300605773926</t>
   </si>
   <si>
     <t xml:space="preserve">8.39438915252686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.604248046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48977947235107</t>
+    <t xml:space="preserve">8.60424900054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48977851867676</t>
   </si>
   <si>
     <t xml:space="preserve">8.29899787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12729454040527</t>
+    <t xml:space="preserve">8.12729549407959</t>
   </si>
   <si>
     <t xml:space="preserve">7.89835643768311</t>
@@ -1100,13 +1100,13 @@
     <t xml:space="preserve">8.10821628570557</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84112215042114</t>
+    <t xml:space="preserve">7.8411226272583</t>
   </si>
   <si>
     <t xml:space="preserve">8.33715343475342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2036075592041</t>
+    <t xml:space="preserve">8.20360660552979</t>
   </si>
   <si>
     <t xml:space="preserve">8.06052017211914</t>
@@ -1115,13 +1115,13 @@
     <t xml:space="preserve">8.07959938049316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07005882263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92697429656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98420858383179</t>
+    <t xml:space="preserve">8.07005977630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92697334289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98420763015747</t>
   </si>
   <si>
     <t xml:space="preserve">8.30853652954102</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">8.26084136962891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27038097381592</t>
+    <t xml:space="preserve">8.2703800201416</t>
   </si>
   <si>
     <t xml:space="preserve">8.18452835083008</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03190326690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96513080596924</t>
+    <t xml:space="preserve">8.03190422058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96512985229492</t>
   </si>
   <si>
     <t xml:space="preserve">7.86019992828369</t>
@@ -1151,10 +1151,10 @@
     <t xml:space="preserve">7.71711397171021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91743516921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76481008529663</t>
+    <t xml:space="preserve">7.91743421554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76480960845947</t>
   </si>
   <si>
     <t xml:space="preserve">7.72665309906006</t>
@@ -1169,10 +1169,10 @@
     <t xml:space="preserve">7.65987968444824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16545104980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32761383056641</t>
+    <t xml:space="preserve">8.165452003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32761478424072</t>
   </si>
   <si>
     <t xml:space="preserve">8.11775588989258</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">8.2322244644165</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31807518005371</t>
+    <t xml:space="preserve">8.31807613372803</t>
   </si>
   <si>
     <t xml:space="preserve">8.15591144561768</t>
@@ -1196,19 +1196,19 @@
     <t xml:space="preserve">8.22268486022949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25130176544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35623168945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24176406860352</t>
+    <t xml:space="preserve">8.25130081176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35623264312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2417631149292</t>
   </si>
   <si>
     <t xml:space="preserve">8.34669303894043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95559167861938</t>
+    <t xml:space="preserve">7.95559072494507</t>
   </si>
   <si>
     <t xml:space="preserve">7.77434825897217</t>
@@ -1220,37 +1220,37 @@
     <t xml:space="preserve">7.97466850280762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01282596588135</t>
+    <t xml:space="preserve">8.01282501220703</t>
   </si>
   <si>
     <t xml:space="preserve">8.05098152160645</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67895746231079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73619174957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69803524017334</t>
+    <t xml:space="preserve">7.67895793914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7361912727356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6980357170105</t>
   </si>
   <si>
     <t xml:space="preserve">7.51679372787476</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59310626983643</t>
+    <t xml:space="preserve">7.59310579299927</t>
   </si>
   <si>
     <t xml:space="preserve">7.44048070907593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5358715057373</t>
+    <t xml:space="preserve">7.53587198257446</t>
   </si>
   <si>
     <t xml:space="preserve">7.62172269821167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52633190155029</t>
+    <t xml:space="preserve">7.52633237838745</t>
   </si>
   <si>
     <t xml:space="preserve">7.34508991241455</t>
@@ -1259,22 +1259,22 @@
     <t xml:space="preserve">7.20200395584106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18292570114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14476871490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12569046020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23062133789062</t>
+    <t xml:space="preserve">7.1829252243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14476919174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12569093704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23062086105347</t>
   </si>
   <si>
     <t xml:space="preserve">7.1543083190918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24969863891602</t>
+    <t xml:space="preserve">7.24969911575317</t>
   </si>
   <si>
     <t xml:space="preserve">7.24016046524048</t>
@@ -1283,16 +1283,16 @@
     <t xml:space="preserve">7.46909809112549</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41186332702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45001983642578</t>
+    <t xml:space="preserve">7.41186380386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45001935958862</t>
   </si>
   <si>
     <t xml:space="preserve">7.28785514831543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39278507232666</t>
+    <t xml:space="preserve">7.39278554916382</t>
   </si>
   <si>
     <t xml:space="preserve">7.3355507850647</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">7.61218404769897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90789556503296</t>
+    <t xml:space="preserve">7.90789604187012</t>
   </si>
   <si>
     <t xml:space="preserve">7.94605159759521</t>
@@ -1313,25 +1313,25 @@
     <t xml:space="preserve">7.70757484436035</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8792781829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99374771118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75527000427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81250381469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79342699050903</t>
+    <t xml:space="preserve">7.87927913665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99374675750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75527048110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81250429153442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79342651367188</t>
   </si>
   <si>
     <t xml:space="preserve">7.80296611785889</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85065984725952</t>
+    <t xml:space="preserve">7.85066080093384</t>
   </si>
   <si>
     <t xml:space="preserve">7.74573087692261</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">7.83158302307129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66941785812378</t>
+    <t xml:space="preserve">7.66941833496094</t>
   </si>
   <si>
     <t xml:space="preserve">7.60264492034912</t>
@@ -1361,13 +1361,13 @@
     <t xml:space="preserve">7.3641676902771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10661268234253</t>
+    <t xml:space="preserve">7.10661315917969</t>
   </si>
   <si>
     <t xml:space="preserve">7.27831649780273</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08753490447998</t>
+    <t xml:space="preserve">7.08753442764282</t>
   </si>
   <si>
     <t xml:space="preserve">7.05891799926758</t>
@@ -63452,7 +63452,7 @@
     </row>
     <row r="2341">
       <c r="A2341" s="1" t="n">
-        <v>46029.6912037037</v>
+        <v>46029.3333333333</v>
       </c>
       <c r="B2341" t="n">
         <v>20919</v>
@@ -63473,6 +63473,32 @@
         <v>722</v>
       </c>
       <c r="H2341" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2342">
+      <c r="A2342" s="1" t="n">
+        <v>46030.69125</v>
+      </c>
+      <c r="B2342" t="n">
+        <v>25819</v>
+      </c>
+      <c r="C2342" t="n">
+        <v>9.39999961853027</v>
+      </c>
+      <c r="D2342" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="E2342" t="n">
+        <v>9.30000019073486</v>
+      </c>
+      <c r="F2342" t="n">
+        <v>9.34000015258789</v>
+      </c>
+      <c r="G2342" t="s">
+        <v>736</v>
+      </c>
+      <c r="H2342" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -50,10 +50,10 @@
     <t xml:space="preserve">9.08549785614014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24887371063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09457588195801</t>
+    <t xml:space="preserve">9.24887275695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09457492828369</t>
   </si>
   <si>
     <t xml:space="preserve">9.12180423736572</t>
@@ -65,49 +65,49 @@
     <t xml:space="preserve">8.95389080047607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89943218231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89489364624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84951114654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85858726501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87673950195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76782417297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8676643371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04919242858887</t>
+    <t xml:space="preserve">8.8994312286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89489269256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84951210021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85858821868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87674045562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76782321929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86766529083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04919338226318</t>
   </si>
   <si>
     <t xml:space="preserve">9.23072147369385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1127290725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96750354766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91304683685303</t>
+    <t xml:space="preserve">9.11272716522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96750450134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91304588317871</t>
   </si>
   <si>
     <t xml:space="preserve">8.92212295532227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00380992889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15810871124268</t>
+    <t xml:space="preserve">9.00381088256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15810966491699</t>
   </si>
   <si>
     <t xml:space="preserve">9.16718578338623</t>
@@ -116,19 +116,19 @@
     <t xml:space="preserve">9.43947792053223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54839706420898</t>
+    <t xml:space="preserve">9.54839611053467</t>
   </si>
   <si>
     <t xml:space="preserve">9.62100791931152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80253601074219</t>
+    <t xml:space="preserve">9.8025369644165</t>
   </si>
   <si>
     <t xml:space="preserve">9.71177101135254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56654739379883</t>
+    <t xml:space="preserve">9.56654930114746</t>
   </si>
   <si>
     <t xml:space="preserve">9.58470249176025</t>
@@ -137,10 +137,10 @@
     <t xml:space="preserve">9.5756254196167</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53024291992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50301456451416</t>
+    <t xml:space="preserve">9.53024196624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50301265716553</t>
   </si>
   <si>
     <t xml:space="preserve">9.60285472869873</t>
@@ -149,13 +149,13 @@
     <t xml:space="preserve">9.63915920257568</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79345989227295</t>
+    <t xml:space="preserve">9.79345893859863</t>
   </si>
   <si>
     <t xml:space="preserve">9.95683479309082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93868160247803</t>
+    <t xml:space="preserve">9.93868255615234</t>
   </si>
   <si>
     <t xml:space="preserve">9.98406410217285</t>
@@ -164,43 +164,43 @@
     <t xml:space="preserve">9.73899936676025</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7662296295166</t>
+    <t xml:space="preserve">9.76623058319092</t>
   </si>
   <si>
     <t xml:space="preserve">9.74807739257812</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75715255737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64823627471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82068729400635</t>
+    <t xml:space="preserve">9.75715351104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64823722839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82068824768066</t>
   </si>
   <si>
     <t xml:space="preserve">9.7026948928833</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72084712982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6754674911499</t>
+    <t xml:space="preserve">9.72084808349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67546463012695</t>
   </si>
   <si>
     <t xml:space="preserve">9.66638946533203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63008308410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65731239318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68454170227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81161403656006</t>
+    <t xml:space="preserve">9.63008213043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65731334686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68454265594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81161212921143</t>
   </si>
   <si>
     <t xml:space="preserve">9.8297643661499</t>
@@ -212,64 +212,64 @@
     <t xml:space="preserve">9.83884143829346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72992420196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78438282012939</t>
+    <t xml:space="preserve">9.7299222946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78438377380371</t>
   </si>
   <si>
     <t xml:space="preserve">9.55747127532959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34871482849121</t>
+    <t xml:space="preserve">9.34871387481689</t>
   </si>
   <si>
     <t xml:space="preserve">9.33963775634766</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27610206604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25795078277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19441699981689</t>
+    <t xml:space="preserve">9.27610397338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25794982910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19441509246826</t>
   </si>
   <si>
     <t xml:space="preserve">9.18533897399902</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4122486114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22164535522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31240940093994</t>
+    <t xml:space="preserve">9.41225051879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22164440155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31240844726562</t>
   </si>
   <si>
     <t xml:space="preserve">9.26702690124512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29425525665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28517818450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37594318389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36686611175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38502216339111</t>
+    <t xml:space="preserve">9.29425621032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28517913818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37594413757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36686706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3850212097168</t>
   </si>
   <si>
     <t xml:space="preserve">9.45763111114502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39409828186035</t>
+    <t xml:space="preserve">9.39409732818604</t>
   </si>
   <si>
     <t xml:space="preserve">9.48486042022705</t>
@@ -278,52 +278,52 @@
     <t xml:space="preserve">9.49393749237061</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44855403900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47578430175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23979759216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14903354644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21256732940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2034912109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13087940216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13995552062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94027519226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80412864685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75874519348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66798400878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62260150909424</t>
+    <t xml:space="preserve">9.44855499267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4757833480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2397985458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14903259277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21256828308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20349311828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13088035583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1399564743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94027423858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80412769317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75874614715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66798210144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62260055541992</t>
   </si>
   <si>
     <t xml:space="preserve">8.53183650970459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35030937194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16877841949463</t>
+    <t xml:space="preserve">8.35030841827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16878032684326</t>
   </si>
   <si>
     <t xml:space="preserve">7.98725128173828</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">7.94186925888062</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30492496490479</t>
+    <t xml:space="preserve">8.30492687225342</t>
   </si>
   <si>
     <t xml:space="preserve">8.21416282653809</t>
@@ -350,22 +350,22 @@
     <t xml:space="preserve">8.39568996429443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57721900939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71336650848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53202247619629</t>
+    <t xml:space="preserve">8.57721710205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71336460113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53202342987061</t>
   </si>
   <si>
     <t xml:space="preserve">9.25706005096436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44036960601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16540622711182</t>
+    <t xml:space="preserve">9.44036865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16540718078613</t>
   </si>
   <si>
     <t xml:space="preserve">9.07375240325928</t>
@@ -374,25 +374,25 @@
     <t xml:space="preserve">9.11957931518555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98209857940674</t>
+    <t xml:space="preserve">8.98209762573242</t>
   </si>
   <si>
     <t xml:space="preserve">9.02792549133301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62367725372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80698394775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89863872528076</t>
+    <t xml:space="preserve">9.62367820739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80698490142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89863967895508</t>
   </si>
   <si>
     <t xml:space="preserve">9.9902925491333</t>
   </si>
   <si>
-    <t xml:space="preserve">10.173602104187</t>
+    <t xml:space="preserve">10.1736011505127</t>
   </si>
   <si>
     <t xml:space="preserve">10.2652549743652</t>
@@ -401,7 +401,7 @@
     <t xml:space="preserve">10.3569097518921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5402173995972</t>
+    <t xml:space="preserve">10.5402183532715</t>
   </si>
   <si>
     <t xml:space="preserve">10.631872177124</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">10.9068326950073</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9984865188599</t>
+    <t xml:space="preserve">10.9984874725342</t>
   </si>
   <si>
     <t xml:space="preserve">11.0901432037354</t>
@@ -437,19 +437,19 @@
     <t xml:space="preserve">10.4485635757446</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71533203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79879093170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24886512756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21123313903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30288696289062</t>
+    <t xml:space="preserve">9.71533107757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79878997802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24886608123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2112340927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30288791656494</t>
   </si>
   <si>
     <t xml:space="preserve">9.03709030151367</t>
@@ -458,127 +458,127 @@
     <t xml:space="preserve">9.3945426940918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76115798950195</t>
+    <t xml:space="preserve">9.76115703582764</t>
   </si>
   <si>
     <t xml:space="preserve">9.66950416564941</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57784938812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0361194610596</t>
+    <t xml:space="preserve">9.57785034179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0361204147339</t>
   </si>
   <si>
     <t xml:space="preserve">9.94446659088135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82552433013916</t>
+    <t xml:space="preserve">9.82552337646484</t>
   </si>
   <si>
     <t xml:space="preserve">9.73283100128174</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59379100799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96456527709961</t>
+    <t xml:space="preserve">9.59379005432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96456432342529</t>
   </si>
   <si>
     <t xml:space="preserve">9.91821765899658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54744434356689</t>
+    <t xml:space="preserve">9.54744338989258</t>
   </si>
   <si>
     <t xml:space="preserve">10.010910987854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1036043167114</t>
+    <t xml:space="preserve">10.1036052703857</t>
   </si>
   <si>
     <t xml:space="preserve">10.1499519348145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1962976455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77917766571045</t>
+    <t xml:space="preserve">10.1962985992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77917671203613</t>
   </si>
   <si>
     <t xml:space="preserve">9.87187004089355</t>
   </si>
   <si>
-    <t xml:space="preserve">10.057258605957</t>
+    <t xml:space="preserve">10.0572576522827</t>
   </si>
   <si>
     <t xml:space="preserve">10.2889928817749</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4743804931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2426443099976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3816843032837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68648242950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64013576507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50109577178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31570816040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23228359222412</t>
+    <t xml:space="preserve">10.4743795394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2426452636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3816862106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68648338317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64013671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50109672546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31570911407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23228454589844</t>
   </si>
   <si>
     <t xml:space="preserve">9.1952075958252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25082397460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.269362449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21374607086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04689788818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12105274200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06543636322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97274303436279</t>
+    <t xml:space="preserve">9.25082302093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26936149597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21374702453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04689693450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12105369567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0654354095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97274208068848</t>
   </si>
   <si>
     <t xml:space="preserve">9.17666816711426</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02835845947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95420455932617</t>
+    <t xml:space="preserve">9.02835941314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95420360565186</t>
   </si>
   <si>
     <t xml:space="preserve">8.71319961547852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99128246307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7688159942627</t>
+    <t xml:space="preserve">8.99128150939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76881694793701</t>
   </si>
   <si>
     <t xml:space="preserve">8.89858818054199</t>
@@ -587,46 +587,46 @@
     <t xml:space="preserve">8.93566513061523</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3353395462036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9841938018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0305414199829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2159290313721</t>
+    <t xml:space="preserve">10.3353385925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9841947555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0305404663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2159280776978</t>
   </si>
   <si>
     <t xml:space="preserve">11.4940090179443</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5403566360474</t>
+    <t xml:space="preserve">11.540355682373</t>
   </si>
   <si>
     <t xml:space="preserve">11.5867033004761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6330490112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7257432937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9111309051514</t>
+    <t xml:space="preserve">11.6330499649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7257423400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9111299514771</t>
   </si>
   <si>
     <t xml:space="preserve">11.9574766159058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1892099380493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2819051742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3745985031128</t>
+    <t xml:space="preserve">12.1892108917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2819042205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3745994567871</t>
   </si>
   <si>
     <t xml:space="preserve">12.5136384963989</t>
@@ -635,16 +635,16 @@
     <t xml:space="preserve">12.3282518386841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1428642272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0965185165405</t>
+    <t xml:space="preserve">12.1428651809692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0965175628662</t>
   </si>
   <si>
     <t xml:space="preserve">12.555121421814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5082740783691</t>
+    <t xml:space="preserve">12.5082750320435</t>
   </si>
   <si>
     <t xml:space="preserve">12.6488170623779</t>
@@ -656,37 +656,37 @@
     <t xml:space="preserve">12.4145793914795</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7425117492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6956634521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2271890640259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1803417205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3208847045898</t>
+    <t xml:space="preserve">12.7425127029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6956644058228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2271900177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1803426742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3208837509155</t>
   </si>
   <si>
     <t xml:space="preserve">12.2740383148193</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8362073898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7893590927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6019687652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9299030303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8830547332764</t>
+    <t xml:space="preserve">12.8362064361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7893581390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6019697189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9299020767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8830537796021</t>
   </si>
   <si>
     <t xml:space="preserve">13.0704441070557</t>
@@ -707,10 +707,10 @@
     <t xml:space="preserve">14.5695638656616</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2254276275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1317319869995</t>
+    <t xml:space="preserve">15.2254285812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1317329406738</t>
   </si>
   <si>
     <t xml:space="preserve">14.7569532394409</t>
@@ -719,34 +719,34 @@
     <t xml:space="preserve">15.0380373001099</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1785802841187</t>
+    <t xml:space="preserve">15.178581237793</t>
   </si>
   <si>
     <t xml:space="preserve">15.3191232681274</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8974952697754</t>
+    <t xml:space="preserve">14.8974943161011</t>
   </si>
   <si>
     <t xml:space="preserve">15.4596662521362</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4128198623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5533590316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0686836242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8650875091553</t>
+    <t xml:space="preserve">15.4128189086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5533599853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0686817169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8650894165039</t>
   </si>
   <si>
     <t xml:space="preserve">17.0056324005127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7713928222656</t>
+    <t xml:space="preserve">16.7713947296143</t>
   </si>
   <si>
     <t xml:space="preserve">17.193021774292</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">17.0524787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9587841033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7245464324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6308498382568</t>
+    <t xml:space="preserve">16.9587860107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7245483398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6308536529541</t>
   </si>
   <si>
     <t xml:space="preserve">16.5371551513672</t>
@@ -770,19 +770,19 @@
     <t xml:space="preserve">16.584005355835</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2092247009277</t>
+    <t xml:space="preserve">16.2092227935791</t>
   </si>
   <si>
     <t xml:space="preserve">16.2560729980469</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1461734771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3966159820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3029193878174</t>
+    <t xml:space="preserve">17.1461715698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.396614074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3029174804688</t>
   </si>
   <si>
     <t xml:space="preserve">15.8344440460205</t>
@@ -797,25 +797,25 @@
     <t xml:space="preserve">16.1623764038086</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9749879837036</t>
+    <t xml:space="preserve">15.974986076355</t>
   </si>
   <si>
     <t xml:space="preserve">15.7407484054565</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4434623718262</t>
+    <t xml:space="preserve">16.4434604644775</t>
   </si>
   <si>
     <t xml:space="preserve">16.9119358062744</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0993270874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6776962280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8182430267334</t>
+    <t xml:space="preserve">17.0993251800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.677698135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.818244934082</t>
   </si>
   <si>
     <t xml:space="preserve">15.272274017334</t>
@@ -824,10 +824,10 @@
     <t xml:space="preserve">15.084885597229</t>
   </si>
   <si>
-    <t xml:space="preserve">14.991189956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8038005828857</t>
+    <t xml:space="preserve">14.9911909103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8037996292114</t>
   </si>
   <si>
     <t xml:space="preserve">14.4758682250977</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">14.1010885238647</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2884788513184</t>
+    <t xml:space="preserve">14.288477897644</t>
   </si>
   <si>
     <t xml:space="preserve">14.5227155685425</t>
@@ -857,7 +857,7 @@
     <t xml:space="preserve">14.0073938369751</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7263078689575</t>
+    <t xml:space="preserve">13.7263088226318</t>
   </si>
   <si>
     <t xml:space="preserve">14.1479358673096</t>
@@ -866,16 +866,16 @@
     <t xml:space="preserve">14.4290199279785</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6164102554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.773154258728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3515291213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3046817779541</t>
+    <t xml:space="preserve">14.6164112091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7731561660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3515281677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3046808242798</t>
   </si>
   <si>
     <t xml:space="preserve">13.3983764648438</t>
@@ -884,28 +884,28 @@
     <t xml:space="preserve">13.0235967636108</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1172914505005</t>
+    <t xml:space="preserve">13.1172924041748</t>
   </si>
   <si>
     <t xml:space="preserve">12.976749420166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.367733001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0866470336914</t>
+    <t xml:space="preserve">12.3677320480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0866460800171</t>
   </si>
   <si>
     <t xml:space="preserve">11.9929523468018</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8992567062378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0397996902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1334934234619</t>
+    <t xml:space="preserve">11.8992576599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0397987365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1334943771362</t>
   </si>
   <si>
     <t xml:space="preserve">11.4776296615601</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">11.3839340209961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6650190353394</t>
+    <t xml:space="preserve">11.6650199890137</t>
   </si>
   <si>
     <t xml:space="preserve">11.4307823181152</t>
@@ -929,10 +929,10 @@
     <t xml:space="preserve">10.7280712127686</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1965446472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.571325302124</t>
+    <t xml:space="preserve">11.1965456008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5713243484497</t>
   </si>
   <si>
     <t xml:space="preserve">11.3370876312256</t>
@@ -941,46 +941,46 @@
     <t xml:space="preserve">11.2902402877808</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7118673324585</t>
+    <t xml:space="preserve">11.7118682861328</t>
   </si>
   <si>
     <t xml:space="preserve">11.7587156295776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8055639266968</t>
+    <t xml:space="preserve">11.8055629730225</t>
   </si>
   <si>
     <t xml:space="preserve">11.0091552734375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46318817138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33884811401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57308673858643</t>
+    <t xml:space="preserve">9.46318912506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33884906768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57308578491211</t>
   </si>
   <si>
     <t xml:space="preserve">8.31074142456055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45128440856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61993408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44191360473633</t>
+    <t xml:space="preserve">8.45128345489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61993312835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44191455841064</t>
   </si>
   <si>
     <t xml:space="preserve">8.32948112487793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25452423095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43254375457764</t>
+    <t xml:space="preserve">8.25452327728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43254470825195</t>
   </si>
   <si>
     <t xml:space="preserve">8.47002220153809</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">8.32011127471924</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20767688751221</t>
+    <t xml:space="preserve">8.20767784118652</t>
   </si>
   <si>
     <t xml:space="preserve">8.08587265014648</t>
@@ -998,7 +998,7 @@
     <t xml:space="preserve">7.78604936599731</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49559497833252</t>
+    <t xml:space="preserve">7.49559545516968</t>
   </si>
   <si>
     <t xml:space="preserve">7.33631372451782</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">7.83289623260498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90785217285156</t>
+    <t xml:space="preserve">7.90785312652588</t>
   </si>
   <si>
     <t xml:space="preserve">7.50496482849121</t>
@@ -1043,7 +1043,7 @@
     <t xml:space="preserve">7.5424427986145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19830799102783</t>
+    <t xml:space="preserve">8.19830703735352</t>
   </si>
   <si>
     <t xml:space="preserve">8.2170467376709</t>
@@ -1055,16 +1055,16 @@
     <t xml:space="preserve">8.46116256713867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53747367858887</t>
+    <t xml:space="preserve">8.53747463226318</t>
   </si>
   <si>
     <t xml:space="preserve">8.68056106567383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77595138549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84272575378418</t>
+    <t xml:space="preserve">8.77595233917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8427267074585</t>
   </si>
   <si>
     <t xml:space="preserve">8.72825527191162</t>
@@ -1073,25 +1073,25 @@
     <t xml:space="preserve">8.66148281097412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49931716918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42300605773926</t>
+    <t xml:space="preserve">8.49931812286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42300510406494</t>
   </si>
   <si>
     <t xml:space="preserve">8.39438915252686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60424900054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48977851867676</t>
+    <t xml:space="preserve">8.604248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48977947235107</t>
   </si>
   <si>
     <t xml:space="preserve">8.29899787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12729549407959</t>
+    <t xml:space="preserve">8.12729454040527</t>
   </si>
   <si>
     <t xml:space="preserve">7.89835643768311</t>
@@ -1100,13 +1100,13 @@
     <t xml:space="preserve">8.10821628570557</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8411226272583</t>
+    <t xml:space="preserve">7.84112215042114</t>
   </si>
   <si>
     <t xml:space="preserve">8.33715343475342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20360660552979</t>
+    <t xml:space="preserve">8.2036075592041</t>
   </si>
   <si>
     <t xml:space="preserve">8.06052017211914</t>
@@ -1115,13 +1115,13 @@
     <t xml:space="preserve">8.07959938049316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07005977630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92697334289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98420763015747</t>
+    <t xml:space="preserve">8.07005882263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92697429656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98420858383179</t>
   </si>
   <si>
     <t xml:space="preserve">8.30853652954102</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">8.26084136962891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2703800201416</t>
+    <t xml:space="preserve">8.27038097381592</t>
   </si>
   <si>
     <t xml:space="preserve">8.18452835083008</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03190422058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96512985229492</t>
+    <t xml:space="preserve">8.03190326690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96513080596924</t>
   </si>
   <si>
     <t xml:space="preserve">7.86019992828369</t>
@@ -1151,10 +1151,10 @@
     <t xml:space="preserve">7.71711397171021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91743421554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76480960845947</t>
+    <t xml:space="preserve">7.91743516921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76481008529663</t>
   </si>
   <si>
     <t xml:space="preserve">7.72665309906006</t>
@@ -1169,10 +1169,10 @@
     <t xml:space="preserve">7.65987968444824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.165452003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32761478424072</t>
+    <t xml:space="preserve">8.16545104980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32761383056641</t>
   </si>
   <si>
     <t xml:space="preserve">8.11775588989258</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">8.2322244644165</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31807613372803</t>
+    <t xml:space="preserve">8.31807518005371</t>
   </si>
   <si>
     <t xml:space="preserve">8.15591144561768</t>
@@ -1196,19 +1196,19 @@
     <t xml:space="preserve">8.22268486022949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25130081176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35623264312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2417631149292</t>
+    <t xml:space="preserve">8.25130176544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35623168945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24176406860352</t>
   </si>
   <si>
     <t xml:space="preserve">8.34669303894043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95559072494507</t>
+    <t xml:space="preserve">7.95559167861938</t>
   </si>
   <si>
     <t xml:space="preserve">7.77434825897217</t>
@@ -1220,37 +1220,37 @@
     <t xml:space="preserve">7.97466850280762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01282501220703</t>
+    <t xml:space="preserve">8.01282596588135</t>
   </si>
   <si>
     <t xml:space="preserve">8.05098152160645</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67895793914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7361912727356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6980357170105</t>
+    <t xml:space="preserve">7.67895746231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73619174957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69803524017334</t>
   </si>
   <si>
     <t xml:space="preserve">7.51679372787476</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59310579299927</t>
+    <t xml:space="preserve">7.59310626983643</t>
   </si>
   <si>
     <t xml:space="preserve">7.44048070907593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53587198257446</t>
+    <t xml:space="preserve">7.5358715057373</t>
   </si>
   <si>
     <t xml:space="preserve">7.62172269821167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52633237838745</t>
+    <t xml:space="preserve">7.52633190155029</t>
   </si>
   <si>
     <t xml:space="preserve">7.34508991241455</t>
@@ -1259,22 +1259,22 @@
     <t xml:space="preserve">7.20200395584106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1829252243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14476919174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12569093704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23062086105347</t>
+    <t xml:space="preserve">7.18292570114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14476871490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12569046020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23062133789062</t>
   </si>
   <si>
     <t xml:space="preserve">7.1543083190918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24969911575317</t>
+    <t xml:space="preserve">7.24969863891602</t>
   </si>
   <si>
     <t xml:space="preserve">7.24016046524048</t>
@@ -1283,16 +1283,16 @@
     <t xml:space="preserve">7.46909809112549</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41186380386353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45001935958862</t>
+    <t xml:space="preserve">7.41186332702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45001983642578</t>
   </si>
   <si>
     <t xml:space="preserve">7.28785514831543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39278554916382</t>
+    <t xml:space="preserve">7.39278507232666</t>
   </si>
   <si>
     <t xml:space="preserve">7.3355507850647</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">7.61218404769897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90789604187012</t>
+    <t xml:space="preserve">7.90789556503296</t>
   </si>
   <si>
     <t xml:space="preserve">7.94605159759521</t>
@@ -1313,25 +1313,25 @@
     <t xml:space="preserve">7.70757484436035</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87927913665771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99374675750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75527048110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81250429153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79342651367188</t>
+    <t xml:space="preserve">7.8792781829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99374771118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75527000427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81250381469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79342699050903</t>
   </si>
   <si>
     <t xml:space="preserve">7.80296611785889</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85066080093384</t>
+    <t xml:space="preserve">7.85065984725952</t>
   </si>
   <si>
     <t xml:space="preserve">7.74573087692261</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">7.83158302307129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66941833496094</t>
+    <t xml:space="preserve">7.66941785812378</t>
   </si>
   <si>
     <t xml:space="preserve">7.60264492034912</t>
@@ -1361,13 +1361,13 @@
     <t xml:space="preserve">7.3641676902771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10661315917969</t>
+    <t xml:space="preserve">7.10661268234253</t>
   </si>
   <si>
     <t xml:space="preserve">7.27831649780273</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08753442764282</t>
+    <t xml:space="preserve">7.08753490447998</t>
   </si>
   <si>
     <t xml:space="preserve">7.05891799926758</t>
@@ -63478,7 +63478,7 @@
     </row>
     <row r="2342">
       <c r="A2342" s="1" t="n">
-        <v>46030.69125</v>
+        <v>46030.3333333333</v>
       </c>
       <c r="B2342" t="n">
         <v>25819</v>
@@ -63499,6 +63499,32 @@
         <v>736</v>
       </c>
       <c r="H2342" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2343">
+      <c r="A2343" s="1" t="n">
+        <v>46031.6912962963</v>
+      </c>
+      <c r="B2343" t="n">
+        <v>42255</v>
+      </c>
+      <c r="C2343" t="n">
+        <v>9.53999996185303</v>
+      </c>
+      <c r="D2343" t="n">
+        <v>9.23999977111816</v>
+      </c>
+      <c r="E2343" t="n">
+        <v>9.34000015258789</v>
+      </c>
+      <c r="F2343" t="n">
+        <v>9.27999973297119</v>
+      </c>
+      <c r="G2343" t="s">
+        <v>732</v>
+      </c>
+      <c r="H2343" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07642078399658</t>
+    <t xml:space="preserve">9.0764217376709</t>
   </si>
   <si>
     <t xml:space="preserve">FF.MI</t>
@@ -47,31 +47,31 @@
     <t xml:space="preserve">8.98565769195557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08549785614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24887275695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09457492828369</t>
+    <t xml:space="preserve">9.08549690246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24887371063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09457683563232</t>
   </si>
   <si>
     <t xml:space="preserve">9.12180423736572</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03104019165039</t>
+    <t xml:space="preserve">9.03103923797607</t>
   </si>
   <si>
     <t xml:space="preserve">8.95389080047607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8994312286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89489269256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84951210021973</t>
+    <t xml:space="preserve">8.89943218231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89489364624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84951114654541</t>
   </si>
   <si>
     <t xml:space="preserve">8.85858821868896</t>
@@ -86,28 +86,28 @@
     <t xml:space="preserve">8.86766529083252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04919338226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23072147369385</t>
+    <t xml:space="preserve">9.04919242858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23072242736816</t>
   </si>
   <si>
     <t xml:space="preserve">9.11272716522217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96750450134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91304588317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92212295532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00381088256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15810966491699</t>
+    <t xml:space="preserve">8.96750545501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91304683685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92212200164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00381183624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15810871124268</t>
   </si>
   <si>
     <t xml:space="preserve">9.16718578338623</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">9.62100791931152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8025369644165</t>
+    <t xml:space="preserve">9.80253601074219</t>
   </si>
   <si>
     <t xml:space="preserve">9.71177101135254</t>
@@ -131,19 +131,19 @@
     <t xml:space="preserve">9.56654930114746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58470249176025</t>
+    <t xml:space="preserve">9.58470058441162</t>
   </si>
   <si>
     <t xml:space="preserve">9.5756254196167</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53024196624756</t>
+    <t xml:space="preserve">9.53024291992188</t>
   </si>
   <si>
     <t xml:space="preserve">9.50301265716553</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60285472869873</t>
+    <t xml:space="preserve">9.60285568237305</t>
   </si>
   <si>
     <t xml:space="preserve">9.63915920257568</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">9.79345893859863</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95683479309082</t>
+    <t xml:space="preserve">9.9568338394165</t>
   </si>
   <si>
     <t xml:space="preserve">9.93868255615234</t>
@@ -161,94 +161,94 @@
     <t xml:space="preserve">9.98406410217285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73899936676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76623058319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74807739257812</t>
+    <t xml:space="preserve">9.73900127410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76622867584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74807643890381</t>
   </si>
   <si>
     <t xml:space="preserve">9.75715351104736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64823722839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82068824768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7026948928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72084808349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67546463012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66638946533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63008213043213</t>
+    <t xml:space="preserve">9.64823627471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82068729400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70269584655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72084712982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67546558380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66638851165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63008403778076</t>
   </si>
   <si>
     <t xml:space="preserve">9.65731334686279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68454265594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81161212921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8297643661499</t>
+    <t xml:space="preserve">9.68454170227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81161308288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82976531982422</t>
   </si>
   <si>
     <t xml:space="preserve">9.8479175567627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83884143829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7299222946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78438377380371</t>
+    <t xml:space="preserve">9.83884334564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72992515563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78438282012939</t>
   </si>
   <si>
     <t xml:space="preserve">9.55747127532959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34871387481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33963775634766</t>
+    <t xml:space="preserve">9.34871482849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33963680267334</t>
   </si>
   <si>
     <t xml:space="preserve">9.27610397338867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25794982910156</t>
+    <t xml:space="preserve">9.25795078277588</t>
   </si>
   <si>
     <t xml:space="preserve">9.19441509246826</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18533897399902</t>
+    <t xml:space="preserve">9.18533992767334</t>
   </si>
   <si>
     <t xml:space="preserve">9.41225051879883</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22164440155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31240844726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26702690124512</t>
+    <t xml:space="preserve">9.22164344787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31240749359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2670259475708</t>
   </si>
   <si>
     <t xml:space="preserve">9.29425621032715</t>
@@ -260,34 +260,34 @@
     <t xml:space="preserve">9.37594413757324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36686706542969</t>
+    <t xml:space="preserve">9.36686611175537</t>
   </si>
   <si>
     <t xml:space="preserve">9.3850212097168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45763111114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39409732818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48486042022705</t>
+    <t xml:space="preserve">9.45763206481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39409637451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48486137390137</t>
   </si>
   <si>
     <t xml:space="preserve">9.49393749237061</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44855499267578</t>
+    <t xml:space="preserve">9.44855308532715</t>
   </si>
   <si>
     <t xml:space="preserve">9.4757833480835</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2397985458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14903259277344</t>
+    <t xml:space="preserve">9.23979759216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14903450012207</t>
   </si>
   <si>
     <t xml:space="preserve">9.21256828308105</t>
@@ -296,34 +296,34 @@
     <t xml:space="preserve">9.20349311828613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13088035583496</t>
+    <t xml:space="preserve">9.13087940216064</t>
   </si>
   <si>
     <t xml:space="preserve">9.1399564743042</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94027423858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80412769317627</t>
+    <t xml:space="preserve">8.94027614593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8041296005249</t>
   </si>
   <si>
     <t xml:space="preserve">8.75874614715576</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66798210144043</t>
+    <t xml:space="preserve">8.66798305511475</t>
   </si>
   <si>
     <t xml:space="preserve">8.62260055541992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53183650970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35030841827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16878032684326</t>
+    <t xml:space="preserve">8.53183555603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35030937194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16878128051758</t>
   </si>
   <si>
     <t xml:space="preserve">7.98725128173828</t>
@@ -332,13 +332,13 @@
     <t xml:space="preserve">8.03263378143311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12339687347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25954341888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94186925888062</t>
+    <t xml:space="preserve">8.12339782714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25954437255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94186878204346</t>
   </si>
   <si>
     <t xml:space="preserve">8.30492687225342</t>
@@ -347,22 +347,22 @@
     <t xml:space="preserve">8.21416282653809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39568996429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57721710205078</t>
+    <t xml:space="preserve">8.39569091796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57721900939941</t>
   </si>
   <si>
     <t xml:space="preserve">8.71336460113525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53202342987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25706005096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44036865234375</t>
+    <t xml:space="preserve">9.53202247619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25706100463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44036960601807</t>
   </si>
   <si>
     <t xml:space="preserve">9.16540718078613</t>
@@ -371,19 +371,19 @@
     <t xml:space="preserve">9.07375240325928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11957931518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98209762573242</t>
+    <t xml:space="preserve">9.11958026885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98209857940674</t>
   </si>
   <si>
     <t xml:space="preserve">9.02792549133301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62367820739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80698490142822</t>
+    <t xml:space="preserve">9.62367630004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80698394775391</t>
   </si>
   <si>
     <t xml:space="preserve">9.89863967895508</t>
@@ -395,22 +395,22 @@
     <t xml:space="preserve">10.1736011505127</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2652549743652</t>
+    <t xml:space="preserve">10.2652559280396</t>
   </si>
   <si>
     <t xml:space="preserve">10.3569097518921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5402183532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.631872177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8151807785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7235250473022</t>
+    <t xml:space="preserve">10.5402173995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6318712234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8151788711548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7235260009766</t>
   </si>
   <si>
     <t xml:space="preserve">10.9068326950073</t>
@@ -419,34 +419,34 @@
     <t xml:space="preserve">10.9984874725342</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0901432037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1817960739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2734508514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4567575454712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3651027679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4485635757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71533107757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79878997802734</t>
+    <t xml:space="preserve">11.090142250061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1817951202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2734498977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4567584991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.36510181427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4485626220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79879093170166</t>
   </si>
   <si>
     <t xml:space="preserve">8.24886608123779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2112340927124</t>
+    <t xml:space="preserve">9.21123313903809</t>
   </si>
   <si>
     <t xml:space="preserve">9.30288791656494</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">9.03709030151367</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3945426940918</t>
+    <t xml:space="preserve">9.39454174041748</t>
   </si>
   <si>
     <t xml:space="preserve">9.76115703582764</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">9.66950416564941</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57785034179688</t>
+    <t xml:space="preserve">9.57784938812256</t>
   </si>
   <si>
     <t xml:space="preserve">10.0361204147339</t>
@@ -473,19 +473,19 @@
     <t xml:space="preserve">9.94446659088135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82552337646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73283100128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59379005432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96456432342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91821765899658</t>
+    <t xml:space="preserve">9.82552528381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73283004760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59379100799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96456527709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91821670532227</t>
   </si>
   <si>
     <t xml:space="preserve">9.54744338989258</t>
@@ -494,49 +494,49 @@
     <t xml:space="preserve">10.010910987854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1036052703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1499519348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1962985992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77917671203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87187004089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0572576522827</t>
+    <t xml:space="preserve">10.1036043167114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1499509811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1962976455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77917766571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87187099456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0572595596313</t>
   </si>
   <si>
     <t xml:space="preserve">10.2889928817749</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4743795394897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2426452636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3816862106323</t>
+    <t xml:space="preserve">10.4743785858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2426462173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.381685256958</t>
   </si>
   <si>
     <t xml:space="preserve">9.68648338317871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64013671875</t>
+    <t xml:space="preserve">9.64013576507568</t>
   </si>
   <si>
     <t xml:space="preserve">9.50109672546387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31570911407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23228454589844</t>
+    <t xml:space="preserve">9.31570816040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23228549957275</t>
   </si>
   <si>
     <t xml:space="preserve">9.1952075958252</t>
@@ -545,34 +545,34 @@
     <t xml:space="preserve">9.25082302093506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26936149597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21374702453613</t>
+    <t xml:space="preserve">9.269362449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2137451171875</t>
   </si>
   <si>
     <t xml:space="preserve">9.04689693450928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12105369567871</t>
+    <t xml:space="preserve">9.12105274200439</t>
   </si>
   <si>
     <t xml:space="preserve">9.0654354095459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97274208068848</t>
+    <t xml:space="preserve">8.97274303436279</t>
   </si>
   <si>
     <t xml:space="preserve">9.17666816711426</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02835941314697</t>
+    <t xml:space="preserve">9.02835845947266</t>
   </si>
   <si>
     <t xml:space="preserve">8.95420360565186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71319961547852</t>
+    <t xml:space="preserve">8.71320056915283</t>
   </si>
   <si>
     <t xml:space="preserve">8.99128150939941</t>
@@ -587,10 +587,10 @@
     <t xml:space="preserve">8.93566513061523</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3353385925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9841947555542</t>
+    <t xml:space="preserve">10.3353395462036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9841938018799</t>
   </si>
   <si>
     <t xml:space="preserve">11.0305404663086</t>
@@ -599,7 +599,7 @@
     <t xml:space="preserve">11.2159280776978</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4940090179443</t>
+    <t xml:space="preserve">11.49400806427</t>
   </si>
   <si>
     <t xml:space="preserve">11.540355682373</t>
@@ -611,52 +611,52 @@
     <t xml:space="preserve">11.6330499649048</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7257423400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9111299514771</t>
+    <t xml:space="preserve">11.7257432937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9111309051514</t>
   </si>
   <si>
     <t xml:space="preserve">11.9574766159058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1892108917236</t>
+    <t xml:space="preserve">12.1892118453979</t>
   </si>
   <si>
     <t xml:space="preserve">12.2819042205811</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3745994567871</t>
+    <t xml:space="preserve">12.3745985031128</t>
   </si>
   <si>
     <t xml:space="preserve">12.5136384963989</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3282518386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1428651809692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0965175628662</t>
+    <t xml:space="preserve">12.3282508850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1428642272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0965185165405</t>
   </si>
   <si>
     <t xml:space="preserve">12.555121421814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5082750320435</t>
+    <t xml:space="preserve">12.5082740783691</t>
   </si>
   <si>
     <t xml:space="preserve">12.6488170623779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4614276885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4145793914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7425127029419</t>
+    <t xml:space="preserve">12.46142578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4145784378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7425117492676</t>
   </si>
   <si>
     <t xml:space="preserve">12.6956644058228</t>
@@ -665,25 +665,25 @@
     <t xml:space="preserve">12.2271900177002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1803426742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3208837509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2740383148193</t>
+    <t xml:space="preserve">12.1803417205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3208847045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.274037361145</t>
   </si>
   <si>
     <t xml:space="preserve">12.8362064361572</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7893581390381</t>
+    <t xml:space="preserve">12.7893590927124</t>
   </si>
   <si>
     <t xml:space="preserve">12.6019697189331</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9299020767212</t>
+    <t xml:space="preserve">12.9299011230469</t>
   </si>
   <si>
     <t xml:space="preserve">12.8830537796021</t>
@@ -692,49 +692,49 @@
     <t xml:space="preserve">13.0704441070557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.679461479187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8668508529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0542402267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3353252410889</t>
+    <t xml:space="preserve">13.6794624328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8668518066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0542411804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3353261947632</t>
   </si>
   <si>
     <t xml:space="preserve">14.5695638656616</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2254285812378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1317329406738</t>
+    <t xml:space="preserve">15.2254276275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1317310333252</t>
   </si>
   <si>
     <t xml:space="preserve">14.7569532394409</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0380373001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.178581237793</t>
+    <t xml:space="preserve">15.0380363464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1785802841187</t>
   </si>
   <si>
     <t xml:space="preserve">15.3191232681274</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8974943161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4596662521362</t>
+    <t xml:space="preserve">14.8974952697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4596643447876</t>
   </si>
   <si>
     <t xml:space="preserve">15.4128189086914</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5533599853516</t>
+    <t xml:space="preserve">15.5533590316772</t>
   </si>
   <si>
     <t xml:space="preserve">16.0686817169189</t>
@@ -743,10 +743,10 @@
     <t xml:space="preserve">16.8650894165039</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0056324005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7713947296143</t>
+    <t xml:space="preserve">17.0056304931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7713928222656</t>
   </si>
   <si>
     <t xml:space="preserve">17.193021774292</t>
@@ -755,25 +755,25 @@
     <t xml:space="preserve">17.0524787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9587860107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7245483398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6308536529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5371551513672</t>
+    <t xml:space="preserve">16.9587841033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7245464324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6308498382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5371570587158</t>
   </si>
   <si>
     <t xml:space="preserve">16.584005355835</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2092227935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2560729980469</t>
+    <t xml:space="preserve">16.2092208862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2560710906982</t>
   </si>
   <si>
     <t xml:space="preserve">17.1461715698242</t>
@@ -782,13 +782,13 @@
     <t xml:space="preserve">16.396614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3029174804688</t>
+    <t xml:space="preserve">16.3029193878174</t>
   </si>
   <si>
     <t xml:space="preserve">15.8344440460205</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1155300140381</t>
+    <t xml:space="preserve">16.1155281066895</t>
   </si>
   <si>
     <t xml:space="preserve">16.0218353271484</t>
@@ -797,28 +797,28 @@
     <t xml:space="preserve">16.1623764038086</t>
   </si>
   <si>
-    <t xml:space="preserve">15.974986076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7407484054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4434604644775</t>
+    <t xml:space="preserve">15.9749870300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7407493591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4434623718262</t>
   </si>
   <si>
     <t xml:space="preserve">16.9119358062744</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0993251800537</t>
+    <t xml:space="preserve">17.0993270874023</t>
   </si>
   <si>
     <t xml:space="preserve">16.677698135376</t>
   </si>
   <si>
-    <t xml:space="preserve">16.818244934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.272274017334</t>
+    <t xml:space="preserve">16.8182411193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2722749710083</t>
   </si>
   <si>
     <t xml:space="preserve">15.084885597229</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">14.9911909103394</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8037996292114</t>
+    <t xml:space="preserve">14.8038015365601</t>
   </si>
   <si>
     <t xml:space="preserve">14.4758682250977</t>
@@ -842,34 +842,34 @@
     <t xml:space="preserve">14.288477897644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5227155685425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.960545539856</t>
+    <t xml:space="preserve">14.5227165222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9605464935303</t>
   </si>
   <si>
     <t xml:space="preserve">14.2416305541992</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1947832107544</t>
+    <t xml:space="preserve">14.1947822570801</t>
   </si>
   <si>
     <t xml:space="preserve">14.0073938369751</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7263088226318</t>
+    <t xml:space="preserve">13.7263078689575</t>
   </si>
   <si>
     <t xml:space="preserve">14.1479358673096</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4290199279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6164112091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7731561660767</t>
+    <t xml:space="preserve">14.4290208816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6164102554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7731552124023</t>
   </si>
   <si>
     <t xml:space="preserve">13.3515281677246</t>
@@ -896,25 +896,25 @@
     <t xml:space="preserve">12.0866460800171</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9929523468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8992576599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0397987365723</t>
+    <t xml:space="preserve">11.9929513931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8992567062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0397996902466</t>
   </si>
   <si>
     <t xml:space="preserve">12.1334943771362</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4776296615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2433938980103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3839340209961</t>
+    <t xml:space="preserve">11.4776306152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2433929443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3839349746704</t>
   </si>
   <si>
     <t xml:space="preserve">11.6650199890137</t>
@@ -926,22 +926,22 @@
     <t xml:space="preserve">10.9623079299927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7280712127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1965456008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5713243484497</t>
+    <t xml:space="preserve">10.7280702590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1965446472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.571325302124</t>
   </si>
   <si>
     <t xml:space="preserve">11.3370876312256</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2902402877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7118682861328</t>
+    <t xml:space="preserve">11.2902412414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7118673324585</t>
   </si>
   <si>
     <t xml:space="preserve">11.7587156295776</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">11.8055629730225</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0091552734375</t>
+    <t xml:space="preserve">11.0091562271118</t>
   </si>
   <si>
     <t xml:space="preserve">9.46318912506104</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">8.31074142456055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45128345489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61993312835693</t>
+    <t xml:space="preserve">8.45128440856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61993408203125</t>
   </si>
   <si>
     <t xml:space="preserve">8.44191455841064</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">8.32948112487793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25452327728271</t>
+    <t xml:space="preserve">8.25452423095703</t>
   </si>
   <si>
     <t xml:space="preserve">8.43254470825195</t>
@@ -986,13 +986,13 @@
     <t xml:space="preserve">8.47002220153809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32011127471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20767784118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08587265014648</t>
+    <t xml:space="preserve">8.32010936737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20767688751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0858736038208</t>
   </si>
   <si>
     <t xml:space="preserve">7.78604936599731</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">7.83289623260498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90785312652588</t>
+    <t xml:space="preserve">7.90785264968872</t>
   </si>
   <si>
     <t xml:space="preserve">7.50496482849121</t>
@@ -1025,19 +1025,19 @@
     <t xml:space="preserve">7.28009700775146</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98027276992798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93342542648315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06459856033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0271201133728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34568309783936</t>
+    <t xml:space="preserve">6.98027324676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93342590332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06459808349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02712059020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34568357467651</t>
   </si>
   <si>
     <t xml:space="preserve">7.5424427986145</t>
@@ -1055,16 +1055,16 @@
     <t xml:space="preserve">8.46116256713867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53747463226318</t>
+    <t xml:space="preserve">8.53747367858887</t>
   </si>
   <si>
     <t xml:space="preserve">8.68056106567383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77595233917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8427267074585</t>
+    <t xml:space="preserve">8.77595138549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84272575378418</t>
   </si>
   <si>
     <t xml:space="preserve">8.72825527191162</t>
@@ -1073,25 +1073,25 @@
     <t xml:space="preserve">8.66148281097412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49931812286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42300510406494</t>
+    <t xml:space="preserve">8.49931716918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42300605773926</t>
   </si>
   <si>
     <t xml:space="preserve">8.39438915252686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.604248046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48977947235107</t>
+    <t xml:space="preserve">8.60424900054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48977851867676</t>
   </si>
   <si>
     <t xml:space="preserve">8.29899787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12729454040527</t>
+    <t xml:space="preserve">8.12729549407959</t>
   </si>
   <si>
     <t xml:space="preserve">7.89835643768311</t>
@@ -1100,13 +1100,13 @@
     <t xml:space="preserve">8.10821628570557</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84112215042114</t>
+    <t xml:space="preserve">7.8411226272583</t>
   </si>
   <si>
     <t xml:space="preserve">8.33715343475342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2036075592041</t>
+    <t xml:space="preserve">8.20360660552979</t>
   </si>
   <si>
     <t xml:space="preserve">8.06052017211914</t>
@@ -1115,13 +1115,13 @@
     <t xml:space="preserve">8.07959938049316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07005882263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92697429656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98420858383179</t>
+    <t xml:space="preserve">8.07005977630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92697334289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98420763015747</t>
   </si>
   <si>
     <t xml:space="preserve">8.30853652954102</t>
@@ -1130,16 +1130,16 @@
     <t xml:space="preserve">8.26084136962891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27038097381592</t>
+    <t xml:space="preserve">8.2703800201416</t>
   </si>
   <si>
     <t xml:space="preserve">8.18452835083008</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03190326690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96513080596924</t>
+    <t xml:space="preserve">8.03190422058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96512985229492</t>
   </si>
   <si>
     <t xml:space="preserve">7.86019992828369</t>
@@ -1151,10 +1151,10 @@
     <t xml:space="preserve">7.71711397171021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91743516921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76481008529663</t>
+    <t xml:space="preserve">7.91743421554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76480960845947</t>
   </si>
   <si>
     <t xml:space="preserve">7.72665309906006</t>
@@ -1169,10 +1169,10 @@
     <t xml:space="preserve">7.65987968444824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16545104980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32761383056641</t>
+    <t xml:space="preserve">8.165452003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32761478424072</t>
   </si>
   <si>
     <t xml:space="preserve">8.11775588989258</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">8.2322244644165</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31807518005371</t>
+    <t xml:space="preserve">8.31807613372803</t>
   </si>
   <si>
     <t xml:space="preserve">8.15591144561768</t>
@@ -1196,19 +1196,19 @@
     <t xml:space="preserve">8.22268486022949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25130176544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35623168945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24176406860352</t>
+    <t xml:space="preserve">8.25130081176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35623264312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2417631149292</t>
   </si>
   <si>
     <t xml:space="preserve">8.34669303894043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95559167861938</t>
+    <t xml:space="preserve">7.95559072494507</t>
   </si>
   <si>
     <t xml:space="preserve">7.77434825897217</t>
@@ -1220,37 +1220,37 @@
     <t xml:space="preserve">7.97466850280762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01282596588135</t>
+    <t xml:space="preserve">8.01282501220703</t>
   </si>
   <si>
     <t xml:space="preserve">8.05098152160645</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67895746231079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73619174957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69803524017334</t>
+    <t xml:space="preserve">7.67895793914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7361912727356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6980357170105</t>
   </si>
   <si>
     <t xml:space="preserve">7.51679372787476</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59310626983643</t>
+    <t xml:space="preserve">7.59310579299927</t>
   </si>
   <si>
     <t xml:space="preserve">7.44048070907593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5358715057373</t>
+    <t xml:space="preserve">7.53587198257446</t>
   </si>
   <si>
     <t xml:space="preserve">7.62172269821167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52633190155029</t>
+    <t xml:space="preserve">7.52633237838745</t>
   </si>
   <si>
     <t xml:space="preserve">7.34508991241455</t>
@@ -1259,22 +1259,22 @@
     <t xml:space="preserve">7.20200395584106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18292570114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14476871490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12569046020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23062133789062</t>
+    <t xml:space="preserve">7.1829252243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14476919174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12569093704224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23062086105347</t>
   </si>
   <si>
     <t xml:space="preserve">7.1543083190918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24969863891602</t>
+    <t xml:space="preserve">7.24969911575317</t>
   </si>
   <si>
     <t xml:space="preserve">7.24016046524048</t>
@@ -1283,16 +1283,16 @@
     <t xml:space="preserve">7.46909809112549</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41186332702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45001983642578</t>
+    <t xml:space="preserve">7.41186380386353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45001935958862</t>
   </si>
   <si>
     <t xml:space="preserve">7.28785514831543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39278507232666</t>
+    <t xml:space="preserve">7.39278554916382</t>
   </si>
   <si>
     <t xml:space="preserve">7.3355507850647</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">7.61218404769897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90789556503296</t>
+    <t xml:space="preserve">7.90789604187012</t>
   </si>
   <si>
     <t xml:space="preserve">7.94605159759521</t>
@@ -1313,25 +1313,25 @@
     <t xml:space="preserve">7.70757484436035</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8792781829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99374771118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75527000427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81250381469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79342699050903</t>
+    <t xml:space="preserve">7.87927913665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99374675750732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75527048110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81250429153442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79342651367188</t>
   </si>
   <si>
     <t xml:space="preserve">7.80296611785889</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85065984725952</t>
+    <t xml:space="preserve">7.85066080093384</t>
   </si>
   <si>
     <t xml:space="preserve">7.74573087692261</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">7.83158302307129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66941785812378</t>
+    <t xml:space="preserve">7.66941833496094</t>
   </si>
   <si>
     <t xml:space="preserve">7.60264492034912</t>
@@ -1361,13 +1361,13 @@
     <t xml:space="preserve">7.3641676902771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10661268234253</t>
+    <t xml:space="preserve">7.10661315917969</t>
   </si>
   <si>
     <t xml:space="preserve">7.27831649780273</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08753490447998</t>
+    <t xml:space="preserve">7.08753442764282</t>
   </si>
   <si>
     <t xml:space="preserve">7.05891799926758</t>
@@ -63504,7 +63504,7 @@
     </row>
     <row r="2343">
       <c r="A2343" s="1" t="n">
-        <v>46031.6912962963</v>
+        <v>46031.3333333333</v>
       </c>
       <c r="B2343" t="n">
         <v>42255</v>
@@ -63525,6 +63525,32 @@
         <v>732</v>
       </c>
       <c r="H2343" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2344">
+      <c r="A2344" s="1" t="n">
+        <v>46034.6910648148</v>
+      </c>
+      <c r="B2344" t="n">
+        <v>100483</v>
+      </c>
+      <c r="C2344" t="n">
+        <v>9.61999988555908</v>
+      </c>
+      <c r="D2344" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="E2344" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="F2344" t="n">
+        <v>9.53999996185303</v>
+      </c>
+      <c r="G2344" t="s">
+        <v>742</v>
+      </c>
+      <c r="H2344" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -47,13 +47,13 @@
     <t xml:space="preserve">8.98565769195557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08549690246582</t>
+    <t xml:space="preserve">9.08549785614014</t>
   </si>
   <si>
     <t xml:space="preserve">9.24887371063232</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09457683563232</t>
+    <t xml:space="preserve">9.09457397460938</t>
   </si>
   <si>
     <t xml:space="preserve">9.12180423736572</t>
@@ -62,7 +62,7 @@
     <t xml:space="preserve">9.03103923797607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95389080047607</t>
+    <t xml:space="preserve">8.95388984680176</t>
   </si>
   <si>
     <t xml:space="preserve">8.89943218231201</t>
@@ -77,19 +77,19 @@
     <t xml:space="preserve">8.85858821868896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87674045562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76782321929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86766529083252</t>
+    <t xml:space="preserve">8.87673950195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.767822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8676643371582</t>
   </si>
   <si>
     <t xml:space="preserve">9.04919242858887</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23072242736816</t>
+    <t xml:space="preserve">9.23072052001953</t>
   </si>
   <si>
     <t xml:space="preserve">9.11272716522217</t>
@@ -98,19 +98,19 @@
     <t xml:space="preserve">8.96750545501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91304683685303</t>
+    <t xml:space="preserve">8.91304588317871</t>
   </si>
   <si>
     <t xml:space="preserve">8.92212200164795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00381183624268</t>
+    <t xml:space="preserve">9.00381088256836</t>
   </si>
   <si>
     <t xml:space="preserve">9.15810871124268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16718578338623</t>
+    <t xml:space="preserve">9.16718673706055</t>
   </si>
   <si>
     <t xml:space="preserve">9.43947792053223</t>
@@ -119,31 +119,31 @@
     <t xml:space="preserve">9.54839611053467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62100791931152</t>
+    <t xml:space="preserve">9.62100601196289</t>
   </si>
   <si>
     <t xml:space="preserve">9.80253601074219</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71177101135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56654930114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58470058441162</t>
+    <t xml:space="preserve">9.71177196502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56655025482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58470153808594</t>
   </si>
   <si>
     <t xml:space="preserve">9.5756254196167</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53024291992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50301265716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60285568237305</t>
+    <t xml:space="preserve">9.53024196624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50301361083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60285472869873</t>
   </si>
   <si>
     <t xml:space="preserve">9.63915920257568</t>
@@ -152,22 +152,22 @@
     <t xml:space="preserve">9.79345893859863</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9568338394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93868255615234</t>
+    <t xml:space="preserve">9.95683574676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93868160247803</t>
   </si>
   <si>
     <t xml:space="preserve">9.98406410217285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73900127410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76622867584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74807643890381</t>
+    <t xml:space="preserve">9.73900032043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76623058319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74807548522949</t>
   </si>
   <si>
     <t xml:space="preserve">9.75715351104736</t>
@@ -176,10 +176,10 @@
     <t xml:space="preserve">9.64823627471924</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82068729400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70269584655762</t>
+    <t xml:space="preserve">9.82068824768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70269393920898</t>
   </si>
   <si>
     <t xml:space="preserve">9.72084712982178</t>
@@ -191,34 +191,34 @@
     <t xml:space="preserve">9.66638851165771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63008403778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65731334686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68454170227051</t>
+    <t xml:space="preserve">9.63008308410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65731239318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68454265594482</t>
   </si>
   <si>
     <t xml:space="preserve">9.81161308288574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82976531982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8479175567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83884334564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72992515563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78438282012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55747127532959</t>
+    <t xml:space="preserve">9.8297643661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84791851043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83884048461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72992420196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78438377380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55747318267822</t>
   </si>
   <si>
     <t xml:space="preserve">9.34871482849121</t>
@@ -227,28 +227,28 @@
     <t xml:space="preserve">9.33963680267334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27610397338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25795078277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19441509246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18533992767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41225051879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22164344787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31240749359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2670259475708</t>
+    <t xml:space="preserve">9.27610492706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25794982910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19441604614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18533897399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41224956512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22164535522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31240844726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26702690124512</t>
   </si>
   <si>
     <t xml:space="preserve">9.29425621032715</t>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">9.37594413757324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36686611175537</t>
+    <t xml:space="preserve">9.36686706542969</t>
   </si>
   <si>
     <t xml:space="preserve">9.3850212097168</t>
@@ -269,64 +269,64 @@
     <t xml:space="preserve">9.45763206481934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39409637451172</t>
+    <t xml:space="preserve">9.39409732818604</t>
   </si>
   <si>
     <t xml:space="preserve">9.48486137390137</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49393749237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44855308532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4757833480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23979759216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14903450012207</t>
+    <t xml:space="preserve">9.49393844604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44855499267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47578430175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23979663848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14903354644775</t>
   </si>
   <si>
     <t xml:space="preserve">9.21256828308105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20349311828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13087940216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1399564743042</t>
+    <t xml:space="preserve">9.20349216461182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13088130950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13995552062988</t>
   </si>
   <si>
     <t xml:space="preserve">8.94027614593506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8041296005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75874614715576</t>
+    <t xml:space="preserve">8.80412864685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75874710083008</t>
   </si>
   <si>
     <t xml:space="preserve">8.66798305511475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62260055541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53183555603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35030937194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16878128051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98725128173828</t>
+    <t xml:space="preserve">8.62260150909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53183650970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35030746459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16877937316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98725175857544</t>
   </si>
   <si>
     <t xml:space="preserve">8.03263378143311</t>
@@ -338,22 +338,22 @@
     <t xml:space="preserve">8.25954437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94186878204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30492687225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21416282653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39569091796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57721900939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71336460113525</t>
+    <t xml:space="preserve">7.9418683052063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30492496490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21416091918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39568996429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57721710205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71336555480957</t>
   </si>
   <si>
     <t xml:space="preserve">9.53202247619629</t>
@@ -362,40 +362,40 @@
     <t xml:space="preserve">9.25706100463867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44036960601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16540718078613</t>
+    <t xml:space="preserve">9.44036865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16540622711182</t>
   </si>
   <si>
     <t xml:space="preserve">9.07375240325928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11958026885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98209857940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02792549133301</t>
+    <t xml:space="preserve">9.11957931518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98209953308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02792644500732</t>
   </si>
   <si>
     <t xml:space="preserve">9.62367630004883</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80698394775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89863967895508</t>
+    <t xml:space="preserve">9.80698490142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89863872528076</t>
   </si>
   <si>
     <t xml:space="preserve">9.9902925491333</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1736011505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2652559280396</t>
+    <t xml:space="preserve">10.173602104187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2652540206909</t>
   </si>
   <si>
     <t xml:space="preserve">10.3569097518921</t>
@@ -404,40 +404,40 @@
     <t xml:space="preserve">10.5402173995972</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6318712234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8151788711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7235260009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9068326950073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9984874725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.090142250061</t>
+    <t xml:space="preserve">10.631872177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8151798248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7235269546509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.906834602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9984884262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0901412963867</t>
   </si>
   <si>
     <t xml:space="preserve">11.1817951202393</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734498977661</t>
+    <t xml:space="preserve">11.2734508514404</t>
   </si>
   <si>
     <t xml:space="preserve">11.4567584991455</t>
   </si>
   <si>
-    <t xml:space="preserve">11.36510181427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4485626220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71533203125</t>
+    <t xml:space="preserve">11.3651037216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4485635757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71533107757568</t>
   </si>
   <si>
     <t xml:space="preserve">8.79879093170166</t>
@@ -452,7 +452,7 @@
     <t xml:space="preserve">9.30288791656494</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03709030151367</t>
+    <t xml:space="preserve">9.03709125518799</t>
   </si>
   <si>
     <t xml:space="preserve">9.39454174041748</t>
@@ -461,10 +461,10 @@
     <t xml:space="preserve">9.76115703582764</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66950416564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57784938812256</t>
+    <t xml:space="preserve">9.66950511932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57785034179688</t>
   </si>
   <si>
     <t xml:space="preserve">10.0361204147339</t>
@@ -473,16 +473,16 @@
     <t xml:space="preserve">9.94446659088135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82552528381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73283004760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59379100799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96456527709961</t>
+    <t xml:space="preserve">9.82552433013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73282909393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59379005432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96456432342529</t>
   </si>
   <si>
     <t xml:space="preserve">9.91821670532227</t>
@@ -494,13 +494,13 @@
     <t xml:space="preserve">10.010910987854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1036043167114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1499509811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1962976455688</t>
+    <t xml:space="preserve">10.1036033630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1499519348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1962985992432</t>
   </si>
   <si>
     <t xml:space="preserve">9.77917766571045</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">9.87187099456787</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0572595596313</t>
+    <t xml:space="preserve">10.057258605957</t>
   </si>
   <si>
     <t xml:space="preserve">10.2889928817749</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4743785858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2426462173462</t>
+    <t xml:space="preserve">10.4743804931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2426452636719</t>
   </si>
   <si>
     <t xml:space="preserve">10.381685256958</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">9.68648338317871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64013576507568</t>
+    <t xml:space="preserve">9.64013671875</t>
   </si>
   <si>
     <t xml:space="preserve">9.50109672546387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31570816040039</t>
+    <t xml:space="preserve">9.31570911407471</t>
   </si>
   <si>
     <t xml:space="preserve">9.23228549957275</t>
@@ -542,22 +542,22 @@
     <t xml:space="preserve">9.1952075958252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25082302093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.269362449646</t>
+    <t xml:space="preserve">9.25082397460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26936149597168</t>
   </si>
   <si>
     <t xml:space="preserve">9.2137451171875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04689693450928</t>
+    <t xml:space="preserve">9.04689788818359</t>
   </si>
   <si>
     <t xml:space="preserve">9.12105274200439</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0654354095459</t>
+    <t xml:space="preserve">9.06543636322021</t>
   </si>
   <si>
     <t xml:space="preserve">8.97274303436279</t>
@@ -566,10 +566,10 @@
     <t xml:space="preserve">9.17666816711426</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02835845947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95420360565186</t>
+    <t xml:space="preserve">9.02835941314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95420265197754</t>
   </si>
   <si>
     <t xml:space="preserve">8.71320056915283</t>
@@ -578,61 +578,61 @@
     <t xml:space="preserve">8.99128150939941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76881694793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89858818054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93566513061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3353395462036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9841938018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0305404663086</t>
+    <t xml:space="preserve">8.7688159942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89858722686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93566703796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3353385925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9841947555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0305414199829</t>
   </si>
   <si>
     <t xml:space="preserve">11.2159280776978</t>
   </si>
   <si>
-    <t xml:space="preserve">11.49400806427</t>
+    <t xml:space="preserve">11.4940099716187</t>
   </si>
   <si>
     <t xml:space="preserve">11.540355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5867033004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6330499649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7257432937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9111309051514</t>
+    <t xml:space="preserve">11.5867023468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6330490112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7257423400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9111318588257</t>
   </si>
   <si>
     <t xml:space="preserve">11.9574766159058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1892118453979</t>
+    <t xml:space="preserve">12.1892127990723</t>
   </si>
   <si>
     <t xml:space="preserve">12.2819042205811</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3745985031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5136384963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3282508850098</t>
+    <t xml:space="preserve">12.3745994567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5136394500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3282518386841</t>
   </si>
   <si>
     <t xml:space="preserve">12.1428642272949</t>
@@ -644,16 +644,16 @@
     <t xml:space="preserve">12.555121421814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5082740783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6488170623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.46142578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4145784378052</t>
+    <t xml:space="preserve">12.5082750320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6488161087036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4614267349243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4145793914795</t>
   </si>
   <si>
     <t xml:space="preserve">12.7425117492676</t>
@@ -668,13 +668,13 @@
     <t xml:space="preserve">12.1803417205811</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3208847045898</t>
+    <t xml:space="preserve">12.3208837509155</t>
   </si>
   <si>
     <t xml:space="preserve">12.274037361145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8362064361572</t>
+    <t xml:space="preserve">12.8362054824829</t>
   </si>
   <si>
     <t xml:space="preserve">12.7893590927124</t>
@@ -704,40 +704,40 @@
     <t xml:space="preserve">14.3353261947632</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5695638656616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2254276275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1317310333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7569532394409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0380363464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1785802841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3191232681274</t>
+    <t xml:space="preserve">14.5695629119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2254285812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1317319869995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7569522857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0380373001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.178581237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3191223144531</t>
   </si>
   <si>
     <t xml:space="preserve">14.8974952697754</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4596643447876</t>
+    <t xml:space="preserve">15.4596652984619</t>
   </si>
   <si>
     <t xml:space="preserve">15.4128189086914</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5533590316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0686817169189</t>
+    <t xml:space="preserve">15.5533618927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0686798095703</t>
   </si>
   <si>
     <t xml:space="preserve">16.8650894165039</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">17.193021774292</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0524787902832</t>
+    <t xml:space="preserve">17.0524806976318</t>
   </si>
   <si>
     <t xml:space="preserve">16.9587841033936</t>
@@ -761,19 +761,19 @@
     <t xml:space="preserve">16.7245464324951</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6308498382568</t>
+    <t xml:space="preserve">16.6308536529541</t>
   </si>
   <si>
     <t xml:space="preserve">16.5371570587158</t>
   </si>
   <si>
-    <t xml:space="preserve">16.584005355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2092208862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2560710906982</t>
+    <t xml:space="preserve">16.5840034484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2092227935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2560729980469</t>
   </si>
   <si>
     <t xml:space="preserve">17.1461715698242</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">16.3029193878174</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8344440460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1155281066895</t>
+    <t xml:space="preserve">15.8344430923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1155319213867</t>
   </si>
   <si>
     <t xml:space="preserve">16.0218353271484</t>
@@ -797,40 +797,40 @@
     <t xml:space="preserve">16.1623764038086</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9749870300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7407493591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4434623718262</t>
+    <t xml:space="preserve">15.9749879837036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7407503128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4434604644775</t>
   </si>
   <si>
     <t xml:space="preserve">16.9119358062744</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0993270874023</t>
+    <t xml:space="preserve">17.0993251800537</t>
   </si>
   <si>
     <t xml:space="preserve">16.677698135376</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8182411193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2722749710083</t>
+    <t xml:space="preserve">16.8182430267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.272274017334</t>
   </si>
   <si>
     <t xml:space="preserve">15.084885597229</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9911909103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8038015365601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4758682250977</t>
+    <t xml:space="preserve">14.991189956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8038005828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4758672714233</t>
   </si>
   <si>
     <t xml:space="preserve">14.382173538208</t>
@@ -842,22 +842,22 @@
     <t xml:space="preserve">14.288477897644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5227165222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9605464935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2416305541992</t>
+    <t xml:space="preserve">14.5227155685425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.960545539856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2416315078735</t>
   </si>
   <si>
     <t xml:space="preserve">14.1947822570801</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0073938369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7263078689575</t>
+    <t xml:space="preserve">14.0073928833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7263088226318</t>
   </si>
   <si>
     <t xml:space="preserve">14.1479358673096</t>
@@ -869,10 +869,10 @@
     <t xml:space="preserve">14.6164102554321</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7731552124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3515281677246</t>
+    <t xml:space="preserve">13.773157119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3515291213989</t>
   </si>
   <si>
     <t xml:space="preserve">13.3046808242798</t>
@@ -881,31 +881,31 @@
     <t xml:space="preserve">13.3983764648438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0235967636108</t>
+    <t xml:space="preserve">13.0235948562622</t>
   </si>
   <si>
     <t xml:space="preserve">13.1172924041748</t>
   </si>
   <si>
-    <t xml:space="preserve">12.976749420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3677320480347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0866460800171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9929513931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8992567062378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0397996902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1334943771362</t>
+    <t xml:space="preserve">12.9767484664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3677310943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0866470336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9929523468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8992576599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0398006439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1334953308105</t>
   </si>
   <si>
     <t xml:space="preserve">11.4776306152344</t>
@@ -917,10 +917,10 @@
     <t xml:space="preserve">11.3839349746704</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6650199890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4307823181152</t>
+    <t xml:space="preserve">11.6650190353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4307832717896</t>
   </si>
   <si>
     <t xml:space="preserve">10.9623079299927</t>
@@ -935,22 +935,22 @@
     <t xml:space="preserve">11.571325302124</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3370876312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2902412414551</t>
+    <t xml:space="preserve">11.3370885848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2902402877808</t>
   </si>
   <si>
     <t xml:space="preserve">11.7118673324585</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7587156295776</t>
+    <t xml:space="preserve">11.7587146759033</t>
   </si>
   <si>
     <t xml:space="preserve">11.8055629730225</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0091562271118</t>
+    <t xml:space="preserve">11.0091552734375</t>
   </si>
   <si>
     <t xml:space="preserve">9.46318912506104</t>
@@ -974,31 +974,31 @@
     <t xml:space="preserve">8.44191455841064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32948112487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25452423095703</t>
+    <t xml:space="preserve">8.32948017120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25452518463135</t>
   </si>
   <si>
     <t xml:space="preserve">8.43254470825195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47002220153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32010936737061</t>
+    <t xml:space="preserve">8.47002124786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32011127471924</t>
   </si>
   <si>
     <t xml:space="preserve">8.20767688751221</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0858736038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78604936599731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49559545516968</t>
+    <t xml:space="preserve">8.08587265014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78604984283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49559497833252</t>
   </si>
   <si>
     <t xml:space="preserve">7.33631372451782</t>
@@ -1007,31 +1007,31 @@
     <t xml:space="preserve">7.23324918746948</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83289623260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90785264968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50496482849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37379169464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12081527709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28009700775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98027324676514</t>
+    <t xml:space="preserve">7.8328971862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90785217285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50496530532837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37379217147827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12081575393677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28009653091431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98027276992798</t>
   </si>
   <si>
     <t xml:space="preserve">6.93342590332031</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06459808349609</t>
+    <t xml:space="preserve">7.06459856033325</t>
   </si>
   <si>
     <t xml:space="preserve">7.02712059020996</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">8.65194320678711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46116256713867</t>
+    <t xml:space="preserve">8.46116161346436</t>
   </si>
   <si>
     <t xml:space="preserve">8.53747367858887</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">8.66148281097412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49931716918945</t>
+    <t xml:space="preserve">8.49931812286377</t>
   </si>
   <si>
     <t xml:space="preserve">8.42300605773926</t>
@@ -1091,22 +1091,22 @@
     <t xml:space="preserve">8.29899787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12729549407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89835643768311</t>
+    <t xml:space="preserve">8.12729454040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89835596084595</t>
   </si>
   <si>
     <t xml:space="preserve">8.10821628570557</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8411226272583</t>
+    <t xml:space="preserve">7.84112215042114</t>
   </si>
   <si>
     <t xml:space="preserve">8.33715343475342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20360660552979</t>
+    <t xml:space="preserve">8.2036075592041</t>
   </si>
   <si>
     <t xml:space="preserve">8.06052017211914</t>
@@ -1118,31 +1118,31 @@
     <t xml:space="preserve">8.07005977630615</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92697334289551</t>
+    <t xml:space="preserve">7.92697381973267</t>
   </si>
   <si>
     <t xml:space="preserve">7.98420763015747</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30853652954102</t>
+    <t xml:space="preserve">8.30853748321533</t>
   </si>
   <si>
     <t xml:space="preserve">8.26084136962891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2703800201416</t>
+    <t xml:space="preserve">8.27038097381592</t>
   </si>
   <si>
     <t xml:space="preserve">8.18452835083008</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03190422058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96512985229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86019992828369</t>
+    <t xml:space="preserve">8.03190326690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96513032913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86019945144653</t>
   </si>
   <si>
     <t xml:space="preserve">7.86973905563354</t>
@@ -1151,43 +1151,43 @@
     <t xml:space="preserve">7.71711397171021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91743421554565</t>
+    <t xml:space="preserve">7.91743516921997</t>
   </si>
   <si>
     <t xml:space="preserve">7.76480960845947</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72665309906006</t>
+    <t xml:space="preserve">7.72665357589722</t>
   </si>
   <si>
     <t xml:space="preserve">7.65034103393555</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63126230239868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65987968444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.165452003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32761478424072</t>
+    <t xml:space="preserve">7.63126182556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65987873077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16545104980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32761383056641</t>
   </si>
   <si>
     <t xml:space="preserve">8.11775588989258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93651247024536</t>
+    <t xml:space="preserve">7.93651151657104</t>
   </si>
   <si>
     <t xml:space="preserve">8.19406795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2322244644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31807613372803</t>
+    <t xml:space="preserve">8.23222351074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31807708740234</t>
   </si>
   <si>
     <t xml:space="preserve">8.15591144561768</t>
@@ -1196,7 +1196,7 @@
     <t xml:space="preserve">8.22268486022949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25130081176758</t>
+    <t xml:space="preserve">8.25130176544189</t>
   </si>
   <si>
     <t xml:space="preserve">8.35623264312744</t>
@@ -1214,37 +1214,37 @@
     <t xml:space="preserve">7.77434825897217</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82204389572144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97466850280762</t>
+    <t xml:space="preserve">7.82204437255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97466897964478</t>
   </si>
   <si>
     <t xml:space="preserve">8.01282501220703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05098152160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67895793914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7361912727356</t>
+    <t xml:space="preserve">8.05098056793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67895746231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73619174957275</t>
   </si>
   <si>
     <t xml:space="preserve">7.6980357170105</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51679372787476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59310579299927</t>
+    <t xml:space="preserve">7.5167932510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59310626983643</t>
   </si>
   <si>
     <t xml:space="preserve">7.44048070907593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53587198257446</t>
+    <t xml:space="preserve">7.5358715057373</t>
   </si>
   <si>
     <t xml:space="preserve">7.62172269821167</t>
@@ -1259,10 +1259,10 @@
     <t xml:space="preserve">7.20200395584106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1829252243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14476919174194</t>
+    <t xml:space="preserve">7.18292570114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14476871490479</t>
   </si>
   <si>
     <t xml:space="preserve">7.12569093704224</t>
@@ -1277,79 +1277,79 @@
     <t xml:space="preserve">7.24969911575317</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24016046524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46909809112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41186380386353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45001935958862</t>
+    <t xml:space="preserve">7.24015998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46909761428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41186285018921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45001983642578</t>
   </si>
   <si>
     <t xml:space="preserve">7.28785514831543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39278554916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3355507850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61218404769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90789604187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94605159759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45955896377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70757484436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87927913665771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99374675750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75527048110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81250429153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79342651367188</t>
+    <t xml:space="preserve">7.39278507232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33555126190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61218357086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90789556503296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94605112075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45955848693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70757436752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8792781829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99374723434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75527000427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81250476837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79342699050903</t>
   </si>
   <si>
     <t xml:space="preserve">7.80296611785889</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85066080093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74573087692261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83158302307129</t>
+    <t xml:space="preserve">7.85066032409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74573135375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83158254623413</t>
   </si>
   <si>
     <t xml:space="preserve">7.66941833496094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60264492034912</t>
+    <t xml:space="preserve">7.60264539718628</t>
   </si>
   <si>
     <t xml:space="preserve">7.58356666564941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88881826400757</t>
+    <t xml:space="preserve">7.88881778717041</t>
   </si>
   <si>
     <t xml:space="preserve">8.00328636169434</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">7.27831649780273</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08753442764282</t>
+    <t xml:space="preserve">7.08753490447998</t>
   </si>
   <si>
     <t xml:space="preserve">7.05891799926758</t>
@@ -1376,10 +1376,10 @@
     <t xml:space="preserve">7.50372648239136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98721408843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02589225769043</t>
+    <t xml:space="preserve">7.98721361160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02589321136475</t>
   </si>
   <si>
     <t xml:space="preserve">8.04523086547852</t>
@@ -1391,25 +1391,25 @@
     <t xml:space="preserve">8.07424163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12258911132812</t>
+    <t xml:space="preserve">8.12259006500244</t>
   </si>
   <si>
     <t xml:space="preserve">8.05490112304688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94853496551514</t>
+    <t xml:space="preserve">7.94853448867798</t>
   </si>
   <si>
     <t xml:space="preserve">8.06457138061523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08390998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97754430770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93886518478394</t>
+    <t xml:space="preserve">8.08391094207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97754383087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93886423110962</t>
   </si>
   <si>
     <t xml:space="preserve">7.79381895065308</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">7.68745088577271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63910293579102</t>
+    <t xml:space="preserve">7.63910245895386</t>
   </si>
   <si>
     <t xml:space="preserve">7.73579978942871</t>
@@ -1436,10 +1436,10 @@
     <t xml:space="preserve">7.90985584259033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85183668136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83249759674072</t>
+    <t xml:space="preserve">7.85183715820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83249807357788</t>
   </si>
   <si>
     <t xml:space="preserve">7.81315755844116</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">7.80348825454712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78414916992188</t>
+    <t xml:space="preserve">7.78414869308472</t>
   </si>
   <si>
     <t xml:space="preserve">7.6681113243103</t>
@@ -1460,13 +1460,13 @@
     <t xml:space="preserve">7.71646022796631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75513982772827</t>
+    <t xml:space="preserve">7.75514030456543</t>
   </si>
   <si>
     <t xml:space="preserve">7.74547004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86150693893433</t>
+    <t xml:space="preserve">7.86150646209717</t>
   </si>
   <si>
     <t xml:space="preserve">7.89051580429077</t>
@@ -1484,10 +1484,10 @@
     <t xml:space="preserve">8.09358024597168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13225936889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1515998840332</t>
+    <t xml:space="preserve">8.1322603225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15159893035889</t>
   </si>
   <si>
     <t xml:space="preserve">8.1129207611084</t>
@@ -1496,10 +1496,10 @@
     <t xml:space="preserve">8.03556251525879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92919492721558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69712066650391</t>
+    <t xml:space="preserve">7.92919540405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69712114334106</t>
   </si>
   <si>
     <t xml:space="preserve">7.60042381286621</t>
@@ -1508,10 +1508,10 @@
     <t xml:space="preserve">7.88084602355957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55207443237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40702819824219</t>
+    <t xml:space="preserve">7.55207490921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40702867507935</t>
   </si>
   <si>
     <t xml:space="preserve">7.34900999069214</t>
@@ -1520,16 +1520,16 @@
     <t xml:space="preserve">7.37801933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43603754043579</t>
+    <t xml:space="preserve">7.43603801727295</t>
   </si>
   <si>
     <t xml:space="preserve">7.41669797897339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52306604385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36834955215454</t>
+    <t xml:space="preserve">7.5230655670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36834907531738</t>
   </si>
   <si>
     <t xml:space="preserve">7.542405128479</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">7.4843864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70679044723511</t>
+    <t xml:space="preserve">7.70679092407227</t>
   </si>
   <si>
     <t xml:space="preserve">7.64877223968506</t>
@@ -1556,10 +1556,10 @@
     <t xml:space="preserve">7.59075355529785</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95820426940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96787405014038</t>
+    <t xml:space="preserve">7.95820331573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96787357330322</t>
   </si>
   <si>
     <t xml:space="preserve">7.90018606185913</t>
@@ -1577,10 +1577,10 @@
     <t xml:space="preserve">8.19027900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29664611816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45136165618896</t>
+    <t xml:space="preserve">8.29664516448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45136070251465</t>
   </si>
   <si>
     <t xml:space="preserve">8.48037147521973</t>
@@ -1607,19 +1607,19 @@
     <t xml:space="preserve">8.50938034057617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4223518371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54805946350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55772972106934</t>
+    <t xml:space="preserve">8.42235279083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54805850982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55772876739502</t>
   </si>
   <si>
     <t xml:space="preserve">8.52871990203857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68343448638916</t>
+    <t xml:space="preserve">8.68343544006348</t>
   </si>
   <si>
     <t xml:space="preserve">8.76079368591309</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">8.65442562103271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75112438201904</t>
+    <t xml:space="preserve">8.75112342834473</t>
   </si>
   <si>
     <t xml:space="preserve">8.70277500152588</t>
@@ -1652,10 +1652,10 @@
     <t xml:space="preserve">8.63508701324463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32565402984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31598472595215</t>
+    <t xml:space="preserve">8.32565498352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31598567962646</t>
   </si>
   <si>
     <t xml:space="preserve">8.30631542205811</t>
@@ -63530,7 +63530,7 @@
     </row>
     <row r="2344">
       <c r="A2344" s="1" t="n">
-        <v>46034.6910648148</v>
+        <v>46034.3333333333</v>
       </c>
       <c r="B2344" t="n">
         <v>100483</v>
@@ -63551,6 +63551,32 @@
         <v>742</v>
       </c>
       <c r="H2344" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2345">
+      <c r="A2345" s="1" t="n">
+        <v>46035.6912962963</v>
+      </c>
+      <c r="B2345" t="n">
+        <v>64306</v>
+      </c>
+      <c r="C2345" t="n">
+        <v>9.65999984741211</v>
+      </c>
+      <c r="D2345" t="n">
+        <v>9.47999954223633</v>
+      </c>
+      <c r="E2345" t="n">
+        <v>9.57999992370605</v>
+      </c>
+      <c r="F2345" t="n">
+        <v>9.52000045776367</v>
+      </c>
+      <c r="G2345" t="s">
+        <v>743</v>
+      </c>
+      <c r="H2345" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="756">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="757">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,37 +38,37 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0764217376709</t>
+    <t xml:space="preserve">9.07642078399658</t>
   </si>
   <si>
     <t xml:space="preserve">FF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98565673828125</t>
+    <t xml:space="preserve">8.98565769195557</t>
   </si>
   <si>
     <t xml:space="preserve">9.08549880981445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24887275695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09457302093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12180328369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03103923797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95388889312744</t>
+    <t xml:space="preserve">9.24887371063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09457492828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12180519104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03104019165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95388984680176</t>
   </si>
   <si>
     <t xml:space="preserve">8.89943218231201</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89489269256592</t>
+    <t xml:space="preserve">8.89489364624023</t>
   </si>
   <si>
     <t xml:space="preserve">8.84951019287109</t>
@@ -83,10 +83,10 @@
     <t xml:space="preserve">8.76782321929932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86766529083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04919338226318</t>
+    <t xml:space="preserve">8.86766338348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04919242858887</t>
   </si>
   <si>
     <t xml:space="preserve">9.23072147369385</t>
@@ -95,43 +95,43 @@
     <t xml:space="preserve">9.11272716522217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96750450134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91304492950439</t>
+    <t xml:space="preserve">8.96750545501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91304683685303</t>
   </si>
   <si>
     <t xml:space="preserve">8.92212295532227</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00380897521973</t>
+    <t xml:space="preserve">9.00380992889404</t>
   </si>
   <si>
     <t xml:space="preserve">9.15810966491699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16718673706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43947887420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54839611053467</t>
+    <t xml:space="preserve">9.16718578338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43947792053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54839515686035</t>
   </si>
   <si>
     <t xml:space="preserve">9.62100791931152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80253505706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71177101135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56654739379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58470249176025</t>
+    <t xml:space="preserve">9.8025369644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71177196502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56654930114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58470153808594</t>
   </si>
   <si>
     <t xml:space="preserve">9.5756254196167</t>
@@ -146,16 +146,16 @@
     <t xml:space="preserve">9.60285472869873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63915920257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79345798492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95683574676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93868350982666</t>
+    <t xml:space="preserve">9.63916015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79345893859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95683670043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93868160247803</t>
   </si>
   <si>
     <t xml:space="preserve">9.98406410217285</t>
@@ -164,37 +164,37 @@
     <t xml:space="preserve">9.73900032043457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76622867584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74807643890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75715446472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64823627471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82068824768066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70269584655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72084808349609</t>
+    <t xml:space="preserve">9.76623058319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74807548522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75715351104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64823722839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82068729400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7026948928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72084712982178</t>
   </si>
   <si>
     <t xml:space="preserve">9.67546558380127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66638851165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63008308410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65731334686279</t>
+    <t xml:space="preserve">9.66638946533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63008213043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65731239318848</t>
   </si>
   <si>
     <t xml:space="preserve">9.68454170227051</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">9.82976531982422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84791851043701</t>
+    <t xml:space="preserve">9.8479175567627</t>
   </si>
   <si>
     <t xml:space="preserve">9.83884143829346</t>
@@ -215,172 +215,172 @@
     <t xml:space="preserve">9.72992420196533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78438377380371</t>
+    <t xml:space="preserve">9.78438282012939</t>
   </si>
   <si>
     <t xml:space="preserve">9.55747127532959</t>
   </si>
   <si>
+    <t xml:space="preserve">9.34871578216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33963775634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27610492706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25794982910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19441509246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18533802032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41224956512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22164535522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31240940093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26702690124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29425525665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28517913818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37594318389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36686611175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38502025604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45763111114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39409732818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48486137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49393844604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44855403900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4757833480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23979663848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14903354644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21256828308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20349216461182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13088130950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13995456695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94027423858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80412864685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75874519348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66798400878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62260150909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53183555603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35030937194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16877937316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9872522354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03263378143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12339687347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25954341888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94186925888062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3049259185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21416187286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39568996429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57721710205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71336555480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53202342987061</t>
+  </si>
+  <si>
     <t xml:space="preserve">9.34871482849121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33963871002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27610301971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2579517364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19441604614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18533897399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4122486114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22164535522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31240940093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26702690124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29425621032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28517913818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37594413757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36686706542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38502025604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45763111114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39409732818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48485946655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49393844604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44855499267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47578430175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23979759216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14903259277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21256732940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20349216461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13088035583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13995742797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94027519226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80412864685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75874614715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66798305511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62260055541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53183555603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35030841827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16877937316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98725175857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03263378143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12339687347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25954437255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94186878204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30492496490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21416187286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39568996429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5772180557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71336555480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53202342987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34871578216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25706100463867</t>
+    <t xml:space="preserve">9.25706005096436</t>
   </si>
   <si>
     <t xml:space="preserve">9.44036960601807</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16540622711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07375144958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11957931518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98209762573242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02792549133301</t>
+    <t xml:space="preserve">9.16540718078613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07375240325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11957836151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98209857940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02792453765869</t>
   </si>
   <si>
     <t xml:space="preserve">9.62367725372314</t>
@@ -389,28 +389,28 @@
     <t xml:space="preserve">9.80698490142822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89863872528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99029350280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1736011505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2652540206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3569107055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5402173995972</t>
+    <t xml:space="preserve">9.89864063262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9902925491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.173602104187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2652559280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3569097518921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5402183532715</t>
   </si>
   <si>
     <t xml:space="preserve">10.631872177124</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8151798248291</t>
+    <t xml:space="preserve">10.8151807785034</t>
   </si>
   <si>
     <t xml:space="preserve">10.7235260009766</t>
@@ -419,37 +419,37 @@
     <t xml:space="preserve">10.9068326950073</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9984874725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.090142250061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1817951202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2734498977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4567584991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3651027679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4485635757446</t>
+    <t xml:space="preserve">10.9984884262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0901412963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1817970275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2734508514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4567575454712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3651037216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4485626220703</t>
   </si>
   <si>
     <t xml:space="preserve">9.71533203125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79879093170166</t>
+    <t xml:space="preserve">8.79878997802734</t>
   </si>
   <si>
     <t xml:space="preserve">8.24886608123779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21123313903809</t>
+    <t xml:space="preserve">9.21123504638672</t>
   </si>
   <si>
     <t xml:space="preserve">9.30288696289062</t>
@@ -458,19 +458,19 @@
     <t xml:space="preserve">9.03709030151367</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39454174041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76115703582764</t>
+    <t xml:space="preserve">9.3945426940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76115798950195</t>
   </si>
   <si>
     <t xml:space="preserve">9.66950416564941</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57784843444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0361213684082</t>
+    <t xml:space="preserve">9.57785034179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0361194610596</t>
   </si>
   <si>
     <t xml:space="preserve">9.94446659088135</t>
@@ -479,52 +479,52 @@
     <t xml:space="preserve">9.82552433013916</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73283004760742</t>
+    <t xml:space="preserve">9.73283100128174</t>
   </si>
   <si>
     <t xml:space="preserve">9.59379005432129</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96456432342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91821670532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54744243621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0109119415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1036043167114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1499519348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1962985992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77917671203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87186908721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0572576522827</t>
+    <t xml:space="preserve">9.96456527709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91821765899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54744338989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.010910987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1036062240601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1499509811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1962976455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77917766571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87187099456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.057258605957</t>
   </si>
   <si>
     <t xml:space="preserve">10.2889919281006</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4743795394897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2426452636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3816862106323</t>
+    <t xml:space="preserve">10.4743785858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2426443099976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.381685256958</t>
   </si>
   <si>
     <t xml:space="preserve">9.68648338317871</t>
@@ -536,7 +536,7 @@
     <t xml:space="preserve">9.50109672546387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31570911407471</t>
+    <t xml:space="preserve">9.31570816040039</t>
   </si>
   <si>
     <t xml:space="preserve">9.23228454589844</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">9.25082302093506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26936149597168</t>
+    <t xml:space="preserve">9.269362449646</t>
   </si>
   <si>
     <t xml:space="preserve">9.21374607086182</t>
@@ -557,28 +557,28 @@
     <t xml:space="preserve">9.04689693450928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12105274200439</t>
+    <t xml:space="preserve">9.12105178833008</t>
   </si>
   <si>
     <t xml:space="preserve">9.0654354095459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97274208068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17666721343994</t>
+    <t xml:space="preserve">8.97274398803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17666912078857</t>
   </si>
   <si>
     <t xml:space="preserve">9.02835845947266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95420265197754</t>
+    <t xml:space="preserve">8.95420360565186</t>
   </si>
   <si>
     <t xml:space="preserve">8.71320056915283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9912805557251</t>
+    <t xml:space="preserve">8.99128150939941</t>
   </si>
   <si>
     <t xml:space="preserve">8.76881694793701</t>
@@ -593,19 +593,19 @@
     <t xml:space="preserve">10.3353395462036</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9841957092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0305414199829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2159290313721</t>
+    <t xml:space="preserve">10.9841938018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0305404663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2159280776978</t>
   </si>
   <si>
     <t xml:space="preserve">11.4940090179443</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5403566360474</t>
+    <t xml:space="preserve">11.540355682373</t>
   </si>
   <si>
     <t xml:space="preserve">11.5867033004761</t>
@@ -614,16 +614,16 @@
     <t xml:space="preserve">11.6330509185791</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7257432937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9111309051514</t>
+    <t xml:space="preserve">11.7257423400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9111299514771</t>
   </si>
   <si>
     <t xml:space="preserve">11.9574766159058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1892118453979</t>
+    <t xml:space="preserve">12.1892108917236</t>
   </si>
   <si>
     <t xml:space="preserve">12.2819042205811</t>
@@ -638,10 +638,10 @@
     <t xml:space="preserve">12.3282518386841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1428651809692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0965185165405</t>
+    <t xml:space="preserve">12.1428642272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0965175628662</t>
   </si>
   <si>
     <t xml:space="preserve">12.555121421814</t>
@@ -650,46 +650,46 @@
     <t xml:space="preserve">12.5082750320435</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6488161087036</t>
+    <t xml:space="preserve">12.6488170623779</t>
   </si>
   <si>
     <t xml:space="preserve">12.4614267349243</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4145784378052</t>
+    <t xml:space="preserve">12.4145793914795</t>
   </si>
   <si>
     <t xml:space="preserve">12.7425117492676</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6956634521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2271900177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1803426742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3208847045898</t>
+    <t xml:space="preserve">12.6956644058228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2271890640259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1803417205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3208837509155</t>
   </si>
   <si>
     <t xml:space="preserve">12.274037361145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8362054824829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7893581390381</t>
+    <t xml:space="preserve">12.8362064361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7893590927124</t>
   </si>
   <si>
     <t xml:space="preserve">12.6019697189331</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9299011230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8830537796021</t>
+    <t xml:space="preserve">12.9299020767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8830547332764</t>
   </si>
   <si>
     <t xml:space="preserve">13.0704441070557</t>
@@ -698,13 +698,13 @@
     <t xml:space="preserve">13.679461479187</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8668518066406</t>
+    <t xml:space="preserve">13.8668508529663</t>
   </si>
   <si>
     <t xml:space="preserve">14.0542402267456</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3353261947632</t>
+    <t xml:space="preserve">14.3353252410889</t>
   </si>
   <si>
     <t xml:space="preserve">14.5695638656616</t>
@@ -713,55 +713,55 @@
     <t xml:space="preserve">15.2254276275635</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1317329406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7569522857666</t>
+    <t xml:space="preserve">15.1317319869995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7569532394409</t>
   </si>
   <si>
     <t xml:space="preserve">15.0380373001099</t>
   </si>
   <si>
-    <t xml:space="preserve">15.178581237793</t>
+    <t xml:space="preserve">15.1785802841187</t>
   </si>
   <si>
     <t xml:space="preserve">15.3191232681274</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8974952697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4596662521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4128198623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5533618927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0686798095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8650913238525</t>
+    <t xml:space="preserve">14.8974943161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4596652984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4128189086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5533599853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0686836242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8650875091553</t>
   </si>
   <si>
     <t xml:space="preserve">17.0056324005127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7713947296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1930198669434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0524806976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9587860107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7245483398438</t>
+    <t xml:space="preserve">16.7713928222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.193021774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0524787902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9587841033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7245464324951</t>
   </si>
   <si>
     <t xml:space="preserve">16.6308517456055</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">16.584005355835</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2092247009277</t>
+    <t xml:space="preserve">16.2092227935791</t>
   </si>
   <si>
     <t xml:space="preserve">16.2560729980469</t>
@@ -785,10 +785,10 @@
     <t xml:space="preserve">16.396614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3029193878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8344430923462</t>
+    <t xml:space="preserve">16.3029174804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8344440460205</t>
   </si>
   <si>
     <t xml:space="preserve">16.1155300140381</t>
@@ -800,7 +800,7 @@
     <t xml:space="preserve">16.1623764038086</t>
   </si>
   <si>
-    <t xml:space="preserve">15.974986076355</t>
+    <t xml:space="preserve">15.9749879837036</t>
   </si>
   <si>
     <t xml:space="preserve">15.7407484054565</t>
@@ -812,22 +812,22 @@
     <t xml:space="preserve">16.9119358062744</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0993251800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.677698135376</t>
+    <t xml:space="preserve">17.0993270874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6776962280273</t>
   </si>
   <si>
     <t xml:space="preserve">16.8182430267334</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2722749710083</t>
+    <t xml:space="preserve">15.272274017334</t>
   </si>
   <si>
     <t xml:space="preserve">15.084885597229</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9911909103394</t>
+    <t xml:space="preserve">14.991189956665</t>
   </si>
   <si>
     <t xml:space="preserve">14.8038005828857</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">14.382173538208</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1010875701904</t>
+    <t xml:space="preserve">14.1010885238647</t>
   </si>
   <si>
     <t xml:space="preserve">14.2884788513184</t>
@@ -854,10 +854,10 @@
     <t xml:space="preserve">14.2416305541992</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1947822570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0073928833008</t>
+    <t xml:space="preserve">14.1947832107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0073938369751</t>
   </si>
   <si>
     <t xml:space="preserve">13.7263088226318</t>
@@ -866,31 +866,31 @@
     <t xml:space="preserve">14.1479358673096</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4290208816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6164112091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7731561660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3515281677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3046808242798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3983755111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0235958099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1172914505005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9767484664917</t>
+    <t xml:space="preserve">14.4290199279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6164102554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7731552124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3515291213989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3046817779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3983764648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0235967636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1172924041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.976749420166</t>
   </si>
   <si>
     <t xml:space="preserve">12.3677320480347</t>
@@ -902,25 +902,25 @@
     <t xml:space="preserve">11.9929523468018</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8992586135864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0398006439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1334943771362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4776306152344</t>
+    <t xml:space="preserve">11.8992567062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0397996902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1334934234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4776296615601</t>
   </si>
   <si>
     <t xml:space="preserve">11.2433929443359</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3839349746704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6650199890137</t>
+    <t xml:space="preserve">11.3839340209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6650190353394</t>
   </si>
   <si>
     <t xml:space="preserve">11.4307823181152</t>
@@ -929,25 +929,25 @@
     <t xml:space="preserve">10.9623079299927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7280702590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1965456008911</t>
+    <t xml:space="preserve">10.7280712127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1965446472168</t>
   </si>
   <si>
     <t xml:space="preserve">11.571325302124</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3370885848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2902393341064</t>
+    <t xml:space="preserve">11.3370876312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2902402877808</t>
   </si>
   <si>
     <t xml:space="preserve">11.7118673324585</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7587156295776</t>
+    <t xml:space="preserve">11.7587146759033</t>
   </si>
   <si>
     <t xml:space="preserve">11.8055629730225</t>
@@ -956,10 +956,10 @@
     <t xml:space="preserve">11.0091552734375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46318817138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33884906768799</t>
+    <t xml:space="preserve">9.46318912506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33884811401367</t>
   </si>
   <si>
     <t xml:space="preserve">8.57308673858643</t>
@@ -971,46 +971,46 @@
     <t xml:space="preserve">8.45128440856934</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61993408203125</t>
+    <t xml:space="preserve">8.61993312835693</t>
   </si>
   <si>
     <t xml:space="preserve">8.44191360473633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32948017120361</t>
+    <t xml:space="preserve">8.32948112487793</t>
   </si>
   <si>
     <t xml:space="preserve">8.25452423095703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43254566192627</t>
+    <t xml:space="preserve">8.43254375457764</t>
   </si>
   <si>
     <t xml:space="preserve">8.47002220153809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32011127471924</t>
+    <t xml:space="preserve">8.32011032104492</t>
   </si>
   <si>
     <t xml:space="preserve">8.20767784118652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0858736038208</t>
+    <t xml:space="preserve">8.08587265014648</t>
   </si>
   <si>
     <t xml:space="preserve">7.78604936599731</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49559545516968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33631372451782</t>
+    <t xml:space="preserve">7.49559497833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33631420135498</t>
   </si>
   <si>
     <t xml:space="preserve">7.23324918746948</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83289623260498</t>
+    <t xml:space="preserve">7.83289670944214</t>
   </si>
   <si>
     <t xml:space="preserve">7.90785217285156</t>
@@ -1031,7 +1031,7 @@
     <t xml:space="preserve">6.98027276992798</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93342590332031</t>
+    <t xml:space="preserve">6.93342542648315</t>
   </si>
   <si>
     <t xml:space="preserve">7.06459856033325</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">7.0271201133728</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34568357467651</t>
+    <t xml:space="preserve">7.34568309783936</t>
   </si>
   <si>
     <t xml:space="preserve">7.5424427986145</t>
@@ -1055,7 +1055,7 @@
     <t xml:space="preserve">8.65194320678711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46116161346436</t>
+    <t xml:space="preserve">8.46116256713867</t>
   </si>
   <si>
     <t xml:space="preserve">8.53747367858887</t>
@@ -1070,7 +1070,7 @@
     <t xml:space="preserve">8.84272575378418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72825622558594</t>
+    <t xml:space="preserve">8.72825527191162</t>
   </si>
   <si>
     <t xml:space="preserve">8.66148281097412</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">8.39438915252686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.604248046875</t>
+    <t xml:space="preserve">8.60424900054932</t>
   </si>
   <si>
     <t xml:space="preserve">8.48977851867676</t>
@@ -1094,10 +1094,10 @@
     <t xml:space="preserve">8.29899787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12729454040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89835596084595</t>
+    <t xml:space="preserve">8.12729549407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89835643768311</t>
   </si>
   <si>
     <t xml:space="preserve">8.10821628570557</t>
@@ -1106,7 +1106,7 @@
     <t xml:space="preserve">7.8411226272583</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33715438842773</t>
+    <t xml:space="preserve">8.33715343475342</t>
   </si>
   <si>
     <t xml:space="preserve">8.20360660552979</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">8.07005977630615</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92697381973267</t>
+    <t xml:space="preserve">7.92697334289551</t>
   </si>
   <si>
     <t xml:space="preserve">7.98420763015747</t>
@@ -1136,19 +1136,19 @@
     <t xml:space="preserve">8.2703800201416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18452930450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03190326690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96513032913208</t>
+    <t xml:space="preserve">8.18452835083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03190422058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96512985229492</t>
   </si>
   <si>
     <t xml:space="preserve">7.86019992828369</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8697395324707</t>
+    <t xml:space="preserve">7.86973905563354</t>
   </si>
   <si>
     <t xml:space="preserve">7.71711397171021</t>
@@ -1163,16 +1163,16 @@
     <t xml:space="preserve">7.72665309906006</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65034055709839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63126182556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65987920761108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16545104980469</t>
+    <t xml:space="preserve">7.65034103393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63126230239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65987968444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.165452003479</t>
   </si>
   <si>
     <t xml:space="preserve">8.32761478424072</t>
@@ -1181,25 +1181,25 @@
     <t xml:space="preserve">8.11775588989258</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93651151657104</t>
+    <t xml:space="preserve">7.93651247024536</t>
   </si>
   <si>
     <t xml:space="preserve">8.19406795501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23222351074219</t>
+    <t xml:space="preserve">8.2322244644165</t>
   </si>
   <si>
     <t xml:space="preserve">8.31807613372803</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15591239929199</t>
+    <t xml:space="preserve">8.15591144561768</t>
   </si>
   <si>
     <t xml:space="preserve">8.22268486022949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25130176544189</t>
+    <t xml:space="preserve">8.25130081176758</t>
   </si>
   <si>
     <t xml:space="preserve">8.35623264312744</t>
@@ -1220,19 +1220,19 @@
     <t xml:space="preserve">7.82204389572144</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97466802597046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01282405853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05098056793213</t>
+    <t xml:space="preserve">7.97466850280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01282501220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05098152160645</t>
   </si>
   <si>
     <t xml:space="preserve">7.67895793914795</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73619174957275</t>
+    <t xml:space="preserve">7.7361912727356</t>
   </si>
   <si>
     <t xml:space="preserve">7.6980357170105</t>
@@ -1262,7 +1262,7 @@
     <t xml:space="preserve">7.20200395584106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18292570114136</t>
+    <t xml:space="preserve">7.1829252243042</t>
   </si>
   <si>
     <t xml:space="preserve">7.14476919174194</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">7.23062086105347</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15430784225464</t>
+    <t xml:space="preserve">7.1543083190918</t>
   </si>
   <si>
     <t xml:space="preserve">7.24969911575317</t>
@@ -1283,10 +1283,10 @@
     <t xml:space="preserve">7.24016046524048</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46909761428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41186332702637</t>
+    <t xml:space="preserve">7.46909809112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41186380386353</t>
   </si>
   <si>
     <t xml:space="preserve">7.45001935958862</t>
@@ -1295,40 +1295,40 @@
     <t xml:space="preserve">7.28785514831543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39278507232666</t>
+    <t xml:space="preserve">7.39278554916382</t>
   </si>
   <si>
     <t xml:space="preserve">7.3355507850647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61218357086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90789556503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94605112075806</t>
+    <t xml:space="preserve">7.61218404769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90789604187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94605159759521</t>
   </si>
   <si>
     <t xml:space="preserve">7.45955896377563</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70757436752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87927865982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99374723434448</t>
+    <t xml:space="preserve">7.70757484436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87927913665771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99374675750732</t>
   </si>
   <si>
     <t xml:space="preserve">7.75527048110962</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81250476837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79342699050903</t>
+    <t xml:space="preserve">7.81250429153442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79342651367188</t>
   </si>
   <si>
     <t xml:space="preserve">7.80296611785889</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">7.74573087692261</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83158349990845</t>
+    <t xml:space="preserve">7.83158302307129</t>
   </si>
   <si>
     <t xml:space="preserve">7.66941833496094</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">7.58356666564941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88881778717041</t>
+    <t xml:space="preserve">7.88881826400757</t>
   </si>
   <si>
     <t xml:space="preserve">8.00328636169434</t>
@@ -1361,7 +1361,7 @@
     <t xml:space="preserve">7.78388738632202</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36416816711426</t>
+    <t xml:space="preserve">7.3641676902771</t>
   </si>
   <si>
     <t xml:space="preserve">7.10661315917969</t>
@@ -1370,10 +1370,10 @@
     <t xml:space="preserve">7.27831649780273</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08753490447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05891752243042</t>
+    <t xml:space="preserve">7.08753442764282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05891799926758</t>
   </si>
   <si>
     <t xml:space="preserve">7.50372648239136</t>
@@ -2280,6 +2280,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.72000026702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81999969482422</t>
   </si>
 </sst>
 </file>
@@ -63588,7 +63591,7 @@
     </row>
     <row r="2346">
       <c r="A2346" s="1" t="n">
-        <v>46036.6911226852</v>
+        <v>46036.3333333333</v>
       </c>
       <c r="B2346" t="n">
         <v>70784</v>
@@ -63609,6 +63612,32 @@
         <v>755</v>
       </c>
       <c r="H2346" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2347">
+      <c r="A2347" s="1" t="n">
+        <v>46037.6910532407</v>
+      </c>
+      <c r="B2347" t="n">
+        <v>87671</v>
+      </c>
+      <c r="C2347" t="n">
+        <v>9.84000015258789</v>
+      </c>
+      <c r="D2347" t="n">
+        <v>9.68000030517578</v>
+      </c>
+      <c r="E2347" t="n">
+        <v>9.72000026702881</v>
+      </c>
+      <c r="F2347" t="n">
+        <v>9.81999969482422</v>
+      </c>
+      <c r="G2347" t="s">
+        <v>756</v>
+      </c>
+      <c r="H2347" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -38,121 +38,121 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07642269134521</t>
+    <t xml:space="preserve">9.0764217376709</t>
   </si>
   <si>
     <t xml:space="preserve">FF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98565769195557</t>
+    <t xml:space="preserve">8.98565673828125</t>
   </si>
   <si>
     <t xml:space="preserve">9.08549880981445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24887371063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09457588195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12180519104004</t>
+    <t xml:space="preserve">9.24887180328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09457492828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12180423736572</t>
   </si>
   <si>
     <t xml:space="preserve">9.03103923797607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95389080047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8994312286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89489364624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84951019287109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85858726501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87673854827881</t>
+    <t xml:space="preserve">8.95388984680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89943218231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89489459991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84951114654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85858821868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87673950195312</t>
   </si>
   <si>
     <t xml:space="preserve">8.76782321929932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86766338348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0491943359375</t>
+    <t xml:space="preserve">8.8676643371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04919147491455</t>
   </si>
   <si>
     <t xml:space="preserve">9.23072147369385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11272716522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96750545501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91304683685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92212390899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00380992889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15810871124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16718482971191</t>
+    <t xml:space="preserve">9.11272811889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96750450134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91304588317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92212200164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00381088256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15810966491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16718578338623</t>
   </si>
   <si>
     <t xml:space="preserve">9.43947792053223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54839515686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62100791931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80253791809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71177101135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56654930114746</t>
+    <t xml:space="preserve">9.54839706420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62100601196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8025369644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71177291870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56654834747314</t>
   </si>
   <si>
     <t xml:space="preserve">9.58470153808594</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5756254196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53024291992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50301456451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60285472869873</t>
+    <t xml:space="preserve">9.57562351226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53024196624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50301265716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60285377502441</t>
   </si>
   <si>
     <t xml:space="preserve">9.63915920257568</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79345989227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95683479309082</t>
+    <t xml:space="preserve">9.79346084594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95683574676514</t>
   </si>
   <si>
     <t xml:space="preserve">9.93868160247803</t>
@@ -164,40 +164,40 @@
     <t xml:space="preserve">9.73899936676025</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7662296295166</t>
+    <t xml:space="preserve">9.76623058319092</t>
   </si>
   <si>
     <t xml:space="preserve">9.74807643890381</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75715255737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64823722839355</t>
+    <t xml:space="preserve">9.75715351104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64823532104492</t>
   </si>
   <si>
     <t xml:space="preserve">9.82068729400635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70269393920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72084712982178</t>
+    <t xml:space="preserve">9.7026948928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72084808349609</t>
   </si>
   <si>
     <t xml:space="preserve">9.67546653747559</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66638851165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63008308410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65731239318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68454170227051</t>
+    <t xml:space="preserve">9.66638946533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63008213043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65731334686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68454265594482</t>
   </si>
   <si>
     <t xml:space="preserve">9.81161308288574</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">9.82976531982422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8479175567627</t>
+    <t xml:space="preserve">9.84791851043701</t>
   </si>
   <si>
     <t xml:space="preserve">9.83884143829346</t>
@@ -224,22 +224,22 @@
     <t xml:space="preserve">9.34871482849121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33963775634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27610397338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25795078277588</t>
+    <t xml:space="preserve">9.33963680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27610301971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25794887542725</t>
   </si>
   <si>
     <t xml:space="preserve">9.19441604614258</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18533802032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41224956512451</t>
+    <t xml:space="preserve">9.18533897399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4122486114502</t>
   </si>
   <si>
     <t xml:space="preserve">9.22164535522461</t>
@@ -260,55 +260,55 @@
     <t xml:space="preserve">9.37594318389893</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36686706542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3850212097168</t>
+    <t xml:space="preserve">9.36686611175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38501930236816</t>
   </si>
   <si>
     <t xml:space="preserve">9.45763111114502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39409637451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48486137390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49393749237061</t>
+    <t xml:space="preserve">9.39409732818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48486042022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49393653869629</t>
   </si>
   <si>
     <t xml:space="preserve">9.44855403900146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47578239440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23979663848877</t>
+    <t xml:space="preserve">9.47578430175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23979759216309</t>
   </si>
   <si>
     <t xml:space="preserve">9.14903259277344</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21256732940674</t>
+    <t xml:space="preserve">9.21256828308105</t>
   </si>
   <si>
     <t xml:space="preserve">9.20349216461182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13087940216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13995456695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94027519226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8041296005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75874710083008</t>
+    <t xml:space="preserve">9.13088035583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13995552062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94027423858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80412864685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75874614715576</t>
   </si>
   <si>
     <t xml:space="preserve">8.66798305511475</t>
@@ -317,28 +317,28 @@
     <t xml:space="preserve">8.62260150909424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53183650970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35030937194824</t>
+    <t xml:space="preserve">8.53183746337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35030841827393</t>
   </si>
   <si>
     <t xml:space="preserve">8.16877937316895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98725128173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03263282775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12339687347412</t>
+    <t xml:space="preserve">7.98725032806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03263378143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12339782714844</t>
   </si>
   <si>
     <t xml:space="preserve">8.25954341888428</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94186925888062</t>
+    <t xml:space="preserve">7.9418683052063</t>
   </si>
   <si>
     <t xml:space="preserve">8.30492496490479</t>
@@ -350,28 +350,28 @@
     <t xml:space="preserve">8.39568996429443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57721900939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71336555480957</t>
+    <t xml:space="preserve">8.5772180557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71336650848389</t>
   </si>
   <si>
     <t xml:space="preserve">9.53202247619629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25705909729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44036960601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16540813446045</t>
+    <t xml:space="preserve">9.25706005096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44036865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16540622711182</t>
   </si>
   <si>
     <t xml:space="preserve">9.07375240325928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11957836151123</t>
+    <t xml:space="preserve">9.11958026885986</t>
   </si>
   <si>
     <t xml:space="preserve">8.98209857940674</t>
@@ -380,28 +380,28 @@
     <t xml:space="preserve">9.02792549133301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62367725372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80698394775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89864063262939</t>
+    <t xml:space="preserve">9.62367820739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80698490142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89863967895508</t>
   </si>
   <si>
     <t xml:space="preserve">9.9902925491333</t>
   </si>
   <si>
-    <t xml:space="preserve">10.173602104187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2652559280396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3569097518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5402173995972</t>
+    <t xml:space="preserve">10.1736030578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2652549743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3569087982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5402164459229</t>
   </si>
   <si>
     <t xml:space="preserve">10.631872177124</t>
@@ -413,43 +413,43 @@
     <t xml:space="preserve">10.7235260009766</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9068326950073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9984884262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0901412963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1817960739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2734508514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4567575454712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3651037216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4485626220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71533203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79878997802734</t>
+    <t xml:space="preserve">10.9068336486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9984874725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.090142250061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1817970275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2734498977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4567584991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3651027679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4485635757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71533107757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79879093170166</t>
   </si>
   <si>
     <t xml:space="preserve">8.24886608123779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2112340927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30288696289062</t>
+    <t xml:space="preserve">9.21123313903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30288791656494</t>
   </si>
   <si>
     <t xml:space="preserve">9.03709030151367</t>
@@ -461,10 +461,10 @@
     <t xml:space="preserve">9.76115703582764</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66950416564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57785034179688</t>
+    <t xml:space="preserve">9.6695032119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57784938812256</t>
   </si>
   <si>
     <t xml:space="preserve">10.0361194610596</t>
@@ -473,13 +473,13 @@
     <t xml:space="preserve">9.94446659088135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82552433013916</t>
+    <t xml:space="preserve">9.82552337646484</t>
   </si>
   <si>
     <t xml:space="preserve">9.73283100128174</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59379005432129</t>
+    <t xml:space="preserve">9.59379196166992</t>
   </si>
   <si>
     <t xml:space="preserve">9.96456527709961</t>
@@ -488,16 +488,16 @@
     <t xml:space="preserve">9.91821765899658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54744338989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.010910987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1036062240601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1499509811401</t>
+    <t xml:space="preserve">9.54744434356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0109100341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1036052703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1499519348145</t>
   </si>
   <si>
     <t xml:space="preserve">10.1962976455688</t>
@@ -506,19 +506,19 @@
     <t xml:space="preserve">9.77917766571045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87187099456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.057258605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2889919281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4743785858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2426443099976</t>
+    <t xml:space="preserve">9.87186908721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0572576522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2889928817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4743795394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2426452636719</t>
   </si>
   <si>
     <t xml:space="preserve">10.381685256958</t>
@@ -527,61 +527,61 @@
     <t xml:space="preserve">9.68648338317871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64013671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50109672546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31570816040039</t>
+    <t xml:space="preserve">9.64013576507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50109577178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31570911407471</t>
   </si>
   <si>
     <t xml:space="preserve">9.23228454589844</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19520854949951</t>
+    <t xml:space="preserve">9.1952075958252</t>
   </si>
   <si>
     <t xml:space="preserve">9.25082302093506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.269362449646</t>
+    <t xml:space="preserve">9.26936149597168</t>
   </si>
   <si>
     <t xml:space="preserve">9.21374607086182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04689693450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12105178833008</t>
+    <t xml:space="preserve">9.04689788818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12105274200439</t>
   </si>
   <si>
     <t xml:space="preserve">9.0654354095459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97274398803711</t>
+    <t xml:space="preserve">8.97274208068848</t>
   </si>
   <si>
     <t xml:space="preserve">9.17666912078857</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02835845947266</t>
+    <t xml:space="preserve">9.02835941314697</t>
   </si>
   <si>
     <t xml:space="preserve">8.95420360565186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71320056915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99128150939941</t>
+    <t xml:space="preserve">8.71319961547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99128246307373</t>
   </si>
   <si>
     <t xml:space="preserve">8.76881694793701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89858722686768</t>
+    <t xml:space="preserve">8.89858818054199</t>
   </si>
   <si>
     <t xml:space="preserve">8.93566513061523</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">10.9841938018799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0305404663086</t>
+    <t xml:space="preserve">11.0305414199829</t>
   </si>
   <si>
     <t xml:space="preserve">11.2159280776978</t>
@@ -608,10 +608,10 @@
     <t xml:space="preserve">11.5867033004761</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6330509185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7257423400879</t>
+    <t xml:space="preserve">11.6330499649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7257432937622</t>
   </si>
   <si>
     <t xml:space="preserve">11.9111299514771</t>
@@ -623,19 +623,19 @@
     <t xml:space="preserve">12.1892108917236</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2819042205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3745985031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5136394500732</t>
+    <t xml:space="preserve">12.2819051742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3745994567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5136384963989</t>
   </si>
   <si>
     <t xml:space="preserve">12.3282518386841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1428642272949</t>
+    <t xml:space="preserve">12.1428651809692</t>
   </si>
   <si>
     <t xml:space="preserve">12.0965175628662</t>
@@ -644,13 +644,13 @@
     <t xml:space="preserve">12.555121421814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5082750320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6488170623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4614267349243</t>
+    <t xml:space="preserve">12.5082740783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6488161087036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4614276885986</t>
   </si>
   <si>
     <t xml:space="preserve">12.4145793914795</t>
@@ -659,34 +659,34 @@
     <t xml:space="preserve">12.7425117492676</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6956644058228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2271890640259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1803417205811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3208837509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.274037361145</t>
+    <t xml:space="preserve">12.6956634521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2271900177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1803426742554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3208847045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2740383148193</t>
   </si>
   <si>
     <t xml:space="preserve">12.8362064361572</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7893590927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6019697189331</t>
+    <t xml:space="preserve">12.7893581390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6019687652588</t>
   </si>
   <si>
     <t xml:space="preserve">12.9299020767212</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8830547332764</t>
+    <t xml:space="preserve">12.8830537796021</t>
   </si>
   <si>
     <t xml:space="preserve">13.0704441070557</t>
@@ -707,10 +707,10 @@
     <t xml:space="preserve">14.5695638656616</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2254276275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1317319869995</t>
+    <t xml:space="preserve">15.2254285812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1317329406738</t>
   </si>
   <si>
     <t xml:space="preserve">14.7569532394409</t>
@@ -719,34 +719,34 @@
     <t xml:space="preserve">15.0380373001099</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1785802841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3191232681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8974943161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4596652984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4128189086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5533599853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0686836242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8650875091553</t>
+    <t xml:space="preserve">15.178581237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3191242218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8974952697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4596662521362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4128198623657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5533609390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0686817169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8650894165039</t>
   </si>
   <si>
     <t xml:space="preserve">17.0056324005127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7713928222656</t>
+    <t xml:space="preserve">16.7713947296143</t>
   </si>
   <si>
     <t xml:space="preserve">17.193021774292</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">17.0524787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9587841033936</t>
+    <t xml:space="preserve">16.9587860107422</t>
   </si>
   <si>
     <t xml:space="preserve">16.7245464324951</t>
@@ -764,13 +764,13 @@
     <t xml:space="preserve">16.6308517456055</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5371570587158</t>
+    <t xml:space="preserve">16.5371551513672</t>
   </si>
   <si>
     <t xml:space="preserve">16.584005355835</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2092227935791</t>
+    <t xml:space="preserve">16.2092247009277</t>
   </si>
   <si>
     <t xml:space="preserve">16.2560729980469</t>
@@ -779,10 +779,10 @@
     <t xml:space="preserve">17.1461734771729</t>
   </si>
   <si>
-    <t xml:space="preserve">16.396614074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3029174804688</t>
+    <t xml:space="preserve">16.3966159820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3029193878174</t>
   </si>
   <si>
     <t xml:space="preserve">15.8344440460205</t>
@@ -797,7 +797,7 @@
     <t xml:space="preserve">16.1623764038086</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9749879837036</t>
+    <t xml:space="preserve">15.974986076355</t>
   </si>
   <si>
     <t xml:space="preserve">15.7407484054565</t>
@@ -809,16 +809,16 @@
     <t xml:space="preserve">16.9119358062744</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0993270874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6776962280273</t>
+    <t xml:space="preserve">17.0993251800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.677698135376</t>
   </si>
   <si>
     <t xml:space="preserve">16.8182430267334</t>
   </si>
   <si>
-    <t xml:space="preserve">15.272274017334</t>
+    <t xml:space="preserve">15.2722749710083</t>
   </si>
   <si>
     <t xml:space="preserve">15.084885597229</t>
@@ -854,10 +854,10 @@
     <t xml:space="preserve">14.1947832107544</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0073938369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7263088226318</t>
+    <t xml:space="preserve">14.0073928833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7263078689575</t>
   </si>
   <si>
     <t xml:space="preserve">14.1479358673096</t>
@@ -866,16 +866,16 @@
     <t xml:space="preserve">14.4290199279785</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6164102554321</t>
+    <t xml:space="preserve">14.6164112091064</t>
   </si>
   <si>
     <t xml:space="preserve">13.7731552124023</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3515291213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3046817779541</t>
+    <t xml:space="preserve">13.3515281677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3046808242798</t>
   </si>
   <si>
     <t xml:space="preserve">13.3983764648438</t>
@@ -884,13 +884,13 @@
     <t xml:space="preserve">13.0235967636108</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1172924041748</t>
+    <t xml:space="preserve">13.1172914505005</t>
   </si>
   <si>
     <t xml:space="preserve">12.976749420166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3677320480347</t>
+    <t xml:space="preserve">12.367733001709</t>
   </si>
   <si>
     <t xml:space="preserve">12.0866470336914</t>
@@ -899,25 +899,25 @@
     <t xml:space="preserve">11.9929523468018</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8992567062378</t>
+    <t xml:space="preserve">11.8992576599121</t>
   </si>
   <si>
     <t xml:space="preserve">12.0397996902466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1334934234619</t>
+    <t xml:space="preserve">12.1334943771362</t>
   </si>
   <si>
     <t xml:space="preserve">11.4776296615601</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2433929443359</t>
+    <t xml:space="preserve">11.2433938980103</t>
   </si>
   <si>
     <t xml:space="preserve">11.3839340209961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6650190353394</t>
+    <t xml:space="preserve">11.6650199890137</t>
   </si>
   <si>
     <t xml:space="preserve">11.4307823181152</t>
@@ -926,10 +926,10 @@
     <t xml:space="preserve">10.9623079299927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7280712127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1965446472168</t>
+    <t xml:space="preserve">10.7280702590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1965456008911</t>
   </si>
   <si>
     <t xml:space="preserve">11.571325302124</t>
@@ -938,25 +938,25 @@
     <t xml:space="preserve">11.3370876312256</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2902402877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7118673324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7587146759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8055629730225</t>
+    <t xml:space="preserve">11.2902393341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7118682861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7587156295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8055639266968</t>
   </si>
   <si>
     <t xml:space="preserve">11.0091552734375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46318912506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33884811401367</t>
+    <t xml:space="preserve">9.46318817138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33884906768799</t>
   </si>
   <si>
     <t xml:space="preserve">8.57308673858643</t>
@@ -968,7 +968,7 @@
     <t xml:space="preserve">8.45128440856934</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61993312835693</t>
+    <t xml:space="preserve">8.61993408203125</t>
   </si>
   <si>
     <t xml:space="preserve">8.44191360473633</t>
@@ -977,22 +977,22 @@
     <t xml:space="preserve">8.32948112487793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25452423095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43254375457764</t>
+    <t xml:space="preserve">8.25452327728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43254470825195</t>
   </si>
   <si>
     <t xml:space="preserve">8.47002220153809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32011032104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20767784118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08587265014648</t>
+    <t xml:space="preserve">8.32011127471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20767688751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0858736038208</t>
   </si>
   <si>
     <t xml:space="preserve">7.78604936599731</t>
@@ -1001,13 +1001,13 @@
     <t xml:space="preserve">7.49559497833252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33631420135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23324918746948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83289670944214</t>
+    <t xml:space="preserve">7.33631372451782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23324871063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83289623260498</t>
   </si>
   <si>
     <t xml:space="preserve">7.90785217285156</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">7.12081527709961</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28009700775146</t>
+    <t xml:space="preserve">7.28009653091431</t>
   </si>
   <si>
     <t xml:space="preserve">6.98027276992798</t>
@@ -1043,7 +1043,7 @@
     <t xml:space="preserve">7.5424427986145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19830703735352</t>
+    <t xml:space="preserve">8.19830799102783</t>
   </si>
   <si>
     <t xml:space="preserve">8.2170467376709</t>
@@ -63643,7 +63643,7 @@
     </row>
     <row r="2348">
       <c r="A2348" s="1" t="n">
-        <v>46038.6911342593</v>
+        <v>46038.3333333333</v>
       </c>
       <c r="B2348" t="n">
         <v>65612</v>
@@ -63664,6 +63664,32 @@
         <v>756</v>
       </c>
       <c r="H2348" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2349">
+      <c r="A2349" s="1" t="n">
+        <v>46041.6910300926</v>
+      </c>
+      <c r="B2349" t="n">
+        <v>39077</v>
+      </c>
+      <c r="C2349" t="n">
+        <v>9.97999954223633</v>
+      </c>
+      <c r="D2349" t="n">
+        <v>9.73999977111816</v>
+      </c>
+      <c r="E2349" t="n">
+        <v>9.97999954223633</v>
+      </c>
+      <c r="F2349" t="n">
+        <v>9.84000015258789</v>
+      </c>
+      <c r="G2349" t="s">
+        <v>748</v>
+      </c>
+      <c r="H2349" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="757">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="758">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -50,46 +50,46 @@
     <t xml:space="preserve">9.08549880981445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24887180328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09457492828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12180423736572</t>
+    <t xml:space="preserve">9.24887371063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09457588195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12180328369141</t>
   </si>
   <si>
     <t xml:space="preserve">9.03103923797607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95388984680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89943218231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89489459991455</t>
+    <t xml:space="preserve">8.95389175415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89943313598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89489364624023</t>
   </si>
   <si>
     <t xml:space="preserve">8.84951114654541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85858821868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87673950195312</t>
+    <t xml:space="preserve">8.85858917236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87674045562744</t>
   </si>
   <si>
     <t xml:space="preserve">8.76782321929932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8676643371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04919147491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23072147369385</t>
+    <t xml:space="preserve">8.86766338348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04919242858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23072242736816</t>
   </si>
   <si>
     <t xml:space="preserve">9.11272811889648</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">8.91304588317871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92212200164795</t>
+    <t xml:space="preserve">8.92212295532227</t>
   </si>
   <si>
     <t xml:space="preserve">9.00381088256836</t>
@@ -110,61 +110,61 @@
     <t xml:space="preserve">9.15810966491699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16718578338623</t>
+    <t xml:space="preserve">9.16718673706055</t>
   </si>
   <si>
     <t xml:space="preserve">9.43947792053223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54839706420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62100601196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8025369644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71177291870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56654834747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58470153808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57562351226807</t>
+    <t xml:space="preserve">9.54839611053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62100696563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80253505706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71177196502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56654930114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58470058441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5756254196167</t>
   </si>
   <si>
     <t xml:space="preserve">9.53024196624756</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50301265716553</t>
+    <t xml:space="preserve">9.50301361083984</t>
   </si>
   <si>
     <t xml:space="preserve">9.60285377502441</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63915920257568</t>
+    <t xml:space="preserve">9.63916015625</t>
   </si>
   <si>
     <t xml:space="preserve">9.79346084594727</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95683574676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93868160247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98406410217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73899936676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76623058319092</t>
+    <t xml:space="preserve">9.95683479309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93868255615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98406505584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7390022277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7662296295166</t>
   </si>
   <si>
     <t xml:space="preserve">9.74807643890381</t>
@@ -173,37 +173,37 @@
     <t xml:space="preserve">9.75715351104736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64823532104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82068729400635</t>
+    <t xml:space="preserve">9.64823722839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82068920135498</t>
   </si>
   <si>
     <t xml:space="preserve">9.7026948928833</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72084808349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67546653747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66638946533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63008213043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65731334686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68454265594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81161308288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82976531982422</t>
+    <t xml:space="preserve">9.72084617614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67546558380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6663875579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63008308410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65731430053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68454170227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81161212921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8297643661499</t>
   </si>
   <si>
     <t xml:space="preserve">9.84791851043701</t>
@@ -218,37 +218,37 @@
     <t xml:space="preserve">9.78438282012939</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55747127532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34871482849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33963680267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27610301971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25794887542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19441604614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18533897399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4122486114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22164535522461</t>
+    <t xml:space="preserve">9.55747318267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34871387481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33963871002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27610397338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2579517364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19441509246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18533802032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41224956512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22164344787598</t>
   </si>
   <si>
     <t xml:space="preserve">9.31240940093994</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26702690124512</t>
+    <t xml:space="preserve">9.2670259475708</t>
   </si>
   <si>
     <t xml:space="preserve">9.29425525665283</t>
@@ -257,28 +257,28 @@
     <t xml:space="preserve">9.28517913818359</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37594318389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36686611175537</t>
+    <t xml:space="preserve">9.37594413757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.366868019104</t>
   </si>
   <si>
     <t xml:space="preserve">9.38501930236816</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45763111114502</t>
+    <t xml:space="preserve">9.45763206481934</t>
   </si>
   <si>
     <t xml:space="preserve">9.39409732818604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48486042022705</t>
+    <t xml:space="preserve">9.48486137390137</t>
   </si>
   <si>
     <t xml:space="preserve">9.49393653869629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44855403900146</t>
+    <t xml:space="preserve">9.44855499267578</t>
   </si>
   <si>
     <t xml:space="preserve">9.47578430175781</t>
@@ -299,73 +299,73 @@
     <t xml:space="preserve">9.13088035583496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13995552062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94027423858643</t>
+    <t xml:space="preserve">9.1399564743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94027614593506</t>
   </si>
   <si>
     <t xml:space="preserve">8.80412864685059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75874614715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66798305511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62260150909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53183746337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35030841827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16877937316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98725032806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03263378143311</t>
+    <t xml:space="preserve">8.75874710083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66798210144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62259960174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53183555603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35030937194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16878032684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98725128173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03263473510742</t>
   </si>
   <si>
     <t xml:space="preserve">8.12339782714844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25954341888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9418683052063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30492496490479</t>
+    <t xml:space="preserve">8.25954437255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94186878204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3049259185791</t>
   </si>
   <si>
     <t xml:space="preserve">8.21416282653809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39568996429443</t>
+    <t xml:space="preserve">8.39569091796875</t>
   </si>
   <si>
     <t xml:space="preserve">8.5772180557251</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71336650848389</t>
+    <t xml:space="preserve">8.71336460113525</t>
   </si>
   <si>
     <t xml:space="preserve">9.53202247619629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25706005096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44036865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16540622711182</t>
+    <t xml:space="preserve">9.25706100463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44036960601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16540718078613</t>
   </si>
   <si>
     <t xml:space="preserve">9.07375240325928</t>
@@ -386,28 +386,28 @@
     <t xml:space="preserve">9.80698490142822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89863967895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9902925491333</t>
+    <t xml:space="preserve">9.89863872528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99029350280762</t>
   </si>
   <si>
     <t xml:space="preserve">10.1736030578613</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2652549743652</t>
+    <t xml:space="preserve">10.2652559280396</t>
   </si>
   <si>
     <t xml:space="preserve">10.3569087982178</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5402164459229</t>
+    <t xml:space="preserve">10.5402183532715</t>
   </si>
   <si>
     <t xml:space="preserve">10.631872177124</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8151807785034</t>
+    <t xml:space="preserve">10.8151798248291</t>
   </si>
   <si>
     <t xml:space="preserve">10.7235260009766</t>
@@ -416,37 +416,37 @@
     <t xml:space="preserve">10.9068336486816</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9984874725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.090142250061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1817970275879</t>
+    <t xml:space="preserve">10.9984884262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0901432037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1817960739136</t>
   </si>
   <si>
     <t xml:space="preserve">11.2734498977661</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4567584991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3651027679443</t>
+    <t xml:space="preserve">11.4567575454712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3651037216187</t>
   </si>
   <si>
     <t xml:space="preserve">10.4485635757446</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71533107757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79879093170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24886608123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21123313903809</t>
+    <t xml:space="preserve">9.71533203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79879188537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24886703491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2112340927124</t>
   </si>
   <si>
     <t xml:space="preserve">9.30288791656494</t>
@@ -455,31 +455,31 @@
     <t xml:space="preserve">9.03709030151367</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3945426940918</t>
+    <t xml:space="preserve">9.39454174041748</t>
   </si>
   <si>
     <t xml:space="preserve">9.76115703582764</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6695032119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57784938812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0361194610596</t>
+    <t xml:space="preserve">9.66950416564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57785034179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0361204147339</t>
   </si>
   <si>
     <t xml:space="preserve">9.94446659088135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82552337646484</t>
+    <t xml:space="preserve">9.82552528381348</t>
   </si>
   <si>
     <t xml:space="preserve">9.73283100128174</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59379196166992</t>
+    <t xml:space="preserve">9.59378910064697</t>
   </si>
   <si>
     <t xml:space="preserve">9.96456527709961</t>
@@ -488,10 +488,10 @@
     <t xml:space="preserve">9.91821765899658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54744434356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0109100341797</t>
+    <t xml:space="preserve">9.54744338989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0109119415283</t>
   </si>
   <si>
     <t xml:space="preserve">10.1036052703857</t>
@@ -500,19 +500,19 @@
     <t xml:space="preserve">10.1499519348145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1962976455688</t>
+    <t xml:space="preserve">10.1962985992432</t>
   </si>
   <si>
     <t xml:space="preserve">9.77917766571045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87186908721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0572576522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2889928817749</t>
+    <t xml:space="preserve">9.87187004089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.057258605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2889938354492</t>
   </si>
   <si>
     <t xml:space="preserve">10.4743795394897</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">10.2426452636719</t>
   </si>
   <si>
-    <t xml:space="preserve">10.381685256958</t>
+    <t xml:space="preserve">10.3816862106323</t>
   </si>
   <si>
     <t xml:space="preserve">9.68648338317871</t>
@@ -542,13 +542,13 @@
     <t xml:space="preserve">9.1952075958252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25082302093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26936149597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21374607086182</t>
+    <t xml:space="preserve">9.25082206726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.269362449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2137451171875</t>
   </si>
   <si>
     <t xml:space="preserve">9.04689788818359</t>
@@ -560,10 +560,10 @@
     <t xml:space="preserve">9.0654354095459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97274208068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17666912078857</t>
+    <t xml:space="preserve">8.97274303436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17666816711426</t>
   </si>
   <si>
     <t xml:space="preserve">9.02835941314697</t>
@@ -575,19 +575,19 @@
     <t xml:space="preserve">8.71319961547852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99128246307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76881694793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89858818054199</t>
+    <t xml:space="preserve">8.99128150939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7688159942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89858913421631</t>
   </si>
   <si>
     <t xml:space="preserve">8.93566513061523</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3353395462036</t>
+    <t xml:space="preserve">10.3353385925293</t>
   </si>
   <si>
     <t xml:space="preserve">10.9841938018799</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">11.0305414199829</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2159280776978</t>
+    <t xml:space="preserve">11.2159290313721</t>
   </si>
   <si>
     <t xml:space="preserve">11.4940090179443</t>
@@ -605,19 +605,19 @@
     <t xml:space="preserve">11.540355682373</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5867033004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6330499649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7257432937622</t>
+    <t xml:space="preserve">11.5867023468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6330490112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7257423400879</t>
   </si>
   <si>
     <t xml:space="preserve">11.9111299514771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9574766159058</t>
+    <t xml:space="preserve">11.9574775695801</t>
   </si>
   <si>
     <t xml:space="preserve">12.1892108917236</t>
@@ -629,7 +629,7 @@
     <t xml:space="preserve">12.3745994567871</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5136384963989</t>
+    <t xml:space="preserve">12.5136394500732</t>
   </si>
   <si>
     <t xml:space="preserve">12.3282518386841</t>
@@ -638,28 +638,28 @@
     <t xml:space="preserve">12.1428651809692</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0965175628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.555121421814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5082740783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6488161087036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4614276885986</t>
+    <t xml:space="preserve">12.0965185165405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5551223754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5082750320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6488170623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4614267349243</t>
   </si>
   <si>
     <t xml:space="preserve">12.4145793914795</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7425117492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6956634521484</t>
+    <t xml:space="preserve">12.7425127029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6956644058228</t>
   </si>
   <si>
     <t xml:space="preserve">12.2271900177002</t>
@@ -668,10 +668,10 @@
     <t xml:space="preserve">12.1803426742554</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3208847045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2740383148193</t>
+    <t xml:space="preserve">12.3208837509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.274037361145</t>
   </si>
   <si>
     <t xml:space="preserve">12.8362064361572</t>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">12.6019687652588</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9299020767212</t>
+    <t xml:space="preserve">12.9299011230469</t>
   </si>
   <si>
     <t xml:space="preserve">12.8830537796021</t>
@@ -698,16 +698,16 @@
     <t xml:space="preserve">13.8668508529663</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0542402267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3353252410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5695638656616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2254285812378</t>
+    <t xml:space="preserve">14.0542411804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3353261947632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5695629119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2254276275635</t>
   </si>
   <si>
     <t xml:space="preserve">15.1317329406738</t>
@@ -716,58 +716,58 @@
     <t xml:space="preserve">14.7569532394409</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0380373001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.178581237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3191242218018</t>
+    <t xml:space="preserve">15.0380382537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1785802841187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3191232681274</t>
   </si>
   <si>
     <t xml:space="preserve">14.8974952697754</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4596662521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4128198623657</t>
+    <t xml:space="preserve">15.4596652984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4128179550171</t>
   </si>
   <si>
     <t xml:space="preserve">15.5533609390259</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0686817169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8650894165039</t>
+    <t xml:space="preserve">16.0686836242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8650913238525</t>
   </si>
   <si>
     <t xml:space="preserve">17.0056324005127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7713947296143</t>
+    <t xml:space="preserve">16.7713928222656</t>
   </si>
   <si>
     <t xml:space="preserve">17.193021774292</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0524787902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9587860107422</t>
+    <t xml:space="preserve">17.0524806976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9587841033936</t>
   </si>
   <si>
     <t xml:space="preserve">16.7245464324951</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6308517456055</t>
+    <t xml:space="preserve">16.6308498382568</t>
   </si>
   <si>
     <t xml:space="preserve">16.5371551513672</t>
   </si>
   <si>
-    <t xml:space="preserve">16.584005355835</t>
+    <t xml:space="preserve">16.5840034484863</t>
   </si>
   <si>
     <t xml:space="preserve">16.2092247009277</t>
@@ -779,31 +779,31 @@
     <t xml:space="preserve">17.1461734771729</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3966159820557</t>
+    <t xml:space="preserve">16.396614074707</t>
   </si>
   <si>
     <t xml:space="preserve">16.3029193878174</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8344440460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1155300140381</t>
+    <t xml:space="preserve">15.8344430923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1155319213867</t>
   </si>
   <si>
     <t xml:space="preserve">16.0218353271484</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1623764038086</t>
+    <t xml:space="preserve">16.1623783111572</t>
   </si>
   <si>
     <t xml:space="preserve">15.974986076355</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7407484054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4434623718262</t>
+    <t xml:space="preserve">15.7407493591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4434604644775</t>
   </si>
   <si>
     <t xml:space="preserve">16.9119358062744</t>
@@ -812,13 +812,13 @@
     <t xml:space="preserve">17.0993251800537</t>
   </si>
   <si>
-    <t xml:space="preserve">16.677698135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8182430267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2722749710083</t>
+    <t xml:space="preserve">16.6777000427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.818244934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.272274017334</t>
   </si>
   <si>
     <t xml:space="preserve">15.084885597229</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">14.991189956665</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8038005828857</t>
+    <t xml:space="preserve">14.8038015365601</t>
   </si>
   <si>
     <t xml:space="preserve">14.4758682250977</t>
@@ -836,22 +836,22 @@
     <t xml:space="preserve">14.382173538208</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1010885238647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2884788513184</t>
+    <t xml:space="preserve">14.1010875701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.288477897644</t>
   </si>
   <si>
     <t xml:space="preserve">14.5227155685425</t>
   </si>
   <si>
-    <t xml:space="preserve">13.960545539856</t>
+    <t xml:space="preserve">13.9605464935303</t>
   </si>
   <si>
     <t xml:space="preserve">14.2416305541992</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1947832107544</t>
+    <t xml:space="preserve">14.1947822570801</t>
   </si>
   <si>
     <t xml:space="preserve">14.0073928833008</t>
@@ -866,7 +866,7 @@
     <t xml:space="preserve">14.4290199279785</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6164112091064</t>
+    <t xml:space="preserve">14.6164102554321</t>
   </si>
   <si>
     <t xml:space="preserve">13.7731552124023</t>
@@ -875,10 +875,10 @@
     <t xml:space="preserve">13.3515281677246</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3046808242798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3983764648438</t>
+    <t xml:space="preserve">13.3046817779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3983774185181</t>
   </si>
   <si>
     <t xml:space="preserve">13.0235967636108</t>
@@ -890,7 +890,7 @@
     <t xml:space="preserve">12.976749420166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.367733001709</t>
+    <t xml:space="preserve">12.3677310943604</t>
   </si>
   <si>
     <t xml:space="preserve">12.0866470336914</t>
@@ -926,67 +926,67 @@
     <t xml:space="preserve">10.9623079299927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7280702590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1965456008911</t>
+    <t xml:space="preserve">10.7280712127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1965446472168</t>
   </si>
   <si>
     <t xml:space="preserve">11.571325302124</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3370876312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2902393341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7118682861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7587156295776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8055639266968</t>
+    <t xml:space="preserve">11.3370885848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2902402877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7118673324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7587146759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8055629730225</t>
   </si>
   <si>
     <t xml:space="preserve">11.0091552734375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46318817138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33884906768799</t>
+    <t xml:space="preserve">9.46318912506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3388500213623</t>
   </si>
   <si>
     <t xml:space="preserve">8.57308673858643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31074142456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45128440856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61993408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44191360473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32948112487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25452327728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43254470825195</t>
+    <t xml:space="preserve">8.31074237823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45128345489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61993503570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44191455841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32948017120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25452518463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43254566192627</t>
   </si>
   <si>
     <t xml:space="preserve">8.47002220153809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32011127471924</t>
+    <t xml:space="preserve">8.32011032104492</t>
   </si>
   <si>
     <t xml:space="preserve">8.20767688751221</t>
@@ -995,7 +995,7 @@
     <t xml:space="preserve">8.0858736038208</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78604936599731</t>
+    <t xml:space="preserve">7.78605031967163</t>
   </si>
   <si>
     <t xml:space="preserve">7.49559497833252</t>
@@ -1007,13 +1007,13 @@
     <t xml:space="preserve">7.23324871063232</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83289623260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90785217285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50496482849121</t>
+    <t xml:space="preserve">7.83289670944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90785264968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50496530532837</t>
   </si>
   <si>
     <t xml:space="preserve">7.37379169464111</t>
@@ -1025,16 +1025,16 @@
     <t xml:space="preserve">7.28009653091431</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98027276992798</t>
+    <t xml:space="preserve">6.98027324676514</t>
   </si>
   <si>
     <t xml:space="preserve">6.93342542648315</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06459856033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0271201133728</t>
+    <t xml:space="preserve">7.06459808349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02712059020996</t>
   </si>
   <si>
     <t xml:space="preserve">7.34568309783936</t>
@@ -1043,7 +1043,7 @@
     <t xml:space="preserve">7.5424427986145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19830799102783</t>
+    <t xml:space="preserve">8.19830703735352</t>
   </si>
   <si>
     <t xml:space="preserve">8.2170467376709</t>
@@ -1058,7 +1058,7 @@
     <t xml:space="preserve">8.53747367858887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68056106567383</t>
+    <t xml:space="preserve">8.68056201934814</t>
   </si>
   <si>
     <t xml:space="preserve">8.77595138549805</t>
@@ -1067,16 +1067,16 @@
     <t xml:space="preserve">8.84272575378418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72825527191162</t>
+    <t xml:space="preserve">8.72825622558594</t>
   </si>
   <si>
     <t xml:space="preserve">8.66148281097412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49931716918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42300605773926</t>
+    <t xml:space="preserve">8.49931812286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42300510406494</t>
   </si>
   <si>
     <t xml:space="preserve">8.39438915252686</t>
@@ -1091,22 +1091,22 @@
     <t xml:space="preserve">8.29899787902832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12729549407959</t>
+    <t xml:space="preserve">8.12729454040527</t>
   </si>
   <si>
     <t xml:space="preserve">7.89835643768311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10821628570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8411226272583</t>
+    <t xml:space="preserve">8.10821723937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84112215042114</t>
   </si>
   <si>
     <t xml:space="preserve">8.33715343475342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20360660552979</t>
+    <t xml:space="preserve">8.2036075592041</t>
   </si>
   <si>
     <t xml:space="preserve">8.06052017211914</t>
@@ -1118,22 +1118,22 @@
     <t xml:space="preserve">8.07005977630615</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92697334289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98420763015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30853652954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26084136962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2703800201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18452835083008</t>
+    <t xml:space="preserve">7.92697429656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98420810699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30853748321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26084041595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27038097381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18452930450439</t>
   </si>
   <si>
     <t xml:space="preserve">8.03190422058105</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">7.96512985229492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86019992828369</t>
+    <t xml:space="preserve">7.86020040512085</t>
   </si>
   <si>
     <t xml:space="preserve">7.86973905563354</t>
@@ -1151,7 +1151,7 @@
     <t xml:space="preserve">7.71711397171021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91743421554565</t>
+    <t xml:space="preserve">7.91743516921997</t>
   </si>
   <si>
     <t xml:space="preserve">7.76480960845947</t>
@@ -1166,19 +1166,19 @@
     <t xml:space="preserve">7.63126230239868</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65987968444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.165452003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32761478424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11775588989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93651247024536</t>
+    <t xml:space="preserve">7.65987920761108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16545009613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32761383056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11775493621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9365119934082</t>
   </si>
   <si>
     <t xml:space="preserve">8.19406795501709</t>
@@ -1190,13 +1190,13 @@
     <t xml:space="preserve">8.31807613372803</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15591144561768</t>
+    <t xml:space="preserve">8.15591239929199</t>
   </si>
   <si>
     <t xml:space="preserve">8.22268486022949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25130081176758</t>
+    <t xml:space="preserve">8.25130176544189</t>
   </si>
   <si>
     <t xml:space="preserve">8.35623264312744</t>
@@ -1208,7 +1208,7 @@
     <t xml:space="preserve">8.34669303894043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95559072494507</t>
+    <t xml:space="preserve">7.95559167861938</t>
   </si>
   <si>
     <t xml:space="preserve">7.77434825897217</t>
@@ -1226,31 +1226,31 @@
     <t xml:space="preserve">8.05098152160645</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67895793914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7361912727356</t>
+    <t xml:space="preserve">7.67895746231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73619222640991</t>
   </si>
   <si>
     <t xml:space="preserve">7.6980357170105</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51679372787476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59310579299927</t>
+    <t xml:space="preserve">7.5167932510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59310626983643</t>
   </si>
   <si>
     <t xml:space="preserve">7.44048070907593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53587198257446</t>
+    <t xml:space="preserve">7.5358715057373</t>
   </si>
   <si>
     <t xml:space="preserve">7.62172269821167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52633237838745</t>
+    <t xml:space="preserve">7.52633190155029</t>
   </si>
   <si>
     <t xml:space="preserve">7.34508991241455</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">7.20200395584106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1829252243042</t>
+    <t xml:space="preserve">7.18292617797852</t>
   </si>
   <si>
     <t xml:space="preserve">7.14476919174194</t>
@@ -1274,37 +1274,37 @@
     <t xml:space="preserve">7.1543083190918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24969911575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24016046524048</t>
+    <t xml:space="preserve">7.24969863891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24015998840332</t>
   </si>
   <si>
     <t xml:space="preserve">7.46909809112549</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41186380386353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45001935958862</t>
+    <t xml:space="preserve">7.41186332702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45001983642578</t>
   </si>
   <si>
     <t xml:space="preserve">7.28785514831543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39278554916382</t>
+    <t xml:space="preserve">7.39278507232666</t>
   </si>
   <si>
     <t xml:space="preserve">7.3355507850647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61218404769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90789604187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94605159759521</t>
+    <t xml:space="preserve">7.61218452453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90789556503296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94605112075806</t>
   </si>
   <si>
     <t xml:space="preserve">7.45955896377563</t>
@@ -1313,25 +1313,25 @@
     <t xml:space="preserve">7.70757484436035</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87927913665771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99374675750732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75527048110962</t>
+    <t xml:space="preserve">7.8792781829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99374723434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75527000427246</t>
   </si>
   <si>
     <t xml:space="preserve">7.81250429153442</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79342651367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80296611785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85066080093384</t>
+    <t xml:space="preserve">7.79342699050903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80296564102173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85066032409668</t>
   </si>
   <si>
     <t xml:space="preserve">7.74573087692261</t>
@@ -1343,25 +1343,25 @@
     <t xml:space="preserve">7.66941833496094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60264492034912</t>
+    <t xml:space="preserve">7.60264444351196</t>
   </si>
   <si>
     <t xml:space="preserve">7.58356666564941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88881826400757</t>
+    <t xml:space="preserve">7.88881778717041</t>
   </si>
   <si>
     <t xml:space="preserve">8.00328636169434</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78388738632202</t>
+    <t xml:space="preserve">7.78388690948486</t>
   </si>
   <si>
     <t xml:space="preserve">7.3641676902771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10661315917969</t>
+    <t xml:space="preserve">7.10661268234253</t>
   </si>
   <si>
     <t xml:space="preserve">7.27831649780273</t>
@@ -1376,10 +1376,10 @@
     <t xml:space="preserve">7.50372648239136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98721408843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02589225769043</t>
+    <t xml:space="preserve">7.98721361160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02589321136475</t>
   </si>
   <si>
     <t xml:space="preserve">8.04523086547852</t>
@@ -1391,25 +1391,25 @@
     <t xml:space="preserve">8.07424163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12258911132812</t>
+    <t xml:space="preserve">8.12259006500244</t>
   </si>
   <si>
     <t xml:space="preserve">8.05490112304688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94853496551514</t>
+    <t xml:space="preserve">7.94853448867798</t>
   </si>
   <si>
     <t xml:space="preserve">8.06457138061523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08390998840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97754430770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93886518478394</t>
+    <t xml:space="preserve">8.08391094207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97754383087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93886423110962</t>
   </si>
   <si>
     <t xml:space="preserve">7.79381895065308</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">7.68745088577271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63910293579102</t>
+    <t xml:space="preserve">7.63910245895386</t>
   </si>
   <si>
     <t xml:space="preserve">7.73579978942871</t>
@@ -1436,10 +1436,10 @@
     <t xml:space="preserve">7.90985584259033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85183668136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83249759674072</t>
+    <t xml:space="preserve">7.85183715820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83249807357788</t>
   </si>
   <si>
     <t xml:space="preserve">7.81315755844116</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">7.80348825454712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78414916992188</t>
+    <t xml:space="preserve">7.78414869308472</t>
   </si>
   <si>
     <t xml:space="preserve">7.6681113243103</t>
@@ -1460,13 +1460,13 @@
     <t xml:space="preserve">7.71646022796631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75513982772827</t>
+    <t xml:space="preserve">7.75514030456543</t>
   </si>
   <si>
     <t xml:space="preserve">7.74547004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86150693893433</t>
+    <t xml:space="preserve">7.86150646209717</t>
   </si>
   <si>
     <t xml:space="preserve">7.89051580429077</t>
@@ -1484,10 +1484,10 @@
     <t xml:space="preserve">8.09358024597168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13225936889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1515998840332</t>
+    <t xml:space="preserve">8.1322603225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15159893035889</t>
   </si>
   <si>
     <t xml:space="preserve">8.1129207611084</t>
@@ -1496,10 +1496,10 @@
     <t xml:space="preserve">8.03556251525879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92919492721558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69712066650391</t>
+    <t xml:space="preserve">7.92919540405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69712114334106</t>
   </si>
   <si>
     <t xml:space="preserve">7.60042381286621</t>
@@ -1508,10 +1508,10 @@
     <t xml:space="preserve">7.88084602355957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55207443237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40702819824219</t>
+    <t xml:space="preserve">7.55207490921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40702867507935</t>
   </si>
   <si>
     <t xml:space="preserve">7.34900999069214</t>
@@ -1520,16 +1520,16 @@
     <t xml:space="preserve">7.37801933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43603754043579</t>
+    <t xml:space="preserve">7.43603801727295</t>
   </si>
   <si>
     <t xml:space="preserve">7.41669797897339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52306604385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36834955215454</t>
+    <t xml:space="preserve">7.5230655670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36834907531738</t>
   </si>
   <si>
     <t xml:space="preserve">7.542405128479</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">7.4843864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70679044723511</t>
+    <t xml:space="preserve">7.70679092407227</t>
   </si>
   <si>
     <t xml:space="preserve">7.64877223968506</t>
@@ -1556,10 +1556,10 @@
     <t xml:space="preserve">7.59075355529785</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95820426940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96787405014038</t>
+    <t xml:space="preserve">7.95820331573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96787357330322</t>
   </si>
   <si>
     <t xml:space="preserve">7.90018606185913</t>
@@ -1577,10 +1577,10 @@
     <t xml:space="preserve">8.19027900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29664611816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45136165618896</t>
+    <t xml:space="preserve">8.29664516448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45136070251465</t>
   </si>
   <si>
     <t xml:space="preserve">8.48037147521973</t>
@@ -1607,19 +1607,19 @@
     <t xml:space="preserve">8.50938034057617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4223518371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54805946350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55772972106934</t>
+    <t xml:space="preserve">8.42235279083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54805850982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55772876739502</t>
   </si>
   <si>
     <t xml:space="preserve">8.52871990203857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68343448638916</t>
+    <t xml:space="preserve">8.68343544006348</t>
   </si>
   <si>
     <t xml:space="preserve">8.76079368591309</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">8.65442562103271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75112438201904</t>
+    <t xml:space="preserve">8.75112342834473</t>
   </si>
   <si>
     <t xml:space="preserve">8.70277500152588</t>
@@ -1652,10 +1652,10 @@
     <t xml:space="preserve">8.63508701324463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32565402984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31598472595215</t>
+    <t xml:space="preserve">8.32565498352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31598567962646</t>
   </si>
   <si>
     <t xml:space="preserve">8.30631542205811</t>
@@ -2283,6 +2283,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.85999965667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60000038146973</t>
   </si>
 </sst>
 </file>
@@ -63669,7 +63672,7 @@
     </row>
     <row r="2349">
       <c r="A2349" s="1" t="n">
-        <v>46041.6910300926</v>
+        <v>46041.3333333333</v>
       </c>
       <c r="B2349" t="n">
         <v>39077</v>
@@ -63690,6 +63693,32 @@
         <v>748</v>
       </c>
       <c r="H2349" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2350">
+      <c r="A2350" s="1" t="n">
+        <v>46042.6912847222</v>
+      </c>
+      <c r="B2350" t="n">
+        <v>28982</v>
+      </c>
+      <c r="C2350" t="n">
+        <v>9.84000015258789</v>
+      </c>
+      <c r="D2350" t="n">
+        <v>9.60000038146973</v>
+      </c>
+      <c r="E2350" t="n">
+        <v>9.84000015258789</v>
+      </c>
+      <c r="F2350" t="n">
+        <v>9.60000038146973</v>
+      </c>
+      <c r="G2350" t="s">
+        <v>757</v>
+      </c>
+      <c r="H2350" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">FF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98565673828125</t>
+    <t xml:space="preserve">8.98565769195557</t>
   </si>
   <si>
     <t xml:space="preserve">9.08549880981445</t>
@@ -56,28 +56,28 @@
     <t xml:space="preserve">9.09457588195801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12180328369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03103923797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95389175415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89943313598633</t>
+    <t xml:space="preserve">9.12180423736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03104019165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95388984680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89943218231201</t>
   </si>
   <si>
     <t xml:space="preserve">8.89489364624023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84951114654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85858917236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87674045562744</t>
+    <t xml:space="preserve">8.84951210021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85858726501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87673950195312</t>
   </si>
   <si>
     <t xml:space="preserve">8.76782321929932</t>
@@ -86,121 +86,121 @@
     <t xml:space="preserve">8.86766338348389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04919242858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23072242736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11272811889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96750450134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91304588317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92212295532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00381088256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15810966491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16718673706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43947792053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54839611053467</t>
+    <t xml:space="preserve">9.04919338226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23072147369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1127290725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96750354766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91304683685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92212390899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00380992889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15810871124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16718578338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43947887420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54839515686035</t>
   </si>
   <si>
     <t xml:space="preserve">9.62100696563721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80253505706787</t>
+    <t xml:space="preserve">9.80253601074219</t>
   </si>
   <si>
     <t xml:space="preserve">9.71177196502686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56654930114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58470058441162</t>
+    <t xml:space="preserve">9.56654834747314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58470249176025</t>
   </si>
   <si>
     <t xml:space="preserve">9.5756254196167</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53024196624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50301361083984</t>
+    <t xml:space="preserve">9.53024291992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50301456451416</t>
   </si>
   <si>
     <t xml:space="preserve">9.60285377502441</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63916015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79346084594727</t>
+    <t xml:space="preserve">9.63915920257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79345893859863</t>
   </si>
   <si>
     <t xml:space="preserve">9.95683479309082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93868255615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98406505584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7390022277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7662296295166</t>
+    <t xml:space="preserve">9.93868160247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98406410217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73899936676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76623058319092</t>
   </si>
   <si>
     <t xml:space="preserve">9.74807643890381</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75715351104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64823722839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82068920135498</t>
+    <t xml:space="preserve">9.75715255737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64823627471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82068729400635</t>
   </si>
   <si>
     <t xml:space="preserve">9.7026948928833</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72084617614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67546558380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6663875579834</t>
+    <t xml:space="preserve">9.72084712982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67546653747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66638946533203</t>
   </si>
   <si>
     <t xml:space="preserve">9.63008308410645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65731430053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68454170227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81161212921143</t>
+    <t xml:space="preserve">9.65731239318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68454265594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81161308288574</t>
   </si>
   <si>
     <t xml:space="preserve">9.8297643661499</t>
@@ -215,34 +215,34 @@
     <t xml:space="preserve">9.72992420196533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78438282012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55747318267822</t>
+    <t xml:space="preserve">9.78438377380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55747222900391</t>
   </si>
   <si>
     <t xml:space="preserve">9.34871387481689</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33963871002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27610397338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2579517364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19441509246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18533802032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41224956512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22164344787598</t>
+    <t xml:space="preserve">9.33963775634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27610206604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25794982910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19441604614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18533992767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4122486114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22164440155029</t>
   </si>
   <si>
     <t xml:space="preserve">9.31240940093994</t>
@@ -260,61 +260,61 @@
     <t xml:space="preserve">9.37594413757324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.366868019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38501930236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45763206481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39409732818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48486137390137</t>
+    <t xml:space="preserve">9.36686706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38502216339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45763111114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39409637451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48486042022705</t>
   </si>
   <si>
     <t xml:space="preserve">9.49393653869629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44855499267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47578430175781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23979759216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14903259277344</t>
+    <t xml:space="preserve">9.44855403900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4757833480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2397985458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14903163909912</t>
   </si>
   <si>
     <t xml:space="preserve">9.21256828308105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20349216461182</t>
+    <t xml:space="preserve">9.2034912109375</t>
   </si>
   <si>
     <t xml:space="preserve">9.13088035583496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1399564743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94027614593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80412864685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75874710083008</t>
+    <t xml:space="preserve">9.13995552062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94027519226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8041296005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75874614715576</t>
   </si>
   <si>
     <t xml:space="preserve">8.66798210144043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62259960174561</t>
+    <t xml:space="preserve">8.62260055541992</t>
   </si>
   <si>
     <t xml:space="preserve">8.53183555603027</t>
@@ -323,22 +323,22 @@
     <t xml:space="preserve">8.35030937194824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16878032684326</t>
+    <t xml:space="preserve">8.16877841949463</t>
   </si>
   <si>
     <t xml:space="preserve">7.98725128173828</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03263473510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12339782714844</t>
+    <t xml:space="preserve">8.03263378143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12339687347412</t>
   </si>
   <si>
     <t xml:space="preserve">8.25954437255859</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94186878204346</t>
+    <t xml:space="preserve">7.9418683052063</t>
   </si>
   <si>
     <t xml:space="preserve">8.3049259185791</t>
@@ -347,22 +347,22 @@
     <t xml:space="preserve">8.21416282653809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39569091796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5772180557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71336460113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53202247619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25706100463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44036960601807</t>
+    <t xml:space="preserve">8.39568901062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57721900939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71336555480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53202342987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25706005096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44036865234375</t>
   </si>
   <si>
     <t xml:space="preserve">9.16540718078613</t>
@@ -371,7 +371,7 @@
     <t xml:space="preserve">9.07375240325928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11958026885986</t>
+    <t xml:space="preserve">9.11957931518555</t>
   </si>
   <si>
     <t xml:space="preserve">8.98209857940674</t>
@@ -380,7 +380,7 @@
     <t xml:space="preserve">9.02792549133301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62367820739746</t>
+    <t xml:space="preserve">9.62367725372314</t>
   </si>
   <si>
     <t xml:space="preserve">9.80698490142822</t>
@@ -389,10 +389,10 @@
     <t xml:space="preserve">9.89863872528076</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99029350280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1736030578613</t>
+    <t xml:space="preserve">9.9902925491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.173602104187</t>
   </si>
   <si>
     <t xml:space="preserve">10.2652559280396</t>
@@ -404,49 +404,49 @@
     <t xml:space="preserve">10.5402183532715</t>
   </si>
   <si>
-    <t xml:space="preserve">10.631872177124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8151798248291</t>
+    <t xml:space="preserve">10.6318712234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8151807785034</t>
   </si>
   <si>
     <t xml:space="preserve">10.7235260009766</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9068336486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9984884262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0901432037354</t>
+    <t xml:space="preserve">10.9068326950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9984874725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.090142250061</t>
   </si>
   <si>
     <t xml:space="preserve">11.1817960739136</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734498977661</t>
+    <t xml:space="preserve">11.2734508514404</t>
   </si>
   <si>
     <t xml:space="preserve">11.4567575454712</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3651037216187</t>
+    <t xml:space="preserve">11.3651027679443</t>
   </si>
   <si>
     <t xml:space="preserve">10.4485635757446</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71533203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79879188537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24886703491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2112340927124</t>
+    <t xml:space="preserve">9.71533107757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79878997802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24886512756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21123313903809</t>
   </si>
   <si>
     <t xml:space="preserve">9.30288791656494</t>
@@ -458,31 +458,31 @@
     <t xml:space="preserve">9.39454174041748</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76115703582764</t>
+    <t xml:space="preserve">9.76115798950195</t>
   </si>
   <si>
     <t xml:space="preserve">9.66950416564941</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57785034179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0361204147339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94446659088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82552528381348</t>
+    <t xml:space="preserve">9.57784938812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0361194610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94446754455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82552337646484</t>
   </si>
   <si>
     <t xml:space="preserve">9.73283100128174</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59378910064697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96456527709961</t>
+    <t xml:space="preserve">9.59379005432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96456432342529</t>
   </si>
   <si>
     <t xml:space="preserve">9.91821765899658</t>
@@ -491,28 +491,28 @@
     <t xml:space="preserve">9.54744338989258</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0109119415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1036052703857</t>
+    <t xml:space="preserve">10.010910987854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1036043167114</t>
   </si>
   <si>
     <t xml:space="preserve">10.1499519348145</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1962985992432</t>
+    <t xml:space="preserve">10.1962976455688</t>
   </si>
   <si>
     <t xml:space="preserve">9.77917766571045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87187004089355</t>
+    <t xml:space="preserve">9.87187099456787</t>
   </si>
   <si>
     <t xml:space="preserve">10.057258605957</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2889938354492</t>
+    <t xml:space="preserve">10.2889928817749</t>
   </si>
   <si>
     <t xml:space="preserve">10.4743795394897</t>
@@ -521,19 +521,19 @@
     <t xml:space="preserve">10.2426452636719</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3816862106323</t>
+    <t xml:space="preserve">10.381685256958</t>
   </si>
   <si>
     <t xml:space="preserve">9.68648338317871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64013576507568</t>
+    <t xml:space="preserve">9.64013671875</t>
   </si>
   <si>
     <t xml:space="preserve">9.50109577178955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31570911407471</t>
+    <t xml:space="preserve">9.31570816040039</t>
   </si>
   <si>
     <t xml:space="preserve">9.23228454589844</t>
@@ -542,16 +542,16 @@
     <t xml:space="preserve">9.1952075958252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25082206726074</t>
+    <t xml:space="preserve">9.25082302093506</t>
   </si>
   <si>
     <t xml:space="preserve">9.269362449646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2137451171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04689788818359</t>
+    <t xml:space="preserve">9.21374607086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04689693450928</t>
   </si>
   <si>
     <t xml:space="preserve">9.12105274200439</t>
@@ -560,13 +560,13 @@
     <t xml:space="preserve">9.0654354095459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97274303436279</t>
+    <t xml:space="preserve">8.97274398803711</t>
   </si>
   <si>
     <t xml:space="preserve">9.17666816711426</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02835941314697</t>
+    <t xml:space="preserve">9.02835845947266</t>
   </si>
   <si>
     <t xml:space="preserve">8.95420360565186</t>
@@ -575,40 +575,40 @@
     <t xml:space="preserve">8.71319961547852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99128150939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7688159942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89858913421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93566513061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3353385925293</t>
+    <t xml:space="preserve">8.99128246307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76881694793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89858722686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93566608428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3353395462036</t>
   </si>
   <si>
     <t xml:space="preserve">10.9841938018799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0305414199829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2159290313721</t>
+    <t xml:space="preserve">11.0305404663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2159280776978</t>
   </si>
   <si>
     <t xml:space="preserve">11.4940090179443</t>
   </si>
   <si>
-    <t xml:space="preserve">11.540355682373</t>
+    <t xml:space="preserve">11.5403566360474</t>
   </si>
   <si>
     <t xml:space="preserve">11.5867023468018</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6330490112305</t>
+    <t xml:space="preserve">11.6330499649048</t>
   </si>
   <si>
     <t xml:space="preserve">11.7257423400879</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">11.9111299514771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9574775695801</t>
+    <t xml:space="preserve">11.9574766159058</t>
   </si>
   <si>
     <t xml:space="preserve">12.1892108917236</t>
@@ -626,19 +626,19 @@
     <t xml:space="preserve">12.2819051742554</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3745994567871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5136394500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3282518386841</t>
+    <t xml:space="preserve">12.3745985031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5136384963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3282527923584</t>
   </si>
   <si>
     <t xml:space="preserve">12.1428651809692</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0965185165405</t>
+    <t xml:space="preserve">12.0965175628662</t>
   </si>
   <si>
     <t xml:space="preserve">12.5551223754883</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">12.6488170623779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4614267349243</t>
+    <t xml:space="preserve">12.4614276885986</t>
   </si>
   <si>
     <t xml:space="preserve">12.4145793914795</t>
@@ -662,7 +662,7 @@
     <t xml:space="preserve">12.6956644058228</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2271900177002</t>
+    <t xml:space="preserve">12.2271890640259</t>
   </si>
   <si>
     <t xml:space="preserve">12.1803426742554</t>
@@ -671,19 +671,19 @@
     <t xml:space="preserve">12.3208837509155</t>
   </si>
   <si>
-    <t xml:space="preserve">12.274037361145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8362064361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7893581390381</t>
+    <t xml:space="preserve">12.2740383148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8362073898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7893590927124</t>
   </si>
   <si>
     <t xml:space="preserve">12.6019687652588</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9299011230469</t>
+    <t xml:space="preserve">12.9299020767212</t>
   </si>
   <si>
     <t xml:space="preserve">12.8830537796021</t>
@@ -692,16 +692,16 @@
     <t xml:space="preserve">13.0704441070557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.679461479187</t>
+    <t xml:space="preserve">13.6794605255127</t>
   </si>
   <si>
     <t xml:space="preserve">13.8668508529663</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0542411804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3353261947632</t>
+    <t xml:space="preserve">14.0542402267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3353252410889</t>
   </si>
   <si>
     <t xml:space="preserve">14.5695629119873</t>
@@ -722,10 +722,10 @@
     <t xml:space="preserve">15.1785802841187</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3191232681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8974952697754</t>
+    <t xml:space="preserve">15.3191242218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8974943161011</t>
   </si>
   <si>
     <t xml:space="preserve">15.4596652984619</t>
@@ -740,19 +740,19 @@
     <t xml:space="preserve">16.0686836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8650913238525</t>
+    <t xml:space="preserve">16.8650875091553</t>
   </si>
   <si>
     <t xml:space="preserve">17.0056324005127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7713928222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.193021774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0524806976318</t>
+    <t xml:space="preserve">16.7713947296143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1930236816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0524787902832</t>
   </si>
   <si>
     <t xml:space="preserve">16.9587841033936</t>
@@ -761,19 +761,19 @@
     <t xml:space="preserve">16.7245464324951</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6308498382568</t>
+    <t xml:space="preserve">16.6308536529541</t>
   </si>
   <si>
     <t xml:space="preserve">16.5371551513672</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5840034484863</t>
+    <t xml:space="preserve">16.584005355835</t>
   </si>
   <si>
     <t xml:space="preserve">16.2092247009277</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2560729980469</t>
+    <t xml:space="preserve">16.2560749053955</t>
   </si>
   <si>
     <t xml:space="preserve">17.1461734771729</t>
@@ -782,37 +782,37 @@
     <t xml:space="preserve">16.396614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3029193878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8344430923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1155319213867</t>
+    <t xml:space="preserve">16.3029174804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8344440460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1155300140381</t>
   </si>
   <si>
     <t xml:space="preserve">16.0218353271484</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1623783111572</t>
+    <t xml:space="preserve">16.1623764038086</t>
   </si>
   <si>
     <t xml:space="preserve">15.974986076355</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7407493591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4434604644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9119358062744</t>
+    <t xml:space="preserve">15.7407503128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4434623718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9119338989258</t>
   </si>
   <si>
     <t xml:space="preserve">17.0993251800537</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6777000427246</t>
+    <t xml:space="preserve">16.677698135376</t>
   </si>
   <si>
     <t xml:space="preserve">16.818244934082</t>
@@ -821,13 +821,13 @@
     <t xml:space="preserve">15.272274017334</t>
   </si>
   <si>
-    <t xml:space="preserve">15.084885597229</t>
+    <t xml:space="preserve">15.0848846435547</t>
   </si>
   <si>
     <t xml:space="preserve">14.991189956665</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8038015365601</t>
+    <t xml:space="preserve">14.8037996292114</t>
   </si>
   <si>
     <t xml:space="preserve">14.4758682250977</t>
@@ -836,22 +836,22 @@
     <t xml:space="preserve">14.382173538208</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1010875701904</t>
+    <t xml:space="preserve">14.1010885238647</t>
   </si>
   <si>
     <t xml:space="preserve">14.288477897644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5227155685425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9605464935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2416305541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1947822570801</t>
+    <t xml:space="preserve">14.5227146148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9605445861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2416296005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1947832107544</t>
   </si>
   <si>
     <t xml:space="preserve">14.0073928833008</t>
@@ -872,127 +872,127 @@
     <t xml:space="preserve">13.7731552124023</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3515281677246</t>
+    <t xml:space="preserve">13.3515291213989</t>
   </si>
   <si>
     <t xml:space="preserve">13.3046817779541</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3983774185181</t>
+    <t xml:space="preserve">13.3983764648438</t>
   </si>
   <si>
     <t xml:space="preserve">13.0235967636108</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1172914505005</t>
+    <t xml:space="preserve">13.1172924041748</t>
   </si>
   <si>
     <t xml:space="preserve">12.976749420166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3677310943604</t>
+    <t xml:space="preserve">12.3677320480347</t>
   </si>
   <si>
     <t xml:space="preserve">12.0866470336914</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9929523468018</t>
+    <t xml:space="preserve">11.9929533004761</t>
   </si>
   <si>
     <t xml:space="preserve">11.8992576599121</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0397996902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1334943771362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4776296615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2433938980103</t>
+    <t xml:space="preserve">12.0397987365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1334934234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4776287078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2433929443359</t>
   </si>
   <si>
     <t xml:space="preserve">11.3839340209961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6650199890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4307823181152</t>
+    <t xml:space="preserve">11.6650190353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4307832717896</t>
   </si>
   <si>
     <t xml:space="preserve">10.9623079299927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7280712127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1965446472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.571325302124</t>
+    <t xml:space="preserve">10.7280702590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1965436935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5713243484497</t>
   </si>
   <si>
     <t xml:space="preserve">11.3370885848999</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2902402877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7118673324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7587146759033</t>
+    <t xml:space="preserve">11.2902393341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7118682861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.758713722229</t>
   </si>
   <si>
     <t xml:space="preserve">11.8055629730225</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0091552734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46318912506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3388500213623</t>
+    <t xml:space="preserve">11.0091543197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46319007873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33884906768799</t>
   </si>
   <si>
     <t xml:space="preserve">8.57308673858643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31074237823486</t>
+    <t xml:space="preserve">8.31074142456055</t>
   </si>
   <si>
     <t xml:space="preserve">8.45128345489502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61993503570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44191455841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32948017120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25452518463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43254566192627</t>
+    <t xml:space="preserve">8.61993408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44191360473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32948112487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25452423095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43254375457764</t>
   </si>
   <si>
     <t xml:space="preserve">8.47002220153809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32011032104492</t>
+    <t xml:space="preserve">8.32011127471924</t>
   </si>
   <si>
     <t xml:space="preserve">8.20767688751221</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0858736038208</t>
+    <t xml:space="preserve">8.08587265014648</t>
   </si>
   <si>
     <t xml:space="preserve">7.78605031967163</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">7.49559497833252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33631372451782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23324871063232</t>
+    <t xml:space="preserve">7.33631420135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23324918746948</t>
   </si>
   <si>
     <t xml:space="preserve">7.83289670944214</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90785264968872</t>
+    <t xml:space="preserve">7.90785217285156</t>
   </si>
   <si>
     <t xml:space="preserve">7.50496530532837</t>
@@ -1019,28 +1019,28 @@
     <t xml:space="preserve">7.37379169464111</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12081527709961</t>
+    <t xml:space="preserve">7.12081480026245</t>
   </si>
   <si>
     <t xml:space="preserve">7.28009653091431</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98027324676514</t>
+    <t xml:space="preserve">6.98027229309082</t>
   </si>
   <si>
     <t xml:space="preserve">6.93342542648315</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06459808349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02712059020996</t>
+    <t xml:space="preserve">7.06459856033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0271201133728</t>
   </si>
   <si>
     <t xml:space="preserve">7.34568309783936</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5424427986145</t>
+    <t xml:space="preserve">7.54244232177734</t>
   </si>
   <si>
     <t xml:space="preserve">8.19830703735352</t>
@@ -1055,19 +1055,19 @@
     <t xml:space="preserve">8.46116256713867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53747367858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68056201934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77595138549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84272575378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825622558594</t>
+    <t xml:space="preserve">8.53747463226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68056106567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77595233917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8427267074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825527191162</t>
   </si>
   <si>
     <t xml:space="preserve">8.66148281097412</t>
@@ -1082,10 +1082,10 @@
     <t xml:space="preserve">8.39438915252686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60424900054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48977851867676</t>
+    <t xml:space="preserve">8.604248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48977947235107</t>
   </si>
   <si>
     <t xml:space="preserve">8.29899787902832</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">7.89835643768311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10821723937988</t>
+    <t xml:space="preserve">8.10821628570557</t>
   </si>
   <si>
     <t xml:space="preserve">7.84112215042114</t>
@@ -1115,34 +1115,34 @@
     <t xml:space="preserve">8.07959938049316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07005977630615</t>
+    <t xml:space="preserve">8.07005882263184</t>
   </si>
   <si>
     <t xml:space="preserve">7.92697429656982</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98420810699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30853748321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26084041595459</t>
+    <t xml:space="preserve">7.98420858383179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30853652954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26084136962891</t>
   </si>
   <si>
     <t xml:space="preserve">8.27038097381592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18452930450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03190422058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96512985229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86020040512085</t>
+    <t xml:space="preserve">8.18452835083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03190326690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96513080596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86019992828369</t>
   </si>
   <si>
     <t xml:space="preserve">7.86973905563354</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">7.91743516921997</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76480960845947</t>
+    <t xml:space="preserve">7.76481008529663</t>
   </si>
   <si>
     <t xml:space="preserve">7.72665309906006</t>
@@ -1166,19 +1166,19 @@
     <t xml:space="preserve">7.63126230239868</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65987920761108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16545009613037</t>
+    <t xml:space="preserve">7.65987968444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16545104980469</t>
   </si>
   <si>
     <t xml:space="preserve">8.32761383056641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11775493621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9365119934082</t>
+    <t xml:space="preserve">8.11775588989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93651247024536</t>
   </si>
   <si>
     <t xml:space="preserve">8.19406795501709</t>
@@ -1187,10 +1187,10 @@
     <t xml:space="preserve">8.2322244644165</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31807613372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15591239929199</t>
+    <t xml:space="preserve">8.31807518005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15591144561768</t>
   </si>
   <si>
     <t xml:space="preserve">8.22268486022949</t>
@@ -1199,10 +1199,10 @@
     <t xml:space="preserve">8.25130176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35623264312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2417631149292</t>
+    <t xml:space="preserve">8.35623168945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24176406860352</t>
   </si>
   <si>
     <t xml:space="preserve">8.34669303894043</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">7.97466850280762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01282501220703</t>
+    <t xml:space="preserve">8.01282596588135</t>
   </si>
   <si>
     <t xml:space="preserve">8.05098152160645</t>
@@ -1229,13 +1229,13 @@
     <t xml:space="preserve">7.67895746231079</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73619222640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6980357170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5167932510376</t>
+    <t xml:space="preserve">7.73619174957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69803524017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51679372787476</t>
   </si>
   <si>
     <t xml:space="preserve">7.59310626983643</t>
@@ -1259,16 +1259,16 @@
     <t xml:space="preserve">7.20200395584106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18292617797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14476919174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12569093704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23062086105347</t>
+    <t xml:space="preserve">7.18292570114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14476871490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12569046020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23062133789062</t>
   </si>
   <si>
     <t xml:space="preserve">7.1543083190918</t>
@@ -1277,7 +1277,7 @@
     <t xml:space="preserve">7.24969863891602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24015998840332</t>
+    <t xml:space="preserve">7.24016046524048</t>
   </si>
   <si>
     <t xml:space="preserve">7.46909809112549</t>
@@ -1298,13 +1298,13 @@
     <t xml:space="preserve">7.3355507850647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61218452453613</t>
+    <t xml:space="preserve">7.61218404769897</t>
   </si>
   <si>
     <t xml:space="preserve">7.90789556503296</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94605112075806</t>
+    <t xml:space="preserve">7.94605159759521</t>
   </si>
   <si>
     <t xml:space="preserve">7.45955896377563</t>
@@ -1316,22 +1316,22 @@
     <t xml:space="preserve">7.8792781829834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99374723434448</t>
+    <t xml:space="preserve">7.99374771118164</t>
   </si>
   <si>
     <t xml:space="preserve">7.75527000427246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81250429153442</t>
+    <t xml:space="preserve">7.81250381469727</t>
   </si>
   <si>
     <t xml:space="preserve">7.79342699050903</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80296564102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85066032409668</t>
+    <t xml:space="preserve">7.80296611785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85065984725952</t>
   </si>
   <si>
     <t xml:space="preserve">7.74573087692261</t>
@@ -1340,22 +1340,22 @@
     <t xml:space="preserve">7.83158302307129</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66941833496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60264444351196</t>
+    <t xml:space="preserve">7.66941785812378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60264492034912</t>
   </si>
   <si>
     <t xml:space="preserve">7.58356666564941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88881778717041</t>
+    <t xml:space="preserve">7.88881826400757</t>
   </si>
   <si>
     <t xml:space="preserve">8.00328636169434</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78388690948486</t>
+    <t xml:space="preserve">7.78388738632202</t>
   </si>
   <si>
     <t xml:space="preserve">7.3641676902771</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">7.27831649780273</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08753442764282</t>
+    <t xml:space="preserve">7.08753490447998</t>
   </si>
   <si>
     <t xml:space="preserve">7.05891799926758</t>
@@ -1376,10 +1376,10 @@
     <t xml:space="preserve">7.50372648239136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98721361160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02589321136475</t>
+    <t xml:space="preserve">7.98721408843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02589225769043</t>
   </si>
   <si>
     <t xml:space="preserve">8.04523086547852</t>
@@ -1391,25 +1391,25 @@
     <t xml:space="preserve">8.07424163818359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12259006500244</t>
+    <t xml:space="preserve">8.12258911132812</t>
   </si>
   <si>
     <t xml:space="preserve">8.05490112304688</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94853448867798</t>
+    <t xml:space="preserve">7.94853496551514</t>
   </si>
   <si>
     <t xml:space="preserve">8.06457138061523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08391094207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97754383087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93886423110962</t>
+    <t xml:space="preserve">8.08390998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97754430770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93886518478394</t>
   </si>
   <si>
     <t xml:space="preserve">7.79381895065308</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">7.68745088577271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63910245895386</t>
+    <t xml:space="preserve">7.63910293579102</t>
   </si>
   <si>
     <t xml:space="preserve">7.73579978942871</t>
@@ -1436,10 +1436,10 @@
     <t xml:space="preserve">7.90985584259033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85183715820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83249807357788</t>
+    <t xml:space="preserve">7.85183668136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83249759674072</t>
   </si>
   <si>
     <t xml:space="preserve">7.81315755844116</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">7.80348825454712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78414869308472</t>
+    <t xml:space="preserve">7.78414916992188</t>
   </si>
   <si>
     <t xml:space="preserve">7.6681113243103</t>
@@ -1460,13 +1460,13 @@
     <t xml:space="preserve">7.71646022796631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75514030456543</t>
+    <t xml:space="preserve">7.75513982772827</t>
   </si>
   <si>
     <t xml:space="preserve">7.74547004699707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86150646209717</t>
+    <t xml:space="preserve">7.86150693893433</t>
   </si>
   <si>
     <t xml:space="preserve">7.89051580429077</t>
@@ -1484,10 +1484,10 @@
     <t xml:space="preserve">8.09358024597168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1322603225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15159893035889</t>
+    <t xml:space="preserve">8.13225936889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1515998840332</t>
   </si>
   <si>
     <t xml:space="preserve">8.1129207611084</t>
@@ -1496,10 +1496,10 @@
     <t xml:space="preserve">8.03556251525879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92919540405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69712114334106</t>
+    <t xml:space="preserve">7.92919492721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69712066650391</t>
   </si>
   <si>
     <t xml:space="preserve">7.60042381286621</t>
@@ -1508,10 +1508,10 @@
     <t xml:space="preserve">7.88084602355957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55207490921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40702867507935</t>
+    <t xml:space="preserve">7.55207443237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40702819824219</t>
   </si>
   <si>
     <t xml:space="preserve">7.34900999069214</t>
@@ -1520,16 +1520,16 @@
     <t xml:space="preserve">7.37801933288574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43603801727295</t>
+    <t xml:space="preserve">7.43603754043579</t>
   </si>
   <si>
     <t xml:space="preserve">7.41669797897339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5230655670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36834907531738</t>
+    <t xml:space="preserve">7.52306604385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36834955215454</t>
   </si>
   <si>
     <t xml:space="preserve">7.542405128479</t>
@@ -1538,7 +1538,7 @@
     <t xml:space="preserve">7.4843864440918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70679092407227</t>
+    <t xml:space="preserve">7.70679044723511</t>
   </si>
   <si>
     <t xml:space="preserve">7.64877223968506</t>
@@ -1556,10 +1556,10 @@
     <t xml:space="preserve">7.59075355529785</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95820331573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96787357330322</t>
+    <t xml:space="preserve">7.95820426940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96787405014038</t>
   </si>
   <si>
     <t xml:space="preserve">7.90018606185913</t>
@@ -1577,10 +1577,10 @@
     <t xml:space="preserve">8.19027900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29664516448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45136070251465</t>
+    <t xml:space="preserve">8.29664611816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45136165618896</t>
   </si>
   <si>
     <t xml:space="preserve">8.48037147521973</t>
@@ -1607,19 +1607,19 @@
     <t xml:space="preserve">8.50938034057617</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42235279083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54805850982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55772876739502</t>
+    <t xml:space="preserve">8.4223518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54805946350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55772972106934</t>
   </si>
   <si>
     <t xml:space="preserve">8.52871990203857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68343544006348</t>
+    <t xml:space="preserve">8.68343448638916</t>
   </si>
   <si>
     <t xml:space="preserve">8.76079368591309</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">8.65442562103271</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75112342834473</t>
+    <t xml:space="preserve">8.75112438201904</t>
   </si>
   <si>
     <t xml:space="preserve">8.70277500152588</t>
@@ -1652,10 +1652,10 @@
     <t xml:space="preserve">8.63508701324463</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32565498352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31598567962646</t>
+    <t xml:space="preserve">8.32565402984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31598472595215</t>
   </si>
   <si>
     <t xml:space="preserve">8.30631542205811</t>
@@ -63698,7 +63698,7 @@
     </row>
     <row r="2350">
       <c r="A2350" s="1" t="n">
-        <v>46042.6912847222</v>
+        <v>46042.3333333333</v>
       </c>
       <c r="B2350" t="n">
         <v>28982</v>
@@ -63719,6 +63719,32 @@
         <v>757</v>
       </c>
       <c r="H2350" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2351">
+      <c r="A2351" s="1" t="n">
+        <v>46043.6909837963</v>
+      </c>
+      <c r="B2351" t="n">
+        <v>25725</v>
+      </c>
+      <c r="C2351" t="n">
+        <v>9.60000038146973</v>
+      </c>
+      <c r="D2351" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E2351" t="n">
+        <v>9.60000038146973</v>
+      </c>
+      <c r="F2351" t="n">
+        <v>9.60000038146973</v>
+      </c>
+      <c r="G2351" t="s">
+        <v>757</v>
+      </c>
+      <c r="H2351" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FF.MI.xlsx
+++ b/data/FF.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="758" uniqueCount="758">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="759">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0764217376709</t>
+    <t xml:space="preserve">9.07642269134521</t>
   </si>
   <si>
     <t xml:space="preserve">FF.MI</t>
@@ -47,25 +47,25 @@
     <t xml:space="preserve">8.98565769195557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08549880981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24887371063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09457588195801</t>
+    <t xml:space="preserve">9.08549785614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24887275695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09457492828369</t>
   </si>
   <si>
     <t xml:space="preserve">9.12180423736572</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03104019165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95388984680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89943218231201</t>
+    <t xml:space="preserve">9.03103923797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95389175415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8994312286377</t>
   </si>
   <si>
     <t xml:space="preserve">8.89489364624023</t>
@@ -77,13 +77,13 @@
     <t xml:space="preserve">8.85858726501465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87673950195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76782321929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86766338348389</t>
+    <t xml:space="preserve">8.87674045562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.767822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8676643371582</t>
   </si>
   <si>
     <t xml:space="preserve">9.04919338226318</t>
@@ -92,34 +92,34 @@
     <t xml:space="preserve">9.23072147369385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1127290725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96750354766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91304683685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92212390899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00380992889404</t>
+    <t xml:space="preserve">9.11272716522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96750450134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91304588317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92212295532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00381088256836</t>
   </si>
   <si>
     <t xml:space="preserve">9.15810871124268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16718578338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43947887420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54839515686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62100696563721</t>
+    <t xml:space="preserve">9.16718769073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43947792053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54839706420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62100887298584</t>
   </si>
   <si>
     <t xml:space="preserve">9.80253601074219</t>
@@ -128,10 +128,10 @@
     <t xml:space="preserve">9.71177196502686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56654834747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58470249176025</t>
+    <t xml:space="preserve">9.56654739379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58470153808594</t>
   </si>
   <si>
     <t xml:space="preserve">9.5756254196167</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">9.50301456451416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60285377502441</t>
+    <t xml:space="preserve">9.60285472869873</t>
   </si>
   <si>
     <t xml:space="preserve">9.63915920257568</t>
@@ -155,37 +155,37 @@
     <t xml:space="preserve">9.95683479309082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93868160247803</t>
+    <t xml:space="preserve">9.93868255615234</t>
   </si>
   <si>
     <t xml:space="preserve">9.98406410217285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73899936676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76623058319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74807643890381</t>
+    <t xml:space="preserve">9.73900127410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7662296295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74807739257812</t>
   </si>
   <si>
     <t xml:space="preserve">9.75715255737305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64823627471924</t>
+    <t xml:space="preserve">9.64823818206787</t>
   </si>
   <si>
     <t xml:space="preserve">9.82068729400635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7026948928833</t>
+    <t xml:space="preserve">9.70269298553467</t>
   </si>
   <si>
     <t xml:space="preserve">9.72084712982178</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67546653747559</t>
+    <t xml:space="preserve">9.67546558380127</t>
   </si>
   <si>
     <t xml:space="preserve">9.66638946533203</t>
@@ -194,34 +194,34 @@
     <t xml:space="preserve">9.63008308410645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65731239318848</t>
+    <t xml:space="preserve">9.65731143951416</t>
   </si>
   <si>
     <t xml:space="preserve">9.68454265594482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81161308288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8297643661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84791851043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83884143829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72992420196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78438377380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55747222900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34871387481689</t>
+    <t xml:space="preserve">9.81161403656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82976531982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8479175567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83884239196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72992324829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78438186645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55747413635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34871482849121</t>
   </si>
   <si>
     <t xml:space="preserve">9.33963775634766</t>
@@ -230,28 +230,28 @@
     <t xml:space="preserve">9.27610206604004</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25794982910156</t>
+    <t xml:space="preserve">9.25795078277588</t>
   </si>
   <si>
     <t xml:space="preserve">9.19441604614258</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18533992767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4122486114502</t>
+    <t xml:space="preserve">9.18533802032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41224956512451</t>
   </si>
   <si>
     <t xml:space="preserve">9.22164440155029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31240940093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2670259475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29425525665283</t>
+    <t xml:space="preserve">9.31240749359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26702785491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29425716400146</t>
   </si>
   <si>
     <t xml:space="preserve">9.28517913818359</t>
@@ -263,16 +263,16 @@
     <t xml:space="preserve">9.36686706542969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38502216339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45763111114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39409637451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48486042022705</t>
+    <t xml:space="preserve">9.3850212097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45763301849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39409732818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48486137390137</t>
   </si>
   <si>
     <t xml:space="preserve">9.49393653869629</t>
@@ -284,49 +284,49 @@
     <t xml:space="preserve">9.4757833480835</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2397985458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14903163909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21256828308105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2034912109375</t>
+    <t xml:space="preserve">9.23979759216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14903354644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21256732940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20349311828613</t>
   </si>
   <si>
     <t xml:space="preserve">9.13088035583496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13995552062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94027519226074</t>
+    <t xml:space="preserve">9.13995742797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94027614593506</t>
   </si>
   <si>
     <t xml:space="preserve">8.8041296005249</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75874614715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66798210144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62260055541992</t>
+    <t xml:space="preserve">8.75874710083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66798400878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62260246276855</t>
   </si>
   <si>
     <t xml:space="preserve">8.53183555603027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35030937194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16877841949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98725128173828</t>
+    <t xml:space="preserve">8.35030841827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16878032684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98725032806396</t>
   </si>
   <si>
     <t xml:space="preserve">8.03263378143311</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">8.3049259185791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21416282653809</t>
+    <t xml:space="preserve">8.21416187286377</t>
   </si>
   <si>
     <t xml:space="preserve">8.39568901062012</t>
@@ -353,25 +353,25 @@
     <t xml:space="preserve">8.57721900939941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71336555480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53202342987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25706005096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44036865234375</t>
+    <t xml:space="preserve">8.71336650848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53202247619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25706100463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44036960601807</t>
   </si>
   <si>
     <t xml:space="preserve">9.16540718078613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07375240325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11957931518555</t>
+    <t xml:space="preserve">9.07375144958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11958026885986</t>
   </si>
   <si>
     <t xml:space="preserve">8.98209857940674</t>
@@ -383,13 +383,13 @@
     <t xml:space="preserve">9.62367725372314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80698490142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89863872528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9902925491333</t>
+    <t xml:space="preserve">9.80698585510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89863967895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99029445648193</t>
   </si>
   <si>
     <t xml:space="preserve">10.173602104187</t>
@@ -398,25 +398,25 @@
     <t xml:space="preserve">10.2652559280396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3569087982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5402183532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6318712234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8151807785034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7235260009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9068326950073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9984874725342</t>
+    <t xml:space="preserve">10.3569107055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5402173995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.631872177124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8151798248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7235250473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9068336486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9984884262085</t>
   </si>
   <si>
     <t xml:space="preserve">11.090142250061</t>
@@ -425,13 +425,13 @@
     <t xml:space="preserve">11.1817960739136</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2734508514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4567575454712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3651027679443</t>
+    <t xml:space="preserve">11.2734498977661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4567594528198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3651037216187</t>
   </si>
   <si>
     <t xml:space="preserve">10.4485635757446</t>
@@ -440,28 +440,28 @@
     <t xml:space="preserve">9.71533107757568</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79878997802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24886512756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21123313903809</t>
+    <t xml:space="preserve">8.79879093170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24886703491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2112340927124</t>
   </si>
   <si>
     <t xml:space="preserve">9.30288791656494</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03709030151367</t>
+    <t xml:space="preserve">9.03708934783936</t>
   </si>
   <si>
     <t xml:space="preserve">9.39454174041748</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76115798950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66950416564941</t>
+    <t xml:space="preserve">9.76115703582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6695032119751</t>
   </si>
   <si>
     <t xml:space="preserve">9.57784938812256</t>
@@ -470,16 +470,16 @@
     <t xml:space="preserve">10.0361194610596</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94446754455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82552337646484</t>
+    <t xml:space="preserve">9.94446659088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82552528381348</t>
   </si>
   <si>
     <t xml:space="preserve">9.73283100128174</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59379005432129</t>
+    <t xml:space="preserve">9.59378910064697</t>
   </si>
   <si>
     <t xml:space="preserve">9.96456432342529</t>
@@ -491,25 +491,25 @@
     <t xml:space="preserve">9.54744338989258</t>
   </si>
   <si>
-    <t xml:space="preserve">10.010910987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1036043167114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1499519348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1962976455688</t>
+    <t xml:space="preserve">10.0109119415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1036052703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1499509811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1962985992432</t>
   </si>
   <si>
     <t xml:space="preserve">9.77917766571045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87187099456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.057258605957</t>
+    <t xml:space="preserve">9.87187004089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0572576522827</t>
   </si>
   <si>
     <t xml:space="preserve">10.2889928817749</t>
@@ -518,22 +518,22 @@
     <t xml:space="preserve">10.4743795394897</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2426452636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.381685256958</t>
+    <t xml:space="preserve">10.2426443099976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3816862106323</t>
   </si>
   <si>
     <t xml:space="preserve">9.68648338317871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64013671875</t>
+    <t xml:space="preserve">9.64013576507568</t>
   </si>
   <si>
     <t xml:space="preserve">9.50109577178955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31570816040039</t>
+    <t xml:space="preserve">9.31570911407471</t>
   </si>
   <si>
     <t xml:space="preserve">9.23228454589844</t>
@@ -545,70 +545,70 @@
     <t xml:space="preserve">9.25082302093506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.269362449646</t>
+    <t xml:space="preserve">9.26936340332031</t>
   </si>
   <si>
     <t xml:space="preserve">9.21374607086182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04689693450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12105274200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0654354095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97274398803711</t>
+    <t xml:space="preserve">9.04689788818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12105369567871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06543636322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97274303436279</t>
   </si>
   <si>
     <t xml:space="preserve">9.17666816711426</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02835845947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95420360565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71319961547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99128246307373</t>
+    <t xml:space="preserve">9.02835941314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95420455932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71320056915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99128150939941</t>
   </si>
   <si>
     <t xml:space="preserve">8.76881694793701</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89858722686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93566608428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3353395462036</t>
+    <t xml:space="preserve">8.89858913421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93566513061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3353385925293</t>
   </si>
   <si>
     <t xml:space="preserve">10.9841938018799</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0305404663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2159280776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4940090179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5403566360474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5867023468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6330499649048</t>
+    <t xml:space="preserve">11.0305414199829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2159290313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4940099716187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.540355682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5867033004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6330490112305</t>
   </si>
   <si>
     <t xml:space="preserve">11.7257423400879</t>
@@ -626,13 +626,13 @@
     <t xml:space="preserve">12.2819051742554</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3745985031128</t>
+    <t xml:space="preserve">12.3745994567871</t>
   </si>
   <si>
     <t xml:space="preserve">12.5136384963989</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3282527923584</t>
+    <t xml:space="preserve">12.3282518386841</t>
   </si>
   <si>
     <t xml:space="preserve">12.1428651809692</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">12.6488170623779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4614276885986</t>
+    <t xml:space="preserve">12.4614267349243</t>
   </si>
   <si>
     <t xml:space="preserve">12.4145793914795</t>
@@ -662,7 +662,7 @@
     <t xml:space="preserve">12.6956644058228</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2271890640259</t>
+    <t xml:space="preserve">12.2271900177002</t>
   </si>
   <si>
     <t xml:space="preserve">12.1803426742554</t>
@@ -671,19 +671,19 @@
     <t xml:space="preserve">12.3208837509155</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2740383148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8362073898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7893590927124</t>
+    <t xml:space="preserve">12.274037361145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8362064361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7893581390381</t>
   </si>
   <si>
     <t xml:space="preserve">12.6019687652588</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9299020767212</t>
+    <t xml:space="preserve">12.9299011230469</t>
   </si>
   <si>
     <t xml:space="preserve">12.8830537796021</t>
@@ -692,16 +692,16 @@
     <t xml:space="preserve">13.0704441070557</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6794605255127</t>
+    <t xml:space="preserve">13.679461479187</t>
   </si>
   <si>
     <t xml:space="preserve">13.8668508529663</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0542402267456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3353252410889</t>
+    <t xml:space="preserve">14.0542411804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3353261947632</t>
   </si>
   <si>
     <t xml:space="preserve">14.5695629119873</t>
@@ -722,10 +722,10 @@
     <t xml:space="preserve">15.1785802841187</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3191242218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8974943161011</t>
+    <t xml:space="preserve">15.3191232681274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8974952697754</t>
   </si>
   <si>
     <t xml:space="preserve">15.4596652984619</t>
@@ -740,19 +740,19 @@
     <t xml:space="preserve">16.0686836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8650875091553</t>
+    <t xml:space="preserve">16.8650913238525</t>
   </si>
   <si>
     <t xml:space="preserve">17.0056324005127</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7713947296143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1930236816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0524787902832</t>
+    <t xml:space="preserve">16.7713928222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.193021774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0524806976318</t>
   </si>
   <si>
     <t xml:space="preserve">16.9587841033936</t>
@@ -761,19 +761,19 @@
     <t xml:space="preserve">16.7245464324951</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6308536529541</t>
+    <t xml:space="preserve">16.6308498382568</t>
   </si>
   <si>
     <t xml:space="preserve">16.5371551513672</t>
   </si>
   <si>
-    <t xml:space="preserve">16.584005355835</t>
+    <t xml:space="preserve">16.5840034484863</t>
   </si>
   <si>
     <t xml:space="preserve">16.2092247009277</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2560749053955</t>
+    <t xml:space="preserve">16.2560729980469</t>
   </si>
   <si>
     <t xml:space="preserve">17.1461734771729</t>
@@ -782,37 +782,37 @@
     <t xml:space="preserve">16.396614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3029174804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8344440460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1155300140381</t>
+    <t xml:space="preserve">16.3029193878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8344430923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1155319213867</t>
   </si>
   <si>
     <t xml:space="preserve">16.0218353271484</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1623764038086</t>
+    <t xml:space="preserve">16.1623783111572</t>
   </si>
   <si>
     <t xml:space="preserve">15.974986076355</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7407503128052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4434623718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9119338989258</t>
+    <t xml:space="preserve">15.7407493591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4434604644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9119358062744</t>
   </si>
   <si>
     <t xml:space="preserve">17.0993251800537</t>
   </si>
   <si>
-    <t xml:space="preserve">16.677698135376</t>
+    <t xml:space="preserve">16.6777000427246</t>
   </si>
   <si>
     <t xml:space="preserve">16.818244934082</t>
@@ -821,13 +821,13 @@
     <t xml:space="preserve">15.272274017334</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0848846435547</t>
+    <t xml:space="preserve">15.084885597229</t>
   </si>
   <si>
     <t xml:space="preserve">14.991189956665</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8037996292114</t>
+    <t xml:space="preserve">14.8038015365601</t>
   </si>
   <si>
     <t xml:space="preserve">14.4758682250977</t>
@@ -836,22 +836,22 @@
     <t xml:space="preserve">14.382173538208</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1010885238647</t>
+    <t xml:space="preserve">14.1010875701904</t>
   </si>
   <si>
     <t xml:space="preserve">14.288477897644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5227146148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9605445861816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2416296005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1947832107544</t>
+    <t xml:space="preserve">14.5227155685425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9605464935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2416305541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1947822570801</t>
   </si>
   <si>
     <t xml:space="preserve">14.0073928833008</t>
@@ -872,127 +872,127 @@
     <t xml:space="preserve">13.7731552124023</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3515291213989</t>
+    <t xml:space="preserve">13.3515281677246</t>
   </si>
   <si>
     <t xml:space="preserve">13.3046817779541</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3983764648438</t>
+    <t xml:space="preserve">13.3983774185181</t>
   </si>
   <si>
     <t xml:space="preserve">13.0235967636108</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1172924041748</t>
+    <t xml:space="preserve">13.1172914505005</t>
   </si>
   <si>
     <t xml:space="preserve">12.976749420166</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3677320480347</t>
+    <t xml:space="preserve">12.3677310943604</t>
   </si>
   <si>
     <t xml:space="preserve">12.0866470336914</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9929533004761</t>
+    <t xml:space="preserve">11.9929523468018</t>
   </si>
   <si>
     <t xml:space="preserve">11.8992576599121</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0397987365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1334934234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4776287078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2433929443359</t>
+    <t xml:space="preserve">12.0397996902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1334943771362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4776296615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2433938980103</t>
   </si>
   <si>
     <t xml:space="preserve">11.3839340209961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6650190353394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4307832717896</t>
+    <t xml:space="preserve">11.6650199890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4307823181152</t>
   </si>
   <si>
     <t xml:space="preserve">10.9623079299927</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7280702590942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1965436935425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5713243484497</t>
+    <t xml:space="preserve">10.7280712127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1965446472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.571325302124</t>
   </si>
   <si>
     <t xml:space="preserve">11.3370885848999</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2902393341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7118682861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.758713722229</t>
+    <t xml:space="preserve">11.2902402877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7118673324585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7587146759033</t>
   </si>
   <si>
     <t xml:space="preserve">11.8055629730225</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0091543197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46319007873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33884906768799</t>
+    <t xml:space="preserve">11.0091552734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46318912506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3388500213623</t>
   </si>
   <si>
     <t xml:space="preserve">8.57308673858643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31074142456055</t>
+    <t xml:space="preserve">8.31074237823486</t>
   </si>
   <si>
     <t xml:space="preserve">8.45128345489502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61993408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44191360473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32948112487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25452423095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43254375457764</t>
+    <t xml:space="preserve">8.61993503570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44191455841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32948017120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25452518463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43254566192627</t>
   </si>
   <si>
     <t xml:space="preserve">8.47002220153809</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32011127471924</t>
+    <t xml:space="preserve">8.32011032104492</t>
   </si>
   <si>
     <t xml:space="preserve">8.20767688751221</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08587265014648</t>
+    <t xml:space="preserve">8.0858736038208</t>
   </si>
   <si>
     <t xml:space="preserve">7.78605031967163</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">7.49559497833252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33631420135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23324918746948</t>
+    <t xml:space="preserve">7.33631372451782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23324871063232</t>
   </si>
   <si>
     <t xml:space="preserve">7.83289670944214</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90785217285156</t>
+    <t xml:space="preserve">7.90785264968872</t>
   </si>
   <si>
     <t xml:space="preserve">7.50496530532837</t>
@@ -1019,28 +1019,28 @@
     <t xml:space="preserve">7.37379169464111</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12081480026245</t>
+    <t xml:space="preserve">7.12081527709961</t>
   </si>
   <si>
     <t xml:space="preserve">7.28009653091431</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98027229309082</t>
+    <t xml:space="preserve">6.98027324676514</t>
   </si>
   <si>
     <t xml:space="preserve">6.93342542648315</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06459856033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0271201133728</t>
+    <t xml:space="preserve">7.06459808349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02712059020996</t>
   </si>
   <si>
     <t xml:space="preserve">7.34568309783936</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54244232177734</t>
+    <t xml:space="preserve">7.5424427986145</t>
   </si>
   <si>
     <t xml:space="preserve">8.19830703735352</t>
@@ -1055,19 +1055,19 @@
     <t xml:space="preserve">8.46116256713867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53747463226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68056106567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77595233917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8427267074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72825527191162</t>
+    <t xml:space="preserve">8.53747367858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68056201934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77595138549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84272575378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72825622558594</t>
   </si>
   <si>
     <t xml:space="preserve">8.66148281097412</t>
@@ -1082,10 +1082,10 @@
     <t xml:space="preserve">8.39438915252686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.604248046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48977947235107</t>
+    <t xml:space="preserve">8.60424900054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48977851867676</t>
   </si>
   <si>
     <t xml:space="preserve">8.29899787902832</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">7.89835643768311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10821628570557</t>
+    <t xml:space="preserve">8.10821723937988</t>
   </si>
   <si>
     <t xml:space="preserve">7.84112215042114</t>
@@ -1115,34 +1115,34 @@
     <t xml:space="preserve">8.07959938049316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07005882263184</t>
+    <t xml:space="preserve">8.07005977630615</t>
   </si>
   <si>
     <t xml:space="preserve">7.92697429656982</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98420858383179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30853652954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26084136962891</t>
+    <t xml:space="preserve">7.98420810699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30853748321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26084041595459</t>
   </si>
   <si>
     <t xml:space="preserve">8.27038097381592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18452835083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03190326690674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96513080596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86019992828369</t>
+    <t xml:space="preserve">8.18452930450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03190422058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96512985229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86020040512085</t>
   </si>
   <si>
     <t xml:space="preserve">7.86973905563354</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">7.91743516921997</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76481008529663</t>
+    <t xml:space="preserve">7.76480960845947</t>
   </si>
   <si>
     <t xml:space="preserve">7.72665309906006</t>
@@ -1166,19 +1166,19 @@
     <t xml:space="preserve">7.63126230239868</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65987968444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16545104980469</t>
+    <t xml:space="preserve">7.65987920761108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16545009613037</t>
   </si>
   <si>
     <t xml:space="preserve">8.32761383056641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11775588989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93651247024536</t>
+    <t xml:space="preserve">8.11775493621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9365119934082</t>
   </si>
   <si>
     <t xml:space="preserve">8.19406795501709</t>
@@ -1187,10 +1187,10 @@
     <t xml:space="preserve">8.2322244644165</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31807518005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15591144561768</t>
+    <t xml:space="preserve">8.31807613372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15591239929199</t>
   </si>
   <si>
     <t xml:space="preserve">8.22268486022949</t>
@@ -1199,10 +1199,10 @@
     <t xml:space="preserve">8.25130176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35623168945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24176406860352</t>
+    <t xml:space="preserve">8.35623264312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2417631149292</t>
   </si>
   <si>
     <t xml:space="preserve">8.34669303894043</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">7.97466850280762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01282596588135</t>
+    <t xml:space="preserve">8.01282501220703</t>
   </si>
   <si>
     <t xml:space="preserve">8.05098152160645</t>
@@ -1229,13 +1229,13 @@
     <t xml:space="preserve">7.67895746231079</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73619174957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69803524017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51679372787476</t>
+    <t xml:space="preserve">7.73619222640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6980357170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5167932510376</t>
   </si>
   <si>
     <t xml:space="preserve">7.59310626983643</t>
@@ -